--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -11,9 +11,9 @@
     <sheet name="Settings" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$N$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$N$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">Weeks!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Body weight'!$A$1:$D$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5">Settings!$A$1:$B$40</definedName>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J15"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -522,39 +522,39 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Grip Trainer</v>
+        <v>Desk Bands</v>
       </c>
       <c r="B4" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-09-28</v>
-      </c>
-      <c r="F4">
-        <v>200</v>
-      </c>
-      <c r="G4">
-        <v>200</v>
-      </c>
-      <c r="H4">
-        <v>200</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>300</v>
+        <v>2026-09-29</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Hip Thrust</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="B5" t="str">
         <v>Strength</v>
@@ -569,24 +569,24 @@
         <v>2026-09-28</v>
       </c>
       <c r="F5">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="G5">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="H5">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="B6" t="str">
         <v>Strength</v>
@@ -601,30 +601,30 @@
         <v>2026-09-28</v>
       </c>
       <c r="F6">
-        <v>180</v>
+        <v>320</v>
       </c>
       <c r="G6">
-        <v>180</v>
+        <v>320</v>
       </c>
       <c r="H6">
-        <v>180</v>
+        <v>320</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Lat Pulldown, alternating single-arm</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="B7" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="str">
         <v>2026-09-28</v>
@@ -633,56 +633,56 @@
         <v>2026-09-28</v>
       </c>
       <c r="F7">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="G7">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="H7">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>90</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Leg Extension ISO hold</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="B8" t="str">
         <v>Isometric</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="F8">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G8">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H8">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J8">
-        <v>80</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Kneeling Cable Ab Crunch</v>
       </c>
       <c r="B9" t="str">
         <v>Strength</v>
@@ -691,33 +691,33 @@
         <v>1</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="F9">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="G9">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H9">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Lat Pulldown, alternating single-arm</v>
       </c>
       <c r="B10" t="str">
-        <v>Isometric</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -729,32 +729,192 @@
         <v>2026-09-28</v>
       </c>
       <c r="F10">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G10">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H10">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Leg Extension ISO hold</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Isometric</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="E11" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="F11">
+        <v>50</v>
+      </c>
+      <c r="G11">
+        <v>60</v>
+      </c>
+      <c r="H11">
+        <v>60</v>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+      <c r="J11">
         <v>80</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Seated Zercher Good Morning</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="E12" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="F12">
+        <v>50</v>
+      </c>
+      <c r="G12">
+        <v>50</v>
+      </c>
+      <c r="H12">
+        <v>50</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Side Rear Delt Fly</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Isometric</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="E13" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="F13">
+        <v>50</v>
+      </c>
+      <c r="G13">
+        <v>50</v>
+      </c>
+      <c r="H13">
+        <v>50</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Suitcase Bottom-Up, single-arm</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="E14" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="F14">
+        <v>25</v>
+      </c>
+      <c r="G14">
+        <v>25</v>
+      </c>
+      <c r="H14">
+        <v>25</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Zottman Curl</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Hypertrophy</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="E15" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="F15">
+        <v>20</v>
+      </c>
+      <c r="G15">
+        <v>20</v>
+      </c>
+      <c r="H15">
+        <v>20</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J10"/>
+  <autoFilter ref="A1:J15"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J15"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N21"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -1388,17 +1548,325 @@
         <v>A-d3s6</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Desk Bands</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Isometric</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15">
+        <v>4</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15">
+        <v>30</v>
+      </c>
+      <c r="I15" t="str">
+        <v>BW×30s, BW×30s, BW×30s, BW×30s</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v>Mobility</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v>A-d3s9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Kettlebell Leg Raise</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Isometric</v>
+      </c>
+      <c r="E16">
+        <v>20</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16">
+        <v>15</v>
+      </c>
+      <c r="I16" t="str">
+        <v>20×15s, 20×15s, 20×15s</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v>Abs, Hip flexors</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v>A-d1s7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Kettlebell Leg Raise</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Isometric</v>
+      </c>
+      <c r="E17">
+        <v>15</v>
+      </c>
+      <c r="F17">
+        <v>3</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17">
+        <v>15</v>
+      </c>
+      <c r="I17" t="str">
+        <v>15×15s, 15×15s, 15×15s</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v>Abs, Hip flexors</v>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v>A-d1s7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Kneeling Cable Ab Crunch</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E18">
+        <v>85</v>
+      </c>
+      <c r="F18">
+        <v>4</v>
+      </c>
+      <c r="G18">
+        <v>6</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>85×6, 85×6, 85×6, 85×6</v>
+      </c>
+      <c r="J18">
+        <v>2040</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Abs</v>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v>From check-off</v>
+      </c>
+      <c r="N18" t="str">
+        <v>A-d2s4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Leg Extension ISO hold</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Isometric</v>
+      </c>
+      <c r="E19">
+        <v>60</v>
+      </c>
+      <c r="F19">
+        <v>4</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19">
+        <v>30</v>
+      </c>
+      <c r="I19" t="str">
+        <v>60×30s, 60×30s, 60×30s, 60×30s</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v>Quads</v>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v>From check-off</v>
+      </c>
+      <c r="N19" t="str">
+        <v>A-d3s5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Suitcase Bottom-Up, single-arm</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E20">
+        <v>25</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20">
+        <v>6</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>25×6, 25×6, 25×6, 25×6</v>
+      </c>
+      <c r="J20">
+        <v>600</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Forearms &amp; grip, Obliques</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Traps</v>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v>A-d4s1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Zottman Curl</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Hypertrophy</v>
+      </c>
+      <c r="E21">
+        <v>20</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21">
+        <v>15</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>20×15, 20×15, 20×15</v>
+      </c>
+      <c r="J21">
+        <v>900</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Biceps, Forearms &amp; grip</v>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v>From check-off</v>
+      </c>
+      <c r="N21" t="str">
+        <v>A-d1s7</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N14"/>
+  <autoFilter ref="A1:N21"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N21"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E18"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -1429,16 +1897,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B2" t="str">
-        <v>Rear delts</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -1446,13 +1914,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B3" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Rear delts</v>
       </c>
       <c r="C3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>12</v>
@@ -1480,16 +1948,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B5" t="str">
-        <v>Lats</v>
+        <v>Abs</v>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -1497,7 +1965,7 @@
         <v>2026-09-27</v>
       </c>
       <c r="B6" t="str">
-        <v>Chest</v>
+        <v>Lats</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -1514,16 +1982,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B7" t="str">
-        <v>Glutes</v>
+        <v>Chest</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1531,16 +1999,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B8" t="str">
-        <v>Biceps</v>
+        <v>Quads</v>
       </c>
       <c r="C8">
+        <v>8</v>
+      </c>
+      <c r="D8">
         <v>0</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>8</v>
-      </c>
-      <c r="E8">
-        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1548,16 +2016,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B9" t="str">
-        <v>Inner thigh (adductors)</v>
+        <v>Biceps</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -1565,16 +2033,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B10" t="str">
-        <v>Front delts</v>
+        <v>Glutes</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1582,16 +2050,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B11" t="str">
-        <v>Triceps</v>
+        <v>Hip flexors</v>
       </c>
       <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11">
         <v>0</v>
       </c>
-      <c r="D11">
-        <v>8</v>
-      </c>
       <c r="E11">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -1599,13 +2067,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B12" t="str">
-        <v>Lower back</v>
+        <v>Hamstrings</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>4</v>
@@ -1616,13 +2084,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B13" t="str">
-        <v>Hamstrings</v>
+        <v>Inner thigh (adductors)</v>
       </c>
       <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13">
         <v>0</v>
-      </c>
-      <c r="D13">
-        <v>8</v>
       </c>
       <c r="E13">
         <v>4</v>
@@ -1633,7 +2101,7 @@
         <v>2026-09-27</v>
       </c>
       <c r="B14" t="str">
-        <v>Quads</v>
+        <v>Lower back</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -1645,10 +2113,78 @@
         <v>4</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Front delts</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>8</v>
+      </c>
+      <c r="E15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Triceps</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>8</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Obliques</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Traps</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E14"/>
+  <autoFilter ref="A1:E18"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E18"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1704,19 +2240,19 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H2">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2098,7 +2634,7 @@
         <v>Exported</v>
       </c>
       <c r="B40" t="str">
-        <v>2026-09-28T18:54:54.308Z</v>
+        <v>2026-09-29T15:54:15.150Z</v>
       </c>
     </row>
   </sheetData>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -11,9 +11,9 @@
     <sheet name="Settings" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$N$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$N$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">Weeks!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Body weight'!$A$1:$D$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5">Settings!$A$1:$B$40</definedName>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J17"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -458,39 +458,39 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Cable Wrist Pulldown</v>
+        <v>Arnold Press</v>
       </c>
       <c r="B2" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-30</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-01</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J2">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Chest Press</v>
+        <v>Cable Wrist Pulldown</v>
       </c>
       <c r="B3" t="str">
         <v>Hypertrophy</v>
@@ -505,88 +505,88 @@
         <v>2026-09-28</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H3">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Desk Bands</v>
+        <v>Chest Press</v>
       </c>
       <c r="B4" t="str">
-        <v>Isometric</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-09-29</v>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4" t="str">
-        <v/>
+        <v>2026-09-30</v>
+      </c>
+      <c r="F4">
+        <v>25</v>
+      </c>
+      <c r="G4">
+        <v>25</v>
+      </c>
+      <c r="H4">
+        <v>25</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Grip Trainer</v>
+        <v>Desk Bands</v>
       </c>
       <c r="B5" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-09-28</v>
-      </c>
-      <c r="F5">
-        <v>200</v>
-      </c>
-      <c r="G5">
-        <v>200</v>
-      </c>
-      <c r="H5">
-        <v>200</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>300</v>
+        <v>2026-09-29</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Hip Thrust</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="B6" t="str">
         <v>Strength</v>
@@ -601,190 +601,190 @@
         <v>2026-09-28</v>
       </c>
       <c r="F6">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="G6">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="H6">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Hack Squat</v>
       </c>
       <c r="B7" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-30</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-01</v>
       </c>
       <c r="F7">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="G7">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="H7">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="B8" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-30</v>
       </c>
       <c r="F8">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="G8">
-        <v>15</v>
+        <v>320</v>
       </c>
       <c r="H8">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="I8">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>30</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Kneeling Cable Ab Crunch</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="B9" t="str">
         <v>Strength</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-30</v>
       </c>
       <c r="F9">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="G9">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="H9">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Lat Pulldown, alternating single-arm</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="B10" t="str">
-        <v>Hypertrophy</v>
+        <v>Isometric</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="F10">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G10">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="H10">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J10">
-        <v>90</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Leg Extension ISO hold</v>
+        <v>Kneeling Cable Ab Crunch</v>
       </c>
       <c r="B11" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="E11" t="str">
         <v>2026-09-29</v>
       </c>
       <c r="F11">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="G11">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="H11">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Lat Pulldown, alternating single-arm</v>
       </c>
       <c r="B12" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="str">
         <v>2026-09-28</v>
@@ -793,24 +793,24 @@
         <v>2026-09-28</v>
       </c>
       <c r="F12">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G12">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H12">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Leg Extension ISO hold</v>
       </c>
       <c r="B13" t="str">
         <v>Isometric</v>
@@ -822,7 +822,7 @@
         <v>2026-09-28</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="F13">
         <v>50</v>
@@ -842,79 +842,143 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Suitcase Bottom-Up, single-arm</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="B14" t="str">
         <v>Strength</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-01</v>
       </c>
       <c r="F14">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G14">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H14">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J14">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Zottman Curl</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="B15" t="str">
-        <v>Hypertrophy</v>
+        <v>Isometric</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-28</v>
       </c>
       <c r="F15">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G15">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H15">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Suitcase Bottom-Up, single-arm</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="E16" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="F16">
+        <v>25</v>
+      </c>
+      <c r="G16">
+        <v>25</v>
+      </c>
+      <c r="H16">
+        <v>25</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
         <v>30</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Zottman Curl</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Hypertrophy</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="E17" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="F17">
+        <v>20</v>
+      </c>
+      <c r="G17">
+        <v>20</v>
+      </c>
+      <c r="H17">
+        <v>20</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J15"/>
+  <autoFilter ref="A1:J17"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J17"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N30"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -1738,7 +1802,7 @@
         <v>Isometric</v>
       </c>
       <c r="E19">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F19">
         <v>4</v>
@@ -1750,7 +1814,7 @@
         <v>30</v>
       </c>
       <c r="I19" t="str">
-        <v>60×30s, 60×30s, 60×30s, 60×30s</v>
+        <v>50×30s, 50×30s, 50×30s, 50×30s</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1762,7 +1826,7 @@
         <v/>
       </c>
       <c r="M19" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N19" t="str">
         <v>A-d3s5</v>
@@ -1856,17 +1920,413 @@
         <v>A-d1s7</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Arnold Press</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E22">
+        <v>35</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22">
+        <v>6</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>35×6, 35×6, 30×6, 30×6</v>
+      </c>
+      <c r="J22">
+        <v>780</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Front delts, Side delts</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Triceps</v>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <v>A-d4s4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Chest Press</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Hypertrophy</v>
+      </c>
+      <c r="E23">
+        <v>25</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>10</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>25×15, 25×10</v>
+      </c>
+      <c r="J23">
+        <v>625</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Chest</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Front delts, Triceps</v>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <v>A-d4s5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Hack Squat</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Hypertrophy</v>
+      </c>
+      <c r="E24">
+        <v>270</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
+      </c>
+      <c r="G24">
+        <v>15</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>270×15, 270×15, 270×15, 270×15</v>
+      </c>
+      <c r="J24">
+        <v>16200</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Quads</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Glutes, Inner thigh (adductors)</v>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v>A-d3s1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Hip Thrust</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E25">
+        <v>320</v>
+      </c>
+      <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25">
+        <v>6</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>320×6, 320×6</v>
+      </c>
+      <c r="J25">
+        <v>3840</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Glutes</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Hamstrings</v>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <v>A-d4s5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Inner Thigh Abduction</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E26">
+        <v>180</v>
+      </c>
+      <c r="F26">
+        <v>4</v>
+      </c>
+      <c r="G26">
+        <v>6</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>180×6, 180×6, 180×6, 180×6</v>
+      </c>
+      <c r="J26">
+        <v>4320</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Inner thigh (adductors)</v>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <v>A-d4s2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Seated Zercher Good Morning</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E27">
+        <v>50</v>
+      </c>
+      <c r="F27">
+        <v>4</v>
+      </c>
+      <c r="G27">
+        <v>6</v>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>50×6, 50×6, 50×6, 50×6</v>
+      </c>
+      <c r="J27">
+        <v>1200</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Lower back</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Glutes, Hamstrings, Upper back</v>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <v>A-d4s4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Arnold Press</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E28">
+        <v>25</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>6</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v>25×6</v>
+      </c>
+      <c r="J28">
+        <v>150</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Front delts, Side delts</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Triceps</v>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <v>A-d6s5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Hack Squat</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Hypertrophy</v>
+      </c>
+      <c r="E29">
+        <v>270</v>
+      </c>
+      <c r="F29">
+        <v>3</v>
+      </c>
+      <c r="G29">
+        <v>15</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v>270×15, 270×15, 270×15</v>
+      </c>
+      <c r="J29">
+        <v>12150</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Quads</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Glutes, Inner thigh (adductors)</v>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v>A-d5s3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Seated Zercher Good Morning</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E30">
+        <v>40</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>6</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v>40×6</v>
+      </c>
+      <c r="J30">
+        <v>240</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Lower back</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Glutes, Hamstrings, Upper back</v>
+      </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
+        <v>A-d6s5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N21"/>
+  <autoFilter ref="A1:N30"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N30"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -1914,16 +2374,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B3" t="str">
-        <v>Rear delts</v>
+        <v>Quads</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -1931,16 +2391,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B4" t="str">
-        <v>Upper back</v>
+        <v>Glutes</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -1948,16 +2408,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B5" t="str">
-        <v>Abs</v>
+        <v>Upper back</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="6">
@@ -1965,16 +2425,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B6" t="str">
-        <v>Lats</v>
+        <v>Rear delts</v>
       </c>
       <c r="C6">
         <v>8</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -1982,16 +2442,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B7" t="str">
-        <v>Chest</v>
+        <v>Inner thigh (adductors)</v>
       </c>
       <c r="C7">
         <v>8</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="8">
@@ -1999,16 +2459,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B8" t="str">
-        <v>Quads</v>
+        <v>Abs</v>
       </c>
       <c r="C8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -2016,16 +2476,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B9" t="str">
-        <v>Biceps</v>
+        <v>Front delts</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -2033,16 +2493,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B10" t="str">
-        <v>Glutes</v>
+        <v>Chest</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -2050,16 +2510,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B11" t="str">
-        <v>Hip flexors</v>
+        <v>Lower back</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -2067,16 +2527,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B12" t="str">
-        <v>Hamstrings</v>
+        <v>Lats</v>
       </c>
       <c r="C12">
+        <v>8</v>
+      </c>
+      <c r="D12">
         <v>0</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>8</v>
-      </c>
-      <c r="E12">
-        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -2084,16 +2544,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B13" t="str">
-        <v>Inner thigh (adductors)</v>
+        <v>Hamstrings</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="14">
@@ -2101,16 +2561,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B14" t="str">
-        <v>Lower back</v>
+        <v>Triceps</v>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="15">
@@ -2118,16 +2578,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B15" t="str">
-        <v>Front delts</v>
+        <v>Biceps</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D15">
         <v>8</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2135,16 +2595,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B16" t="str">
-        <v>Triceps</v>
+        <v>Hip flexors</v>
       </c>
       <c r="C16">
+        <v>6</v>
+      </c>
+      <c r="D16">
         <v>0</v>
       </c>
-      <c r="D16">
-        <v>8</v>
-      </c>
       <c r="E16">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -2152,16 +2612,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B17" t="str">
-        <v>Obliques</v>
+        <v>Side delts</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -2169,22 +2629,39 @@
         <v>2026-09-27</v>
       </c>
       <c r="B18" t="str">
+        <v>Obliques</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B19" t="str">
         <v>Traps</v>
       </c>
-      <c r="C18">
+      <c r="C19">
         <v>0</v>
       </c>
-      <c r="D18">
+      <c r="D19">
         <v>4</v>
       </c>
-      <c r="E18">
+      <c r="E19">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E18"/>
+  <autoFilter ref="A1:E19"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2237,22 +2714,22 @@
         <v>A</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="H2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2634,7 +3111,7 @@
         <v>Exported</v>
       </c>
       <c r="B40" t="str">
-        <v>2026-09-29T15:54:15.150Z</v>
+        <v>2026-10-02T02:07:31.209Z</v>
       </c>
     </row>
   </sheetData>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -9,14 +9,23 @@
     <sheet name="Weeks" sheetId="4" r:id="rId4"/>
     <sheet name="Body weight" sheetId="5" r:id="rId5"/>
     <sheet name="Settings" sheetId="6" r:id="rId6"/>
+    <sheet name="Programs" sheetId="7" r:id="rId7"/>
+    <sheet name="Program info" sheetId="8" r:id="rId8"/>
+    <sheet name="Saved versions" sheetId="9" r:id="rId9"/>
+    <sheet name="Check-offs" sheetId="10" r:id="rId10"/>
+    <sheet name="Config" sheetId="11" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$N$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">Weeks!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Body weight'!$A$1:$D$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5">Settings!$A$1:$B$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6">Programs!$A$1:$R$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Program info'!$A$1:$B$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9">'Check-offs'!$A$1:$D$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10">Config!$A$1:$B$13</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -976,9 +985,945 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D57"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" customWidth="1"/>
+    <col min="3" max="3" width="24.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Week of</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Kind</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Key</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B2" t="str">
+        <v>done</v>
+      </c>
+      <c r="C2" t="str">
+        <v>A-d1s1</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B3" t="str">
+        <v>done</v>
+      </c>
+      <c r="C3" t="str">
+        <v>A-d1s2</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B4" t="str">
+        <v>done</v>
+      </c>
+      <c r="C4" t="str">
+        <v>A-d1s4</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B5" t="str">
+        <v>done</v>
+      </c>
+      <c r="C5" t="str">
+        <v>A-d1s6</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B6" t="str">
+        <v>done</v>
+      </c>
+      <c r="C6" t="str">
+        <v>A-d1s8</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B7" t="str">
+        <v>done</v>
+      </c>
+      <c r="C7" t="str">
+        <v>A-d2s3</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B8" t="str">
+        <v>done</v>
+      </c>
+      <c r="C8" t="str">
+        <v>A-d2s5</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B9" t="str">
+        <v>done</v>
+      </c>
+      <c r="C9" t="str">
+        <v>A-d3s2</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B10" t="str">
+        <v>done</v>
+      </c>
+      <c r="C10" t="str">
+        <v>A-d3s3</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B11" t="str">
+        <v>done</v>
+      </c>
+      <c r="C11" t="str">
+        <v>A-d2s2</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B12" t="str">
+        <v>done</v>
+      </c>
+      <c r="C12" t="str">
+        <v>A-d2s2#0</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B13" t="str">
+        <v>done</v>
+      </c>
+      <c r="C13" t="str">
+        <v>A-d3s6</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B14" t="str">
+        <v>done</v>
+      </c>
+      <c r="C14" t="str">
+        <v>A-d3s6#0</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B15" t="str">
+        <v>done</v>
+      </c>
+      <c r="C15" t="str">
+        <v>A-d2s4</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B16" t="str">
+        <v>done</v>
+      </c>
+      <c r="C16" t="str">
+        <v>A-d1s7</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B17" t="str">
+        <v>done</v>
+      </c>
+      <c r="C17" t="str">
+        <v>A-d3s5</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B18" t="str">
+        <v>done</v>
+      </c>
+      <c r="C18" t="str">
+        <v>A-d3s1</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B19" t="str">
+        <v>done</v>
+      </c>
+      <c r="C19" t="str">
+        <v>A-d4s5</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B20" t="str">
+        <v>done</v>
+      </c>
+      <c r="C20" t="str">
+        <v>A-d4s2</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B21" t="str">
+        <v>done</v>
+      </c>
+      <c r="C21" t="str">
+        <v>A-d4s4</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B22" t="str">
+        <v>done</v>
+      </c>
+      <c r="C22" t="str">
+        <v>A-d6s5</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B23" t="str">
+        <v>done</v>
+      </c>
+      <c r="C23" t="str">
+        <v>A-d5s3</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B24" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C24" t="str">
+        <v>A-d1s9</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B25" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C25" t="str">
+        <v>A-d1s5</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B26" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C26" t="str">
+        <v>A-d1s3</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B27" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C27" t="str">
+        <v>A-d2s6</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C28" t="str">
+        <v>A-d2s8</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B29" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C29" t="str">
+        <v>A-d2s7</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B30" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C30" t="str">
+        <v>A-d3s7</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B31" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C31" t="str">
+        <v>A-d3s4</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B32" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C32" t="str">
+        <v>A-d3s9</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B33" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C33" t="str">
+        <v>A-d3s8</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B34" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C34" t="str">
+        <v>A-d4s1</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B35" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C35" t="str">
+        <v>A-d4s3</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B36" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C36" t="str">
+        <v>A-d4s8</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B37" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C37" t="str">
+        <v>A-d4s7</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B38" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C38" t="str">
+        <v>A-d5s9</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B39" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C39" t="str">
+        <v>A-d5s10</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B40" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C40" t="str">
+        <v>A-d2s1</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B41" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C41" t="str">
+        <v>A-d4s6</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B42" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C42" t="str">
+        <v>A-d3s2</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B43" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C43" t="str">
+        <v>A-d3s3</v>
+      </c>
+      <c r="D43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B44" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C44" t="str">
+        <v>A-d2s4</v>
+      </c>
+      <c r="D44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B45" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C45" t="str">
+        <v>A-d1s7</v>
+      </c>
+      <c r="D45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B46" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C46" t="str">
+        <v>A-d3s6</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B47" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C47" t="str">
+        <v>A-d3s1</v>
+      </c>
+      <c r="D47">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B48" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C48" t="str">
+        <v>A-d4s6</v>
+      </c>
+      <c r="D48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B49" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C49" t="str">
+        <v>A-d2s1</v>
+      </c>
+      <c r="D49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B50" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C50" t="str">
+        <v>A-d6s5</v>
+      </c>
+      <c r="D50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B51" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C51" t="str">
+        <v>A-d5s8</v>
+      </c>
+      <c r="D51">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B52" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C52" t="str">
+        <v>A-d5s7</v>
+      </c>
+      <c r="D52">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B53" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C53" t="str">
+        <v>A-d5s6</v>
+      </c>
+      <c r="D53">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B54" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C54" t="str">
+        <v>A-d5s5</v>
+      </c>
+      <c r="D54">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B55" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C55" t="str">
+        <v>A-d5s4</v>
+      </c>
+      <c r="D55">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B56" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C56" t="str">
+        <v>A-d5s2</v>
+      </c>
+      <c r="D56">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B57" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C57" t="str">
+        <v>A-d5s1</v>
+      </c>
+      <c r="D57">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D57"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D57"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B13"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="60.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Setting</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Value (JSON)</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ex</v>
+      </c>
+      <c r="B2" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ghBackup</v>
+      </c>
+      <c r="B3" t="str">
+        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"1r0xg3l","last":{"at":"2026-10-02T02:07:33.781Z","url":"https://github.com/jacgit18/iron-log/commit/34dcc108fb277928b41a6ef04e695a35b5d7f16f"}}</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>m2Even</v>
+      </c>
+      <c r="B4" t="str">
+        <v>"B"</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>m3First</v>
+      </c>
+      <c r="B5" t="str">
+        <v>"A"</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>m3Start</v>
+      </c>
+      <c r="B6" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>mode</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>muscleMap</v>
+      </c>
+      <c r="B8" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>pct</v>
+      </c>
+      <c r="B9" t="str">
+        <v>{"strength":85,"iso":75,"hyp":65,"exp":45}</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>phDef</v>
+      </c>
+      <c r="B10" t="str">
+        <v>{"A-d1s1:0":"hyp","A-d3s9:0":"iso","A-d4s1:0":"strength","A-d1s7:1":"iso"}</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>progNames</v>
+      </c>
+      <c r="B11" t="str">
+        <v>{"A":"Program A - Unilateral","B":"Program B - Bilateral"}</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>rm</v>
+      </c>
+      <c r="B12" t="str">
+        <v>{"latpd":90,"wristpd":55,"platerot":35,"innerthigh":200,"chestpress":45,"zercher":80,"zottman":30,"kbleg":30,"grip":300,"canoe":45,"suitcase":30,"reardelt":80,"facepull":50,"legext":80,"cablecrunch":100,"hipthrust":400,"db6":20,"hack":400,"pallof":40,"cablerow":70,"arnold":45,"dbclean":45,"latpdbi":90,"outerthigh":180,"farmers":65,"dblunge":65,"ohtri":30,"bss":65,"legcurl":100,"cablepunch":50}</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>rxOverride</v>
+      </c>
+      <c r="B13" t="str">
+        <v>{}</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B13"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:O30"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -994,6 +1939,7 @@
     <col min="12" max="12" width="28.83203125" customWidth="1"/>
     <col min="13" max="13" width="30.83203125" customWidth="1"/>
     <col min="14" max="14" width="14.83203125" customWidth="1"/>
+    <col min="15" max="15" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,6 +1985,9 @@
       <c r="N1" t="str">
         <v>Program slot</v>
       </c>
+      <c r="O1" t="str">
+        <v>Exercise id</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1083,6 +2032,9 @@
       <c r="N2" t="str">
         <v>A-d1s2</v>
       </c>
+      <c r="O2" t="str">
+        <v>wristpd</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -1127,6 +2079,9 @@
       <c r="N3" t="str">
         <v>A-d3s3</v>
       </c>
+      <c r="O3" t="str">
+        <v>wristpd</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -1171,6 +2126,9 @@
       <c r="N4" t="str">
         <v>A-d1s6</v>
       </c>
+      <c r="O4" t="str">
+        <v>chestpress</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -1215,6 +2173,9 @@
       <c r="N5" t="str">
         <v>A-d2s5</v>
       </c>
+      <c r="O5" t="str">
+        <v>chestpress</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -1259,6 +2220,9 @@
       <c r="N6" t="str">
         <v>A-d1s8</v>
       </c>
+      <c r="O6" t="str">
+        <v>grip</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -1303,6 +2267,9 @@
       <c r="N7" t="str">
         <v>A-d2s5</v>
       </c>
+      <c r="O7" t="str">
+        <v>hipthrust</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -1347,6 +2314,9 @@
       <c r="N8" t="str">
         <v>A-d1s4</v>
       </c>
+      <c r="O8" t="str">
+        <v>innerthigh</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -1391,6 +2361,9 @@
       <c r="N9" t="str">
         <v>A-d1s1</v>
       </c>
+      <c r="O9" t="str">
+        <v>latpd</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -1435,6 +2408,9 @@
       <c r="N10" t="str">
         <v>A-d3s2</v>
       </c>
+      <c r="O10" t="str">
+        <v>latpd</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -1479,6 +2455,9 @@
       <c r="N11" t="str">
         <v>A-d2s3</v>
       </c>
+      <c r="O11" t="str">
+        <v>legext</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -1523,6 +2502,9 @@
       <c r="N12" t="str">
         <v>A-d1s6</v>
       </c>
+      <c r="O12" t="str">
+        <v>zercher</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -1567,6 +2549,9 @@
       <c r="N13" t="str">
         <v>A-d2s2</v>
       </c>
+      <c r="O13" t="str">
+        <v>reardelt</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -1611,6 +2596,9 @@
       <c r="N14" t="str">
         <v>A-d3s6</v>
       </c>
+      <c r="O14" t="str">
+        <v>reardelt</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -1655,6 +2643,9 @@
       <c r="N15" t="str">
         <v>A-d3s9</v>
       </c>
+      <c r="O15" t="str">
+        <v>deskbands</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1699,6 +2690,9 @@
       <c r="N16" t="str">
         <v>A-d1s7</v>
       </c>
+      <c r="O16" t="str">
+        <v>kbleg</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -1743,6 +2737,9 @@
       <c r="N17" t="str">
         <v>A-d1s7</v>
       </c>
+      <c r="O17" t="str">
+        <v>kbleg</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -1787,6 +2784,9 @@
       <c r="N18" t="str">
         <v>A-d2s4</v>
       </c>
+      <c r="O18" t="str">
+        <v>cablecrunch</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -1831,6 +2831,9 @@
       <c r="N19" t="str">
         <v>A-d3s5</v>
       </c>
+      <c r="O19" t="str">
+        <v>legext</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1875,6 +2878,9 @@
       <c r="N20" t="str">
         <v>A-d4s1</v>
       </c>
+      <c r="O20" t="str">
+        <v>suitcase</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1919,6 +2925,9 @@
       <c r="N21" t="str">
         <v>A-d1s7</v>
       </c>
+      <c r="O21" t="str">
+        <v>zottman</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1963,6 +2972,9 @@
       <c r="N22" t="str">
         <v>A-d4s4</v>
       </c>
+      <c r="O22" t="str">
+        <v>arnold</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -2007,6 +3019,9 @@
       <c r="N23" t="str">
         <v>A-d4s5</v>
       </c>
+      <c r="O23" t="str">
+        <v>chestpress</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -2051,6 +3066,9 @@
       <c r="N24" t="str">
         <v>A-d3s1</v>
       </c>
+      <c r="O24" t="str">
+        <v>hack</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -2095,6 +3113,9 @@
       <c r="N25" t="str">
         <v>A-d4s5</v>
       </c>
+      <c r="O25" t="str">
+        <v>hipthrust</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -2139,6 +3160,9 @@
       <c r="N26" t="str">
         <v>A-d4s2</v>
       </c>
+      <c r="O26" t="str">
+        <v>innerthigh</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -2183,6 +3207,9 @@
       <c r="N27" t="str">
         <v>A-d4s4</v>
       </c>
+      <c r="O27" t="str">
+        <v>zercher</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -2227,6 +3254,9 @@
       <c r="N28" t="str">
         <v>A-d6s5</v>
       </c>
+      <c r="O28" t="str">
+        <v>arnold</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -2271,6 +3301,9 @@
       <c r="N29" t="str">
         <v>A-d5s3</v>
       </c>
+      <c r="O29" t="str">
+        <v>hack</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -2315,11 +3348,14 @@
       <c r="N30" t="str">
         <v>A-d6s5</v>
       </c>
+      <c r="O30" t="str">
+        <v>zercher</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N30"/>
+  <autoFilter ref="A1:O30"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O30"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2714,7 +3750,7 @@
         <v>A</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2">
         <v>26</v>
@@ -3111,7 +4147,7 @@
         <v>Exported</v>
       </c>
       <c r="B40" t="str">
-        <v>2026-10-02T02:07:31.209Z</v>
+        <v>2026-10-02T04:16:19.015Z</v>
       </c>
     </row>
   </sheetData>
@@ -3120,4 +4156,3747 @@
     <ignoredError numberStoredAsText="1" sqref="A1:B40"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:R65"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="5.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="7.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="11.83203125" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" customWidth="1"/>
+    <col min="10" max="10" width="9.83203125" customWidth="1"/>
+    <col min="11" max="11" width="24.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="13" max="13" width="30.83203125" customWidth="1"/>
+    <col min="14" max="14" width="11.83203125" customWidth="1"/>
+    <col min="15" max="15" width="11.83203125" customWidth="1"/>
+    <col min="16" max="16" width="10.83203125" customWidth="1"/>
+    <col min="17" max="17" width="16.83203125" customWidth="1"/>
+    <col min="18" max="18" width="24.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Program</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Day</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Day title</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Day subtitle</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Make-up day</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Slot #</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Slot id</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Section</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Tier</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Type</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Slot note</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Exercise id</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Exercise</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Phase</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Weight (lb)</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Bodyweight</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>Rx</v>
+      </c>
+      <c r="R1" t="str">
+        <v>Item note</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>A</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="str">
+        <v>A-d1s1</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v>latpd</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Lat Pulldown, alternating single-arm</v>
+      </c>
+      <c r="N2" t="str">
+        <v>hyp</v>
+      </c>
+      <c r="O2">
+        <v>45</v>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>A</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3" t="str">
+        <v>A-d1s2</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>wristpd</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Cable Wrist Pulldown</v>
+      </c>
+      <c r="N3" t="str">
+        <v>hyp</v>
+      </c>
+      <c r="O3">
+        <v>33</v>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>A</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4" t="str">
+        <v>A-d1s3</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>platerot</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Plate Torso Rotation</v>
+      </c>
+      <c r="N4" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O4">
+        <v>10</v>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>A</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5" t="str">
+        <v>A-d1s4</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>innerthigh</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Inner Thigh Abduction</v>
+      </c>
+      <c r="N5" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O5">
+        <v>180</v>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>A</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6" t="str">
+        <v>A-d1s5</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>romanadd</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Roman Chair Hip Adduction</v>
+      </c>
+      <c r="N6" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v>On the back-extension bench</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>A</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7" t="str">
+        <v>A-d1s6</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J7" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>chestpress</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Chest Press</v>
+      </c>
+      <c r="N7" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O7">
+        <v>35</v>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>A</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+      <c r="G8" t="str">
+        <v>A-d1s6</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J8" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>zercher</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Seated Zercher Good Morning</v>
+      </c>
+      <c r="N8" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O8">
+        <v>50</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>A</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9">
+        <v>7</v>
+      </c>
+      <c r="G9" t="str">
+        <v>A-d1s7</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J9" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>zottman</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Zottman Curl</v>
+      </c>
+      <c r="N9" t="str">
+        <v>hyp</v>
+      </c>
+      <c r="O9">
+        <v>15</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v>3 × 15</v>
+      </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>A</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10">
+        <v>7</v>
+      </c>
+      <c r="G10" t="str">
+        <v>A-d1s7</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J10" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>kbleg</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Kettlebell Leg Raise</v>
+      </c>
+      <c r="N10" t="str">
+        <v>iso</v>
+      </c>
+      <c r="O10">
+        <v>15</v>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v>3 × 15 s hold</v>
+      </c>
+      <c r="R10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>A</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="G11" t="str">
+        <v>A-d1s8</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>grip</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Grip Trainer</v>
+      </c>
+      <c r="N11" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O11">
+        <v>200</v>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>A</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12">
+        <v>9</v>
+      </c>
+      <c r="G12" t="str">
+        <v>A-d1s9</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>canoe</v>
+      </c>
+      <c r="M12" t="str">
+        <v>Canoe Stretch</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12">
+        <v>10</v>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>A</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="str">
+        <v>A-d2s1</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>suitcase</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Suitcase Bottom-Up, single-arm</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13">
+        <v>20</v>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v>3 × 4 each arm</v>
+      </c>
+      <c r="R13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>A</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="str">
+        <v>A-d2s2</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J14" t="str">
+        <v>either</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Whichever is free</v>
+      </c>
+      <c r="L14" t="str">
+        <v>reardelt</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Side Rear Delt Fly</v>
+      </c>
+      <c r="N14" t="str">
+        <v>iso</v>
+      </c>
+      <c r="O14">
+        <v>50</v>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v>4 × 15 s per arm</v>
+      </c>
+      <c r="R14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>A</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" t="str">
+        <v>A-d2s2</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J15" t="str">
+        <v>either</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Whichever is free</v>
+      </c>
+      <c r="L15" t="str">
+        <v>facepull</v>
+      </c>
+      <c r="M15" t="str">
+        <v>Face Pull</v>
+      </c>
+      <c r="N15" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O15">
+        <v>30</v>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>A</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16" t="str">
+        <v>A-d2s3</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>legext</v>
+      </c>
+      <c r="M16" t="str">
+        <v>Leg Extension ISO hold</v>
+      </c>
+      <c r="N16" t="str">
+        <v>iso</v>
+      </c>
+      <c r="O16">
+        <v>50</v>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v>4 × 30 s</v>
+      </c>
+      <c r="R16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>A</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17">
+        <v>4</v>
+      </c>
+      <c r="G17" t="str">
+        <v>A-d2s4</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>cablecrunch</v>
+      </c>
+      <c r="M17" t="str">
+        <v>Kneeling Cable Ab Crunch</v>
+      </c>
+      <c r="N17" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O17">
+        <v>60</v>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>A</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+      <c r="G18" t="str">
+        <v>A-d2s5</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J18" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>hipthrust</v>
+      </c>
+      <c r="M18" t="str">
+        <v>Hip Thrust</v>
+      </c>
+      <c r="N18" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O18">
+        <v>320</v>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>A</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+      <c r="G19" t="str">
+        <v>A-d2s5</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J19" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>chestpress</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Chest Press</v>
+      </c>
+      <c r="N19" t="str">
+        <v>hyp</v>
+      </c>
+      <c r="O19">
+        <v>25</v>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>A</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20">
+        <v>6</v>
+      </c>
+      <c r="G20" t="str">
+        <v>A-d2s6</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J20" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>dip</v>
+      </c>
+      <c r="M20" t="str">
+        <v>Wide Tricep Dip</v>
+      </c>
+      <c r="N20" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+      <c r="R20" t="str">
+        <v>Bodyweight, working toward +10 lb</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>A</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21">
+        <v>6</v>
+      </c>
+      <c r="G21" t="str">
+        <v>A-d2s6</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J21" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>kneeraise</v>
+      </c>
+      <c r="M21" t="str">
+        <v>Hanging Knee Raise</v>
+      </c>
+      <c r="N21" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>A</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22">
+        <v>7</v>
+      </c>
+      <c r="G22" t="str">
+        <v>A-d2s7</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v>grip</v>
+      </c>
+      <c r="M22" t="str">
+        <v>Grip Trainer</v>
+      </c>
+      <c r="N22" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O22">
+        <v>200</v>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
+      <c r="R22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>A</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23">
+        <v>8</v>
+      </c>
+      <c r="G23" t="str">
+        <v>A-d2s8</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>db6</v>
+      </c>
+      <c r="M23" t="str">
+        <v>DB 6 Ways</v>
+      </c>
+      <c r="N23" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O23">
+        <v>10</v>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v>2 × 6</v>
+      </c>
+      <c r="R23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>A</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" t="str">
+        <v>A-d3s1</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v>hack</v>
+      </c>
+      <c r="M24" t="str">
+        <v>Hack Squat</v>
+      </c>
+      <c r="N24" t="str">
+        <v>hyp</v>
+      </c>
+      <c r="O24">
+        <v>270</v>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
+      <c r="R24" t="str">
+        <v>Feet low on the plate, narrow stance for quads</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>A</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25" t="str">
+        <v>A-d3s2</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v>latpd</v>
+      </c>
+      <c r="M25" t="str">
+        <v>Lat Pulldown, alternating single-arm</v>
+      </c>
+      <c r="N25" t="str">
+        <v>hyp</v>
+      </c>
+      <c r="O25">
+        <v>45</v>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
+        <v/>
+      </c>
+      <c r="R25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>A</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26" t="str">
+        <v>A-d3s3</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v>wristpd</v>
+      </c>
+      <c r="M26" t="str">
+        <v>Cable Wrist Pulldown</v>
+      </c>
+      <c r="N26" t="str">
+        <v>hyp</v>
+      </c>
+      <c r="O26">
+        <v>33</v>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <v/>
+      </c>
+      <c r="R26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>A</v>
+      </c>
+      <c r="B27">
+        <v>3</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27">
+        <v>4</v>
+      </c>
+      <c r="G27" t="str">
+        <v>A-d3s4</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v>platerot</v>
+      </c>
+      <c r="M27" t="str">
+        <v>Plate Torso Rotation</v>
+      </c>
+      <c r="N27" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O27">
+        <v>10</v>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <v/>
+      </c>
+      <c r="R27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>A</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28">
+        <v>5</v>
+      </c>
+      <c r="G28" t="str">
+        <v>A-d3s5</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v>legext</v>
+      </c>
+      <c r="M28" t="str">
+        <v>Leg Extension ISO hold</v>
+      </c>
+      <c r="N28" t="str">
+        <v>iso</v>
+      </c>
+      <c r="O28">
+        <v>50</v>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
+        <v>4 × 30 s</v>
+      </c>
+      <c r="R28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>A</v>
+      </c>
+      <c r="B29">
+        <v>3</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29">
+        <v>6</v>
+      </c>
+      <c r="G29" t="str">
+        <v>A-d3s6</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J29" t="str">
+        <v>either</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Whichever is free</v>
+      </c>
+      <c r="L29" t="str">
+        <v>reardelt</v>
+      </c>
+      <c r="M29" t="str">
+        <v>Side Rear Delt Fly</v>
+      </c>
+      <c r="N29" t="str">
+        <v>iso</v>
+      </c>
+      <c r="O29">
+        <v>50</v>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+      <c r="Q29" t="str">
+        <v>4 × 15 s per arm</v>
+      </c>
+      <c r="R29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>A</v>
+      </c>
+      <c r="B30">
+        <v>3</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30">
+        <v>6</v>
+      </c>
+      <c r="G30" t="str">
+        <v>A-d3s6</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J30" t="str">
+        <v>either</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Whichever is free</v>
+      </c>
+      <c r="L30" t="str">
+        <v>facepull</v>
+      </c>
+      <c r="M30" t="str">
+        <v>Face Pull</v>
+      </c>
+      <c r="N30" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O30">
+        <v>30</v>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+      <c r="Q30" t="str">
+        <v/>
+      </c>
+      <c r="R30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>A</v>
+      </c>
+      <c r="B31">
+        <v>3</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31">
+        <v>7</v>
+      </c>
+      <c r="G31" t="str">
+        <v>A-d3s7</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J31" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
+        <v>pallof</v>
+      </c>
+      <c r="M31" t="str">
+        <v>Pallof Press</v>
+      </c>
+      <c r="N31" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O31">
+        <v>30</v>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+      <c r="Q31" t="str">
+        <v/>
+      </c>
+      <c r="R31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>A</v>
+      </c>
+      <c r="B32">
+        <v>3</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32">
+        <v>7</v>
+      </c>
+      <c r="G32" t="str">
+        <v>A-d3s7</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J32" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K32" t="str">
+        <v/>
+      </c>
+      <c r="L32" t="str">
+        <v>cablerow</v>
+      </c>
+      <c r="M32" t="str">
+        <v>Explosive Unilateral Cable Row</v>
+      </c>
+      <c r="N32" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O32">
+        <v>30</v>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+      <c r="Q32" t="str">
+        <v/>
+      </c>
+      <c r="R32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>A</v>
+      </c>
+      <c r="B33">
+        <v>3</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33">
+        <v>8</v>
+      </c>
+      <c r="G33" t="str">
+        <v>A-d3s8</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
+        <v>grip</v>
+      </c>
+      <c r="M33" t="str">
+        <v>Grip Trainer</v>
+      </c>
+      <c r="N33" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O33">
+        <v>200</v>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+      <c r="Q33" t="str">
+        <v/>
+      </c>
+      <c r="R33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>A</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34">
+        <v>9</v>
+      </c>
+      <c r="G34" t="str">
+        <v>A-d3s9</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
+        <v>deskbands</v>
+      </c>
+      <c r="M34" t="str">
+        <v>Desk Bands</v>
+      </c>
+      <c r="N34" t="str">
+        <v>iso</v>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+      <c r="P34" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q34" t="str">
+        <v/>
+      </c>
+      <c r="R34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>A</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35" t="str">
+        <v>A-d4s1</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v/>
+      </c>
+      <c r="L35" t="str">
+        <v>suitcase</v>
+      </c>
+      <c r="M35" t="str">
+        <v>Suitcase Bottom-Up, single-arm</v>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35">
+        <v>20</v>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+      <c r="Q35" t="str">
+        <v>3 × 4 each arm</v>
+      </c>
+      <c r="R35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>A</v>
+      </c>
+      <c r="B36">
+        <v>4</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36">
+        <v>2</v>
+      </c>
+      <c r="G36" t="str">
+        <v>A-d4s2</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
+      <c r="L36" t="str">
+        <v>innerthigh</v>
+      </c>
+      <c r="M36" t="str">
+        <v>Inner Thigh Abduction</v>
+      </c>
+      <c r="N36" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O36">
+        <v>180</v>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+      <c r="Q36" t="str">
+        <v/>
+      </c>
+      <c r="R36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>A</v>
+      </c>
+      <c r="B37">
+        <v>4</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37" t="str">
+        <v>A-d4s3</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
+        <v>romanadd</v>
+      </c>
+      <c r="M37" t="str">
+        <v>Roman Chair Hip Adduction</v>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+      <c r="P37" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q37" t="str">
+        <v/>
+      </c>
+      <c r="R37" t="str">
+        <v>On the back-extension bench</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>A</v>
+      </c>
+      <c r="B38">
+        <v>4</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38">
+        <v>4</v>
+      </c>
+      <c r="G38" t="str">
+        <v>A-d4s4</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J38" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
+        <v>arnold</v>
+      </c>
+      <c r="M38" t="str">
+        <v>Arnold Press</v>
+      </c>
+      <c r="N38" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O38">
+        <v>35</v>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+      <c r="Q38" t="str">
+        <v/>
+      </c>
+      <c r="R38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>A</v>
+      </c>
+      <c r="B39">
+        <v>4</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39">
+        <v>4</v>
+      </c>
+      <c r="G39" t="str">
+        <v>A-d4s4</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J39" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
+        <v>zercher</v>
+      </c>
+      <c r="M39" t="str">
+        <v>Seated Zercher Good Morning</v>
+      </c>
+      <c r="N39" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O39">
+        <v>50</v>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+      <c r="Q39" t="str">
+        <v/>
+      </c>
+      <c r="R39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>A</v>
+      </c>
+      <c r="B40">
+        <v>4</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40">
+        <v>5</v>
+      </c>
+      <c r="G40" t="str">
+        <v>A-d4s5</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J40" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
+        <v>hipthrust</v>
+      </c>
+      <c r="M40" t="str">
+        <v>Hip Thrust</v>
+      </c>
+      <c r="N40" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O40">
+        <v>320</v>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+      <c r="Q40" t="str">
+        <v/>
+      </c>
+      <c r="R40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>A</v>
+      </c>
+      <c r="B41">
+        <v>4</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41">
+        <v>5</v>
+      </c>
+      <c r="G41" t="str">
+        <v>A-d4s5</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J41" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
+        <v>chestpress</v>
+      </c>
+      <c r="M41" t="str">
+        <v>Chest Press</v>
+      </c>
+      <c r="N41" t="str">
+        <v>hyp</v>
+      </c>
+      <c r="O41">
+        <v>25</v>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+      <c r="Q41" t="str">
+        <v/>
+      </c>
+      <c r="R41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>A</v>
+      </c>
+      <c r="B42">
+        <v>4</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42">
+        <v>6</v>
+      </c>
+      <c r="G42" t="str">
+        <v>A-d4s6</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I42" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J42" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
+        <v>zottman</v>
+      </c>
+      <c r="M42" t="str">
+        <v>Zottman Curl</v>
+      </c>
+      <c r="N42" t="str">
+        <v>hyp</v>
+      </c>
+      <c r="O42">
+        <v>15</v>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+      <c r="Q42" t="str">
+        <v>3 × 15</v>
+      </c>
+      <c r="R42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>A</v>
+      </c>
+      <c r="B43">
+        <v>4</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43">
+        <v>6</v>
+      </c>
+      <c r="G43" t="str">
+        <v>A-d4s6</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I43" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J43" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
+        <v>kbleg</v>
+      </c>
+      <c r="M43" t="str">
+        <v>Kettlebell Leg Raise</v>
+      </c>
+      <c r="N43" t="str">
+        <v>iso</v>
+      </c>
+      <c r="O43">
+        <v>15</v>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+      <c r="Q43" t="str">
+        <v>3 × 15 s hold</v>
+      </c>
+      <c r="R43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>A</v>
+      </c>
+      <c r="B44">
+        <v>4</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44">
+        <v>7</v>
+      </c>
+      <c r="G44" t="str">
+        <v>A-d4s7</v>
+      </c>
+      <c r="H44" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
+        <v>grip</v>
+      </c>
+      <c r="M44" t="str">
+        <v>Grip Trainer</v>
+      </c>
+      <c r="N44" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O44">
+        <v>200</v>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+      <c r="Q44" t="str">
+        <v/>
+      </c>
+      <c r="R44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>A</v>
+      </c>
+      <c r="B45">
+        <v>4</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45">
+        <v>8</v>
+      </c>
+      <c r="G45" t="str">
+        <v>A-d4s8</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
+        <v>deskbands</v>
+      </c>
+      <c r="M45" t="str">
+        <v>Desk Bands</v>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="P45" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q45" t="str">
+        <v/>
+      </c>
+      <c r="R45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>A</v>
+      </c>
+      <c r="B46">
+        <v>5</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Upper body + rotational power</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46" t="str">
+        <v>A-d5s1</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
+        <v>cablecrunch</v>
+      </c>
+      <c r="M46" t="str">
+        <v>Kneeling Cable Ab Crunch</v>
+      </c>
+      <c r="N46" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O46">
+        <v>60</v>
+      </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
+      <c r="Q46" t="str">
+        <v/>
+      </c>
+      <c r="R46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>A</v>
+      </c>
+      <c r="B47">
+        <v>5</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Upper body + rotational power</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F47">
+        <v>2</v>
+      </c>
+      <c r="G47" t="str">
+        <v>A-d5s2</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="L47" t="str">
+        <v>dbclean</v>
+      </c>
+      <c r="M47" t="str">
+        <v>DB Clean &amp; Jerk Press</v>
+      </c>
+      <c r="N47" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O47">
+        <v>20</v>
+      </c>
+      <c r="P47" t="str">
+        <v/>
+      </c>
+      <c r="Q47" t="str">
+        <v/>
+      </c>
+      <c r="R47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>A</v>
+      </c>
+      <c r="B48">
+        <v>5</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Upper body + rotational power</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F48">
+        <v>3</v>
+      </c>
+      <c r="G48" t="str">
+        <v>A-d5s3</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
+        <v>hack</v>
+      </c>
+      <c r="M48" t="str">
+        <v>Hack Squat</v>
+      </c>
+      <c r="N48" t="str">
+        <v>hyp</v>
+      </c>
+      <c r="O48">
+        <v>270</v>
+      </c>
+      <c r="P48" t="str">
+        <v/>
+      </c>
+      <c r="Q48" t="str">
+        <v/>
+      </c>
+      <c r="R48" t="str">
+        <v>Feet low on the plate, narrow stance for quads</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>A</v>
+      </c>
+      <c r="B49">
+        <v>5</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Upper body + rotational power</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F49">
+        <v>4</v>
+      </c>
+      <c r="G49" t="str">
+        <v>A-d5s4</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I49" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J49" t="str">
+        <v>either</v>
+      </c>
+      <c r="K49" t="str">
+        <v>Whichever is free</v>
+      </c>
+      <c r="L49" t="str">
+        <v>reardelt</v>
+      </c>
+      <c r="M49" t="str">
+        <v>Side Rear Delt Fly</v>
+      </c>
+      <c r="N49" t="str">
+        <v>iso</v>
+      </c>
+      <c r="O49">
+        <v>50</v>
+      </c>
+      <c r="P49" t="str">
+        <v/>
+      </c>
+      <c r="Q49" t="str">
+        <v>4 × 15 s per arm</v>
+      </c>
+      <c r="R49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>A</v>
+      </c>
+      <c r="B50">
+        <v>5</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Upper body + rotational power</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F50">
+        <v>4</v>
+      </c>
+      <c r="G50" t="str">
+        <v>A-d5s4</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I50" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J50" t="str">
+        <v>either</v>
+      </c>
+      <c r="K50" t="str">
+        <v>Whichever is free</v>
+      </c>
+      <c r="L50" t="str">
+        <v>facepull</v>
+      </c>
+      <c r="M50" t="str">
+        <v>Face Pull</v>
+      </c>
+      <c r="N50" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O50">
+        <v>30</v>
+      </c>
+      <c r="P50" t="str">
+        <v/>
+      </c>
+      <c r="Q50" t="str">
+        <v/>
+      </c>
+      <c r="R50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>A</v>
+      </c>
+      <c r="B51">
+        <v>5</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Upper body + rotational power</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F51">
+        <v>5</v>
+      </c>
+      <c r="G51" t="str">
+        <v>A-d5s5</v>
+      </c>
+      <c r="H51" t="str">
+        <v>Plyometric</v>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
+        <v/>
+      </c>
+      <c r="L51" t="str">
+        <v>trxpike</v>
+      </c>
+      <c r="M51" t="str">
+        <v>TRX Pike Push-Up</v>
+      </c>
+      <c r="N51" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+      <c r="P51" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q51" t="str">
+        <v/>
+      </c>
+      <c r="R51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>A</v>
+      </c>
+      <c r="B52">
+        <v>5</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Upper body + rotational power</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F52">
+        <v>6</v>
+      </c>
+      <c r="G52" t="str">
+        <v>A-d5s6</v>
+      </c>
+      <c r="H52" t="str">
+        <v>Plyometric</v>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
+        <v/>
+      </c>
+      <c r="L52" t="str">
+        <v>trxrow</v>
+      </c>
+      <c r="M52" t="str">
+        <v>TRX Wide-Grip Row</v>
+      </c>
+      <c r="N52" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+      <c r="P52" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q52" t="str">
+        <v/>
+      </c>
+      <c r="R52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>A</v>
+      </c>
+      <c r="B53">
+        <v>5</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Upper body + rotational power</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F53">
+        <v>7</v>
+      </c>
+      <c r="G53" t="str">
+        <v>A-d5s7</v>
+      </c>
+      <c r="H53" t="str">
+        <v>Plyometric</v>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
+        <v/>
+      </c>
+      <c r="L53" t="str">
+        <v>medball</v>
+      </c>
+      <c r="M53" t="str">
+        <v>Med Ball Rotational Scoop</v>
+      </c>
+      <c r="N53" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+      <c r="P53" t="str">
+        <v/>
+      </c>
+      <c r="Q53" t="str">
+        <v/>
+      </c>
+      <c r="R53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>A</v>
+      </c>
+      <c r="B54">
+        <v>5</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Upper body + rotational power</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F54">
+        <v>8</v>
+      </c>
+      <c r="G54" t="str">
+        <v>A-d5s8</v>
+      </c>
+      <c r="H54" t="str">
+        <v>Plyometric</v>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <v/>
+      </c>
+      <c r="L54" t="str">
+        <v>latwall</v>
+      </c>
+      <c r="M54" t="str">
+        <v>Lateral Wall Push</v>
+      </c>
+      <c r="N54" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+      <c r="P54" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q54" t="str">
+        <v/>
+      </c>
+      <c r="R54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>A</v>
+      </c>
+      <c r="B55">
+        <v>5</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Upper body + rotational power</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F55">
+        <v>9</v>
+      </c>
+      <c r="G55" t="str">
+        <v>A-d5s9</v>
+      </c>
+      <c r="H55" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
+        <v/>
+      </c>
+      <c r="L55" t="str">
+        <v>db6</v>
+      </c>
+      <c r="M55" t="str">
+        <v>DB 6 Ways</v>
+      </c>
+      <c r="N55" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O55">
+        <v>10</v>
+      </c>
+      <c r="P55" t="str">
+        <v/>
+      </c>
+      <c r="Q55" t="str">
+        <v>2 × 6</v>
+      </c>
+      <c r="R55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>A</v>
+      </c>
+      <c r="B56">
+        <v>5</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Upper body + rotational power</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F56">
+        <v>10</v>
+      </c>
+      <c r="G56" t="str">
+        <v>A-d5s10</v>
+      </c>
+      <c r="H56" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
+        <v/>
+      </c>
+      <c r="L56" t="str">
+        <v>spinal</v>
+      </c>
+      <c r="M56" t="str">
+        <v>Spinal Waves</v>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
+      <c r="P56" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q56" t="str">
+        <v/>
+      </c>
+      <c r="R56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>A</v>
+      </c>
+      <c r="B57">
+        <v>6</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Lower body + reactive power</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57" t="str">
+        <v>A-d6s1</v>
+      </c>
+      <c r="H57" t="str">
+        <v>Plyometric</v>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <v/>
+      </c>
+      <c r="L57" t="str">
+        <v>pogo</v>
+      </c>
+      <c r="M57" t="str">
+        <v>Pogo Hops</v>
+      </c>
+      <c r="N57" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
+      <c r="P57" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q57" t="str">
+        <v>3 × 10</v>
+      </c>
+      <c r="R57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>A</v>
+      </c>
+      <c r="B58">
+        <v>6</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Lower body + reactive power</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58">
+        <v>2</v>
+      </c>
+      <c r="G58" t="str">
+        <v>A-d6s2</v>
+      </c>
+      <c r="H58" t="str">
+        <v>Plyometric</v>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
+        <v/>
+      </c>
+      <c r="L58" t="str">
+        <v>skater</v>
+      </c>
+      <c r="M58" t="str">
+        <v>Lateral Bound / Skater Hop with Stick</v>
+      </c>
+      <c r="N58" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
+      <c r="P58" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q58" t="str">
+        <v>3 × 5, hold 3 s</v>
+      </c>
+      <c r="R58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>A</v>
+      </c>
+      <c r="B59">
+        <v>6</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Lower body + reactive power</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59">
+        <v>3</v>
+      </c>
+      <c r="G59" t="str">
+        <v>A-d6s3</v>
+      </c>
+      <c r="H59" t="str">
+        <v>Plyometric</v>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
+        <v/>
+      </c>
+      <c r="L59" t="str">
+        <v>splitjump</v>
+      </c>
+      <c r="M59" t="str">
+        <v>Split Squat Jumps</v>
+      </c>
+      <c r="N59" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
+      <c r="P59" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q59" t="str">
+        <v>3 × 5</v>
+      </c>
+      <c r="R59" t="str">
+        <v>Vertical drive, soft landings</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>A</v>
+      </c>
+      <c r="B60">
+        <v>6</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Lower body + reactive power</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60">
+        <v>4</v>
+      </c>
+      <c r="G60" t="str">
+        <v>A-d6s4</v>
+      </c>
+      <c r="H60" t="str">
+        <v>Plyometric</v>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
+        <v/>
+      </c>
+      <c r="L60" t="str">
+        <v>depthcombo</v>
+      </c>
+      <c r="M60" t="str">
+        <v>Depth Drop → Broad Jump → Box Jump</v>
+      </c>
+      <c r="N60" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+      <c r="P60" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q60" t="str">
+        <v>4 × 5</v>
+      </c>
+      <c r="R60" t="str">
+        <v>Controlled landings</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>A</v>
+      </c>
+      <c r="B61">
+        <v>6</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Lower body + reactive power</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61">
+        <v>5</v>
+      </c>
+      <c r="G61" t="str">
+        <v>A-d6s5</v>
+      </c>
+      <c r="H61" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I61" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J61" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
+        <v>arnold</v>
+      </c>
+      <c r="M61" t="str">
+        <v>Arnold Press</v>
+      </c>
+      <c r="N61" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O61">
+        <v>35</v>
+      </c>
+      <c r="P61" t="str">
+        <v/>
+      </c>
+      <c r="Q61" t="str">
+        <v/>
+      </c>
+      <c r="R61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>A</v>
+      </c>
+      <c r="B62">
+        <v>6</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Lower body + reactive power</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62">
+        <v>5</v>
+      </c>
+      <c r="G62" t="str">
+        <v>A-d6s5</v>
+      </c>
+      <c r="H62" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I62" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J62" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K62" t="str">
+        <v/>
+      </c>
+      <c r="L62" t="str">
+        <v>zercher</v>
+      </c>
+      <c r="M62" t="str">
+        <v>Seated Zercher Good Morning</v>
+      </c>
+      <c r="N62" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O62">
+        <v>50</v>
+      </c>
+      <c r="P62" t="str">
+        <v/>
+      </c>
+      <c r="Q62" t="str">
+        <v/>
+      </c>
+      <c r="R62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>A</v>
+      </c>
+      <c r="B63">
+        <v>6</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Lower body + reactive power</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63">
+        <v>6</v>
+      </c>
+      <c r="G63" t="str">
+        <v>A-d6s6</v>
+      </c>
+      <c r="H63" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I63" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J63" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K63" t="str">
+        <v/>
+      </c>
+      <c r="L63" t="str">
+        <v>pallof</v>
+      </c>
+      <c r="M63" t="str">
+        <v>Pallof Press</v>
+      </c>
+      <c r="N63" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O63">
+        <v>30</v>
+      </c>
+      <c r="P63" t="str">
+        <v/>
+      </c>
+      <c r="Q63" t="str">
+        <v/>
+      </c>
+      <c r="R63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>A</v>
+      </c>
+      <c r="B64">
+        <v>6</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Lower body + reactive power</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64">
+        <v>6</v>
+      </c>
+      <c r="G64" t="str">
+        <v>A-d6s6</v>
+      </c>
+      <c r="H64" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I64" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J64" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K64" t="str">
+        <v/>
+      </c>
+      <c r="L64" t="str">
+        <v>cablerow</v>
+      </c>
+      <c r="M64" t="str">
+        <v>Explosive Unilateral Cable Row</v>
+      </c>
+      <c r="N64" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O64">
+        <v>30</v>
+      </c>
+      <c r="P64" t="str">
+        <v/>
+      </c>
+      <c r="Q64" t="str">
+        <v/>
+      </c>
+      <c r="R64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>A</v>
+      </c>
+      <c r="B65">
+        <v>7</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Day 7</v>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+      <c r="K65" t="str">
+        <v/>
+      </c>
+      <c r="L65" t="str">
+        <v/>
+      </c>
+      <c r="M65" t="str">
+        <v/>
+      </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+      <c r="P65" t="str">
+        <v/>
+      </c>
+      <c r="Q65" t="str">
+        <v/>
+      </c>
+      <c r="R65" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:R65"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:R65"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Program</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Warm-up</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>A</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B2"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F1"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="36.83203125" customWidth="1"/>
+    <col min="3" max="3" width="7.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="9.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>From</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Saved at</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Auto-saved</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Created</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -12,20 +12,22 @@
     <sheet name="Programs" sheetId="7" r:id="rId7"/>
     <sheet name="Program info" sheetId="8" r:id="rId8"/>
     <sheet name="Saved versions" sheetId="9" r:id="rId9"/>
-    <sheet name="Check-offs" sheetId="10" r:id="rId10"/>
-    <sheet name="Config" sheetId="11" r:id="rId11"/>
+    <sheet name="Experiments" sheetId="10" r:id="rId10"/>
+    <sheet name="Check-offs" sheetId="11" r:id="rId11"/>
+    <sheet name="Config" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">Weeks!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Body weight'!$A$1:$D$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5">Settings!$A$1:$B$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5">Settings!$A$1:$B$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">Programs!$A$1:$R$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Program info'!$A$1:$B$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9">'Check-offs'!$A$1:$D$57</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10">Config!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11">Config!$A$1:$B$16</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -419,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J16"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -494,7 +496,7 @@
         <v>-10</v>
       </c>
       <c r="J2">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -526,7 +528,7 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -558,108 +560,108 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Desk Bands</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="B5" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-09-29</v>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5" t="str">
-        <v/>
+        <v>2026-09-28</v>
+      </c>
+      <c r="F5">
+        <v>200</v>
+      </c>
+      <c r="G5">
+        <v>200</v>
+      </c>
+      <c r="H5">
+        <v>200</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>235</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Grip Trainer</v>
+        <v>Hack Squat</v>
       </c>
       <c r="B6" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-30</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-01</v>
       </c>
       <c r="F6">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="G6">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="H6">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>300</v>
+        <v>415</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Hack Squat</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="B7" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="E7" t="str">
         <v>2026-09-30</v>
       </c>
-      <c r="E7" t="str">
-        <v>2026-10-01</v>
-      </c>
       <c r="F7">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="G7">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="H7">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>400</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Hip Thrust</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="B8" t="str">
         <v>Strength</v>
@@ -674,62 +676,62 @@
         <v>2026-09-30</v>
       </c>
       <c r="F8">
-        <v>320</v>
+        <v>180</v>
       </c>
       <c r="G8">
-        <v>320</v>
+        <v>180</v>
       </c>
       <c r="H8">
-        <v>320</v>
+        <v>180</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>400</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="B9" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-09-30</v>
+        <v>2026-09-29</v>
       </c>
       <c r="F9">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="G9">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="H9">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>200</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Kneeling Cable Ab Crunch</v>
       </c>
       <c r="B10" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="str">
         <v>2026-09-29</v>
@@ -738,59 +740,59 @@
         <v>2026-09-29</v>
       </c>
       <c r="F10">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="G10">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="H10">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="I10">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Kneeling Cable Ab Crunch</v>
+        <v>Lat Pulldown, alternating single-arm</v>
       </c>
       <c r="B11" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-28</v>
       </c>
       <c r="F11">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="G11">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="H11">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Lat Pulldown, alternating single-arm</v>
+        <v>Leg Extension ISO hold</v>
       </c>
       <c r="B12" t="str">
-        <v>Hypertrophy</v>
+        <v>Isometric</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -799,51 +801,51 @@
         <v>2026-09-28</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="F12">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G12">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H12">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>90</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Leg Extension ISO hold</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="B13" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="str">
         <v>2026-09-28</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-01</v>
       </c>
       <c r="F13">
         <v>50</v>
       </c>
       <c r="G13">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H13">
         <v>50</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J13">
         <v>80</v>
@@ -851,74 +853,74 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="B14" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="str">
         <v>2026-09-28</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-10-01</v>
+        <v>2026-09-28</v>
       </c>
       <c r="F14">
         <v>50</v>
       </c>
       <c r="G14">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H14">
         <v>50</v>
       </c>
       <c r="I14">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>80</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Suitcase Bottom-Up, single-arm</v>
       </c>
       <c r="B15" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="F15">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G15">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H15">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>80</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Suitcase Bottom-Up, single-arm</v>
+        <v>Zottman Curl</v>
       </c>
       <c r="B16" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -930,64 +932,85 @@
         <v>2026-09-29</v>
       </c>
       <c r="F16">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G16">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H16">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Zottman Curl</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Hypertrophy</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17" t="str">
-        <v>2026-09-29</v>
-      </c>
-      <c r="E17" t="str">
-        <v>2026-09-29</v>
-      </c>
-      <c r="F17">
-        <v>20</v>
-      </c>
-      <c r="G17">
-        <v>20</v>
-      </c>
-      <c r="H17">
-        <v>20</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J17"/>
+  <autoFilter ref="A1:J16"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J16"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:E2"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" customWidth="1"/>
+    <col min="5" max="5" width="40.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Exercise id</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Exercise</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Phase</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Note</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Emurmrw6glcpc</v>
+      </c>
+      <c r="B2" t="str">
+        <v>deadlift</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Deadlift</v>
+      </c>
+      <c r="D2" t="str">
+        <v>strength</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E2"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D60"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.83203125" customWidth="1"/>
@@ -1014,13 +1037,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B2" t="str">
-        <v>done</v>
+        <v>rest</v>
       </c>
       <c r="C2" t="str">
-        <v>A-d1s1</v>
+        <v/>
       </c>
       <c r="D2" t="str">
-        <v>Yes</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1028,13 +1051,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B3" t="str">
-        <v>done</v>
+        <v>restOn</v>
       </c>
       <c r="C3" t="str">
-        <v>A-d1s2</v>
+        <v/>
       </c>
       <c r="D3" t="str">
-        <v>Yes</v>
+        <v>2026-10-02</v>
       </c>
     </row>
     <row r="4">
@@ -1045,7 +1068,7 @@
         <v>done</v>
       </c>
       <c r="C4" t="str">
-        <v>A-d1s4</v>
+        <v>A-d1s1</v>
       </c>
       <c r="D4" t="str">
         <v>Yes</v>
@@ -1059,7 +1082,7 @@
         <v>done</v>
       </c>
       <c r="C5" t="str">
-        <v>A-d1s6</v>
+        <v>A-d1s2</v>
       </c>
       <c r="D5" t="str">
         <v>Yes</v>
@@ -1073,7 +1096,7 @@
         <v>done</v>
       </c>
       <c r="C6" t="str">
-        <v>A-d1s8</v>
+        <v>A-d1s4</v>
       </c>
       <c r="D6" t="str">
         <v>Yes</v>
@@ -1087,7 +1110,7 @@
         <v>done</v>
       </c>
       <c r="C7" t="str">
-        <v>A-d2s3</v>
+        <v>A-d1s6</v>
       </c>
       <c r="D7" t="str">
         <v>Yes</v>
@@ -1101,7 +1124,7 @@
         <v>done</v>
       </c>
       <c r="C8" t="str">
-        <v>A-d2s5</v>
+        <v>A-d1s8</v>
       </c>
       <c r="D8" t="str">
         <v>Yes</v>
@@ -1115,7 +1138,7 @@
         <v>done</v>
       </c>
       <c r="C9" t="str">
-        <v>A-d3s2</v>
+        <v>A-d2s3</v>
       </c>
       <c r="D9" t="str">
         <v>Yes</v>
@@ -1129,7 +1152,7 @@
         <v>done</v>
       </c>
       <c r="C10" t="str">
-        <v>A-d3s3</v>
+        <v>A-d2s5</v>
       </c>
       <c r="D10" t="str">
         <v>Yes</v>
@@ -1143,7 +1166,7 @@
         <v>done</v>
       </c>
       <c r="C11" t="str">
-        <v>A-d2s2</v>
+        <v>A-d3s2</v>
       </c>
       <c r="D11" t="str">
         <v>Yes</v>
@@ -1157,7 +1180,7 @@
         <v>done</v>
       </c>
       <c r="C12" t="str">
-        <v>A-d2s2#0</v>
+        <v>A-d3s3</v>
       </c>
       <c r="D12" t="str">
         <v>Yes</v>
@@ -1171,7 +1194,7 @@
         <v>done</v>
       </c>
       <c r="C13" t="str">
-        <v>A-d3s6</v>
+        <v>A-d2s2</v>
       </c>
       <c r="D13" t="str">
         <v>Yes</v>
@@ -1185,7 +1208,7 @@
         <v>done</v>
       </c>
       <c r="C14" t="str">
-        <v>A-d3s6#0</v>
+        <v>A-d2s2#0</v>
       </c>
       <c r="D14" t="str">
         <v>Yes</v>
@@ -1199,7 +1222,7 @@
         <v>done</v>
       </c>
       <c r="C15" t="str">
-        <v>A-d2s4</v>
+        <v>A-d3s6</v>
       </c>
       <c r="D15" t="str">
         <v>Yes</v>
@@ -1213,7 +1236,7 @@
         <v>done</v>
       </c>
       <c r="C16" t="str">
-        <v>A-d1s7</v>
+        <v>A-d3s6#0</v>
       </c>
       <c r="D16" t="str">
         <v>Yes</v>
@@ -1227,7 +1250,7 @@
         <v>done</v>
       </c>
       <c r="C17" t="str">
-        <v>A-d3s5</v>
+        <v>A-d2s4</v>
       </c>
       <c r="D17" t="str">
         <v>Yes</v>
@@ -1241,7 +1264,7 @@
         <v>done</v>
       </c>
       <c r="C18" t="str">
-        <v>A-d3s1</v>
+        <v>A-d1s7</v>
       </c>
       <c r="D18" t="str">
         <v>Yes</v>
@@ -1255,7 +1278,7 @@
         <v>done</v>
       </c>
       <c r="C19" t="str">
-        <v>A-d4s5</v>
+        <v>A-d3s5</v>
       </c>
       <c r="D19" t="str">
         <v>Yes</v>
@@ -1269,7 +1292,7 @@
         <v>done</v>
       </c>
       <c r="C20" t="str">
-        <v>A-d4s2</v>
+        <v>A-d3s1</v>
       </c>
       <c r="D20" t="str">
         <v>Yes</v>
@@ -1283,7 +1306,7 @@
         <v>done</v>
       </c>
       <c r="C21" t="str">
-        <v>A-d4s4</v>
+        <v>A-d4s5</v>
       </c>
       <c r="D21" t="str">
         <v>Yes</v>
@@ -1297,7 +1320,7 @@
         <v>done</v>
       </c>
       <c r="C22" t="str">
-        <v>A-d6s5</v>
+        <v>A-d4s2</v>
       </c>
       <c r="D22" t="str">
         <v>Yes</v>
@@ -1311,7 +1334,7 @@
         <v>done</v>
       </c>
       <c r="C23" t="str">
-        <v>A-d5s3</v>
+        <v>A-d4s4</v>
       </c>
       <c r="D23" t="str">
         <v>Yes</v>
@@ -1322,10 +1345,10 @@
         <v>2026-09-27</v>
       </c>
       <c r="B24" t="str">
-        <v>skipped</v>
+        <v>done</v>
       </c>
       <c r="C24" t="str">
-        <v>A-d1s9</v>
+        <v>A-d6s5</v>
       </c>
       <c r="D24" t="str">
         <v>Yes</v>
@@ -1336,10 +1359,10 @@
         <v>2026-09-27</v>
       </c>
       <c r="B25" t="str">
-        <v>skipped</v>
+        <v>done</v>
       </c>
       <c r="C25" t="str">
-        <v>A-d1s5</v>
+        <v>A-d5s3</v>
       </c>
       <c r="D25" t="str">
         <v>Yes</v>
@@ -1353,7 +1376,7 @@
         <v>skipped</v>
       </c>
       <c r="C26" t="str">
-        <v>A-d1s3</v>
+        <v>A-d1s9</v>
       </c>
       <c r="D26" t="str">
         <v>Yes</v>
@@ -1367,7 +1390,7 @@
         <v>skipped</v>
       </c>
       <c r="C27" t="str">
-        <v>A-d2s6</v>
+        <v>A-d1s5</v>
       </c>
       <c r="D27" t="str">
         <v>Yes</v>
@@ -1381,7 +1404,7 @@
         <v>skipped</v>
       </c>
       <c r="C28" t="str">
-        <v>A-d2s8</v>
+        <v>A-d2s6</v>
       </c>
       <c r="D28" t="str">
         <v>Yes</v>
@@ -1395,7 +1418,7 @@
         <v>skipped</v>
       </c>
       <c r="C29" t="str">
-        <v>A-d2s7</v>
+        <v>A-d2s8</v>
       </c>
       <c r="D29" t="str">
         <v>Yes</v>
@@ -1409,7 +1432,7 @@
         <v>skipped</v>
       </c>
       <c r="C30" t="str">
-        <v>A-d3s7</v>
+        <v>A-d2s7</v>
       </c>
       <c r="D30" t="str">
         <v>Yes</v>
@@ -1423,7 +1446,7 @@
         <v>skipped</v>
       </c>
       <c r="C31" t="str">
-        <v>A-d3s4</v>
+        <v>A-d3s7</v>
       </c>
       <c r="D31" t="str">
         <v>Yes</v>
@@ -1437,7 +1460,7 @@
         <v>skipped</v>
       </c>
       <c r="C32" t="str">
-        <v>A-d3s9</v>
+        <v>A-d3s4</v>
       </c>
       <c r="D32" t="str">
         <v>Yes</v>
@@ -1451,7 +1474,7 @@
         <v>skipped</v>
       </c>
       <c r="C33" t="str">
-        <v>A-d3s8</v>
+        <v>A-d3s9</v>
       </c>
       <c r="D33" t="str">
         <v>Yes</v>
@@ -1465,7 +1488,7 @@
         <v>skipped</v>
       </c>
       <c r="C34" t="str">
-        <v>A-d4s1</v>
+        <v>A-d3s8</v>
       </c>
       <c r="D34" t="str">
         <v>Yes</v>
@@ -1479,7 +1502,7 @@
         <v>skipped</v>
       </c>
       <c r="C35" t="str">
-        <v>A-d4s3</v>
+        <v>A-d4s1</v>
       </c>
       <c r="D35" t="str">
         <v>Yes</v>
@@ -1493,7 +1516,7 @@
         <v>skipped</v>
       </c>
       <c r="C36" t="str">
-        <v>A-d4s8</v>
+        <v>A-d4s3</v>
       </c>
       <c r="D36" t="str">
         <v>Yes</v>
@@ -1507,7 +1530,7 @@
         <v>skipped</v>
       </c>
       <c r="C37" t="str">
-        <v>A-d4s7</v>
+        <v>A-d4s8</v>
       </c>
       <c r="D37" t="str">
         <v>Yes</v>
@@ -1521,7 +1544,7 @@
         <v>skipped</v>
       </c>
       <c r="C38" t="str">
-        <v>A-d5s9</v>
+        <v>A-d4s7</v>
       </c>
       <c r="D38" t="str">
         <v>Yes</v>
@@ -1535,7 +1558,7 @@
         <v>skipped</v>
       </c>
       <c r="C39" t="str">
-        <v>A-d5s10</v>
+        <v>A-d5s9</v>
       </c>
       <c r="D39" t="str">
         <v>Yes</v>
@@ -1549,7 +1572,7 @@
         <v>skipped</v>
       </c>
       <c r="C40" t="str">
-        <v>A-d2s1</v>
+        <v>A-d5s10</v>
       </c>
       <c r="D40" t="str">
         <v>Yes</v>
@@ -1563,7 +1586,7 @@
         <v>skipped</v>
       </c>
       <c r="C41" t="str">
-        <v>A-d4s6</v>
+        <v>A-d2s1</v>
       </c>
       <c r="D41" t="str">
         <v>Yes</v>
@@ -1574,13 +1597,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B42" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C42" t="str">
-        <v>A-d3s2</v>
-      </c>
-      <c r="D42">
-        <v>2</v>
+        <v>A-d4s6</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="43">
@@ -1588,13 +1611,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B43" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C43" t="str">
-        <v>A-d3s3</v>
-      </c>
-      <c r="D43">
-        <v>2</v>
+        <v>A-d1s3</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="44">
@@ -1605,10 +1628,10 @@
         <v>moved</v>
       </c>
       <c r="C44" t="str">
-        <v>A-d2s4</v>
+        <v>A-d3s2</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -1619,10 +1642,10 @@
         <v>moved</v>
       </c>
       <c r="C45" t="str">
-        <v>A-d1s7</v>
+        <v>A-d3s3</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -1633,10 +1656,10 @@
         <v>moved</v>
       </c>
       <c r="C46" t="str">
-        <v>A-d3s6</v>
+        <v>A-d2s4</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -1647,10 +1670,10 @@
         <v>moved</v>
       </c>
       <c r="C47" t="str">
-        <v>A-d3s1</v>
+        <v>A-d1s7</v>
       </c>
       <c r="D47">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -1661,10 +1684,10 @@
         <v>moved</v>
       </c>
       <c r="C48" t="str">
-        <v>A-d4s6</v>
+        <v>A-d3s6</v>
       </c>
       <c r="D48">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -1675,10 +1698,10 @@
         <v>moved</v>
       </c>
       <c r="C49" t="str">
-        <v>A-d2s1</v>
+        <v>A-d3s1</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -1689,7 +1712,7 @@
         <v>moved</v>
       </c>
       <c r="C50" t="str">
-        <v>A-d6s5</v>
+        <v>A-d4s6</v>
       </c>
       <c r="D50">
         <v>5</v>
@@ -1703,10 +1726,10 @@
         <v>moved</v>
       </c>
       <c r="C51" t="str">
-        <v>A-d5s8</v>
+        <v>A-d2s1</v>
       </c>
       <c r="D51">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -1717,10 +1740,10 @@
         <v>moved</v>
       </c>
       <c r="C52" t="str">
-        <v>A-d5s7</v>
+        <v>A-d6s5</v>
       </c>
       <c r="D52">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -1731,7 +1754,7 @@
         <v>moved</v>
       </c>
       <c r="C53" t="str">
-        <v>A-d5s6</v>
+        <v>A-d5s8</v>
       </c>
       <c r="D53">
         <v>6</v>
@@ -1745,7 +1768,7 @@
         <v>moved</v>
       </c>
       <c r="C54" t="str">
-        <v>A-d5s5</v>
+        <v>A-d5s7</v>
       </c>
       <c r="D54">
         <v>6</v>
@@ -1759,7 +1782,7 @@
         <v>moved</v>
       </c>
       <c r="C55" t="str">
-        <v>A-d5s4</v>
+        <v>A-d5s6</v>
       </c>
       <c r="D55">
         <v>6</v>
@@ -1773,7 +1796,7 @@
         <v>moved</v>
       </c>
       <c r="C56" t="str">
-        <v>A-d5s2</v>
+        <v>A-d5s5</v>
       </c>
       <c r="D56">
         <v>6</v>
@@ -1787,23 +1810,65 @@
         <v>moved</v>
       </c>
       <c r="C57" t="str">
-        <v>A-d5s1</v>
+        <v>A-d5s4</v>
       </c>
       <c r="D57">
         <v>6</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B58" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C58" t="str">
+        <v>A-d5s2</v>
+      </c>
+      <c r="D58">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B59" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C59" t="str">
+        <v>A-d5s1</v>
+      </c>
+      <c r="D59">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B60" t="str">
+        <v>prog</v>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60" t="str">
+        <v>A</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D57"/>
+  <autoFilter ref="A1:D60"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D57"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D60"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B16"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -1819,111 +1884,135 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ex</v>
+        <v>bwGoal</v>
       </c>
       <c r="B2" t="str">
-        <v>{}</v>
+        <v>{"w":155,"start":{"w":130,"d":"2026-10-02"}}</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ghBackup</v>
+        <v>ex</v>
       </c>
       <c r="B3" t="str">
-        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"1r0xg3l","last":{"at":"2026-10-02T02:07:33.781Z","url":"https://github.com/jacgit18/iron-log/commit/34dcc108fb277928b41a6ef04e695a35b5d7f16f"}}</v>
+        <v>{"deadlift":{"n":"Deadlift","eq":"barbell"}}</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>m2Even</v>
+        <v>exPh</v>
       </c>
       <c r="B4" t="str">
-        <v>"B"</v>
+        <v>{"canoe":"iso","romanadd":"strength","deskbands":"iso","spinal":"mob","platerot":"strength"}</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>m3First</v>
+        <v>ghBackup</v>
       </c>
       <c r="B5" t="str">
-        <v>"A"</v>
+        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":null,"last":{"at":"2026-10-02T02:07:33.781Z","url":"https://github.com/jacgit18/iron-log/commit/34dcc108fb277928b41a6ef04e695a35b5d7f16f"}}</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>m3Start</v>
+        <v>liftGoals</v>
       </c>
       <c r="B6" t="str">
-        <v>1</v>
+        <v>{"deadlift":{"exp":{"w":185,"start":0},"strength":{"w":300,"start":0},"hyp":{"w":225,"start":0}}}</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>mode</v>
+        <v>m2Even</v>
       </c>
       <c r="B7" t="str">
-        <v>2</v>
+        <v>"B"</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>muscleMap</v>
+        <v>m3First</v>
       </c>
       <c r="B8" t="str">
-        <v>{}</v>
+        <v>"A"</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>pct</v>
+        <v>m3Start</v>
       </c>
       <c r="B9" t="str">
-        <v>{"strength":85,"iso":75,"hyp":65,"exp":45}</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>phDef</v>
+        <v>mode</v>
       </c>
       <c r="B10" t="str">
-        <v>{"A-d1s1:0":"hyp","A-d3s9:0":"iso","A-d4s1:0":"strength","A-d1s7:1":"iso"}</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>progNames</v>
+        <v>muscleMap</v>
       </c>
       <c r="B11" t="str">
-        <v>{"A":"Program A - Unilateral","B":"Program B - Bilateral"}</v>
+        <v>{}</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>rm</v>
+        <v>pct</v>
       </c>
       <c r="B12" t="str">
-        <v>{"latpd":90,"wristpd":55,"platerot":35,"innerthigh":200,"chestpress":45,"zercher":80,"zottman":30,"kbleg":30,"grip":300,"canoe":45,"suitcase":30,"reardelt":80,"facepull":50,"legext":80,"cablecrunch":100,"hipthrust":400,"db6":20,"hack":400,"pallof":40,"cablerow":70,"arnold":45,"dbclean":45,"latpdbi":90,"outerthigh":180,"farmers":65,"dblunge":65,"ohtri":30,"bss":65,"legcurl":100,"cablepunch":50}</v>
+        <v>{"strength":85,"iso":75,"hyp":65,"exp":45}</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
+        <v>phDef</v>
+      </c>
+      <c r="B13" t="str">
+        <v>{"A-d1s1:0":"hyp","A-d4s1:0":"strength","A-d1s7:1":"iso","A-d1s3:0":"strength"}</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>progNames</v>
+      </c>
+      <c r="B14" t="str">
+        <v>{"A":"Program A - Unilateral","B":"Program B - Bilateral"}</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>rm</v>
+      </c>
+      <c r="B15" t="str">
+        <v>{"latpd":70,"wristpd":48,"platerot":30,"innerthigh":210,"chestpress":40,"zercher":80,"zottman":23,"kbleg":21,"grip":235,"canoe":13.33,"suitcase":30,"reardelt":65,"facepull":50,"legext":65,"cablecrunch":100,"hipthrust":375,"db6":20,"hack":415,"pallof":40,"cablerow":70,"arnold":40,"dbclean":45,"latpdbi":90,"outerthigh":180,"farmers":65,"dblunge":65,"ohtri":30,"bss":65,"legcurl":100,"cablepunch":50}</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
         <v>rxOverride</v>
       </c>
-      <c r="B13" t="str">
+      <c r="B16" t="str">
         <v>{}</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B13"/>
+  <autoFilter ref="A1:B16"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B16"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O28"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -2608,31 +2697,31 @@
         <v>2026-09-27</v>
       </c>
       <c r="C15" t="str">
-        <v>Desk Bands</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="D15" t="str">
         <v>Isometric</v>
       </c>
-      <c r="E15" t="str">
-        <v/>
+      <c r="E15">
+        <v>15</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I15" t="str">
-        <v>BW×30s, BW×30s, BW×30s, BW×30s</v>
+        <v>15×15s, 15×15s, 15×15s</v>
       </c>
       <c r="J15" t="str">
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>Mobility</v>
+        <v>Abs, Hip flexors</v>
       </c>
       <c r="L15" t="str">
         <v/>
@@ -2641,10 +2730,10 @@
         <v/>
       </c>
       <c r="N15" t="str">
-        <v>A-d3s9</v>
+        <v>A-d1s7</v>
       </c>
       <c r="O15" t="str">
-        <v>deskbands</v>
+        <v>kbleg</v>
       </c>
     </row>
     <row r="16">
@@ -2655,43 +2744,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C16" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Kneeling Cable Ab Crunch</v>
       </c>
       <c r="D16" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="F16">
-        <v>3</v>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16">
-        <v>15</v>
+        <v>4</v>
+      </c>
+      <c r="G16">
+        <v>6</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>20×15s, 20×15s, 20×15s</v>
-      </c>
-      <c r="J16" t="str">
-        <v/>
+        <v>85×6, 85×6, 85×6, 85×6</v>
+      </c>
+      <c r="J16">
+        <v>2040</v>
       </c>
       <c r="K16" t="str">
-        <v>Abs, Hip flexors</v>
+        <v>Abs</v>
       </c>
       <c r="L16" t="str">
         <v/>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N16" t="str">
-        <v>A-d1s7</v>
+        <v>A-d2s4</v>
       </c>
       <c r="O16" t="str">
-        <v>kbleg</v>
+        <v>cablecrunch</v>
       </c>
     </row>
     <row r="17">
@@ -2702,31 +2791,31 @@
         <v>2026-09-27</v>
       </c>
       <c r="C17" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Leg Extension ISO hold</v>
       </c>
       <c r="D17" t="str">
         <v>Isometric</v>
       </c>
       <c r="E17">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I17" t="str">
-        <v>15×15s, 15×15s, 15×15s</v>
+        <v>50×30s, 50×30s, 50×30s, 50×30s</v>
       </c>
       <c r="J17" t="str">
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>Abs, Hip flexors</v>
+        <v>Quads</v>
       </c>
       <c r="L17" t="str">
         <v/>
@@ -2735,10 +2824,10 @@
         <v/>
       </c>
       <c r="N17" t="str">
-        <v>A-d1s7</v>
+        <v>A-d3s5</v>
       </c>
       <c r="O17" t="str">
-        <v>kbleg</v>
+        <v>legext</v>
       </c>
     </row>
     <row r="18">
@@ -2749,13 +2838,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="C18" t="str">
-        <v>Kneeling Cable Ab Crunch</v>
+        <v>Suitcase Bottom-Up, single-arm</v>
       </c>
       <c r="D18" t="str">
         <v>Strength</v>
       </c>
       <c r="E18">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="F18">
         <v>4</v>
@@ -2767,25 +2856,25 @@
         <v/>
       </c>
       <c r="I18" t="str">
-        <v>85×6, 85×6, 85×6, 85×6</v>
+        <v>25×6, 25×6, 25×6, 25×6</v>
       </c>
       <c r="J18">
-        <v>2040</v>
+        <v>600</v>
       </c>
       <c r="K18" t="str">
-        <v>Abs</v>
+        <v>Forearms &amp; grip, Obliques</v>
       </c>
       <c r="L18" t="str">
-        <v/>
+        <v>Traps</v>
       </c>
       <c r="M18" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N18" t="str">
-        <v>A-d2s4</v>
+        <v>A-d4s1</v>
       </c>
       <c r="O18" t="str">
-        <v>cablecrunch</v>
+        <v>suitcase</v>
       </c>
     </row>
     <row r="19">
@@ -2796,31 +2885,31 @@
         <v>2026-09-27</v>
       </c>
       <c r="C19" t="str">
-        <v>Leg Extension ISO hold</v>
+        <v>Zottman Curl</v>
       </c>
       <c r="D19" t="str">
-        <v>Isometric</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E19">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F19">
-        <v>4</v>
-      </c>
-      <c r="G19" t="str">
-        <v/>
-      </c>
-      <c r="H19">
-        <v>30</v>
+        <v>3</v>
+      </c>
+      <c r="G19">
+        <v>15</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
       </c>
       <c r="I19" t="str">
-        <v>50×30s, 50×30s, 50×30s, 50×30s</v>
-      </c>
-      <c r="J19" t="str">
-        <v/>
+        <v>15×15, 15×15, 15×15</v>
+      </c>
+      <c r="J19">
+        <v>675</v>
       </c>
       <c r="K19" t="str">
-        <v>Quads</v>
+        <v>Biceps, Forearms &amp; grip</v>
       </c>
       <c r="L19" t="str">
         <v/>
@@ -2829,27 +2918,27 @@
         <v/>
       </c>
       <c r="N19" t="str">
-        <v>A-d3s5</v>
+        <v>A-d1s7</v>
       </c>
       <c r="O19" t="str">
-        <v>legext</v>
+        <v>zottman</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-30</v>
       </c>
       <c r="B20" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="C20" t="str">
-        <v>Suitcase Bottom-Up, single-arm</v>
+        <v>Arnold Press</v>
       </c>
       <c r="D20" t="str">
         <v>Strength</v>
       </c>
       <c r="E20">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F20">
         <v>4</v>
@@ -2861,72 +2950,72 @@
         <v/>
       </c>
       <c r="I20" t="str">
-        <v>25×6, 25×6, 25×6, 25×6</v>
+        <v>35×6, 35×6, 30×6, 30×6</v>
       </c>
       <c r="J20">
-        <v>600</v>
+        <v>780</v>
       </c>
       <c r="K20" t="str">
-        <v>Forearms &amp; grip, Obliques</v>
+        <v>Front delts, Side delts</v>
       </c>
       <c r="L20" t="str">
-        <v>Traps</v>
+        <v>Triceps</v>
       </c>
       <c r="M20" t="str">
         <v/>
       </c>
       <c r="N20" t="str">
-        <v>A-d4s1</v>
+        <v>A-d4s4</v>
       </c>
       <c r="O20" t="str">
-        <v>suitcase</v>
+        <v>arnold</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-30</v>
       </c>
       <c r="B21" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="C21" t="str">
-        <v>Zottman Curl</v>
+        <v>Chest Press</v>
       </c>
       <c r="D21" t="str">
         <v>Hypertrophy</v>
       </c>
       <c r="E21">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H21" t="str">
         <v/>
       </c>
       <c r="I21" t="str">
-        <v>20×15, 20×15, 20×15</v>
+        <v>25×15, 25×10</v>
       </c>
       <c r="J21">
-        <v>900</v>
+        <v>625</v>
       </c>
       <c r="K21" t="str">
-        <v>Biceps, Forearms &amp; grip</v>
+        <v>Chest</v>
       </c>
       <c r="L21" t="str">
-        <v/>
+        <v>Front delts, Triceps</v>
       </c>
       <c r="M21" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N21" t="str">
-        <v>A-d1s7</v>
+        <v>A-d4s5</v>
       </c>
       <c r="O21" t="str">
-        <v>zottman</v>
+        <v>chestpress</v>
       </c>
     </row>
     <row r="22">
@@ -2937,43 +3026,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C22" t="str">
-        <v>Arnold Press</v>
+        <v>Hack Squat</v>
       </c>
       <c r="D22" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E22">
-        <v>35</v>
+        <v>270</v>
       </c>
       <c r="F22">
         <v>4</v>
       </c>
       <c r="G22">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H22" t="str">
         <v/>
       </c>
       <c r="I22" t="str">
-        <v>35×6, 35×6, 30×6, 30×6</v>
+        <v>270×15, 270×15, 270×15, 270×15</v>
       </c>
       <c r="J22">
-        <v>780</v>
+        <v>16200</v>
       </c>
       <c r="K22" t="str">
-        <v>Front delts, Side delts</v>
+        <v>Quads</v>
       </c>
       <c r="L22" t="str">
-        <v>Triceps</v>
+        <v>Glutes, Inner thigh (adductors)</v>
       </c>
       <c r="M22" t="str">
         <v/>
       </c>
       <c r="N22" t="str">
-        <v>A-d4s4</v>
+        <v>A-d3s1</v>
       </c>
       <c r="O22" t="str">
-        <v>arnold</v>
+        <v>hack</v>
       </c>
     </row>
     <row r="23">
@@ -2984,34 +3073,34 @@
         <v>2026-09-27</v>
       </c>
       <c r="C23" t="str">
-        <v>Chest Press</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="D23" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E23">
-        <v>25</v>
+        <v>320</v>
       </c>
       <c r="F23">
         <v>2</v>
       </c>
       <c r="G23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H23" t="str">
         <v/>
       </c>
       <c r="I23" t="str">
-        <v>25×15, 25×10</v>
+        <v>320×6, 320×6</v>
       </c>
       <c r="J23">
-        <v>625</v>
+        <v>3840</v>
       </c>
       <c r="K23" t="str">
-        <v>Chest</v>
+        <v>Glutes</v>
       </c>
       <c r="L23" t="str">
-        <v>Front delts, Triceps</v>
+        <v>Hamstrings</v>
       </c>
       <c r="M23" t="str">
         <v/>
@@ -3020,7 +3109,7 @@
         <v>A-d4s5</v>
       </c>
       <c r="O23" t="str">
-        <v>chestpress</v>
+        <v>hipthrust</v>
       </c>
     </row>
     <row r="24">
@@ -3031,43 +3120,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C24" t="str">
-        <v>Hack Squat</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="D24" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E24">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="F24">
         <v>4</v>
       </c>
       <c r="G24">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H24" t="str">
         <v/>
       </c>
       <c r="I24" t="str">
-        <v>270×15, 270×15, 270×15, 270×15</v>
+        <v>180×6, 180×6, 180×6, 180×6</v>
       </c>
       <c r="J24">
-        <v>16200</v>
+        <v>4320</v>
       </c>
       <c r="K24" t="str">
-        <v>Quads</v>
+        <v>Inner thigh (adductors)</v>
       </c>
       <c r="L24" t="str">
-        <v>Glutes, Inner thigh (adductors)</v>
+        <v/>
       </c>
       <c r="M24" t="str">
         <v/>
       </c>
       <c r="N24" t="str">
-        <v>A-d3s1</v>
+        <v>A-d4s2</v>
       </c>
       <c r="O24" t="str">
-        <v>hack</v>
+        <v>innerthigh</v>
       </c>
     </row>
     <row r="25">
@@ -3078,16 +3167,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="C25" t="str">
-        <v>Hip Thrust</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="D25" t="str">
         <v>Strength</v>
       </c>
       <c r="E25">
-        <v>320</v>
+        <v>50</v>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G25">
         <v>6</v>
@@ -3096,45 +3185,45 @@
         <v/>
       </c>
       <c r="I25" t="str">
-        <v>320×6, 320×6</v>
+        <v>50×6, 50×6, 50×6, 50×6</v>
       </c>
       <c r="J25">
-        <v>3840</v>
+        <v>1200</v>
       </c>
       <c r="K25" t="str">
-        <v>Glutes</v>
+        <v>Lower back</v>
       </c>
       <c r="L25" t="str">
-        <v>Hamstrings</v>
+        <v>Glutes, Hamstrings, Upper back</v>
       </c>
       <c r="M25" t="str">
         <v/>
       </c>
       <c r="N25" t="str">
-        <v>A-d4s5</v>
+        <v>A-d4s4</v>
       </c>
       <c r="O25" t="str">
-        <v>hipthrust</v>
+        <v>zercher</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-09-30</v>
+        <v>2026-10-01</v>
       </c>
       <c r="B26" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="C26" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Arnold Press</v>
       </c>
       <c r="D26" t="str">
         <v>Strength</v>
       </c>
       <c r="E26">
-        <v>180</v>
+        <v>25</v>
       </c>
       <c r="F26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G26">
         <v>6</v>
@@ -3143,72 +3232,72 @@
         <v/>
       </c>
       <c r="I26" t="str">
-        <v>180×6, 180×6, 180×6, 180×6</v>
+        <v>25×6</v>
       </c>
       <c r="J26">
-        <v>4320</v>
+        <v>150</v>
       </c>
       <c r="K26" t="str">
-        <v>Inner thigh (adductors)</v>
+        <v>Front delts, Side delts</v>
       </c>
       <c r="L26" t="str">
-        <v/>
+        <v>Triceps</v>
       </c>
       <c r="M26" t="str">
         <v/>
       </c>
       <c r="N26" t="str">
-        <v>A-d4s2</v>
+        <v>A-d6s5</v>
       </c>
       <c r="O26" t="str">
-        <v>innerthigh</v>
+        <v>arnold</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-09-30</v>
+        <v>2026-10-01</v>
       </c>
       <c r="B27" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="C27" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Hack Squat</v>
       </c>
       <c r="D27" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E27">
-        <v>50</v>
+        <v>270</v>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H27" t="str">
         <v/>
       </c>
       <c r="I27" t="str">
-        <v>50×6, 50×6, 50×6, 50×6</v>
+        <v>270×15, 270×15, 270×15</v>
       </c>
       <c r="J27">
-        <v>1200</v>
+        <v>12150</v>
       </c>
       <c r="K27" t="str">
-        <v>Lower back</v>
+        <v>Quads</v>
       </c>
       <c r="L27" t="str">
-        <v>Glutes, Hamstrings, Upper back</v>
+        <v>Glutes, Inner thigh (adductors)</v>
       </c>
       <c r="M27" t="str">
         <v/>
       </c>
       <c r="N27" t="str">
-        <v>A-d4s4</v>
+        <v>A-d5s3</v>
       </c>
       <c r="O27" t="str">
-        <v>zercher</v>
+        <v>hack</v>
       </c>
     </row>
     <row r="28">
@@ -3219,13 +3308,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="C28" t="str">
-        <v>Arnold Press</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="D28" t="str">
         <v>Strength</v>
       </c>
       <c r="E28">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -3237,16 +3326,16 @@
         <v/>
       </c>
       <c r="I28" t="str">
-        <v>25×6</v>
+        <v>40×6</v>
       </c>
       <c r="J28">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="K28" t="str">
-        <v>Front delts, Side delts</v>
+        <v>Lower back</v>
       </c>
       <c r="L28" t="str">
-        <v>Triceps</v>
+        <v>Glutes, Hamstrings, Upper back</v>
       </c>
       <c r="M28" t="str">
         <v/>
@@ -3255,107 +3344,13 @@
         <v>A-d6s5</v>
       </c>
       <c r="O28" t="str">
-        <v>arnold</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>2026-10-01</v>
-      </c>
-      <c r="B29" t="str">
-        <v>2026-09-27</v>
-      </c>
-      <c r="C29" t="str">
-        <v>Hack Squat</v>
-      </c>
-      <c r="D29" t="str">
-        <v>Hypertrophy</v>
-      </c>
-      <c r="E29">
-        <v>270</v>
-      </c>
-      <c r="F29">
-        <v>3</v>
-      </c>
-      <c r="G29">
-        <v>15</v>
-      </c>
-      <c r="H29" t="str">
-        <v/>
-      </c>
-      <c r="I29" t="str">
-        <v>270×15, 270×15, 270×15</v>
-      </c>
-      <c r="J29">
-        <v>12150</v>
-      </c>
-      <c r="K29" t="str">
-        <v>Quads</v>
-      </c>
-      <c r="L29" t="str">
-        <v>Glutes, Inner thigh (adductors)</v>
-      </c>
-      <c r="M29" t="str">
-        <v/>
-      </c>
-      <c r="N29" t="str">
-        <v>A-d5s3</v>
-      </c>
-      <c r="O29" t="str">
-        <v>hack</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>2026-10-01</v>
-      </c>
-      <c r="B30" t="str">
-        <v>2026-09-27</v>
-      </c>
-      <c r="C30" t="str">
-        <v>Seated Zercher Good Morning</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="E30">
-        <v>40</v>
-      </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-      <c r="G30">
-        <v>6</v>
-      </c>
-      <c r="H30" t="str">
-        <v/>
-      </c>
-      <c r="I30" t="str">
-        <v>40×6</v>
-      </c>
-      <c r="J30">
-        <v>240</v>
-      </c>
-      <c r="K30" t="str">
-        <v>Lower back</v>
-      </c>
-      <c r="L30" t="str">
-        <v>Glutes, Hamstrings, Upper back</v>
-      </c>
-      <c r="M30" t="str">
-        <v/>
-      </c>
-      <c r="N30" t="str">
-        <v>A-d6s5</v>
-      </c>
-      <c r="O30" t="str">
         <v>zercher</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O30"/>
+  <autoFilter ref="A1:O28"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O28"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3495,7 +3490,7 @@
         <v>2026-09-27</v>
       </c>
       <c r="B8" t="str">
-        <v>Abs</v>
+        <v>Chest</v>
       </c>
       <c r="C8">
         <v>10</v>
@@ -3529,16 +3524,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B10" t="str">
-        <v>Chest</v>
+        <v>Lower back</v>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -3546,16 +3541,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B11" t="str">
-        <v>Lower back</v>
+        <v>Lats</v>
       </c>
       <c r="C11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -3563,16 +3558,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B12" t="str">
-        <v>Lats</v>
+        <v>Hamstrings</v>
       </c>
       <c r="C12">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13">
@@ -3580,7 +3575,7 @@
         <v>2026-09-27</v>
       </c>
       <c r="B13" t="str">
-        <v>Hamstrings</v>
+        <v>Triceps</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -3597,16 +3592,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B14" t="str">
-        <v>Triceps</v>
+        <v>Abs</v>
       </c>
       <c r="C14">
+        <v>7</v>
+      </c>
+      <c r="D14">
         <v>0</v>
       </c>
-      <c r="D14">
-        <v>15</v>
-      </c>
       <c r="E14">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -3631,16 +3626,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B16" t="str">
-        <v>Hip flexors</v>
+        <v>Side delts</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -3648,16 +3643,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B17" t="str">
-        <v>Side delts</v>
+        <v>Obliques</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -3665,16 +3660,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B18" t="str">
-        <v>Obliques</v>
+        <v>Hip flexors</v>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -3750,7 +3745,7 @@
         <v>A</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2">
         <v>26</v>
@@ -3765,7 +3760,7 @@
         <v>67</v>
       </c>
       <c r="H2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -3805,7 +3800,7 @@
         <v>2026-09-27</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-02</v>
       </c>
       <c r="C2">
         <v>130</v>
@@ -3824,7 +3819,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B41"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -3904,256 +3899,264 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1RM: Arnold Press</v>
+        <v>Mobility % of 1RM</v>
       </c>
       <c r="B10">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>1RM: Bulgarian Split Squat</v>
+        <v>1RM: Arnold Press</v>
       </c>
       <c r="B11">
-        <v>65</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>1RM: Kneeling Cable Ab Crunch</v>
+        <v>1RM: Bulgarian Split Squat</v>
       </c>
       <c r="B12">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>1RM: Cable Punch ISO hold</v>
+        <v>1RM: Kneeling Cable Ab Crunch</v>
       </c>
       <c r="B13">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>1RM: Explosive Unilateral Cable Row</v>
+        <v>1RM: Cable Punch ISO hold</v>
       </c>
       <c r="B14">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>1RM: Canoe Stretch</v>
+        <v>1RM: Explosive Unilateral Cable Row</v>
       </c>
       <c r="B15">
-        <v>45</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>1RM: Chest Press</v>
+        <v>1RM: Canoe Stretch</v>
       </c>
       <c r="B16">
-        <v>45</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>1RM: DB 6 Ways</v>
+        <v>1RM: Chest Press</v>
       </c>
       <c r="B17">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>1RM: DB Clean &amp; Jerk Press</v>
+        <v>1RM: DB 6 Ways</v>
       </c>
       <c r="B18">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>1RM: DB Lunge</v>
+        <v>1RM: DB Clean &amp; Jerk Press</v>
       </c>
       <c r="B19">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>1RM: Face Pull</v>
+        <v>1RM: DB Lunge</v>
       </c>
       <c r="B20">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>1RM: Farmers Carry</v>
+        <v>1RM: Face Pull</v>
       </c>
       <c r="B21">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>1RM: Grip Trainer</v>
+        <v>1RM: Farmers Carry</v>
       </c>
       <c r="B22">
-        <v>300</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>1RM: Hack Squat</v>
+        <v>1RM: Grip Trainer</v>
       </c>
       <c r="B23">
-        <v>400</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>1RM: Hip Thrust</v>
+        <v>1RM: Hack Squat</v>
       </c>
       <c r="B24">
-        <v>400</v>
+        <v>415</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>1RM: Inner Thigh Abduction</v>
+        <v>1RM: Hip Thrust</v>
       </c>
       <c r="B25">
-        <v>200</v>
+        <v>375</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>1RM: Kettlebell Leg Raise</v>
+        <v>1RM: Inner Thigh Abduction</v>
       </c>
       <c r="B26">
-        <v>30</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>1RM: Lat Pulldown, alternating single-arm</v>
+        <v>1RM: Kettlebell Leg Raise</v>
       </c>
       <c r="B27">
-        <v>90</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>1RM: Lat Pulldown</v>
+        <v>1RM: Lat Pulldown, alternating single-arm</v>
       </c>
       <c r="B28">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>1RM: Prone Leg Curl</v>
+        <v>1RM: Lat Pulldown</v>
       </c>
       <c r="B29">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>1RM: Leg Extension ISO hold</v>
+        <v>1RM: Prone Leg Curl</v>
       </c>
       <c r="B30">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>1RM: Overhead Tricep Extension</v>
+        <v>1RM: Leg Extension ISO hold</v>
       </c>
       <c r="B31">
-        <v>30</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>1RM: Outer Thigh Adduction</v>
+        <v>1RM: Overhead Tricep Extension</v>
       </c>
       <c r="B32">
-        <v>180</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>1RM: Pallof Press</v>
+        <v>1RM: Outer Thigh Adduction</v>
       </c>
       <c r="B33">
-        <v>40</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>1RM: Plate Torso Rotation</v>
+        <v>1RM: Pallof Press</v>
       </c>
       <c r="B34">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>1RM: Side Rear Delt Fly</v>
+        <v>1RM: Plate Torso Rotation</v>
       </c>
       <c r="B35">
-        <v>80</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>1RM: Suitcase Bottom-Up, single-arm</v>
+        <v>1RM: Side Rear Delt Fly</v>
       </c>
       <c r="B36">
-        <v>30</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>1RM: Cable Wrist Pulldown</v>
+        <v>1RM: Suitcase Bottom-Up, single-arm</v>
       </c>
       <c r="B37">
-        <v>55</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>1RM: Seated Zercher Good Morning</v>
+        <v>1RM: Cable Wrist Pulldown</v>
       </c>
       <c r="B38">
-        <v>80</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>1RM: Zottman Curl</v>
+        <v>1RM: Seated Zercher Good Morning</v>
       </c>
       <c r="B39">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
+        <v>1RM: Zottman Curl</v>
+      </c>
+      <c r="B40">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
         <v>Exported</v>
       </c>
-      <c r="B40" t="str">
-        <v>2026-10-02T04:16:19.015Z</v>
+      <c r="B41" t="str">
+        <v>2026-10-03T00:13:45.822Z</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B40"/>
+  <autoFilter ref="A1:B41"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B40"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -6713,7 +6716,7 @@
         <v>Day 5</v>
       </c>
       <c r="D46" t="str">
-        <v>Upper body + rotational power</v>
+        <v/>
       </c>
       <c r="E46" t="str">
         <v>Yes</v>
@@ -6769,7 +6772,7 @@
         <v>Day 5</v>
       </c>
       <c r="D47" t="str">
-        <v>Upper body + rotational power</v>
+        <v/>
       </c>
       <c r="E47" t="str">
         <v>Yes</v>
@@ -6825,7 +6828,7 @@
         <v>Day 5</v>
       </c>
       <c r="D48" t="str">
-        <v>Upper body + rotational power</v>
+        <v/>
       </c>
       <c r="E48" t="str">
         <v>Yes</v>
@@ -6881,7 +6884,7 @@
         <v>Day 5</v>
       </c>
       <c r="D49" t="str">
-        <v>Upper body + rotational power</v>
+        <v/>
       </c>
       <c r="E49" t="str">
         <v>Yes</v>
@@ -6937,7 +6940,7 @@
         <v>Day 5</v>
       </c>
       <c r="D50" t="str">
-        <v>Upper body + rotational power</v>
+        <v/>
       </c>
       <c r="E50" t="str">
         <v>Yes</v>
@@ -6993,7 +6996,7 @@
         <v>Day 5</v>
       </c>
       <c r="D51" t="str">
-        <v>Upper body + rotational power</v>
+        <v/>
       </c>
       <c r="E51" t="str">
         <v>Yes</v>
@@ -7049,7 +7052,7 @@
         <v>Day 5</v>
       </c>
       <c r="D52" t="str">
-        <v>Upper body + rotational power</v>
+        <v/>
       </c>
       <c r="E52" t="str">
         <v>Yes</v>
@@ -7105,7 +7108,7 @@
         <v>Day 5</v>
       </c>
       <c r="D53" t="str">
-        <v>Upper body + rotational power</v>
+        <v/>
       </c>
       <c r="E53" t="str">
         <v>Yes</v>
@@ -7161,7 +7164,7 @@
         <v>Day 5</v>
       </c>
       <c r="D54" t="str">
-        <v>Upper body + rotational power</v>
+        <v/>
       </c>
       <c r="E54" t="str">
         <v>Yes</v>
@@ -7217,7 +7220,7 @@
         <v>Day 5</v>
       </c>
       <c r="D55" t="str">
-        <v>Upper body + rotational power</v>
+        <v/>
       </c>
       <c r="E55" t="str">
         <v>Yes</v>
@@ -7273,7 +7276,7 @@
         <v>Day 5</v>
       </c>
       <c r="D56" t="str">
-        <v>Upper body + rotational power</v>
+        <v/>
       </c>
       <c r="E56" t="str">
         <v>Yes</v>
@@ -7329,7 +7332,7 @@
         <v>Day 6</v>
       </c>
       <c r="D57" t="str">
-        <v>Lower body + reactive power</v>
+        <v/>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -7385,7 +7388,7 @@
         <v>Day 6</v>
       </c>
       <c r="D58" t="str">
-        <v>Lower body + reactive power</v>
+        <v/>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -7441,7 +7444,7 @@
         <v>Day 6</v>
       </c>
       <c r="D59" t="str">
-        <v>Lower body + reactive power</v>
+        <v/>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -7497,7 +7500,7 @@
         <v>Day 6</v>
       </c>
       <c r="D60" t="str">
-        <v>Lower body + reactive power</v>
+        <v/>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -7553,7 +7556,7 @@
         <v>Day 6</v>
       </c>
       <c r="D61" t="str">
-        <v>Lower body + reactive power</v>
+        <v/>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -7609,7 +7612,7 @@
         <v>Day 6</v>
       </c>
       <c r="D62" t="str">
-        <v>Lower body + reactive power</v>
+        <v/>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -7665,7 +7668,7 @@
         <v>Day 6</v>
       </c>
       <c r="D63" t="str">
-        <v>Lower body + reactive power</v>
+        <v/>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -7721,7 +7724,7 @@
         <v>Day 6</v>
       </c>
       <c r="D64" t="str">
-        <v>Lower body + reactive power</v>
+        <v/>
       </c>
       <c r="E64" t="str">
         <v/>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">Weeks!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Body weight'!$A$1:$D$2</definedName>
@@ -510,13 +510,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-27</v>
       </c>
       <c r="E3" t="str">
         <v>2026-09-28</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G3">
         <v>33</v>
@@ -525,7 +525,7 @@
         <v>33</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>48</v>
@@ -670,7 +670,7 @@
         <v>2</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-27</v>
       </c>
       <c r="E8" t="str">
         <v>2026-09-30</v>
@@ -769,7 +769,7 @@
         <v>2026-09-28</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="F11">
         <v>45</v>
@@ -830,7 +830,7 @@
         <v>3</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-27</v>
       </c>
       <c r="E13" t="str">
         <v>2026-10-01</v>
@@ -891,13 +891,13 @@
         <v>Strength</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="str">
         <v>2026-09-29</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-02</v>
       </c>
       <c r="F15">
         <v>25</v>
@@ -1082,7 +1082,7 @@
         <v>done</v>
       </c>
       <c r="C5" t="str">
-        <v>A-d1s2</v>
+        <v>A-d1s4</v>
       </c>
       <c r="D5" t="str">
         <v>Yes</v>
@@ -1096,7 +1096,7 @@
         <v>done</v>
       </c>
       <c r="C6" t="str">
-        <v>A-d1s4</v>
+        <v>A-d1s6</v>
       </c>
       <c r="D6" t="str">
         <v>Yes</v>
@@ -1110,7 +1110,7 @@
         <v>done</v>
       </c>
       <c r="C7" t="str">
-        <v>A-d1s6</v>
+        <v>A-d1s8</v>
       </c>
       <c r="D7" t="str">
         <v>Yes</v>
@@ -1124,7 +1124,7 @@
         <v>done</v>
       </c>
       <c r="C8" t="str">
-        <v>A-d1s8</v>
+        <v>A-d2s3</v>
       </c>
       <c r="D8" t="str">
         <v>Yes</v>
@@ -1138,7 +1138,7 @@
         <v>done</v>
       </c>
       <c r="C9" t="str">
-        <v>A-d2s3</v>
+        <v>A-d2s5</v>
       </c>
       <c r="D9" t="str">
         <v>Yes</v>
@@ -1152,7 +1152,7 @@
         <v>done</v>
       </c>
       <c r="C10" t="str">
-        <v>A-d2s5</v>
+        <v>A-d3s3</v>
       </c>
       <c r="D10" t="str">
         <v>Yes</v>
@@ -1166,7 +1166,7 @@
         <v>done</v>
       </c>
       <c r="C11" t="str">
-        <v>A-d3s2</v>
+        <v>A-d3s6</v>
       </c>
       <c r="D11" t="str">
         <v>Yes</v>
@@ -1180,7 +1180,7 @@
         <v>done</v>
       </c>
       <c r="C12" t="str">
-        <v>A-d3s3</v>
+        <v>A-d3s6#0</v>
       </c>
       <c r="D12" t="str">
         <v>Yes</v>
@@ -1194,7 +1194,7 @@
         <v>done</v>
       </c>
       <c r="C13" t="str">
-        <v>A-d2s2</v>
+        <v>A-d2s4</v>
       </c>
       <c r="D13" t="str">
         <v>Yes</v>
@@ -1208,7 +1208,7 @@
         <v>done</v>
       </c>
       <c r="C14" t="str">
-        <v>A-d2s2#0</v>
+        <v>A-d1s7</v>
       </c>
       <c r="D14" t="str">
         <v>Yes</v>
@@ -1222,7 +1222,7 @@
         <v>done</v>
       </c>
       <c r="C15" t="str">
-        <v>A-d3s6</v>
+        <v>A-d3s5</v>
       </c>
       <c r="D15" t="str">
         <v>Yes</v>
@@ -1236,7 +1236,7 @@
         <v>done</v>
       </c>
       <c r="C16" t="str">
-        <v>A-d3s6#0</v>
+        <v>A-d3s1</v>
       </c>
       <c r="D16" t="str">
         <v>Yes</v>
@@ -1250,7 +1250,7 @@
         <v>done</v>
       </c>
       <c r="C17" t="str">
-        <v>A-d2s4</v>
+        <v>A-d4s5</v>
       </c>
       <c r="D17" t="str">
         <v>Yes</v>
@@ -1264,7 +1264,7 @@
         <v>done</v>
       </c>
       <c r="C18" t="str">
-        <v>A-d1s7</v>
+        <v>A-d4s2</v>
       </c>
       <c r="D18" t="str">
         <v>Yes</v>
@@ -1278,7 +1278,7 @@
         <v>done</v>
       </c>
       <c r="C19" t="str">
-        <v>A-d3s5</v>
+        <v>A-d4s4</v>
       </c>
       <c r="D19" t="str">
         <v>Yes</v>
@@ -1292,7 +1292,7 @@
         <v>done</v>
       </c>
       <c r="C20" t="str">
-        <v>A-d3s1</v>
+        <v>A-d6s5</v>
       </c>
       <c r="D20" t="str">
         <v>Yes</v>
@@ -1306,7 +1306,7 @@
         <v>done</v>
       </c>
       <c r="C21" t="str">
-        <v>A-d4s5</v>
+        <v>A-d5s3</v>
       </c>
       <c r="D21" t="str">
         <v>Yes</v>
@@ -1320,7 +1320,7 @@
         <v>done</v>
       </c>
       <c r="C22" t="str">
-        <v>A-d4s2</v>
+        <v>A-d2s2</v>
       </c>
       <c r="D22" t="str">
         <v>Yes</v>
@@ -1334,7 +1334,7 @@
         <v>done</v>
       </c>
       <c r="C23" t="str">
-        <v>A-d4s4</v>
+        <v>A-d2s2#0</v>
       </c>
       <c r="D23" t="str">
         <v>Yes</v>
@@ -1348,7 +1348,7 @@
         <v>done</v>
       </c>
       <c r="C24" t="str">
-        <v>A-d6s5</v>
+        <v>A-d3s2</v>
       </c>
       <c r="D24" t="str">
         <v>Yes</v>
@@ -1362,7 +1362,7 @@
         <v>done</v>
       </c>
       <c r="C25" t="str">
-        <v>A-d5s3</v>
+        <v>A-d1s2</v>
       </c>
       <c r="D25" t="str">
         <v>Yes</v>
@@ -1903,7 +1903,7 @@
         <v>exPh</v>
       </c>
       <c r="B4" t="str">
-        <v>{"canoe":"iso","romanadd":"strength","deskbands":"iso","spinal":"mob","platerot":"strength"}</v>
+        <v>{"canoe":"iso","romanadd":"strength","deskbands":"iso","spinal":"mob","platerot":"strength","suitcase":"strength"}</v>
       </c>
     </row>
     <row r="5">
@@ -1911,7 +1911,7 @@
         <v>ghBackup</v>
       </c>
       <c r="B5" t="str">
-        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":null,"last":{"at":"2026-10-02T02:07:33.781Z","url":"https://github.com/jacgit18/iron-log/commit/34dcc108fb277928b41a6ef04e695a35b5d7f16f"}}</v>
+        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"glvchv","last":{"at":"2026-10-03T00:13:47.807Z","url":"https://github.com/jacgit18/iron-log/commit/bc31dfa37bf7c23ac9b50000268dc6adfb9813c0"}}</v>
       </c>
     </row>
     <row r="6">
@@ -1975,7 +1975,7 @@
         <v>phDef</v>
       </c>
       <c r="B13" t="str">
-        <v>{"A-d1s1:0":"hyp","A-d4s1:0":"strength","A-d1s7:1":"iso","A-d1s3:0":"strength"}</v>
+        <v>{"A-d1s1:0":"hyp","A-d1s7:1":"iso","A-d1s3:0":"strength"}</v>
       </c>
     </row>
     <row r="14">
@@ -2012,7 +2012,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O29"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -2080,7 +2080,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-27</v>
       </c>
       <c r="B2" t="str">
         <v>2026-09-27</v>
@@ -2092,7 +2092,7 @@
         <v>Hypertrophy</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -2104,10 +2104,10 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>33×15, 33×15, 33×15, 33×15</v>
+        <v>30×15, 30×15, 30×15, 30×15</v>
       </c>
       <c r="J2">
-        <v>1980</v>
+        <v>1800</v>
       </c>
       <c r="K2" t="str">
         <v>Forearms &amp; grip</v>
@@ -2116,7 +2116,7 @@
         <v/>
       </c>
       <c r="M2" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N2" t="str">
         <v>A-d1s2</v>
@@ -2127,66 +2127,66 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-27</v>
       </c>
       <c r="B3" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="C3" t="str">
-        <v>Cable Wrist Pulldown</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="D3" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>180</v>
       </c>
       <c r="F3">
         <v>4</v>
       </c>
       <c r="G3">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H3" t="str">
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>33×15, 33×15, 33×15, 33×15</v>
+        <v>180×6, 180×6, 180×6, 180×6</v>
       </c>
       <c r="J3">
-        <v>1980</v>
+        <v>4320</v>
       </c>
       <c r="K3" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Inner thigh (adductors)</v>
       </c>
       <c r="L3" t="str">
         <v/>
       </c>
       <c r="M3" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N3" t="str">
-        <v>A-d3s3</v>
+        <v>A-d1s4</v>
       </c>
       <c r="O3" t="str">
-        <v>wristpd</v>
+        <v>innerthigh</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-27</v>
       </c>
       <c r="B4" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="C4" t="str">
-        <v>Chest Press</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="D4" t="str">
         <v>Strength</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F4">
         <v>4</v>
@@ -2198,25 +2198,25 @@
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>35×6, 35×6, 35×6, 35×6</v>
+        <v>50×6, 50×6, 50×6, 50×6</v>
       </c>
       <c r="J4">
-        <v>840</v>
+        <v>1200</v>
       </c>
       <c r="K4" t="str">
-        <v>Chest</v>
+        <v>Lower back</v>
       </c>
       <c r="L4" t="str">
-        <v>Front delts, Triceps</v>
+        <v>Glutes, Hamstrings, Upper back</v>
       </c>
       <c r="M4" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N4" t="str">
         <v>A-d1s6</v>
       </c>
       <c r="O4" t="str">
-        <v>chestpress</v>
+        <v>zercher</v>
       </c>
     </row>
     <row r="5">
@@ -2227,13 +2227,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="C5" t="str">
-        <v>Chest Press</v>
+        <v>Cable Wrist Pulldown</v>
       </c>
       <c r="D5" t="str">
         <v>Hypertrophy</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -2245,25 +2245,25 @@
         <v/>
       </c>
       <c r="I5" t="str">
-        <v>25×15, 25×15, 25×15, 25×15</v>
+        <v>33×15, 33×15, 33×15, 33×15</v>
       </c>
       <c r="J5">
-        <v>1500</v>
+        <v>1980</v>
       </c>
       <c r="K5" t="str">
-        <v>Chest</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="L5" t="str">
-        <v>Front delts, Triceps</v>
+        <v/>
       </c>
       <c r="M5" t="str">
         <v>From check-off</v>
       </c>
       <c r="N5" t="str">
-        <v>A-d2s5</v>
+        <v>A-d3s3</v>
       </c>
       <c r="O5" t="str">
-        <v>chestpress</v>
+        <v>wristpd</v>
       </c>
     </row>
     <row r="6">
@@ -2274,13 +2274,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="C6" t="str">
-        <v>Grip Trainer</v>
+        <v>Chest Press</v>
       </c>
       <c r="D6" t="str">
         <v>Strength</v>
       </c>
       <c r="E6">
-        <v>200</v>
+        <v>35</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -2292,25 +2292,25 @@
         <v/>
       </c>
       <c r="I6" t="str">
-        <v>200×6, 200×6, 200×6, 200×6</v>
+        <v>35×6, 35×6, 35×6, 35×6</v>
       </c>
       <c r="J6">
-        <v>4800</v>
+        <v>840</v>
       </c>
       <c r="K6" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Chest</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>Front delts, Triceps</v>
       </c>
       <c r="M6" t="str">
         <v>From check-off</v>
       </c>
       <c r="N6" t="str">
-        <v>A-d1s8</v>
+        <v>A-d1s6</v>
       </c>
       <c r="O6" t="str">
-        <v>grip</v>
+        <v>chestpress</v>
       </c>
     </row>
     <row r="7">
@@ -2321,34 +2321,34 @@
         <v>2026-09-27</v>
       </c>
       <c r="C7" t="str">
-        <v>Hip Thrust</v>
+        <v>Chest Press</v>
       </c>
       <c r="D7" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E7">
-        <v>320</v>
+        <v>25</v>
       </c>
       <c r="F7">
         <v>4</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H7" t="str">
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>320×6, 320×6, 320×6, 320×6</v>
+        <v>25×15, 25×15, 25×15, 25×15</v>
       </c>
       <c r="J7">
-        <v>7680</v>
+        <v>1500</v>
       </c>
       <c r="K7" t="str">
-        <v>Glutes</v>
+        <v>Chest</v>
       </c>
       <c r="L7" t="str">
-        <v>Hamstrings</v>
+        <v>Front delts, Triceps</v>
       </c>
       <c r="M7" t="str">
         <v>From check-off</v>
@@ -2357,7 +2357,7 @@
         <v>A-d2s5</v>
       </c>
       <c r="O7" t="str">
-        <v>hipthrust</v>
+        <v>chestpress</v>
       </c>
     </row>
     <row r="8">
@@ -2368,13 +2368,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="C8" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="D8" t="str">
         <v>Strength</v>
       </c>
       <c r="E8">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="F8">
         <v>4</v>
@@ -2386,13 +2386,13 @@
         <v/>
       </c>
       <c r="I8" t="str">
-        <v>180×6, 180×6, 180×6, 180×6</v>
+        <v>200×6, 200×6, 200×6, 200×6</v>
       </c>
       <c r="J8">
-        <v>4320</v>
+        <v>4800</v>
       </c>
       <c r="K8" t="str">
-        <v>Inner thigh (adductors)</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="L8" t="str">
         <v/>
@@ -2401,10 +2401,10 @@
         <v>From check-off</v>
       </c>
       <c r="N8" t="str">
-        <v>A-d1s4</v>
+        <v>A-d1s8</v>
       </c>
       <c r="O8" t="str">
-        <v>innerthigh</v>
+        <v>grip</v>
       </c>
     </row>
     <row r="9">
@@ -2415,43 +2415,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C9" t="str">
-        <v>Lat Pulldown, alternating single-arm</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="D9" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E9">
-        <v>45</v>
+        <v>320</v>
       </c>
       <c r="F9">
         <v>4</v>
       </c>
       <c r="G9">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H9" t="str">
         <v/>
       </c>
       <c r="I9" t="str">
-        <v>45×15, 45×15, 45×15, 45×15</v>
+        <v>320×6, 320×6, 320×6, 320×6</v>
       </c>
       <c r="J9">
-        <v>2700</v>
+        <v>7680</v>
       </c>
       <c r="K9" t="str">
-        <v>Lats</v>
+        <v>Glutes</v>
       </c>
       <c r="L9" t="str">
-        <v>Biceps, Upper back, Rear delts</v>
+        <v>Hamstrings</v>
       </c>
       <c r="M9" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N9" t="str">
-        <v>A-d1s1</v>
+        <v>A-d2s5</v>
       </c>
       <c r="O9" t="str">
-        <v>latpd</v>
+        <v>hipthrust</v>
       </c>
     </row>
     <row r="10">
@@ -2492,10 +2492,10 @@
         <v>Biceps, Upper back, Rear delts</v>
       </c>
       <c r="M10" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N10" t="str">
-        <v>A-d3s2</v>
+        <v>A-d1s1</v>
       </c>
       <c r="O10" t="str">
         <v>latpd</v>
@@ -2556,10 +2556,10 @@
         <v>2026-09-27</v>
       </c>
       <c r="C12" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="D12" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="E12">
         <v>50</v>
@@ -2567,32 +2567,32 @@
       <c r="F12">
         <v>4</v>
       </c>
-      <c r="G12">
-        <v>6</v>
-      </c>
-      <c r="H12" t="str">
-        <v/>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12">
+        <v>15</v>
       </c>
       <c r="I12" t="str">
-        <v>50×6, 50×6, 50×6, 50×6</v>
-      </c>
-      <c r="J12">
-        <v>1200</v>
+        <v>50×15s, 50×15s, 50×15s, 50×15s</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
       </c>
       <c r="K12" t="str">
-        <v>Lower back</v>
+        <v>Rear delts</v>
       </c>
       <c r="L12" t="str">
-        <v>Glutes, Hamstrings, Upper back</v>
+        <v>Upper back</v>
       </c>
       <c r="M12" t="str">
         <v>From check-off</v>
       </c>
       <c r="N12" t="str">
-        <v>A-d1s6</v>
+        <v>A-d3s6</v>
       </c>
       <c r="O12" t="str">
-        <v>zercher</v>
+        <v>reardelt</v>
       </c>
     </row>
     <row r="13">
@@ -2633,7 +2633,7 @@
         <v>Upper back</v>
       </c>
       <c r="M13" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N13" t="str">
         <v>A-d2s2</v>
@@ -2644,22 +2644,22 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="B14" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="C14" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="D14" t="str">
         <v>Isometric</v>
       </c>
       <c r="E14">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -2668,25 +2668,25 @@
         <v>15</v>
       </c>
       <c r="I14" t="str">
-        <v>50×15s, 50×15s, 50×15s, 50×15s</v>
+        <v>15×15s, 15×15s, 15×15s</v>
       </c>
       <c r="J14" t="str">
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>Rear delts</v>
+        <v>Abs, Hip flexors</v>
       </c>
       <c r="L14" t="str">
-        <v>Upper back</v>
+        <v/>
       </c>
       <c r="M14" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N14" t="str">
-        <v>A-d3s6</v>
+        <v>A-d1s7</v>
       </c>
       <c r="O14" t="str">
-        <v>reardelt</v>
+        <v>kbleg</v>
       </c>
     </row>
     <row r="15">
@@ -2697,43 +2697,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C15" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Kneeling Cable Ab Crunch</v>
       </c>
       <c r="D15" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="E15">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="F15">
-        <v>3</v>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15">
-        <v>15</v>
+        <v>4</v>
+      </c>
+      <c r="G15">
+        <v>6</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>15×15s, 15×15s, 15×15s</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
+        <v>85×6, 85×6, 85×6, 85×6</v>
+      </c>
+      <c r="J15">
+        <v>2040</v>
       </c>
       <c r="K15" t="str">
-        <v>Abs, Hip flexors</v>
+        <v>Abs</v>
       </c>
       <c r="L15" t="str">
         <v/>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N15" t="str">
-        <v>A-d1s7</v>
+        <v>A-d2s4</v>
       </c>
       <c r="O15" t="str">
-        <v>kbleg</v>
+        <v>cablecrunch</v>
       </c>
     </row>
     <row r="16">
@@ -2744,43 +2744,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C16" t="str">
-        <v>Kneeling Cable Ab Crunch</v>
+        <v>Lat Pulldown, alternating single-arm</v>
       </c>
       <c r="D16" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E16">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="F16">
         <v>4</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H16" t="str">
         <v/>
       </c>
       <c r="I16" t="str">
-        <v>85×6, 85×6, 85×6, 85×6</v>
+        <v>45×15, 45×15, 45×15, 45×15</v>
       </c>
       <c r="J16">
-        <v>2040</v>
+        <v>2700</v>
       </c>
       <c r="K16" t="str">
-        <v>Abs</v>
+        <v>Lats</v>
       </c>
       <c r="L16" t="str">
-        <v/>
+        <v>Biceps, Upper back, Rear delts</v>
       </c>
       <c r="M16" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N16" t="str">
-        <v>A-d2s4</v>
+        <v>A-d3s2</v>
       </c>
       <c r="O16" t="str">
-        <v>cablecrunch</v>
+        <v>latpd</v>
       </c>
     </row>
     <row r="17">
@@ -3347,10 +3347,57 @@
         <v>zercher</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Suitcase Bottom-Up, single-arm</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E29">
+        <v>25</v>
+      </c>
+      <c r="F29">
+        <v>4</v>
+      </c>
+      <c r="G29">
+        <v>6</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v>25×6, 25×6, 25×6, 25×6</v>
+      </c>
+      <c r="J29">
+        <v>600</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Forearms &amp; grip, Obliques</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Traps</v>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v>A-d4s1</v>
+      </c>
+      <c r="O29" t="str">
+        <v>suitcase</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O28"/>
+  <autoFilter ref="A1:O29"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O29"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3391,13 +3438,13 @@
         <v>Forearms &amp; grip</v>
       </c>
       <c r="C2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -3541,7 +3588,7 @@
         <v>2026-09-27</v>
       </c>
       <c r="B11" t="str">
-        <v>Lats</v>
+        <v>Obliques</v>
       </c>
       <c r="C11">
         <v>8</v>
@@ -3558,16 +3605,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B12" t="str">
-        <v>Hamstrings</v>
+        <v>Lats</v>
       </c>
       <c r="C12">
+        <v>8</v>
+      </c>
+      <c r="D12">
         <v>0</v>
       </c>
-      <c r="D12">
-        <v>15</v>
-      </c>
       <c r="E12">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -3575,7 +3622,7 @@
         <v>2026-09-27</v>
       </c>
       <c r="B13" t="str">
-        <v>Triceps</v>
+        <v>Hamstrings</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -3592,16 +3639,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B14" t="str">
-        <v>Abs</v>
+        <v>Triceps</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E14">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="15">
@@ -3609,13 +3656,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B15" t="str">
-        <v>Biceps</v>
+        <v>Abs</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>7</v>
@@ -3626,16 +3673,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B16" t="str">
-        <v>Side delts</v>
+        <v>Biceps</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3643,16 +3690,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B17" t="str">
-        <v>Obliques</v>
+        <v>Side delts</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -3660,16 +3707,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B18" t="str">
-        <v>Hip flexors</v>
+        <v>Traps</v>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -3677,16 +3724,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B19" t="str">
-        <v>Traps</v>
+        <v>Hip flexors</v>
       </c>
       <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19">
         <v>0</v>
       </c>
-      <c r="D19">
-        <v>4</v>
-      </c>
       <c r="E19">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3760,7 +3807,7 @@
         <v>67</v>
       </c>
       <c r="H2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -4150,7 +4197,7 @@
         <v>Exported</v>
       </c>
       <c r="B41" t="str">
-        <v>2026-10-03T00:13:45.822Z</v>
+        <v>2026-10-03T00:33:46.543Z</v>
       </c>
     </row>
   </sheetData>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">Weeks!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Body weight'!$A$1:$D$2</definedName>
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">Programs!$A$1:$R$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Program info'!$A$1:$B$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11">Config!$A$1:$B$16</definedName>
   </definedNames>
 </workbook>
@@ -516,7 +516,7 @@
         <v>2026-09-28</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G3">
         <v>33</v>
@@ -525,7 +525,7 @@
         <v>33</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>48</v>
@@ -539,7 +539,7 @@
         <v>Hypertrophy</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="str">
         <v>2026-09-28</v>
@@ -740,13 +740,13 @@
         <v>2026-09-29</v>
       </c>
       <c r="F10">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="G10">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="H10">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>2</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-27</v>
       </c>
       <c r="E14" t="str">
         <v>2026-09-28</v>
@@ -891,13 +891,13 @@
         <v>Strength</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="str">
         <v>2026-09-29</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-10-02</v>
+        <v>2026-09-29</v>
       </c>
       <c r="F15">
         <v>25</v>
@@ -1010,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D59"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.83203125" customWidth="1"/>
@@ -1844,24 +1844,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="B60" t="str">
-        <v>prog</v>
-      </c>
-      <c r="C60" t="str">
-        <v/>
-      </c>
-      <c r="D60" t="str">
-        <v>A</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D60"/>
+  <autoFilter ref="A1:D59"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D59"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1903,7 +1889,7 @@
         <v>exPh</v>
       </c>
       <c r="B4" t="str">
-        <v>{"canoe":"iso","romanadd":"strength","deskbands":"iso","spinal":"mob","platerot":"strength","suitcase":"strength"}</v>
+        <v>{"canoe":"iso","romanadd":"strength","deskbands":"iso","spinal":"mob","platerot":"strength","suitcase":"strength","qlext":"strength"}</v>
       </c>
     </row>
     <row r="5">
@@ -1911,7 +1897,7 @@
         <v>ghBackup</v>
       </c>
       <c r="B5" t="str">
-        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"glvchv","last":{"at":"2026-10-03T00:13:47.807Z","url":"https://github.com/jacgit18/iron-log/commit/bc31dfa37bf7c23ac9b50000268dc6adfb9813c0"}}</v>
+        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"5oi19c","last":{"at":"2026-10-03T00:33:48.747Z","url":"https://github.com/jacgit18/iron-log/commit/575e42b0dddf1fec3435ae130c83ec09596aaa61"}}</v>
       </c>
     </row>
     <row r="6">
@@ -2012,7 +1998,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O27"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -2092,7 +2078,7 @@
         <v>Hypertrophy</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -2104,10 +2090,10 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>30×15, 30×15, 30×15, 30×15</v>
+        <v>33×15, 33×15, 33×15, 33×15</v>
       </c>
       <c r="J2">
-        <v>1800</v>
+        <v>1980</v>
       </c>
       <c r="K2" t="str">
         <v>Forearms &amp; grip</v>
@@ -2221,49 +2207,49 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-27</v>
       </c>
       <c r="B5" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="C5" t="str">
-        <v>Cable Wrist Pulldown</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="D5" t="str">
-        <v>Hypertrophy</v>
+        <v>Isometric</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F5">
         <v>4</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5">
         <v>15</v>
       </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
       <c r="I5" t="str">
-        <v>33×15, 33×15, 33×15, 33×15</v>
-      </c>
-      <c r="J5">
-        <v>1980</v>
+        <v>50×15s, 50×15s, 50×15s, 50×15s</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
       </c>
       <c r="K5" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Rear delts</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>Upper back</v>
       </c>
       <c r="M5" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N5" t="str">
-        <v>A-d3s3</v>
+        <v>A-d3s6</v>
       </c>
       <c r="O5" t="str">
-        <v>wristpd</v>
+        <v>reardelt</v>
       </c>
     </row>
     <row r="6">
@@ -2274,43 +2260,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C6" t="str">
-        <v>Chest Press</v>
+        <v>Cable Wrist Pulldown</v>
       </c>
       <c r="D6" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E6">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F6">
         <v>4</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H6" t="str">
         <v/>
       </c>
       <c r="I6" t="str">
-        <v>35×6, 35×6, 35×6, 35×6</v>
+        <v>33×15, 33×15, 33×15, 33×15</v>
       </c>
       <c r="J6">
-        <v>840</v>
+        <v>1980</v>
       </c>
       <c r="K6" t="str">
-        <v>Chest</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="L6" t="str">
-        <v>Front delts, Triceps</v>
+        <v/>
       </c>
       <c r="M6" t="str">
         <v>From check-off</v>
       </c>
       <c r="N6" t="str">
-        <v>A-d1s6</v>
+        <v>A-d3s3</v>
       </c>
       <c r="O6" t="str">
-        <v>chestpress</v>
+        <v>wristpd</v>
       </c>
     </row>
     <row r="7">
@@ -2324,25 +2310,25 @@
         <v>Chest Press</v>
       </c>
       <c r="D7" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F7">
         <v>4</v>
       </c>
       <c r="G7">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H7" t="str">
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>25×15, 25×15, 25×15, 25×15</v>
+        <v>35×6, 35×6, 35×6, 35×6</v>
       </c>
       <c r="J7">
-        <v>1500</v>
+        <v>840</v>
       </c>
       <c r="K7" t="str">
         <v>Chest</v>
@@ -2354,7 +2340,7 @@
         <v>From check-off</v>
       </c>
       <c r="N7" t="str">
-        <v>A-d2s5</v>
+        <v>A-d1s6</v>
       </c>
       <c r="O7" t="str">
         <v>chestpress</v>
@@ -2586,10 +2572,10 @@
         <v>Upper back</v>
       </c>
       <c r="M12" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N12" t="str">
-        <v>A-d3s6</v>
+        <v>A-d2s2</v>
       </c>
       <c r="O12" t="str">
         <v>reardelt</v>
@@ -2597,22 +2583,22 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="B13" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="C13" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="D13" t="str">
         <v>Isometric</v>
       </c>
       <c r="E13">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -2621,25 +2607,25 @@
         <v>15</v>
       </c>
       <c r="I13" t="str">
-        <v>50×15s, 50×15s, 50×15s, 50×15s</v>
+        <v>15×15s, 15×15s, 15×15s</v>
       </c>
       <c r="J13" t="str">
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>Rear delts</v>
+        <v>Abs, Hip flexors</v>
       </c>
       <c r="L13" t="str">
-        <v>Upper back</v>
+        <v/>
       </c>
       <c r="M13" t="str">
         <v/>
       </c>
       <c r="N13" t="str">
-        <v>A-d2s2</v>
+        <v>A-d1s7</v>
       </c>
       <c r="O13" t="str">
-        <v>reardelt</v>
+        <v>kbleg</v>
       </c>
     </row>
     <row r="14">
@@ -2650,31 +2636,31 @@
         <v>2026-09-27</v>
       </c>
       <c r="C14" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Kneeling Cable Ab Crunch</v>
       </c>
       <c r="D14" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="E14">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="F14">
-        <v>3</v>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14">
-        <v>15</v>
+        <v>4</v>
+      </c>
+      <c r="G14">
+        <v>6</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>15×15s, 15×15s, 15×15s</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
+        <v>60×6, 60×6, 60×6, 60×6</v>
+      </c>
+      <c r="J14">
+        <v>1440</v>
       </c>
       <c r="K14" t="str">
-        <v>Abs, Hip flexors</v>
+        <v>Abs</v>
       </c>
       <c r="L14" t="str">
         <v/>
@@ -2683,10 +2669,10 @@
         <v/>
       </c>
       <c r="N14" t="str">
-        <v>A-d1s7</v>
+        <v>A-d2s4</v>
       </c>
       <c r="O14" t="str">
-        <v>kbleg</v>
+        <v>cablecrunch</v>
       </c>
     </row>
     <row r="15">
@@ -2697,43 +2683,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C15" t="str">
-        <v>Kneeling Cable Ab Crunch</v>
+        <v>Lat Pulldown, alternating single-arm</v>
       </c>
       <c r="D15" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E15">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="F15">
         <v>4</v>
       </c>
       <c r="G15">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H15" t="str">
         <v/>
       </c>
       <c r="I15" t="str">
-        <v>85×6, 85×6, 85×6, 85×6</v>
+        <v>45×15, 45×15, 45×15, 45×15</v>
       </c>
       <c r="J15">
-        <v>2040</v>
+        <v>2700</v>
       </c>
       <c r="K15" t="str">
-        <v>Abs</v>
+        <v>Lats</v>
       </c>
       <c r="L15" t="str">
-        <v/>
+        <v>Biceps, Upper back, Rear delts</v>
       </c>
       <c r="M15" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N15" t="str">
-        <v>A-d2s4</v>
+        <v>A-d3s2</v>
       </c>
       <c r="O15" t="str">
-        <v>cablecrunch</v>
+        <v>latpd</v>
       </c>
     </row>
     <row r="16">
@@ -2744,43 +2730,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C16" t="str">
-        <v>Lat Pulldown, alternating single-arm</v>
+        <v>Leg Extension ISO hold</v>
       </c>
       <c r="D16" t="str">
-        <v>Hypertrophy</v>
+        <v>Isometric</v>
       </c>
       <c r="E16">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F16">
         <v>4</v>
       </c>
-      <c r="G16">
-        <v>15</v>
-      </c>
-      <c r="H16" t="str">
-        <v/>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16">
+        <v>30</v>
       </c>
       <c r="I16" t="str">
-        <v>45×15, 45×15, 45×15, 45×15</v>
-      </c>
-      <c r="J16">
-        <v>2700</v>
+        <v>50×30s, 50×30s, 50×30s, 50×30s</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
       </c>
       <c r="K16" t="str">
-        <v>Lats</v>
+        <v>Quads</v>
       </c>
       <c r="L16" t="str">
-        <v>Biceps, Upper back, Rear delts</v>
+        <v/>
       </c>
       <c r="M16" t="str">
         <v/>
       </c>
       <c r="N16" t="str">
-        <v>A-d3s2</v>
+        <v>A-d3s5</v>
       </c>
       <c r="O16" t="str">
-        <v>latpd</v>
+        <v>legext</v>
       </c>
     </row>
     <row r="17">
@@ -2791,43 +2777,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C17" t="str">
-        <v>Leg Extension ISO hold</v>
+        <v>Suitcase Bottom-Up, single-arm</v>
       </c>
       <c r="D17" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="E17">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F17">
         <v>4</v>
       </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17">
-        <v>30</v>
+      <c r="G17">
+        <v>6</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v>50×30s, 50×30s, 50×30s, 50×30s</v>
-      </c>
-      <c r="J17" t="str">
-        <v/>
+        <v>25×6, 25×6, 25×6, 25×6</v>
+      </c>
+      <c r="J17">
+        <v>600</v>
       </c>
       <c r="K17" t="str">
-        <v>Quads</v>
+        <v>Forearms &amp; grip, Obliques</v>
       </c>
       <c r="L17" t="str">
-        <v/>
+        <v>Traps</v>
       </c>
       <c r="M17" t="str">
         <v/>
       </c>
       <c r="N17" t="str">
-        <v>A-d3s5</v>
+        <v>A-d4s1</v>
       </c>
       <c r="O17" t="str">
-        <v>legext</v>
+        <v>suitcase</v>
       </c>
     </row>
     <row r="18">
@@ -2838,90 +2824,90 @@
         <v>2026-09-27</v>
       </c>
       <c r="C18" t="str">
-        <v>Suitcase Bottom-Up, single-arm</v>
+        <v>Zottman Curl</v>
       </c>
       <c r="D18" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E18">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H18" t="str">
         <v/>
       </c>
       <c r="I18" t="str">
-        <v>25×6, 25×6, 25×6, 25×6</v>
+        <v>15×15, 15×15, 15×15</v>
       </c>
       <c r="J18">
-        <v>600</v>
+        <v>675</v>
       </c>
       <c r="K18" t="str">
-        <v>Forearms &amp; grip, Obliques</v>
+        <v>Biceps, Forearms &amp; grip</v>
       </c>
       <c r="L18" t="str">
-        <v>Traps</v>
+        <v/>
       </c>
       <c r="M18" t="str">
         <v/>
       </c>
       <c r="N18" t="str">
-        <v>A-d4s1</v>
+        <v>A-d1s7</v>
       </c>
       <c r="O18" t="str">
-        <v>suitcase</v>
+        <v>zottman</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-30</v>
       </c>
       <c r="B19" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="C19" t="str">
-        <v>Zottman Curl</v>
+        <v>Arnold Press</v>
       </c>
       <c r="D19" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E19">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G19">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H19" t="str">
         <v/>
       </c>
       <c r="I19" t="str">
-        <v>15×15, 15×15, 15×15</v>
+        <v>35×6, 35×6, 30×6, 30×6</v>
       </c>
       <c r="J19">
-        <v>675</v>
+        <v>780</v>
       </c>
       <c r="K19" t="str">
-        <v>Biceps, Forearms &amp; grip</v>
+        <v>Front delts, Side delts</v>
       </c>
       <c r="L19" t="str">
-        <v/>
+        <v>Triceps</v>
       </c>
       <c r="M19" t="str">
         <v/>
       </c>
       <c r="N19" t="str">
-        <v>A-d1s7</v>
+        <v>A-d4s4</v>
       </c>
       <c r="O19" t="str">
-        <v>zottman</v>
+        <v>arnold</v>
       </c>
     </row>
     <row r="20">
@@ -2932,43 +2918,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C20" t="str">
-        <v>Arnold Press</v>
+        <v>Chest Press</v>
       </c>
       <c r="D20" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E20">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H20" t="str">
         <v/>
       </c>
       <c r="I20" t="str">
-        <v>35×6, 35×6, 30×6, 30×6</v>
+        <v>25×15, 25×10</v>
       </c>
       <c r="J20">
-        <v>780</v>
+        <v>625</v>
       </c>
       <c r="K20" t="str">
-        <v>Front delts, Side delts</v>
+        <v>Chest</v>
       </c>
       <c r="L20" t="str">
-        <v>Triceps</v>
+        <v>Front delts, Triceps</v>
       </c>
       <c r="M20" t="str">
         <v/>
       </c>
       <c r="N20" t="str">
-        <v>A-d4s4</v>
+        <v>A-d4s5</v>
       </c>
       <c r="O20" t="str">
-        <v>arnold</v>
+        <v>chestpress</v>
       </c>
     </row>
     <row r="21">
@@ -2979,43 +2965,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C21" t="str">
-        <v>Chest Press</v>
+        <v>Hack Squat</v>
       </c>
       <c r="D21" t="str">
         <v>Hypertrophy</v>
       </c>
       <c r="E21">
-        <v>25</v>
+        <v>270</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G21">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H21" t="str">
         <v/>
       </c>
       <c r="I21" t="str">
-        <v>25×15, 25×10</v>
+        <v>270×15, 270×15, 270×15, 270×15</v>
       </c>
       <c r="J21">
-        <v>625</v>
+        <v>16200</v>
       </c>
       <c r="K21" t="str">
-        <v>Chest</v>
+        <v>Quads</v>
       </c>
       <c r="L21" t="str">
-        <v>Front delts, Triceps</v>
+        <v>Glutes, Inner thigh (adductors)</v>
       </c>
       <c r="M21" t="str">
         <v/>
       </c>
       <c r="N21" t="str">
-        <v>A-d4s5</v>
+        <v>A-d3s1</v>
       </c>
       <c r="O21" t="str">
-        <v>chestpress</v>
+        <v>hack</v>
       </c>
     </row>
     <row r="22">
@@ -3026,43 +3012,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C22" t="str">
-        <v>Hack Squat</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="D22" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E22">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H22" t="str">
         <v/>
       </c>
       <c r="I22" t="str">
-        <v>270×15, 270×15, 270×15, 270×15</v>
+        <v>320×6, 320×6</v>
       </c>
       <c r="J22">
-        <v>16200</v>
+        <v>3840</v>
       </c>
       <c r="K22" t="str">
-        <v>Quads</v>
+        <v>Glutes</v>
       </c>
       <c r="L22" t="str">
-        <v>Glutes, Inner thigh (adductors)</v>
+        <v>Hamstrings</v>
       </c>
       <c r="M22" t="str">
         <v/>
       </c>
       <c r="N22" t="str">
-        <v>A-d3s1</v>
+        <v>A-d4s5</v>
       </c>
       <c r="O22" t="str">
-        <v>hack</v>
+        <v>hipthrust</v>
       </c>
     </row>
     <row r="23">
@@ -3073,16 +3059,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="C23" t="str">
-        <v>Hip Thrust</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="D23" t="str">
         <v>Strength</v>
       </c>
       <c r="E23">
-        <v>320</v>
+        <v>180</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G23">
         <v>6</v>
@@ -3091,25 +3077,25 @@
         <v/>
       </c>
       <c r="I23" t="str">
-        <v>320×6, 320×6</v>
+        <v>180×6, 180×6, 180×6, 180×6</v>
       </c>
       <c r="J23">
-        <v>3840</v>
+        <v>4320</v>
       </c>
       <c r="K23" t="str">
-        <v>Glutes</v>
+        <v>Inner thigh (adductors)</v>
       </c>
       <c r="L23" t="str">
-        <v>Hamstrings</v>
+        <v/>
       </c>
       <c r="M23" t="str">
         <v/>
       </c>
       <c r="N23" t="str">
-        <v>A-d4s5</v>
+        <v>A-d4s2</v>
       </c>
       <c r="O23" t="str">
-        <v>hipthrust</v>
+        <v>innerthigh</v>
       </c>
     </row>
     <row r="24">
@@ -3120,13 +3106,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="C24" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="D24" t="str">
         <v>Strength</v>
       </c>
       <c r="E24">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="F24">
         <v>4</v>
@@ -3138,45 +3124,45 @@
         <v/>
       </c>
       <c r="I24" t="str">
-        <v>180×6, 180×6, 180×6, 180×6</v>
+        <v>50×6, 50×6, 50×6, 50×6</v>
       </c>
       <c r="J24">
-        <v>4320</v>
+        <v>1200</v>
       </c>
       <c r="K24" t="str">
-        <v>Inner thigh (adductors)</v>
+        <v>Lower back</v>
       </c>
       <c r="L24" t="str">
-        <v/>
+        <v>Glutes, Hamstrings, Upper back</v>
       </c>
       <c r="M24" t="str">
         <v/>
       </c>
       <c r="N24" t="str">
-        <v>A-d4s2</v>
+        <v>A-d4s4</v>
       </c>
       <c r="O24" t="str">
-        <v>innerthigh</v>
+        <v>zercher</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-09-30</v>
+        <v>2026-10-01</v>
       </c>
       <c r="B25" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="C25" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Arnold Press</v>
       </c>
       <c r="D25" t="str">
         <v>Strength</v>
       </c>
       <c r="E25">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G25">
         <v>6</v>
@@ -3185,25 +3171,25 @@
         <v/>
       </c>
       <c r="I25" t="str">
-        <v>50×6, 50×6, 50×6, 50×6</v>
+        <v>25×6</v>
       </c>
       <c r="J25">
-        <v>1200</v>
+        <v>150</v>
       </c>
       <c r="K25" t="str">
-        <v>Lower back</v>
+        <v>Front delts, Side delts</v>
       </c>
       <c r="L25" t="str">
-        <v>Glutes, Hamstrings, Upper back</v>
+        <v>Triceps</v>
       </c>
       <c r="M25" t="str">
         <v/>
       </c>
       <c r="N25" t="str">
-        <v>A-d4s4</v>
+        <v>A-d6s5</v>
       </c>
       <c r="O25" t="str">
-        <v>zercher</v>
+        <v>arnold</v>
       </c>
     </row>
     <row r="26">
@@ -3214,43 +3200,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C26" t="str">
-        <v>Arnold Press</v>
+        <v>Hack Squat</v>
       </c>
       <c r="D26" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E26">
-        <v>25</v>
+        <v>270</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G26">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H26" t="str">
         <v/>
       </c>
       <c r="I26" t="str">
-        <v>25×6</v>
+        <v>270×15, 270×15, 270×15</v>
       </c>
       <c r="J26">
-        <v>150</v>
+        <v>12150</v>
       </c>
       <c r="K26" t="str">
-        <v>Front delts, Side delts</v>
+        <v>Quads</v>
       </c>
       <c r="L26" t="str">
-        <v>Triceps</v>
+        <v>Glutes, Inner thigh (adductors)</v>
       </c>
       <c r="M26" t="str">
         <v/>
       </c>
       <c r="N26" t="str">
-        <v>A-d6s5</v>
+        <v>A-d5s3</v>
       </c>
       <c r="O26" t="str">
-        <v>arnold</v>
+        <v>hack</v>
       </c>
     </row>
     <row r="27">
@@ -3261,143 +3247,49 @@
         <v>2026-09-27</v>
       </c>
       <c r="C27" t="str">
-        <v>Hack Squat</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="D27" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E27">
-        <v>270</v>
+        <v>40</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H27" t="str">
         <v/>
       </c>
       <c r="I27" t="str">
-        <v>270×15, 270×15, 270×15</v>
+        <v>40×6</v>
       </c>
       <c r="J27">
-        <v>12150</v>
+        <v>240</v>
       </c>
       <c r="K27" t="str">
-        <v>Quads</v>
+        <v>Lower back</v>
       </c>
       <c r="L27" t="str">
-        <v>Glutes, Inner thigh (adductors)</v>
+        <v>Glutes, Hamstrings, Upper back</v>
       </c>
       <c r="M27" t="str">
         <v/>
       </c>
       <c r="N27" t="str">
-        <v>A-d5s3</v>
+        <v>A-d6s5</v>
       </c>
       <c r="O27" t="str">
-        <v>hack</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>2026-10-01</v>
-      </c>
-      <c r="B28" t="str">
-        <v>2026-09-27</v>
-      </c>
-      <c r="C28" t="str">
-        <v>Seated Zercher Good Morning</v>
-      </c>
-      <c r="D28" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="E28">
-        <v>40</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28">
-        <v>6</v>
-      </c>
-      <c r="H28" t="str">
-        <v/>
-      </c>
-      <c r="I28" t="str">
-        <v>40×6</v>
-      </c>
-      <c r="J28">
-        <v>240</v>
-      </c>
-      <c r="K28" t="str">
-        <v>Lower back</v>
-      </c>
-      <c r="L28" t="str">
-        <v>Glutes, Hamstrings, Upper back</v>
-      </c>
-      <c r="M28" t="str">
-        <v/>
-      </c>
-      <c r="N28" t="str">
-        <v>A-d6s5</v>
-      </c>
-      <c r="O28" t="str">
         <v>zercher</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>2026-10-02</v>
-      </c>
-      <c r="B29" t="str">
-        <v>2026-09-27</v>
-      </c>
-      <c r="C29" t="str">
-        <v>Suitcase Bottom-Up, single-arm</v>
-      </c>
-      <c r="D29" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="E29">
-        <v>25</v>
-      </c>
-      <c r="F29">
-        <v>4</v>
-      </c>
-      <c r="G29">
-        <v>6</v>
-      </c>
-      <c r="H29" t="str">
-        <v/>
-      </c>
-      <c r="I29" t="str">
-        <v>25×6, 25×6, 25×6, 25×6</v>
-      </c>
-      <c r="J29">
-        <v>600</v>
-      </c>
-      <c r="K29" t="str">
-        <v>Forearms &amp; grip, Obliques</v>
-      </c>
-      <c r="L29" t="str">
-        <v>Traps</v>
-      </c>
-      <c r="M29" t="str">
-        <v/>
-      </c>
-      <c r="N29" t="str">
-        <v>A-d4s1</v>
-      </c>
-      <c r="O29" t="str">
-        <v>suitcase</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O29"/>
+  <autoFilter ref="A1:O27"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O27"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3438,13 +3330,13 @@
         <v>Forearms &amp; grip</v>
       </c>
       <c r="C2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -3537,16 +3429,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B8" t="str">
-        <v>Chest</v>
+        <v>Lower back</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -3560,10 +3452,10 @@
         <v>5</v>
       </c>
       <c r="D9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -3571,16 +3463,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B10" t="str">
-        <v>Lower back</v>
+        <v>Lats</v>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -3588,16 +3480,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B11" t="str">
-        <v>Obliques</v>
+        <v>Hamstrings</v>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="12">
@@ -3605,16 +3497,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B12" t="str">
-        <v>Lats</v>
+        <v>Abs</v>
       </c>
       <c r="C12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -3622,16 +3514,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B13" t="str">
-        <v>Hamstrings</v>
+        <v>Biceps</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D13">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E13">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -3639,16 +3531,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B14" t="str">
-        <v>Triceps</v>
+        <v>Chest</v>
       </c>
       <c r="C14">
+        <v>6</v>
+      </c>
+      <c r="D14">
         <v>0</v>
       </c>
-      <c r="D14">
-        <v>15</v>
-      </c>
       <c r="E14">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -3656,16 +3548,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B15" t="str">
-        <v>Abs</v>
+        <v>Triceps</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E15">
-        <v>7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="16">
@@ -3673,16 +3565,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B16" t="str">
-        <v>Biceps</v>
+        <v>Side delts</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -3690,16 +3582,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B17" t="str">
-        <v>Side delts</v>
+        <v>Obliques</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -3707,16 +3599,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B18" t="str">
-        <v>Traps</v>
+        <v>Hip flexors</v>
       </c>
       <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18">
         <v>0</v>
       </c>
-      <c r="D18">
-        <v>8</v>
-      </c>
       <c r="E18">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -3724,16 +3616,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B19" t="str">
-        <v>Hip flexors</v>
+        <v>Traps</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3807,7 +3699,7 @@
         <v>67</v>
       </c>
       <c r="H2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -4197,7 +4089,7 @@
         <v>Exported</v>
       </c>
       <c r="B41" t="str">
-        <v>2026-10-03T00:33:46.543Z</v>
+        <v>2026-10-03T00:36:39.731Z</v>
       </c>
     </row>
   </sheetData>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">Programs!$A$1:$R$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Program info'!$A$1:$B$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11">Config!$A$1:$B$16</definedName>
   </definedNames>
 </workbook>
@@ -1010,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D71"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.83203125" customWidth="1"/>
@@ -1043,7 +1043,7 @@
         <v/>
       </c>
       <c r="D2" t="str">
-        <v>6</v>
+        <v>6 7</v>
       </c>
     </row>
     <row r="3">
@@ -1625,13 +1625,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B44" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C44" t="str">
-        <v>A-d3s2</v>
-      </c>
-      <c r="D44">
-        <v>2</v>
+        <v>A-d5s1</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="45">
@@ -1639,13 +1639,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B45" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C45" t="str">
-        <v>A-d3s3</v>
-      </c>
-      <c r="D45">
-        <v>2</v>
+        <v>A-d5s2</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="46">
@@ -1653,13 +1653,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B46" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C46" t="str">
-        <v>A-d2s4</v>
-      </c>
-      <c r="D46">
-        <v>3</v>
+        <v>A-d5s4</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="47">
@@ -1667,13 +1667,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B47" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C47" t="str">
-        <v>A-d1s7</v>
-      </c>
-      <c r="D47">
-        <v>3</v>
+        <v>A-d5s5</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="48">
@@ -1681,13 +1681,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B48" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C48" t="str">
-        <v>A-d3s6</v>
-      </c>
-      <c r="D48">
-        <v>1</v>
+        <v>A-d5s6</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="49">
@@ -1695,13 +1695,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B49" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C49" t="str">
-        <v>A-d3s1</v>
-      </c>
-      <c r="D49">
-        <v>4</v>
+        <v>A-d5s7</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="50">
@@ -1709,13 +1709,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B50" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C50" t="str">
-        <v>A-d4s6</v>
-      </c>
-      <c r="D50">
-        <v>5</v>
+        <v>A-d5s8</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="51">
@@ -1723,13 +1723,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B51" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C51" t="str">
-        <v>A-d2s1</v>
-      </c>
-      <c r="D51">
-        <v>5</v>
+        <v>A-d6s1</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="52">
@@ -1737,13 +1737,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B52" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C52" t="str">
-        <v>A-d6s5</v>
-      </c>
-      <c r="D52">
-        <v>5</v>
+        <v>A-d6s2</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="53">
@@ -1751,13 +1751,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B53" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C53" t="str">
-        <v>A-d5s8</v>
-      </c>
-      <c r="D53">
-        <v>6</v>
+        <v>A-d6s3</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="54">
@@ -1765,13 +1765,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B54" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C54" t="str">
-        <v>A-d5s7</v>
-      </c>
-      <c r="D54">
-        <v>6</v>
+        <v>A-d6s4</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="55">
@@ -1779,13 +1779,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B55" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C55" t="str">
-        <v>A-d5s6</v>
-      </c>
-      <c r="D55">
-        <v>6</v>
+        <v>A-d6s6</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="56">
@@ -1796,10 +1796,10 @@
         <v>moved</v>
       </c>
       <c r="C56" t="str">
-        <v>A-d5s5</v>
+        <v>A-d3s2</v>
       </c>
       <c r="D56">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -1810,10 +1810,10 @@
         <v>moved</v>
       </c>
       <c r="C57" t="str">
-        <v>A-d5s4</v>
+        <v>A-d3s3</v>
       </c>
       <c r="D57">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -1824,10 +1824,10 @@
         <v>moved</v>
       </c>
       <c r="C58" t="str">
-        <v>A-d5s2</v>
+        <v>A-d2s4</v>
       </c>
       <c r="D58">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -1838,16 +1838,184 @@
         <v>moved</v>
       </c>
       <c r="C59" t="str">
+        <v>A-d1s7</v>
+      </c>
+      <c r="D59">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B60" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C60" t="str">
+        <v>A-d3s6</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B61" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C61" t="str">
+        <v>A-d3s1</v>
+      </c>
+      <c r="D61">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B62" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C62" t="str">
+        <v>A-d4s6</v>
+      </c>
+      <c r="D62">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B63" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C63" t="str">
+        <v>A-d2s1</v>
+      </c>
+      <c r="D63">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B64" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C64" t="str">
+        <v>A-d6s5</v>
+      </c>
+      <c r="D64">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B65" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C65" t="str">
+        <v>A-d5s8</v>
+      </c>
+      <c r="D65">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B66" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C66" t="str">
+        <v>A-d5s7</v>
+      </c>
+      <c r="D66">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B67" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C67" t="str">
+        <v>A-d5s6</v>
+      </c>
+      <c r="D67">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B68" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C68" t="str">
+        <v>A-d5s5</v>
+      </c>
+      <c r="D68">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B69" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C69" t="str">
+        <v>A-d5s4</v>
+      </c>
+      <c r="D69">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B70" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C70" t="str">
+        <v>A-d5s2</v>
+      </c>
+      <c r="D70">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="B71" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C71" t="str">
         <v>A-d5s1</v>
       </c>
-      <c r="D59">
+      <c r="D71">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D59"/>
+  <autoFilter ref="A1:D71"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D59"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D71"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3497,13 +3665,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B12" t="str">
-        <v>Abs</v>
+        <v>Biceps</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>7</v>
@@ -3514,13 +3682,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B13" t="str">
-        <v>Biceps</v>
+        <v>Abs</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>7</v>
@@ -3684,19 +3852,19 @@
         <v>A</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>26</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="H2">
         <v>26</v>
@@ -4089,7 +4257,7 @@
         <v>Exported</v>
       </c>
       <c r="B41" t="str">
-        <v>2026-10-03T00:36:39.731Z</v>
+        <v>2026-10-03T13:49:21.057Z</v>
       </c>
     </row>
   </sheetData>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -17,16 +17,16 @@
     <sheet name="Config" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3">Weeks!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Body weight'!$A$1:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3">Weeks!$A$1:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Body weight'!$A$1:$D$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5">Settings!$A$1:$B$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">Programs!$A$1:$R$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Program info'!$A$1:$B$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11">Config!$A$1:$B$16</definedName>
   </definedNames>
 </workbook>
@@ -421,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J23"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -501,266 +501,266 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Cable Wrist Pulldown</v>
+        <v>Cable Punch ISO hold</v>
       </c>
       <c r="B3" t="str">
-        <v>Hypertrophy</v>
+        <v>Isometric</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-09-27</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-04</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H3">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Chest Press</v>
+        <v>Cable Wrist Pulldown</v>
       </c>
       <c r="B4" t="str">
         <v>Hypertrophy</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-27</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-09-30</v>
+        <v>2026-10-04</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H4">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Grip Trainer</v>
+        <v>Chest Press</v>
       </c>
       <c r="B5" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="str">
         <v>2026-09-28</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-30</v>
       </c>
       <c r="F5">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="H5">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>235</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Hack Squat</v>
+        <v>DB Clean &amp; Jerk Press</v>
       </c>
       <c r="B6" t="str">
-        <v>Hypertrophy</v>
+        <v>Explosive</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-09-30</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-04</v>
       </c>
       <c r="F6">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="H6">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>415</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Hip Thrust</v>
+        <v>Depth Drop → Broad Jump → Box Jump</v>
       </c>
       <c r="B7" t="str">
-        <v>Strength</v>
+        <v>Explosive</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-09-30</v>
-      </c>
-      <c r="F7">
-        <v>320</v>
-      </c>
-      <c r="G7">
-        <v>320</v>
-      </c>
-      <c r="H7">
-        <v>320</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>375</v>
+        <v>2026-10-04</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Explosive Unilateral Cable Row</v>
       </c>
       <c r="B8" t="str">
-        <v>Strength</v>
+        <v>Explosive</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-09-27</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-09-30</v>
+        <v>2026-10-04</v>
       </c>
       <c r="F8">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="G8">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="H8">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>210</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="B9" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-28</v>
       </c>
       <c r="F9">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="G9">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="H9">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>21</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Kneeling Cable Ab Crunch</v>
+        <v>Hack Squat</v>
       </c>
       <c r="B10" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-30</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-01</v>
       </c>
       <c r="F10">
-        <v>60</v>
+        <v>270</v>
       </c>
       <c r="G10">
-        <v>60</v>
+        <v>270</v>
       </c>
       <c r="H10">
-        <v>60</v>
+        <v>270</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>100</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Lat Pulldown, alternating single-arm</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="B11" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -769,188 +769,412 @@
         <v>2026-09-28</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-30</v>
       </c>
       <c r="F11">
-        <v>45</v>
+        <v>320</v>
       </c>
       <c r="G11">
-        <v>45</v>
+        <v>320</v>
       </c>
       <c r="H11">
-        <v>45</v>
+        <v>320</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>70</v>
+        <v>375</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Leg Extension ISO hold</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="B12" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-27</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-30</v>
       </c>
       <c r="F12">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="G12">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="H12">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>65</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="B13" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-29</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-10-01</v>
+        <v>2026-09-29</v>
       </c>
       <c r="F13">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="G13">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H13">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="I13">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>80</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Kneeling Cable Ab Crunch</v>
       </c>
       <c r="B14" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-29</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="F14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>65</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Suitcase Bottom-Up, single-arm</v>
+        <v>Lat Pulldown, alternating single-arm</v>
       </c>
       <c r="B15" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E15" t="str">
         <v>2026-09-29</v>
       </c>
       <c r="F15">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="G15">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="H15">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Zottman Curl</v>
+        <v>Lateral Bound / Skater Hop with Stick</v>
       </c>
       <c r="B16" t="str">
-        <v>Hypertrophy</v>
+        <v>Explosive</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="E16" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Leg Extension ISO hold</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Isometric</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="E17" t="str">
         <v>2026-09-29</v>
       </c>
-      <c r="E16" t="str">
+      <c r="F17">
+        <v>50</v>
+      </c>
+      <c r="G17">
+        <v>50</v>
+      </c>
+      <c r="H17">
+        <v>50</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Pogo Hops</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Explosive</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="E18" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Seated Zercher Good Morning</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="E19" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="F19">
+        <v>50</v>
+      </c>
+      <c r="G19">
+        <v>50</v>
+      </c>
+      <c r="H19">
+        <v>50</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Side Rear Delt Fly</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Isometric</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="E20" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="F20">
+        <v>50</v>
+      </c>
+      <c r="G20">
+        <v>50</v>
+      </c>
+      <c r="H20">
+        <v>50</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Split Squat Jumps</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Explosive</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="E21" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Suitcase Bottom-Up, single-arm</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="str">
         <v>2026-09-29</v>
       </c>
-      <c r="F16">
+      <c r="E22" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="F22">
+        <v>25</v>
+      </c>
+      <c r="G22">
+        <v>25</v>
+      </c>
+      <c r="H22">
+        <v>25</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Zottman Curl</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Hypertrophy</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="E23" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="F23">
         <v>15</v>
       </c>
-      <c r="G16">
+      <c r="G23">
         <v>15</v>
       </c>
-      <c r="H16">
+      <c r="H23">
         <v>15</v>
       </c>
-      <c r="I16">
+      <c r="I23">
         <v>0</v>
       </c>
-      <c r="J16">
+      <c r="J23">
         <v>23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J16"/>
+  <autoFilter ref="A1:J23"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J23"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1010,7 +1234,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D82"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.83203125" customWidth="1"/>
@@ -2012,10 +2236,164 @@
         <v>6</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B72" t="str">
+        <v>order</v>
+      </c>
+      <c r="C72" t="str">
+        <v/>
+      </c>
+      <c r="D72" t="str">
+        <v>6 1 2 3 4 5 7</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B73" t="str">
+        <v>done</v>
+      </c>
+      <c r="C73" t="str">
+        <v>B-d6s1</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B74" t="str">
+        <v>done</v>
+      </c>
+      <c r="C74" t="str">
+        <v>B-d6s2</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B75" t="str">
+        <v>done</v>
+      </c>
+      <c r="C75" t="str">
+        <v>B-d6s3</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B76" t="str">
+        <v>done</v>
+      </c>
+      <c r="C76" t="str">
+        <v>B-d6s6</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B77" t="str">
+        <v>done</v>
+      </c>
+      <c r="C77" t="str">
+        <v>B-d6s4</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B78" t="str">
+        <v>done</v>
+      </c>
+      <c r="C78" t="str">
+        <v>B-d5s2</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B79" t="str">
+        <v>done</v>
+      </c>
+      <c r="C79" t="str">
+        <v>B-d1s3</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B80" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C80" t="str">
+        <v>B-d6s5</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B81" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C81" t="str">
+        <v>B-d5s2</v>
+      </c>
+      <c r="D81">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B82" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C82" t="str">
+        <v>B-d1s3</v>
+      </c>
+      <c r="D82">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D71"/>
+  <autoFilter ref="A1:D82"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D71"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D82"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2049,7 +2427,7 @@
         <v>ex</v>
       </c>
       <c r="B3" t="str">
-        <v>{"deadlift":{"n":"Deadlift","eq":"barbell"}}</v>
+        <v>{"deadlift":{"n":"Deadlift","eq":"barbell"},"zercher":{"eq":"shortbar"}}</v>
       </c>
     </row>
     <row r="4">
@@ -2057,7 +2435,7 @@
         <v>exPh</v>
       </c>
       <c r="B4" t="str">
-        <v>{"canoe":"iso","romanadd":"strength","deskbands":"iso","spinal":"mob","platerot":"strength","suitcase":"strength","qlext":"strength"}</v>
+        <v>{"canoe":"iso","romanadd":"strength","deskbands":"iso","spinal":"mob","platerot":"strength","suitcase":"strength","qlext":"strength","skater":"exp","splitjump":"exp","cablerow":"exp","cablepunch":"iso","depthcombo":"exp","zercher":"strength"}</v>
       </c>
     </row>
     <row r="5">
@@ -2065,7 +2443,7 @@
         <v>ghBackup</v>
       </c>
       <c r="B5" t="str">
-        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"5oi19c","last":{"at":"2026-10-03T00:33:48.747Z","url":"https://github.com/jacgit18/iron-log/commit/575e42b0dddf1fec3435ae130c83ec09596aaa61"}}</v>
+        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"15dqvqq","last":{"at":"2026-10-03T13:49:23.534Z","url":"https://github.com/jacgit18/iron-log/commit/20cd6d3d4efda877aa668cc99be7edb20a759be7"}}</v>
       </c>
     </row>
     <row r="6">
@@ -2129,7 +2507,7 @@
         <v>phDef</v>
       </c>
       <c r="B13" t="str">
-        <v>{"A-d1s1:0":"hyp","A-d1s7:1":"iso","A-d1s3:0":"strength"}</v>
+        <v>{"A-d1s1:0":"hyp","A-d1s7:1":"iso","A-d1s3:0":"strength","B-d6s2:0":"exp","B-d6s3:0":"exp","B-d6s6:1":"exp","B-d6s6:0":"iso","B-d6s4:0":"exp","B-d6s5:1":"strength"}</v>
       </c>
     </row>
     <row r="14">
@@ -2166,7 +2544,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O36"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -3454,17 +3832,440 @@
         <v>zercher</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Cable Punch ISO hold</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Isometric</v>
+      </c>
+      <c r="E28">
+        <v>30</v>
+      </c>
+      <c r="F28">
+        <v>4</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28">
+        <v>15</v>
+      </c>
+      <c r="I28" t="str">
+        <v>30×15s, 30×15s, 30×15s, 30×15s</v>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v>Obliques, Abs</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Chest, Front delts</v>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <v>B-d6s6</v>
+      </c>
+      <c r="O28" t="str">
+        <v>cablepunch</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Cable Wrist Pulldown</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Hypertrophy</v>
+      </c>
+      <c r="E29">
+        <v>33</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29">
+        <v>15</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v>33×15, 33×15</v>
+      </c>
+      <c r="J29">
+        <v>990</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Forearms &amp; grip</v>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v>B-d1s3</v>
+      </c>
+      <c r="O29" t="str">
+        <v>wristpd</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C30" t="str">
+        <v>DB Clean &amp; Jerk Press</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Explosive</v>
+      </c>
+      <c r="E30">
+        <v>20</v>
+      </c>
+      <c r="F30">
+        <v>3</v>
+      </c>
+      <c r="G30">
+        <v>10</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v>20×10, 20×10, 20×10</v>
+      </c>
+      <c r="J30">
+        <v>600</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Quads, Glutes, Front delts</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Traps, Triceps, Hamstrings</v>
+      </c>
+      <c r="M30" t="str">
+        <v>From check-off</v>
+      </c>
+      <c r="N30" t="str">
+        <v>B-d5s2</v>
+      </c>
+      <c r="O30" t="str">
+        <v>dbclean</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Depth Drop → Broad Jump → Box Jump</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Explosive</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31">
+        <v>3</v>
+      </c>
+      <c r="G31">
+        <v>5</v>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v>BW×5, BW×5, BW×5</v>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v>Quads, Glutes, Calves</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Hamstrings</v>
+      </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
+        <v>B-d6s4</v>
+      </c>
+      <c r="O31" t="str">
+        <v>depthcombo</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Explosive Unilateral Cable Row</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Explosive</v>
+      </c>
+      <c r="E32">
+        <v>30</v>
+      </c>
+      <c r="F32">
+        <v>4</v>
+      </c>
+      <c r="G32">
+        <v>10</v>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v>30×10, 30×10, 30×10, 30×10</v>
+      </c>
+      <c r="J32">
+        <v>1200</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Lats, Upper back</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Rear delts, Biceps</v>
+      </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
+        <v>B-d6s6</v>
+      </c>
+      <c r="O32" t="str">
+        <v>cablerow</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Lateral Bound / Skater Hop with Stick</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Explosive</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33">
+        <v>3</v>
+      </c>
+      <c r="G33">
+        <v>10</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v>BW×10, BW×10, BW×10</v>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v>Glutes, Outer hip (abductors), Quads</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Inner thigh (adductors), Calves</v>
+      </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <v>B-d6s2</v>
+      </c>
+      <c r="O33" t="str">
+        <v>skater</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Pogo Hops</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Explosive</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34">
+        <v>3</v>
+      </c>
+      <c r="G34">
+        <v>10</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v>BW×10, BW×10, BW×10</v>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v>Calves</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Shins</v>
+      </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
+        <v>B-d6s1</v>
+      </c>
+      <c r="O34" t="str">
+        <v>pogo</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Seated Zercher Good Morning</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E35">
+        <v>50</v>
+      </c>
+      <c r="F35">
+        <v>4</v>
+      </c>
+      <c r="G35">
+        <v>6</v>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v>50×6, 50×6, 50×6, 50×6</v>
+      </c>
+      <c r="J35">
+        <v>1200</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Lower back</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Glutes, Hamstrings, Upper back</v>
+      </c>
+      <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
+        <v>B-d6s5</v>
+      </c>
+      <c r="O35" t="str">
+        <v>zercher</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Split Squat Jumps</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Explosive</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36">
+        <v>3</v>
+      </c>
+      <c r="G36">
+        <v>10</v>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v>BW×10, BW×10, BW×10</v>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v>Quads, Glutes</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Calves, Hamstrings</v>
+      </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
+        <v>B-d6s3</v>
+      </c>
+      <c r="O36" t="str">
+        <v>splitjump</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O27"/>
+  <autoFilter ref="A1:O36"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O36"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E38"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -3665,13 +4466,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B12" t="str">
-        <v>Biceps</v>
+        <v>Abs</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>7</v>
@@ -3682,13 +4483,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B13" t="str">
-        <v>Abs</v>
+        <v>Biceps</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E13">
         <v>7</v>
@@ -3796,17 +4597,340 @@
         <v>2</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Glutes</v>
+      </c>
+      <c r="C20">
+        <v>12</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Quads</v>
+      </c>
+      <c r="C21">
+        <v>12</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Calves</v>
+      </c>
+      <c r="C22">
+        <v>6</v>
+      </c>
+      <c r="D22">
+        <v>6</v>
+      </c>
+      <c r="E22">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Hamstrings</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>13</v>
+      </c>
+      <c r="E23">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Upper back</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="E24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Front delts</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Lats</v>
+      </c>
+      <c r="C26">
+        <v>4</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Lower back</v>
+      </c>
+      <c r="C27">
+        <v>4</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Obliques</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Abs</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Outer hip (abductors)</v>
+      </c>
+      <c r="C30">
+        <v>3</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Rear delts</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Biceps</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>4</v>
+      </c>
+      <c r="E32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Forearms &amp; grip</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Chest</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>4</v>
+      </c>
+      <c r="E34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Traps</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>3</v>
+      </c>
+      <c r="E35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Triceps</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>3</v>
+      </c>
+      <c r="E36">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Shins</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>3</v>
+      </c>
+      <c r="E37">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Inner thigh (adductors)</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>3</v>
+      </c>
+      <c r="E38">
+        <v>1.5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E19"/>
+  <autoFilter ref="A1:E38"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E38"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.83203125" customWidth="1"/>
@@ -3870,17 +4994,43 @@
         <v>26</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B3" t="str">
+        <v>B</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>60</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>13</v>
+      </c>
+      <c r="H3">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H2"/>
+  <autoFilter ref="A1:H3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -3916,10 +5066,24 @@
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C3">
+        <v>130.2</v>
+      </c>
+      <c r="D3">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D2"/>
+  <autoFilter ref="A1:D3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4257,7 +5421,7 @@
         <v>Exported</v>
       </c>
       <c r="B41" t="str">
-        <v>2026-10-03T13:49:21.057Z</v>
+        <v>2026-10-04T12:55:27.793Z</v>
       </c>
     </row>
   </sheetData>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -23,8 +23,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">Weeks!$A$1:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Body weight'!$A$1:$D$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5">Settings!$A$1:$B$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6">Programs!$A$1:$R$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Program info'!$A$1:$B$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6">Programs!$A$1:$R$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Program info'!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11">Config!$A$1:$B$16</definedName>
@@ -1209,13 +1209,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Emurmrw6glcpc</v>
+        <v>Emutz0kdpoll0</v>
       </c>
       <c r="B2" t="str">
-        <v>deadlift</v>
+        <v>split-stance-cable-hip-rotation</v>
       </c>
       <c r="C2" t="str">
-        <v>Deadlift</v>
+        <v>Split Stance Cable Hip Rotation</v>
       </c>
       <c r="D2" t="str">
         <v>strength</v>
@@ -2427,7 +2427,7 @@
         <v>ex</v>
       </c>
       <c r="B3" t="str">
-        <v>{"deadlift":{"n":"Deadlift","eq":"barbell"},"zercher":{"eq":"shortbar"}}</v>
+        <v>{"deadlift":{"n":"Deadlift","eq":"barbell"},"zercher":{"eq":"shortbar"},"split-stance-cable-hip-rotation":{"n":"Split Stance Cable Hip Rotation","url":"https://youtu.be/ixIEilUM2aY","eq":"cable"}}</v>
       </c>
     </row>
     <row r="4">
@@ -5421,7 +5421,7 @@
         <v>Exported</v>
       </c>
       <c r="B41" t="str">
-        <v>2026-10-04T12:55:27.793Z</v>
+        <v>2026-10-04T15:24:02.324Z</v>
       </c>
     </row>
   </sheetData>
@@ -5434,7 +5434,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R65"/>
+  <dimension ref="A1:R133"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="5.83203125" customWidth="1"/>
@@ -9096,17 +9096,3825 @@
         <v/>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>B</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66" t="str">
+        <v>B-d1s1</v>
+      </c>
+      <c r="H66" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I66" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
+        <v/>
+      </c>
+      <c r="L66" t="str">
+        <v>latpdbi</v>
+      </c>
+      <c r="M66" t="str">
+        <v>Lat Pulldown</v>
+      </c>
+      <c r="N66" t="str">
+        <v>hyp</v>
+      </c>
+      <c r="O66">
+        <v>45</v>
+      </c>
+      <c r="P66" t="str">
+        <v/>
+      </c>
+      <c r="Q66" t="str">
+        <v/>
+      </c>
+      <c r="R66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>B</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67">
+        <v>2</v>
+      </c>
+      <c r="G67" t="str">
+        <v>B-d1s2</v>
+      </c>
+      <c r="H67" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I67" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+      <c r="K67" t="str">
+        <v/>
+      </c>
+      <c r="L67" t="str">
+        <v>hack</v>
+      </c>
+      <c r="M67" t="str">
+        <v>Hack Squat</v>
+      </c>
+      <c r="N67" t="str">
+        <v>hyp</v>
+      </c>
+      <c r="O67">
+        <v>270</v>
+      </c>
+      <c r="P67" t="str">
+        <v/>
+      </c>
+      <c r="Q67" t="str">
+        <v/>
+      </c>
+      <c r="R67" t="str">
+        <v>Feet low on the plate, narrow stance for quads</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>B</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68">
+        <v>3</v>
+      </c>
+      <c r="G68" t="str">
+        <v>B-d1s3</v>
+      </c>
+      <c r="H68" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I68" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+      <c r="K68" t="str">
+        <v/>
+      </c>
+      <c r="L68" t="str">
+        <v>wristpd</v>
+      </c>
+      <c r="M68" t="str">
+        <v>Cable Wrist Pulldown</v>
+      </c>
+      <c r="N68" t="str">
+        <v>hyp</v>
+      </c>
+      <c r="O68">
+        <v>33</v>
+      </c>
+      <c r="P68" t="str">
+        <v/>
+      </c>
+      <c r="Q68" t="str">
+        <v/>
+      </c>
+      <c r="R68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>B</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69">
+        <v>4</v>
+      </c>
+      <c r="G69" t="str">
+        <v>B-d1s4</v>
+      </c>
+      <c r="H69" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I69" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+      <c r="K69" t="str">
+        <v/>
+      </c>
+      <c r="L69" t="str">
+        <v>platerot</v>
+      </c>
+      <c r="M69" t="str">
+        <v>Plate Torso Rotation</v>
+      </c>
+      <c r="N69" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O69">
+        <v>10</v>
+      </c>
+      <c r="P69" t="str">
+        <v/>
+      </c>
+      <c r="Q69" t="str">
+        <v/>
+      </c>
+      <c r="R69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>B</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70">
+        <v>5</v>
+      </c>
+      <c r="G70" t="str">
+        <v>B-d1s5</v>
+      </c>
+      <c r="H70" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I70" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+      <c r="K70" t="str">
+        <v/>
+      </c>
+      <c r="L70" t="str">
+        <v>innerthigh</v>
+      </c>
+      <c r="M70" t="str">
+        <v>Inner Thigh Abduction</v>
+      </c>
+      <c r="N70" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O70">
+        <v>180</v>
+      </c>
+      <c r="P70" t="str">
+        <v/>
+      </c>
+      <c r="Q70" t="str">
+        <v/>
+      </c>
+      <c r="R70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>B</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71">
+        <v>6</v>
+      </c>
+      <c r="G71" t="str">
+        <v>B-d1s6</v>
+      </c>
+      <c r="H71" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I71" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
+      <c r="K71" t="str">
+        <v/>
+      </c>
+      <c r="L71" t="str">
+        <v>outerthigh</v>
+      </c>
+      <c r="M71" t="str">
+        <v>Outer Thigh Adduction</v>
+      </c>
+      <c r="N71" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O71">
+        <v>160</v>
+      </c>
+      <c r="P71" t="str">
+        <v/>
+      </c>
+      <c r="Q71" t="str">
+        <v/>
+      </c>
+      <c r="R71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>B</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D72" t="str">
+        <v/>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72">
+        <v>7</v>
+      </c>
+      <c r="G72" t="str">
+        <v>B-d1s7</v>
+      </c>
+      <c r="H72" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I72" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J72" t="str">
+        <v/>
+      </c>
+      <c r="K72" t="str">
+        <v/>
+      </c>
+      <c r="L72" t="str">
+        <v>qlext</v>
+      </c>
+      <c r="M72" t="str">
+        <v>Side Lateral QL Extension</v>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+      <c r="P72" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q72" t="str">
+        <v/>
+      </c>
+      <c r="R72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>B</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D73" t="str">
+        <v/>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73">
+        <v>8</v>
+      </c>
+      <c r="G73" t="str">
+        <v>B-d1s8</v>
+      </c>
+      <c r="H73" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I73" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J73" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K73" t="str">
+        <v/>
+      </c>
+      <c r="L73" t="str">
+        <v>chestpress</v>
+      </c>
+      <c r="M73" t="str">
+        <v>Chest Press</v>
+      </c>
+      <c r="N73" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O73">
+        <v>35</v>
+      </c>
+      <c r="P73" t="str">
+        <v/>
+      </c>
+      <c r="Q73" t="str">
+        <v/>
+      </c>
+      <c r="R73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>B</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D74" t="str">
+        <v/>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74">
+        <v>8</v>
+      </c>
+      <c r="G74" t="str">
+        <v>B-d1s8</v>
+      </c>
+      <c r="H74" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I74" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J74" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K74" t="str">
+        <v/>
+      </c>
+      <c r="L74" t="str">
+        <v>zercher</v>
+      </c>
+      <c r="M74" t="str">
+        <v>Seated Zercher Good Morning</v>
+      </c>
+      <c r="N74" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O74">
+        <v>50</v>
+      </c>
+      <c r="P74" t="str">
+        <v/>
+      </c>
+      <c r="Q74" t="str">
+        <v/>
+      </c>
+      <c r="R74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>B</v>
+      </c>
+      <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D75" t="str">
+        <v/>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75">
+        <v>9</v>
+      </c>
+      <c r="G75" t="str">
+        <v>B-d1s9</v>
+      </c>
+      <c r="H75" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I75" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J75" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K75" t="str">
+        <v/>
+      </c>
+      <c r="L75" t="str">
+        <v>zottman</v>
+      </c>
+      <c r="M75" t="str">
+        <v>Zottman Curl</v>
+      </c>
+      <c r="N75" t="str">
+        <v>hyp</v>
+      </c>
+      <c r="O75">
+        <v>15</v>
+      </c>
+      <c r="P75" t="str">
+        <v/>
+      </c>
+      <c r="Q75" t="str">
+        <v>3 × 15</v>
+      </c>
+      <c r="R75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>B</v>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D76" t="str">
+        <v/>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76">
+        <v>9</v>
+      </c>
+      <c r="G76" t="str">
+        <v>B-d1s9</v>
+      </c>
+      <c r="H76" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I76" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J76" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K76" t="str">
+        <v/>
+      </c>
+      <c r="L76" t="str">
+        <v>kbleg</v>
+      </c>
+      <c r="M76" t="str">
+        <v>Kettlebell Leg Raise</v>
+      </c>
+      <c r="N76" t="str">
+        <v>iso</v>
+      </c>
+      <c r="O76">
+        <v>15</v>
+      </c>
+      <c r="P76" t="str">
+        <v/>
+      </c>
+      <c r="Q76" t="str">
+        <v>3 × 15 s hold</v>
+      </c>
+      <c r="R76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>B</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D77" t="str">
+        <v/>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77">
+        <v>10</v>
+      </c>
+      <c r="G77" t="str">
+        <v>B-d1s10</v>
+      </c>
+      <c r="H77" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+      <c r="K77" t="str">
+        <v/>
+      </c>
+      <c r="L77" t="str">
+        <v>grip</v>
+      </c>
+      <c r="M77" t="str">
+        <v>Grip Trainer</v>
+      </c>
+      <c r="N77" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O77">
+        <v>200</v>
+      </c>
+      <c r="P77" t="str">
+        <v/>
+      </c>
+      <c r="Q77" t="str">
+        <v/>
+      </c>
+      <c r="R77" t="str">
+        <v>With a grip trainer</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>B</v>
+      </c>
+      <c r="B78">
+        <v>1</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Day 1</v>
+      </c>
+      <c r="D78" t="str">
+        <v/>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78">
+        <v>11</v>
+      </c>
+      <c r="G78" t="str">
+        <v>B-d1s11</v>
+      </c>
+      <c r="H78" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I78" t="str">
+        <v/>
+      </c>
+      <c r="J78" t="str">
+        <v/>
+      </c>
+      <c r="K78" t="str">
+        <v/>
+      </c>
+      <c r="L78" t="str">
+        <v>canoe</v>
+      </c>
+      <c r="M78" t="str">
+        <v>Canoe Stretch</v>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78">
+        <v>10</v>
+      </c>
+      <c r="P78" t="str">
+        <v/>
+      </c>
+      <c r="Q78" t="str">
+        <v/>
+      </c>
+      <c r="R78" t="str">
+        <v>With a stick or barbell</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>B</v>
+      </c>
+      <c r="B79">
+        <v>2</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="G79" t="str">
+        <v>B-d2s1</v>
+      </c>
+      <c r="H79" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I79" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J79" t="str">
+        <v>either</v>
+      </c>
+      <c r="K79" t="str">
+        <v>Whichever is free</v>
+      </c>
+      <c r="L79" t="str">
+        <v>farmers</v>
+      </c>
+      <c r="M79" t="str">
+        <v>Farmers Carry</v>
+      </c>
+      <c r="N79" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O79">
+        <v>40</v>
+      </c>
+      <c r="P79" t="str">
+        <v/>
+      </c>
+      <c r="Q79" t="str">
+        <v/>
+      </c>
+      <c r="R79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>B</v>
+      </c>
+      <c r="B80">
+        <v>2</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="G80" t="str">
+        <v>B-d2s1</v>
+      </c>
+      <c r="H80" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I80" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J80" t="str">
+        <v>either</v>
+      </c>
+      <c r="K80" t="str">
+        <v>Whichever is free</v>
+      </c>
+      <c r="L80" t="str">
+        <v>dblunge</v>
+      </c>
+      <c r="M80" t="str">
+        <v>DB Lunge</v>
+      </c>
+      <c r="N80" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O80">
+        <v>40</v>
+      </c>
+      <c r="P80" t="str">
+        <v/>
+      </c>
+      <c r="Q80" t="str">
+        <v/>
+      </c>
+      <c r="R80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>B</v>
+      </c>
+      <c r="B81">
+        <v>2</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D81" t="str">
+        <v/>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81">
+        <v>2</v>
+      </c>
+      <c r="G81" t="str">
+        <v>B-d2s2</v>
+      </c>
+      <c r="H81" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I81" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J81" t="str">
+        <v/>
+      </c>
+      <c r="K81" t="str">
+        <v/>
+      </c>
+      <c r="L81" t="str">
+        <v>ohtri</v>
+      </c>
+      <c r="M81" t="str">
+        <v>Overhead Tricep Extension</v>
+      </c>
+      <c r="N81" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O81">
+        <v>17</v>
+      </c>
+      <c r="P81" t="str">
+        <v/>
+      </c>
+      <c r="Q81" t="str">
+        <v/>
+      </c>
+      <c r="R81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>B</v>
+      </c>
+      <c r="B82">
+        <v>2</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D82" t="str">
+        <v/>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82">
+        <v>3</v>
+      </c>
+      <c r="G82" t="str">
+        <v>B-d2s3</v>
+      </c>
+      <c r="H82" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I82" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J82" t="str">
+        <v>either</v>
+      </c>
+      <c r="K82" t="str">
+        <v>Whichever is free</v>
+      </c>
+      <c r="L82" t="str">
+        <v>reardelt</v>
+      </c>
+      <c r="M82" t="str">
+        <v>Side Rear Delt Fly</v>
+      </c>
+      <c r="N82" t="str">
+        <v>iso</v>
+      </c>
+      <c r="O82">
+        <v>50</v>
+      </c>
+      <c r="P82" t="str">
+        <v/>
+      </c>
+      <c r="Q82" t="str">
+        <v>4 × 15 s per arm</v>
+      </c>
+      <c r="R82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>B</v>
+      </c>
+      <c r="B83">
+        <v>2</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D83" t="str">
+        <v/>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83">
+        <v>3</v>
+      </c>
+      <c r="G83" t="str">
+        <v>B-d2s3</v>
+      </c>
+      <c r="H83" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I83" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J83" t="str">
+        <v>either</v>
+      </c>
+      <c r="K83" t="str">
+        <v>Whichever is free</v>
+      </c>
+      <c r="L83" t="str">
+        <v>facepull</v>
+      </c>
+      <c r="M83" t="str">
+        <v>Face Pull</v>
+      </c>
+      <c r="N83" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O83">
+        <v>30</v>
+      </c>
+      <c r="P83" t="str">
+        <v/>
+      </c>
+      <c r="Q83" t="str">
+        <v/>
+      </c>
+      <c r="R83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>B</v>
+      </c>
+      <c r="B84">
+        <v>2</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84">
+        <v>4</v>
+      </c>
+      <c r="G84" t="str">
+        <v>B-d2s4</v>
+      </c>
+      <c r="H84" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I84" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J84" t="str">
+        <v/>
+      </c>
+      <c r="K84" t="str">
+        <v/>
+      </c>
+      <c r="L84" t="str">
+        <v>cablecrunch</v>
+      </c>
+      <c r="M84" t="str">
+        <v>Kneeling Cable Ab Crunch</v>
+      </c>
+      <c r="N84" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O84">
+        <v>60</v>
+      </c>
+      <c r="P84" t="str">
+        <v/>
+      </c>
+      <c r="Q84" t="str">
+        <v/>
+      </c>
+      <c r="R84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>B</v>
+      </c>
+      <c r="B85">
+        <v>2</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85">
+        <v>5</v>
+      </c>
+      <c r="G85" t="str">
+        <v>B-d2s5</v>
+      </c>
+      <c r="H85" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I85" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J85" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K85" t="str">
+        <v/>
+      </c>
+      <c r="L85" t="str">
+        <v>hipthrust</v>
+      </c>
+      <c r="M85" t="str">
+        <v>Hip Thrust</v>
+      </c>
+      <c r="N85" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O85">
+        <v>320</v>
+      </c>
+      <c r="P85" t="str">
+        <v/>
+      </c>
+      <c r="Q85" t="str">
+        <v/>
+      </c>
+      <c r="R85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>B</v>
+      </c>
+      <c r="B86">
+        <v>2</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D86" t="str">
+        <v/>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86">
+        <v>5</v>
+      </c>
+      <c r="G86" t="str">
+        <v>B-d2s5</v>
+      </c>
+      <c r="H86" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I86" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J86" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K86" t="str">
+        <v/>
+      </c>
+      <c r="L86" t="str">
+        <v>chestpress</v>
+      </c>
+      <c r="M86" t="str">
+        <v>Chest Press</v>
+      </c>
+      <c r="N86" t="str">
+        <v>hyp</v>
+      </c>
+      <c r="O86">
+        <v>25</v>
+      </c>
+      <c r="P86" t="str">
+        <v/>
+      </c>
+      <c r="Q86" t="str">
+        <v/>
+      </c>
+      <c r="R86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>B</v>
+      </c>
+      <c r="B87">
+        <v>2</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D87" t="str">
+        <v/>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87">
+        <v>6</v>
+      </c>
+      <c r="G87" t="str">
+        <v>B-d2s6</v>
+      </c>
+      <c r="H87" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I87" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J87" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K87" t="str">
+        <v/>
+      </c>
+      <c r="L87" t="str">
+        <v>bss</v>
+      </c>
+      <c r="M87" t="str">
+        <v>Bulgarian Split Squat</v>
+      </c>
+      <c r="N87" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O87">
+        <v>40</v>
+      </c>
+      <c r="P87" t="str">
+        <v/>
+      </c>
+      <c r="Q87" t="str">
+        <v/>
+      </c>
+      <c r="R87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>B</v>
+      </c>
+      <c r="B88">
+        <v>2</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D88" t="str">
+        <v/>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88">
+        <v>6</v>
+      </c>
+      <c r="G88" t="str">
+        <v>B-d2s6</v>
+      </c>
+      <c r="H88" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I88" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J88" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K88" t="str">
+        <v/>
+      </c>
+      <c r="L88" t="str">
+        <v>legcurl</v>
+      </c>
+      <c r="M88" t="str">
+        <v>Prone Leg Curl</v>
+      </c>
+      <c r="N88" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O88">
+        <v>50</v>
+      </c>
+      <c r="P88" t="str">
+        <v/>
+      </c>
+      <c r="Q88" t="str">
+        <v/>
+      </c>
+      <c r="R88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>B</v>
+      </c>
+      <c r="B89">
+        <v>2</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D89" t="str">
+        <v/>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89">
+        <v>7</v>
+      </c>
+      <c r="G89" t="str">
+        <v>B-d2s7</v>
+      </c>
+      <c r="H89" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+      <c r="J89" t="str">
+        <v/>
+      </c>
+      <c r="K89" t="str">
+        <v/>
+      </c>
+      <c r="L89" t="str">
+        <v>grip</v>
+      </c>
+      <c r="M89" t="str">
+        <v>Grip Trainer</v>
+      </c>
+      <c r="N89" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O89">
+        <v>200</v>
+      </c>
+      <c r="P89" t="str">
+        <v/>
+      </c>
+      <c r="Q89" t="str">
+        <v/>
+      </c>
+      <c r="R89" t="str">
+        <v>With a grip trainer</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>B</v>
+      </c>
+      <c r="B90">
+        <v>2</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D90" t="str">
+        <v/>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90">
+        <v>8</v>
+      </c>
+      <c r="G90" t="str">
+        <v>B-d2s8</v>
+      </c>
+      <c r="H90" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90" t="str">
+        <v/>
+      </c>
+      <c r="K90" t="str">
+        <v/>
+      </c>
+      <c r="L90" t="str">
+        <v>db6</v>
+      </c>
+      <c r="M90" t="str">
+        <v>DB 6 Ways</v>
+      </c>
+      <c r="N90" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O90">
+        <v>10</v>
+      </c>
+      <c r="P90" t="str">
+        <v/>
+      </c>
+      <c r="Q90" t="str">
+        <v>2 × 6</v>
+      </c>
+      <c r="R90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>B</v>
+      </c>
+      <c r="B91">
+        <v>3</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D91" t="str">
+        <v/>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91" t="str">
+        <v>B-d3s1</v>
+      </c>
+      <c r="H91" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I91" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J91" t="str">
+        <v/>
+      </c>
+      <c r="K91" t="str">
+        <v/>
+      </c>
+      <c r="L91" t="str">
+        <v>hack</v>
+      </c>
+      <c r="M91" t="str">
+        <v>Hack Squat</v>
+      </c>
+      <c r="N91" t="str">
+        <v>hyp</v>
+      </c>
+      <c r="O91">
+        <v>270</v>
+      </c>
+      <c r="P91" t="str">
+        <v/>
+      </c>
+      <c r="Q91" t="str">
+        <v/>
+      </c>
+      <c r="R91" t="str">
+        <v>Feet low on the plate, narrow stance for quads</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>B</v>
+      </c>
+      <c r="B92">
+        <v>3</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D92" t="str">
+        <v/>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92">
+        <v>2</v>
+      </c>
+      <c r="G92" t="str">
+        <v>B-d3s2</v>
+      </c>
+      <c r="H92" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I92" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J92" t="str">
+        <v/>
+      </c>
+      <c r="K92" t="str">
+        <v/>
+      </c>
+      <c r="L92" t="str">
+        <v>latpdbi</v>
+      </c>
+      <c r="M92" t="str">
+        <v>Lat Pulldown</v>
+      </c>
+      <c r="N92" t="str">
+        <v>hyp</v>
+      </c>
+      <c r="O92">
+        <v>45</v>
+      </c>
+      <c r="P92" t="str">
+        <v/>
+      </c>
+      <c r="Q92" t="str">
+        <v/>
+      </c>
+      <c r="R92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>B</v>
+      </c>
+      <c r="B93">
+        <v>3</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D93" t="str">
+        <v/>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93">
+        <v>3</v>
+      </c>
+      <c r="G93" t="str">
+        <v>B-d3s3</v>
+      </c>
+      <c r="H93" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I93" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J93" t="str">
+        <v/>
+      </c>
+      <c r="K93" t="str">
+        <v/>
+      </c>
+      <c r="L93" t="str">
+        <v>wristpd</v>
+      </c>
+      <c r="M93" t="str">
+        <v>Cable Wrist Pulldown</v>
+      </c>
+      <c r="N93" t="str">
+        <v>hyp</v>
+      </c>
+      <c r="O93">
+        <v>33</v>
+      </c>
+      <c r="P93" t="str">
+        <v/>
+      </c>
+      <c r="Q93" t="str">
+        <v/>
+      </c>
+      <c r="R93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>B</v>
+      </c>
+      <c r="B94">
+        <v>3</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D94" t="str">
+        <v/>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94">
+        <v>4</v>
+      </c>
+      <c r="G94" t="str">
+        <v>B-d3s4</v>
+      </c>
+      <c r="H94" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I94" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J94" t="str">
+        <v/>
+      </c>
+      <c r="K94" t="str">
+        <v/>
+      </c>
+      <c r="L94" t="str">
+        <v>platerot</v>
+      </c>
+      <c r="M94" t="str">
+        <v>Plate Torso Rotation</v>
+      </c>
+      <c r="N94" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O94">
+        <v>10</v>
+      </c>
+      <c r="P94" t="str">
+        <v/>
+      </c>
+      <c r="Q94" t="str">
+        <v/>
+      </c>
+      <c r="R94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>B</v>
+      </c>
+      <c r="B95">
+        <v>3</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D95" t="str">
+        <v/>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95">
+        <v>5</v>
+      </c>
+      <c r="G95" t="str">
+        <v>B-d3s5</v>
+      </c>
+      <c r="H95" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I95" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J95" t="str">
+        <v>either</v>
+      </c>
+      <c r="K95" t="str">
+        <v>Whichever is free</v>
+      </c>
+      <c r="L95" t="str">
+        <v>reardelt</v>
+      </c>
+      <c r="M95" t="str">
+        <v>Side Rear Delt Fly</v>
+      </c>
+      <c r="N95" t="str">
+        <v>iso</v>
+      </c>
+      <c r="O95">
+        <v>50</v>
+      </c>
+      <c r="P95" t="str">
+        <v/>
+      </c>
+      <c r="Q95" t="str">
+        <v>4 × 15 s per arm</v>
+      </c>
+      <c r="R95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>B</v>
+      </c>
+      <c r="B96">
+        <v>3</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D96" t="str">
+        <v/>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96">
+        <v>5</v>
+      </c>
+      <c r="G96" t="str">
+        <v>B-d3s5</v>
+      </c>
+      <c r="H96" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I96" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J96" t="str">
+        <v>either</v>
+      </c>
+      <c r="K96" t="str">
+        <v>Whichever is free</v>
+      </c>
+      <c r="L96" t="str">
+        <v>facepull</v>
+      </c>
+      <c r="M96" t="str">
+        <v>Face Pull</v>
+      </c>
+      <c r="N96" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O96">
+        <v>30</v>
+      </c>
+      <c r="P96" t="str">
+        <v/>
+      </c>
+      <c r="Q96" t="str">
+        <v/>
+      </c>
+      <c r="R96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>B</v>
+      </c>
+      <c r="B97">
+        <v>3</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D97" t="str">
+        <v/>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97">
+        <v>6</v>
+      </c>
+      <c r="G97" t="str">
+        <v>B-d3s6</v>
+      </c>
+      <c r="H97" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I97" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J97" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K97" t="str">
+        <v/>
+      </c>
+      <c r="L97" t="str">
+        <v>cablepunch</v>
+      </c>
+      <c r="M97" t="str">
+        <v>Cable Punch ISO hold</v>
+      </c>
+      <c r="N97" t="str">
+        <v>iso</v>
+      </c>
+      <c r="O97">
+        <v>30</v>
+      </c>
+      <c r="P97" t="str">
+        <v/>
+      </c>
+      <c r="Q97" t="str">
+        <v>4 × 30 s hold</v>
+      </c>
+      <c r="R97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>B</v>
+      </c>
+      <c r="B98">
+        <v>3</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D98" t="str">
+        <v/>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98">
+        <v>6</v>
+      </c>
+      <c r="G98" t="str">
+        <v>B-d3s6</v>
+      </c>
+      <c r="H98" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I98" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J98" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K98" t="str">
+        <v/>
+      </c>
+      <c r="L98" t="str">
+        <v>cablerow</v>
+      </c>
+      <c r="M98" t="str">
+        <v>Explosive Unilateral Cable Row</v>
+      </c>
+      <c r="N98" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O98">
+        <v>30</v>
+      </c>
+      <c r="P98" t="str">
+        <v/>
+      </c>
+      <c r="Q98" t="str">
+        <v/>
+      </c>
+      <c r="R98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>B</v>
+      </c>
+      <c r="B99">
+        <v>3</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D99" t="str">
+        <v/>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99">
+        <v>7</v>
+      </c>
+      <c r="G99" t="str">
+        <v>B-d3s7</v>
+      </c>
+      <c r="H99" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+      <c r="J99" t="str">
+        <v/>
+      </c>
+      <c r="K99" t="str">
+        <v/>
+      </c>
+      <c r="L99" t="str">
+        <v>grip</v>
+      </c>
+      <c r="M99" t="str">
+        <v>Grip Trainer</v>
+      </c>
+      <c r="N99" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O99">
+        <v>200</v>
+      </c>
+      <c r="P99" t="str">
+        <v/>
+      </c>
+      <c r="Q99" t="str">
+        <v/>
+      </c>
+      <c r="R99" t="str">
+        <v>With a grip trainer</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>B</v>
+      </c>
+      <c r="B100">
+        <v>3</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D100" t="str">
+        <v/>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100">
+        <v>8</v>
+      </c>
+      <c r="G100" t="str">
+        <v>B-d3s8</v>
+      </c>
+      <c r="H100" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I100" t="str">
+        <v/>
+      </c>
+      <c r="J100" t="str">
+        <v/>
+      </c>
+      <c r="K100" t="str">
+        <v/>
+      </c>
+      <c r="L100" t="str">
+        <v>deskbands</v>
+      </c>
+      <c r="M100" t="str">
+        <v>Desk Bands</v>
+      </c>
+      <c r="N100" t="str">
+        <v/>
+      </c>
+      <c r="O100" t="str">
+        <v/>
+      </c>
+      <c r="P100" t="str">
+        <v/>
+      </c>
+      <c r="Q100" t="str">
+        <v/>
+      </c>
+      <c r="R100" t="str">
+        <v>With a resistance band</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>B</v>
+      </c>
+      <c r="B101">
+        <v>4</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D101" t="str">
+        <v/>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101" t="str">
+        <v>B-d4s1</v>
+      </c>
+      <c r="H101" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I101" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J101" t="str">
+        <v>either</v>
+      </c>
+      <c r="K101" t="str">
+        <v>Whichever is free</v>
+      </c>
+      <c r="L101" t="str">
+        <v>farmers</v>
+      </c>
+      <c r="M101" t="str">
+        <v>Farmers Carry</v>
+      </c>
+      <c r="N101" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O101">
+        <v>40</v>
+      </c>
+      <c r="P101" t="str">
+        <v/>
+      </c>
+      <c r="Q101" t="str">
+        <v/>
+      </c>
+      <c r="R101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>B</v>
+      </c>
+      <c r="B102">
+        <v>4</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D102" t="str">
+        <v/>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="G102" t="str">
+        <v>B-d4s1</v>
+      </c>
+      <c r="H102" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I102" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J102" t="str">
+        <v>either</v>
+      </c>
+      <c r="K102" t="str">
+        <v>Whichever is free</v>
+      </c>
+      <c r="L102" t="str">
+        <v>dblunge</v>
+      </c>
+      <c r="M102" t="str">
+        <v>DB Lunge</v>
+      </c>
+      <c r="N102" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O102">
+        <v>40</v>
+      </c>
+      <c r="P102" t="str">
+        <v/>
+      </c>
+      <c r="Q102" t="str">
+        <v/>
+      </c>
+      <c r="R102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>B</v>
+      </c>
+      <c r="B103">
+        <v>4</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D103" t="str">
+        <v/>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103">
+        <v>2</v>
+      </c>
+      <c r="G103" t="str">
+        <v>B-d4s2</v>
+      </c>
+      <c r="H103" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I103" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J103" t="str">
+        <v/>
+      </c>
+      <c r="K103" t="str">
+        <v/>
+      </c>
+      <c r="L103" t="str">
+        <v>innerthigh</v>
+      </c>
+      <c r="M103" t="str">
+        <v>Inner Thigh Abduction</v>
+      </c>
+      <c r="N103" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O103">
+        <v>180</v>
+      </c>
+      <c r="P103" t="str">
+        <v/>
+      </c>
+      <c r="Q103" t="str">
+        <v/>
+      </c>
+      <c r="R103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>B</v>
+      </c>
+      <c r="B104">
+        <v>4</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104">
+        <v>3</v>
+      </c>
+      <c r="G104" t="str">
+        <v>B-d4s3</v>
+      </c>
+      <c r="H104" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I104" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J104" t="str">
+        <v/>
+      </c>
+      <c r="K104" t="str">
+        <v/>
+      </c>
+      <c r="L104" t="str">
+        <v>outerthigh</v>
+      </c>
+      <c r="M104" t="str">
+        <v>Outer Thigh Adduction</v>
+      </c>
+      <c r="N104" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O104">
+        <v>160</v>
+      </c>
+      <c r="P104" t="str">
+        <v/>
+      </c>
+      <c r="Q104" t="str">
+        <v/>
+      </c>
+      <c r="R104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>B</v>
+      </c>
+      <c r="B105">
+        <v>4</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D105" t="str">
+        <v/>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105">
+        <v>4</v>
+      </c>
+      <c r="G105" t="str">
+        <v>B-d4s4</v>
+      </c>
+      <c r="H105" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I105" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J105" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K105" t="str">
+        <v/>
+      </c>
+      <c r="L105" t="str">
+        <v>arnold</v>
+      </c>
+      <c r="M105" t="str">
+        <v>Arnold Press</v>
+      </c>
+      <c r="N105" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O105">
+        <v>35</v>
+      </c>
+      <c r="P105" t="str">
+        <v/>
+      </c>
+      <c r="Q105" t="str">
+        <v/>
+      </c>
+      <c r="R105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>B</v>
+      </c>
+      <c r="B106">
+        <v>4</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D106" t="str">
+        <v/>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106">
+        <v>4</v>
+      </c>
+      <c r="G106" t="str">
+        <v>B-d4s4</v>
+      </c>
+      <c r="H106" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I106" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J106" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K106" t="str">
+        <v/>
+      </c>
+      <c r="L106" t="str">
+        <v>zercher</v>
+      </c>
+      <c r="M106" t="str">
+        <v>Seated Zercher Good Morning</v>
+      </c>
+      <c r="N106" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O106">
+        <v>50</v>
+      </c>
+      <c r="P106" t="str">
+        <v/>
+      </c>
+      <c r="Q106" t="str">
+        <v/>
+      </c>
+      <c r="R106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>B</v>
+      </c>
+      <c r="B107">
+        <v>4</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D107" t="str">
+        <v/>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107">
+        <v>5</v>
+      </c>
+      <c r="G107" t="str">
+        <v>B-d4s5</v>
+      </c>
+      <c r="H107" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I107" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J107" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K107" t="str">
+        <v/>
+      </c>
+      <c r="L107" t="str">
+        <v>hipthrust</v>
+      </c>
+      <c r="M107" t="str">
+        <v>Hip Thrust</v>
+      </c>
+      <c r="N107" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O107">
+        <v>320</v>
+      </c>
+      <c r="P107" t="str">
+        <v/>
+      </c>
+      <c r="Q107" t="str">
+        <v/>
+      </c>
+      <c r="R107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>B</v>
+      </c>
+      <c r="B108">
+        <v>4</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D108" t="str">
+        <v/>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108">
+        <v>5</v>
+      </c>
+      <c r="G108" t="str">
+        <v>B-d4s5</v>
+      </c>
+      <c r="H108" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I108" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J108" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K108" t="str">
+        <v/>
+      </c>
+      <c r="L108" t="str">
+        <v>chestpress</v>
+      </c>
+      <c r="M108" t="str">
+        <v>Chest Press</v>
+      </c>
+      <c r="N108" t="str">
+        <v>hyp</v>
+      </c>
+      <c r="O108">
+        <v>25</v>
+      </c>
+      <c r="P108" t="str">
+        <v/>
+      </c>
+      <c r="Q108" t="str">
+        <v/>
+      </c>
+      <c r="R108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>B</v>
+      </c>
+      <c r="B109">
+        <v>4</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D109" t="str">
+        <v/>
+      </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109">
+        <v>6</v>
+      </c>
+      <c r="G109" t="str">
+        <v>B-d4s6</v>
+      </c>
+      <c r="H109" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I109" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J109" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K109" t="str">
+        <v/>
+      </c>
+      <c r="L109" t="str">
+        <v>bss</v>
+      </c>
+      <c r="M109" t="str">
+        <v>Bulgarian Split Squat</v>
+      </c>
+      <c r="N109" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O109">
+        <v>40</v>
+      </c>
+      <c r="P109" t="str">
+        <v/>
+      </c>
+      <c r="Q109" t="str">
+        <v/>
+      </c>
+      <c r="R109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>B</v>
+      </c>
+      <c r="B110">
+        <v>4</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D110" t="str">
+        <v/>
+      </c>
+      <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110">
+        <v>6</v>
+      </c>
+      <c r="G110" t="str">
+        <v>B-d4s6</v>
+      </c>
+      <c r="H110" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I110" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J110" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K110" t="str">
+        <v/>
+      </c>
+      <c r="L110" t="str">
+        <v>legcurl</v>
+      </c>
+      <c r="M110" t="str">
+        <v>Prone Leg Curl</v>
+      </c>
+      <c r="N110" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O110">
+        <v>50</v>
+      </c>
+      <c r="P110" t="str">
+        <v/>
+      </c>
+      <c r="Q110" t="str">
+        <v/>
+      </c>
+      <c r="R110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>B</v>
+      </c>
+      <c r="B111">
+        <v>4</v>
+      </c>
+      <c r="C111" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D111" t="str">
+        <v/>
+      </c>
+      <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111">
+        <v>7</v>
+      </c>
+      <c r="G111" t="str">
+        <v>B-d4s7</v>
+      </c>
+      <c r="H111" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I111" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J111" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K111" t="str">
+        <v/>
+      </c>
+      <c r="L111" t="str">
+        <v>zottman</v>
+      </c>
+      <c r="M111" t="str">
+        <v>Zottman Curl</v>
+      </c>
+      <c r="N111" t="str">
+        <v>hyp</v>
+      </c>
+      <c r="O111">
+        <v>15</v>
+      </c>
+      <c r="P111" t="str">
+        <v/>
+      </c>
+      <c r="Q111" t="str">
+        <v>3 × 15</v>
+      </c>
+      <c r="R111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>B</v>
+      </c>
+      <c r="B112">
+        <v>4</v>
+      </c>
+      <c r="C112" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D112" t="str">
+        <v/>
+      </c>
+      <c r="E112" t="str">
+        <v/>
+      </c>
+      <c r="F112">
+        <v>7</v>
+      </c>
+      <c r="G112" t="str">
+        <v>B-d4s7</v>
+      </c>
+      <c r="H112" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I112" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J112" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K112" t="str">
+        <v/>
+      </c>
+      <c r="L112" t="str">
+        <v>kbleg</v>
+      </c>
+      <c r="M112" t="str">
+        <v>Kettlebell Leg Raise</v>
+      </c>
+      <c r="N112" t="str">
+        <v>iso</v>
+      </c>
+      <c r="O112">
+        <v>15</v>
+      </c>
+      <c r="P112" t="str">
+        <v/>
+      </c>
+      <c r="Q112" t="str">
+        <v>3 × 15 s hold</v>
+      </c>
+      <c r="R112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>B</v>
+      </c>
+      <c r="B113">
+        <v>4</v>
+      </c>
+      <c r="C113" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D113" t="str">
+        <v/>
+      </c>
+      <c r="E113" t="str">
+        <v/>
+      </c>
+      <c r="F113">
+        <v>8</v>
+      </c>
+      <c r="G113" t="str">
+        <v>B-d4s8</v>
+      </c>
+      <c r="H113" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I113" t="str">
+        <v/>
+      </c>
+      <c r="J113" t="str">
+        <v/>
+      </c>
+      <c r="K113" t="str">
+        <v/>
+      </c>
+      <c r="L113" t="str">
+        <v>grip</v>
+      </c>
+      <c r="M113" t="str">
+        <v>Grip Trainer</v>
+      </c>
+      <c r="N113" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O113">
+        <v>200</v>
+      </c>
+      <c r="P113" t="str">
+        <v/>
+      </c>
+      <c r="Q113" t="str">
+        <v/>
+      </c>
+      <c r="R113" t="str">
+        <v>With a grip trainer</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>B</v>
+      </c>
+      <c r="B114">
+        <v>4</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D114" t="str">
+        <v/>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114">
+        <v>9</v>
+      </c>
+      <c r="G114" t="str">
+        <v>B-d4s9</v>
+      </c>
+      <c r="H114" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I114" t="str">
+        <v/>
+      </c>
+      <c r="J114" t="str">
+        <v/>
+      </c>
+      <c r="K114" t="str">
+        <v/>
+      </c>
+      <c r="L114" t="str">
+        <v>deskbands</v>
+      </c>
+      <c r="M114" t="str">
+        <v>Desk Bands</v>
+      </c>
+      <c r="N114" t="str">
+        <v/>
+      </c>
+      <c r="O114" t="str">
+        <v/>
+      </c>
+      <c r="P114" t="str">
+        <v/>
+      </c>
+      <c r="Q114" t="str">
+        <v/>
+      </c>
+      <c r="R114" t="str">
+        <v>With a resistance band</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>B</v>
+      </c>
+      <c r="B115">
+        <v>5</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D115" t="str">
+        <v/>
+      </c>
+      <c r="E115" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F115">
+        <v>1</v>
+      </c>
+      <c r="G115" t="str">
+        <v>B-d5s1</v>
+      </c>
+      <c r="H115" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I115" t="str">
+        <v/>
+      </c>
+      <c r="J115" t="str">
+        <v/>
+      </c>
+      <c r="K115" t="str">
+        <v/>
+      </c>
+      <c r="L115" t="str">
+        <v>cablecrunch</v>
+      </c>
+      <c r="M115" t="str">
+        <v>Kneeling Cable Ab Crunch</v>
+      </c>
+      <c r="N115" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O115">
+        <v>60</v>
+      </c>
+      <c r="P115" t="str">
+        <v/>
+      </c>
+      <c r="Q115" t="str">
+        <v/>
+      </c>
+      <c r="R115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>B</v>
+      </c>
+      <c r="B116">
+        <v>5</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D116" t="str">
+        <v/>
+      </c>
+      <c r="E116" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F116">
+        <v>2</v>
+      </c>
+      <c r="G116" t="str">
+        <v>B-d5s2</v>
+      </c>
+      <c r="H116" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I116" t="str">
+        <v/>
+      </c>
+      <c r="J116" t="str">
+        <v/>
+      </c>
+      <c r="K116" t="str">
+        <v/>
+      </c>
+      <c r="L116" t="str">
+        <v>dbclean</v>
+      </c>
+      <c r="M116" t="str">
+        <v>DB Clean &amp; Jerk Press</v>
+      </c>
+      <c r="N116" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O116">
+        <v>20</v>
+      </c>
+      <c r="P116" t="str">
+        <v/>
+      </c>
+      <c r="Q116" t="str">
+        <v/>
+      </c>
+      <c r="R116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>B</v>
+      </c>
+      <c r="B117">
+        <v>5</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D117" t="str">
+        <v/>
+      </c>
+      <c r="E117" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F117">
+        <v>3</v>
+      </c>
+      <c r="G117" t="str">
+        <v>B-d5s3</v>
+      </c>
+      <c r="H117" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I117" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J117" t="str">
+        <v>either</v>
+      </c>
+      <c r="K117" t="str">
+        <v>Whichever is free</v>
+      </c>
+      <c r="L117" t="str">
+        <v>reardelt</v>
+      </c>
+      <c r="M117" t="str">
+        <v>Side Rear Delt Fly</v>
+      </c>
+      <c r="N117" t="str">
+        <v>iso</v>
+      </c>
+      <c r="O117">
+        <v>50</v>
+      </c>
+      <c r="P117" t="str">
+        <v/>
+      </c>
+      <c r="Q117" t="str">
+        <v>4 × 15 s per arm</v>
+      </c>
+      <c r="R117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>B</v>
+      </c>
+      <c r="B118">
+        <v>5</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D118" t="str">
+        <v/>
+      </c>
+      <c r="E118" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F118">
+        <v>3</v>
+      </c>
+      <c r="G118" t="str">
+        <v>B-d5s3</v>
+      </c>
+      <c r="H118" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I118" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J118" t="str">
+        <v>either</v>
+      </c>
+      <c r="K118" t="str">
+        <v>Whichever is free</v>
+      </c>
+      <c r="L118" t="str">
+        <v>facepull</v>
+      </c>
+      <c r="M118" t="str">
+        <v>Face Pull</v>
+      </c>
+      <c r="N118" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O118">
+        <v>30</v>
+      </c>
+      <c r="P118" t="str">
+        <v/>
+      </c>
+      <c r="Q118" t="str">
+        <v/>
+      </c>
+      <c r="R118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>B</v>
+      </c>
+      <c r="B119">
+        <v>5</v>
+      </c>
+      <c r="C119" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D119" t="str">
+        <v/>
+      </c>
+      <c r="E119" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F119">
+        <v>4</v>
+      </c>
+      <c r="G119" t="str">
+        <v>B-d5s4</v>
+      </c>
+      <c r="H119" t="str">
+        <v>Plyometric</v>
+      </c>
+      <c r="I119" t="str">
+        <v/>
+      </c>
+      <c r="J119" t="str">
+        <v/>
+      </c>
+      <c r="K119" t="str">
+        <v/>
+      </c>
+      <c r="L119" t="str">
+        <v>trxpike</v>
+      </c>
+      <c r="M119" t="str">
+        <v>TRX Pike Push-Up</v>
+      </c>
+      <c r="N119" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O119" t="str">
+        <v/>
+      </c>
+      <c r="P119" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q119" t="str">
+        <v/>
+      </c>
+      <c r="R119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>B</v>
+      </c>
+      <c r="B120">
+        <v>5</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D120" t="str">
+        <v/>
+      </c>
+      <c r="E120" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F120">
+        <v>5</v>
+      </c>
+      <c r="G120" t="str">
+        <v>B-d5s5</v>
+      </c>
+      <c r="H120" t="str">
+        <v>Plyometric</v>
+      </c>
+      <c r="I120" t="str">
+        <v/>
+      </c>
+      <c r="J120" t="str">
+        <v/>
+      </c>
+      <c r="K120" t="str">
+        <v/>
+      </c>
+      <c r="L120" t="str">
+        <v>trxrow</v>
+      </c>
+      <c r="M120" t="str">
+        <v>TRX Wide-Grip Row</v>
+      </c>
+      <c r="N120" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O120" t="str">
+        <v/>
+      </c>
+      <c r="P120" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q120" t="str">
+        <v/>
+      </c>
+      <c r="R120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>B</v>
+      </c>
+      <c r="B121">
+        <v>5</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D121" t="str">
+        <v/>
+      </c>
+      <c r="E121" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F121">
+        <v>6</v>
+      </c>
+      <c r="G121" t="str">
+        <v>B-d5s6</v>
+      </c>
+      <c r="H121" t="str">
+        <v>Plyometric</v>
+      </c>
+      <c r="I121" t="str">
+        <v/>
+      </c>
+      <c r="J121" t="str">
+        <v/>
+      </c>
+      <c r="K121" t="str">
+        <v/>
+      </c>
+      <c r="L121" t="str">
+        <v>medball</v>
+      </c>
+      <c r="M121" t="str">
+        <v>Med Ball Rotational Scoop</v>
+      </c>
+      <c r="N121" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O121" t="str">
+        <v/>
+      </c>
+      <c r="P121" t="str">
+        <v/>
+      </c>
+      <c r="Q121" t="str">
+        <v/>
+      </c>
+      <c r="R121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>B</v>
+      </c>
+      <c r="B122">
+        <v>5</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D122" t="str">
+        <v/>
+      </c>
+      <c r="E122" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F122">
+        <v>7</v>
+      </c>
+      <c r="G122" t="str">
+        <v>B-d5s7</v>
+      </c>
+      <c r="H122" t="str">
+        <v>Plyometric</v>
+      </c>
+      <c r="I122" t="str">
+        <v/>
+      </c>
+      <c r="J122" t="str">
+        <v/>
+      </c>
+      <c r="K122" t="str">
+        <v/>
+      </c>
+      <c r="L122" t="str">
+        <v>latwall</v>
+      </c>
+      <c r="M122" t="str">
+        <v>Lateral Wall Push</v>
+      </c>
+      <c r="N122" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O122" t="str">
+        <v/>
+      </c>
+      <c r="P122" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q122" t="str">
+        <v/>
+      </c>
+      <c r="R122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>B</v>
+      </c>
+      <c r="B123">
+        <v>5</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D123" t="str">
+        <v/>
+      </c>
+      <c r="E123" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F123">
+        <v>8</v>
+      </c>
+      <c r="G123" t="str">
+        <v>B-d5s8</v>
+      </c>
+      <c r="H123" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I123" t="str">
+        <v/>
+      </c>
+      <c r="J123" t="str">
+        <v/>
+      </c>
+      <c r="K123" t="str">
+        <v/>
+      </c>
+      <c r="L123" t="str">
+        <v>db6</v>
+      </c>
+      <c r="M123" t="str">
+        <v>DB 6 Ways</v>
+      </c>
+      <c r="N123" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O123">
+        <v>10</v>
+      </c>
+      <c r="P123" t="str">
+        <v/>
+      </c>
+      <c r="Q123" t="str">
+        <v>2 × 6</v>
+      </c>
+      <c r="R123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>B</v>
+      </c>
+      <c r="B124">
+        <v>5</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D124" t="str">
+        <v/>
+      </c>
+      <c r="E124" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F124">
+        <v>9</v>
+      </c>
+      <c r="G124" t="str">
+        <v>B-d5s9</v>
+      </c>
+      <c r="H124" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I124" t="str">
+        <v/>
+      </c>
+      <c r="J124" t="str">
+        <v/>
+      </c>
+      <c r="K124" t="str">
+        <v/>
+      </c>
+      <c r="L124" t="str">
+        <v>spinal</v>
+      </c>
+      <c r="M124" t="str">
+        <v>Spinal Waves</v>
+      </c>
+      <c r="N124" t="str">
+        <v>mob</v>
+      </c>
+      <c r="O124" t="str">
+        <v/>
+      </c>
+      <c r="P124" t="str">
+        <v/>
+      </c>
+      <c r="Q124" t="str">
+        <v/>
+      </c>
+      <c r="R124" t="str">
+        <v>Standing, no equipment</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>B</v>
+      </c>
+      <c r="B125">
+        <v>6</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D125" t="str">
+        <v/>
+      </c>
+      <c r="E125" t="str">
+        <v/>
+      </c>
+      <c r="F125">
+        <v>1</v>
+      </c>
+      <c r="G125" t="str">
+        <v>B-d6s1</v>
+      </c>
+      <c r="H125" t="str">
+        <v>Plyometric</v>
+      </c>
+      <c r="I125" t="str">
+        <v/>
+      </c>
+      <c r="J125" t="str">
+        <v/>
+      </c>
+      <c r="K125" t="str">
+        <v/>
+      </c>
+      <c r="L125" t="str">
+        <v>pogo</v>
+      </c>
+      <c r="M125" t="str">
+        <v>Pogo Hops</v>
+      </c>
+      <c r="N125" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O125" t="str">
+        <v/>
+      </c>
+      <c r="P125" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q125" t="str">
+        <v>3 × 10</v>
+      </c>
+      <c r="R125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>B</v>
+      </c>
+      <c r="B126">
+        <v>6</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D126" t="str">
+        <v/>
+      </c>
+      <c r="E126" t="str">
+        <v/>
+      </c>
+      <c r="F126">
+        <v>2</v>
+      </c>
+      <c r="G126" t="str">
+        <v>B-d6s2</v>
+      </c>
+      <c r="H126" t="str">
+        <v>Plyometric</v>
+      </c>
+      <c r="I126" t="str">
+        <v/>
+      </c>
+      <c r="J126" t="str">
+        <v/>
+      </c>
+      <c r="K126" t="str">
+        <v/>
+      </c>
+      <c r="L126" t="str">
+        <v>skater</v>
+      </c>
+      <c r="M126" t="str">
+        <v>Lateral Bound / Skater Hop with Stick</v>
+      </c>
+      <c r="N126" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O126" t="str">
+        <v/>
+      </c>
+      <c r="P126" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q126" t="str">
+        <v>3 × 5, hold 3 s</v>
+      </c>
+      <c r="R126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>B</v>
+      </c>
+      <c r="B127">
+        <v>6</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D127" t="str">
+        <v/>
+      </c>
+      <c r="E127" t="str">
+        <v/>
+      </c>
+      <c r="F127">
+        <v>3</v>
+      </c>
+      <c r="G127" t="str">
+        <v>B-d6s3</v>
+      </c>
+      <c r="H127" t="str">
+        <v>Plyometric</v>
+      </c>
+      <c r="I127" t="str">
+        <v/>
+      </c>
+      <c r="J127" t="str">
+        <v/>
+      </c>
+      <c r="K127" t="str">
+        <v/>
+      </c>
+      <c r="L127" t="str">
+        <v>splitjump</v>
+      </c>
+      <c r="M127" t="str">
+        <v>Split Squat Jumps</v>
+      </c>
+      <c r="N127" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O127" t="str">
+        <v/>
+      </c>
+      <c r="P127" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q127" t="str">
+        <v>3 × 5</v>
+      </c>
+      <c r="R127" t="str">
+        <v>Vertical drive, soft landings</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>B</v>
+      </c>
+      <c r="B128">
+        <v>6</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D128" t="str">
+        <v/>
+      </c>
+      <c r="E128" t="str">
+        <v/>
+      </c>
+      <c r="F128">
+        <v>4</v>
+      </c>
+      <c r="G128" t="str">
+        <v>B-d6s4</v>
+      </c>
+      <c r="H128" t="str">
+        <v>Plyometric</v>
+      </c>
+      <c r="I128" t="str">
+        <v/>
+      </c>
+      <c r="J128" t="str">
+        <v/>
+      </c>
+      <c r="K128" t="str">
+        <v/>
+      </c>
+      <c r="L128" t="str">
+        <v>depthcombo</v>
+      </c>
+      <c r="M128" t="str">
+        <v>Depth Drop → Broad Jump → Box Jump</v>
+      </c>
+      <c r="N128" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O128" t="str">
+        <v/>
+      </c>
+      <c r="P128" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q128" t="str">
+        <v>4 × 5</v>
+      </c>
+      <c r="R128" t="str">
+        <v>Controlled landings</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>B</v>
+      </c>
+      <c r="B129">
+        <v>6</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D129" t="str">
+        <v/>
+      </c>
+      <c r="E129" t="str">
+        <v/>
+      </c>
+      <c r="F129">
+        <v>5</v>
+      </c>
+      <c r="G129" t="str">
+        <v>B-d6s5</v>
+      </c>
+      <c r="H129" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I129" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J129" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K129" t="str">
+        <v/>
+      </c>
+      <c r="L129" t="str">
+        <v>arnold</v>
+      </c>
+      <c r="M129" t="str">
+        <v>Arnold Press</v>
+      </c>
+      <c r="N129" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O129">
+        <v>35</v>
+      </c>
+      <c r="P129" t="str">
+        <v/>
+      </c>
+      <c r="Q129" t="str">
+        <v/>
+      </c>
+      <c r="R129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>B</v>
+      </c>
+      <c r="B130">
+        <v>6</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D130" t="str">
+        <v/>
+      </c>
+      <c r="E130" t="str">
+        <v/>
+      </c>
+      <c r="F130">
+        <v>5</v>
+      </c>
+      <c r="G130" t="str">
+        <v>B-d6s5</v>
+      </c>
+      <c r="H130" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I130" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J130" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K130" t="str">
+        <v/>
+      </c>
+      <c r="L130" t="str">
+        <v>zercher</v>
+      </c>
+      <c r="M130" t="str">
+        <v>Seated Zercher Good Morning</v>
+      </c>
+      <c r="N130" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O130">
+        <v>50</v>
+      </c>
+      <c r="P130" t="str">
+        <v/>
+      </c>
+      <c r="Q130" t="str">
+        <v/>
+      </c>
+      <c r="R130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>B</v>
+      </c>
+      <c r="B131">
+        <v>6</v>
+      </c>
+      <c r="C131" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D131" t="str">
+        <v/>
+      </c>
+      <c r="E131" t="str">
+        <v/>
+      </c>
+      <c r="F131">
+        <v>6</v>
+      </c>
+      <c r="G131" t="str">
+        <v>B-d6s6</v>
+      </c>
+      <c r="H131" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I131" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J131" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K131" t="str">
+        <v/>
+      </c>
+      <c r="L131" t="str">
+        <v>cablepunch</v>
+      </c>
+      <c r="M131" t="str">
+        <v>Cable Punch ISO hold</v>
+      </c>
+      <c r="N131" t="str">
+        <v>iso</v>
+      </c>
+      <c r="O131">
+        <v>30</v>
+      </c>
+      <c r="P131" t="str">
+        <v/>
+      </c>
+      <c r="Q131" t="str">
+        <v>4 × 30 s hold</v>
+      </c>
+      <c r="R131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>B</v>
+      </c>
+      <c r="B132">
+        <v>6</v>
+      </c>
+      <c r="C132" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D132" t="str">
+        <v/>
+      </c>
+      <c r="E132" t="str">
+        <v/>
+      </c>
+      <c r="F132">
+        <v>6</v>
+      </c>
+      <c r="G132" t="str">
+        <v>B-d6s6</v>
+      </c>
+      <c r="H132" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I132" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J132" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K132" t="str">
+        <v/>
+      </c>
+      <c r="L132" t="str">
+        <v>cablerow</v>
+      </c>
+      <c r="M132" t="str">
+        <v>Explosive Unilateral Cable Row</v>
+      </c>
+      <c r="N132" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O132">
+        <v>30</v>
+      </c>
+      <c r="P132" t="str">
+        <v/>
+      </c>
+      <c r="Q132" t="str">
+        <v/>
+      </c>
+      <c r="R132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>B</v>
+      </c>
+      <c r="B133">
+        <v>7</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Day 7</v>
+      </c>
+      <c r="D133" t="str">
+        <v/>
+      </c>
+      <c r="E133" t="str">
+        <v/>
+      </c>
+      <c r="F133" t="str">
+        <v/>
+      </c>
+      <c r="G133" t="str">
+        <v/>
+      </c>
+      <c r="H133" t="str">
+        <v/>
+      </c>
+      <c r="I133" t="str">
+        <v/>
+      </c>
+      <c r="J133" t="str">
+        <v/>
+      </c>
+      <c r="K133" t="str">
+        <v/>
+      </c>
+      <c r="L133" t="str">
+        <v/>
+      </c>
+      <c r="M133" t="str">
+        <v/>
+      </c>
+      <c r="N133" t="str">
+        <v/>
+      </c>
+      <c r="O133" t="str">
+        <v/>
+      </c>
+      <c r="P133" t="str">
+        <v/>
+      </c>
+      <c r="Q133" t="str">
+        <v/>
+      </c>
+      <c r="R133" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R65"/>
+  <autoFilter ref="A1:R133"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R65"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R133"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -9128,10 +12936,18 @@
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>B</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Sled push → pull</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B2"/>
+  <autoFilter ref="A1:B3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -2427,7 +2427,7 @@
         <v>ex</v>
       </c>
       <c r="B3" t="str">
-        <v>{"deadlift":{"n":"Deadlift","eq":"barbell"},"zercher":{"eq":"shortbar"},"split-stance-cable-hip-rotation":{"n":"Split Stance Cable Hip Rotation","url":"https://youtu.be/ixIEilUM2aY","eq":"cable"}}</v>
+        <v>{"deadlift":{"n":"Deadlift","eq":"barbell"},"zercher":{"eq":"shortbar"},"split-stance-cable-hip-rotation":{"n":"Split Stance Cable Hip Rotation","url":"https://youtu.be/ixIEilUM2aY","eq":"cable"},"clean-jerk-overhead-press":{"n":"Clean Jerk &amp; Overhead Press","eq":"dumbbell"}}</v>
       </c>
     </row>
     <row r="4">
@@ -2443,7 +2443,7 @@
         <v>ghBackup</v>
       </c>
       <c r="B5" t="str">
-        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"15dqvqq","last":{"at":"2026-10-03T13:49:23.534Z","url":"https://github.com/jacgit18/iron-log/commit/20cd6d3d4efda877aa668cc99be7edb20a759be7"}}</v>
+        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"jd0ayc","last":{"at":"2026-10-04T15:24:05.090Z","url":"https://github.com/jacgit18/iron-log/commit/31a63f35c5396fef9883932e703c0f0dd264248e"}}</v>
       </c>
     </row>
     <row r="6">
@@ -5421,7 +5421,7 @@
         <v>Exported</v>
       </c>
       <c r="B41" t="str">
-        <v>2026-10-04T15:24:02.324Z</v>
+        <v>2026-10-04T15:29:02.184Z</v>
       </c>
     </row>
   </sheetData>
@@ -11916,37 +11916,37 @@
         <v>2</v>
       </c>
       <c r="G116" t="str">
-        <v>B-d5s2</v>
+        <v>B-d5s3</v>
       </c>
       <c r="H116" t="str">
         <v>Regular</v>
       </c>
       <c r="I116" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J116" t="str">
-        <v/>
+        <v>either</v>
       </c>
       <c r="K116" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L116" t="str">
-        <v>dbclean</v>
+        <v>reardelt</v>
       </c>
       <c r="M116" t="str">
-        <v>DB Clean &amp; Jerk Press</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="N116" t="str">
-        <v>exp</v>
+        <v>iso</v>
       </c>
       <c r="O116">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="P116" t="str">
         <v/>
       </c>
       <c r="Q116" t="str">
-        <v/>
+        <v>4 × 15 s per arm</v>
       </c>
       <c r="R116" t="str">
         <v/>
@@ -11969,7 +11969,7 @@
         <v>Yes</v>
       </c>
       <c r="F117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G117" t="str">
         <v>B-d5s3</v>
@@ -11987,22 +11987,22 @@
         <v>Whichever is free</v>
       </c>
       <c r="L117" t="str">
-        <v>reardelt</v>
+        <v>facepull</v>
       </c>
       <c r="M117" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Face Pull</v>
       </c>
       <c r="N117" t="str">
-        <v>iso</v>
+        <v>strength</v>
       </c>
       <c r="O117">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P117" t="str">
         <v/>
       </c>
       <c r="Q117" t="str">
-        <v>4 × 15 s per arm</v>
+        <v/>
       </c>
       <c r="R117" t="str">
         <v/>
@@ -12028,34 +12028,34 @@
         <v>3</v>
       </c>
       <c r="G118" t="str">
-        <v>B-d5s3</v>
+        <v>B-d5s4</v>
       </c>
       <c r="H118" t="str">
-        <v>Regular</v>
+        <v>Plyometric</v>
       </c>
       <c r="I118" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J118" t="str">
-        <v>either</v>
+        <v/>
       </c>
       <c r="K118" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L118" t="str">
-        <v>facepull</v>
+        <v>trxpike</v>
       </c>
       <c r="M118" t="str">
-        <v>Face Pull</v>
+        <v>TRX Pike Push-Up</v>
       </c>
       <c r="N118" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O118">
-        <v>30</v>
+        <v>exp</v>
+      </c>
+      <c r="O118" t="str">
+        <v/>
       </c>
       <c r="P118" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q118" t="str">
         <v/>
@@ -12084,7 +12084,7 @@
         <v>4</v>
       </c>
       <c r="G119" t="str">
-        <v>B-d5s4</v>
+        <v>B-d5s5</v>
       </c>
       <c r="H119" t="str">
         <v>Plyometric</v>
@@ -12099,10 +12099,10 @@
         <v/>
       </c>
       <c r="L119" t="str">
-        <v>trxpike</v>
+        <v>trxrow</v>
       </c>
       <c r="M119" t="str">
-        <v>TRX Pike Push-Up</v>
+        <v>TRX Wide-Grip Row</v>
       </c>
       <c r="N119" t="str">
         <v>exp</v>
@@ -12140,7 +12140,7 @@
         <v>5</v>
       </c>
       <c r="G120" t="str">
-        <v>B-d5s5</v>
+        <v>B-d5s6</v>
       </c>
       <c r="H120" t="str">
         <v>Plyometric</v>
@@ -12155,10 +12155,10 @@
         <v/>
       </c>
       <c r="L120" t="str">
-        <v>trxrow</v>
+        <v>medball</v>
       </c>
       <c r="M120" t="str">
-        <v>TRX Wide-Grip Row</v>
+        <v>Med Ball Rotational Scoop</v>
       </c>
       <c r="N120" t="str">
         <v>exp</v>
@@ -12167,7 +12167,7 @@
         <v/>
       </c>
       <c r="P120" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q120" t="str">
         <v/>
@@ -12196,7 +12196,7 @@
         <v>6</v>
       </c>
       <c r="G121" t="str">
-        <v>B-d5s6</v>
+        <v>B-d5s7</v>
       </c>
       <c r="H121" t="str">
         <v>Plyometric</v>
@@ -12211,10 +12211,10 @@
         <v/>
       </c>
       <c r="L121" t="str">
-        <v>medball</v>
+        <v>latwall</v>
       </c>
       <c r="M121" t="str">
-        <v>Med Ball Rotational Scoop</v>
+        <v>Lateral Wall Push</v>
       </c>
       <c r="N121" t="str">
         <v>exp</v>
@@ -12223,7 +12223,7 @@
         <v/>
       </c>
       <c r="P121" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q121" t="str">
         <v/>
@@ -12252,10 +12252,10 @@
         <v>7</v>
       </c>
       <c r="G122" t="str">
-        <v>B-d5s7</v>
+        <v>B-d5s8</v>
       </c>
       <c r="H122" t="str">
-        <v>Plyometric</v>
+        <v>Home</v>
       </c>
       <c r="I122" t="str">
         <v/>
@@ -12267,22 +12267,22 @@
         <v/>
       </c>
       <c r="L122" t="str">
-        <v>latwall</v>
+        <v>db6</v>
       </c>
       <c r="M122" t="str">
-        <v>Lateral Wall Push</v>
+        <v>DB 6 Ways</v>
       </c>
       <c r="N122" t="str">
-        <v>exp</v>
-      </c>
-      <c r="O122" t="str">
-        <v/>
+        <v>strength</v>
+      </c>
+      <c r="O122">
+        <v>10</v>
       </c>
       <c r="P122" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q122" t="str">
-        <v/>
+        <v>2 × 6</v>
       </c>
       <c r="R122" t="str">
         <v/>
@@ -12308,7 +12308,7 @@
         <v>8</v>
       </c>
       <c r="G123" t="str">
-        <v>B-d5s8</v>
+        <v>B-d5s9</v>
       </c>
       <c r="H123" t="str">
         <v>Home</v>
@@ -12323,25 +12323,25 @@
         <v/>
       </c>
       <c r="L123" t="str">
-        <v>db6</v>
+        <v>spinal</v>
       </c>
       <c r="M123" t="str">
-        <v>DB 6 Ways</v>
+        <v>Spinal Waves</v>
       </c>
       <c r="N123" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O123">
-        <v>10</v>
+        <v>mob</v>
+      </c>
+      <c r="O123" t="str">
+        <v/>
       </c>
       <c r="P123" t="str">
         <v/>
       </c>
       <c r="Q123" t="str">
-        <v>2 × 6</v>
+        <v/>
       </c>
       <c r="R123" t="str">
-        <v/>
+        <v>Standing, no equipment</v>
       </c>
     </row>
     <row r="124">
@@ -12349,55 +12349,55 @@
         <v>B</v>
       </c>
       <c r="B124">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C124" t="str">
-        <v>Day 5</v>
+        <v>Day 6</v>
       </c>
       <c r="D124" t="str">
         <v/>
       </c>
       <c r="E124" t="str">
+        <v/>
+      </c>
+      <c r="F124">
+        <v>1</v>
+      </c>
+      <c r="G124" t="str">
+        <v>B-d6s1</v>
+      </c>
+      <c r="H124" t="str">
+        <v>Plyometric</v>
+      </c>
+      <c r="I124" t="str">
+        <v/>
+      </c>
+      <c r="J124" t="str">
+        <v/>
+      </c>
+      <c r="K124" t="str">
+        <v/>
+      </c>
+      <c r="L124" t="str">
+        <v>pogo</v>
+      </c>
+      <c r="M124" t="str">
+        <v>Pogo Hops</v>
+      </c>
+      <c r="N124" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O124" t="str">
+        <v/>
+      </c>
+      <c r="P124" t="str">
         <v>Yes</v>
       </c>
-      <c r="F124">
-        <v>9</v>
-      </c>
-      <c r="G124" t="str">
-        <v>B-d5s9</v>
-      </c>
-      <c r="H124" t="str">
-        <v>Home</v>
-      </c>
-      <c r="I124" t="str">
-        <v/>
-      </c>
-      <c r="J124" t="str">
-        <v/>
-      </c>
-      <c r="K124" t="str">
-        <v/>
-      </c>
-      <c r="L124" t="str">
-        <v>spinal</v>
-      </c>
-      <c r="M124" t="str">
-        <v>Spinal Waves</v>
-      </c>
-      <c r="N124" t="str">
-        <v>mob</v>
-      </c>
-      <c r="O124" t="str">
-        <v/>
-      </c>
-      <c r="P124" t="str">
-        <v/>
-      </c>
       <c r="Q124" t="str">
-        <v/>
+        <v>3 × 10</v>
       </c>
       <c r="R124" t="str">
-        <v>Standing, no equipment</v>
+        <v/>
       </c>
     </row>
     <row r="125">
@@ -12417,10 +12417,10 @@
         <v/>
       </c>
       <c r="F125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G125" t="str">
-        <v>B-d6s1</v>
+        <v>B-d6s2</v>
       </c>
       <c r="H125" t="str">
         <v>Plyometric</v>
@@ -12435,10 +12435,10 @@
         <v/>
       </c>
       <c r="L125" t="str">
-        <v>pogo</v>
+        <v>skater</v>
       </c>
       <c r="M125" t="str">
-        <v>Pogo Hops</v>
+        <v>Lateral Bound / Skater Hop with Stick</v>
       </c>
       <c r="N125" t="str">
         <v>exp</v>
@@ -12450,7 +12450,7 @@
         <v>Yes</v>
       </c>
       <c r="Q125" t="str">
-        <v>3 × 10</v>
+        <v>3 × 5, hold 3 s</v>
       </c>
       <c r="R125" t="str">
         <v/>
@@ -12473,10 +12473,10 @@
         <v/>
       </c>
       <c r="F126">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G126" t="str">
-        <v>B-d6s2</v>
+        <v>B-d6s3</v>
       </c>
       <c r="H126" t="str">
         <v>Plyometric</v>
@@ -12491,10 +12491,10 @@
         <v/>
       </c>
       <c r="L126" t="str">
-        <v>skater</v>
+        <v>splitjump</v>
       </c>
       <c r="M126" t="str">
-        <v>Lateral Bound / Skater Hop with Stick</v>
+        <v>Split Squat Jumps</v>
       </c>
       <c r="N126" t="str">
         <v>exp</v>
@@ -12506,10 +12506,10 @@
         <v>Yes</v>
       </c>
       <c r="Q126" t="str">
-        <v>3 × 5, hold 3 s</v>
+        <v>3 × 5</v>
       </c>
       <c r="R126" t="str">
-        <v/>
+        <v>Vertical drive, soft landings</v>
       </c>
     </row>
     <row r="127">
@@ -12529,10 +12529,10 @@
         <v/>
       </c>
       <c r="F127">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G127" t="str">
-        <v>B-d6s3</v>
+        <v>B-d6s4</v>
       </c>
       <c r="H127" t="str">
         <v>Plyometric</v>
@@ -12547,10 +12547,10 @@
         <v/>
       </c>
       <c r="L127" t="str">
-        <v>splitjump</v>
+        <v>depthcombo</v>
       </c>
       <c r="M127" t="str">
-        <v>Split Squat Jumps</v>
+        <v>Depth Drop → Broad Jump → Box Jump</v>
       </c>
       <c r="N127" t="str">
         <v>exp</v>
@@ -12562,10 +12562,10 @@
         <v>Yes</v>
       </c>
       <c r="Q127" t="str">
-        <v>3 × 5</v>
+        <v>4 × 5</v>
       </c>
       <c r="R127" t="str">
-        <v>Vertical drive, soft landings</v>
+        <v>Controlled landings</v>
       </c>
     </row>
     <row r="128">
@@ -12585,43 +12585,43 @@
         <v/>
       </c>
       <c r="F128">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G128" t="str">
-        <v>B-d6s4</v>
+        <v>B-d6s5</v>
       </c>
       <c r="H128" t="str">
-        <v>Plyometric</v>
+        <v>Supersets</v>
       </c>
       <c r="I128" t="str">
-        <v/>
+        <v>Primary</v>
       </c>
       <c r="J128" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K128" t="str">
         <v/>
       </c>
       <c r="L128" t="str">
-        <v>depthcombo</v>
+        <v>arnold</v>
       </c>
       <c r="M128" t="str">
-        <v>Depth Drop → Broad Jump → Box Jump</v>
+        <v>Arnold Press</v>
       </c>
       <c r="N128" t="str">
-        <v>exp</v>
-      </c>
-      <c r="O128" t="str">
-        <v/>
+        <v>strength</v>
+      </c>
+      <c r="O128">
+        <v>35</v>
       </c>
       <c r="P128" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q128" t="str">
-        <v>4 × 5</v>
+        <v/>
       </c>
       <c r="R128" t="str">
-        <v>Controlled landings</v>
+        <v/>
       </c>
     </row>
     <row r="129">
@@ -12659,16 +12659,16 @@
         <v/>
       </c>
       <c r="L129" t="str">
-        <v>arnold</v>
+        <v>zercher</v>
       </c>
       <c r="M129" t="str">
-        <v>Arnold Press</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="N129" t="str">
         <v>strength</v>
       </c>
       <c r="O129">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="P129" t="str">
         <v/>
@@ -12697,16 +12697,16 @@
         <v/>
       </c>
       <c r="F130">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G130" t="str">
-        <v>B-d6s5</v>
+        <v>B-d6s6</v>
       </c>
       <c r="H130" t="str">
         <v>Supersets</v>
       </c>
       <c r="I130" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J130" t="str">
         <v>superset</v>
@@ -12715,22 +12715,22 @@
         <v/>
       </c>
       <c r="L130" t="str">
-        <v>zercher</v>
+        <v>cablepunch</v>
       </c>
       <c r="M130" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Cable Punch ISO hold</v>
       </c>
       <c r="N130" t="str">
-        <v>strength</v>
+        <v>iso</v>
       </c>
       <c r="O130">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P130" t="str">
         <v/>
       </c>
       <c r="Q130" t="str">
-        <v/>
+        <v>4 × 30 s hold</v>
       </c>
       <c r="R130" t="str">
         <v/>
@@ -12771,13 +12771,13 @@
         <v/>
       </c>
       <c r="L131" t="str">
-        <v>cablepunch</v>
+        <v>cablerow</v>
       </c>
       <c r="M131" t="str">
-        <v>Cable Punch ISO hold</v>
+        <v>Explosive Unilateral Cable Row</v>
       </c>
       <c r="N131" t="str">
-        <v>iso</v>
+        <v>exp</v>
       </c>
       <c r="O131">
         <v>30</v>
@@ -12786,7 +12786,7 @@
         <v/>
       </c>
       <c r="Q131" t="str">
-        <v>4 × 30 s hold</v>
+        <v/>
       </c>
       <c r="R131" t="str">
         <v/>
@@ -12809,34 +12809,34 @@
         <v/>
       </c>
       <c r="F132">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G132" t="str">
-        <v>B-d6s6</v>
+        <v>B-d5s2</v>
       </c>
       <c r="H132" t="str">
-        <v>Supersets</v>
+        <v>Regular</v>
       </c>
       <c r="I132" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J132" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K132" t="str">
         <v/>
       </c>
       <c r="L132" t="str">
-        <v>cablerow</v>
+        <v>clean-jerk-overhead-press</v>
       </c>
       <c r="M132" t="str">
-        <v>Explosive Unilateral Cable Row</v>
+        <v>Clean Jerk &amp; Overhead Press</v>
       </c>
       <c r="N132" t="str">
         <v>exp</v>
       </c>
       <c r="O132">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P132" t="str">
         <v/>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -17,16 +17,16 @@
     <sheet name="Config" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">Weeks!$A$1:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Body weight'!$A$1:$D$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5">Settings!$A$1:$B$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6">Programs!$A$1:$R$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6">Programs!$A$1:$R$145</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Program info'!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$83</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11">Config!$A$1:$B$16</definedName>
   </definedNames>
 </workbook>
@@ -421,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -1077,7 +1077,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Split Squat Jumps</v>
+        <v>Sled push → pull</v>
       </c>
       <c r="B21" t="str">
         <v>Explosive</v>
@@ -1109,42 +1109,42 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Suitcase Bottom-Up, single-arm</v>
+        <v>Split Squat Jumps</v>
       </c>
       <c r="B22" t="str">
-        <v>Strength</v>
+        <v>Explosive</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-09-29</v>
-      </c>
-      <c r="F22">
-        <v>25</v>
-      </c>
-      <c r="G22">
-        <v>25</v>
-      </c>
-      <c r="H22">
-        <v>25</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>30</v>
+        <v>2026-10-04</v>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Zottman Curl</v>
+        <v>Suitcase Bottom-Up, single-arm</v>
       </c>
       <c r="B23" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1156,25 +1156,57 @@
         <v>2026-09-29</v>
       </c>
       <c r="F23">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G23">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H23">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="J23">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Zottman Curl</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Hypertrophy</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="E24" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="F24">
+        <v>15</v>
+      </c>
+      <c r="G24">
+        <v>15</v>
+      </c>
+      <c r="H24">
+        <v>15</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
         <v>23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J23"/>
+  <autoFilter ref="A1:J24"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J24"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1234,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D83"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.83203125" customWidth="1"/>
@@ -2353,10 +2385,10 @@
         <v>2026-10-04</v>
       </c>
       <c r="B80" t="str">
-        <v>skipped</v>
+        <v>done</v>
       </c>
       <c r="C80" t="str">
-        <v>B-d6s5</v>
+        <v>B-sled6</v>
       </c>
       <c r="D80" t="str">
         <v>Yes</v>
@@ -2367,13 +2399,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B81" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C81" t="str">
-        <v>B-d5s2</v>
-      </c>
-      <c r="D81">
-        <v>6</v>
+        <v>B-d6s5</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="82">
@@ -2384,16 +2416,30 @@
         <v>moved</v>
       </c>
       <c r="C82" t="str">
-        <v>B-d1s3</v>
+        <v>B-d5s2</v>
       </c>
       <c r="D82">
         <v>6</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B83" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C83" t="str">
+        <v>B-d1s3</v>
+      </c>
+      <c r="D83">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D82"/>
+  <autoFilter ref="A1:D83"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D83"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2544,7 +2590,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O37"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -4216,7 +4262,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="C36" t="str">
-        <v>Split Squat Jumps</v>
+        <v>Sled push → pull</v>
       </c>
       <c r="D36" t="str">
         <v>Explosive</v>
@@ -4225,16 +4271,16 @@
         <v/>
       </c>
       <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="G36">
         <v>3</v>
       </c>
-      <c r="G36">
-        <v>10</v>
-      </c>
       <c r="H36" t="str">
         <v/>
       </c>
       <c r="I36" t="str">
-        <v>BW×10, BW×10, BW×10</v>
+        <v>BW×3</v>
       </c>
       <c r="J36" t="str">
         <v/>
@@ -4243,22 +4289,69 @@
         <v>Quads, Glutes</v>
       </c>
       <c r="L36" t="str">
+        <v>Lats, Upper back, Calves</v>
+      </c>
+      <c r="M36" t="str">
+        <v>From check-off</v>
+      </c>
+      <c r="N36" t="str">
+        <v>B-sled6</v>
+      </c>
+      <c r="O36" t="str">
+        <v>sled</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Split Squat Jumps</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Explosive</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37">
+        <v>10</v>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v>BW×10, BW×10, BW×10</v>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v>Quads, Glutes</v>
+      </c>
+      <c r="L37" t="str">
         <v>Calves, Hamstrings</v>
       </c>
-      <c r="M36" t="str">
-        <v/>
-      </c>
-      <c r="N36" t="str">
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
         <v>B-d6s3</v>
       </c>
-      <c r="O36" t="str">
+      <c r="O37" t="str">
         <v>splitjump</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O36"/>
+  <autoFilter ref="A1:O37"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O37"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4605,13 +4698,13 @@
         <v>Glutes</v>
       </c>
       <c r="C20">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20">
         <v>4</v>
       </c>
       <c r="E20">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -4622,13 +4715,13 @@
         <v>Quads</v>
       </c>
       <c r="C21">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
@@ -4642,10 +4735,10 @@
         <v>6</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22">
-        <v>9</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="23">
@@ -4653,13 +4746,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B23" t="str">
-        <v>Hamstrings</v>
+        <v>Upper back</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D23">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E23">
         <v>6.5</v>
@@ -4670,16 +4763,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B24" t="str">
-        <v>Upper back</v>
+        <v>Hamstrings</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E24">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="25">
@@ -4710,10 +4803,10 @@
         <v>4</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="27">
@@ -4721,7 +4814,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="B27" t="str">
-        <v>Lower back</v>
+        <v>Obliques</v>
       </c>
       <c r="C27">
         <v>4</v>
@@ -4738,7 +4831,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="B28" t="str">
-        <v>Obliques</v>
+        <v>Abs</v>
       </c>
       <c r="C28">
         <v>4</v>
@@ -4755,7 +4848,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="B29" t="str">
-        <v>Abs</v>
+        <v>Lower back</v>
       </c>
       <c r="C29">
         <v>4</v>
@@ -4789,7 +4882,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="B31" t="str">
-        <v>Rear delts</v>
+        <v>Chest</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -4806,7 +4899,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="B32" t="str">
-        <v>Biceps</v>
+        <v>Rear delts</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -4823,13 +4916,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B33" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Biceps</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E33">
         <v>2</v>
@@ -4840,13 +4933,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B34" t="str">
-        <v>Chest</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34">
         <v>0</v>
-      </c>
-      <c r="D34">
-        <v>4</v>
       </c>
       <c r="E34">
         <v>2</v>
@@ -4976,19 +5069,19 @@
         <v>A</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>26</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>30</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="H2">
         <v>26</v>
@@ -5005,19 +5098,19 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -5421,7 +5514,7 @@
         <v>Exported</v>
       </c>
       <c r="B41" t="str">
-        <v>2026-10-04T15:29:02.184Z</v>
+        <v>2026-10-04T16:53:09.216Z</v>
       </c>
     </row>
   </sheetData>
@@ -5434,7 +5527,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R133"/>
+  <dimension ref="A1:R145"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="5.83203125" customWidth="1"/>
@@ -5532,37 +5625,37 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>A-d1s1</v>
+        <v>A-sled1</v>
       </c>
       <c r="H2" t="str">
-        <v>Regular</v>
+        <v>Optional</v>
       </c>
       <c r="I2" t="str">
-        <v>Primary</v>
+        <v/>
       </c>
       <c r="J2" t="str">
         <v/>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>Optional</v>
       </c>
       <c r="L2" t="str">
-        <v>latpd</v>
+        <v>sledlat</v>
       </c>
       <c r="M2" t="str">
-        <v>Lat Pulldown, alternating single-arm</v>
+        <v>Sled push → lateral pull</v>
       </c>
       <c r="N2" t="str">
-        <v>hyp</v>
-      </c>
-      <c r="O2">
-        <v>45</v>
+        <v>exp</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
       </c>
       <c r="P2" t="str">
         <v/>
       </c>
       <c r="Q2" t="str">
-        <v/>
+        <v>1 × 3</v>
       </c>
       <c r="R2" t="str">
         <v/>
@@ -5588,13 +5681,13 @@
         <v>2</v>
       </c>
       <c r="G3" t="str">
-        <v>A-d1s2</v>
+        <v>A-d1s1</v>
       </c>
       <c r="H3" t="str">
         <v>Regular</v>
       </c>
       <c r="I3" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -5603,16 +5696,16 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>wristpd</v>
+        <v>latpd</v>
       </c>
       <c r="M3" t="str">
-        <v>Cable Wrist Pulldown</v>
+        <v>Lat Pulldown, alternating single-arm</v>
       </c>
       <c r="N3" t="str">
         <v>hyp</v>
       </c>
       <c r="O3">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="P3" t="str">
         <v/>
@@ -5644,7 +5737,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="str">
-        <v>A-d1s3</v>
+        <v>A-d1s2</v>
       </c>
       <c r="H4" t="str">
         <v>Regular</v>
@@ -5659,16 +5752,16 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>platerot</v>
+        <v>wristpd</v>
       </c>
       <c r="M4" t="str">
-        <v>Plate Torso Rotation</v>
+        <v>Cable Wrist Pulldown</v>
       </c>
       <c r="N4" t="str">
-        <v>strength</v>
+        <v>hyp</v>
       </c>
       <c r="O4">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="P4" t="str">
         <v/>
@@ -5700,7 +5793,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="str">
-        <v>A-d1s4</v>
+        <v>A-d1s3</v>
       </c>
       <c r="H5" t="str">
         <v>Regular</v>
@@ -5715,16 +5808,16 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>innerthigh</v>
+        <v>platerot</v>
       </c>
       <c r="M5" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Plate Torso Rotation</v>
       </c>
       <c r="N5" t="str">
         <v>strength</v>
       </c>
       <c r="O5">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="P5" t="str">
         <v/>
@@ -5756,7 +5849,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="str">
-        <v>A-d1s5</v>
+        <v>A-d1s4</v>
       </c>
       <c r="H6" t="str">
         <v>Regular</v>
@@ -5771,25 +5864,25 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>romanadd</v>
+        <v>innerthigh</v>
       </c>
       <c r="M6" t="str">
-        <v>Roman Chair Hip Adduction</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="N6" t="str">
         <v>strength</v>
       </c>
-      <c r="O6" t="str">
-        <v/>
+      <c r="O6">
+        <v>180</v>
       </c>
       <c r="P6" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q6" t="str">
         <v/>
       </c>
       <c r="R6" t="str">
-        <v>On the back-extension bench</v>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -5812,40 +5905,40 @@
         <v>6</v>
       </c>
       <c r="G7" t="str">
-        <v>A-d1s6</v>
+        <v>A-d1s5</v>
       </c>
       <c r="H7" t="str">
-        <v>Supersets</v>
+        <v>Regular</v>
       </c>
       <c r="I7" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J7" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K7" t="str">
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>chestpress</v>
+        <v>romanadd</v>
       </c>
       <c r="M7" t="str">
-        <v>Chest Press</v>
+        <v>Roman Chair Hip Adduction</v>
       </c>
       <c r="N7" t="str">
         <v>strength</v>
       </c>
-      <c r="O7">
-        <v>35</v>
+      <c r="O7" t="str">
+        <v/>
       </c>
       <c r="P7" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q7" t="str">
         <v/>
       </c>
       <c r="R7" t="str">
-        <v/>
+        <v>On the back-extension bench</v>
       </c>
     </row>
     <row r="8">
@@ -5865,7 +5958,7 @@
         <v/>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G8" t="str">
         <v>A-d1s6</v>
@@ -5883,16 +5976,16 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>zercher</v>
+        <v>chestpress</v>
       </c>
       <c r="M8" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Chest Press</v>
       </c>
       <c r="N8" t="str">
         <v>strength</v>
       </c>
       <c r="O8">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="P8" t="str">
         <v/>
@@ -5924,13 +6017,13 @@
         <v>7</v>
       </c>
       <c r="G9" t="str">
-        <v>A-d1s7</v>
+        <v>A-d1s6</v>
       </c>
       <c r="H9" t="str">
         <v>Supersets</v>
       </c>
       <c r="I9" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J9" t="str">
         <v>superset</v>
@@ -5939,22 +6032,22 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>zottman</v>
+        <v>zercher</v>
       </c>
       <c r="M9" t="str">
-        <v>Zottman Curl</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="N9" t="str">
-        <v>hyp</v>
+        <v>strength</v>
       </c>
       <c r="O9">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="P9" t="str">
         <v/>
       </c>
       <c r="Q9" t="str">
-        <v>3 × 15</v>
+        <v/>
       </c>
       <c r="R9" t="str">
         <v/>
@@ -5977,7 +6070,7 @@
         <v/>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G10" t="str">
         <v>A-d1s7</v>
@@ -5995,13 +6088,13 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>kbleg</v>
+        <v>zottman</v>
       </c>
       <c r="M10" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Zottman Curl</v>
       </c>
       <c r="N10" t="str">
-        <v>iso</v>
+        <v>hyp</v>
       </c>
       <c r="O10">
         <v>15</v>
@@ -6010,7 +6103,7 @@
         <v/>
       </c>
       <c r="Q10" t="str">
-        <v>3 × 15 s hold</v>
+        <v>3 × 15</v>
       </c>
       <c r="R10" t="str">
         <v/>
@@ -6036,37 +6129,37 @@
         <v>8</v>
       </c>
       <c r="G11" t="str">
-        <v>A-d1s8</v>
+        <v>A-d1s7</v>
       </c>
       <c r="H11" t="str">
-        <v>Home</v>
+        <v>Supersets</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K11" t="str">
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>grip</v>
+        <v>kbleg</v>
       </c>
       <c r="M11" t="str">
-        <v>Grip Trainer</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="N11" t="str">
-        <v>strength</v>
+        <v>iso</v>
       </c>
       <c r="O11">
-        <v>200</v>
+        <v>15</v>
       </c>
       <c r="P11" t="str">
         <v/>
       </c>
       <c r="Q11" t="str">
-        <v/>
+        <v>3 × 15 s hold</v>
       </c>
       <c r="R11" t="str">
         <v/>
@@ -6092,7 +6185,7 @@
         <v>9</v>
       </c>
       <c r="G12" t="str">
-        <v>A-d1s9</v>
+        <v>A-d1s8</v>
       </c>
       <c r="H12" t="str">
         <v>Home</v>
@@ -6107,16 +6200,16 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>canoe</v>
+        <v>grip</v>
       </c>
       <c r="M12" t="str">
-        <v>Canoe Stretch</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="N12" t="str">
-        <v/>
+        <v>strength</v>
       </c>
       <c r="O12">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="P12" t="str">
         <v/>
@@ -6133,10 +6226,10 @@
         <v>A</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="str">
-        <v>Day 2</v>
+        <v>Day 1</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -6145,16 +6238,16 @@
         <v/>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G13" t="str">
-        <v>A-d2s1</v>
+        <v>A-d1s9</v>
       </c>
       <c r="H13" t="str">
-        <v>Regular</v>
+        <v>Home</v>
       </c>
       <c r="I13" t="str">
-        <v>Primary</v>
+        <v/>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -6163,22 +6256,22 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>suitcase</v>
+        <v>canoe</v>
       </c>
       <c r="M13" t="str">
-        <v>Suitcase Bottom-Up, single-arm</v>
+        <v>Canoe Stretch</v>
       </c>
       <c r="N13" t="str">
         <v/>
       </c>
       <c r="O13">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="P13" t="str">
         <v/>
       </c>
       <c r="Q13" t="str">
-        <v>3 × 4 each arm</v>
+        <v/>
       </c>
       <c r="R13" t="str">
         <v/>
@@ -6201,40 +6294,40 @@
         <v/>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="str">
-        <v>A-d2s2</v>
+        <v>A-sled2</v>
       </c>
       <c r="H14" t="str">
-        <v>Regular</v>
+        <v>Optional</v>
       </c>
       <c r="I14" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J14" t="str">
-        <v>either</v>
+        <v/>
       </c>
       <c r="K14" t="str">
-        <v>Whichever is free</v>
+        <v>Optional</v>
       </c>
       <c r="L14" t="str">
-        <v>reardelt</v>
+        <v>sledlat</v>
       </c>
       <c r="M14" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Sled push → lateral pull</v>
       </c>
       <c r="N14" t="str">
-        <v>iso</v>
-      </c>
-      <c r="O14">
-        <v>50</v>
+        <v>exp</v>
+      </c>
+      <c r="O14" t="str">
+        <v/>
       </c>
       <c r="P14" t="str">
         <v/>
       </c>
       <c r="Q14" t="str">
-        <v>4 × 15 s per arm</v>
+        <v>1 × 3</v>
       </c>
       <c r="R14" t="str">
         <v/>
@@ -6260,37 +6353,37 @@
         <v>2</v>
       </c>
       <c r="G15" t="str">
-        <v>A-d2s2</v>
+        <v>A-d2s1</v>
       </c>
       <c r="H15" t="str">
         <v>Regular</v>
       </c>
       <c r="I15" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J15" t="str">
-        <v>either</v>
+        <v/>
       </c>
       <c r="K15" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L15" t="str">
-        <v>facepull</v>
+        <v>suitcase</v>
       </c>
       <c r="M15" t="str">
-        <v>Face Pull</v>
+        <v>Suitcase Bottom-Up, single-arm</v>
       </c>
       <c r="N15" t="str">
-        <v>strength</v>
+        <v/>
       </c>
       <c r="O15">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P15" t="str">
         <v/>
       </c>
       <c r="Q15" t="str">
-        <v/>
+        <v>3 × 4 each arm</v>
       </c>
       <c r="R15" t="str">
         <v/>
@@ -6316,7 +6409,7 @@
         <v>3</v>
       </c>
       <c r="G16" t="str">
-        <v>A-d2s3</v>
+        <v>A-d2s2</v>
       </c>
       <c r="H16" t="str">
         <v>Regular</v>
@@ -6325,16 +6418,16 @@
         <v>Accessory</v>
       </c>
       <c r="J16" t="str">
-        <v/>
+        <v>either</v>
       </c>
       <c r="K16" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L16" t="str">
-        <v>legext</v>
+        <v>reardelt</v>
       </c>
       <c r="M16" t="str">
-        <v>Leg Extension ISO hold</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="N16" t="str">
         <v>iso</v>
@@ -6346,7 +6439,7 @@
         <v/>
       </c>
       <c r="Q16" t="str">
-        <v>4 × 30 s</v>
+        <v>4 × 15 s per arm</v>
       </c>
       <c r="R16" t="str">
         <v/>
@@ -6369,10 +6462,10 @@
         <v/>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" t="str">
-        <v>A-d2s4</v>
+        <v>A-d2s2</v>
       </c>
       <c r="H17" t="str">
         <v>Regular</v>
@@ -6381,22 +6474,22 @@
         <v>Accessory</v>
       </c>
       <c r="J17" t="str">
-        <v/>
+        <v>either</v>
       </c>
       <c r="K17" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L17" t="str">
-        <v>cablecrunch</v>
+        <v>facepull</v>
       </c>
       <c r="M17" t="str">
-        <v>Kneeling Cable Ab Crunch</v>
+        <v>Face Pull</v>
       </c>
       <c r="N17" t="str">
         <v>strength</v>
       </c>
       <c r="O17">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P17" t="str">
         <v/>
@@ -6425,40 +6518,40 @@
         <v/>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" t="str">
-        <v>A-d2s5</v>
+        <v>A-d2s3</v>
       </c>
       <c r="H18" t="str">
-        <v>Supersets</v>
+        <v>Regular</v>
       </c>
       <c r="I18" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J18" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K18" t="str">
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>hipthrust</v>
+        <v>legext</v>
       </c>
       <c r="M18" t="str">
-        <v>Hip Thrust</v>
+        <v>Leg Extension ISO hold</v>
       </c>
       <c r="N18" t="str">
-        <v>strength</v>
+        <v>iso</v>
       </c>
       <c r="O18">
-        <v>320</v>
+        <v>50</v>
       </c>
       <c r="P18" t="str">
         <v/>
       </c>
       <c r="Q18" t="str">
-        <v/>
+        <v>4 × 30 s</v>
       </c>
       <c r="R18" t="str">
         <v/>
@@ -6484,31 +6577,31 @@
         <v>5</v>
       </c>
       <c r="G19" t="str">
-        <v>A-d2s5</v>
+        <v>A-d2s4</v>
       </c>
       <c r="H19" t="str">
-        <v>Supersets</v>
+        <v>Regular</v>
       </c>
       <c r="I19" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J19" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K19" t="str">
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>chestpress</v>
+        <v>cablecrunch</v>
       </c>
       <c r="M19" t="str">
-        <v>Chest Press</v>
+        <v>Kneeling Cable Ab Crunch</v>
       </c>
       <c r="N19" t="str">
-        <v>hyp</v>
+        <v>strength</v>
       </c>
       <c r="O19">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="P19" t="str">
         <v/>
@@ -6540,13 +6633,13 @@
         <v>6</v>
       </c>
       <c r="G20" t="str">
-        <v>A-d2s6</v>
+        <v>A-d2s5</v>
       </c>
       <c r="H20" t="str">
         <v>Supersets</v>
       </c>
       <c r="I20" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J20" t="str">
         <v>superset</v>
@@ -6555,25 +6648,25 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>dip</v>
+        <v>hipthrust</v>
       </c>
       <c r="M20" t="str">
-        <v>Wide Tricep Dip</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="N20" t="str">
         <v>strength</v>
       </c>
-      <c r="O20" t="str">
-        <v/>
+      <c r="O20">
+        <v>320</v>
       </c>
       <c r="P20" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q20" t="str">
         <v/>
       </c>
       <c r="R20" t="str">
-        <v>Bodyweight, working toward +10 lb</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -6596,13 +6689,13 @@
         <v>6</v>
       </c>
       <c r="G21" t="str">
-        <v>A-d2s6</v>
+        <v>A-d2s5</v>
       </c>
       <c r="H21" t="str">
         <v>Supersets</v>
       </c>
       <c r="I21" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J21" t="str">
         <v>superset</v>
@@ -6611,19 +6704,19 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>kneeraise</v>
+        <v>chestpress</v>
       </c>
       <c r="M21" t="str">
-        <v>Hanging Knee Raise</v>
+        <v>Chest Press</v>
       </c>
       <c r="N21" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O21" t="str">
-        <v/>
+        <v>hyp</v>
+      </c>
+      <c r="O21">
+        <v>25</v>
       </c>
       <c r="P21" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q21" t="str">
         <v/>
@@ -6652,40 +6745,40 @@
         <v>7</v>
       </c>
       <c r="G22" t="str">
-        <v>A-d2s7</v>
+        <v>A-d2s6</v>
       </c>
       <c r="H22" t="str">
-        <v>Home</v>
+        <v>Supersets</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J22" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K22" t="str">
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>grip</v>
+        <v>dip</v>
       </c>
       <c r="M22" t="str">
-        <v>Grip Trainer</v>
+        <v>Wide Tricep Dip</v>
       </c>
       <c r="N22" t="str">
         <v>strength</v>
       </c>
-      <c r="O22">
-        <v>200</v>
+      <c r="O22" t="str">
+        <v/>
       </c>
       <c r="P22" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q22" t="str">
         <v/>
       </c>
       <c r="R22" t="str">
-        <v/>
+        <v>Bodyweight, working toward +10 lb</v>
       </c>
     </row>
     <row r="23">
@@ -6705,40 +6798,40 @@
         <v/>
       </c>
       <c r="F23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G23" t="str">
-        <v>A-d2s8</v>
+        <v>A-d2s6</v>
       </c>
       <c r="H23" t="str">
-        <v>Home</v>
+        <v>Supersets</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J23" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K23" t="str">
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>db6</v>
+        <v>kneeraise</v>
       </c>
       <c r="M23" t="str">
-        <v>DB 6 Ways</v>
+        <v>Hanging Knee Raise</v>
       </c>
       <c r="N23" t="str">
         <v>strength</v>
       </c>
-      <c r="O23">
-        <v>10</v>
+      <c r="O23" t="str">
+        <v/>
       </c>
       <c r="P23" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q23" t="str">
-        <v>2 × 6</v>
+        <v/>
       </c>
       <c r="R23" t="str">
         <v/>
@@ -6749,10 +6842,10 @@
         <v>A</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24" t="str">
-        <v>Day 3</v>
+        <v>Day 2</v>
       </c>
       <c r="D24" t="str">
         <v/>
@@ -6761,16 +6854,16 @@
         <v/>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G24" t="str">
-        <v>A-d3s1</v>
+        <v>A-d2s7</v>
       </c>
       <c r="H24" t="str">
-        <v>Regular</v>
+        <v>Home</v>
       </c>
       <c r="I24" t="str">
-        <v>Primary</v>
+        <v/>
       </c>
       <c r="J24" t="str">
         <v/>
@@ -6779,16 +6872,16 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>hack</v>
+        <v>grip</v>
       </c>
       <c r="M24" t="str">
-        <v>Hack Squat</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="N24" t="str">
-        <v>hyp</v>
+        <v>strength</v>
       </c>
       <c r="O24">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="P24" t="str">
         <v/>
@@ -6797,7 +6890,7 @@
         <v/>
       </c>
       <c r="R24" t="str">
-        <v>Feet low on the plate, narrow stance for quads</v>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -6805,10 +6898,10 @@
         <v>A</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" t="str">
-        <v>Day 3</v>
+        <v>Day 2</v>
       </c>
       <c r="D25" t="str">
         <v/>
@@ -6817,16 +6910,16 @@
         <v/>
       </c>
       <c r="F25">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G25" t="str">
-        <v>A-d3s2</v>
+        <v>A-d2s8</v>
       </c>
       <c r="H25" t="str">
-        <v>Regular</v>
+        <v>Home</v>
       </c>
       <c r="I25" t="str">
-        <v>Primary</v>
+        <v/>
       </c>
       <c r="J25" t="str">
         <v/>
@@ -6835,22 +6928,22 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>latpd</v>
+        <v>db6</v>
       </c>
       <c r="M25" t="str">
-        <v>Lat Pulldown, alternating single-arm</v>
+        <v>DB 6 Ways</v>
       </c>
       <c r="N25" t="str">
-        <v>hyp</v>
+        <v>strength</v>
       </c>
       <c r="O25">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="P25" t="str">
         <v/>
       </c>
       <c r="Q25" t="str">
-        <v/>
+        <v>2 × 6</v>
       </c>
       <c r="R25" t="str">
         <v/>
@@ -6873,40 +6966,40 @@
         <v/>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G26" t="str">
-        <v>A-d3s3</v>
+        <v>A-sled3</v>
       </c>
       <c r="H26" t="str">
-        <v>Regular</v>
+        <v>Optional</v>
       </c>
       <c r="I26" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J26" t="str">
         <v/>
       </c>
       <c r="K26" t="str">
-        <v/>
+        <v>Optional</v>
       </c>
       <c r="L26" t="str">
-        <v>wristpd</v>
+        <v>sledlat</v>
       </c>
       <c r="M26" t="str">
-        <v>Cable Wrist Pulldown</v>
+        <v>Sled push → lateral pull</v>
       </c>
       <c r="N26" t="str">
-        <v>hyp</v>
-      </c>
-      <c r="O26">
-        <v>33</v>
+        <v>exp</v>
+      </c>
+      <c r="O26" t="str">
+        <v/>
       </c>
       <c r="P26" t="str">
         <v/>
       </c>
       <c r="Q26" t="str">
-        <v/>
+        <v>1 × 3</v>
       </c>
       <c r="R26" t="str">
         <v/>
@@ -6929,16 +7022,16 @@
         <v/>
       </c>
       <c r="F27">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G27" t="str">
-        <v>A-d3s4</v>
+        <v>A-d3s1</v>
       </c>
       <c r="H27" t="str">
         <v>Regular</v>
       </c>
       <c r="I27" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J27" t="str">
         <v/>
@@ -6947,16 +7040,16 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>platerot</v>
+        <v>hack</v>
       </c>
       <c r="M27" t="str">
-        <v>Plate Torso Rotation</v>
+        <v>Hack Squat</v>
       </c>
       <c r="N27" t="str">
-        <v>strength</v>
+        <v>hyp</v>
       </c>
       <c r="O27">
-        <v>10</v>
+        <v>270</v>
       </c>
       <c r="P27" t="str">
         <v/>
@@ -6965,7 +7058,7 @@
         <v/>
       </c>
       <c r="R27" t="str">
-        <v/>
+        <v>Feet low on the plate, narrow stance for quads</v>
       </c>
     </row>
     <row r="28">
@@ -6985,16 +7078,16 @@
         <v/>
       </c>
       <c r="F28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28" t="str">
-        <v>A-d3s5</v>
+        <v>A-d3s2</v>
       </c>
       <c r="H28" t="str">
         <v>Regular</v>
       </c>
       <c r="I28" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J28" t="str">
         <v/>
@@ -7003,22 +7096,22 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>legext</v>
+        <v>latpd</v>
       </c>
       <c r="M28" t="str">
-        <v>Leg Extension ISO hold</v>
+        <v>Lat Pulldown, alternating single-arm</v>
       </c>
       <c r="N28" t="str">
-        <v>iso</v>
+        <v>hyp</v>
       </c>
       <c r="O28">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P28" t="str">
         <v/>
       </c>
       <c r="Q28" t="str">
-        <v>4 × 30 s</v>
+        <v/>
       </c>
       <c r="R28" t="str">
         <v/>
@@ -7041,10 +7134,10 @@
         <v/>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G29" t="str">
-        <v>A-d3s6</v>
+        <v>A-d3s3</v>
       </c>
       <c r="H29" t="str">
         <v>Regular</v>
@@ -7053,28 +7146,28 @@
         <v>Accessory</v>
       </c>
       <c r="J29" t="str">
-        <v>either</v>
+        <v/>
       </c>
       <c r="K29" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L29" t="str">
-        <v>reardelt</v>
+        <v>wristpd</v>
       </c>
       <c r="M29" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Cable Wrist Pulldown</v>
       </c>
       <c r="N29" t="str">
-        <v>iso</v>
+        <v>hyp</v>
       </c>
       <c r="O29">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="P29" t="str">
         <v/>
       </c>
       <c r="Q29" t="str">
-        <v>4 × 15 s per arm</v>
+        <v/>
       </c>
       <c r="R29" t="str">
         <v/>
@@ -7097,10 +7190,10 @@
         <v/>
       </c>
       <c r="F30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G30" t="str">
-        <v>A-d3s6</v>
+        <v>A-d3s4</v>
       </c>
       <c r="H30" t="str">
         <v>Regular</v>
@@ -7109,22 +7202,22 @@
         <v>Accessory</v>
       </c>
       <c r="J30" t="str">
-        <v>either</v>
+        <v/>
       </c>
       <c r="K30" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L30" t="str">
-        <v>facepull</v>
+        <v>platerot</v>
       </c>
       <c r="M30" t="str">
-        <v>Face Pull</v>
+        <v>Plate Torso Rotation</v>
       </c>
       <c r="N30" t="str">
         <v>strength</v>
       </c>
       <c r="O30">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="P30" t="str">
         <v/>
@@ -7153,40 +7246,40 @@
         <v/>
       </c>
       <c r="F31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G31" t="str">
-        <v>A-d3s7</v>
+        <v>A-d3s5</v>
       </c>
       <c r="H31" t="str">
-        <v>Supersets</v>
+        <v>Regular</v>
       </c>
       <c r="I31" t="str">
         <v>Accessory</v>
       </c>
       <c r="J31" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K31" t="str">
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>pallof</v>
+        <v>legext</v>
       </c>
       <c r="M31" t="str">
-        <v>Pallof Press</v>
+        <v>Leg Extension ISO hold</v>
       </c>
       <c r="N31" t="str">
-        <v>strength</v>
+        <v>iso</v>
       </c>
       <c r="O31">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="P31" t="str">
         <v/>
       </c>
       <c r="Q31" t="str">
-        <v/>
+        <v>4 × 30 s</v>
       </c>
       <c r="R31" t="str">
         <v/>
@@ -7212,37 +7305,37 @@
         <v>7</v>
       </c>
       <c r="G32" t="str">
-        <v>A-d3s7</v>
+        <v>A-d3s6</v>
       </c>
       <c r="H32" t="str">
-        <v>Supersets</v>
+        <v>Regular</v>
       </c>
       <c r="I32" t="str">
         <v>Accessory</v>
       </c>
       <c r="J32" t="str">
-        <v>superset</v>
+        <v>either</v>
       </c>
       <c r="K32" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L32" t="str">
-        <v>cablerow</v>
+        <v>reardelt</v>
       </c>
       <c r="M32" t="str">
-        <v>Explosive Unilateral Cable Row</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="N32" t="str">
-        <v>exp</v>
+        <v>iso</v>
       </c>
       <c r="O32">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="P32" t="str">
         <v/>
       </c>
       <c r="Q32" t="str">
-        <v/>
+        <v>4 × 15 s per arm</v>
       </c>
       <c r="R32" t="str">
         <v/>
@@ -7265,34 +7358,34 @@
         <v/>
       </c>
       <c r="F33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G33" t="str">
-        <v>A-d3s8</v>
+        <v>A-d3s6</v>
       </c>
       <c r="H33" t="str">
-        <v>Home</v>
+        <v>Regular</v>
       </c>
       <c r="I33" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J33" t="str">
-        <v/>
+        <v>either</v>
       </c>
       <c r="K33" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L33" t="str">
-        <v>grip</v>
+        <v>facepull</v>
       </c>
       <c r="M33" t="str">
-        <v>Grip Trainer</v>
+        <v>Face Pull</v>
       </c>
       <c r="N33" t="str">
         <v>strength</v>
       </c>
       <c r="O33">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="P33" t="str">
         <v/>
@@ -7321,37 +7414,37 @@
         <v/>
       </c>
       <c r="F34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G34" t="str">
-        <v>A-d3s9</v>
+        <v>A-d3s7</v>
       </c>
       <c r="H34" t="str">
-        <v>Home</v>
+        <v>Supersets</v>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J34" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K34" t="str">
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>deskbands</v>
+        <v>pallof</v>
       </c>
       <c r="M34" t="str">
-        <v>Desk Bands</v>
+        <v>Pallof Press</v>
       </c>
       <c r="N34" t="str">
-        <v>iso</v>
-      </c>
-      <c r="O34" t="str">
-        <v/>
+        <v>strength</v>
+      </c>
+      <c r="O34">
+        <v>30</v>
       </c>
       <c r="P34" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q34" t="str">
         <v/>
@@ -7365,10 +7458,10 @@
         <v>A</v>
       </c>
       <c r="B35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C35" t="str">
-        <v>Day 4</v>
+        <v>Day 3</v>
       </c>
       <c r="D35" t="str">
         <v/>
@@ -7377,40 +7470,40 @@
         <v/>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G35" t="str">
-        <v>A-d4s1</v>
+        <v>A-d3s7</v>
       </c>
       <c r="H35" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I35" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J35" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K35" t="str">
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>suitcase</v>
+        <v>cablerow</v>
       </c>
       <c r="M35" t="str">
-        <v>Suitcase Bottom-Up, single-arm</v>
+        <v>Explosive Unilateral Cable Row</v>
       </c>
       <c r="N35" t="str">
-        <v/>
+        <v>exp</v>
       </c>
       <c r="O35">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P35" t="str">
         <v/>
       </c>
       <c r="Q35" t="str">
-        <v>3 × 4 each arm</v>
+        <v/>
       </c>
       <c r="R35" t="str">
         <v/>
@@ -7421,10 +7514,10 @@
         <v>A</v>
       </c>
       <c r="B36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C36" t="str">
-        <v>Day 4</v>
+        <v>Day 3</v>
       </c>
       <c r="D36" t="str">
         <v/>
@@ -7433,16 +7526,16 @@
         <v/>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G36" t="str">
-        <v>A-d4s2</v>
+        <v>A-d3s8</v>
       </c>
       <c r="H36" t="str">
-        <v>Regular</v>
+        <v>Home</v>
       </c>
       <c r="I36" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J36" t="str">
         <v/>
@@ -7451,16 +7544,16 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>innerthigh</v>
+        <v>grip</v>
       </c>
       <c r="M36" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="N36" t="str">
         <v>strength</v>
       </c>
       <c r="O36">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="P36" t="str">
         <v/>
@@ -7477,10 +7570,10 @@
         <v>A</v>
       </c>
       <c r="B37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C37" t="str">
-        <v>Day 4</v>
+        <v>Day 3</v>
       </c>
       <c r="D37" t="str">
         <v/>
@@ -7489,16 +7582,16 @@
         <v/>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G37" t="str">
-        <v>A-d4s3</v>
+        <v>A-d3s9</v>
       </c>
       <c r="H37" t="str">
-        <v>Regular</v>
+        <v>Home</v>
       </c>
       <c r="I37" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J37" t="str">
         <v/>
@@ -7507,13 +7600,13 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>romanadd</v>
+        <v>deskbands</v>
       </c>
       <c r="M37" t="str">
-        <v>Roman Chair Hip Adduction</v>
+        <v>Desk Bands</v>
       </c>
       <c r="N37" t="str">
-        <v/>
+        <v>iso</v>
       </c>
       <c r="O37" t="str">
         <v/>
@@ -7525,7 +7618,7 @@
         <v/>
       </c>
       <c r="R37" t="str">
-        <v>On the back-extension bench</v>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -7545,40 +7638,40 @@
         <v/>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G38" t="str">
-        <v>A-d4s4</v>
+        <v>A-sled4</v>
       </c>
       <c r="H38" t="str">
-        <v>Supersets</v>
+        <v>Optional</v>
       </c>
       <c r="I38" t="str">
-        <v>Primary</v>
+        <v/>
       </c>
       <c r="J38" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K38" t="str">
-        <v/>
+        <v>Optional</v>
       </c>
       <c r="L38" t="str">
-        <v>arnold</v>
+        <v>sledlat</v>
       </c>
       <c r="M38" t="str">
-        <v>Arnold Press</v>
+        <v>Sled push → lateral pull</v>
       </c>
       <c r="N38" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O38">
-        <v>35</v>
+        <v>exp</v>
+      </c>
+      <c r="O38" t="str">
+        <v/>
       </c>
       <c r="P38" t="str">
         <v/>
       </c>
       <c r="Q38" t="str">
-        <v/>
+        <v>1 × 3</v>
       </c>
       <c r="R38" t="str">
         <v/>
@@ -7601,40 +7694,40 @@
         <v/>
       </c>
       <c r="F39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G39" t="str">
-        <v>A-d4s4</v>
+        <v>A-d4s1</v>
       </c>
       <c r="H39" t="str">
-        <v>Supersets</v>
+        <v>Regular</v>
       </c>
       <c r="I39" t="str">
         <v>Primary</v>
       </c>
       <c r="J39" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K39" t="str">
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>zercher</v>
+        <v>suitcase</v>
       </c>
       <c r="M39" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Suitcase Bottom-Up, single-arm</v>
       </c>
       <c r="N39" t="str">
-        <v>strength</v>
+        <v/>
       </c>
       <c r="O39">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="P39" t="str">
         <v/>
       </c>
       <c r="Q39" t="str">
-        <v/>
+        <v>3 × 4 each arm</v>
       </c>
       <c r="R39" t="str">
         <v/>
@@ -7657,34 +7750,34 @@
         <v/>
       </c>
       <c r="F40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G40" t="str">
-        <v>A-d4s5</v>
+        <v>A-d4s2</v>
       </c>
       <c r="H40" t="str">
-        <v>Supersets</v>
+        <v>Regular</v>
       </c>
       <c r="I40" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J40" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K40" t="str">
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>hipthrust</v>
+        <v>innerthigh</v>
       </c>
       <c r="M40" t="str">
-        <v>Hip Thrust</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="N40" t="str">
         <v>strength</v>
       </c>
       <c r="O40">
-        <v>320</v>
+        <v>180</v>
       </c>
       <c r="P40" t="str">
         <v/>
@@ -7713,43 +7806,43 @@
         <v/>
       </c>
       <c r="F41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G41" t="str">
-        <v>A-d4s5</v>
+        <v>A-d4s3</v>
       </c>
       <c r="H41" t="str">
-        <v>Supersets</v>
+        <v>Regular</v>
       </c>
       <c r="I41" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J41" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K41" t="str">
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>chestpress</v>
+        <v>romanadd</v>
       </c>
       <c r="M41" t="str">
-        <v>Chest Press</v>
+        <v>Roman Chair Hip Adduction</v>
       </c>
       <c r="N41" t="str">
-        <v>hyp</v>
-      </c>
-      <c r="O41">
-        <v>25</v>
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
       </c>
       <c r="P41" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q41" t="str">
         <v/>
       </c>
       <c r="R41" t="str">
-        <v/>
+        <v>On the back-extension bench</v>
       </c>
     </row>
     <row r="42">
@@ -7769,16 +7862,16 @@
         <v/>
       </c>
       <c r="F42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G42" t="str">
-        <v>A-d4s6</v>
+        <v>A-d4s4</v>
       </c>
       <c r="H42" t="str">
         <v>Supersets</v>
       </c>
       <c r="I42" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J42" t="str">
         <v>superset</v>
@@ -7787,22 +7880,22 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>zottman</v>
+        <v>arnold</v>
       </c>
       <c r="M42" t="str">
-        <v>Zottman Curl</v>
+        <v>Arnold Press</v>
       </c>
       <c r="N42" t="str">
-        <v>hyp</v>
+        <v>strength</v>
       </c>
       <c r="O42">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="P42" t="str">
         <v/>
       </c>
       <c r="Q42" t="str">
-        <v>3 × 15</v>
+        <v/>
       </c>
       <c r="R42" t="str">
         <v/>
@@ -7825,16 +7918,16 @@
         <v/>
       </c>
       <c r="F43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G43" t="str">
-        <v>A-d4s6</v>
+        <v>A-d4s4</v>
       </c>
       <c r="H43" t="str">
         <v>Supersets</v>
       </c>
       <c r="I43" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J43" t="str">
         <v>superset</v>
@@ -7843,22 +7936,22 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>kbleg</v>
+        <v>zercher</v>
       </c>
       <c r="M43" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="N43" t="str">
-        <v>iso</v>
+        <v>strength</v>
       </c>
       <c r="O43">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="P43" t="str">
         <v/>
       </c>
       <c r="Q43" t="str">
-        <v>3 × 15 s hold</v>
+        <v/>
       </c>
       <c r="R43" t="str">
         <v/>
@@ -7881,34 +7974,34 @@
         <v/>
       </c>
       <c r="F44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G44" t="str">
-        <v>A-d4s7</v>
+        <v>A-d4s5</v>
       </c>
       <c r="H44" t="str">
-        <v>Home</v>
+        <v>Supersets</v>
       </c>
       <c r="I44" t="str">
-        <v/>
+        <v>Primary</v>
       </c>
       <c r="J44" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K44" t="str">
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>grip</v>
+        <v>hipthrust</v>
       </c>
       <c r="M44" t="str">
-        <v>Grip Trainer</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="N44" t="str">
         <v>strength</v>
       </c>
       <c r="O44">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="P44" t="str">
         <v/>
@@ -7937,37 +8030,37 @@
         <v/>
       </c>
       <c r="F45">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G45" t="str">
-        <v>A-d4s8</v>
+        <v>A-d4s5</v>
       </c>
       <c r="H45" t="str">
-        <v>Home</v>
+        <v>Supersets</v>
       </c>
       <c r="I45" t="str">
-        <v/>
+        <v>Primary</v>
       </c>
       <c r="J45" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K45" t="str">
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>deskbands</v>
+        <v>chestpress</v>
       </c>
       <c r="M45" t="str">
-        <v>Desk Bands</v>
+        <v>Chest Press</v>
       </c>
       <c r="N45" t="str">
-        <v/>
-      </c>
-      <c r="O45" t="str">
-        <v/>
+        <v>hyp</v>
+      </c>
+      <c r="O45">
+        <v>25</v>
       </c>
       <c r="P45" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q45" t="str">
         <v/>
@@ -7981,52 +8074,52 @@
         <v>A</v>
       </c>
       <c r="B46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C46" t="str">
-        <v>Day 5</v>
+        <v>Day 4</v>
       </c>
       <c r="D46" t="str">
         <v/>
       </c>
       <c r="E46" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G46" t="str">
-        <v>A-d5s1</v>
+        <v>A-d4s6</v>
       </c>
       <c r="H46" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I46" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J46" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K46" t="str">
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>cablecrunch</v>
+        <v>zottman</v>
       </c>
       <c r="M46" t="str">
-        <v>Kneeling Cable Ab Crunch</v>
+        <v>Zottman Curl</v>
       </c>
       <c r="N46" t="str">
-        <v>strength</v>
+        <v>hyp</v>
       </c>
       <c r="O46">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="P46" t="str">
         <v/>
       </c>
       <c r="Q46" t="str">
-        <v/>
+        <v>3 × 15</v>
       </c>
       <c r="R46" t="str">
         <v/>
@@ -8037,52 +8130,52 @@
         <v>A</v>
       </c>
       <c r="B47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C47" t="str">
-        <v>Day 5</v>
+        <v>Day 4</v>
       </c>
       <c r="D47" t="str">
         <v/>
       </c>
       <c r="E47" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="F47">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G47" t="str">
-        <v>A-d5s2</v>
+        <v>A-d4s6</v>
       </c>
       <c r="H47" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I47" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J47" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K47" t="str">
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>dbclean</v>
+        <v>kbleg</v>
       </c>
       <c r="M47" t="str">
-        <v>DB Clean &amp; Jerk Press</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="N47" t="str">
-        <v>exp</v>
+        <v>iso</v>
       </c>
       <c r="O47">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="P47" t="str">
         <v/>
       </c>
       <c r="Q47" t="str">
-        <v/>
+        <v>3 × 15 s hold</v>
       </c>
       <c r="R47" t="str">
         <v/>
@@ -8093,25 +8186,25 @@
         <v>A</v>
       </c>
       <c r="B48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C48" t="str">
-        <v>Day 5</v>
+        <v>Day 4</v>
       </c>
       <c r="D48" t="str">
         <v/>
       </c>
       <c r="E48" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G48" t="str">
-        <v>A-d5s3</v>
+        <v>A-d4s7</v>
       </c>
       <c r="H48" t="str">
-        <v>Regular</v>
+        <v>Home</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -8123,16 +8216,16 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>hack</v>
+        <v>grip</v>
       </c>
       <c r="M48" t="str">
-        <v>Hack Squat</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="N48" t="str">
-        <v>hyp</v>
+        <v>strength</v>
       </c>
       <c r="O48">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="P48" t="str">
         <v/>
@@ -8141,7 +8234,7 @@
         <v/>
       </c>
       <c r="R48" t="str">
-        <v>Feet low on the plate, narrow stance for quads</v>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -8149,52 +8242,52 @@
         <v>A</v>
       </c>
       <c r="B49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C49" t="str">
-        <v>Day 5</v>
+        <v>Day 4</v>
       </c>
       <c r="D49" t="str">
         <v/>
       </c>
       <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49">
+        <v>9</v>
+      </c>
+      <c r="G49" t="str">
+        <v>A-d4s8</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+      <c r="K49" t="str">
+        <v/>
+      </c>
+      <c r="L49" t="str">
+        <v>deskbands</v>
+      </c>
+      <c r="M49" t="str">
+        <v>Desk Bands</v>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+      <c r="P49" t="str">
         <v>Yes</v>
       </c>
-      <c r="F49">
-        <v>4</v>
-      </c>
-      <c r="G49" t="str">
-        <v>A-d5s4</v>
-      </c>
-      <c r="H49" t="str">
-        <v>Regular</v>
-      </c>
-      <c r="I49" t="str">
-        <v>Accessory</v>
-      </c>
-      <c r="J49" t="str">
-        <v>either</v>
-      </c>
-      <c r="K49" t="str">
-        <v>Whichever is free</v>
-      </c>
-      <c r="L49" t="str">
-        <v>reardelt</v>
-      </c>
-      <c r="M49" t="str">
-        <v>Side Rear Delt Fly</v>
-      </c>
-      <c r="N49" t="str">
-        <v>iso</v>
-      </c>
-      <c r="O49">
-        <v>50</v>
-      </c>
-      <c r="P49" t="str">
-        <v/>
-      </c>
       <c r="Q49" t="str">
-        <v>4 × 15 s per arm</v>
+        <v/>
       </c>
       <c r="R49" t="str">
         <v/>
@@ -8217,40 +8310,40 @@
         <v>Yes</v>
       </c>
       <c r="F50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G50" t="str">
-        <v>A-d5s4</v>
+        <v>A-sled5</v>
       </c>
       <c r="H50" t="str">
-        <v>Regular</v>
+        <v>Optional</v>
       </c>
       <c r="I50" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J50" t="str">
-        <v>either</v>
+        <v/>
       </c>
       <c r="K50" t="str">
-        <v>Whichever is free</v>
+        <v>Optional</v>
       </c>
       <c r="L50" t="str">
-        <v>facepull</v>
+        <v>sledlat</v>
       </c>
       <c r="M50" t="str">
-        <v>Face Pull</v>
+        <v>Sled push → lateral pull</v>
       </c>
       <c r="N50" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O50">
-        <v>30</v>
+        <v>exp</v>
+      </c>
+      <c r="O50" t="str">
+        <v/>
       </c>
       <c r="P50" t="str">
         <v/>
       </c>
       <c r="Q50" t="str">
-        <v/>
+        <v>1 × 3</v>
       </c>
       <c r="R50" t="str">
         <v/>
@@ -8273,13 +8366,13 @@
         <v>Yes</v>
       </c>
       <c r="F51">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G51" t="str">
-        <v>A-d5s5</v>
+        <v>A-d5s1</v>
       </c>
       <c r="H51" t="str">
-        <v>Plyometric</v>
+        <v>Regular</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -8291,19 +8384,19 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>trxpike</v>
+        <v>cablecrunch</v>
       </c>
       <c r="M51" t="str">
-        <v>TRX Pike Push-Up</v>
+        <v>Kneeling Cable Ab Crunch</v>
       </c>
       <c r="N51" t="str">
-        <v>exp</v>
-      </c>
-      <c r="O51" t="str">
-        <v/>
+        <v>strength</v>
+      </c>
+      <c r="O51">
+        <v>60</v>
       </c>
       <c r="P51" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q51" t="str">
         <v/>
@@ -8329,13 +8422,13 @@
         <v>Yes</v>
       </c>
       <c r="F52">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G52" t="str">
-        <v>A-d5s6</v>
+        <v>A-d5s2</v>
       </c>
       <c r="H52" t="str">
-        <v>Plyometric</v>
+        <v>Regular</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -8347,19 +8440,19 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>trxrow</v>
+        <v>dbclean</v>
       </c>
       <c r="M52" t="str">
-        <v>TRX Wide-Grip Row</v>
+        <v>DB Clean &amp; Jerk Press</v>
       </c>
       <c r="N52" t="str">
         <v>exp</v>
       </c>
-      <c r="O52" t="str">
-        <v/>
+      <c r="O52">
+        <v>20</v>
       </c>
       <c r="P52" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q52" t="str">
         <v/>
@@ -8385,13 +8478,13 @@
         <v>Yes</v>
       </c>
       <c r="F53">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G53" t="str">
-        <v>A-d5s7</v>
+        <v>A-d5s3</v>
       </c>
       <c r="H53" t="str">
-        <v>Plyometric</v>
+        <v>Regular</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -8403,16 +8496,16 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>medball</v>
+        <v>hack</v>
       </c>
       <c r="M53" t="str">
-        <v>Med Ball Rotational Scoop</v>
+        <v>Hack Squat</v>
       </c>
       <c r="N53" t="str">
-        <v>exp</v>
-      </c>
-      <c r="O53" t="str">
-        <v/>
+        <v>hyp</v>
+      </c>
+      <c r="O53">
+        <v>270</v>
       </c>
       <c r="P53" t="str">
         <v/>
@@ -8421,7 +8514,7 @@
         <v/>
       </c>
       <c r="R53" t="str">
-        <v/>
+        <v>Feet low on the plate, narrow stance for quads</v>
       </c>
     </row>
     <row r="54">
@@ -8441,40 +8534,40 @@
         <v>Yes</v>
       </c>
       <c r="F54">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G54" t="str">
-        <v>A-d5s8</v>
+        <v>A-d5s4</v>
       </c>
       <c r="H54" t="str">
-        <v>Plyometric</v>
+        <v>Regular</v>
       </c>
       <c r="I54" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J54" t="str">
-        <v/>
+        <v>either</v>
       </c>
       <c r="K54" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L54" t="str">
-        <v>latwall</v>
+        <v>reardelt</v>
       </c>
       <c r="M54" t="str">
-        <v>Lateral Wall Push</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="N54" t="str">
-        <v>exp</v>
-      </c>
-      <c r="O54" t="str">
-        <v/>
+        <v>iso</v>
+      </c>
+      <c r="O54">
+        <v>50</v>
       </c>
       <c r="P54" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q54" t="str">
-        <v/>
+        <v>4 × 15 s per arm</v>
       </c>
       <c r="R54" t="str">
         <v/>
@@ -8497,40 +8590,40 @@
         <v>Yes</v>
       </c>
       <c r="F55">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G55" t="str">
-        <v>A-d5s9</v>
+        <v>A-d5s4</v>
       </c>
       <c r="H55" t="str">
-        <v>Home</v>
+        <v>Regular</v>
       </c>
       <c r="I55" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J55" t="str">
-        <v/>
+        <v>either</v>
       </c>
       <c r="K55" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L55" t="str">
-        <v>db6</v>
+        <v>facepull</v>
       </c>
       <c r="M55" t="str">
-        <v>DB 6 Ways</v>
+        <v>Face Pull</v>
       </c>
       <c r="N55" t="str">
         <v>strength</v>
       </c>
       <c r="O55">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="P55" t="str">
         <v/>
       </c>
       <c r="Q55" t="str">
-        <v>2 × 6</v>
+        <v/>
       </c>
       <c r="R55" t="str">
         <v/>
@@ -8553,13 +8646,13 @@
         <v>Yes</v>
       </c>
       <c r="F56">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G56" t="str">
-        <v>A-d5s10</v>
+        <v>A-d5s5</v>
       </c>
       <c r="H56" t="str">
-        <v>Home</v>
+        <v>Plyometric</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -8571,13 +8664,13 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>spinal</v>
+        <v>trxpike</v>
       </c>
       <c r="M56" t="str">
-        <v>Spinal Waves</v>
+        <v>TRX Pike Push-Up</v>
       </c>
       <c r="N56" t="str">
-        <v/>
+        <v>exp</v>
       </c>
       <c r="O56" t="str">
         <v/>
@@ -8597,22 +8690,22 @@
         <v>A</v>
       </c>
       <c r="B57">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C57" t="str">
-        <v>Day 6</v>
+        <v>Day 5</v>
       </c>
       <c r="D57" t="str">
         <v/>
       </c>
       <c r="E57" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G57" t="str">
-        <v>A-d6s1</v>
+        <v>A-d5s6</v>
       </c>
       <c r="H57" t="str">
         <v>Plyometric</v>
@@ -8627,10 +8720,10 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>pogo</v>
+        <v>trxrow</v>
       </c>
       <c r="M57" t="str">
-        <v>Pogo Hops</v>
+        <v>TRX Wide-Grip Row</v>
       </c>
       <c r="N57" t="str">
         <v>exp</v>
@@ -8642,7 +8735,7 @@
         <v>Yes</v>
       </c>
       <c r="Q57" t="str">
-        <v>3 × 10</v>
+        <v/>
       </c>
       <c r="R57" t="str">
         <v/>
@@ -8653,22 +8746,22 @@
         <v>A</v>
       </c>
       <c r="B58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C58" t="str">
-        <v>Day 6</v>
+        <v>Day 5</v>
       </c>
       <c r="D58" t="str">
         <v/>
       </c>
       <c r="E58" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="F58">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G58" t="str">
-        <v>A-d6s2</v>
+        <v>A-d5s7</v>
       </c>
       <c r="H58" t="str">
         <v>Plyometric</v>
@@ -8683,10 +8776,10 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>skater</v>
+        <v>medball</v>
       </c>
       <c r="M58" t="str">
-        <v>Lateral Bound / Skater Hop with Stick</v>
+        <v>Med Ball Rotational Scoop</v>
       </c>
       <c r="N58" t="str">
         <v>exp</v>
@@ -8695,10 +8788,10 @@
         <v/>
       </c>
       <c r="P58" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q58" t="str">
-        <v>3 × 5, hold 3 s</v>
+        <v/>
       </c>
       <c r="R58" t="str">
         <v/>
@@ -8709,22 +8802,22 @@
         <v>A</v>
       </c>
       <c r="B59">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C59" t="str">
-        <v>Day 6</v>
+        <v>Day 5</v>
       </c>
       <c r="D59" t="str">
         <v/>
       </c>
       <c r="E59" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="F59">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G59" t="str">
-        <v>A-d6s3</v>
+        <v>A-d5s8</v>
       </c>
       <c r="H59" t="str">
         <v>Plyometric</v>
@@ -8739,10 +8832,10 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>splitjump</v>
+        <v>latwall</v>
       </c>
       <c r="M59" t="str">
-        <v>Split Squat Jumps</v>
+        <v>Lateral Wall Push</v>
       </c>
       <c r="N59" t="str">
         <v>exp</v>
@@ -8754,10 +8847,10 @@
         <v>Yes</v>
       </c>
       <c r="Q59" t="str">
-        <v>3 × 5</v>
+        <v/>
       </c>
       <c r="R59" t="str">
-        <v>Vertical drive, soft landings</v>
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -8765,25 +8858,25 @@
         <v>A</v>
       </c>
       <c r="B60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C60" t="str">
-        <v>Day 6</v>
+        <v>Day 5</v>
       </c>
       <c r="D60" t="str">
         <v/>
       </c>
       <c r="E60" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="F60">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G60" t="str">
-        <v>A-d6s4</v>
+        <v>A-d5s9</v>
       </c>
       <c r="H60" t="str">
-        <v>Plyometric</v>
+        <v>Home</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -8795,25 +8888,25 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>depthcombo</v>
+        <v>db6</v>
       </c>
       <c r="M60" t="str">
-        <v>Depth Drop → Broad Jump → Box Jump</v>
+        <v>DB 6 Ways</v>
       </c>
       <c r="N60" t="str">
-        <v>exp</v>
-      </c>
-      <c r="O60" t="str">
-        <v/>
+        <v>strength</v>
+      </c>
+      <c r="O60">
+        <v>10</v>
       </c>
       <c r="P60" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q60" t="str">
-        <v>4 × 5</v>
+        <v>2 × 6</v>
       </c>
       <c r="R60" t="str">
-        <v>Controlled landings</v>
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -8821,49 +8914,49 @@
         <v>A</v>
       </c>
       <c r="B61">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C61" t="str">
-        <v>Day 6</v>
+        <v>Day 5</v>
       </c>
       <c r="D61" t="str">
         <v/>
       </c>
       <c r="E61" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="F61">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G61" t="str">
-        <v>A-d6s5</v>
+        <v>A-d5s10</v>
       </c>
       <c r="H61" t="str">
-        <v>Supersets</v>
+        <v>Home</v>
       </c>
       <c r="I61" t="str">
-        <v>Primary</v>
+        <v/>
       </c>
       <c r="J61" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K61" t="str">
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>arnold</v>
+        <v>spinal</v>
       </c>
       <c r="M61" t="str">
-        <v>Arnold Press</v>
+        <v>Spinal Waves</v>
       </c>
       <c r="N61" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O61">
-        <v>35</v>
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
       </c>
       <c r="P61" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q61" t="str">
         <v/>
@@ -8889,40 +8982,40 @@
         <v/>
       </c>
       <c r="F62">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G62" t="str">
-        <v>A-d6s5</v>
+        <v>A-sled6</v>
       </c>
       <c r="H62" t="str">
-        <v>Supersets</v>
+        <v>Optional</v>
       </c>
       <c r="I62" t="str">
-        <v>Primary</v>
+        <v/>
       </c>
       <c r="J62" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K62" t="str">
-        <v/>
+        <v>Optional</v>
       </c>
       <c r="L62" t="str">
-        <v>zercher</v>
+        <v>sledlat</v>
       </c>
       <c r="M62" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Sled push → lateral pull</v>
       </c>
       <c r="N62" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O62">
-        <v>50</v>
+        <v>exp</v>
+      </c>
+      <c r="O62" t="str">
+        <v/>
       </c>
       <c r="P62" t="str">
         <v/>
       </c>
       <c r="Q62" t="str">
-        <v/>
+        <v>1 × 3</v>
       </c>
       <c r="R62" t="str">
         <v/>
@@ -8945,40 +9038,40 @@
         <v/>
       </c>
       <c r="F63">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G63" t="str">
-        <v>A-d6s6</v>
+        <v>A-d6s1</v>
       </c>
       <c r="H63" t="str">
-        <v>Supersets</v>
+        <v>Plyometric</v>
       </c>
       <c r="I63" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J63" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K63" t="str">
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>pallof</v>
+        <v>pogo</v>
       </c>
       <c r="M63" t="str">
-        <v>Pallof Press</v>
+        <v>Pogo Hops</v>
       </c>
       <c r="N63" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O63">
-        <v>30</v>
+        <v>exp</v>
+      </c>
+      <c r="O63" t="str">
+        <v/>
       </c>
       <c r="P63" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q63" t="str">
-        <v/>
+        <v>3 × 10</v>
       </c>
       <c r="R63" t="str">
         <v/>
@@ -9001,40 +9094,40 @@
         <v/>
       </c>
       <c r="F64">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G64" t="str">
-        <v>A-d6s6</v>
+        <v>A-d6s2</v>
       </c>
       <c r="H64" t="str">
-        <v>Supersets</v>
+        <v>Plyometric</v>
       </c>
       <c r="I64" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J64" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K64" t="str">
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>cablerow</v>
+        <v>skater</v>
       </c>
       <c r="M64" t="str">
-        <v>Explosive Unilateral Cable Row</v>
+        <v>Lateral Bound / Skater Hop with Stick</v>
       </c>
       <c r="N64" t="str">
         <v>exp</v>
       </c>
-      <c r="O64">
-        <v>30</v>
+      <c r="O64" t="str">
+        <v/>
       </c>
       <c r="P64" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q64" t="str">
-        <v/>
+        <v>3 × 5, hold 3 s</v>
       </c>
       <c r="R64" t="str">
         <v/>
@@ -9045,10 +9138,10 @@
         <v>A</v>
       </c>
       <c r="B65">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C65" t="str">
-        <v>Day 7</v>
+        <v>Day 6</v>
       </c>
       <c r="D65" t="str">
         <v/>
@@ -9056,14 +9149,14 @@
       <c r="E65" t="str">
         <v/>
       </c>
-      <c r="F65" t="str">
-        <v/>
+      <c r="F65">
+        <v>4</v>
       </c>
       <c r="G65" t="str">
-        <v/>
+        <v>A-d6s3</v>
       </c>
       <c r="H65" t="str">
-        <v/>
+        <v>Plyometric</v>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -9075,36 +9168,36 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v/>
+        <v>splitjump</v>
       </c>
       <c r="M65" t="str">
-        <v/>
+        <v>Split Squat Jumps</v>
       </c>
       <c r="N65" t="str">
-        <v/>
+        <v>exp</v>
       </c>
       <c r="O65" t="str">
         <v/>
       </c>
       <c r="P65" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q65" t="str">
-        <v/>
+        <v>3 × 5</v>
       </c>
       <c r="R65" t="str">
-        <v/>
+        <v>Vertical drive, soft landings</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="B66">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C66" t="str">
-        <v>Day 1</v>
+        <v>Day 6</v>
       </c>
       <c r="D66" t="str">
         <v/>
@@ -9113,16 +9206,16 @@
         <v/>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G66" t="str">
-        <v>B-d1s1</v>
+        <v>A-d6s4</v>
       </c>
       <c r="H66" t="str">
-        <v>Regular</v>
+        <v>Plyometric</v>
       </c>
       <c r="I66" t="str">
-        <v>Primary</v>
+        <v/>
       </c>
       <c r="J66" t="str">
         <v/>
@@ -9131,36 +9224,36 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>latpdbi</v>
+        <v>depthcombo</v>
       </c>
       <c r="M66" t="str">
-        <v>Lat Pulldown</v>
+        <v>Depth Drop → Broad Jump → Box Jump</v>
       </c>
       <c r="N66" t="str">
-        <v>hyp</v>
-      </c>
-      <c r="O66">
-        <v>45</v>
+        <v>exp</v>
+      </c>
+      <c r="O66" t="str">
+        <v/>
       </c>
       <c r="P66" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q66" t="str">
-        <v/>
+        <v>4 × 5</v>
       </c>
       <c r="R66" t="str">
-        <v/>
+        <v>Controlled landings</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C67" t="str">
-        <v>Day 1</v>
+        <v>Day 6</v>
       </c>
       <c r="D67" t="str">
         <v/>
@@ -9169,34 +9262,34 @@
         <v/>
       </c>
       <c r="F67">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G67" t="str">
-        <v>B-d1s2</v>
+        <v>A-d6s5</v>
       </c>
       <c r="H67" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I67" t="str">
         <v>Primary</v>
       </c>
       <c r="J67" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K67" t="str">
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>hack</v>
+        <v>arnold</v>
       </c>
       <c r="M67" t="str">
-        <v>Hack Squat</v>
+        <v>Arnold Press</v>
       </c>
       <c r="N67" t="str">
-        <v>hyp</v>
+        <v>strength</v>
       </c>
       <c r="O67">
-        <v>270</v>
+        <v>35</v>
       </c>
       <c r="P67" t="str">
         <v/>
@@ -9205,18 +9298,18 @@
         <v/>
       </c>
       <c r="R67" t="str">
-        <v>Feet low on the plate, narrow stance for quads</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C68" t="str">
-        <v>Day 1</v>
+        <v>Day 6</v>
       </c>
       <c r="D68" t="str">
         <v/>
@@ -9225,34 +9318,34 @@
         <v/>
       </c>
       <c r="F68">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G68" t="str">
-        <v>B-d1s3</v>
+        <v>A-d6s5</v>
       </c>
       <c r="H68" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I68" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J68" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K68" t="str">
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>wristpd</v>
+        <v>zercher</v>
       </c>
       <c r="M68" t="str">
-        <v>Cable Wrist Pulldown</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="N68" t="str">
-        <v>hyp</v>
+        <v>strength</v>
       </c>
       <c r="O68">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="P68" t="str">
         <v/>
@@ -9266,13 +9359,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C69" t="str">
-        <v>Day 1</v>
+        <v>Day 6</v>
       </c>
       <c r="D69" t="str">
         <v/>
@@ -9281,34 +9374,34 @@
         <v/>
       </c>
       <c r="F69">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G69" t="str">
-        <v>B-d1s4</v>
+        <v>A-d6s6</v>
       </c>
       <c r="H69" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I69" t="str">
         <v>Accessory</v>
       </c>
       <c r="J69" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K69" t="str">
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>platerot</v>
+        <v>pallof</v>
       </c>
       <c r="M69" t="str">
-        <v>Plate Torso Rotation</v>
+        <v>Pallof Press</v>
       </c>
       <c r="N69" t="str">
         <v>strength</v>
       </c>
       <c r="O69">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="P69" t="str">
         <v/>
@@ -9322,13 +9415,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C70" t="str">
-        <v>Day 1</v>
+        <v>Day 6</v>
       </c>
       <c r="D70" t="str">
         <v/>
@@ -9337,34 +9430,34 @@
         <v/>
       </c>
       <c r="F70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G70" t="str">
-        <v>B-d1s5</v>
+        <v>A-d6s6</v>
       </c>
       <c r="H70" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I70" t="str">
         <v>Accessory</v>
       </c>
       <c r="J70" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K70" t="str">
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>innerthigh</v>
+        <v>cablerow</v>
       </c>
       <c r="M70" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Explosive Unilateral Cable Row</v>
       </c>
       <c r="N70" t="str">
-        <v>strength</v>
+        <v>exp</v>
       </c>
       <c r="O70">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="P70" t="str">
         <v/>
@@ -9378,13 +9471,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="B71">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C71" t="str">
-        <v>Day 1</v>
+        <v>Day 7</v>
       </c>
       <c r="D71" t="str">
         <v/>
@@ -9392,17 +9485,17 @@
       <c r="E71" t="str">
         <v/>
       </c>
-      <c r="F71">
-        <v>6</v>
+      <c r="F71" t="str">
+        <v/>
       </c>
       <c r="G71" t="str">
-        <v>B-d1s6</v>
+        <v/>
       </c>
       <c r="H71" t="str">
-        <v>Regular</v>
+        <v/>
       </c>
       <c r="I71" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J71" t="str">
         <v/>
@@ -9411,16 +9504,16 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>outerthigh</v>
+        <v/>
       </c>
       <c r="M71" t="str">
-        <v>Outer Thigh Adduction</v>
+        <v/>
       </c>
       <c r="N71" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O71">
-        <v>160</v>
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
       </c>
       <c r="P71" t="str">
         <v/>
@@ -9449,40 +9542,40 @@
         <v/>
       </c>
       <c r="F72">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G72" t="str">
-        <v>B-d1s7</v>
+        <v>B-sled1</v>
       </c>
       <c r="H72" t="str">
-        <v>Regular</v>
+        <v>Optional</v>
       </c>
       <c r="I72" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J72" t="str">
         <v/>
       </c>
       <c r="K72" t="str">
-        <v/>
+        <v>Optional</v>
       </c>
       <c r="L72" t="str">
-        <v>qlext</v>
+        <v>sled</v>
       </c>
       <c r="M72" t="str">
-        <v>Side Lateral QL Extension</v>
+        <v>Sled push → pull</v>
       </c>
       <c r="N72" t="str">
-        <v/>
+        <v>exp</v>
       </c>
       <c r="O72" t="str">
         <v/>
       </c>
       <c r="P72" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q72" t="str">
-        <v/>
+        <v>1 × 3</v>
       </c>
       <c r="R72" t="str">
         <v/>
@@ -9505,34 +9598,34 @@
         <v/>
       </c>
       <c r="F73">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G73" t="str">
-        <v>B-d1s8</v>
+        <v>B-d1s1</v>
       </c>
       <c r="H73" t="str">
-        <v>Supersets</v>
+        <v>Regular</v>
       </c>
       <c r="I73" t="str">
         <v>Primary</v>
       </c>
       <c r="J73" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K73" t="str">
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>chestpress</v>
+        <v>latpdbi</v>
       </c>
       <c r="M73" t="str">
-        <v>Chest Press</v>
+        <v>Lat Pulldown</v>
       </c>
       <c r="N73" t="str">
-        <v>strength</v>
+        <v>hyp</v>
       </c>
       <c r="O73">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="P73" t="str">
         <v/>
@@ -9561,34 +9654,34 @@
         <v/>
       </c>
       <c r="F74">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G74" t="str">
-        <v>B-d1s8</v>
+        <v>B-d1s2</v>
       </c>
       <c r="H74" t="str">
-        <v>Supersets</v>
+        <v>Regular</v>
       </c>
       <c r="I74" t="str">
         <v>Primary</v>
       </c>
       <c r="J74" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K74" t="str">
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>zercher</v>
+        <v>hack</v>
       </c>
       <c r="M74" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Hack Squat</v>
       </c>
       <c r="N74" t="str">
-        <v>strength</v>
+        <v>hyp</v>
       </c>
       <c r="O74">
-        <v>50</v>
+        <v>270</v>
       </c>
       <c r="P74" t="str">
         <v/>
@@ -9597,7 +9690,7 @@
         <v/>
       </c>
       <c r="R74" t="str">
-        <v/>
+        <v>Feet low on the plate, narrow stance for quads</v>
       </c>
     </row>
     <row r="75">
@@ -9617,40 +9710,40 @@
         <v/>
       </c>
       <c r="F75">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G75" t="str">
-        <v>B-d1s9</v>
+        <v>B-d1s3</v>
       </c>
       <c r="H75" t="str">
-        <v>Supersets</v>
+        <v>Regular</v>
       </c>
       <c r="I75" t="str">
         <v>Accessory</v>
       </c>
       <c r="J75" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K75" t="str">
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>zottman</v>
+        <v>wristpd</v>
       </c>
       <c r="M75" t="str">
-        <v>Zottman Curl</v>
+        <v>Cable Wrist Pulldown</v>
       </c>
       <c r="N75" t="str">
         <v>hyp</v>
       </c>
       <c r="O75">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="P75" t="str">
         <v/>
       </c>
       <c r="Q75" t="str">
-        <v>3 × 15</v>
+        <v/>
       </c>
       <c r="R75" t="str">
         <v/>
@@ -9673,40 +9766,40 @@
         <v/>
       </c>
       <c r="F76">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G76" t="str">
-        <v>B-d1s9</v>
+        <v>B-d1s4</v>
       </c>
       <c r="H76" t="str">
-        <v>Supersets</v>
+        <v>Regular</v>
       </c>
       <c r="I76" t="str">
         <v>Accessory</v>
       </c>
       <c r="J76" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K76" t="str">
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>kbleg</v>
+        <v>platerot</v>
       </c>
       <c r="M76" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Plate Torso Rotation</v>
       </c>
       <c r="N76" t="str">
-        <v>iso</v>
+        <v>strength</v>
       </c>
       <c r="O76">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="P76" t="str">
         <v/>
       </c>
       <c r="Q76" t="str">
-        <v>3 × 15 s hold</v>
+        <v/>
       </c>
       <c r="R76" t="str">
         <v/>
@@ -9729,16 +9822,16 @@
         <v/>
       </c>
       <c r="F77">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G77" t="str">
-        <v>B-d1s10</v>
+        <v>B-d1s5</v>
       </c>
       <c r="H77" t="str">
-        <v>Home</v>
+        <v>Regular</v>
       </c>
       <c r="I77" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J77" t="str">
         <v/>
@@ -9747,16 +9840,16 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>grip</v>
+        <v>innerthigh</v>
       </c>
       <c r="M77" t="str">
-        <v>Grip Trainer</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="N77" t="str">
         <v>strength</v>
       </c>
       <c r="O77">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="P77" t="str">
         <v/>
@@ -9765,7 +9858,7 @@
         <v/>
       </c>
       <c r="R77" t="str">
-        <v>With a grip trainer</v>
+        <v/>
       </c>
     </row>
     <row r="78">
@@ -9785,16 +9878,16 @@
         <v/>
       </c>
       <c r="F78">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G78" t="str">
-        <v>B-d1s11</v>
+        <v>B-d1s6</v>
       </c>
       <c r="H78" t="str">
-        <v>Home</v>
+        <v>Regular</v>
       </c>
       <c r="I78" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J78" t="str">
         <v/>
@@ -9803,16 +9896,16 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>canoe</v>
+        <v>outerthigh</v>
       </c>
       <c r="M78" t="str">
-        <v>Canoe Stretch</v>
+        <v>Outer Thigh Adduction</v>
       </c>
       <c r="N78" t="str">
-        <v/>
+        <v>strength</v>
       </c>
       <c r="O78">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="P78" t="str">
         <v/>
@@ -9821,7 +9914,7 @@
         <v/>
       </c>
       <c r="R78" t="str">
-        <v>With a stick or barbell</v>
+        <v/>
       </c>
     </row>
     <row r="79">
@@ -9829,10 +9922,10 @@
         <v>B</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" t="str">
-        <v>Day 2</v>
+        <v>Day 1</v>
       </c>
       <c r="D79" t="str">
         <v/>
@@ -9841,37 +9934,37 @@
         <v/>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G79" t="str">
-        <v>B-d2s1</v>
+        <v>B-d1s7</v>
       </c>
       <c r="H79" t="str">
         <v>Regular</v>
       </c>
       <c r="I79" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J79" t="str">
-        <v>either</v>
+        <v/>
       </c>
       <c r="K79" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L79" t="str">
-        <v>farmers</v>
+        <v>qlext</v>
       </c>
       <c r="M79" t="str">
-        <v>Farmers Carry</v>
+        <v>Side Lateral QL Extension</v>
       </c>
       <c r="N79" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O79">
-        <v>40</v>
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
       </c>
       <c r="P79" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q79" t="str">
         <v/>
@@ -9885,10 +9978,10 @@
         <v>B</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80" t="str">
-        <v>Day 2</v>
+        <v>Day 1</v>
       </c>
       <c r="D80" t="str">
         <v/>
@@ -9897,34 +9990,34 @@
         <v/>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G80" t="str">
-        <v>B-d2s1</v>
+        <v>B-d1s8</v>
       </c>
       <c r="H80" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I80" t="str">
         <v>Primary</v>
       </c>
       <c r="J80" t="str">
-        <v>either</v>
+        <v>superset</v>
       </c>
       <c r="K80" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L80" t="str">
-        <v>dblunge</v>
+        <v>chestpress</v>
       </c>
       <c r="M80" t="str">
-        <v>DB Lunge</v>
+        <v>Chest Press</v>
       </c>
       <c r="N80" t="str">
         <v>strength</v>
       </c>
       <c r="O80">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="P80" t="str">
         <v/>
@@ -9941,10 +10034,10 @@
         <v>B</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" t="str">
-        <v>Day 2</v>
+        <v>Day 1</v>
       </c>
       <c r="D81" t="str">
         <v/>
@@ -9953,34 +10046,34 @@
         <v/>
       </c>
       <c r="F81">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G81" t="str">
-        <v>B-d2s2</v>
+        <v>B-d1s8</v>
       </c>
       <c r="H81" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I81" t="str">
         <v>Primary</v>
       </c>
       <c r="J81" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K81" t="str">
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>ohtri</v>
+        <v>zercher</v>
       </c>
       <c r="M81" t="str">
-        <v>Overhead Tricep Extension</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="N81" t="str">
         <v>strength</v>
       </c>
       <c r="O81">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="P81" t="str">
         <v/>
@@ -9997,10 +10090,10 @@
         <v>B</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82" t="str">
-        <v>Day 2</v>
+        <v>Day 1</v>
       </c>
       <c r="D82" t="str">
         <v/>
@@ -10009,40 +10102,40 @@
         <v/>
       </c>
       <c r="F82">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G82" t="str">
-        <v>B-d2s3</v>
+        <v>B-d1s9</v>
       </c>
       <c r="H82" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I82" t="str">
         <v>Accessory</v>
       </c>
       <c r="J82" t="str">
-        <v>either</v>
+        <v>superset</v>
       </c>
       <c r="K82" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L82" t="str">
-        <v>reardelt</v>
+        <v>zottman</v>
       </c>
       <c r="M82" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Zottman Curl</v>
       </c>
       <c r="N82" t="str">
-        <v>iso</v>
+        <v>hyp</v>
       </c>
       <c r="O82">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="P82" t="str">
         <v/>
       </c>
       <c r="Q82" t="str">
-        <v>4 × 15 s per arm</v>
+        <v>3 × 15</v>
       </c>
       <c r="R82" t="str">
         <v/>
@@ -10053,10 +10146,10 @@
         <v>B</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C83" t="str">
-        <v>Day 2</v>
+        <v>Day 1</v>
       </c>
       <c r="D83" t="str">
         <v/>
@@ -10065,40 +10158,40 @@
         <v/>
       </c>
       <c r="F83">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G83" t="str">
-        <v>B-d2s3</v>
+        <v>B-d1s9</v>
       </c>
       <c r="H83" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I83" t="str">
         <v>Accessory</v>
       </c>
       <c r="J83" t="str">
-        <v>either</v>
+        <v>superset</v>
       </c>
       <c r="K83" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L83" t="str">
-        <v>facepull</v>
+        <v>kbleg</v>
       </c>
       <c r="M83" t="str">
-        <v>Face Pull</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="N83" t="str">
-        <v>strength</v>
+        <v>iso</v>
       </c>
       <c r="O83">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="P83" t="str">
         <v/>
       </c>
       <c r="Q83" t="str">
-        <v/>
+        <v>3 × 15 s hold</v>
       </c>
       <c r="R83" t="str">
         <v/>
@@ -10109,10 +10202,10 @@
         <v>B</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84" t="str">
-        <v>Day 2</v>
+        <v>Day 1</v>
       </c>
       <c r="D84" t="str">
         <v/>
@@ -10121,16 +10214,16 @@
         <v/>
       </c>
       <c r="F84">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G84" t="str">
-        <v>B-d2s4</v>
+        <v>B-d1s10</v>
       </c>
       <c r="H84" t="str">
-        <v>Regular</v>
+        <v>Home</v>
       </c>
       <c r="I84" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J84" t="str">
         <v/>
@@ -10139,16 +10232,16 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>cablecrunch</v>
+        <v>grip</v>
       </c>
       <c r="M84" t="str">
-        <v>Kneeling Cable Ab Crunch</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="N84" t="str">
         <v>strength</v>
       </c>
       <c r="O84">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="P84" t="str">
         <v/>
@@ -10157,7 +10250,7 @@
         <v/>
       </c>
       <c r="R84" t="str">
-        <v/>
+        <v>With a grip trainer</v>
       </c>
     </row>
     <row r="85">
@@ -10165,10 +10258,10 @@
         <v>B</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85" t="str">
-        <v>Day 2</v>
+        <v>Day 1</v>
       </c>
       <c r="D85" t="str">
         <v/>
@@ -10177,34 +10270,34 @@
         <v/>
       </c>
       <c r="F85">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G85" t="str">
-        <v>B-d2s5</v>
+        <v>B-d1s11</v>
       </c>
       <c r="H85" t="str">
-        <v>Supersets</v>
+        <v>Home</v>
       </c>
       <c r="I85" t="str">
-        <v>Primary</v>
+        <v/>
       </c>
       <c r="J85" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K85" t="str">
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>hipthrust</v>
+        <v>canoe</v>
       </c>
       <c r="M85" t="str">
-        <v>Hip Thrust</v>
+        <v>Canoe Stretch</v>
       </c>
       <c r="N85" t="str">
-        <v>strength</v>
+        <v/>
       </c>
       <c r="O85">
-        <v>320</v>
+        <v>10</v>
       </c>
       <c r="P85" t="str">
         <v/>
@@ -10213,7 +10306,7 @@
         <v/>
       </c>
       <c r="R85" t="str">
-        <v/>
+        <v>With a stick or barbell</v>
       </c>
     </row>
     <row r="86">
@@ -10233,40 +10326,40 @@
         <v/>
       </c>
       <c r="F86">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G86" t="str">
-        <v>B-d2s5</v>
+        <v>B-sled2</v>
       </c>
       <c r="H86" t="str">
-        <v>Supersets</v>
+        <v>Optional</v>
       </c>
       <c r="I86" t="str">
-        <v>Primary</v>
+        <v/>
       </c>
       <c r="J86" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K86" t="str">
-        <v/>
+        <v>Optional</v>
       </c>
       <c r="L86" t="str">
-        <v>chestpress</v>
+        <v>sled</v>
       </c>
       <c r="M86" t="str">
-        <v>Chest Press</v>
+        <v>Sled push → pull</v>
       </c>
       <c r="N86" t="str">
-        <v>hyp</v>
-      </c>
-      <c r="O86">
-        <v>25</v>
+        <v>exp</v>
+      </c>
+      <c r="O86" t="str">
+        <v/>
       </c>
       <c r="P86" t="str">
         <v/>
       </c>
       <c r="Q86" t="str">
-        <v/>
+        <v>1 × 3</v>
       </c>
       <c r="R86" t="str">
         <v/>
@@ -10289,28 +10382,28 @@
         <v/>
       </c>
       <c r="F87">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G87" t="str">
-        <v>B-d2s6</v>
+        <v>B-d2s1</v>
       </c>
       <c r="H87" t="str">
-        <v>Supersets</v>
+        <v>Regular</v>
       </c>
       <c r="I87" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J87" t="str">
-        <v>superset</v>
+        <v>either</v>
       </c>
       <c r="K87" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L87" t="str">
-        <v>bss</v>
+        <v>farmers</v>
       </c>
       <c r="M87" t="str">
-        <v>Bulgarian Split Squat</v>
+        <v>Farmers Carry</v>
       </c>
       <c r="N87" t="str">
         <v>strength</v>
@@ -10345,34 +10438,34 @@
         <v/>
       </c>
       <c r="F88">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G88" t="str">
-        <v>B-d2s6</v>
+        <v>B-d2s1</v>
       </c>
       <c r="H88" t="str">
-        <v>Supersets</v>
+        <v>Regular</v>
       </c>
       <c r="I88" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J88" t="str">
-        <v>superset</v>
+        <v>either</v>
       </c>
       <c r="K88" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L88" t="str">
-        <v>legcurl</v>
+        <v>dblunge</v>
       </c>
       <c r="M88" t="str">
-        <v>Prone Leg Curl</v>
+        <v>DB Lunge</v>
       </c>
       <c r="N88" t="str">
         <v>strength</v>
       </c>
       <c r="O88">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P88" t="str">
         <v/>
@@ -10401,16 +10494,16 @@
         <v/>
       </c>
       <c r="F89">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G89" t="str">
-        <v>B-d2s7</v>
+        <v>B-d2s2</v>
       </c>
       <c r="H89" t="str">
-        <v>Home</v>
+        <v>Regular</v>
       </c>
       <c r="I89" t="str">
-        <v/>
+        <v>Primary</v>
       </c>
       <c r="J89" t="str">
         <v/>
@@ -10419,16 +10512,16 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>grip</v>
+        <v>ohtri</v>
       </c>
       <c r="M89" t="str">
-        <v>Grip Trainer</v>
+        <v>Overhead Tricep Extension</v>
       </c>
       <c r="N89" t="str">
         <v>strength</v>
       </c>
       <c r="O89">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="P89" t="str">
         <v/>
@@ -10437,7 +10530,7 @@
         <v/>
       </c>
       <c r="R89" t="str">
-        <v>With a grip trainer</v>
+        <v/>
       </c>
     </row>
     <row r="90">
@@ -10457,40 +10550,40 @@
         <v/>
       </c>
       <c r="F90">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G90" t="str">
-        <v>B-d2s8</v>
+        <v>B-d2s3</v>
       </c>
       <c r="H90" t="str">
-        <v>Home</v>
+        <v>Regular</v>
       </c>
       <c r="I90" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J90" t="str">
-        <v/>
+        <v>either</v>
       </c>
       <c r="K90" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L90" t="str">
-        <v>db6</v>
+        <v>reardelt</v>
       </c>
       <c r="M90" t="str">
-        <v>DB 6 Ways</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="N90" t="str">
-        <v>strength</v>
+        <v>iso</v>
       </c>
       <c r="O90">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="P90" t="str">
         <v/>
       </c>
       <c r="Q90" t="str">
-        <v>2 × 6</v>
+        <v>4 × 15 s per arm</v>
       </c>
       <c r="R90" t="str">
         <v/>
@@ -10501,10 +10594,10 @@
         <v>B</v>
       </c>
       <c r="B91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C91" t="str">
-        <v>Day 3</v>
+        <v>Day 2</v>
       </c>
       <c r="D91" t="str">
         <v/>
@@ -10513,34 +10606,34 @@
         <v/>
       </c>
       <c r="F91">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G91" t="str">
-        <v>B-d3s1</v>
+        <v>B-d2s3</v>
       </c>
       <c r="H91" t="str">
         <v>Regular</v>
       </c>
       <c r="I91" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J91" t="str">
-        <v/>
+        <v>either</v>
       </c>
       <c r="K91" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L91" t="str">
-        <v>hack</v>
+        <v>facepull</v>
       </c>
       <c r="M91" t="str">
-        <v>Hack Squat</v>
+        <v>Face Pull</v>
       </c>
       <c r="N91" t="str">
-        <v>hyp</v>
+        <v>strength</v>
       </c>
       <c r="O91">
-        <v>270</v>
+        <v>30</v>
       </c>
       <c r="P91" t="str">
         <v/>
@@ -10549,7 +10642,7 @@
         <v/>
       </c>
       <c r="R91" t="str">
-        <v>Feet low on the plate, narrow stance for quads</v>
+        <v/>
       </c>
     </row>
     <row r="92">
@@ -10557,10 +10650,10 @@
         <v>B</v>
       </c>
       <c r="B92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C92" t="str">
-        <v>Day 3</v>
+        <v>Day 2</v>
       </c>
       <c r="D92" t="str">
         <v/>
@@ -10569,16 +10662,16 @@
         <v/>
       </c>
       <c r="F92">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G92" t="str">
-        <v>B-d3s2</v>
+        <v>B-d2s4</v>
       </c>
       <c r="H92" t="str">
         <v>Regular</v>
       </c>
       <c r="I92" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J92" t="str">
         <v/>
@@ -10587,16 +10680,16 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>latpdbi</v>
+        <v>cablecrunch</v>
       </c>
       <c r="M92" t="str">
-        <v>Lat Pulldown</v>
+        <v>Kneeling Cable Ab Crunch</v>
       </c>
       <c r="N92" t="str">
-        <v>hyp</v>
+        <v>strength</v>
       </c>
       <c r="O92">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="P92" t="str">
         <v/>
@@ -10613,10 +10706,10 @@
         <v>B</v>
       </c>
       <c r="B93">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C93" t="str">
-        <v>Day 3</v>
+        <v>Day 2</v>
       </c>
       <c r="D93" t="str">
         <v/>
@@ -10625,34 +10718,34 @@
         <v/>
       </c>
       <c r="F93">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G93" t="str">
-        <v>B-d3s3</v>
+        <v>B-d2s5</v>
       </c>
       <c r="H93" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I93" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J93" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K93" t="str">
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>wristpd</v>
+        <v>hipthrust</v>
       </c>
       <c r="M93" t="str">
-        <v>Cable Wrist Pulldown</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="N93" t="str">
-        <v>hyp</v>
+        <v>strength</v>
       </c>
       <c r="O93">
-        <v>33</v>
+        <v>320</v>
       </c>
       <c r="P93" t="str">
         <v/>
@@ -10669,10 +10762,10 @@
         <v>B</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C94" t="str">
-        <v>Day 3</v>
+        <v>Day 2</v>
       </c>
       <c r="D94" t="str">
         <v/>
@@ -10681,34 +10774,34 @@
         <v/>
       </c>
       <c r="F94">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G94" t="str">
-        <v>B-d3s4</v>
+        <v>B-d2s5</v>
       </c>
       <c r="H94" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I94" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J94" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K94" t="str">
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>platerot</v>
+        <v>chestpress</v>
       </c>
       <c r="M94" t="str">
-        <v>Plate Torso Rotation</v>
+        <v>Chest Press</v>
       </c>
       <c r="N94" t="str">
-        <v>strength</v>
+        <v>hyp</v>
       </c>
       <c r="O94">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="P94" t="str">
         <v/>
@@ -10725,10 +10818,10 @@
         <v>B</v>
       </c>
       <c r="B95">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C95" t="str">
-        <v>Day 3</v>
+        <v>Day 2</v>
       </c>
       <c r="D95" t="str">
         <v/>
@@ -10737,40 +10830,40 @@
         <v/>
       </c>
       <c r="F95">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G95" t="str">
-        <v>B-d3s5</v>
+        <v>B-d2s6</v>
       </c>
       <c r="H95" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I95" t="str">
         <v>Accessory</v>
       </c>
       <c r="J95" t="str">
-        <v>either</v>
+        <v>superset</v>
       </c>
       <c r="K95" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L95" t="str">
-        <v>reardelt</v>
+        <v>bss</v>
       </c>
       <c r="M95" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Bulgarian Split Squat</v>
       </c>
       <c r="N95" t="str">
-        <v>iso</v>
+        <v>strength</v>
       </c>
       <c r="O95">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P95" t="str">
         <v/>
       </c>
       <c r="Q95" t="str">
-        <v>4 × 15 s per arm</v>
+        <v/>
       </c>
       <c r="R95" t="str">
         <v/>
@@ -10781,10 +10874,10 @@
         <v>B</v>
       </c>
       <c r="B96">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C96" t="str">
-        <v>Day 3</v>
+        <v>Day 2</v>
       </c>
       <c r="D96" t="str">
         <v/>
@@ -10793,34 +10886,34 @@
         <v/>
       </c>
       <c r="F96">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G96" t="str">
-        <v>B-d3s5</v>
+        <v>B-d2s6</v>
       </c>
       <c r="H96" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I96" t="str">
         <v>Accessory</v>
       </c>
       <c r="J96" t="str">
-        <v>either</v>
+        <v>superset</v>
       </c>
       <c r="K96" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L96" t="str">
-        <v>facepull</v>
+        <v>legcurl</v>
       </c>
       <c r="M96" t="str">
-        <v>Face Pull</v>
+        <v>Prone Leg Curl</v>
       </c>
       <c r="N96" t="str">
         <v>strength</v>
       </c>
       <c r="O96">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="P96" t="str">
         <v/>
@@ -10837,10 +10930,10 @@
         <v>B</v>
       </c>
       <c r="B97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C97" t="str">
-        <v>Day 3</v>
+        <v>Day 2</v>
       </c>
       <c r="D97" t="str">
         <v/>
@@ -10849,43 +10942,43 @@
         <v/>
       </c>
       <c r="F97">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G97" t="str">
-        <v>B-d3s6</v>
+        <v>B-d2s7</v>
       </c>
       <c r="H97" t="str">
-        <v>Supersets</v>
+        <v>Home</v>
       </c>
       <c r="I97" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J97" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K97" t="str">
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>cablepunch</v>
+        <v>grip</v>
       </c>
       <c r="M97" t="str">
-        <v>Cable Punch ISO hold</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="N97" t="str">
-        <v>iso</v>
+        <v>strength</v>
       </c>
       <c r="O97">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="P97" t="str">
         <v/>
       </c>
       <c r="Q97" t="str">
-        <v>4 × 30 s hold</v>
+        <v/>
       </c>
       <c r="R97" t="str">
-        <v/>
+        <v>With a grip trainer</v>
       </c>
     </row>
     <row r="98">
@@ -10893,10 +10986,10 @@
         <v>B</v>
       </c>
       <c r="B98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C98" t="str">
-        <v>Day 3</v>
+        <v>Day 2</v>
       </c>
       <c r="D98" t="str">
         <v/>
@@ -10905,40 +10998,40 @@
         <v/>
       </c>
       <c r="F98">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G98" t="str">
-        <v>B-d3s6</v>
+        <v>B-d2s8</v>
       </c>
       <c r="H98" t="str">
-        <v>Supersets</v>
+        <v>Home</v>
       </c>
       <c r="I98" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J98" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K98" t="str">
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>cablerow</v>
+        <v>db6</v>
       </c>
       <c r="M98" t="str">
-        <v>Explosive Unilateral Cable Row</v>
+        <v>DB 6 Ways</v>
       </c>
       <c r="N98" t="str">
-        <v>exp</v>
+        <v>strength</v>
       </c>
       <c r="O98">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="P98" t="str">
         <v/>
       </c>
       <c r="Q98" t="str">
-        <v/>
+        <v>2 × 6</v>
       </c>
       <c r="R98" t="str">
         <v/>
@@ -10961,13 +11054,13 @@
         <v/>
       </c>
       <c r="F99">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G99" t="str">
-        <v>B-d3s7</v>
+        <v>B-sled3</v>
       </c>
       <c r="H99" t="str">
-        <v>Home</v>
+        <v>Optional</v>
       </c>
       <c r="I99" t="str">
         <v/>
@@ -10976,28 +11069,28 @@
         <v/>
       </c>
       <c r="K99" t="str">
-        <v/>
+        <v>Optional</v>
       </c>
       <c r="L99" t="str">
-        <v>grip</v>
+        <v>sled</v>
       </c>
       <c r="M99" t="str">
-        <v>Grip Trainer</v>
+        <v>Sled push → pull</v>
       </c>
       <c r="N99" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O99">
-        <v>200</v>
+        <v>exp</v>
+      </c>
+      <c r="O99" t="str">
+        <v/>
       </c>
       <c r="P99" t="str">
         <v/>
       </c>
       <c r="Q99" t="str">
-        <v/>
+        <v>1 × 3</v>
       </c>
       <c r="R99" t="str">
-        <v>With a grip trainer</v>
+        <v/>
       </c>
     </row>
     <row r="100">
@@ -11017,16 +11110,16 @@
         <v/>
       </c>
       <c r="F100">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G100" t="str">
-        <v>B-d3s8</v>
+        <v>B-d3s1</v>
       </c>
       <c r="H100" t="str">
-        <v>Home</v>
+        <v>Regular</v>
       </c>
       <c r="I100" t="str">
-        <v/>
+        <v>Primary</v>
       </c>
       <c r="J100" t="str">
         <v/>
@@ -11035,16 +11128,16 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>deskbands</v>
+        <v>hack</v>
       </c>
       <c r="M100" t="str">
-        <v>Desk Bands</v>
+        <v>Hack Squat</v>
       </c>
       <c r="N100" t="str">
-        <v/>
-      </c>
-      <c r="O100" t="str">
-        <v/>
+        <v>hyp</v>
+      </c>
+      <c r="O100">
+        <v>270</v>
       </c>
       <c r="P100" t="str">
         <v/>
@@ -11053,7 +11146,7 @@
         <v/>
       </c>
       <c r="R100" t="str">
-        <v>With a resistance band</v>
+        <v>Feet low on the plate, narrow stance for quads</v>
       </c>
     </row>
     <row r="101">
@@ -11061,10 +11154,10 @@
         <v>B</v>
       </c>
       <c r="B101">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C101" t="str">
-        <v>Day 4</v>
+        <v>Day 3</v>
       </c>
       <c r="D101" t="str">
         <v/>
@@ -11073,10 +11166,10 @@
         <v/>
       </c>
       <c r="F101">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G101" t="str">
-        <v>B-d4s1</v>
+        <v>B-d3s2</v>
       </c>
       <c r="H101" t="str">
         <v>Regular</v>
@@ -11085,22 +11178,22 @@
         <v>Primary</v>
       </c>
       <c r="J101" t="str">
-        <v>either</v>
+        <v/>
       </c>
       <c r="K101" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L101" t="str">
-        <v>farmers</v>
+        <v>latpdbi</v>
       </c>
       <c r="M101" t="str">
-        <v>Farmers Carry</v>
+        <v>Lat Pulldown</v>
       </c>
       <c r="N101" t="str">
-        <v>strength</v>
+        <v>hyp</v>
       </c>
       <c r="O101">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P101" t="str">
         <v/>
@@ -11117,46 +11210,46 @@
         <v>B</v>
       </c>
       <c r="B102">
+        <v>3</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Day 3</v>
+      </c>
+      <c r="D102" t="str">
+        <v/>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102">
         <v>4</v>
       </c>
-      <c r="C102" t="str">
-        <v>Day 4</v>
-      </c>
-      <c r="D102" t="str">
-        <v/>
-      </c>
-      <c r="E102" t="str">
-        <v/>
-      </c>
-      <c r="F102">
-        <v>1</v>
-      </c>
       <c r="G102" t="str">
-        <v>B-d4s1</v>
+        <v>B-d3s3</v>
       </c>
       <c r="H102" t="str">
         <v>Regular</v>
       </c>
       <c r="I102" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J102" t="str">
-        <v>either</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>dblunge</v>
+        <v>wristpd</v>
       </c>
       <c r="M102" t="str">
-        <v>DB Lunge</v>
+        <v>Cable Wrist Pulldown</v>
       </c>
       <c r="N102" t="str">
-        <v>strength</v>
+        <v>hyp</v>
       </c>
       <c r="O102">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="P102" t="str">
         <v/>
@@ -11173,10 +11266,10 @@
         <v>B</v>
       </c>
       <c r="B103">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C103" t="str">
-        <v>Day 4</v>
+        <v>Day 3</v>
       </c>
       <c r="D103" t="str">
         <v/>
@@ -11185,10 +11278,10 @@
         <v/>
       </c>
       <c r="F103">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G103" t="str">
-        <v>B-d4s2</v>
+        <v>B-d3s4</v>
       </c>
       <c r="H103" t="str">
         <v>Regular</v>
@@ -11203,16 +11296,16 @@
         <v/>
       </c>
       <c r="L103" t="str">
-        <v>innerthigh</v>
+        <v>platerot</v>
       </c>
       <c r="M103" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Plate Torso Rotation</v>
       </c>
       <c r="N103" t="str">
         <v>strength</v>
       </c>
       <c r="O103">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="P103" t="str">
         <v/>
@@ -11229,10 +11322,10 @@
         <v>B</v>
       </c>
       <c r="B104">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C104" t="str">
-        <v>Day 4</v>
+        <v>Day 3</v>
       </c>
       <c r="D104" t="str">
         <v/>
@@ -11241,10 +11334,10 @@
         <v/>
       </c>
       <c r="F104">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G104" t="str">
-        <v>B-d4s3</v>
+        <v>B-d3s5</v>
       </c>
       <c r="H104" t="str">
         <v>Regular</v>
@@ -11253,28 +11346,28 @@
         <v>Accessory</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>either</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L104" t="str">
-        <v>outerthigh</v>
+        <v>reardelt</v>
       </c>
       <c r="M104" t="str">
-        <v>Outer Thigh Adduction</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="N104" t="str">
-        <v>strength</v>
+        <v>iso</v>
       </c>
       <c r="O104">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="P104" t="str">
         <v/>
       </c>
       <c r="Q104" t="str">
-        <v/>
+        <v>4 × 15 s per arm</v>
       </c>
       <c r="R104" t="str">
         <v/>
@@ -11285,10 +11378,10 @@
         <v>B</v>
       </c>
       <c r="B105">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C105" t="str">
-        <v>Day 4</v>
+        <v>Day 3</v>
       </c>
       <c r="D105" t="str">
         <v/>
@@ -11297,34 +11390,34 @@
         <v/>
       </c>
       <c r="F105">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G105" t="str">
-        <v>B-d4s4</v>
+        <v>B-d3s5</v>
       </c>
       <c r="H105" t="str">
-        <v>Supersets</v>
+        <v>Regular</v>
       </c>
       <c r="I105" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J105" t="str">
-        <v>superset</v>
+        <v>either</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L105" t="str">
-        <v>arnold</v>
+        <v>facepull</v>
       </c>
       <c r="M105" t="str">
-        <v>Arnold Press</v>
+        <v>Face Pull</v>
       </c>
       <c r="N105" t="str">
         <v>strength</v>
       </c>
       <c r="O105">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="P105" t="str">
         <v/>
@@ -11341,10 +11434,10 @@
         <v>B</v>
       </c>
       <c r="B106">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C106" t="str">
-        <v>Day 4</v>
+        <v>Day 3</v>
       </c>
       <c r="D106" t="str">
         <v/>
@@ -11353,16 +11446,16 @@
         <v/>
       </c>
       <c r="F106">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G106" t="str">
-        <v>B-d4s4</v>
+        <v>B-d3s6</v>
       </c>
       <c r="H106" t="str">
         <v>Supersets</v>
       </c>
       <c r="I106" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J106" t="str">
         <v>superset</v>
@@ -11371,22 +11464,22 @@
         <v/>
       </c>
       <c r="L106" t="str">
-        <v>zercher</v>
+        <v>cablepunch</v>
       </c>
       <c r="M106" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Cable Punch ISO hold</v>
       </c>
       <c r="N106" t="str">
-        <v>strength</v>
+        <v>iso</v>
       </c>
       <c r="O106">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P106" t="str">
         <v/>
       </c>
       <c r="Q106" t="str">
-        <v/>
+        <v>4 × 30 s hold</v>
       </c>
       <c r="R106" t="str">
         <v/>
@@ -11397,10 +11490,10 @@
         <v>B</v>
       </c>
       <c r="B107">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C107" t="str">
-        <v>Day 4</v>
+        <v>Day 3</v>
       </c>
       <c r="D107" t="str">
         <v/>
@@ -11409,16 +11502,16 @@
         <v/>
       </c>
       <c r="F107">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G107" t="str">
-        <v>B-d4s5</v>
+        <v>B-d3s6</v>
       </c>
       <c r="H107" t="str">
         <v>Supersets</v>
       </c>
       <c r="I107" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J107" t="str">
         <v>superset</v>
@@ -11427,16 +11520,16 @@
         <v/>
       </c>
       <c r="L107" t="str">
-        <v>hipthrust</v>
+        <v>cablerow</v>
       </c>
       <c r="M107" t="str">
-        <v>Hip Thrust</v>
+        <v>Explosive Unilateral Cable Row</v>
       </c>
       <c r="N107" t="str">
-        <v>strength</v>
+        <v>exp</v>
       </c>
       <c r="O107">
-        <v>320</v>
+        <v>30</v>
       </c>
       <c r="P107" t="str">
         <v/>
@@ -11453,10 +11546,10 @@
         <v>B</v>
       </c>
       <c r="B108">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C108" t="str">
-        <v>Day 4</v>
+        <v>Day 3</v>
       </c>
       <c r="D108" t="str">
         <v/>
@@ -11465,34 +11558,34 @@
         <v/>
       </c>
       <c r="F108">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G108" t="str">
-        <v>B-d4s5</v>
+        <v>B-d3s7</v>
       </c>
       <c r="H108" t="str">
-        <v>Supersets</v>
+        <v>Home</v>
       </c>
       <c r="I108" t="str">
-        <v>Primary</v>
+        <v/>
       </c>
       <c r="J108" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K108" t="str">
         <v/>
       </c>
       <c r="L108" t="str">
-        <v>chestpress</v>
+        <v>grip</v>
       </c>
       <c r="M108" t="str">
-        <v>Chest Press</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="N108" t="str">
-        <v>hyp</v>
+        <v>strength</v>
       </c>
       <c r="O108">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="P108" t="str">
         <v/>
@@ -11501,7 +11594,7 @@
         <v/>
       </c>
       <c r="R108" t="str">
-        <v/>
+        <v>With a grip trainer</v>
       </c>
     </row>
     <row r="109">
@@ -11509,10 +11602,10 @@
         <v>B</v>
       </c>
       <c r="B109">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C109" t="str">
-        <v>Day 4</v>
+        <v>Day 3</v>
       </c>
       <c r="D109" t="str">
         <v/>
@@ -11521,34 +11614,34 @@
         <v/>
       </c>
       <c r="F109">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G109" t="str">
-        <v>B-d4s6</v>
+        <v>B-d3s8</v>
       </c>
       <c r="H109" t="str">
-        <v>Supersets</v>
+        <v>Home</v>
       </c>
       <c r="I109" t="str">
-        <v>Primary</v>
+        <v/>
       </c>
       <c r="J109" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K109" t="str">
         <v/>
       </c>
       <c r="L109" t="str">
-        <v>bss</v>
+        <v>deskbands</v>
       </c>
       <c r="M109" t="str">
-        <v>Bulgarian Split Squat</v>
+        <v>Desk Bands</v>
       </c>
       <c r="N109" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O109">
-        <v>40</v>
+        <v/>
+      </c>
+      <c r="O109" t="str">
+        <v/>
       </c>
       <c r="P109" t="str">
         <v/>
@@ -11557,7 +11650,7 @@
         <v/>
       </c>
       <c r="R109" t="str">
-        <v/>
+        <v>With a resistance band</v>
       </c>
     </row>
     <row r="110">
@@ -11577,40 +11670,40 @@
         <v/>
       </c>
       <c r="F110">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G110" t="str">
-        <v>B-d4s6</v>
+        <v>B-sled4</v>
       </c>
       <c r="H110" t="str">
-        <v>Supersets</v>
+        <v>Optional</v>
       </c>
       <c r="I110" t="str">
-        <v>Primary</v>
+        <v/>
       </c>
       <c r="J110" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>Optional</v>
       </c>
       <c r="L110" t="str">
-        <v>legcurl</v>
+        <v>sled</v>
       </c>
       <c r="M110" t="str">
-        <v>Prone Leg Curl</v>
+        <v>Sled push → pull</v>
       </c>
       <c r="N110" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O110">
-        <v>50</v>
+        <v>exp</v>
+      </c>
+      <c r="O110" t="str">
+        <v/>
       </c>
       <c r="P110" t="str">
         <v/>
       </c>
       <c r="Q110" t="str">
-        <v/>
+        <v>1 × 3</v>
       </c>
       <c r="R110" t="str">
         <v/>
@@ -11633,40 +11726,40 @@
         <v/>
       </c>
       <c r="F111">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G111" t="str">
-        <v>B-d4s7</v>
+        <v>B-d4s1</v>
       </c>
       <c r="H111" t="str">
-        <v>Supersets</v>
+        <v>Regular</v>
       </c>
       <c r="I111" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J111" t="str">
-        <v>superset</v>
+        <v>either</v>
       </c>
       <c r="K111" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L111" t="str">
-        <v>zottman</v>
+        <v>farmers</v>
       </c>
       <c r="M111" t="str">
-        <v>Zottman Curl</v>
+        <v>Farmers Carry</v>
       </c>
       <c r="N111" t="str">
-        <v>hyp</v>
+        <v>strength</v>
       </c>
       <c r="O111">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="P111" t="str">
         <v/>
       </c>
       <c r="Q111" t="str">
-        <v>3 × 15</v>
+        <v/>
       </c>
       <c r="R111" t="str">
         <v/>
@@ -11689,40 +11782,40 @@
         <v/>
       </c>
       <c r="F112">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G112" t="str">
-        <v>B-d4s7</v>
+        <v>B-d4s1</v>
       </c>
       <c r="H112" t="str">
-        <v>Supersets</v>
+        <v>Regular</v>
       </c>
       <c r="I112" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J112" t="str">
-        <v>superset</v>
+        <v>either</v>
       </c>
       <c r="K112" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L112" t="str">
-        <v>kbleg</v>
+        <v>dblunge</v>
       </c>
       <c r="M112" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>DB Lunge</v>
       </c>
       <c r="N112" t="str">
-        <v>iso</v>
+        <v>strength</v>
       </c>
       <c r="O112">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="P112" t="str">
         <v/>
       </c>
       <c r="Q112" t="str">
-        <v>3 × 15 s hold</v>
+        <v/>
       </c>
       <c r="R112" t="str">
         <v/>
@@ -11745,16 +11838,16 @@
         <v/>
       </c>
       <c r="F113">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G113" t="str">
-        <v>B-d4s8</v>
+        <v>B-d4s2</v>
       </c>
       <c r="H113" t="str">
-        <v>Home</v>
+        <v>Regular</v>
       </c>
       <c r="I113" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J113" t="str">
         <v/>
@@ -11763,16 +11856,16 @@
         <v/>
       </c>
       <c r="L113" t="str">
-        <v>grip</v>
+        <v>innerthigh</v>
       </c>
       <c r="M113" t="str">
-        <v>Grip Trainer</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="N113" t="str">
         <v>strength</v>
       </c>
       <c r="O113">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="P113" t="str">
         <v/>
@@ -11781,7 +11874,7 @@
         <v/>
       </c>
       <c r="R113" t="str">
-        <v>With a grip trainer</v>
+        <v/>
       </c>
     </row>
     <row r="114">
@@ -11801,16 +11894,16 @@
         <v/>
       </c>
       <c r="F114">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G114" t="str">
-        <v>B-d4s9</v>
+        <v>B-d4s3</v>
       </c>
       <c r="H114" t="str">
-        <v>Home</v>
+        <v>Regular</v>
       </c>
       <c r="I114" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J114" t="str">
         <v/>
@@ -11819,16 +11912,16 @@
         <v/>
       </c>
       <c r="L114" t="str">
-        <v>deskbands</v>
+        <v>outerthigh</v>
       </c>
       <c r="M114" t="str">
-        <v>Desk Bands</v>
+        <v>Outer Thigh Adduction</v>
       </c>
       <c r="N114" t="str">
-        <v/>
-      </c>
-      <c r="O114" t="str">
-        <v/>
+        <v>strength</v>
+      </c>
+      <c r="O114">
+        <v>160</v>
       </c>
       <c r="P114" t="str">
         <v/>
@@ -11837,7 +11930,7 @@
         <v/>
       </c>
       <c r="R114" t="str">
-        <v>With a resistance band</v>
+        <v/>
       </c>
     </row>
     <row r="115">
@@ -11845,46 +11938,46 @@
         <v>B</v>
       </c>
       <c r="B115">
+        <v>4</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D115" t="str">
+        <v/>
+      </c>
+      <c r="E115" t="str">
+        <v/>
+      </c>
+      <c r="F115">
         <v>5</v>
       </c>
-      <c r="C115" t="str">
-        <v>Day 5</v>
-      </c>
-      <c r="D115" t="str">
-        <v/>
-      </c>
-      <c r="E115" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="F115">
-        <v>1</v>
-      </c>
       <c r="G115" t="str">
-        <v>B-d5s1</v>
+        <v>B-d4s4</v>
       </c>
       <c r="H115" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I115" t="str">
-        <v/>
+        <v>Primary</v>
       </c>
       <c r="J115" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K115" t="str">
         <v/>
       </c>
       <c r="L115" t="str">
-        <v>cablecrunch</v>
+        <v>arnold</v>
       </c>
       <c r="M115" t="str">
-        <v>Kneeling Cable Ab Crunch</v>
+        <v>Arnold Press</v>
       </c>
       <c r="N115" t="str">
         <v>strength</v>
       </c>
       <c r="O115">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="P115" t="str">
         <v/>
@@ -11901,43 +11994,43 @@
         <v>B</v>
       </c>
       <c r="B116">
+        <v>4</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Day 4</v>
+      </c>
+      <c r="D116" t="str">
+        <v/>
+      </c>
+      <c r="E116" t="str">
+        <v/>
+      </c>
+      <c r="F116">
         <v>5</v>
       </c>
-      <c r="C116" t="str">
-        <v>Day 5</v>
-      </c>
-      <c r="D116" t="str">
-        <v/>
-      </c>
-      <c r="E116" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="F116">
-        <v>2</v>
-      </c>
       <c r="G116" t="str">
-        <v>B-d5s3</v>
+        <v>B-d4s4</v>
       </c>
       <c r="H116" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I116" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J116" t="str">
-        <v>either</v>
+        <v>superset</v>
       </c>
       <c r="K116" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L116" t="str">
-        <v>reardelt</v>
+        <v>zercher</v>
       </c>
       <c r="M116" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="N116" t="str">
-        <v>iso</v>
+        <v>strength</v>
       </c>
       <c r="O116">
         <v>50</v>
@@ -11946,7 +12039,7 @@
         <v/>
       </c>
       <c r="Q116" t="str">
-        <v>4 × 15 s per arm</v>
+        <v/>
       </c>
       <c r="R116" t="str">
         <v/>
@@ -11957,46 +12050,46 @@
         <v>B</v>
       </c>
       <c r="B117">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C117" t="str">
-        <v>Day 5</v>
+        <v>Day 4</v>
       </c>
       <c r="D117" t="str">
         <v/>
       </c>
       <c r="E117" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="F117">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G117" t="str">
-        <v>B-d5s3</v>
+        <v>B-d4s5</v>
       </c>
       <c r="H117" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I117" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J117" t="str">
-        <v>either</v>
+        <v>superset</v>
       </c>
       <c r="K117" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L117" t="str">
-        <v>facepull</v>
+        <v>hipthrust</v>
       </c>
       <c r="M117" t="str">
-        <v>Face Pull</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="N117" t="str">
         <v>strength</v>
       </c>
       <c r="O117">
-        <v>30</v>
+        <v>320</v>
       </c>
       <c r="P117" t="str">
         <v/>
@@ -12013,49 +12106,49 @@
         <v>B</v>
       </c>
       <c r="B118">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C118" t="str">
-        <v>Day 5</v>
+        <v>Day 4</v>
       </c>
       <c r="D118" t="str">
         <v/>
       </c>
       <c r="E118" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="F118">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G118" t="str">
-        <v>B-d5s4</v>
+        <v>B-d4s5</v>
       </c>
       <c r="H118" t="str">
-        <v>Plyometric</v>
+        <v>Supersets</v>
       </c>
       <c r="I118" t="str">
-        <v/>
+        <v>Primary</v>
       </c>
       <c r="J118" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K118" t="str">
         <v/>
       </c>
       <c r="L118" t="str">
-        <v>trxpike</v>
+        <v>chestpress</v>
       </c>
       <c r="M118" t="str">
-        <v>TRX Pike Push-Up</v>
+        <v>Chest Press</v>
       </c>
       <c r="N118" t="str">
-        <v>exp</v>
-      </c>
-      <c r="O118" t="str">
-        <v/>
+        <v>hyp</v>
+      </c>
+      <c r="O118">
+        <v>25</v>
       </c>
       <c r="P118" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q118" t="str">
         <v/>
@@ -12069,49 +12162,49 @@
         <v>B</v>
       </c>
       <c r="B119">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C119" t="str">
-        <v>Day 5</v>
+        <v>Day 4</v>
       </c>
       <c r="D119" t="str">
         <v/>
       </c>
       <c r="E119" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="F119">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G119" t="str">
-        <v>B-d5s5</v>
+        <v>B-d4s6</v>
       </c>
       <c r="H119" t="str">
-        <v>Plyometric</v>
+        <v>Supersets</v>
       </c>
       <c r="I119" t="str">
-        <v/>
+        <v>Primary</v>
       </c>
       <c r="J119" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K119" t="str">
         <v/>
       </c>
       <c r="L119" t="str">
-        <v>trxrow</v>
+        <v>bss</v>
       </c>
       <c r="M119" t="str">
-        <v>TRX Wide-Grip Row</v>
+        <v>Bulgarian Split Squat</v>
       </c>
       <c r="N119" t="str">
-        <v>exp</v>
-      </c>
-      <c r="O119" t="str">
-        <v/>
+        <v>strength</v>
+      </c>
+      <c r="O119">
+        <v>40</v>
       </c>
       <c r="P119" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q119" t="str">
         <v/>
@@ -12125,46 +12218,46 @@
         <v>B</v>
       </c>
       <c r="B120">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C120" t="str">
-        <v>Day 5</v>
+        <v>Day 4</v>
       </c>
       <c r="D120" t="str">
         <v/>
       </c>
       <c r="E120" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="F120">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G120" t="str">
-        <v>B-d5s6</v>
+        <v>B-d4s6</v>
       </c>
       <c r="H120" t="str">
-        <v>Plyometric</v>
+        <v>Supersets</v>
       </c>
       <c r="I120" t="str">
-        <v/>
+        <v>Primary</v>
       </c>
       <c r="J120" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K120" t="str">
         <v/>
       </c>
       <c r="L120" t="str">
-        <v>medball</v>
+        <v>legcurl</v>
       </c>
       <c r="M120" t="str">
-        <v>Med Ball Rotational Scoop</v>
+        <v>Prone Leg Curl</v>
       </c>
       <c r="N120" t="str">
-        <v>exp</v>
-      </c>
-      <c r="O120" t="str">
-        <v/>
+        <v>strength</v>
+      </c>
+      <c r="O120">
+        <v>50</v>
       </c>
       <c r="P120" t="str">
         <v/>
@@ -12181,52 +12274,52 @@
         <v>B</v>
       </c>
       <c r="B121">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C121" t="str">
-        <v>Day 5</v>
+        <v>Day 4</v>
       </c>
       <c r="D121" t="str">
         <v/>
       </c>
       <c r="E121" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="F121">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G121" t="str">
-        <v>B-d5s7</v>
+        <v>B-d4s7</v>
       </c>
       <c r="H121" t="str">
-        <v>Plyometric</v>
+        <v>Supersets</v>
       </c>
       <c r="I121" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J121" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K121" t="str">
         <v/>
       </c>
       <c r="L121" t="str">
-        <v>latwall</v>
+        <v>zottman</v>
       </c>
       <c r="M121" t="str">
-        <v>Lateral Wall Push</v>
+        <v>Zottman Curl</v>
       </c>
       <c r="N121" t="str">
-        <v>exp</v>
-      </c>
-      <c r="O121" t="str">
-        <v/>
+        <v>hyp</v>
+      </c>
+      <c r="O121">
+        <v>15</v>
       </c>
       <c r="P121" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q121" t="str">
-        <v/>
+        <v>3 × 15</v>
       </c>
       <c r="R121" t="str">
         <v/>
@@ -12237,52 +12330,52 @@
         <v>B</v>
       </c>
       <c r="B122">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C122" t="str">
-        <v>Day 5</v>
+        <v>Day 4</v>
       </c>
       <c r="D122" t="str">
         <v/>
       </c>
       <c r="E122" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="F122">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G122" t="str">
-        <v>B-d5s8</v>
+        <v>B-d4s7</v>
       </c>
       <c r="H122" t="str">
-        <v>Home</v>
+        <v>Supersets</v>
       </c>
       <c r="I122" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J122" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K122" t="str">
         <v/>
       </c>
       <c r="L122" t="str">
-        <v>db6</v>
+        <v>kbleg</v>
       </c>
       <c r="M122" t="str">
-        <v>DB 6 Ways</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="N122" t="str">
-        <v>strength</v>
+        <v>iso</v>
       </c>
       <c r="O122">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P122" t="str">
         <v/>
       </c>
       <c r="Q122" t="str">
-        <v>2 × 6</v>
+        <v>3 × 15 s hold</v>
       </c>
       <c r="R122" t="str">
         <v/>
@@ -12293,22 +12386,22 @@
         <v>B</v>
       </c>
       <c r="B123">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C123" t="str">
-        <v>Day 5</v>
+        <v>Day 4</v>
       </c>
       <c r="D123" t="str">
         <v/>
       </c>
       <c r="E123" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="F123">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G123" t="str">
-        <v>B-d5s9</v>
+        <v>B-d4s8</v>
       </c>
       <c r="H123" t="str">
         <v>Home</v>
@@ -12323,16 +12416,16 @@
         <v/>
       </c>
       <c r="L123" t="str">
-        <v>spinal</v>
+        <v>grip</v>
       </c>
       <c r="M123" t="str">
-        <v>Spinal Waves</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="N123" t="str">
-        <v>mob</v>
-      </c>
-      <c r="O123" t="str">
-        <v/>
+        <v>strength</v>
+      </c>
+      <c r="O123">
+        <v>200</v>
       </c>
       <c r="P123" t="str">
         <v/>
@@ -12341,7 +12434,7 @@
         <v/>
       </c>
       <c r="R123" t="str">
-        <v>Standing, no equipment</v>
+        <v>With a grip trainer</v>
       </c>
     </row>
     <row r="124">
@@ -12349,10 +12442,10 @@
         <v>B</v>
       </c>
       <c r="B124">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C124" t="str">
-        <v>Day 6</v>
+        <v>Day 4</v>
       </c>
       <c r="D124" t="str">
         <v/>
@@ -12361,13 +12454,13 @@
         <v/>
       </c>
       <c r="F124">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G124" t="str">
-        <v>B-d6s1</v>
+        <v>B-d4s9</v>
       </c>
       <c r="H124" t="str">
-        <v>Plyometric</v>
+        <v>Home</v>
       </c>
       <c r="I124" t="str">
         <v/>
@@ -12379,25 +12472,25 @@
         <v/>
       </c>
       <c r="L124" t="str">
-        <v>pogo</v>
+        <v>deskbands</v>
       </c>
       <c r="M124" t="str">
-        <v>Pogo Hops</v>
+        <v>Desk Bands</v>
       </c>
       <c r="N124" t="str">
-        <v>exp</v>
+        <v/>
       </c>
       <c r="O124" t="str">
         <v/>
       </c>
       <c r="P124" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q124" t="str">
-        <v>3 × 10</v>
+        <v/>
       </c>
       <c r="R124" t="str">
-        <v/>
+        <v>With a resistance band</v>
       </c>
     </row>
     <row r="125">
@@ -12405,25 +12498,25 @@
         <v>B</v>
       </c>
       <c r="B125">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C125" t="str">
-        <v>Day 6</v>
+        <v>Day 5</v>
       </c>
       <c r="D125" t="str">
         <v/>
       </c>
       <c r="E125" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="F125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G125" t="str">
-        <v>B-d6s2</v>
+        <v>B-sled5</v>
       </c>
       <c r="H125" t="str">
-        <v>Plyometric</v>
+        <v>Optional</v>
       </c>
       <c r="I125" t="str">
         <v/>
@@ -12432,13 +12525,13 @@
         <v/>
       </c>
       <c r="K125" t="str">
-        <v/>
+        <v>Optional</v>
       </c>
       <c r="L125" t="str">
-        <v>skater</v>
+        <v>sled</v>
       </c>
       <c r="M125" t="str">
-        <v>Lateral Bound / Skater Hop with Stick</v>
+        <v>Sled push → pull</v>
       </c>
       <c r="N125" t="str">
         <v>exp</v>
@@ -12447,10 +12540,10 @@
         <v/>
       </c>
       <c r="P125" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q125" t="str">
-        <v>3 × 5, hold 3 s</v>
+        <v>1 × 3</v>
       </c>
       <c r="R125" t="str">
         <v/>
@@ -12461,25 +12554,25 @@
         <v>B</v>
       </c>
       <c r="B126">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C126" t="str">
-        <v>Day 6</v>
+        <v>Day 5</v>
       </c>
       <c r="D126" t="str">
         <v/>
       </c>
       <c r="E126" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="F126">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G126" t="str">
-        <v>B-d6s3</v>
+        <v>B-d5s1</v>
       </c>
       <c r="H126" t="str">
-        <v>Plyometric</v>
+        <v>Regular</v>
       </c>
       <c r="I126" t="str">
         <v/>
@@ -12491,25 +12584,25 @@
         <v/>
       </c>
       <c r="L126" t="str">
-        <v>splitjump</v>
+        <v>cablecrunch</v>
       </c>
       <c r="M126" t="str">
-        <v>Split Squat Jumps</v>
+        <v>Kneeling Cable Ab Crunch</v>
       </c>
       <c r="N126" t="str">
-        <v>exp</v>
-      </c>
-      <c r="O126" t="str">
-        <v/>
+        <v>strength</v>
+      </c>
+      <c r="O126">
+        <v>60</v>
       </c>
       <c r="P126" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q126" t="str">
-        <v>3 × 5</v>
+        <v/>
       </c>
       <c r="R126" t="str">
-        <v>Vertical drive, soft landings</v>
+        <v/>
       </c>
     </row>
     <row r="127">
@@ -12517,55 +12610,55 @@
         <v>B</v>
       </c>
       <c r="B127">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C127" t="str">
-        <v>Day 6</v>
+        <v>Day 5</v>
       </c>
       <c r="D127" t="str">
         <v/>
       </c>
       <c r="E127" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="F127">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G127" t="str">
-        <v>B-d6s4</v>
+        <v>B-d5s3</v>
       </c>
       <c r="H127" t="str">
-        <v>Plyometric</v>
+        <v>Regular</v>
       </c>
       <c r="I127" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J127" t="str">
-        <v/>
+        <v>either</v>
       </c>
       <c r="K127" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L127" t="str">
-        <v>depthcombo</v>
+        <v>reardelt</v>
       </c>
       <c r="M127" t="str">
-        <v>Depth Drop → Broad Jump → Box Jump</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="N127" t="str">
-        <v>exp</v>
-      </c>
-      <c r="O127" t="str">
-        <v/>
+        <v>iso</v>
+      </c>
+      <c r="O127">
+        <v>50</v>
       </c>
       <c r="P127" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q127" t="str">
-        <v>4 × 5</v>
+        <v>4 × 15 s per arm</v>
       </c>
       <c r="R127" t="str">
-        <v>Controlled landings</v>
+        <v/>
       </c>
     </row>
     <row r="128">
@@ -12573,46 +12666,46 @@
         <v>B</v>
       </c>
       <c r="B128">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C128" t="str">
-        <v>Day 6</v>
+        <v>Day 5</v>
       </c>
       <c r="D128" t="str">
         <v/>
       </c>
       <c r="E128" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="F128">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G128" t="str">
-        <v>B-d6s5</v>
+        <v>B-d5s3</v>
       </c>
       <c r="H128" t="str">
-        <v>Supersets</v>
+        <v>Regular</v>
       </c>
       <c r="I128" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J128" t="str">
-        <v>superset</v>
+        <v>either</v>
       </c>
       <c r="K128" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L128" t="str">
-        <v>arnold</v>
+        <v>facepull</v>
       </c>
       <c r="M128" t="str">
-        <v>Arnold Press</v>
+        <v>Face Pull</v>
       </c>
       <c r="N128" t="str">
         <v>strength</v>
       </c>
       <c r="O128">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="P128" t="str">
         <v/>
@@ -12629,49 +12722,49 @@
         <v>B</v>
       </c>
       <c r="B129">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C129" t="str">
-        <v>Day 6</v>
+        <v>Day 5</v>
       </c>
       <c r="D129" t="str">
         <v/>
       </c>
       <c r="E129" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="F129">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G129" t="str">
-        <v>B-d6s5</v>
+        <v>B-d5s4</v>
       </c>
       <c r="H129" t="str">
-        <v>Supersets</v>
+        <v>Plyometric</v>
       </c>
       <c r="I129" t="str">
-        <v>Primary</v>
+        <v/>
       </c>
       <c r="J129" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K129" t="str">
         <v/>
       </c>
       <c r="L129" t="str">
-        <v>zercher</v>
+        <v>trxpike</v>
       </c>
       <c r="M129" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>TRX Pike Push-Up</v>
       </c>
       <c r="N129" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O129">
-        <v>50</v>
+        <v>exp</v>
+      </c>
+      <c r="O129" t="str">
+        <v/>
       </c>
       <c r="P129" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q129" t="str">
         <v/>
@@ -12685,52 +12778,52 @@
         <v>B</v>
       </c>
       <c r="B130">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C130" t="str">
-        <v>Day 6</v>
+        <v>Day 5</v>
       </c>
       <c r="D130" t="str">
         <v/>
       </c>
       <c r="E130" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="F130">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G130" t="str">
-        <v>B-d6s6</v>
+        <v>B-d5s5</v>
       </c>
       <c r="H130" t="str">
-        <v>Supersets</v>
+        <v>Plyometric</v>
       </c>
       <c r="I130" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J130" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K130" t="str">
         <v/>
       </c>
       <c r="L130" t="str">
-        <v>cablepunch</v>
+        <v>trxrow</v>
       </c>
       <c r="M130" t="str">
-        <v>Cable Punch ISO hold</v>
+        <v>TRX Wide-Grip Row</v>
       </c>
       <c r="N130" t="str">
-        <v>iso</v>
-      </c>
-      <c r="O130">
-        <v>30</v>
+        <v>exp</v>
+      </c>
+      <c r="O130" t="str">
+        <v/>
       </c>
       <c r="P130" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q130" t="str">
-        <v>4 × 30 s hold</v>
+        <v/>
       </c>
       <c r="R130" t="str">
         <v/>
@@ -12741,46 +12834,46 @@
         <v>B</v>
       </c>
       <c r="B131">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C131" t="str">
-        <v>Day 6</v>
+        <v>Day 5</v>
       </c>
       <c r="D131" t="str">
         <v/>
       </c>
       <c r="E131" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="F131">
         <v>6</v>
       </c>
       <c r="G131" t="str">
-        <v>B-d6s6</v>
+        <v>B-d5s6</v>
       </c>
       <c r="H131" t="str">
-        <v>Supersets</v>
+        <v>Plyometric</v>
       </c>
       <c r="I131" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J131" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K131" t="str">
         <v/>
       </c>
       <c r="L131" t="str">
-        <v>cablerow</v>
+        <v>medball</v>
       </c>
       <c r="M131" t="str">
-        <v>Explosive Unilateral Cable Row</v>
+        <v>Med Ball Rotational Scoop</v>
       </c>
       <c r="N131" t="str">
         <v>exp</v>
       </c>
-      <c r="O131">
-        <v>30</v>
+      <c r="O131" t="str">
+        <v/>
       </c>
       <c r="P131" t="str">
         <v/>
@@ -12797,25 +12890,25 @@
         <v>B</v>
       </c>
       <c r="B132">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C132" t="str">
-        <v>Day 6</v>
+        <v>Day 5</v>
       </c>
       <c r="D132" t="str">
         <v/>
       </c>
       <c r="E132" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="F132">
         <v>7</v>
       </c>
       <c r="G132" t="str">
-        <v>B-d5s2</v>
+        <v>B-d5s7</v>
       </c>
       <c r="H132" t="str">
-        <v>Regular</v>
+        <v>Plyometric</v>
       </c>
       <c r="I132" t="str">
         <v/>
@@ -12827,19 +12920,19 @@
         <v/>
       </c>
       <c r="L132" t="str">
-        <v>clean-jerk-overhead-press</v>
+        <v>latwall</v>
       </c>
       <c r="M132" t="str">
-        <v>Clean Jerk &amp; Overhead Press</v>
+        <v>Lateral Wall Push</v>
       </c>
       <c r="N132" t="str">
         <v>exp</v>
       </c>
-      <c r="O132">
-        <v>20</v>
+      <c r="O132" t="str">
+        <v/>
       </c>
       <c r="P132" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q132" t="str">
         <v/>
@@ -12853,61 +12946,733 @@
         <v>B</v>
       </c>
       <c r="B133">
+        <v>5</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D133" t="str">
+        <v/>
+      </c>
+      <c r="E133" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F133">
+        <v>8</v>
+      </c>
+      <c r="G133" t="str">
+        <v>B-d5s8</v>
+      </c>
+      <c r="H133" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I133" t="str">
+        <v/>
+      </c>
+      <c r="J133" t="str">
+        <v/>
+      </c>
+      <c r="K133" t="str">
+        <v/>
+      </c>
+      <c r="L133" t="str">
+        <v>db6</v>
+      </c>
+      <c r="M133" t="str">
+        <v>DB 6 Ways</v>
+      </c>
+      <c r="N133" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O133">
+        <v>10</v>
+      </c>
+      <c r="P133" t="str">
+        <v/>
+      </c>
+      <c r="Q133" t="str">
+        <v>2 × 6</v>
+      </c>
+      <c r="R133" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>B</v>
+      </c>
+      <c r="B134">
+        <v>5</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Day 5</v>
+      </c>
+      <c r="D134" t="str">
+        <v/>
+      </c>
+      <c r="E134" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="F134">
+        <v>9</v>
+      </c>
+      <c r="G134" t="str">
+        <v>B-d5s9</v>
+      </c>
+      <c r="H134" t="str">
+        <v>Home</v>
+      </c>
+      <c r="I134" t="str">
+        <v/>
+      </c>
+      <c r="J134" t="str">
+        <v/>
+      </c>
+      <c r="K134" t="str">
+        <v/>
+      </c>
+      <c r="L134" t="str">
+        <v>spinal</v>
+      </c>
+      <c r="M134" t="str">
+        <v>Spinal Waves</v>
+      </c>
+      <c r="N134" t="str">
+        <v>mob</v>
+      </c>
+      <c r="O134" t="str">
+        <v/>
+      </c>
+      <c r="P134" t="str">
+        <v/>
+      </c>
+      <c r="Q134" t="str">
+        <v/>
+      </c>
+      <c r="R134" t="str">
+        <v>Standing, no equipment</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>B</v>
+      </c>
+      <c r="B135">
+        <v>6</v>
+      </c>
+      <c r="C135" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D135" t="str">
+        <v/>
+      </c>
+      <c r="E135" t="str">
+        <v/>
+      </c>
+      <c r="F135">
+        <v>1</v>
+      </c>
+      <c r="G135" t="str">
+        <v>B-sled6</v>
+      </c>
+      <c r="H135" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="I135" t="str">
+        <v/>
+      </c>
+      <c r="J135" t="str">
+        <v/>
+      </c>
+      <c r="K135" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="L135" t="str">
+        <v>sled</v>
+      </c>
+      <c r="M135" t="str">
+        <v>Sled push → pull</v>
+      </c>
+      <c r="N135" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O135" t="str">
+        <v/>
+      </c>
+      <c r="P135" t="str">
+        <v/>
+      </c>
+      <c r="Q135" t="str">
+        <v>1 × 3</v>
+      </c>
+      <c r="R135" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>B</v>
+      </c>
+      <c r="B136">
+        <v>6</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D136" t="str">
+        <v/>
+      </c>
+      <c r="E136" t="str">
+        <v/>
+      </c>
+      <c r="F136">
+        <v>2</v>
+      </c>
+      <c r="G136" t="str">
+        <v>B-d6s1</v>
+      </c>
+      <c r="H136" t="str">
+        <v>Plyometric</v>
+      </c>
+      <c r="I136" t="str">
+        <v/>
+      </c>
+      <c r="J136" t="str">
+        <v/>
+      </c>
+      <c r="K136" t="str">
+        <v/>
+      </c>
+      <c r="L136" t="str">
+        <v>pogo</v>
+      </c>
+      <c r="M136" t="str">
+        <v>Pogo Hops</v>
+      </c>
+      <c r="N136" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O136" t="str">
+        <v/>
+      </c>
+      <c r="P136" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q136" t="str">
+        <v>3 × 10</v>
+      </c>
+      <c r="R136" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>B</v>
+      </c>
+      <c r="B137">
+        <v>6</v>
+      </c>
+      <c r="C137" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D137" t="str">
+        <v/>
+      </c>
+      <c r="E137" t="str">
+        <v/>
+      </c>
+      <c r="F137">
+        <v>3</v>
+      </c>
+      <c r="G137" t="str">
+        <v>B-d6s2</v>
+      </c>
+      <c r="H137" t="str">
+        <v>Plyometric</v>
+      </c>
+      <c r="I137" t="str">
+        <v/>
+      </c>
+      <c r="J137" t="str">
+        <v/>
+      </c>
+      <c r="K137" t="str">
+        <v/>
+      </c>
+      <c r="L137" t="str">
+        <v>skater</v>
+      </c>
+      <c r="M137" t="str">
+        <v>Lateral Bound / Skater Hop with Stick</v>
+      </c>
+      <c r="N137" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O137" t="str">
+        <v/>
+      </c>
+      <c r="P137" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q137" t="str">
+        <v>3 × 5, hold 3 s</v>
+      </c>
+      <c r="R137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>B</v>
+      </c>
+      <c r="B138">
+        <v>6</v>
+      </c>
+      <c r="C138" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D138" t="str">
+        <v/>
+      </c>
+      <c r="E138" t="str">
+        <v/>
+      </c>
+      <c r="F138">
+        <v>4</v>
+      </c>
+      <c r="G138" t="str">
+        <v>B-d6s3</v>
+      </c>
+      <c r="H138" t="str">
+        <v>Plyometric</v>
+      </c>
+      <c r="I138" t="str">
+        <v/>
+      </c>
+      <c r="J138" t="str">
+        <v/>
+      </c>
+      <c r="K138" t="str">
+        <v/>
+      </c>
+      <c r="L138" t="str">
+        <v>splitjump</v>
+      </c>
+      <c r="M138" t="str">
+        <v>Split Squat Jumps</v>
+      </c>
+      <c r="N138" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O138" t="str">
+        <v/>
+      </c>
+      <c r="P138" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q138" t="str">
+        <v>3 × 5</v>
+      </c>
+      <c r="R138" t="str">
+        <v>Vertical drive, soft landings</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>B</v>
+      </c>
+      <c r="B139">
+        <v>6</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D139" t="str">
+        <v/>
+      </c>
+      <c r="E139" t="str">
+        <v/>
+      </c>
+      <c r="F139">
+        <v>5</v>
+      </c>
+      <c r="G139" t="str">
+        <v>B-d6s4</v>
+      </c>
+      <c r="H139" t="str">
+        <v>Plyometric</v>
+      </c>
+      <c r="I139" t="str">
+        <v/>
+      </c>
+      <c r="J139" t="str">
+        <v/>
+      </c>
+      <c r="K139" t="str">
+        <v/>
+      </c>
+      <c r="L139" t="str">
+        <v>depthcombo</v>
+      </c>
+      <c r="M139" t="str">
+        <v>Depth Drop → Broad Jump → Box Jump</v>
+      </c>
+      <c r="N139" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O139" t="str">
+        <v/>
+      </c>
+      <c r="P139" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Q139" t="str">
+        <v>4 × 5</v>
+      </c>
+      <c r="R139" t="str">
+        <v>Controlled landings</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>B</v>
+      </c>
+      <c r="B140">
+        <v>6</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D140" t="str">
+        <v/>
+      </c>
+      <c r="E140" t="str">
+        <v/>
+      </c>
+      <c r="F140">
+        <v>6</v>
+      </c>
+      <c r="G140" t="str">
+        <v>B-d6s5</v>
+      </c>
+      <c r="H140" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I140" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J140" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K140" t="str">
+        <v/>
+      </c>
+      <c r="L140" t="str">
+        <v>arnold</v>
+      </c>
+      <c r="M140" t="str">
+        <v>Arnold Press</v>
+      </c>
+      <c r="N140" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O140">
+        <v>35</v>
+      </c>
+      <c r="P140" t="str">
+        <v/>
+      </c>
+      <c r="Q140" t="str">
+        <v/>
+      </c>
+      <c r="R140" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>B</v>
+      </c>
+      <c r="B141">
+        <v>6</v>
+      </c>
+      <c r="C141" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D141" t="str">
+        <v/>
+      </c>
+      <c r="E141" t="str">
+        <v/>
+      </c>
+      <c r="F141">
+        <v>6</v>
+      </c>
+      <c r="G141" t="str">
+        <v>B-d6s5</v>
+      </c>
+      <c r="H141" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I141" t="str">
+        <v>Primary</v>
+      </c>
+      <c r="J141" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K141" t="str">
+        <v/>
+      </c>
+      <c r="L141" t="str">
+        <v>zercher</v>
+      </c>
+      <c r="M141" t="str">
+        <v>Seated Zercher Good Morning</v>
+      </c>
+      <c r="N141" t="str">
+        <v>strength</v>
+      </c>
+      <c r="O141">
+        <v>50</v>
+      </c>
+      <c r="P141" t="str">
+        <v/>
+      </c>
+      <c r="Q141" t="str">
+        <v/>
+      </c>
+      <c r="R141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>B</v>
+      </c>
+      <c r="B142">
+        <v>6</v>
+      </c>
+      <c r="C142" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D142" t="str">
+        <v/>
+      </c>
+      <c r="E142" t="str">
+        <v/>
+      </c>
+      <c r="F142">
         <v>7</v>
       </c>
-      <c r="C133" t="str">
+      <c r="G142" t="str">
+        <v>B-d6s6</v>
+      </c>
+      <c r="H142" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I142" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J142" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K142" t="str">
+        <v/>
+      </c>
+      <c r="L142" t="str">
+        <v>cablepunch</v>
+      </c>
+      <c r="M142" t="str">
+        <v>Cable Punch ISO hold</v>
+      </c>
+      <c r="N142" t="str">
+        <v>iso</v>
+      </c>
+      <c r="O142">
+        <v>30</v>
+      </c>
+      <c r="P142" t="str">
+        <v/>
+      </c>
+      <c r="Q142" t="str">
+        <v>4 × 30 s hold</v>
+      </c>
+      <c r="R142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>B</v>
+      </c>
+      <c r="B143">
+        <v>6</v>
+      </c>
+      <c r="C143" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D143" t="str">
+        <v/>
+      </c>
+      <c r="E143" t="str">
+        <v/>
+      </c>
+      <c r="F143">
+        <v>7</v>
+      </c>
+      <c r="G143" t="str">
+        <v>B-d6s6</v>
+      </c>
+      <c r="H143" t="str">
+        <v>Supersets</v>
+      </c>
+      <c r="I143" t="str">
+        <v>Accessory</v>
+      </c>
+      <c r="J143" t="str">
+        <v>superset</v>
+      </c>
+      <c r="K143" t="str">
+        <v/>
+      </c>
+      <c r="L143" t="str">
+        <v>cablerow</v>
+      </c>
+      <c r="M143" t="str">
+        <v>Explosive Unilateral Cable Row</v>
+      </c>
+      <c r="N143" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O143">
+        <v>30</v>
+      </c>
+      <c r="P143" t="str">
+        <v/>
+      </c>
+      <c r="Q143" t="str">
+        <v/>
+      </c>
+      <c r="R143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>B</v>
+      </c>
+      <c r="B144">
+        <v>6</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Day 6</v>
+      </c>
+      <c r="D144" t="str">
+        <v/>
+      </c>
+      <c r="E144" t="str">
+        <v/>
+      </c>
+      <c r="F144">
+        <v>8</v>
+      </c>
+      <c r="G144" t="str">
+        <v>B-d5s2</v>
+      </c>
+      <c r="H144" t="str">
+        <v>Regular</v>
+      </c>
+      <c r="I144" t="str">
+        <v/>
+      </c>
+      <c r="J144" t="str">
+        <v/>
+      </c>
+      <c r="K144" t="str">
+        <v/>
+      </c>
+      <c r="L144" t="str">
+        <v>clean-jerk-overhead-press</v>
+      </c>
+      <c r="M144" t="str">
+        <v>Clean Jerk &amp; Overhead Press</v>
+      </c>
+      <c r="N144" t="str">
+        <v>exp</v>
+      </c>
+      <c r="O144">
+        <v>20</v>
+      </c>
+      <c r="P144" t="str">
+        <v/>
+      </c>
+      <c r="Q144" t="str">
+        <v/>
+      </c>
+      <c r="R144" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>B</v>
+      </c>
+      <c r="B145">
+        <v>7</v>
+      </c>
+      <c r="C145" t="str">
         <v>Day 7</v>
       </c>
-      <c r="D133" t="str">
-        <v/>
-      </c>
-      <c r="E133" t="str">
-        <v/>
-      </c>
-      <c r="F133" t="str">
-        <v/>
-      </c>
-      <c r="G133" t="str">
-        <v/>
-      </c>
-      <c r="H133" t="str">
-        <v/>
-      </c>
-      <c r="I133" t="str">
-        <v/>
-      </c>
-      <c r="J133" t="str">
-        <v/>
-      </c>
-      <c r="K133" t="str">
-        <v/>
-      </c>
-      <c r="L133" t="str">
-        <v/>
-      </c>
-      <c r="M133" t="str">
-        <v/>
-      </c>
-      <c r="N133" t="str">
-        <v/>
-      </c>
-      <c r="O133" t="str">
-        <v/>
-      </c>
-      <c r="P133" t="str">
-        <v/>
-      </c>
-      <c r="Q133" t="str">
-        <v/>
-      </c>
-      <c r="R133" t="str">
+      <c r="D145" t="str">
+        <v/>
+      </c>
+      <c r="E145" t="str">
+        <v/>
+      </c>
+      <c r="F145" t="str">
+        <v/>
+      </c>
+      <c r="G145" t="str">
+        <v/>
+      </c>
+      <c r="H145" t="str">
+        <v/>
+      </c>
+      <c r="I145" t="str">
+        <v/>
+      </c>
+      <c r="J145" t="str">
+        <v/>
+      </c>
+      <c r="K145" t="str">
+        <v/>
+      </c>
+      <c r="L145" t="str">
+        <v/>
+      </c>
+      <c r="M145" t="str">
+        <v/>
+      </c>
+      <c r="N145" t="str">
+        <v/>
+      </c>
+      <c r="O145" t="str">
+        <v/>
+      </c>
+      <c r="P145" t="str">
+        <v/>
+      </c>
+      <c r="Q145" t="str">
+        <v/>
+      </c>
+      <c r="R145" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R133"/>
+  <autoFilter ref="A1:R145"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R133"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R145"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -4814,7 +4814,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="B27" t="str">
-        <v>Obliques</v>
+        <v>Lower back</v>
       </c>
       <c r="C27">
         <v>4</v>
@@ -4831,7 +4831,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="B28" t="str">
-        <v>Abs</v>
+        <v>Obliques</v>
       </c>
       <c r="C28">
         <v>4</v>
@@ -4848,7 +4848,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="B29" t="str">
-        <v>Lower back</v>
+        <v>Abs</v>
       </c>
       <c r="C29">
         <v>4</v>
@@ -4882,7 +4882,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="B31" t="str">
-        <v>Chest</v>
+        <v>Rear delts</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -4899,7 +4899,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="B32" t="str">
-        <v>Rear delts</v>
+        <v>Biceps</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -4916,13 +4916,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B33" t="str">
-        <v>Biceps</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
         <v>0</v>
-      </c>
-      <c r="D33">
-        <v>4</v>
       </c>
       <c r="E33">
         <v>2</v>
@@ -4933,13 +4933,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B34" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Chest</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E34">
         <v>2</v>
@@ -5514,7 +5514,7 @@
         <v>Exported</v>
       </c>
       <c r="B41" t="str">
-        <v>2026-10-04T16:53:09.216Z</v>
+        <v>2026-10-04T17:18:01.121Z</v>
       </c>
     </row>
   </sheetData>
@@ -8425,7 +8425,7 @@
         <v>3</v>
       </c>
       <c r="G52" t="str">
-        <v>A-d5s2</v>
+        <v>A-d5s3</v>
       </c>
       <c r="H52" t="str">
         <v>Regular</v>
@@ -8440,16 +8440,16 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>dbclean</v>
+        <v>hack</v>
       </c>
       <c r="M52" t="str">
-        <v>DB Clean &amp; Jerk Press</v>
+        <v>Hack Squat</v>
       </c>
       <c r="N52" t="str">
-        <v>exp</v>
+        <v>hyp</v>
       </c>
       <c r="O52">
-        <v>20</v>
+        <v>270</v>
       </c>
       <c r="P52" t="str">
         <v/>
@@ -8458,7 +8458,7 @@
         <v/>
       </c>
       <c r="R52" t="str">
-        <v/>
+        <v>Feet low on the plate, narrow stance for quads</v>
       </c>
     </row>
     <row r="53">
@@ -8481,40 +8481,40 @@
         <v>4</v>
       </c>
       <c r="G53" t="str">
-        <v>A-d5s3</v>
+        <v>A-d5s4</v>
       </c>
       <c r="H53" t="str">
         <v>Regular</v>
       </c>
       <c r="I53" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J53" t="str">
-        <v/>
+        <v>either</v>
       </c>
       <c r="K53" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L53" t="str">
-        <v>hack</v>
+        <v>reardelt</v>
       </c>
       <c r="M53" t="str">
-        <v>Hack Squat</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="N53" t="str">
-        <v>hyp</v>
+        <v>iso</v>
       </c>
       <c r="O53">
-        <v>270</v>
+        <v>50</v>
       </c>
       <c r="P53" t="str">
         <v/>
       </c>
       <c r="Q53" t="str">
-        <v/>
+        <v>4 × 15 s per arm</v>
       </c>
       <c r="R53" t="str">
-        <v>Feet low on the plate, narrow stance for quads</v>
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -8534,7 +8534,7 @@
         <v>Yes</v>
       </c>
       <c r="F54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G54" t="str">
         <v>A-d5s4</v>
@@ -8552,22 +8552,22 @@
         <v>Whichever is free</v>
       </c>
       <c r="L54" t="str">
-        <v>reardelt</v>
+        <v>facepull</v>
       </c>
       <c r="M54" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Face Pull</v>
       </c>
       <c r="N54" t="str">
-        <v>iso</v>
+        <v>strength</v>
       </c>
       <c r="O54">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P54" t="str">
         <v/>
       </c>
       <c r="Q54" t="str">
-        <v>4 × 15 s per arm</v>
+        <v/>
       </c>
       <c r="R54" t="str">
         <v/>
@@ -8593,34 +8593,34 @@
         <v>5</v>
       </c>
       <c r="G55" t="str">
-        <v>A-d5s4</v>
+        <v>A-d5s5</v>
       </c>
       <c r="H55" t="str">
-        <v>Regular</v>
+        <v>Plyometric</v>
       </c>
       <c r="I55" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J55" t="str">
-        <v>either</v>
+        <v/>
       </c>
       <c r="K55" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L55" t="str">
-        <v>facepull</v>
+        <v>trxpike</v>
       </c>
       <c r="M55" t="str">
-        <v>Face Pull</v>
+        <v>TRX Pike Push-Up</v>
       </c>
       <c r="N55" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O55">
-        <v>30</v>
+        <v>exp</v>
+      </c>
+      <c r="O55" t="str">
+        <v/>
       </c>
       <c r="P55" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q55" t="str">
         <v/>
@@ -8649,7 +8649,7 @@
         <v>6</v>
       </c>
       <c r="G56" t="str">
-        <v>A-d5s5</v>
+        <v>A-d5s6</v>
       </c>
       <c r="H56" t="str">
         <v>Plyometric</v>
@@ -8664,10 +8664,10 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>trxpike</v>
+        <v>trxrow</v>
       </c>
       <c r="M56" t="str">
-        <v>TRX Pike Push-Up</v>
+        <v>TRX Wide-Grip Row</v>
       </c>
       <c r="N56" t="str">
         <v>exp</v>
@@ -8705,7 +8705,7 @@
         <v>7</v>
       </c>
       <c r="G57" t="str">
-        <v>A-d5s6</v>
+        <v>A-d5s7</v>
       </c>
       <c r="H57" t="str">
         <v>Plyometric</v>
@@ -8720,10 +8720,10 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>trxrow</v>
+        <v>medball</v>
       </c>
       <c r="M57" t="str">
-        <v>TRX Wide-Grip Row</v>
+        <v>Med Ball Rotational Scoop</v>
       </c>
       <c r="N57" t="str">
         <v>exp</v>
@@ -8732,7 +8732,7 @@
         <v/>
       </c>
       <c r="P57" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q57" t="str">
         <v/>
@@ -8761,7 +8761,7 @@
         <v>8</v>
       </c>
       <c r="G58" t="str">
-        <v>A-d5s7</v>
+        <v>A-d5s8</v>
       </c>
       <c r="H58" t="str">
         <v>Plyometric</v>
@@ -8776,10 +8776,10 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>medball</v>
+        <v>latwall</v>
       </c>
       <c r="M58" t="str">
-        <v>Med Ball Rotational Scoop</v>
+        <v>Lateral Wall Push</v>
       </c>
       <c r="N58" t="str">
         <v>exp</v>
@@ -8788,7 +8788,7 @@
         <v/>
       </c>
       <c r="P58" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q58" t="str">
         <v/>
@@ -8817,10 +8817,10 @@
         <v>9</v>
       </c>
       <c r="G59" t="str">
-        <v>A-d5s8</v>
+        <v>A-d5s9</v>
       </c>
       <c r="H59" t="str">
-        <v>Plyometric</v>
+        <v>Home</v>
       </c>
       <c r="I59" t="str">
         <v/>
@@ -8832,22 +8832,22 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>latwall</v>
+        <v>db6</v>
       </c>
       <c r="M59" t="str">
-        <v>Lateral Wall Push</v>
+        <v>DB 6 Ways</v>
       </c>
       <c r="N59" t="str">
-        <v>exp</v>
-      </c>
-      <c r="O59" t="str">
-        <v/>
+        <v>strength</v>
+      </c>
+      <c r="O59">
+        <v>10</v>
       </c>
       <c r="P59" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q59" t="str">
-        <v/>
+        <v>2 × 6</v>
       </c>
       <c r="R59" t="str">
         <v/>
@@ -8873,7 +8873,7 @@
         <v>10</v>
       </c>
       <c r="G60" t="str">
-        <v>A-d5s9</v>
+        <v>A-d5s10</v>
       </c>
       <c r="H60" t="str">
         <v>Home</v>
@@ -8888,22 +8888,22 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>db6</v>
+        <v>spinal</v>
       </c>
       <c r="M60" t="str">
-        <v>DB 6 Ways</v>
+        <v>Spinal Waves</v>
       </c>
       <c r="N60" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O60">
-        <v>10</v>
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
       </c>
       <c r="P60" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q60" t="str">
-        <v>2 × 6</v>
+        <v/>
       </c>
       <c r="R60" t="str">
         <v/>
@@ -8914,25 +8914,25 @@
         <v>A</v>
       </c>
       <c r="B61">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C61" t="str">
-        <v>Day 5</v>
+        <v>Day 6</v>
       </c>
       <c r="D61" t="str">
         <v/>
       </c>
       <c r="E61" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="F61">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G61" t="str">
-        <v>A-d5s10</v>
+        <v>A-sled6</v>
       </c>
       <c r="H61" t="str">
-        <v>Home</v>
+        <v>Optional</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -8941,25 +8941,25 @@
         <v/>
       </c>
       <c r="K61" t="str">
-        <v/>
+        <v>Optional</v>
       </c>
       <c r="L61" t="str">
-        <v>spinal</v>
+        <v>sledlat</v>
       </c>
       <c r="M61" t="str">
-        <v>Spinal Waves</v>
+        <v>Sled push → lateral pull</v>
       </c>
       <c r="N61" t="str">
-        <v/>
+        <v>exp</v>
       </c>
       <c r="O61" t="str">
         <v/>
       </c>
       <c r="P61" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q61" t="str">
-        <v/>
+        <v>1 × 3</v>
       </c>
       <c r="R61" t="str">
         <v/>
@@ -8982,13 +8982,13 @@
         <v/>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62" t="str">
-        <v>A-sled6</v>
+        <v>A-d6s1</v>
       </c>
       <c r="H62" t="str">
-        <v>Optional</v>
+        <v>Plyometric</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -8997,13 +8997,13 @@
         <v/>
       </c>
       <c r="K62" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="L62" t="str">
-        <v>sledlat</v>
+        <v>pogo</v>
       </c>
       <c r="M62" t="str">
-        <v>Sled push → lateral pull</v>
+        <v>Pogo Hops</v>
       </c>
       <c r="N62" t="str">
         <v>exp</v>
@@ -9012,10 +9012,10 @@
         <v/>
       </c>
       <c r="P62" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q62" t="str">
-        <v>1 × 3</v>
+        <v>3 × 10</v>
       </c>
       <c r="R62" t="str">
         <v/>
@@ -9038,10 +9038,10 @@
         <v/>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G63" t="str">
-        <v>A-d6s1</v>
+        <v>A-d6s2</v>
       </c>
       <c r="H63" t="str">
         <v>Plyometric</v>
@@ -9056,10 +9056,10 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>pogo</v>
+        <v>skater</v>
       </c>
       <c r="M63" t="str">
-        <v>Pogo Hops</v>
+        <v>Lateral Bound / Skater Hop with Stick</v>
       </c>
       <c r="N63" t="str">
         <v>exp</v>
@@ -9071,7 +9071,7 @@
         <v>Yes</v>
       </c>
       <c r="Q63" t="str">
-        <v>3 × 10</v>
+        <v>3 × 5, hold 3 s</v>
       </c>
       <c r="R63" t="str">
         <v/>
@@ -9094,10 +9094,10 @@
         <v/>
       </c>
       <c r="F64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="str">
-        <v>A-d6s2</v>
+        <v>A-d6s3</v>
       </c>
       <c r="H64" t="str">
         <v>Plyometric</v>
@@ -9112,10 +9112,10 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>skater</v>
+        <v>splitjump</v>
       </c>
       <c r="M64" t="str">
-        <v>Lateral Bound / Skater Hop with Stick</v>
+        <v>Split Squat Jumps</v>
       </c>
       <c r="N64" t="str">
         <v>exp</v>
@@ -9127,10 +9127,10 @@
         <v>Yes</v>
       </c>
       <c r="Q64" t="str">
-        <v>3 × 5, hold 3 s</v>
+        <v>3 × 5</v>
       </c>
       <c r="R64" t="str">
-        <v/>
+        <v>Vertical drive, soft landings</v>
       </c>
     </row>
     <row r="65">
@@ -9150,10 +9150,10 @@
         <v/>
       </c>
       <c r="F65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G65" t="str">
-        <v>A-d6s3</v>
+        <v>A-d6s4</v>
       </c>
       <c r="H65" t="str">
         <v>Plyometric</v>
@@ -9168,10 +9168,10 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>splitjump</v>
+        <v>depthcombo</v>
       </c>
       <c r="M65" t="str">
-        <v>Split Squat Jumps</v>
+        <v>Depth Drop → Broad Jump → Box Jump</v>
       </c>
       <c r="N65" t="str">
         <v>exp</v>
@@ -9183,10 +9183,10 @@
         <v>Yes</v>
       </c>
       <c r="Q65" t="str">
-        <v>3 × 5</v>
+        <v>4 × 5</v>
       </c>
       <c r="R65" t="str">
-        <v>Vertical drive, soft landings</v>
+        <v>Controlled landings</v>
       </c>
     </row>
     <row r="66">
@@ -9206,43 +9206,43 @@
         <v/>
       </c>
       <c r="F66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G66" t="str">
-        <v>A-d6s4</v>
+        <v>A-d6s5</v>
       </c>
       <c r="H66" t="str">
-        <v>Plyometric</v>
+        <v>Supersets</v>
       </c>
       <c r="I66" t="str">
-        <v/>
+        <v>Primary</v>
       </c>
       <c r="J66" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K66" t="str">
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>depthcombo</v>
+        <v>arnold</v>
       </c>
       <c r="M66" t="str">
-        <v>Depth Drop → Broad Jump → Box Jump</v>
+        <v>Arnold Press</v>
       </c>
       <c r="N66" t="str">
-        <v>exp</v>
-      </c>
-      <c r="O66" t="str">
-        <v/>
+        <v>strength</v>
+      </c>
+      <c r="O66">
+        <v>35</v>
       </c>
       <c r="P66" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q66" t="str">
-        <v>4 × 5</v>
+        <v/>
       </c>
       <c r="R66" t="str">
-        <v>Controlled landings</v>
+        <v/>
       </c>
     </row>
     <row r="67">
@@ -9280,16 +9280,16 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>arnold</v>
+        <v>zercher</v>
       </c>
       <c r="M67" t="str">
-        <v>Arnold Press</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="N67" t="str">
         <v>strength</v>
       </c>
       <c r="O67">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="P67" t="str">
         <v/>
@@ -9318,16 +9318,16 @@
         <v/>
       </c>
       <c r="F68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G68" t="str">
-        <v>A-d6s5</v>
+        <v>A-d6s6</v>
       </c>
       <c r="H68" t="str">
         <v>Supersets</v>
       </c>
       <c r="I68" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J68" t="str">
         <v>superset</v>
@@ -9336,16 +9336,16 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>zercher</v>
+        <v>pallof</v>
       </c>
       <c r="M68" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Pallof Press</v>
       </c>
       <c r="N68" t="str">
         <v>strength</v>
       </c>
       <c r="O68">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P68" t="str">
         <v/>
@@ -9392,13 +9392,13 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>pallof</v>
+        <v>cablerow</v>
       </c>
       <c r="M69" t="str">
-        <v>Pallof Press</v>
+        <v>Explosive Unilateral Cable Row</v>
       </c>
       <c r="N69" t="str">
-        <v>strength</v>
+        <v>exp</v>
       </c>
       <c r="O69">
         <v>30</v>
@@ -9430,34 +9430,34 @@
         <v/>
       </c>
       <c r="F70">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G70" t="str">
-        <v>A-d6s6</v>
+        <v>A-d5s2</v>
       </c>
       <c r="H70" t="str">
-        <v>Supersets</v>
+        <v>Regular</v>
       </c>
       <c r="I70" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J70" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K70" t="str">
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>cablerow</v>
+        <v>clean-jerk-overhead-press</v>
       </c>
       <c r="M70" t="str">
-        <v>Explosive Unilateral Cable Row</v>
+        <v>Clean Jerk &amp; Overhead Press</v>
       </c>
       <c r="N70" t="str">
         <v>exp</v>
       </c>
       <c r="O70">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P70" t="str">
         <v/>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -19,14 +19,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">Weeks!$A$1:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Body weight'!$A$1:$D$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5">Settings!$A$1:$B$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5">Settings!$A$1:$B$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">Programs!$A$1:$R$145</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Program info'!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11">Config!$A$1:$B$16</definedName>
   </definedNames>
 </workbook>
@@ -597,7 +597,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>DB Clean &amp; Jerk Press</v>
+        <v>Clean Jerk &amp; Overhead Press</v>
       </c>
       <c r="B6" t="str">
         <v>Explosive</v>
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D88"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.83203125" customWidth="1"/>
@@ -2049,13 +2049,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B56" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C56" t="str">
-        <v>A-d3s2</v>
-      </c>
-      <c r="D56">
-        <v>2</v>
+        <v>A-sled1</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="57">
@@ -2063,13 +2063,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B57" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C57" t="str">
-        <v>A-d3s3</v>
-      </c>
-      <c r="D57">
-        <v>2</v>
+        <v>A-sled2</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="58">
@@ -2077,13 +2077,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B58" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C58" t="str">
-        <v>A-d2s4</v>
-      </c>
-      <c r="D58">
-        <v>3</v>
+        <v>A-sled3</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="59">
@@ -2091,13 +2091,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B59" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C59" t="str">
-        <v>A-d1s7</v>
-      </c>
-      <c r="D59">
-        <v>3</v>
+        <v>A-sled4</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="60">
@@ -2105,13 +2105,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B60" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C60" t="str">
-        <v>A-d3s6</v>
-      </c>
-      <c r="D60">
-        <v>1</v>
+        <v>A-sled5</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="61">
@@ -2122,10 +2122,10 @@
         <v>moved</v>
       </c>
       <c r="C61" t="str">
-        <v>A-d3s1</v>
+        <v>A-d3s2</v>
       </c>
       <c r="D61">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -2136,10 +2136,10 @@
         <v>moved</v>
       </c>
       <c r="C62" t="str">
-        <v>A-d4s6</v>
+        <v>A-d3s3</v>
       </c>
       <c r="D62">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -2150,10 +2150,10 @@
         <v>moved</v>
       </c>
       <c r="C63" t="str">
-        <v>A-d2s1</v>
+        <v>A-d2s4</v>
       </c>
       <c r="D63">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -2164,10 +2164,10 @@
         <v>moved</v>
       </c>
       <c r="C64" t="str">
-        <v>A-d6s5</v>
+        <v>A-d1s7</v>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -2178,10 +2178,10 @@
         <v>moved</v>
       </c>
       <c r="C65" t="str">
-        <v>A-d5s8</v>
+        <v>A-d3s6</v>
       </c>
       <c r="D65">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -2192,10 +2192,10 @@
         <v>moved</v>
       </c>
       <c r="C66" t="str">
-        <v>A-d5s7</v>
+        <v>A-d3s1</v>
       </c>
       <c r="D66">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -2206,10 +2206,10 @@
         <v>moved</v>
       </c>
       <c r="C67" t="str">
-        <v>A-d5s6</v>
+        <v>A-d4s6</v>
       </c>
       <c r="D67">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -2220,10 +2220,10 @@
         <v>moved</v>
       </c>
       <c r="C68" t="str">
-        <v>A-d5s5</v>
+        <v>A-d2s1</v>
       </c>
       <c r="D68">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -2234,10 +2234,10 @@
         <v>moved</v>
       </c>
       <c r="C69" t="str">
-        <v>A-d5s4</v>
+        <v>A-d6s5</v>
       </c>
       <c r="D69">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -2248,7 +2248,7 @@
         <v>moved</v>
       </c>
       <c r="C70" t="str">
-        <v>A-d5s2</v>
+        <v>A-d5s8</v>
       </c>
       <c r="D70">
         <v>6</v>
@@ -2262,7 +2262,7 @@
         <v>moved</v>
       </c>
       <c r="C71" t="str">
-        <v>A-d5s1</v>
+        <v>A-d5s7</v>
       </c>
       <c r="D71">
         <v>6</v>
@@ -2270,72 +2270,72 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2026-10-04</v>
+        <v>2026-09-27</v>
       </c>
       <c r="B72" t="str">
-        <v>order</v>
+        <v>moved</v>
       </c>
       <c r="C72" t="str">
-        <v/>
-      </c>
-      <c r="D72" t="str">
-        <v>6 1 2 3 4 5 7</v>
+        <v>A-d5s6</v>
+      </c>
+      <c r="D72">
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2026-10-04</v>
+        <v>2026-09-27</v>
       </c>
       <c r="B73" t="str">
-        <v>done</v>
+        <v>moved</v>
       </c>
       <c r="C73" t="str">
-        <v>B-d6s1</v>
-      </c>
-      <c r="D73" t="str">
-        <v>Yes</v>
+        <v>A-d5s5</v>
+      </c>
+      <c r="D73">
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2026-10-04</v>
+        <v>2026-09-27</v>
       </c>
       <c r="B74" t="str">
-        <v>done</v>
+        <v>moved</v>
       </c>
       <c r="C74" t="str">
-        <v>B-d6s2</v>
-      </c>
-      <c r="D74" t="str">
-        <v>Yes</v>
+        <v>A-d5s4</v>
+      </c>
+      <c r="D74">
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2026-10-04</v>
+        <v>2026-09-27</v>
       </c>
       <c r="B75" t="str">
-        <v>done</v>
+        <v>moved</v>
       </c>
       <c r="C75" t="str">
-        <v>B-d6s3</v>
-      </c>
-      <c r="D75" t="str">
-        <v>Yes</v>
+        <v>A-d5s2</v>
+      </c>
+      <c r="D75">
+        <v>6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2026-10-04</v>
+        <v>2026-09-27</v>
       </c>
       <c r="B76" t="str">
-        <v>done</v>
+        <v>moved</v>
       </c>
       <c r="C76" t="str">
-        <v>B-d6s6</v>
-      </c>
-      <c r="D76" t="str">
-        <v>Yes</v>
+        <v>A-d5s1</v>
+      </c>
+      <c r="D76">
+        <v>6</v>
       </c>
     </row>
     <row r="77">
@@ -2343,13 +2343,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B77" t="str">
-        <v>done</v>
+        <v>order</v>
       </c>
       <c r="C77" t="str">
-        <v>B-d6s4</v>
+        <v/>
       </c>
       <c r="D77" t="str">
-        <v>Yes</v>
+        <v>6 1 2 3 4 5 7</v>
       </c>
     </row>
     <row r="78">
@@ -2360,7 +2360,7 @@
         <v>done</v>
       </c>
       <c r="C78" t="str">
-        <v>B-d5s2</v>
+        <v>B-d6s1</v>
       </c>
       <c r="D78" t="str">
         <v>Yes</v>
@@ -2374,7 +2374,7 @@
         <v>done</v>
       </c>
       <c r="C79" t="str">
-        <v>B-d1s3</v>
+        <v>B-d6s2</v>
       </c>
       <c r="D79" t="str">
         <v>Yes</v>
@@ -2388,7 +2388,7 @@
         <v>done</v>
       </c>
       <c r="C80" t="str">
-        <v>B-sled6</v>
+        <v>B-d6s3</v>
       </c>
       <c r="D80" t="str">
         <v>Yes</v>
@@ -2399,10 +2399,10 @@
         <v>2026-10-04</v>
       </c>
       <c r="B81" t="str">
-        <v>skipped</v>
+        <v>done</v>
       </c>
       <c r="C81" t="str">
-        <v>B-d6s5</v>
+        <v>B-d6s6</v>
       </c>
       <c r="D81" t="str">
         <v>Yes</v>
@@ -2413,13 +2413,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B82" t="str">
-        <v>moved</v>
+        <v>done</v>
       </c>
       <c r="C82" t="str">
-        <v>B-d5s2</v>
-      </c>
-      <c r="D82">
-        <v>6</v>
+        <v>B-d6s4</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="83">
@@ -2427,19 +2427,89 @@
         <v>2026-10-04</v>
       </c>
       <c r="B83" t="str">
-        <v>moved</v>
+        <v>done</v>
       </c>
       <c r="C83" t="str">
         <v>B-d1s3</v>
       </c>
-      <c r="D83">
+      <c r="D83" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B84" t="str">
+        <v>done</v>
+      </c>
+      <c r="C84" t="str">
+        <v>B-sled6</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B85" t="str">
+        <v>done</v>
+      </c>
+      <c r="C85" t="str">
+        <v>B-d5s2</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B86" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C86" t="str">
+        <v>B-d6s5</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B87" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C87" t="str">
+        <v>B-d5s2</v>
+      </c>
+      <c r="D87">
         <v>6</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B88" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C88" t="str">
+        <v>B-d1s3</v>
+      </c>
+      <c r="D88">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D83"/>
+  <autoFilter ref="A1:D88"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D83"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D88"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2569,7 +2639,7 @@
         <v>rm</v>
       </c>
       <c r="B15" t="str">
-        <v>{"latpd":70,"wristpd":48,"platerot":30,"innerthigh":210,"chestpress":40,"zercher":80,"zottman":23,"kbleg":21,"grip":235,"canoe":13.33,"suitcase":30,"reardelt":65,"facepull":50,"legext":65,"cablecrunch":100,"hipthrust":375,"db6":20,"hack":415,"pallof":40,"cablerow":70,"arnold":40,"dbclean":45,"latpdbi":90,"outerthigh":180,"farmers":65,"dblunge":65,"ohtri":30,"bss":65,"legcurl":100,"cablepunch":50}</v>
+        <v>{"latpd":70,"wristpd":48,"platerot":30,"innerthigh":210,"chestpress":40,"zercher":80,"zottman":23,"kbleg":21,"grip":235,"canoe":13.33,"suitcase":30,"reardelt":65,"facepull":50,"legext":65,"cablecrunch":100,"hipthrust":375,"db6":20,"hack":415,"pallof":40,"cablerow":70,"arnold":40,"dbclean":45,"latpdbi":90,"outerthigh":180,"farmers":65,"dblunge":65,"ohtri":30,"bss":65,"legcurl":100,"cablepunch":50,"clean-jerk-overhead-press":45}</v>
       </c>
     </row>
     <row r="16">
@@ -3980,7 +4050,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="C30" t="str">
-        <v>DB Clean &amp; Jerk Press</v>
+        <v>Clean Jerk &amp; Overhead Press</v>
       </c>
       <c r="D30" t="str">
         <v>Explosive</v>
@@ -4004,19 +4074,19 @@
         <v>600</v>
       </c>
       <c r="K30" t="str">
-        <v>Quads, Glutes, Front delts</v>
+        <v/>
       </c>
       <c r="L30" t="str">
-        <v>Traps, Triceps, Hamstrings</v>
+        <v/>
       </c>
       <c r="M30" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N30" t="str">
         <v>B-d5s2</v>
       </c>
       <c r="O30" t="str">
-        <v>dbclean</v>
+        <v>clean-jerk-overhead-press</v>
       </c>
     </row>
     <row r="31">
@@ -4358,7 +4428,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E36"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -4698,13 +4768,13 @@
         <v>Glutes</v>
       </c>
       <c r="C20">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D20">
         <v>4</v>
       </c>
       <c r="E20">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -4715,13 +4785,13 @@
         <v>Quads</v>
       </c>
       <c r="C21">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -4769,10 +4839,10 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E24">
-        <v>6.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -4780,16 +4850,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B25" t="str">
-        <v>Front delts</v>
+        <v>Lats</v>
       </c>
       <c r="C25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="26">
@@ -4797,16 +4867,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B26" t="str">
-        <v>Lats</v>
+        <v>Lower back</v>
       </c>
       <c r="C26">
         <v>4</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -4814,7 +4884,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="B27" t="str">
-        <v>Lower back</v>
+        <v>Obliques</v>
       </c>
       <c r="C27">
         <v>4</v>
@@ -4831,7 +4901,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="B28" t="str">
-        <v>Obliques</v>
+        <v>Abs</v>
       </c>
       <c r="C28">
         <v>4</v>
@@ -4848,16 +4918,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B29" t="str">
-        <v>Abs</v>
+        <v>Outer hip (abductors)</v>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -4865,16 +4935,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B30" t="str">
-        <v>Outer hip (abductors)</v>
+        <v>Rear delts</v>
       </c>
       <c r="C30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -4882,7 +4952,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="B31" t="str">
-        <v>Rear delts</v>
+        <v>Biceps</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -4899,13 +4969,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B32" t="str">
-        <v>Biceps</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32">
         <v>0</v>
-      </c>
-      <c r="D32">
-        <v>4</v>
       </c>
       <c r="E32">
         <v>2</v>
@@ -4916,13 +4986,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B33" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Chest</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E33">
         <v>2</v>
@@ -4933,7 +5003,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="B34" t="str">
-        <v>Chest</v>
+        <v>Front delts</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -4950,7 +5020,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="B35" t="str">
-        <v>Traps</v>
+        <v>Shins</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -4967,7 +5037,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="B36" t="str">
-        <v>Triceps</v>
+        <v>Inner thigh (adductors)</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -4979,44 +5049,10 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="B37" t="str">
-        <v>Shins</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="D37">
-        <v>3</v>
-      </c>
-      <c r="E37">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="B38" t="str">
-        <v>Inner thigh (adductors)</v>
-      </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-      <c r="D38">
-        <v>3</v>
-      </c>
-      <c r="E38">
-        <v>1.5</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E38"/>
+  <autoFilter ref="A1:E36"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E36"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5069,19 +5105,19 @@
         <v>A</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D2">
         <v>26</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="H2">
         <v>26</v>
@@ -5183,7 +5219,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -5327,200 +5363,208 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>1RM: DB 6 Ways</v>
+        <v>1RM: Clean Jerk &amp; Overhead Press</v>
       </c>
       <c r="B18">
-        <v>20</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>1RM: DB Clean &amp; Jerk Press</v>
+        <v>1RM: DB 6 Ways</v>
       </c>
       <c r="B19">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>1RM: DB Lunge</v>
+        <v>1RM: DB Clean &amp; Jerk Press</v>
       </c>
       <c r="B20">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>1RM: Face Pull</v>
+        <v>1RM: DB Lunge</v>
       </c>
       <c r="B21">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>1RM: Farmers Carry</v>
+        <v>1RM: Face Pull</v>
       </c>
       <c r="B22">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>1RM: Grip Trainer</v>
+        <v>1RM: Farmers Carry</v>
       </c>
       <c r="B23">
-        <v>235</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>1RM: Hack Squat</v>
+        <v>1RM: Grip Trainer</v>
       </c>
       <c r="B24">
-        <v>415</v>
+        <v>235</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>1RM: Hip Thrust</v>
+        <v>1RM: Hack Squat</v>
       </c>
       <c r="B25">
-        <v>375</v>
+        <v>415</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>1RM: Inner Thigh Abduction</v>
+        <v>1RM: Hip Thrust</v>
       </c>
       <c r="B26">
-        <v>210</v>
+        <v>375</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>1RM: Kettlebell Leg Raise</v>
+        <v>1RM: Inner Thigh Abduction</v>
       </c>
       <c r="B27">
-        <v>21</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>1RM: Lat Pulldown, alternating single-arm</v>
+        <v>1RM: Kettlebell Leg Raise</v>
       </c>
       <c r="B28">
-        <v>70</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>1RM: Lat Pulldown</v>
+        <v>1RM: Lat Pulldown, alternating single-arm</v>
       </c>
       <c r="B29">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>1RM: Prone Leg Curl</v>
+        <v>1RM: Lat Pulldown</v>
       </c>
       <c r="B30">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>1RM: Leg Extension ISO hold</v>
+        <v>1RM: Prone Leg Curl</v>
       </c>
       <c r="B31">
-        <v>65</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>1RM: Overhead Tricep Extension</v>
+        <v>1RM: Leg Extension ISO hold</v>
       </c>
       <c r="B32">
-        <v>30</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>1RM: Outer Thigh Adduction</v>
+        <v>1RM: Overhead Tricep Extension</v>
       </c>
       <c r="B33">
-        <v>180</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>1RM: Pallof Press</v>
+        <v>1RM: Outer Thigh Adduction</v>
       </c>
       <c r="B34">
-        <v>40</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>1RM: Plate Torso Rotation</v>
+        <v>1RM: Pallof Press</v>
       </c>
       <c r="B35">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>1RM: Side Rear Delt Fly</v>
+        <v>1RM: Plate Torso Rotation</v>
       </c>
       <c r="B36">
-        <v>65</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>1RM: Suitcase Bottom-Up, single-arm</v>
+        <v>1RM: Side Rear Delt Fly</v>
       </c>
       <c r="B37">
-        <v>30</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>1RM: Cable Wrist Pulldown</v>
+        <v>1RM: Suitcase Bottom-Up, single-arm</v>
       </c>
       <c r="B38">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>1RM: Seated Zercher Good Morning</v>
+        <v>1RM: Cable Wrist Pulldown</v>
       </c>
       <c r="B39">
-        <v>80</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>1RM: Zottman Curl</v>
+        <v>1RM: Seated Zercher Good Morning</v>
       </c>
       <c r="B40">
-        <v>23</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
+        <v>1RM: Zottman Curl</v>
+      </c>
+      <c r="B41">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
         <v>Exported</v>
       </c>
-      <c r="B41" t="str">
-        <v>2026-10-04T17:18:01.121Z</v>
+      <c r="B42" t="str">
+        <v>2026-10-04T22:49:49.239Z</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B41"/>
+  <autoFilter ref="A1:B42"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B42"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -17,16 +17,16 @@
     <sheet name="Config" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">Weeks!$A$1:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Body weight'!$A$1:$D$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5">Settings!$A$1:$B$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">Programs!$A$1:$R$145</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Program info'!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$98</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11">Config!$A$1:$B$16</definedName>
   </definedNames>
 </workbook>
@@ -421,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J28"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -565,71 +565,71 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Chest Press</v>
+        <v>Canoe Stretch</v>
       </c>
       <c r="B5" t="str">
-        <v>Hypertrophy</v>
+        <v>Isometric</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-05</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-09-30</v>
+        <v>2026-10-05</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>40</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Clean Jerk &amp; Overhead Press</v>
+        <v>Chest Press</v>
       </c>
       <c r="B6" t="str">
-        <v>Explosive</v>
+        <v>Strength</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-10-04</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-05</v>
       </c>
       <c r="F6">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Depth Drop → Broad Jump → Box Jump</v>
+        <v>Clean Jerk &amp; Overhead Press</v>
       </c>
       <c r="B7" t="str">
         <v>Explosive</v>
@@ -643,25 +643,25 @@
       <c r="E7" t="str">
         <v>2026-10-04</v>
       </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v/>
-      </c>
-      <c r="J7" t="str">
-        <v/>
+      <c r="F7">
+        <v>20</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="H7">
+        <v>20</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Explosive Unilateral Cable Row</v>
+        <v>Depth Drop → Broad Jump → Box Jump</v>
       </c>
       <c r="B8" t="str">
         <v>Explosive</v>
@@ -675,121 +675,121 @@
       <c r="E8" t="str">
         <v>2026-10-04</v>
       </c>
-      <c r="F8">
-        <v>30</v>
-      </c>
-      <c r="G8">
-        <v>30</v>
-      </c>
-      <c r="H8">
-        <v>30</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>70</v>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Grip Trainer</v>
+        <v>Explosive Unilateral Cable Row</v>
       </c>
       <c r="B9" t="str">
-        <v>Strength</v>
+        <v>Explosive</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-04</v>
       </c>
       <c r="F9">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="G9">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="H9">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>235</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Hack Squat</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="B10" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-09-30</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-10-01</v>
+        <v>2026-09-28</v>
       </c>
       <c r="F10">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="G10">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H10">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>415</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Hip Thrust</v>
+        <v>Hack Squat</v>
       </c>
       <c r="B11" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-30</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-09-30</v>
+        <v>2026-10-05</v>
       </c>
       <c r="F11">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="G11">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="H11">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>375</v>
+        <v>415</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="B12" t="str">
         <v>Strength</v>
@@ -798,65 +798,65 @@
         <v>2</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E12" t="str">
         <v>2026-09-30</v>
       </c>
       <c r="F12">
-        <v>180</v>
+        <v>320</v>
       </c>
       <c r="G12">
-        <v>180</v>
+        <v>320</v>
       </c>
       <c r="H12">
-        <v>180</v>
+        <v>320</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>210</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="B13" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-27</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-30</v>
       </c>
       <c r="F13">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="G13">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="H13">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>21</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Kneeling Cable Ab Crunch</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="B14" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -868,91 +868,91 @@
         <v>2026-09-29</v>
       </c>
       <c r="F14">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="G14">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="H14">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>100</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Lat Pulldown, alternating single-arm</v>
+        <v>Kneeling Cable Ab Crunch</v>
       </c>
       <c r="B15" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="E15" t="str">
         <v>2026-09-29</v>
       </c>
       <c r="F15">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G15">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H15">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>70</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Lateral Bound / Skater Hop with Stick</v>
+        <v>Lat Pulldown</v>
       </c>
       <c r="B16" t="str">
-        <v>Explosive</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-05</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v/>
-      </c>
-      <c r="J16" t="str">
-        <v/>
+        <v>2026-10-05</v>
+      </c>
+      <c r="F16">
+        <v>45</v>
+      </c>
+      <c r="G16">
+        <v>45</v>
+      </c>
+      <c r="H16">
+        <v>45</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>90</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Leg Extension ISO hold</v>
+        <v>Lat Pulldown, alternating single-arm</v>
       </c>
       <c r="B17" t="str">
-        <v>Isometric</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -964,24 +964,24 @@
         <v>2026-09-29</v>
       </c>
       <c r="F17">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G17">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H17">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Pogo Hops</v>
+        <v>Lateral Bound / Skater Hop with Stick</v>
       </c>
       <c r="B18" t="str">
         <v>Explosive</v>
@@ -1013,19 +1013,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Leg Extension ISO hold</v>
       </c>
       <c r="B19" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-10-04</v>
+        <v>2026-09-29</v>
       </c>
       <c r="F19">
         <v>50</v>
@@ -1040,76 +1040,76 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>80</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Outer Thigh Adduction</v>
       </c>
       <c r="B20" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-09-27</v>
+        <v>2026-10-05</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-05</v>
       </c>
       <c r="F20">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="G20">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="H20">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>65</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Sled push → pull</v>
+        <v>Plate Torso Rotation</v>
       </c>
       <c r="B21" t="str">
-        <v>Explosive</v>
+        <v>Strength</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-05</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
-      <c r="G21" t="str">
-        <v/>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21" t="str">
-        <v/>
-      </c>
-      <c r="J21" t="str">
-        <v/>
+        <v>2026-10-05</v>
+      </c>
+      <c r="F21">
+        <v>10</v>
+      </c>
+      <c r="G21">
+        <v>10</v>
+      </c>
+      <c r="H21">
+        <v>10</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>30</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Split Squat Jumps</v>
+        <v>Pogo Hops</v>
       </c>
       <c r="B22" t="str">
         <v>Explosive</v>
@@ -1141,72 +1141,200 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Suitcase Bottom-Up, single-arm</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="B23" t="str">
         <v>Strength</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-27</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-05</v>
       </c>
       <c r="F23">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G23">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H23">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="J23">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Zottman Curl</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="B24" t="str">
-        <v>Hypertrophy</v>
+        <v>Isometric</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-27</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-28</v>
       </c>
       <c r="F24">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="G24">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="H24">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Sled push → pull</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Explosive</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="E25" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Split Squat Jumps</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Explosive</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="E26" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Suitcase Bottom-Up, single-arm</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="E27" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="F27">
+        <v>25</v>
+      </c>
+      <c r="G27">
+        <v>25</v>
+      </c>
+      <c r="H27">
+        <v>25</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Zottman Curl</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Hypertrophy</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="E28" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="F28">
+        <v>15</v>
+      </c>
+      <c r="G28">
+        <v>15</v>
+      </c>
+      <c r="H28">
+        <v>15</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
         <v>23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J24"/>
+  <autoFilter ref="A1:J28"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J28"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1266,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D98"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.83203125" customWidth="1"/>
@@ -2469,10 +2597,10 @@
         <v>2026-10-04</v>
       </c>
       <c r="B86" t="str">
-        <v>skipped</v>
+        <v>done</v>
       </c>
       <c r="C86" t="str">
-        <v>B-d6s5</v>
+        <v>B-d1s1</v>
       </c>
       <c r="D86" t="str">
         <v>Yes</v>
@@ -2483,13 +2611,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B87" t="str">
-        <v>moved</v>
+        <v>done</v>
       </c>
       <c r="C87" t="str">
-        <v>B-d5s2</v>
-      </c>
-      <c r="D87">
-        <v>6</v>
+        <v>B-d1s4</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="88">
@@ -2497,19 +2625,159 @@
         <v>2026-10-04</v>
       </c>
       <c r="B88" t="str">
+        <v>done</v>
+      </c>
+      <c r="C88" t="str">
+        <v>B-d1s11</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B89" t="str">
+        <v>done</v>
+      </c>
+      <c r="C89" t="str">
+        <v>B-d1s8</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B90" t="str">
+        <v>done</v>
+      </c>
+      <c r="C90" t="str">
+        <v>B-d1s2</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B91" t="str">
+        <v>done</v>
+      </c>
+      <c r="C91" t="str">
+        <v>B-d1s6</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B92" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C92" t="str">
+        <v>B-d6s5</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B93" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C93" t="str">
+        <v>B-sled1</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B94" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C94" t="str">
+        <v>B-d1s7</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B95" t="str">
         <v>moved</v>
       </c>
-      <c r="C88" t="str">
+      <c r="C95" t="str">
+        <v>B-d5s2</v>
+      </c>
+      <c r="D95">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B96" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C96" t="str">
         <v>B-d1s3</v>
       </c>
-      <c r="D88">
+      <c r="D96">
         <v>6</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B97" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C97" t="str">
+        <v>B-d1s9</v>
+      </c>
+      <c r="D97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B98" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C98" t="str">
+        <v>B-d1s5</v>
+      </c>
+      <c r="D98">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D88"/>
+  <autoFilter ref="A1:D98"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D88"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D98"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2660,7 +2928,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O44"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -4418,17 +4686,346 @@
         <v>splitjump</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Canoe Stretch</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Isometric</v>
+      </c>
+      <c r="E38">
+        <v>10</v>
+      </c>
+      <c r="F38">
+        <v>4</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38">
+        <v>15</v>
+      </c>
+      <c r="I38" t="str">
+        <v>10×15s, 10×15s, 10×15s, 10×15s</v>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v>Mobility</v>
+      </c>
+      <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
+        <v>From check-off</v>
+      </c>
+      <c r="N38" t="str">
+        <v>B-d1s11</v>
+      </c>
+      <c r="O38" t="str">
+        <v>canoe</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Chest Press</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E39">
+        <v>35</v>
+      </c>
+      <c r="F39">
+        <v>4</v>
+      </c>
+      <c r="G39">
+        <v>6</v>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v>35×6, 35×6, 35×6, 35×6</v>
+      </c>
+      <c r="J39">
+        <v>840</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Chest</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Front delts, Triceps</v>
+      </c>
+      <c r="M39" t="str">
+        <v>From check-off</v>
+      </c>
+      <c r="N39" t="str">
+        <v>B-d1s8</v>
+      </c>
+      <c r="O39" t="str">
+        <v>chestpress</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Hack Squat</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Hypertrophy</v>
+      </c>
+      <c r="E40">
+        <v>270</v>
+      </c>
+      <c r="F40">
+        <v>4</v>
+      </c>
+      <c r="G40">
+        <v>15</v>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v>270×15, 270×15, 270×15, 270×15</v>
+      </c>
+      <c r="J40">
+        <v>16200</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Quads</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Glutes, Inner thigh (adductors)</v>
+      </c>
+      <c r="M40" t="str">
+        <v>From check-off</v>
+      </c>
+      <c r="N40" t="str">
+        <v>B-d1s2</v>
+      </c>
+      <c r="O40" t="str">
+        <v>hack</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Lat Pulldown</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Hypertrophy</v>
+      </c>
+      <c r="E41">
+        <v>45</v>
+      </c>
+      <c r="F41">
+        <v>4</v>
+      </c>
+      <c r="G41">
+        <v>15</v>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v>45×15, 45×15, 45×15, 45×15</v>
+      </c>
+      <c r="J41">
+        <v>2700</v>
+      </c>
+      <c r="K41" t="str">
+        <v>Lats</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Biceps, Upper back, Rear delts</v>
+      </c>
+      <c r="M41" t="str">
+        <v>From check-off</v>
+      </c>
+      <c r="N41" t="str">
+        <v>B-d1s1</v>
+      </c>
+      <c r="O41" t="str">
+        <v>latpdbi</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Outer Thigh Adduction</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E42">
+        <v>160</v>
+      </c>
+      <c r="F42">
+        <v>4</v>
+      </c>
+      <c r="G42">
+        <v>6</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v>160×6, 160×6, 160×6, 160×6</v>
+      </c>
+      <c r="J42">
+        <v>3840</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Outer hip (abductors)</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Glutes</v>
+      </c>
+      <c r="M42" t="str">
+        <v>From check-off</v>
+      </c>
+      <c r="N42" t="str">
+        <v>B-d1s6</v>
+      </c>
+      <c r="O42" t="str">
+        <v>outerthigh</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Plate Torso Rotation</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E43">
+        <v>10</v>
+      </c>
+      <c r="F43">
+        <v>4</v>
+      </c>
+      <c r="G43">
+        <v>6</v>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v>10×6, 10×6, 10×6, 10×6</v>
+      </c>
+      <c r="J43">
+        <v>240</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Obliques</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Abs</v>
+      </c>
+      <c r="M43" t="str">
+        <v>From check-off</v>
+      </c>
+      <c r="N43" t="str">
+        <v>B-d1s4</v>
+      </c>
+      <c r="O43" t="str">
+        <v>platerot</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Seated Zercher Good Morning</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E44">
+        <v>50</v>
+      </c>
+      <c r="F44">
+        <v>4</v>
+      </c>
+      <c r="G44">
+        <v>6</v>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v>50×6, 50×6, 50×6, 50×6</v>
+      </c>
+      <c r="J44">
+        <v>1200</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Lower back</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Glutes, Hamstrings, Upper back</v>
+      </c>
+      <c r="M44" t="str">
+        <v>From check-off</v>
+      </c>
+      <c r="N44" t="str">
+        <v>B-d1s8</v>
+      </c>
+      <c r="O44" t="str">
+        <v>zercher</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O37"/>
+  <autoFilter ref="A1:O44"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O44"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -4771,10 +5368,10 @@
         <v>10</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E20">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -4785,13 +5382,13 @@
         <v>Quads</v>
       </c>
       <c r="C21">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -4799,16 +5396,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B22" t="str">
-        <v>Calves</v>
+        <v>Upper back</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E22">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="23">
@@ -4816,16 +5413,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B23" t="str">
-        <v>Upper back</v>
+        <v>Calves</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E23">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="24">
@@ -4833,16 +5430,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B24" t="str">
-        <v>Hamstrings</v>
+        <v>Lats</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="25">
@@ -4850,16 +5447,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B25" t="str">
-        <v>Lats</v>
+        <v>Obliques</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>4.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -4870,13 +5467,13 @@
         <v>Lower back</v>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -4884,16 +5481,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B27" t="str">
-        <v>Obliques</v>
+        <v>Outer hip (abductors)</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -4901,16 +5498,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B28" t="str">
-        <v>Abs</v>
+        <v>Hamstrings</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -4918,16 +5515,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B29" t="str">
-        <v>Outer hip (abductors)</v>
+        <v>Abs</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -4935,16 +5532,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B30" t="str">
-        <v>Rear delts</v>
+        <v>Chest</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D30">
         <v>4</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -4952,16 +5549,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B31" t="str">
-        <v>Biceps</v>
+        <v>Rear delts</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
+        <v>8</v>
+      </c>
+      <c r="E31">
         <v>4</v>
-      </c>
-      <c r="E31">
-        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -4969,16 +5566,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B32" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Biceps</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -4986,16 +5583,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B33" t="str">
-        <v>Chest</v>
+        <v>Front delts</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33">
+        <v>8</v>
+      </c>
+      <c r="E33">
         <v>4</v>
-      </c>
-      <c r="E33">
-        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -5003,16 +5600,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B34" t="str">
-        <v>Front delts</v>
+        <v>Inner thigh (adductors)</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="35">
@@ -5020,16 +5617,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B35" t="str">
-        <v>Shins</v>
+        <v>Triceps</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -5037,22 +5634,39 @@
         <v>2026-10-04</v>
       </c>
       <c r="B36" t="str">
-        <v>Inner thigh (adductors)</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36">
         <v>0</v>
       </c>
-      <c r="D36">
+      <c r="E36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Shins</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
         <v>3</v>
       </c>
-      <c r="E36">
+      <c r="E37">
         <v>1.5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E36"/>
+  <autoFilter ref="A1:E37"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E37"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5134,19 +5748,19 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -5558,7 +6172,7 @@
         <v>Exported</v>
       </c>
       <c r="B42" t="str">
-        <v>2026-10-04T22:49:49.239Z</v>
+        <v>2026-10-05T10:48:43.329Z</v>
       </c>
     </row>
   </sheetData>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -2827,7 +2827,7 @@
         <v>ghBackup</v>
       </c>
       <c r="B5" t="str">
-        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"jd0ayc","last":{"at":"2026-10-04T15:24:05.090Z","url":"https://github.com/jacgit18/iron-log/commit/31a63f35c5396fef9883932e703c0f0dd264248e"}}</v>
+        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"w210d7","last":{"at":"2026-10-05T10:48:46.014Z","url":"https://github.com/jacgit18/iron-log/commit/97bdc9b38051ba269c0413b769896aa3cf71c092"}}</v>
       </c>
     </row>
     <row r="6">
@@ -6172,7 +6172,7 @@
         <v>Exported</v>
       </c>
       <c r="B42" t="str">
-        <v>2026-10-05T10:48:43.329Z</v>
+        <v>2026-10-05T10:49:05.483Z</v>
       </c>
     </row>
   </sheetData>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">Programs!$A$1:$R$145</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Program info'!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$99</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11">Config!$A$1:$B$16</definedName>
   </definedNames>
 </workbook>
@@ -1394,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D98"/>
+  <dimension ref="A1:D99"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.83203125" customWidth="1"/>
@@ -2774,10 +2774,24 @@
         <v>5</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B99" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C99" t="str">
+        <v>B-d2s8</v>
+      </c>
+      <c r="D99">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D98"/>
+  <autoFilter ref="A1:D99"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D99"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5481,13 +5495,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B27" t="str">
-        <v>Outer hip (abductors)</v>
+        <v>Hamstrings</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E27">
         <v>7</v>
@@ -5498,13 +5512,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B28" t="str">
-        <v>Hamstrings</v>
+        <v>Outer hip (abductors)</v>
       </c>
       <c r="C28">
+        <v>7</v>
+      </c>
+      <c r="D28">
         <v>0</v>
-      </c>
-      <c r="D28">
-        <v>14</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -5549,7 +5563,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="B31" t="str">
-        <v>Rear delts</v>
+        <v>Front delts</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -5566,7 +5580,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="B32" t="str">
-        <v>Biceps</v>
+        <v>Rear delts</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -5583,7 +5597,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="B33" t="str">
-        <v>Front delts</v>
+        <v>Biceps</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -6172,7 +6186,7 @@
         <v>Exported</v>
       </c>
       <c r="B42" t="str">
-        <v>2026-10-05T10:49:05.483Z</v>
+        <v>2026-10-05T10:56:54.685Z</v>
       </c>
     </row>
   </sheetData>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -6186,7 +6186,7 @@
         <v>Exported</v>
       </c>
       <c r="B42" t="str">
-        <v>2026-10-05T10:56:54.685Z</v>
+        <v>2026-10-05T16:24:29.110Z</v>
       </c>
     </row>
   </sheetData>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -17,16 +17,16 @@
     <sheet name="Config" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">Weeks!$A$1:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Body weight'!$A$1:$D$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5">Settings!$A$1:$B$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">Programs!$A$1:$R$145</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Program info'!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11">Config!$A$1:$B$16</definedName>
   </definedNames>
 </workbook>
@@ -421,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -661,39 +661,39 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Depth Drop → Broad Jump → Box Jump</v>
+        <v>DB 6 Ways</v>
       </c>
       <c r="B8" t="str">
-        <v>Explosive</v>
+        <v>Strength</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-05</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v/>
-      </c>
-      <c r="J8" t="str">
-        <v/>
+        <v>2026-10-05</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Explosive Unilateral Cable Row</v>
+        <v>Depth Drop → Broad Jump → Box Jump</v>
       </c>
       <c r="B9" t="str">
         <v>Explosive</v>
@@ -707,121 +707,121 @@
       <c r="E9" t="str">
         <v>2026-10-04</v>
       </c>
-      <c r="F9">
-        <v>30</v>
-      </c>
-      <c r="G9">
-        <v>30</v>
-      </c>
-      <c r="H9">
-        <v>30</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>70</v>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Grip Trainer</v>
+        <v>Explosive Unilateral Cable Row</v>
       </c>
       <c r="B10" t="str">
-        <v>Strength</v>
+        <v>Explosive</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-04</v>
       </c>
       <c r="F10">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="G10">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="H10">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>235</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Hack Squat</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="B11" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-09-30</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E11" t="str">
         <v>2026-10-05</v>
       </c>
       <c r="F11">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="G11">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H11">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>415</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Hip Thrust</v>
+        <v>Hack Squat</v>
       </c>
       <c r="B12" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-30</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-09-30</v>
+        <v>2026-10-05</v>
       </c>
       <c r="F12">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="G12">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="H12">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>375</v>
+        <v>415</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="B13" t="str">
         <v>Strength</v>
@@ -830,65 +830,65 @@
         <v>2</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E13" t="str">
         <v>2026-09-30</v>
       </c>
       <c r="F13">
-        <v>180</v>
+        <v>320</v>
       </c>
       <c r="G13">
-        <v>180</v>
+        <v>320</v>
       </c>
       <c r="H13">
-        <v>180</v>
+        <v>320</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>210</v>
+        <v>375</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="B14" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-27</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-30</v>
       </c>
       <c r="F14">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="G14">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="H14">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>21</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Kneeling Cable Ab Crunch</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="B15" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -900,68 +900,68 @@
         <v>2026-09-29</v>
       </c>
       <c r="F15">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="G15">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="H15">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>100</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Lat Pulldown</v>
+        <v>Kneeling Cable Ab Crunch</v>
       </c>
       <c r="B16" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-10-05</v>
+        <v>2026-09-29</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-10-05</v>
+        <v>2026-09-29</v>
       </c>
       <c r="F16">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G16">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H16">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Lat Pulldown, alternating single-arm</v>
+        <v>Lat Pulldown</v>
       </c>
       <c r="B17" t="str">
         <v>Hypertrophy</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-05</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-05</v>
       </c>
       <c r="F17">
         <v>45</v>
@@ -976,108 +976,108 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Lateral Bound / Skater Hop with Stick</v>
+        <v>Lat Pulldown, alternating single-arm</v>
       </c>
       <c r="B18" t="str">
-        <v>Explosive</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-10-04</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v/>
-      </c>
-      <c r="J18" t="str">
-        <v/>
+        <v>2026-09-29</v>
+      </c>
+      <c r="F18">
+        <v>45</v>
+      </c>
+      <c r="G18">
+        <v>45</v>
+      </c>
+      <c r="H18">
+        <v>45</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>70</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Leg Extension ISO hold</v>
+        <v>Lateral Bound / Skater Hop with Stick</v>
       </c>
       <c r="B19" t="str">
-        <v>Isometric</v>
+        <v>Explosive</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-09-29</v>
-      </c>
-      <c r="F19">
-        <v>50</v>
-      </c>
-      <c r="G19">
-        <v>50</v>
-      </c>
-      <c r="H19">
-        <v>50</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>65</v>
+        <v>2026-10-04</v>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Outer Thigh Adduction</v>
+        <v>Leg Extension ISO hold</v>
       </c>
       <c r="B20" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-10-05</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-10-05</v>
+        <v>2026-09-29</v>
       </c>
       <c r="F20">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="G20">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="H20">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>180</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Plate Torso Rotation</v>
+        <v>Outer Thigh Adduction</v>
       </c>
       <c r="B21" t="str">
         <v>Strength</v>
@@ -1092,100 +1092,100 @@
         <v>2026-10-05</v>
       </c>
       <c r="F21">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="G21">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="H21">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>30</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Pogo Hops</v>
+        <v>Plate Torso Rotation</v>
       </c>
       <c r="B22" t="str">
-        <v>Explosive</v>
+        <v>Strength</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-05</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="F22" t="str">
-        <v/>
-      </c>
-      <c r="G22" t="str">
-        <v/>
-      </c>
-      <c r="H22" t="str">
-        <v/>
-      </c>
-      <c r="I22" t="str">
-        <v/>
-      </c>
-      <c r="J22" t="str">
-        <v/>
+        <v>2026-10-05</v>
+      </c>
+      <c r="F22">
+        <v>10</v>
+      </c>
+      <c r="G22">
+        <v>10</v>
+      </c>
+      <c r="H22">
+        <v>10</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Pogo Hops</v>
       </c>
       <c r="B23" t="str">
-        <v>Strength</v>
+        <v>Explosive</v>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-09-27</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-10-05</v>
-      </c>
-      <c r="F23">
-        <v>50</v>
-      </c>
-      <c r="G23">
-        <v>50</v>
-      </c>
-      <c r="H23">
-        <v>50</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>80</v>
+        <v>2026-10-04</v>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="B24" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D24" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-05</v>
       </c>
       <c r="F24">
         <v>50</v>
@@ -1200,44 +1200,44 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Sled push → pull</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="B25" t="str">
-        <v>Explosive</v>
+        <v>Isometric</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-10-04</v>
+        <v>2026-09-27</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="F25" t="str">
-        <v/>
-      </c>
-      <c r="G25" t="str">
-        <v/>
-      </c>
-      <c r="H25" t="str">
-        <v/>
-      </c>
-      <c r="I25" t="str">
-        <v/>
-      </c>
-      <c r="J25" t="str">
-        <v/>
+        <v>2026-09-28</v>
+      </c>
+      <c r="F25">
+        <v>50</v>
+      </c>
+      <c r="G25">
+        <v>50</v>
+      </c>
+      <c r="H25">
+        <v>50</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>65</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Split Squat Jumps</v>
+        <v>Sled push → pull</v>
       </c>
       <c r="B26" t="str">
         <v>Explosive</v>
@@ -1269,42 +1269,42 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Suitcase Bottom-Up, single-arm</v>
+        <v>Split Squat Jumps</v>
       </c>
       <c r="B27" t="str">
-        <v>Strength</v>
+        <v>Explosive</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-09-29</v>
-      </c>
-      <c r="F27">
-        <v>25</v>
-      </c>
-      <c r="G27">
-        <v>25</v>
-      </c>
-      <c r="H27">
-        <v>25</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>30</v>
+        <v>2026-10-04</v>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Zottman Curl</v>
+        <v>Suitcase Bottom-Up, single-arm</v>
       </c>
       <c r="B28" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1316,25 +1316,57 @@
         <v>2026-09-29</v>
       </c>
       <c r="F28">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G28">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H28">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Zottman Curl</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Hypertrophy</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="E29" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="F29">
+        <v>15</v>
+      </c>
+      <c r="G29">
+        <v>15</v>
+      </c>
+      <c r="H29">
+        <v>15</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
         <v>23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J28"/>
+  <autoFilter ref="A1:J29"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J29"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1394,7 +1426,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D101"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.83203125" customWidth="1"/>
@@ -2681,10 +2713,10 @@
         <v>2026-10-04</v>
       </c>
       <c r="B92" t="str">
-        <v>skipped</v>
+        <v>done</v>
       </c>
       <c r="C92" t="str">
-        <v>B-d6s5</v>
+        <v>B-d1s10</v>
       </c>
       <c r="D92" t="str">
         <v>Yes</v>
@@ -2695,10 +2727,10 @@
         <v>2026-10-04</v>
       </c>
       <c r="B93" t="str">
-        <v>skipped</v>
+        <v>done</v>
       </c>
       <c r="C93" t="str">
-        <v>B-sled1</v>
+        <v>B-d2s8</v>
       </c>
       <c r="D93" t="str">
         <v>Yes</v>
@@ -2712,7 +2744,7 @@
         <v>skipped</v>
       </c>
       <c r="C94" t="str">
-        <v>B-d1s7</v>
+        <v>B-d6s5</v>
       </c>
       <c r="D94" t="str">
         <v>Yes</v>
@@ -2723,13 +2755,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B95" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C95" t="str">
-        <v>B-d5s2</v>
-      </c>
-      <c r="D95">
-        <v>6</v>
+        <v>B-sled1</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="96">
@@ -2737,13 +2769,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B96" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C96" t="str">
-        <v>B-d1s3</v>
-      </c>
-      <c r="D96">
-        <v>6</v>
+        <v>B-d1s7</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="97">
@@ -2754,10 +2786,10 @@
         <v>moved</v>
       </c>
       <c r="C97" t="str">
-        <v>B-d1s9</v>
+        <v>B-d5s2</v>
       </c>
       <c r="D97">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98">
@@ -2768,10 +2800,10 @@
         <v>moved</v>
       </c>
       <c r="C98" t="str">
-        <v>B-d1s5</v>
+        <v>B-d1s3</v>
       </c>
       <c r="D98">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
@@ -2782,16 +2814,44 @@
         <v>moved</v>
       </c>
       <c r="C99" t="str">
+        <v>B-d1s9</v>
+      </c>
+      <c r="D99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B100" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C100" t="str">
+        <v>B-d1s5</v>
+      </c>
+      <c r="D100">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B101" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C101" t="str">
         <v>B-d2s8</v>
       </c>
-      <c r="D99">
+      <c r="D101">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D99"/>
+  <autoFilter ref="A1:D101"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D99"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D101"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2841,7 +2901,7 @@
         <v>ghBackup</v>
       </c>
       <c r="B5" t="str">
-        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"w210d7","last":{"at":"2026-10-05T10:48:46.014Z","url":"https://github.com/jacgit18/iron-log/commit/97bdc9b38051ba269c0413b769896aa3cf71c092"}}</v>
+        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"pwpexa","last":{"at":"2026-10-05T16:24:32.013Z","url":"https://github.com/jacgit18/iron-log/commit/73c1da16e69b595cd367f894c0821fd86b56c162"}}</v>
       </c>
     </row>
     <row r="6">
@@ -2942,7 +3002,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O46"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -4802,43 +4862,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C40" t="str">
-        <v>Hack Squat</v>
+        <v>DB 6 Ways</v>
       </c>
       <c r="D40" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E40">
-        <v>270</v>
+        <v>5</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G40">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H40" t="str">
         <v/>
       </c>
       <c r="I40" t="str">
-        <v>270×15, 270×15, 270×15, 270×15</v>
+        <v>5×6, 5×6</v>
       </c>
       <c r="J40">
-        <v>16200</v>
+        <v>60</v>
       </c>
       <c r="K40" t="str">
-        <v>Quads</v>
+        <v>Front delts, Side delts</v>
       </c>
       <c r="L40" t="str">
-        <v>Glutes, Inner thigh (adductors)</v>
+        <v/>
       </c>
       <c r="M40" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N40" t="str">
-        <v>B-d1s2</v>
+        <v>B-d2s8</v>
       </c>
       <c r="O40" t="str">
-        <v>hack</v>
+        <v>db6</v>
       </c>
     </row>
     <row r="41">
@@ -4849,43 +4909,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C41" t="str">
-        <v>Lat Pulldown</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="D41" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E41">
-        <v>45</v>
+        <v>200</v>
       </c>
       <c r="F41">
         <v>4</v>
       </c>
       <c r="G41">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H41" t="str">
         <v/>
       </c>
       <c r="I41" t="str">
-        <v>45×15, 45×15, 45×15, 45×15</v>
+        <v>200×6, 200×6, 200×6, 200×6</v>
       </c>
       <c r="J41">
-        <v>2700</v>
+        <v>4800</v>
       </c>
       <c r="K41" t="str">
-        <v>Lats</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="L41" t="str">
-        <v>Biceps, Upper back, Rear delts</v>
+        <v/>
       </c>
       <c r="M41" t="str">
         <v>From check-off</v>
       </c>
       <c r="N41" t="str">
-        <v>B-d1s1</v>
+        <v>B-d1s10</v>
       </c>
       <c r="O41" t="str">
-        <v>latpdbi</v>
+        <v>grip</v>
       </c>
     </row>
     <row r="42">
@@ -4896,43 +4956,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C42" t="str">
-        <v>Outer Thigh Adduction</v>
+        <v>Hack Squat</v>
       </c>
       <c r="D42" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E42">
-        <v>160</v>
+        <v>270</v>
       </c>
       <c r="F42">
         <v>4</v>
       </c>
       <c r="G42">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H42" t="str">
         <v/>
       </c>
       <c r="I42" t="str">
-        <v>160×6, 160×6, 160×6, 160×6</v>
+        <v>270×15, 270×15, 270×15, 270×15</v>
       </c>
       <c r="J42">
-        <v>3840</v>
+        <v>16200</v>
       </c>
       <c r="K42" t="str">
-        <v>Outer hip (abductors)</v>
+        <v>Quads</v>
       </c>
       <c r="L42" t="str">
-        <v>Glutes</v>
+        <v>Glutes, Inner thigh (adductors)</v>
       </c>
       <c r="M42" t="str">
         <v>From check-off</v>
       </c>
       <c r="N42" t="str">
-        <v>B-d1s6</v>
+        <v>B-d1s2</v>
       </c>
       <c r="O42" t="str">
-        <v>outerthigh</v>
+        <v>hack</v>
       </c>
     </row>
     <row r="43">
@@ -4943,43 +5003,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C43" t="str">
-        <v>Plate Torso Rotation</v>
+        <v>Lat Pulldown</v>
       </c>
       <c r="D43" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E43">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="F43">
         <v>4</v>
       </c>
       <c r="G43">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H43" t="str">
         <v/>
       </c>
       <c r="I43" t="str">
-        <v>10×6, 10×6, 10×6, 10×6</v>
+        <v>45×15, 45×15, 45×15, 45×15</v>
       </c>
       <c r="J43">
-        <v>240</v>
+        <v>2700</v>
       </c>
       <c r="K43" t="str">
-        <v>Obliques</v>
+        <v>Lats</v>
       </c>
       <c r="L43" t="str">
-        <v>Abs</v>
+        <v>Biceps, Upper back, Rear delts</v>
       </c>
       <c r="M43" t="str">
         <v>From check-off</v>
       </c>
       <c r="N43" t="str">
-        <v>B-d1s4</v>
+        <v>B-d1s1</v>
       </c>
       <c r="O43" t="str">
-        <v>platerot</v>
+        <v>latpdbi</v>
       </c>
     </row>
     <row r="44">
@@ -4990,13 +5050,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="C44" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Outer Thigh Adduction</v>
       </c>
       <c r="D44" t="str">
         <v>Strength</v>
       </c>
       <c r="E44">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="F44">
         <v>4</v>
@@ -5008,38 +5068,132 @@
         <v/>
       </c>
       <c r="I44" t="str">
-        <v>50×6, 50×6, 50×6, 50×6</v>
+        <v>160×6, 160×6, 160×6, 160×6</v>
       </c>
       <c r="J44">
-        <v>1200</v>
+        <v>3840</v>
       </c>
       <c r="K44" t="str">
-        <v>Lower back</v>
+        <v>Outer hip (abductors)</v>
       </c>
       <c r="L44" t="str">
-        <v>Glutes, Hamstrings, Upper back</v>
+        <v>Glutes</v>
       </c>
       <c r="M44" t="str">
         <v>From check-off</v>
       </c>
       <c r="N44" t="str">
+        <v>B-d1s6</v>
+      </c>
+      <c r="O44" t="str">
+        <v>outerthigh</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Plate Torso Rotation</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E45">
+        <v>10</v>
+      </c>
+      <c r="F45">
+        <v>4</v>
+      </c>
+      <c r="G45">
+        <v>6</v>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v>10×6, 10×6, 10×6, 10×6</v>
+      </c>
+      <c r="J45">
+        <v>240</v>
+      </c>
+      <c r="K45" t="str">
+        <v>Obliques</v>
+      </c>
+      <c r="L45" t="str">
+        <v>Abs</v>
+      </c>
+      <c r="M45" t="str">
+        <v>From check-off</v>
+      </c>
+      <c r="N45" t="str">
+        <v>B-d1s4</v>
+      </c>
+      <c r="O45" t="str">
+        <v>platerot</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2026-10-05</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Seated Zercher Good Morning</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E46">
+        <v>50</v>
+      </c>
+      <c r="F46">
+        <v>4</v>
+      </c>
+      <c r="G46">
+        <v>6</v>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v>50×6, 50×6, 50×6, 50×6</v>
+      </c>
+      <c r="J46">
+        <v>1200</v>
+      </c>
+      <c r="K46" t="str">
+        <v>Lower back</v>
+      </c>
+      <c r="L46" t="str">
+        <v>Glutes, Hamstrings, Upper back</v>
+      </c>
+      <c r="M46" t="str">
+        <v>From check-off</v>
+      </c>
+      <c r="N46" t="str">
         <v>B-d1s8</v>
       </c>
-      <c r="O44" t="str">
+      <c r="O46" t="str">
         <v>zercher</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O44"/>
+  <autoFilter ref="A1:O46"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O46"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -5495,13 +5649,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B27" t="str">
-        <v>Hamstrings</v>
+        <v>Outer hip (abductors)</v>
       </c>
       <c r="C27">
+        <v>7</v>
+      </c>
+      <c r="D27">
         <v>0</v>
-      </c>
-      <c r="D27">
-        <v>14</v>
       </c>
       <c r="E27">
         <v>7</v>
@@ -5512,13 +5666,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B28" t="str">
-        <v>Outer hip (abductors)</v>
+        <v>Hamstrings</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -5566,13 +5720,13 @@
         <v>Front delts</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D31">
         <v>8</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -5580,16 +5734,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B32" t="str">
-        <v>Rear delts</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="C32">
+        <v>6</v>
+      </c>
+      <c r="D32">
         <v>0</v>
       </c>
-      <c r="D32">
-        <v>8</v>
-      </c>
       <c r="E32">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -5597,7 +5751,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="B33" t="str">
-        <v>Biceps</v>
+        <v>Rear delts</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -5614,16 +5768,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B34" t="str">
-        <v>Inner thigh (adductors)</v>
+        <v>Biceps</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E34">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -5631,16 +5785,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B35" t="str">
-        <v>Triceps</v>
+        <v>Inner thigh (adductors)</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="36">
@@ -5648,13 +5802,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B36" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Triceps</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E36">
         <v>2</v>
@@ -5665,22 +5819,39 @@
         <v>2026-10-04</v>
       </c>
       <c r="B37" t="str">
+        <v>Side delts</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B38" t="str">
         <v>Shins</v>
       </c>
-      <c r="C37">
+      <c r="C38">
         <v>0</v>
       </c>
-      <c r="D37">
+      <c r="D38">
         <v>3</v>
       </c>
-      <c r="E37">
+      <c r="E38">
         <v>1.5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E37"/>
+  <autoFilter ref="A1:E38"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E38"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5759,10 +5930,10 @@
         <v>B</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E3">
         <v>64</v>
@@ -5771,10 +5942,10 @@
         <v>3</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -6186,7 +6357,7 @@
         <v>Exported</v>
       </c>
       <c r="B42" t="str">
-        <v>2026-10-05T16:24:29.110Z</v>
+        <v>2026-10-05T17:18:53.952Z</v>
       </c>
     </row>
   </sheetData>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -2901,7 +2901,7 @@
         <v>ghBackup</v>
       </c>
       <c r="B5" t="str">
-        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"pwpexa","last":{"at":"2026-10-05T16:24:32.013Z","url":"https://github.com/jacgit18/iron-log/commit/73c1da16e69b595cd367f894c0821fd86b56c162"}}</v>
+        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"1dsxvfk","last":{"at":"2026-10-05T17:18:56.872Z","url":"https://github.com/jacgit18/iron-log/commit/6d6d915c6bfa2e12c3d4d034bd1d6b84b4dd9190"}}</v>
       </c>
     </row>
     <row r="6">
@@ -6357,7 +6357,7 @@
         <v>Exported</v>
       </c>
       <c r="B42" t="str">
-        <v>2026-10-05T17:18:53.952Z</v>
+        <v>2026-10-05T21:43:14.827Z</v>
       </c>
     </row>
   </sheetData>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">Programs!$A$1:$R$145</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Program info'!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11">Config!$A$1:$B$16</definedName>
   </definedNames>
 </workbook>
@@ -1426,7 +1426,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D103"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.83203125" customWidth="1"/>
@@ -2503,13 +2503,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B77" t="str">
-        <v>order</v>
+        <v>rest</v>
       </c>
       <c r="C77" t="str">
         <v/>
       </c>
       <c r="D77" t="str">
-        <v>6 1 2 3 4 5 7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -2517,13 +2517,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B78" t="str">
-        <v>done</v>
+        <v>restOn</v>
       </c>
       <c r="C78" t="str">
-        <v>B-d6s1</v>
+        <v/>
       </c>
       <c r="D78" t="str">
-        <v>Yes</v>
+        <v>2026-10-06</v>
       </c>
     </row>
     <row r="79">
@@ -2531,13 +2531,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B79" t="str">
-        <v>done</v>
+        <v>order</v>
       </c>
       <c r="C79" t="str">
-        <v>B-d6s2</v>
+        <v/>
       </c>
       <c r="D79" t="str">
-        <v>Yes</v>
+        <v>6 1 2 3 4 5 7</v>
       </c>
     </row>
     <row r="80">
@@ -2548,7 +2548,7 @@
         <v>done</v>
       </c>
       <c r="C80" t="str">
-        <v>B-d6s3</v>
+        <v>B-d6s1</v>
       </c>
       <c r="D80" t="str">
         <v>Yes</v>
@@ -2562,7 +2562,7 @@
         <v>done</v>
       </c>
       <c r="C81" t="str">
-        <v>B-d6s6</v>
+        <v>B-d6s2</v>
       </c>
       <c r="D81" t="str">
         <v>Yes</v>
@@ -2576,7 +2576,7 @@
         <v>done</v>
       </c>
       <c r="C82" t="str">
-        <v>B-d6s4</v>
+        <v>B-d6s3</v>
       </c>
       <c r="D82" t="str">
         <v>Yes</v>
@@ -2590,7 +2590,7 @@
         <v>done</v>
       </c>
       <c r="C83" t="str">
-        <v>B-d1s3</v>
+        <v>B-d6s6</v>
       </c>
       <c r="D83" t="str">
         <v>Yes</v>
@@ -2604,7 +2604,7 @@
         <v>done</v>
       </c>
       <c r="C84" t="str">
-        <v>B-sled6</v>
+        <v>B-d6s4</v>
       </c>
       <c r="D84" t="str">
         <v>Yes</v>
@@ -2618,7 +2618,7 @@
         <v>done</v>
       </c>
       <c r="C85" t="str">
-        <v>B-d5s2</v>
+        <v>B-d1s3</v>
       </c>
       <c r="D85" t="str">
         <v>Yes</v>
@@ -2632,7 +2632,7 @@
         <v>done</v>
       </c>
       <c r="C86" t="str">
-        <v>B-d1s1</v>
+        <v>B-sled6</v>
       </c>
       <c r="D86" t="str">
         <v>Yes</v>
@@ -2646,7 +2646,7 @@
         <v>done</v>
       </c>
       <c r="C87" t="str">
-        <v>B-d1s4</v>
+        <v>B-d5s2</v>
       </c>
       <c r="D87" t="str">
         <v>Yes</v>
@@ -2660,7 +2660,7 @@
         <v>done</v>
       </c>
       <c r="C88" t="str">
-        <v>B-d1s11</v>
+        <v>B-d1s1</v>
       </c>
       <c r="D88" t="str">
         <v>Yes</v>
@@ -2674,7 +2674,7 @@
         <v>done</v>
       </c>
       <c r="C89" t="str">
-        <v>B-d1s8</v>
+        <v>B-d1s4</v>
       </c>
       <c r="D89" t="str">
         <v>Yes</v>
@@ -2688,7 +2688,7 @@
         <v>done</v>
       </c>
       <c r="C90" t="str">
-        <v>B-d1s2</v>
+        <v>B-d1s11</v>
       </c>
       <c r="D90" t="str">
         <v>Yes</v>
@@ -2702,7 +2702,7 @@
         <v>done</v>
       </c>
       <c r="C91" t="str">
-        <v>B-d1s6</v>
+        <v>B-d1s8</v>
       </c>
       <c r="D91" t="str">
         <v>Yes</v>
@@ -2716,7 +2716,7 @@
         <v>done</v>
       </c>
       <c r="C92" t="str">
-        <v>B-d1s10</v>
+        <v>B-d1s2</v>
       </c>
       <c r="D92" t="str">
         <v>Yes</v>
@@ -2730,7 +2730,7 @@
         <v>done</v>
       </c>
       <c r="C93" t="str">
-        <v>B-d2s8</v>
+        <v>B-d1s6</v>
       </c>
       <c r="D93" t="str">
         <v>Yes</v>
@@ -2741,10 +2741,10 @@
         <v>2026-10-04</v>
       </c>
       <c r="B94" t="str">
-        <v>skipped</v>
+        <v>done</v>
       </c>
       <c r="C94" t="str">
-        <v>B-d6s5</v>
+        <v>B-d1s10</v>
       </c>
       <c r="D94" t="str">
         <v>Yes</v>
@@ -2755,10 +2755,10 @@
         <v>2026-10-04</v>
       </c>
       <c r="B95" t="str">
-        <v>skipped</v>
+        <v>done</v>
       </c>
       <c r="C95" t="str">
-        <v>B-sled1</v>
+        <v>B-d2s8</v>
       </c>
       <c r="D95" t="str">
         <v>Yes</v>
@@ -2772,7 +2772,7 @@
         <v>skipped</v>
       </c>
       <c r="C96" t="str">
-        <v>B-d1s7</v>
+        <v>B-d6s5</v>
       </c>
       <c r="D96" t="str">
         <v>Yes</v>
@@ -2783,13 +2783,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B97" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C97" t="str">
-        <v>B-d5s2</v>
-      </c>
-      <c r="D97">
-        <v>6</v>
+        <v>B-sled1</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="98">
@@ -2797,13 +2797,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B98" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C98" t="str">
-        <v>B-d1s3</v>
-      </c>
-      <c r="D98">
-        <v>6</v>
+        <v>B-d1s7</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="99">
@@ -2814,10 +2814,10 @@
         <v>moved</v>
       </c>
       <c r="C99" t="str">
-        <v>B-d1s9</v>
+        <v>B-d5s2</v>
       </c>
       <c r="D99">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100">
@@ -2828,10 +2828,10 @@
         <v>moved</v>
       </c>
       <c r="C100" t="str">
-        <v>B-d1s5</v>
+        <v>B-d1s3</v>
       </c>
       <c r="D100">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101">
@@ -2842,16 +2842,44 @@
         <v>moved</v>
       </c>
       <c r="C101" t="str">
+        <v>B-d1s9</v>
+      </c>
+      <c r="D101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B102" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C102" t="str">
+        <v>B-d1s5</v>
+      </c>
+      <c r="D102">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B103" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C103" t="str">
         <v>B-d2s8</v>
       </c>
-      <c r="D101">
+      <c r="D103">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D101"/>
+  <autoFilter ref="A1:D103"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D103"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2901,7 +2929,7 @@
         <v>ghBackup</v>
       </c>
       <c r="B5" t="str">
-        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"1dsxvfk","last":{"at":"2026-10-05T17:18:56.872Z","url":"https://github.com/jacgit18/iron-log/commit/6d6d915c6bfa2e12c3d4d034bd1d6b84b4dd9190"}}</v>
+        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"1x46bwu","last":{"at":"2026-10-05T21:44:09.148Z","url":"https://github.com/jacgit18/iron-log/commit/289f6b650fb2b6e816ac898a7d72d8c9b8f06932"}}</v>
       </c>
     </row>
     <row r="6">
@@ -6357,7 +6385,7 @@
         <v>Exported</v>
       </c>
       <c r="B42" t="str">
-        <v>2026-10-05T21:43:14.827Z</v>
+        <v>2026-10-06T20:03:48.676Z</v>
       </c>
     </row>
   </sheetData>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -17,16 +17,16 @@
     <sheet name="Config" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">Weeks!$A$1:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Body weight'!$A$1:$D$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5">Settings!$A$1:$B$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">Programs!$A$1:$R$145</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Program info'!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11">Config!$A$1:$B$16</definedName>
   </definedNames>
 </workbook>
@@ -421,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J32"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -600,25 +600,25 @@
         <v>Chest Press</v>
       </c>
       <c r="B6" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="str">
         <v>2026-09-28</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-07</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H6">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -757,298 +757,298 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Grip Trainer</v>
+        <v>Face Pull</v>
       </c>
       <c r="B11" t="str">
         <v>Strength</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-07</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-07</v>
       </c>
       <c r="F11">
-        <v>200</v>
+        <v>27</v>
       </c>
       <c r="G11">
-        <v>200</v>
+        <v>27</v>
       </c>
       <c r="H11">
-        <v>200</v>
+        <v>27</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>235</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Hack Squat</v>
+        <v>Farmers Carry</v>
       </c>
       <c r="B12" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-09-30</v>
+        <v>2026-10-07</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-07</v>
       </c>
       <c r="F12">
-        <v>270</v>
+        <v>40</v>
       </c>
       <c r="G12">
-        <v>270</v>
+        <v>40</v>
       </c>
       <c r="H12">
-        <v>270</v>
+        <v>40</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>415</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Hip Thrust</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="B13" t="str">
         <v>Strength</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="str">
         <v>2026-09-28</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-09-30</v>
+        <v>2026-10-07</v>
       </c>
       <c r="F13">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="G13">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="H13">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>375</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Hack Squat</v>
       </c>
       <c r="B14" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-30</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-09-30</v>
+        <v>2026-10-05</v>
       </c>
       <c r="F14">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="G14">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="H14">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>210</v>
+        <v>415</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="B15" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-07</v>
       </c>
       <c r="F15">
-        <v>15</v>
+        <v>320</v>
       </c>
       <c r="G15">
-        <v>15</v>
+        <v>320</v>
       </c>
       <c r="H15">
-        <v>15</v>
+        <v>320</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>21</v>
+        <v>375</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Kneeling Cable Ab Crunch</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="B16" t="str">
         <v>Strength</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-27</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-30</v>
       </c>
       <c r="F16">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="G16">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="H16">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>100</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Lat Pulldown</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="B17" t="str">
-        <v>Hypertrophy</v>
+        <v>Isometric</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-10-05</v>
+        <v>2026-09-29</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-07</v>
       </c>
       <c r="F17">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="G17">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="H17">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>90</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Lat Pulldown, alternating single-arm</v>
+        <v>Kneeling Cable Ab Crunch</v>
       </c>
       <c r="B18" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-07</v>
       </c>
       <c r="F18">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G18">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H18">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J18">
-        <v>70</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Lateral Bound / Skater Hop with Stick</v>
+        <v>Lat Pulldown</v>
       </c>
       <c r="B19" t="str">
-        <v>Explosive</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-05</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="F19" t="str">
-        <v/>
-      </c>
-      <c r="G19" t="str">
-        <v/>
-      </c>
-      <c r="H19" t="str">
-        <v/>
-      </c>
-      <c r="I19" t="str">
-        <v/>
-      </c>
-      <c r="J19" t="str">
-        <v/>
+        <v>2026-10-05</v>
+      </c>
+      <c r="F19">
+        <v>45</v>
+      </c>
+      <c r="G19">
+        <v>45</v>
+      </c>
+      <c r="H19">
+        <v>45</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>90</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Leg Extension ISO hold</v>
+        <v>Lat Pulldown, alternating single-arm</v>
       </c>
       <c r="B20" t="str">
-        <v>Isometric</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -1060,184 +1060,184 @@
         <v>2026-09-29</v>
       </c>
       <c r="F20">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G20">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H20">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Outer Thigh Adduction</v>
+        <v>Lateral Bound / Skater Hop with Stick</v>
       </c>
       <c r="B21" t="str">
-        <v>Strength</v>
+        <v>Explosive</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-10-05</v>
-      </c>
-      <c r="F21">
-        <v>160</v>
-      </c>
-      <c r="G21">
-        <v>160</v>
-      </c>
-      <c r="H21">
-        <v>160</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>180</v>
+        <v>2026-10-04</v>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Plate Torso Rotation</v>
+        <v>Leg Extension ISO hold</v>
       </c>
       <c r="B22" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-10-05</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-10-05</v>
+        <v>2026-09-29</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G22">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H22">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>30</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Pogo Hops</v>
+        <v>Outer Thigh Adduction</v>
       </c>
       <c r="B23" t="str">
-        <v>Explosive</v>
+        <v>Strength</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-05</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="F23" t="str">
-        <v/>
-      </c>
-      <c r="G23" t="str">
-        <v/>
-      </c>
-      <c r="H23" t="str">
-        <v/>
-      </c>
-      <c r="I23" t="str">
-        <v/>
-      </c>
-      <c r="J23" t="str">
-        <v/>
+        <v>2026-10-05</v>
+      </c>
+      <c r="F23">
+        <v>160</v>
+      </c>
+      <c r="G23">
+        <v>160</v>
+      </c>
+      <c r="H23">
+        <v>160</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>180</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Overhead Tricep Extension</v>
       </c>
       <c r="B24" t="str">
         <v>Strength</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-09-27</v>
+        <v>2026-10-07</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-07</v>
       </c>
       <c r="F24">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="G24">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="H24">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
-        <v>80</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Plate Torso Rotation</v>
       </c>
       <c r="B25" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-09-27</v>
+        <v>2026-10-05</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-05</v>
       </c>
       <c r="F25">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G25">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H25">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25">
-        <v>65</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Sled push → pull</v>
+        <v>Pogo Hops</v>
       </c>
       <c r="B26" t="str">
         <v>Explosive</v>
@@ -1269,104 +1269,200 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Split Squat Jumps</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="B27" t="str">
-        <v>Explosive</v>
+        <v>Strength</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-10-04</v>
+        <v>2026-09-27</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="F27" t="str">
-        <v/>
-      </c>
-      <c r="G27" t="str">
-        <v/>
-      </c>
-      <c r="H27" t="str">
-        <v/>
-      </c>
-      <c r="I27" t="str">
-        <v/>
-      </c>
-      <c r="J27" t="str">
-        <v/>
+        <v>2026-10-05</v>
+      </c>
+      <c r="F27">
+        <v>50</v>
+      </c>
+      <c r="G27">
+        <v>50</v>
+      </c>
+      <c r="H27">
+        <v>50</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Suitcase Bottom-Up, single-arm</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="B28" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-27</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-28</v>
       </c>
       <c r="F28">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G28">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H28">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>30</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Zottman Curl</v>
+        <v>Sled push → pull</v>
       </c>
       <c r="B29" t="str">
-        <v>Hypertrophy</v>
+        <v>Explosive</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="E29" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Split Squat Jumps</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Explosive</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="E30" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Suitcase Bottom-Up, single-arm</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" t="str">
         <v>2026-09-29</v>
       </c>
-      <c r="E29" t="str">
+      <c r="E31" t="str">
         <v>2026-09-29</v>
       </c>
-      <c r="F29">
+      <c r="F31">
+        <v>25</v>
+      </c>
+      <c r="G31">
+        <v>25</v>
+      </c>
+      <c r="H31">
+        <v>25</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Zottman Curl</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Hypertrophy</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="E32" t="str">
+        <v>2026-10-07</v>
+      </c>
+      <c r="F32">
         <v>15</v>
       </c>
-      <c r="G29">
+      <c r="G32">
         <v>15</v>
       </c>
-      <c r="H29">
+      <c r="H32">
         <v>15</v>
       </c>
-      <c r="I29">
+      <c r="I32">
         <v>0</v>
       </c>
-      <c r="J29">
+      <c r="J32">
         <v>23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J32"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J32"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1426,7 +1522,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D103"/>
+  <dimension ref="A1:D115"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.83203125" customWidth="1"/>
@@ -2769,10 +2865,10 @@
         <v>2026-10-04</v>
       </c>
       <c r="B96" t="str">
-        <v>skipped</v>
+        <v>done</v>
       </c>
       <c r="C96" t="str">
-        <v>B-d6s5</v>
+        <v>B-d1s9</v>
       </c>
       <c r="D96" t="str">
         <v>Yes</v>
@@ -2783,10 +2879,10 @@
         <v>2026-10-04</v>
       </c>
       <c r="B97" t="str">
-        <v>skipped</v>
+        <v>done</v>
       </c>
       <c r="C97" t="str">
-        <v>B-sled1</v>
+        <v>B-d2s1</v>
       </c>
       <c r="D97" t="str">
         <v>Yes</v>
@@ -2797,10 +2893,10 @@
         <v>2026-10-04</v>
       </c>
       <c r="B98" t="str">
-        <v>skipped</v>
+        <v>done</v>
       </c>
       <c r="C98" t="str">
-        <v>B-d1s7</v>
+        <v>B-d2s1#0</v>
       </c>
       <c r="D98" t="str">
         <v>Yes</v>
@@ -2811,13 +2907,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B99" t="str">
-        <v>moved</v>
+        <v>done</v>
       </c>
       <c r="C99" t="str">
-        <v>B-d5s2</v>
-      </c>
-      <c r="D99">
-        <v>6</v>
+        <v>B-d2s2</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="100">
@@ -2825,13 +2921,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B100" t="str">
-        <v>moved</v>
+        <v>done</v>
       </c>
       <c r="C100" t="str">
-        <v>B-d1s3</v>
-      </c>
-      <c r="D100">
-        <v>6</v>
+        <v>B-d2s4</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="101">
@@ -2839,13 +2935,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B101" t="str">
-        <v>moved</v>
+        <v>done</v>
       </c>
       <c r="C101" t="str">
-        <v>B-d1s9</v>
-      </c>
-      <c r="D101">
-        <v>2</v>
+        <v>B-d2s3</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="102">
@@ -2853,13 +2949,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B102" t="str">
-        <v>moved</v>
+        <v>done</v>
       </c>
       <c r="C102" t="str">
-        <v>B-d1s5</v>
-      </c>
-      <c r="D102">
-        <v>5</v>
+        <v>B-d2s3#1</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="103">
@@ -2867,19 +2963,187 @@
         <v>2026-10-04</v>
       </c>
       <c r="B103" t="str">
+        <v>done</v>
+      </c>
+      <c r="C103" t="str">
+        <v>B-d2s5</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B104" t="str">
+        <v>done</v>
+      </c>
+      <c r="C104" t="str">
+        <v>B-d2s7</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B105" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C105" t="str">
+        <v>B-d6s5</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B106" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C106" t="str">
+        <v>B-sled1</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B107" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C107" t="str">
+        <v>B-d1s7</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B108" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C108" t="str">
+        <v>B-sled2</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B109" t="str">
+        <v>skipped</v>
+      </c>
+      <c r="C109" t="str">
+        <v>B-d2s6</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B110" t="str">
         <v>moved</v>
       </c>
-      <c r="C103" t="str">
+      <c r="C110" t="str">
+        <v>B-d5s2</v>
+      </c>
+      <c r="D110">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B111" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C111" t="str">
+        <v>B-d1s3</v>
+      </c>
+      <c r="D111">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B112" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C112" t="str">
+        <v>B-d1s9</v>
+      </c>
+      <c r="D112">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B113" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C113" t="str">
+        <v>B-d1s5</v>
+      </c>
+      <c r="D113">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B114" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C114" t="str">
         <v>B-d2s8</v>
       </c>
-      <c r="D103">
+      <c r="D114">
         <v>1</v>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B115" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C115" t="str">
+        <v>B-d3s2</v>
+      </c>
+      <c r="D115">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D103"/>
+  <autoFilter ref="A1:D115"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D103"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D115"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2929,7 +3193,7 @@
         <v>ghBackup</v>
       </c>
       <c r="B5" t="str">
-        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"1x46bwu","last":{"at":"2026-10-05T21:44:09.148Z","url":"https://github.com/jacgit18/iron-log/commit/289f6b650fb2b6e816ac898a7d72d8c9b8f06932"}}</v>
+        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"33b887","last":{"at":"2026-10-06T20:03:53.123Z","url":"https://github.com/jacgit18/iron-log/commit/5fc919acf3fbf1788fe4ae6911c92ce8c750c435"}}</v>
       </c>
     </row>
     <row r="6">
@@ -3030,7 +3294,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O55"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -5211,17 +5475,440 @@
         <v>zercher</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2026-10-07</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Chest Press</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Hypertrophy</v>
+      </c>
+      <c r="E47">
+        <v>25</v>
+      </c>
+      <c r="F47">
+        <v>2</v>
+      </c>
+      <c r="G47">
+        <v>12</v>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v>25×15, 25×12</v>
+      </c>
+      <c r="J47">
+        <v>675</v>
+      </c>
+      <c r="K47" t="str">
+        <v>Chest</v>
+      </c>
+      <c r="L47" t="str">
+        <v>Front delts, Triceps</v>
+      </c>
+      <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47" t="str">
+        <v>B-d2s5</v>
+      </c>
+      <c r="O47" t="str">
+        <v>chestpress</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>2026-10-07</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Face Pull</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E48">
+        <v>27</v>
+      </c>
+      <c r="F48">
+        <v>2</v>
+      </c>
+      <c r="G48">
+        <v>6</v>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v>27×6, 27×6</v>
+      </c>
+      <c r="J48">
+        <v>324</v>
+      </c>
+      <c r="K48" t="str">
+        <v>Rear delts</v>
+      </c>
+      <c r="L48" t="str">
+        <v>Upper back, Traps</v>
+      </c>
+      <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48" t="str">
+        <v>B-d2s3</v>
+      </c>
+      <c r="O48" t="str">
+        <v>facepull</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2026-10-07</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Farmers Carry</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E49">
+        <v>40</v>
+      </c>
+      <c r="F49">
+        <v>4</v>
+      </c>
+      <c r="G49">
+        <v>6</v>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v>40×6, 40×6, 40×6, 40×6</v>
+      </c>
+      <c r="J49">
+        <v>960</v>
+      </c>
+      <c r="K49" t="str">
+        <v>Forearms &amp; grip, Traps</v>
+      </c>
+      <c r="L49" t="str">
+        <v>Obliques, Abs</v>
+      </c>
+      <c r="M49" t="str">
+        <v>From check-off</v>
+      </c>
+      <c r="N49" t="str">
+        <v>B-d2s1</v>
+      </c>
+      <c r="O49" t="str">
+        <v>farmers</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>2026-10-07</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Grip Trainer</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E50">
+        <v>200</v>
+      </c>
+      <c r="F50">
+        <v>4</v>
+      </c>
+      <c r="G50">
+        <v>6</v>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v>200×6, 200×6, 200×6, 200×6</v>
+      </c>
+      <c r="J50">
+        <v>4800</v>
+      </c>
+      <c r="K50" t="str">
+        <v>Forearms &amp; grip</v>
+      </c>
+      <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v>From check-off</v>
+      </c>
+      <c r="N50" t="str">
+        <v>B-d2s7</v>
+      </c>
+      <c r="O50" t="str">
+        <v>grip</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2026-10-07</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Hip Thrust</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E51">
+        <v>320</v>
+      </c>
+      <c r="F51">
+        <v>2</v>
+      </c>
+      <c r="G51">
+        <v>6</v>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v>320×6, 320×6</v>
+      </c>
+      <c r="J51">
+        <v>3840</v>
+      </c>
+      <c r="K51" t="str">
+        <v>Glutes</v>
+      </c>
+      <c r="L51" t="str">
+        <v>Hamstrings</v>
+      </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
+        <v>B-d2s5</v>
+      </c>
+      <c r="O51" t="str">
+        <v>hipthrust</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2026-10-07</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Kettlebell Leg Raise</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Isometric</v>
+      </c>
+      <c r="E52">
+        <v>15</v>
+      </c>
+      <c r="F52">
+        <v>3</v>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52">
+        <v>15</v>
+      </c>
+      <c r="I52" t="str">
+        <v>15×15s, 15×15s, 15×15s</v>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
+        <v>Abs, Hip flexors</v>
+      </c>
+      <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
+        <v>From check-off</v>
+      </c>
+      <c r="N52" t="str">
+        <v>B-d1s9</v>
+      </c>
+      <c r="O52" t="str">
+        <v>kbleg</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2026-10-07</v>
+      </c>
+      <c r="B53" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Kneeling Cable Ab Crunch</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E53">
+        <v>44</v>
+      </c>
+      <c r="F53">
+        <v>4</v>
+      </c>
+      <c r="G53">
+        <v>6</v>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v>44×6, 44×6, 44×6, 44×6</v>
+      </c>
+      <c r="J53">
+        <v>1056</v>
+      </c>
+      <c r="K53" t="str">
+        <v>Abs</v>
+      </c>
+      <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
+        <v>B-d2s4</v>
+      </c>
+      <c r="O53" t="str">
+        <v>cablecrunch</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2026-10-07</v>
+      </c>
+      <c r="B54" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Overhead Tricep Extension</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Strength</v>
+      </c>
+      <c r="E54">
+        <v>17</v>
+      </c>
+      <c r="F54">
+        <v>2</v>
+      </c>
+      <c r="G54">
+        <v>6</v>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v>17×6, 17×6</v>
+      </c>
+      <c r="J54">
+        <v>204</v>
+      </c>
+      <c r="K54" t="str">
+        <v>Triceps</v>
+      </c>
+      <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
+        <v>B-d2s2</v>
+      </c>
+      <c r="O54" t="str">
+        <v>ohtri</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2026-10-07</v>
+      </c>
+      <c r="B55" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Zottman Curl</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Hypertrophy</v>
+      </c>
+      <c r="E55">
+        <v>15</v>
+      </c>
+      <c r="F55">
+        <v>3</v>
+      </c>
+      <c r="G55">
+        <v>15</v>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v>15×15, 15×15, 15×15</v>
+      </c>
+      <c r="J55">
+        <v>675</v>
+      </c>
+      <c r="K55" t="str">
+        <v>Biceps, Forearms &amp; grip</v>
+      </c>
+      <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
+        <v>From check-off</v>
+      </c>
+      <c r="N55" t="str">
+        <v>B-d1s9</v>
+      </c>
+      <c r="O55" t="str">
+        <v>zottman</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O46"/>
+  <autoFilter ref="A1:O55"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O55"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E40"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -5561,13 +6248,13 @@
         <v>Glutes</v>
       </c>
       <c r="C20">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D20">
         <v>16</v>
       </c>
       <c r="E20">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5575,16 +6262,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B21" t="str">
-        <v>Quads</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="C21">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -5592,16 +6279,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B22" t="str">
-        <v>Upper back</v>
+        <v>Abs</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D22">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E22">
-        <v>10.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -5609,16 +6296,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B23" t="str">
-        <v>Calves</v>
+        <v>Quads</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D23">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>9.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -5626,16 +6313,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B24" t="str">
-        <v>Lats</v>
+        <v>Upper back</v>
       </c>
       <c r="C24">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E24">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="25">
@@ -5649,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E25">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -5660,16 +6347,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B26" t="str">
-        <v>Lower back</v>
+        <v>Calves</v>
       </c>
       <c r="C26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E26">
-        <v>8</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="27">
@@ -5677,16 +6364,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B27" t="str">
-        <v>Outer hip (abductors)</v>
+        <v>Lats</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>7</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="28">
@@ -5694,16 +6381,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B28" t="str">
-        <v>Hamstrings</v>
+        <v>Lower back</v>
       </c>
       <c r="C28">
+        <v>8</v>
+      </c>
+      <c r="D28">
         <v>0</v>
       </c>
-      <c r="D28">
-        <v>14</v>
-      </c>
       <c r="E28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -5711,16 +6398,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B29" t="str">
-        <v>Abs</v>
+        <v>Hamstrings</v>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E29">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -5731,13 +6418,13 @@
         <v>Chest</v>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D30">
         <v>4</v>
       </c>
       <c r="E30">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -5745,16 +6432,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B31" t="str">
-        <v>Front delts</v>
+        <v>Biceps</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31">
         <v>8</v>
       </c>
       <c r="E31">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -5762,16 +6449,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B32" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Outer hip (abductors)</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -5779,16 +6466,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B33" t="str">
-        <v>Rear delts</v>
+        <v>Front delts</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -5796,16 +6483,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B34" t="str">
-        <v>Biceps</v>
+        <v>Rear delts</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D34">
         <v>8</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -5813,16 +6500,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B35" t="str">
-        <v>Inner thigh (adductors)</v>
+        <v>Traps</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D35">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>3.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -5833,13 +6520,13 @@
         <v>Triceps</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -5847,16 +6534,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B37" t="str">
-        <v>Side delts</v>
+        <v>Inner thigh (adductors)</v>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="38">
@@ -5864,22 +6551,56 @@
         <v>2026-10-04</v>
       </c>
       <c r="B38" t="str">
+        <v>Hip flexors</v>
+      </c>
+      <c r="C38">
+        <v>3</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Side delts</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B40" t="str">
         <v>Shins</v>
       </c>
-      <c r="C38">
+      <c r="C40">
         <v>0</v>
       </c>
-      <c r="D38">
+      <c r="D40">
         <v>3</v>
       </c>
-      <c r="E38">
+      <c r="E40">
         <v>1.5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E38"/>
+  <autoFilter ref="A1:E40"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E40"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5958,22 +6679,22 @@
         <v>B</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3">
+        <v>44</v>
+      </c>
+      <c r="H3">
         <v>28</v>
-      </c>
-      <c r="H3">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -6385,7 +7106,7 @@
         <v>Exported</v>
       </c>
       <c r="B42" t="str">
-        <v>2026-10-06T20:03:48.676Z</v>
+        <v>2026-10-07T11:39:25.272Z</v>
       </c>
     </row>
   </sheetData>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">Weeks!$A$1:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Body weight'!$A$1:$D$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5">Settings!$A$1:$B$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5">Settings!$A$1:$B$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">Programs!$A$1:$R$145</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Program info'!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$2</definedName>
@@ -3177,7 +3177,7 @@
         <v>ex</v>
       </c>
       <c r="B3" t="str">
-        <v>{"deadlift":{"n":"Deadlift","eq":"barbell"},"zercher":{"eq":"shortbar"},"split-stance-cable-hip-rotation":{"n":"Split Stance Cable Hip Rotation","url":"https://youtu.be/ixIEilUM2aY","eq":"cable"},"clean-jerk-overhead-press":{"n":"Clean Jerk &amp; Overhead Press","eq":"dumbbell"}}</v>
+        <v>{"deadlift":{"n":"Deadlift","eq":"barbell"},"zercher":{"eq":"shortbar"},"split-stance-cable-hip-rotation":{"n":"Split Stance Cable Hip Rotation","url":"https://youtu.be/ixIEilUM2aY","eq":"cable"},"clean-jerk-overhead-press":{"n":"Clean Jerk &amp; Overhead Press","eq":"dumbbell"},"seated-cable-crunch":{"n":"Seated Cable Crunch","url":"https://youtube.com/shorts/bIbm-p6Q4s8?is=aiC1fOhPbN5QMcgq","eq":"cable"}}</v>
       </c>
     </row>
     <row r="4">
@@ -3185,7 +3185,7 @@
         <v>exPh</v>
       </c>
       <c r="B4" t="str">
-        <v>{"canoe":"iso","romanadd":"strength","deskbands":"iso","spinal":"mob","platerot":"strength","suitcase":"strength","qlext":"strength","skater":"exp","splitjump":"exp","cablerow":"exp","cablepunch":"iso","depthcombo":"exp","zercher":"strength"}</v>
+        <v>{"canoe":"iso","romanadd":"strength","deskbands":"iso","spinal":"mob","platerot":"strength","suitcase":"strength","qlext":"strength","skater":"exp","splitjump":"exp","cablerow":"exp","cablepunch":"iso","depthcombo":"exp","zercher":"strength","seated-cable-crunch":"strength"}</v>
       </c>
     </row>
     <row r="5">
@@ -3193,7 +3193,7 @@
         <v>ghBackup</v>
       </c>
       <c r="B5" t="str">
-        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"33b887","last":{"at":"2026-10-06T20:03:53.123Z","url":"https://github.com/jacgit18/iron-log/commit/5fc919acf3fbf1788fe4ae6911c92ce8c750c435"}}</v>
+        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"1sdqb2a","last":{"at":"2026-10-05T10:56:57.524Z","url":"https://github.com/jacgit18/iron-log/commit/f6b67ee93ead4d55569495213b1371f9ba297d63"}}</v>
       </c>
     </row>
     <row r="6">
@@ -3241,7 +3241,7 @@
         <v>muscleMap</v>
       </c>
       <c r="B11" t="str">
-        <v>{}</v>
+        <v>{"seated-cable-crunch":{"p":["abs"],"s":[]}}</v>
       </c>
     </row>
     <row r="12">
@@ -3273,7 +3273,7 @@
         <v>rm</v>
       </c>
       <c r="B15" t="str">
-        <v>{"latpd":70,"wristpd":48,"platerot":30,"innerthigh":210,"chestpress":40,"zercher":80,"zottman":23,"kbleg":21,"grip":235,"canoe":13.33,"suitcase":30,"reardelt":65,"facepull":50,"legext":65,"cablecrunch":100,"hipthrust":375,"db6":20,"hack":415,"pallof":40,"cablerow":70,"arnold":40,"dbclean":45,"latpdbi":90,"outerthigh":180,"farmers":65,"dblunge":65,"ohtri":30,"bss":65,"legcurl":100,"cablepunch":50,"clean-jerk-overhead-press":45}</v>
+        <v>{"latpd":70,"wristpd":48,"platerot":30,"innerthigh":210,"chestpress":40,"zercher":80,"zottman":23,"kbleg":21,"grip":235,"canoe":13.33,"suitcase":30,"reardelt":65,"facepull":50,"legext":65,"cablecrunch":100,"hipthrust":375,"db6":20,"hack":415,"pallof":40,"cablerow":70,"arnold":40,"dbclean":45,"latpdbi":90,"outerthigh":180,"farmers":65,"dblunge":65,"ohtri":30,"bss":65,"legcurl":100,"cablepunch":50,"clean-jerk-overhead-press":45,"seated-cable-crunch":77}</v>
       </c>
     </row>
     <row r="16">
@@ -6381,13 +6381,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B28" t="str">
-        <v>Lower back</v>
+        <v>Chest</v>
       </c>
       <c r="C28">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E28">
         <v>8</v>
@@ -6415,13 +6415,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B30" t="str">
-        <v>Chest</v>
+        <v>Lower back</v>
       </c>
       <c r="C30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -6432,13 +6432,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B31" t="str">
-        <v>Biceps</v>
+        <v>Front delts</v>
       </c>
       <c r="C31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E31">
         <v>7</v>
@@ -6449,13 +6449,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B32" t="str">
-        <v>Outer hip (abductors)</v>
+        <v>Biceps</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E32">
         <v>7</v>
@@ -6466,13 +6466,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B33" t="str">
-        <v>Front delts</v>
+        <v>Outer hip (abductors)</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D33">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>7</v>
@@ -6500,13 +6500,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B35" t="str">
-        <v>Traps</v>
+        <v>Triceps</v>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E35">
         <v>5</v>
@@ -6517,13 +6517,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B36" t="str">
-        <v>Triceps</v>
+        <v>Traps</v>
       </c>
       <c r="C36">
+        <v>4</v>
+      </c>
+      <c r="D36">
         <v>2</v>
-      </c>
-      <c r="D36">
-        <v>6</v>
       </c>
       <c r="E36">
         <v>5</v>
@@ -6653,19 +6653,19 @@
         <v>A</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="H2">
         <v>26</v>
@@ -6679,10 +6679,10 @@
         <v>B</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E3">
         <v>61</v>
@@ -6691,7 +6691,7 @@
         <v>5</v>
       </c>
       <c r="G3">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H3">
         <v>28</v>
@@ -6767,7 +6767,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -7071,48 +7071,56 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>1RM: Suitcase Bottom-Up, single-arm</v>
+        <v>1RM: Seated Cable Crunch</v>
       </c>
       <c r="B38">
-        <v>30</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>1RM: Cable Wrist Pulldown</v>
+        <v>1RM: Suitcase Bottom-Up, single-arm</v>
       </c>
       <c r="B39">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>1RM: Seated Zercher Good Morning</v>
+        <v>1RM: Cable Wrist Pulldown</v>
       </c>
       <c r="B40">
-        <v>80</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>1RM: Zottman Curl</v>
+        <v>1RM: Seated Zercher Good Morning</v>
       </c>
       <c r="B41">
-        <v>23</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
+        <v>1RM: Zottman Curl</v>
+      </c>
+      <c r="B42">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
         <v>Exported</v>
       </c>
-      <c r="B42" t="str">
-        <v>2026-10-07T11:39:25.272Z</v>
+      <c r="B43" t="str">
+        <v>2026-10-07T11:56:02.918Z</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B42"/>
+  <autoFilter ref="A1:B43"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B42"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B43"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7288,10 +7296,10 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>latpd</v>
+        <v>latpdbi</v>
       </c>
       <c r="M3" t="str">
-        <v>Lat Pulldown, alternating single-arm</v>
+        <v>Lat Pulldown</v>
       </c>
       <c r="N3" t="str">
         <v>hyp</v>
@@ -7329,7 +7337,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="str">
-        <v>A-d1s2</v>
+        <v>A-d1s3</v>
       </c>
       <c r="H4" t="str">
         <v>Regular</v>
@@ -7344,16 +7352,16 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>wristpd</v>
+        <v>platerot</v>
       </c>
       <c r="M4" t="str">
-        <v>Cable Wrist Pulldown</v>
+        <v>Plate Torso Rotation</v>
       </c>
       <c r="N4" t="str">
-        <v>hyp</v>
+        <v>strength</v>
       </c>
       <c r="O4">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="P4" t="str">
         <v/>
@@ -7385,7 +7393,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="str">
-        <v>A-d1s3</v>
+        <v>A-d1s4</v>
       </c>
       <c r="H5" t="str">
         <v>Regular</v>
@@ -7400,16 +7408,16 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>platerot</v>
+        <v>innerthigh</v>
       </c>
       <c r="M5" t="str">
-        <v>Plate Torso Rotation</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="N5" t="str">
         <v>strength</v>
       </c>
       <c r="O5">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="P5" t="str">
         <v/>
@@ -7441,7 +7449,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="str">
-        <v>A-d1s4</v>
+        <v>A-d1s5</v>
       </c>
       <c r="H6" t="str">
         <v>Regular</v>
@@ -7456,25 +7464,25 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>innerthigh</v>
+        <v>romanadd</v>
       </c>
       <c r="M6" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Roman Chair Hip Adduction</v>
       </c>
       <c r="N6" t="str">
         <v>strength</v>
       </c>
-      <c r="O6">
-        <v>180</v>
+      <c r="O6" t="str">
+        <v/>
       </c>
       <c r="P6" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q6" t="str">
         <v/>
       </c>
       <c r="R6" t="str">
-        <v/>
+        <v>On the back-extension bench</v>
       </c>
     </row>
     <row r="7">
@@ -7497,40 +7505,40 @@
         <v>6</v>
       </c>
       <c r="G7" t="str">
-        <v>A-d1s5</v>
+        <v>A-d1s6</v>
       </c>
       <c r="H7" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I7" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J7" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K7" t="str">
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>romanadd</v>
+        <v>chestpress</v>
       </c>
       <c r="M7" t="str">
-        <v>Roman Chair Hip Adduction</v>
+        <v>Chest Press</v>
       </c>
       <c r="N7" t="str">
         <v>strength</v>
       </c>
-      <c r="O7" t="str">
-        <v/>
+      <c r="O7">
+        <v>35</v>
       </c>
       <c r="P7" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q7" t="str">
         <v/>
       </c>
       <c r="R7" t="str">
-        <v>On the back-extension bench</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -7550,7 +7558,7 @@
         <v/>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G8" t="str">
         <v>A-d1s6</v>
@@ -7568,16 +7576,16 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>chestpress</v>
+        <v>zercher</v>
       </c>
       <c r="M8" t="str">
-        <v>Chest Press</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="N8" t="str">
         <v>strength</v>
       </c>
       <c r="O8">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="P8" t="str">
         <v/>
@@ -7609,13 +7617,13 @@
         <v>7</v>
       </c>
       <c r="G9" t="str">
-        <v>A-d1s6</v>
+        <v>A-d1s7</v>
       </c>
       <c r="H9" t="str">
         <v>Supersets</v>
       </c>
       <c r="I9" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J9" t="str">
         <v>superset</v>
@@ -7624,22 +7632,22 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>zercher</v>
+        <v>zottman</v>
       </c>
       <c r="M9" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Zottman Curl</v>
       </c>
       <c r="N9" t="str">
-        <v>strength</v>
+        <v>hyp</v>
       </c>
       <c r="O9">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="P9" t="str">
         <v/>
       </c>
       <c r="Q9" t="str">
-        <v/>
+        <v>3 × 15</v>
       </c>
       <c r="R9" t="str">
         <v/>
@@ -7662,7 +7670,7 @@
         <v/>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" t="str">
         <v>A-d1s7</v>
@@ -7680,13 +7688,13 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>zottman</v>
+        <v>kbleg</v>
       </c>
       <c r="M10" t="str">
-        <v>Zottman Curl</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="N10" t="str">
-        <v>hyp</v>
+        <v>iso</v>
       </c>
       <c r="O10">
         <v>15</v>
@@ -7695,7 +7703,7 @@
         <v/>
       </c>
       <c r="Q10" t="str">
-        <v>3 × 15</v>
+        <v>3 × 15 s hold</v>
       </c>
       <c r="R10" t="str">
         <v/>
@@ -7721,37 +7729,37 @@
         <v>8</v>
       </c>
       <c r="G11" t="str">
-        <v>A-d1s7</v>
+        <v>A-d1s8</v>
       </c>
       <c r="H11" t="str">
-        <v>Supersets</v>
+        <v>Home</v>
       </c>
       <c r="I11" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J11" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K11" t="str">
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>kbleg</v>
+        <v>grip</v>
       </c>
       <c r="M11" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="N11" t="str">
-        <v>iso</v>
+        <v>strength</v>
       </c>
       <c r="O11">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="P11" t="str">
         <v/>
       </c>
       <c r="Q11" t="str">
-        <v>3 × 15 s hold</v>
+        <v/>
       </c>
       <c r="R11" t="str">
         <v/>
@@ -7777,7 +7785,7 @@
         <v>9</v>
       </c>
       <c r="G12" t="str">
-        <v>A-d1s8</v>
+        <v>A-d1s9</v>
       </c>
       <c r="H12" t="str">
         <v>Home</v>
@@ -7792,16 +7800,16 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>grip</v>
+        <v>canoe</v>
       </c>
       <c r="M12" t="str">
-        <v>Grip Trainer</v>
+        <v>Canoe Stretch</v>
       </c>
       <c r="N12" t="str">
-        <v>strength</v>
+        <v/>
       </c>
       <c r="O12">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="P12" t="str">
         <v/>
@@ -7818,25 +7826,25 @@
         <v>A</v>
       </c>
       <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13">
         <v>1</v>
       </c>
-      <c r="C13" t="str">
-        <v>Day 1</v>
-      </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13">
-        <v>10</v>
-      </c>
       <c r="G13" t="str">
-        <v>A-d1s9</v>
+        <v>A-sled2</v>
       </c>
       <c r="H13" t="str">
-        <v>Home</v>
+        <v>Optional</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -7845,25 +7853,25 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v/>
+        <v>Optional</v>
       </c>
       <c r="L13" t="str">
-        <v>canoe</v>
+        <v>sledlat</v>
       </c>
       <c r="M13" t="str">
-        <v>Canoe Stretch</v>
+        <v>Sled push → lateral pull</v>
       </c>
       <c r="N13" t="str">
-        <v/>
-      </c>
-      <c r="O13">
-        <v>10</v>
+        <v>exp</v>
+      </c>
+      <c r="O13" t="str">
+        <v/>
       </c>
       <c r="P13" t="str">
         <v/>
       </c>
       <c r="Q13" t="str">
-        <v/>
+        <v>1 × 3</v>
       </c>
       <c r="R13" t="str">
         <v/>
@@ -7886,40 +7894,40 @@
         <v/>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" t="str">
-        <v>A-sled2</v>
+        <v>A-d2s1</v>
       </c>
       <c r="H14" t="str">
-        <v>Optional</v>
+        <v>Regular</v>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>Primary</v>
       </c>
       <c r="J14" t="str">
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="L14" t="str">
-        <v>sledlat</v>
+        <v>suitcase</v>
       </c>
       <c r="M14" t="str">
-        <v>Sled push → lateral pull</v>
+        <v>Suitcase Bottom-Up, single-arm</v>
       </c>
       <c r="N14" t="str">
-        <v>exp</v>
-      </c>
-      <c r="O14" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="O14">
+        <v>20</v>
       </c>
       <c r="P14" t="str">
         <v/>
       </c>
       <c r="Q14" t="str">
-        <v>1 × 3</v>
+        <v>3 × 4 each arm</v>
       </c>
       <c r="R14" t="str">
         <v/>
@@ -7942,40 +7950,40 @@
         <v/>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" t="str">
-        <v>A-d2s1</v>
+        <v>A-d2s2</v>
       </c>
       <c r="H15" t="str">
         <v>Regular</v>
       </c>
       <c r="I15" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J15" t="str">
-        <v/>
+        <v>either</v>
       </c>
       <c r="K15" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L15" t="str">
-        <v>suitcase</v>
+        <v>reardelt</v>
       </c>
       <c r="M15" t="str">
-        <v>Suitcase Bottom-Up, single-arm</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="N15" t="str">
-        <v/>
+        <v>iso</v>
       </c>
       <c r="O15">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="P15" t="str">
         <v/>
       </c>
       <c r="Q15" t="str">
-        <v>3 × 4 each arm</v>
+        <v>4 × 15 s per arm</v>
       </c>
       <c r="R15" t="str">
         <v/>
@@ -8016,22 +8024,22 @@
         <v>Whichever is free</v>
       </c>
       <c r="L16" t="str">
-        <v>reardelt</v>
+        <v>facepull</v>
       </c>
       <c r="M16" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Face Pull</v>
       </c>
       <c r="N16" t="str">
-        <v>iso</v>
+        <v>strength</v>
       </c>
       <c r="O16">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P16" t="str">
         <v/>
       </c>
       <c r="Q16" t="str">
-        <v>4 × 15 s per arm</v>
+        <v/>
       </c>
       <c r="R16" t="str">
         <v/>
@@ -8054,10 +8062,10 @@
         <v/>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" t="str">
-        <v>A-d2s2</v>
+        <v>A-d2s3</v>
       </c>
       <c r="H17" t="str">
         <v>Regular</v>
@@ -8066,28 +8074,28 @@
         <v>Accessory</v>
       </c>
       <c r="J17" t="str">
-        <v>either</v>
+        <v/>
       </c>
       <c r="K17" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L17" t="str">
-        <v>facepull</v>
+        <v>legext</v>
       </c>
       <c r="M17" t="str">
-        <v>Face Pull</v>
+        <v>Leg Extension ISO hold</v>
       </c>
       <c r="N17" t="str">
-        <v>strength</v>
+        <v>iso</v>
       </c>
       <c r="O17">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="P17" t="str">
         <v/>
       </c>
       <c r="Q17" t="str">
-        <v/>
+        <v>4 × 30 s</v>
       </c>
       <c r="R17" t="str">
         <v/>
@@ -8110,40 +8118,40 @@
         <v/>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" t="str">
-        <v>A-d2s3</v>
+        <v>A-d2s5</v>
       </c>
       <c r="H18" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I18" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J18" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K18" t="str">
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>legext</v>
+        <v>hipthrust</v>
       </c>
       <c r="M18" t="str">
-        <v>Leg Extension ISO hold</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="N18" t="str">
-        <v>iso</v>
+        <v>strength</v>
       </c>
       <c r="O18">
-        <v>50</v>
+        <v>320</v>
       </c>
       <c r="P18" t="str">
         <v/>
       </c>
       <c r="Q18" t="str">
-        <v>4 × 30 s</v>
+        <v/>
       </c>
       <c r="R18" t="str">
         <v/>
@@ -8169,31 +8177,31 @@
         <v>5</v>
       </c>
       <c r="G19" t="str">
-        <v>A-d2s4</v>
+        <v>A-d2s5</v>
       </c>
       <c r="H19" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I19" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J19" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K19" t="str">
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>cablecrunch</v>
+        <v>chestpress</v>
       </c>
       <c r="M19" t="str">
-        <v>Kneeling Cable Ab Crunch</v>
+        <v>Chest Press</v>
       </c>
       <c r="N19" t="str">
-        <v>strength</v>
+        <v>hyp</v>
       </c>
       <c r="O19">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="P19" t="str">
         <v/>
@@ -8225,13 +8233,13 @@
         <v>6</v>
       </c>
       <c r="G20" t="str">
-        <v>A-d2s5</v>
+        <v>A-d2s6</v>
       </c>
       <c r="H20" t="str">
         <v>Supersets</v>
       </c>
       <c r="I20" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J20" t="str">
         <v>superset</v>
@@ -8240,25 +8248,25 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>hipthrust</v>
+        <v>dip</v>
       </c>
       <c r="M20" t="str">
-        <v>Hip Thrust</v>
+        <v>Wide Tricep Dip</v>
       </c>
       <c r="N20" t="str">
         <v>strength</v>
       </c>
-      <c r="O20">
-        <v>320</v>
+      <c r="O20" t="str">
+        <v/>
       </c>
       <c r="P20" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q20" t="str">
         <v/>
       </c>
       <c r="R20" t="str">
-        <v/>
+        <v>Bodyweight, working toward +10 lb</v>
       </c>
     </row>
     <row r="21">
@@ -8281,13 +8289,13 @@
         <v>6</v>
       </c>
       <c r="G21" t="str">
-        <v>A-d2s5</v>
+        <v>A-d2s6</v>
       </c>
       <c r="H21" t="str">
         <v>Supersets</v>
       </c>
       <c r="I21" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J21" t="str">
         <v>superset</v>
@@ -8296,19 +8304,19 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>chestpress</v>
+        <v>kneeraise</v>
       </c>
       <c r="M21" t="str">
-        <v>Chest Press</v>
+        <v>Hanging Knee Raise</v>
       </c>
       <c r="N21" t="str">
-        <v>hyp</v>
-      </c>
-      <c r="O21">
-        <v>25</v>
+        <v>strength</v>
+      </c>
+      <c r="O21" t="str">
+        <v/>
       </c>
       <c r="P21" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q21" t="str">
         <v/>
@@ -8337,7 +8345,7 @@
         <v>7</v>
       </c>
       <c r="G22" t="str">
-        <v>A-d2s6</v>
+        <v>A-xmuy1vz1s5qy</v>
       </c>
       <c r="H22" t="str">
         <v>Supersets</v>
@@ -8352,10 +8360,10 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>dip</v>
+        <v>seated-cable-crunch</v>
       </c>
       <c r="M22" t="str">
-        <v>Wide Tricep Dip</v>
+        <v>Seated Cable Crunch</v>
       </c>
       <c r="N22" t="str">
         <v>strength</v>
@@ -8364,13 +8372,13 @@
         <v/>
       </c>
       <c r="P22" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q22" t="str">
         <v/>
       </c>
       <c r="R22" t="str">
-        <v>Bodyweight, working toward +10 lb</v>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -8393,7 +8401,7 @@
         <v>7</v>
       </c>
       <c r="G23" t="str">
-        <v>A-d2s6</v>
+        <v>A-xmuy1vz1s5qy</v>
       </c>
       <c r="H23" t="str">
         <v>Supersets</v>
@@ -8408,10 +8416,10 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>kneeraise</v>
+        <v>wristpd</v>
       </c>
       <c r="M23" t="str">
-        <v>Hanging Knee Raise</v>
+        <v>Cable Wrist Pulldown</v>
       </c>
       <c r="N23" t="str">
         <v>strength</v>
@@ -8420,7 +8428,7 @@
         <v/>
       </c>
       <c r="P23" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q23" t="str">
         <v/>
@@ -8688,10 +8696,10 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>latpd</v>
+        <v>latpdbi</v>
       </c>
       <c r="M28" t="str">
-        <v>Lat Pulldown, alternating single-arm</v>
+        <v>Lat Pulldown</v>
       </c>
       <c r="N28" t="str">
         <v>hyp</v>
@@ -8729,7 +8737,7 @@
         <v>4</v>
       </c>
       <c r="G29" t="str">
-        <v>A-d3s3</v>
+        <v>A-d3s4</v>
       </c>
       <c r="H29" t="str">
         <v>Regular</v>
@@ -8744,16 +8752,16 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>wristpd</v>
+        <v>platerot</v>
       </c>
       <c r="M29" t="str">
-        <v>Cable Wrist Pulldown</v>
+        <v>Plate Torso Rotation</v>
       </c>
       <c r="N29" t="str">
-        <v>hyp</v>
+        <v>strength</v>
       </c>
       <c r="O29">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="P29" t="str">
         <v/>
@@ -8785,7 +8793,7 @@
         <v>5</v>
       </c>
       <c r="G30" t="str">
-        <v>A-d3s4</v>
+        <v>A-d3s5</v>
       </c>
       <c r="H30" t="str">
         <v>Regular</v>
@@ -8800,22 +8808,22 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>platerot</v>
+        <v>legext</v>
       </c>
       <c r="M30" t="str">
-        <v>Plate Torso Rotation</v>
+        <v>Leg Extension ISO hold</v>
       </c>
       <c r="N30" t="str">
-        <v>strength</v>
+        <v>iso</v>
       </c>
       <c r="O30">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="P30" t="str">
         <v/>
       </c>
       <c r="Q30" t="str">
-        <v/>
+        <v>4 × 30 s</v>
       </c>
       <c r="R30" t="str">
         <v/>
@@ -8841,7 +8849,7 @@
         <v>6</v>
       </c>
       <c r="G31" t="str">
-        <v>A-d3s5</v>
+        <v>A-d3s6</v>
       </c>
       <c r="H31" t="str">
         <v>Regular</v>
@@ -8850,16 +8858,16 @@
         <v>Accessory</v>
       </c>
       <c r="J31" t="str">
-        <v/>
+        <v>either</v>
       </c>
       <c r="K31" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L31" t="str">
-        <v>legext</v>
+        <v>reardelt</v>
       </c>
       <c r="M31" t="str">
-        <v>Leg Extension ISO hold</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="N31" t="str">
         <v>iso</v>
@@ -8871,7 +8879,7 @@
         <v/>
       </c>
       <c r="Q31" t="str">
-        <v>4 × 30 s</v>
+        <v>4 × 15 s per arm</v>
       </c>
       <c r="R31" t="str">
         <v/>
@@ -8894,7 +8902,7 @@
         <v/>
       </c>
       <c r="F32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G32" t="str">
         <v>A-d3s6</v>
@@ -8912,22 +8920,22 @@
         <v>Whichever is free</v>
       </c>
       <c r="L32" t="str">
-        <v>reardelt</v>
+        <v>facepull</v>
       </c>
       <c r="M32" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Face Pull</v>
       </c>
       <c r="N32" t="str">
-        <v>iso</v>
+        <v>strength</v>
       </c>
       <c r="O32">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P32" t="str">
         <v/>
       </c>
       <c r="Q32" t="str">
-        <v>4 × 15 s per arm</v>
+        <v/>
       </c>
       <c r="R32" t="str">
         <v/>
@@ -8953,25 +8961,25 @@
         <v>7</v>
       </c>
       <c r="G33" t="str">
-        <v>A-d3s6</v>
+        <v>A-d3s7</v>
       </c>
       <c r="H33" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I33" t="str">
         <v>Accessory</v>
       </c>
       <c r="J33" t="str">
-        <v>either</v>
+        <v>superset</v>
       </c>
       <c r="K33" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L33" t="str">
-        <v>facepull</v>
+        <v>pallof</v>
       </c>
       <c r="M33" t="str">
-        <v>Face Pull</v>
+        <v>Pallof Press</v>
       </c>
       <c r="N33" t="str">
         <v>strength</v>
@@ -9006,7 +9014,7 @@
         <v/>
       </c>
       <c r="F34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G34" t="str">
         <v>A-d3s7</v>
@@ -9024,13 +9032,13 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>pallof</v>
+        <v>cablerow</v>
       </c>
       <c r="M34" t="str">
-        <v>Pallof Press</v>
+        <v>Explosive Unilateral Cable Row</v>
       </c>
       <c r="N34" t="str">
-        <v>strength</v>
+        <v>exp</v>
       </c>
       <c r="O34">
         <v>30</v>
@@ -9065,31 +9073,31 @@
         <v>8</v>
       </c>
       <c r="G35" t="str">
-        <v>A-d3s7</v>
+        <v>A-d3s8</v>
       </c>
       <c r="H35" t="str">
-        <v>Supersets</v>
+        <v>Home</v>
       </c>
       <c r="I35" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J35" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K35" t="str">
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>cablerow</v>
+        <v>grip</v>
       </c>
       <c r="M35" t="str">
-        <v>Explosive Unilateral Cable Row</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="N35" t="str">
-        <v>exp</v>
+        <v>strength</v>
       </c>
       <c r="O35">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="P35" t="str">
         <v/>
@@ -9121,7 +9129,7 @@
         <v>9</v>
       </c>
       <c r="G36" t="str">
-        <v>A-d3s8</v>
+        <v>A-d3s9</v>
       </c>
       <c r="H36" t="str">
         <v>Home</v>
@@ -9136,19 +9144,19 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>grip</v>
+        <v>deskbands</v>
       </c>
       <c r="M36" t="str">
-        <v>Grip Trainer</v>
+        <v>Desk Bands</v>
       </c>
       <c r="N36" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O36">
-        <v>200</v>
+        <v>iso</v>
+      </c>
+      <c r="O36" t="str">
+        <v/>
       </c>
       <c r="P36" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q36" t="str">
         <v/>
@@ -9162,10 +9170,10 @@
         <v>A</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C37" t="str">
-        <v>Day 3</v>
+        <v>Day 4</v>
       </c>
       <c r="D37" t="str">
         <v/>
@@ -9174,13 +9182,13 @@
         <v/>
       </c>
       <c r="F37">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G37" t="str">
-        <v>A-d3s9</v>
+        <v>A-sled4</v>
       </c>
       <c r="H37" t="str">
-        <v>Home</v>
+        <v>Optional</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -9189,25 +9197,25 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v/>
+        <v>Optional</v>
       </c>
       <c r="L37" t="str">
-        <v>deskbands</v>
+        <v>sledlat</v>
       </c>
       <c r="M37" t="str">
-        <v>Desk Bands</v>
+        <v>Sled push → lateral pull</v>
       </c>
       <c r="N37" t="str">
-        <v>iso</v>
+        <v>exp</v>
       </c>
       <c r="O37" t="str">
         <v/>
       </c>
       <c r="P37" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q37" t="str">
-        <v/>
+        <v>1 × 3</v>
       </c>
       <c r="R37" t="str">
         <v/>
@@ -9230,40 +9238,40 @@
         <v/>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" t="str">
-        <v>A-sled4</v>
+        <v>A-d4s1</v>
       </c>
       <c r="H38" t="str">
-        <v>Optional</v>
+        <v>Regular</v>
       </c>
       <c r="I38" t="str">
-        <v/>
+        <v>Primary</v>
       </c>
       <c r="J38" t="str">
         <v/>
       </c>
       <c r="K38" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="L38" t="str">
-        <v>sledlat</v>
+        <v>suitcase</v>
       </c>
       <c r="M38" t="str">
-        <v>Sled push → lateral pull</v>
+        <v>Suitcase Bottom-Up, single-arm</v>
       </c>
       <c r="N38" t="str">
-        <v>exp</v>
-      </c>
-      <c r="O38" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="O38">
+        <v>20</v>
       </c>
       <c r="P38" t="str">
         <v/>
       </c>
       <c r="Q38" t="str">
-        <v>1 × 3</v>
+        <v>3 × 4 each arm</v>
       </c>
       <c r="R38" t="str">
         <v/>
@@ -9286,16 +9294,16 @@
         <v/>
       </c>
       <c r="F39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" t="str">
-        <v>A-d4s1</v>
+        <v>A-d4s2</v>
       </c>
       <c r="H39" t="str">
         <v>Regular</v>
       </c>
       <c r="I39" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J39" t="str">
         <v/>
@@ -9304,22 +9312,22 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>suitcase</v>
+        <v>innerthigh</v>
       </c>
       <c r="M39" t="str">
-        <v>Suitcase Bottom-Up, single-arm</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="N39" t="str">
-        <v/>
+        <v>strength</v>
       </c>
       <c r="O39">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="P39" t="str">
         <v/>
       </c>
       <c r="Q39" t="str">
-        <v>3 × 4 each arm</v>
+        <v/>
       </c>
       <c r="R39" t="str">
         <v/>
@@ -9342,10 +9350,10 @@
         <v/>
       </c>
       <c r="F40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G40" t="str">
-        <v>A-d4s2</v>
+        <v>A-d4s3</v>
       </c>
       <c r="H40" t="str">
         <v>Regular</v>
@@ -9360,25 +9368,25 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>innerthigh</v>
+        <v>romanadd</v>
       </c>
       <c r="M40" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Roman Chair Hip Adduction</v>
       </c>
       <c r="N40" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O40">
-        <v>180</v>
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
       </c>
       <c r="P40" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q40" t="str">
         <v/>
       </c>
       <c r="R40" t="str">
-        <v/>
+        <v>On the back-extension bench</v>
       </c>
     </row>
     <row r="41">
@@ -9398,43 +9406,43 @@
         <v/>
       </c>
       <c r="F41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G41" t="str">
-        <v>A-d4s3</v>
+        <v>A-d4s4</v>
       </c>
       <c r="H41" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I41" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J41" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K41" t="str">
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>romanadd</v>
+        <v>arnold</v>
       </c>
       <c r="M41" t="str">
-        <v>Roman Chair Hip Adduction</v>
+        <v>Arnold Press</v>
       </c>
       <c r="N41" t="str">
-        <v/>
-      </c>
-      <c r="O41" t="str">
-        <v/>
+        <v>strength</v>
+      </c>
+      <c r="O41">
+        <v>35</v>
       </c>
       <c r="P41" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q41" t="str">
         <v/>
       </c>
       <c r="R41" t="str">
-        <v>On the back-extension bench</v>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -9472,16 +9480,16 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>arnold</v>
+        <v>zercher</v>
       </c>
       <c r="M42" t="str">
-        <v>Arnold Press</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="N42" t="str">
         <v>strength</v>
       </c>
       <c r="O42">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="P42" t="str">
         <v/>
@@ -9510,10 +9518,10 @@
         <v/>
       </c>
       <c r="F43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G43" t="str">
-        <v>A-d4s4</v>
+        <v>A-d4s5</v>
       </c>
       <c r="H43" t="str">
         <v>Supersets</v>
@@ -9528,16 +9536,16 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>zercher</v>
+        <v>hipthrust</v>
       </c>
       <c r="M43" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="N43" t="str">
         <v>strength</v>
       </c>
       <c r="O43">
-        <v>50</v>
+        <v>320</v>
       </c>
       <c r="P43" t="str">
         <v/>
@@ -9584,16 +9592,16 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>hipthrust</v>
+        <v>chestpress</v>
       </c>
       <c r="M44" t="str">
-        <v>Hip Thrust</v>
+        <v>Chest Press</v>
       </c>
       <c r="N44" t="str">
-        <v>strength</v>
+        <v>hyp</v>
       </c>
       <c r="O44">
-        <v>320</v>
+        <v>25</v>
       </c>
       <c r="P44" t="str">
         <v/>
@@ -9622,16 +9630,16 @@
         <v/>
       </c>
       <c r="F45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G45" t="str">
-        <v>A-d4s5</v>
+        <v>A-d4s6</v>
       </c>
       <c r="H45" t="str">
         <v>Supersets</v>
       </c>
       <c r="I45" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J45" t="str">
         <v>superset</v>
@@ -9640,22 +9648,22 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>chestpress</v>
+        <v>zottman</v>
       </c>
       <c r="M45" t="str">
-        <v>Chest Press</v>
+        <v>Zottman Curl</v>
       </c>
       <c r="N45" t="str">
         <v>hyp</v>
       </c>
       <c r="O45">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="P45" t="str">
         <v/>
       </c>
       <c r="Q45" t="str">
-        <v/>
+        <v>3 × 15</v>
       </c>
       <c r="R45" t="str">
         <v/>
@@ -9696,13 +9704,13 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>zottman</v>
+        <v>kbleg</v>
       </c>
       <c r="M46" t="str">
-        <v>Zottman Curl</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="N46" t="str">
-        <v>hyp</v>
+        <v>iso</v>
       </c>
       <c r="O46">
         <v>15</v>
@@ -9711,7 +9719,7 @@
         <v/>
       </c>
       <c r="Q46" t="str">
-        <v>3 × 15</v>
+        <v>3 × 15 s hold</v>
       </c>
       <c r="R46" t="str">
         <v/>
@@ -9734,40 +9742,40 @@
         <v/>
       </c>
       <c r="F47">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G47" t="str">
-        <v>A-d4s6</v>
+        <v>A-d4s7</v>
       </c>
       <c r="H47" t="str">
-        <v>Supersets</v>
+        <v>Home</v>
       </c>
       <c r="I47" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J47" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K47" t="str">
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>kbleg</v>
+        <v>grip</v>
       </c>
       <c r="M47" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="N47" t="str">
-        <v>iso</v>
+        <v>strength</v>
       </c>
       <c r="O47">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="P47" t="str">
         <v/>
       </c>
       <c r="Q47" t="str">
-        <v>3 × 15 s hold</v>
+        <v/>
       </c>
       <c r="R47" t="str">
         <v/>
@@ -9790,10 +9798,10 @@
         <v/>
       </c>
       <c r="F48">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G48" t="str">
-        <v>A-d4s7</v>
+        <v>A-d4s8</v>
       </c>
       <c r="H48" t="str">
         <v>Home</v>
@@ -9808,19 +9816,19 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>grip</v>
+        <v>deskbands</v>
       </c>
       <c r="M48" t="str">
-        <v>Grip Trainer</v>
+        <v>Desk Bands</v>
       </c>
       <c r="N48" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O48">
-        <v>200</v>
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
       </c>
       <c r="P48" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q48" t="str">
         <v/>
@@ -9834,25 +9842,25 @@
         <v>A</v>
       </c>
       <c r="B49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C49" t="str">
-        <v>Day 4</v>
+        <v>Day 5</v>
       </c>
       <c r="D49" t="str">
         <v/>
       </c>
       <c r="E49" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="F49">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G49" t="str">
-        <v>A-d4s8</v>
+        <v>A-sled5</v>
       </c>
       <c r="H49" t="str">
-        <v>Home</v>
+        <v>Optional</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -9861,25 +9869,25 @@
         <v/>
       </c>
       <c r="K49" t="str">
-        <v/>
+        <v>Optional</v>
       </c>
       <c r="L49" t="str">
-        <v>deskbands</v>
+        <v>sledlat</v>
       </c>
       <c r="M49" t="str">
-        <v>Desk Bands</v>
+        <v>Sled push → lateral pull</v>
       </c>
       <c r="N49" t="str">
-        <v/>
+        <v>exp</v>
       </c>
       <c r="O49" t="str">
         <v/>
       </c>
       <c r="P49" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q49" t="str">
-        <v/>
+        <v>1 × 3</v>
       </c>
       <c r="R49" t="str">
         <v/>
@@ -9902,13 +9910,13 @@
         <v>Yes</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50" t="str">
-        <v>A-sled5</v>
+        <v>A-d5s3</v>
       </c>
       <c r="H50" t="str">
-        <v>Optional</v>
+        <v>Regular</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -9917,28 +9925,28 @@
         <v/>
       </c>
       <c r="K50" t="str">
-        <v>Optional</v>
+        <v/>
       </c>
       <c r="L50" t="str">
-        <v>sledlat</v>
+        <v>hack</v>
       </c>
       <c r="M50" t="str">
-        <v>Sled push → lateral pull</v>
+        <v>Hack Squat</v>
       </c>
       <c r="N50" t="str">
-        <v>exp</v>
-      </c>
-      <c r="O50" t="str">
-        <v/>
+        <v>hyp</v>
+      </c>
+      <c r="O50">
+        <v>270</v>
       </c>
       <c r="P50" t="str">
         <v/>
       </c>
       <c r="Q50" t="str">
-        <v>1 × 3</v>
+        <v/>
       </c>
       <c r="R50" t="str">
-        <v/>
+        <v>Feet low on the plate, narrow stance for quads</v>
       </c>
     </row>
     <row r="51">
@@ -9958,40 +9966,40 @@
         <v>Yes</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G51" t="str">
-        <v>A-d5s1</v>
+        <v>A-d5s4</v>
       </c>
       <c r="H51" t="str">
         <v>Regular</v>
       </c>
       <c r="I51" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J51" t="str">
-        <v/>
+        <v>either</v>
       </c>
       <c r="K51" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L51" t="str">
-        <v>cablecrunch</v>
+        <v>reardelt</v>
       </c>
       <c r="M51" t="str">
-        <v>Kneeling Cable Ab Crunch</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="N51" t="str">
-        <v>strength</v>
+        <v>iso</v>
       </c>
       <c r="O51">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P51" t="str">
         <v/>
       </c>
       <c r="Q51" t="str">
-        <v/>
+        <v>4 × 15 s per arm</v>
       </c>
       <c r="R51" t="str">
         <v/>
@@ -10017,31 +10025,31 @@
         <v>3</v>
       </c>
       <c r="G52" t="str">
-        <v>A-d5s3</v>
+        <v>A-d5s4</v>
       </c>
       <c r="H52" t="str">
         <v>Regular</v>
       </c>
       <c r="I52" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J52" t="str">
-        <v/>
+        <v>either</v>
       </c>
       <c r="K52" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L52" t="str">
-        <v>hack</v>
+        <v>facepull</v>
       </c>
       <c r="M52" t="str">
-        <v>Hack Squat</v>
+        <v>Face Pull</v>
       </c>
       <c r="N52" t="str">
-        <v>hyp</v>
+        <v>strength</v>
       </c>
       <c r="O52">
-        <v>270</v>
+        <v>30</v>
       </c>
       <c r="P52" t="str">
         <v/>
@@ -10050,7 +10058,7 @@
         <v/>
       </c>
       <c r="R52" t="str">
-        <v>Feet low on the plate, narrow stance for quads</v>
+        <v/>
       </c>
     </row>
     <row r="53">
@@ -10073,37 +10081,37 @@
         <v>4</v>
       </c>
       <c r="G53" t="str">
-        <v>A-d5s4</v>
+        <v>A-d5s5</v>
       </c>
       <c r="H53" t="str">
-        <v>Regular</v>
+        <v>Plyometric</v>
       </c>
       <c r="I53" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J53" t="str">
-        <v>either</v>
+        <v/>
       </c>
       <c r="K53" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L53" t="str">
-        <v>reardelt</v>
+        <v>trxpike</v>
       </c>
       <c r="M53" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>TRX Pike Push-Up</v>
       </c>
       <c r="N53" t="str">
-        <v>iso</v>
-      </c>
-      <c r="O53">
-        <v>50</v>
+        <v>exp</v>
+      </c>
+      <c r="O53" t="str">
+        <v/>
       </c>
       <c r="P53" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q53" t="str">
-        <v>4 × 15 s per arm</v>
+        <v/>
       </c>
       <c r="R53" t="str">
         <v/>
@@ -10126,37 +10134,37 @@
         <v>Yes</v>
       </c>
       <c r="F54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G54" t="str">
-        <v>A-d5s4</v>
+        <v>A-d5s6</v>
       </c>
       <c r="H54" t="str">
-        <v>Regular</v>
+        <v>Plyometric</v>
       </c>
       <c r="I54" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J54" t="str">
-        <v>either</v>
+        <v/>
       </c>
       <c r="K54" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L54" t="str">
-        <v>facepull</v>
+        <v>trxrow</v>
       </c>
       <c r="M54" t="str">
-        <v>Face Pull</v>
+        <v>TRX Wide-Grip Row</v>
       </c>
       <c r="N54" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O54">
-        <v>30</v>
+        <v>exp</v>
+      </c>
+      <c r="O54" t="str">
+        <v/>
       </c>
       <c r="P54" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q54" t="str">
         <v/>
@@ -10182,10 +10190,10 @@
         <v>Yes</v>
       </c>
       <c r="F55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G55" t="str">
-        <v>A-d5s5</v>
+        <v>A-d5s7</v>
       </c>
       <c r="H55" t="str">
         <v>Plyometric</v>
@@ -10200,10 +10208,10 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>trxpike</v>
+        <v>medball</v>
       </c>
       <c r="M55" t="str">
-        <v>TRX Pike Push-Up</v>
+        <v>Med Ball Rotational Scoop</v>
       </c>
       <c r="N55" t="str">
         <v>exp</v>
@@ -10212,7 +10220,7 @@
         <v/>
       </c>
       <c r="P55" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q55" t="str">
         <v/>
@@ -10238,10 +10246,10 @@
         <v>Yes</v>
       </c>
       <c r="F56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G56" t="str">
-        <v>A-d5s6</v>
+        <v>A-d5s8</v>
       </c>
       <c r="H56" t="str">
         <v>Plyometric</v>
@@ -10256,10 +10264,10 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>trxrow</v>
+        <v>latwall</v>
       </c>
       <c r="M56" t="str">
-        <v>TRX Wide-Grip Row</v>
+        <v>Lateral Wall Push</v>
       </c>
       <c r="N56" t="str">
         <v>exp</v>
@@ -10294,31 +10302,31 @@
         <v>Yes</v>
       </c>
       <c r="F57">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G57" t="str">
-        <v>A-d5s7</v>
+        <v>A-xmuy1u0ehkgt</v>
       </c>
       <c r="H57" t="str">
-        <v>Plyometric</v>
+        <v>Supersets</v>
       </c>
       <c r="I57" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J57" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K57" t="str">
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>medball</v>
+        <v>seated-cable-crunch</v>
       </c>
       <c r="M57" t="str">
-        <v>Med Ball Rotational Scoop</v>
+        <v>Seated Cable Crunch</v>
       </c>
       <c r="N57" t="str">
-        <v>exp</v>
+        <v>strength</v>
       </c>
       <c r="O57" t="str">
         <v/>
@@ -10353,34 +10361,34 @@
         <v>8</v>
       </c>
       <c r="G58" t="str">
-        <v>A-d5s8</v>
+        <v>A-xmuy1u0ehkgt</v>
       </c>
       <c r="H58" t="str">
-        <v>Plyometric</v>
+        <v>Supersets</v>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J58" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K58" t="str">
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>latwall</v>
+        <v>wristpd</v>
       </c>
       <c r="M58" t="str">
-        <v>Lateral Wall Push</v>
+        <v>Cable Wrist Pulldown</v>
       </c>
       <c r="N58" t="str">
-        <v>exp</v>
+        <v>strength</v>
       </c>
       <c r="O58" t="str">
         <v/>
       </c>
       <c r="P58" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q58" t="str">
         <v/>
@@ -11305,7 +11313,7 @@
         <v>4</v>
       </c>
       <c r="G75" t="str">
-        <v>B-d1s3</v>
+        <v>B-d1s4</v>
       </c>
       <c r="H75" t="str">
         <v>Regular</v>
@@ -11320,16 +11328,16 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>wristpd</v>
+        <v>platerot</v>
       </c>
       <c r="M75" t="str">
-        <v>Cable Wrist Pulldown</v>
+        <v>Plate Torso Rotation</v>
       </c>
       <c r="N75" t="str">
-        <v>hyp</v>
+        <v>strength</v>
       </c>
       <c r="O75">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="P75" t="str">
         <v/>
@@ -11361,7 +11369,7 @@
         <v>5</v>
       </c>
       <c r="G76" t="str">
-        <v>B-d1s4</v>
+        <v>B-d1s5</v>
       </c>
       <c r="H76" t="str">
         <v>Regular</v>
@@ -11376,16 +11384,16 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>platerot</v>
+        <v>innerthigh</v>
       </c>
       <c r="M76" t="str">
-        <v>Plate Torso Rotation</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="N76" t="str">
         <v>strength</v>
       </c>
       <c r="O76">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="P76" t="str">
         <v/>
@@ -11417,7 +11425,7 @@
         <v>6</v>
       </c>
       <c r="G77" t="str">
-        <v>B-d1s5</v>
+        <v>B-d1s6</v>
       </c>
       <c r="H77" t="str">
         <v>Regular</v>
@@ -11432,16 +11440,16 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>innerthigh</v>
+        <v>outerthigh</v>
       </c>
       <c r="M77" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Outer Thigh Adduction</v>
       </c>
       <c r="N77" t="str">
         <v>strength</v>
       </c>
       <c r="O77">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="P77" t="str">
         <v/>
@@ -11473,7 +11481,7 @@
         <v>7</v>
       </c>
       <c r="G78" t="str">
-        <v>B-d1s6</v>
+        <v>B-d1s7</v>
       </c>
       <c r="H78" t="str">
         <v>Regular</v>
@@ -11488,19 +11496,19 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>outerthigh</v>
+        <v>qlext</v>
       </c>
       <c r="M78" t="str">
-        <v>Outer Thigh Adduction</v>
+        <v>Side Lateral QL Extension</v>
       </c>
       <c r="N78" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O78">
-        <v>160</v>
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
       </c>
       <c r="P78" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q78" t="str">
         <v/>
@@ -11529,34 +11537,34 @@
         <v>8</v>
       </c>
       <c r="G79" t="str">
-        <v>B-d1s7</v>
+        <v>B-d1s8</v>
       </c>
       <c r="H79" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I79" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J79" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K79" t="str">
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>qlext</v>
+        <v>chestpress</v>
       </c>
       <c r="M79" t="str">
-        <v>Side Lateral QL Extension</v>
+        <v>Chest Press</v>
       </c>
       <c r="N79" t="str">
-        <v/>
-      </c>
-      <c r="O79" t="str">
-        <v/>
+        <v>strength</v>
+      </c>
+      <c r="O79">
+        <v>35</v>
       </c>
       <c r="P79" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q79" t="str">
         <v/>
@@ -11582,7 +11590,7 @@
         <v/>
       </c>
       <c r="F80">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G80" t="str">
         <v>B-d1s8</v>
@@ -11600,16 +11608,16 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>chestpress</v>
+        <v>zercher</v>
       </c>
       <c r="M80" t="str">
-        <v>Chest Press</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="N80" t="str">
         <v>strength</v>
       </c>
       <c r="O80">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="P80" t="str">
         <v/>
@@ -11641,13 +11649,13 @@
         <v>9</v>
       </c>
       <c r="G81" t="str">
-        <v>B-d1s8</v>
+        <v>B-d1s9</v>
       </c>
       <c r="H81" t="str">
         <v>Supersets</v>
       </c>
       <c r="I81" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J81" t="str">
         <v>superset</v>
@@ -11656,22 +11664,22 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>zercher</v>
+        <v>zottman</v>
       </c>
       <c r="M81" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Zottman Curl</v>
       </c>
       <c r="N81" t="str">
-        <v>strength</v>
+        <v>hyp</v>
       </c>
       <c r="O81">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="P81" t="str">
         <v/>
       </c>
       <c r="Q81" t="str">
-        <v/>
+        <v>3 × 15</v>
       </c>
       <c r="R81" t="str">
         <v/>
@@ -11694,7 +11702,7 @@
         <v/>
       </c>
       <c r="F82">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G82" t="str">
         <v>B-d1s9</v>
@@ -11712,13 +11720,13 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>zottman</v>
+        <v>kbleg</v>
       </c>
       <c r="M82" t="str">
-        <v>Zottman Curl</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="N82" t="str">
-        <v>hyp</v>
+        <v>iso</v>
       </c>
       <c r="O82">
         <v>15</v>
@@ -11727,7 +11735,7 @@
         <v/>
       </c>
       <c r="Q82" t="str">
-        <v>3 × 15</v>
+        <v>3 × 15 s hold</v>
       </c>
       <c r="R82" t="str">
         <v/>
@@ -11753,40 +11761,40 @@
         <v>10</v>
       </c>
       <c r="G83" t="str">
-        <v>B-d1s9</v>
+        <v>B-d1s10</v>
       </c>
       <c r="H83" t="str">
-        <v>Supersets</v>
+        <v>Home</v>
       </c>
       <c r="I83" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J83" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K83" t="str">
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>kbleg</v>
+        <v>grip</v>
       </c>
       <c r="M83" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="N83" t="str">
-        <v>iso</v>
+        <v>strength</v>
       </c>
       <c r="O83">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="P83" t="str">
         <v/>
       </c>
       <c r="Q83" t="str">
-        <v>3 × 15 s hold</v>
+        <v/>
       </c>
       <c r="R83" t="str">
-        <v/>
+        <v>With a grip trainer</v>
       </c>
     </row>
     <row r="84">
@@ -11809,7 +11817,7 @@
         <v>11</v>
       </c>
       <c r="G84" t="str">
-        <v>B-d1s10</v>
+        <v>B-d1s11</v>
       </c>
       <c r="H84" t="str">
         <v>Home</v>
@@ -11824,16 +11832,16 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>grip</v>
+        <v>canoe</v>
       </c>
       <c r="M84" t="str">
-        <v>Grip Trainer</v>
+        <v>Canoe Stretch</v>
       </c>
       <c r="N84" t="str">
-        <v>strength</v>
+        <v/>
       </c>
       <c r="O84">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="P84" t="str">
         <v/>
@@ -11842,7 +11850,7 @@
         <v/>
       </c>
       <c r="R84" t="str">
-        <v>With a grip trainer</v>
+        <v>With a stick or barbell</v>
       </c>
     </row>
     <row r="85">
@@ -11850,25 +11858,25 @@
         <v>B</v>
       </c>
       <c r="B85">
+        <v>2</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Day 2</v>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85">
         <v>1</v>
       </c>
-      <c r="C85" t="str">
-        <v>Day 1</v>
-      </c>
-      <c r="D85" t="str">
-        <v/>
-      </c>
-      <c r="E85" t="str">
-        <v/>
-      </c>
-      <c r="F85">
-        <v>12</v>
-      </c>
       <c r="G85" t="str">
-        <v>B-d1s11</v>
+        <v>B-sled2</v>
       </c>
       <c r="H85" t="str">
-        <v>Home</v>
+        <v>Optional</v>
       </c>
       <c r="I85" t="str">
         <v/>
@@ -11877,28 +11885,28 @@
         <v/>
       </c>
       <c r="K85" t="str">
-        <v/>
+        <v>Optional</v>
       </c>
       <c r="L85" t="str">
-        <v>canoe</v>
+        <v>sled</v>
       </c>
       <c r="M85" t="str">
-        <v>Canoe Stretch</v>
+        <v>Sled push → pull</v>
       </c>
       <c r="N85" t="str">
-        <v/>
-      </c>
-      <c r="O85">
-        <v>10</v>
+        <v>exp</v>
+      </c>
+      <c r="O85" t="str">
+        <v/>
       </c>
       <c r="P85" t="str">
         <v/>
       </c>
       <c r="Q85" t="str">
-        <v/>
+        <v>1 × 3</v>
       </c>
       <c r="R85" t="str">
-        <v>With a stick or barbell</v>
+        <v/>
       </c>
     </row>
     <row r="86">
@@ -11918,40 +11926,40 @@
         <v/>
       </c>
       <c r="F86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G86" t="str">
-        <v>B-sled2</v>
+        <v>B-d2s1</v>
       </c>
       <c r="H86" t="str">
-        <v>Optional</v>
+        <v>Regular</v>
       </c>
       <c r="I86" t="str">
-        <v/>
+        <v>Primary</v>
       </c>
       <c r="J86" t="str">
-        <v/>
+        <v>either</v>
       </c>
       <c r="K86" t="str">
-        <v>Optional</v>
+        <v>Whichever is free</v>
       </c>
       <c r="L86" t="str">
-        <v>sled</v>
+        <v>farmers</v>
       </c>
       <c r="M86" t="str">
-        <v>Sled push → pull</v>
+        <v>Farmers Carry</v>
       </c>
       <c r="N86" t="str">
-        <v>exp</v>
-      </c>
-      <c r="O86" t="str">
-        <v/>
+        <v>strength</v>
+      </c>
+      <c r="O86">
+        <v>40</v>
       </c>
       <c r="P86" t="str">
         <v/>
       </c>
       <c r="Q86" t="str">
-        <v>1 × 3</v>
+        <v/>
       </c>
       <c r="R86" t="str">
         <v/>
@@ -11992,10 +12000,10 @@
         <v>Whichever is free</v>
       </c>
       <c r="L87" t="str">
-        <v>farmers</v>
+        <v>dblunge</v>
       </c>
       <c r="M87" t="str">
-        <v>Farmers Carry</v>
+        <v>DB Lunge</v>
       </c>
       <c r="N87" t="str">
         <v>strength</v>
@@ -12030,10 +12038,10 @@
         <v/>
       </c>
       <c r="F88">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G88" t="str">
-        <v>B-d2s1</v>
+        <v>B-d2s2</v>
       </c>
       <c r="H88" t="str">
         <v>Regular</v>
@@ -12042,22 +12050,22 @@
         <v>Primary</v>
       </c>
       <c r="J88" t="str">
-        <v>either</v>
+        <v/>
       </c>
       <c r="K88" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L88" t="str">
-        <v>dblunge</v>
+        <v>ohtri</v>
       </c>
       <c r="M88" t="str">
-        <v>DB Lunge</v>
+        <v>Overhead Tricep Extension</v>
       </c>
       <c r="N88" t="str">
         <v>strength</v>
       </c>
       <c r="O88">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="P88" t="str">
         <v/>
@@ -12086,40 +12094,40 @@
         <v/>
       </c>
       <c r="F89">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G89" t="str">
-        <v>B-d2s2</v>
+        <v>B-d2s3</v>
       </c>
       <c r="H89" t="str">
         <v>Regular</v>
       </c>
       <c r="I89" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J89" t="str">
-        <v/>
+        <v>either</v>
       </c>
       <c r="K89" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L89" t="str">
-        <v>ohtri</v>
+        <v>reardelt</v>
       </c>
       <c r="M89" t="str">
-        <v>Overhead Tricep Extension</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="N89" t="str">
-        <v>strength</v>
+        <v>iso</v>
       </c>
       <c r="O89">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="P89" t="str">
         <v/>
       </c>
       <c r="Q89" t="str">
-        <v/>
+        <v>4 × 15 s per arm</v>
       </c>
       <c r="R89" t="str">
         <v/>
@@ -12160,22 +12168,22 @@
         <v>Whichever is free</v>
       </c>
       <c r="L90" t="str">
-        <v>reardelt</v>
+        <v>facepull</v>
       </c>
       <c r="M90" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Face Pull</v>
       </c>
       <c r="N90" t="str">
-        <v>iso</v>
+        <v>strength</v>
       </c>
       <c r="O90">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P90" t="str">
         <v/>
       </c>
       <c r="Q90" t="str">
-        <v>4 × 15 s per arm</v>
+        <v/>
       </c>
       <c r="R90" t="str">
         <v/>
@@ -12198,34 +12206,34 @@
         <v/>
       </c>
       <c r="F91">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G91" t="str">
-        <v>B-d2s3</v>
+        <v>B-d2s5</v>
       </c>
       <c r="H91" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I91" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J91" t="str">
-        <v>either</v>
+        <v>superset</v>
       </c>
       <c r="K91" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L91" t="str">
-        <v>facepull</v>
+        <v>hipthrust</v>
       </c>
       <c r="M91" t="str">
-        <v>Face Pull</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="N91" t="str">
         <v>strength</v>
       </c>
       <c r="O91">
-        <v>30</v>
+        <v>320</v>
       </c>
       <c r="P91" t="str">
         <v/>
@@ -12257,31 +12265,31 @@
         <v>5</v>
       </c>
       <c r="G92" t="str">
-        <v>B-d2s4</v>
+        <v>B-d2s5</v>
       </c>
       <c r="H92" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I92" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J92" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K92" t="str">
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>cablecrunch</v>
+        <v>chestpress</v>
       </c>
       <c r="M92" t="str">
-        <v>Kneeling Cable Ab Crunch</v>
+        <v>Chest Press</v>
       </c>
       <c r="N92" t="str">
-        <v>strength</v>
+        <v>hyp</v>
       </c>
       <c r="O92">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="P92" t="str">
         <v/>
@@ -12313,13 +12321,13 @@
         <v>6</v>
       </c>
       <c r="G93" t="str">
-        <v>B-d2s5</v>
+        <v>B-d2s6</v>
       </c>
       <c r="H93" t="str">
         <v>Supersets</v>
       </c>
       <c r="I93" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J93" t="str">
         <v>superset</v>
@@ -12328,16 +12336,16 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>hipthrust</v>
+        <v>bss</v>
       </c>
       <c r="M93" t="str">
-        <v>Hip Thrust</v>
+        <v>Bulgarian Split Squat</v>
       </c>
       <c r="N93" t="str">
         <v>strength</v>
       </c>
       <c r="O93">
-        <v>320</v>
+        <v>40</v>
       </c>
       <c r="P93" t="str">
         <v/>
@@ -12369,13 +12377,13 @@
         <v>6</v>
       </c>
       <c r="G94" t="str">
-        <v>B-d2s5</v>
+        <v>B-d2s6</v>
       </c>
       <c r="H94" t="str">
         <v>Supersets</v>
       </c>
       <c r="I94" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J94" t="str">
         <v>superset</v>
@@ -12384,16 +12392,16 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>chestpress</v>
+        <v>legcurl</v>
       </c>
       <c r="M94" t="str">
-        <v>Chest Press</v>
+        <v>Prone Leg Curl</v>
       </c>
       <c r="N94" t="str">
-        <v>hyp</v>
+        <v>strength</v>
       </c>
       <c r="O94">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="P94" t="str">
         <v/>
@@ -12425,7 +12433,7 @@
         <v>7</v>
       </c>
       <c r="G95" t="str">
-        <v>B-d2s6</v>
+        <v>B-xmuy1nsai5fs</v>
       </c>
       <c r="H95" t="str">
         <v>Supersets</v>
@@ -12440,16 +12448,16 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>bss</v>
+        <v>seated-cable-crunch</v>
       </c>
       <c r="M95" t="str">
-        <v>Bulgarian Split Squat</v>
+        <v>Seated Cable Crunch</v>
       </c>
       <c r="N95" t="str">
         <v>strength</v>
       </c>
-      <c r="O95">
-        <v>40</v>
+      <c r="O95" t="str">
+        <v/>
       </c>
       <c r="P95" t="str">
         <v/>
@@ -12481,7 +12489,7 @@
         <v>7</v>
       </c>
       <c r="G96" t="str">
-        <v>B-d2s6</v>
+        <v>B-xmuy1nsai5fs</v>
       </c>
       <c r="H96" t="str">
         <v>Supersets</v>
@@ -12496,16 +12504,16 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>legcurl</v>
+        <v>wristpd</v>
       </c>
       <c r="M96" t="str">
-        <v>Prone Leg Curl</v>
+        <v>Cable Wrist Pulldown</v>
       </c>
       <c r="N96" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O96">
-        <v>50</v>
+        <v>hyp</v>
+      </c>
+      <c r="O96" t="str">
+        <v/>
       </c>
       <c r="P96" t="str">
         <v/>
@@ -12817,7 +12825,7 @@
         <v>4</v>
       </c>
       <c r="G102" t="str">
-        <v>B-d3s3</v>
+        <v>B-d3s4</v>
       </c>
       <c r="H102" t="str">
         <v>Regular</v>
@@ -12832,16 +12840,16 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>wristpd</v>
+        <v>platerot</v>
       </c>
       <c r="M102" t="str">
-        <v>Cable Wrist Pulldown</v>
+        <v>Plate Torso Rotation</v>
       </c>
       <c r="N102" t="str">
-        <v>hyp</v>
+        <v>strength</v>
       </c>
       <c r="O102">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="P102" t="str">
         <v/>
@@ -12873,7 +12881,7 @@
         <v>5</v>
       </c>
       <c r="G103" t="str">
-        <v>B-d3s4</v>
+        <v>B-d3s5</v>
       </c>
       <c r="H103" t="str">
         <v>Regular</v>
@@ -12882,28 +12890,28 @@
         <v>Accessory</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>either</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L103" t="str">
-        <v>platerot</v>
+        <v>reardelt</v>
       </c>
       <c r="M103" t="str">
-        <v>Plate Torso Rotation</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="N103" t="str">
-        <v>strength</v>
+        <v>iso</v>
       </c>
       <c r="O103">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="P103" t="str">
         <v/>
       </c>
       <c r="Q103" t="str">
-        <v/>
+        <v>4 × 15 s per arm</v>
       </c>
       <c r="R103" t="str">
         <v/>
@@ -12926,7 +12934,7 @@
         <v/>
       </c>
       <c r="F104">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G104" t="str">
         <v>B-d3s5</v>
@@ -12944,22 +12952,22 @@
         <v>Whichever is free</v>
       </c>
       <c r="L104" t="str">
-        <v>reardelt</v>
+        <v>facepull</v>
       </c>
       <c r="M104" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Face Pull</v>
       </c>
       <c r="N104" t="str">
-        <v>iso</v>
+        <v>strength</v>
       </c>
       <c r="O104">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P104" t="str">
         <v/>
       </c>
       <c r="Q104" t="str">
-        <v>4 × 15 s per arm</v>
+        <v/>
       </c>
       <c r="R104" t="str">
         <v/>
@@ -12985,28 +12993,28 @@
         <v>6</v>
       </c>
       <c r="G105" t="str">
-        <v>B-d3s5</v>
+        <v>B-d3s6</v>
       </c>
       <c r="H105" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I105" t="str">
         <v>Accessory</v>
       </c>
       <c r="J105" t="str">
-        <v>either</v>
+        <v>superset</v>
       </c>
       <c r="K105" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>facepull</v>
+        <v>cablepunch</v>
       </c>
       <c r="M105" t="str">
-        <v>Face Pull</v>
+        <v>Cable Punch ISO hold</v>
       </c>
       <c r="N105" t="str">
-        <v>strength</v>
+        <v>iso</v>
       </c>
       <c r="O105">
         <v>30</v>
@@ -13015,7 +13023,7 @@
         <v/>
       </c>
       <c r="Q105" t="str">
-        <v/>
+        <v>4 × 30 s hold</v>
       </c>
       <c r="R105" t="str">
         <v/>
@@ -13038,7 +13046,7 @@
         <v/>
       </c>
       <c r="F106">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G106" t="str">
         <v>B-d3s6</v>
@@ -13056,13 +13064,13 @@
         <v/>
       </c>
       <c r="L106" t="str">
-        <v>cablepunch</v>
+        <v>cablerow</v>
       </c>
       <c r="M106" t="str">
-        <v>Cable Punch ISO hold</v>
+        <v>Explosive Unilateral Cable Row</v>
       </c>
       <c r="N106" t="str">
-        <v>iso</v>
+        <v>exp</v>
       </c>
       <c r="O106">
         <v>30</v>
@@ -13071,7 +13079,7 @@
         <v/>
       </c>
       <c r="Q106" t="str">
-        <v>4 × 30 s hold</v>
+        <v/>
       </c>
       <c r="R106" t="str">
         <v/>
@@ -13097,31 +13105,31 @@
         <v>7</v>
       </c>
       <c r="G107" t="str">
-        <v>B-d3s6</v>
+        <v>B-d3s7</v>
       </c>
       <c r="H107" t="str">
-        <v>Supersets</v>
+        <v>Home</v>
       </c>
       <c r="I107" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J107" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K107" t="str">
         <v/>
       </c>
       <c r="L107" t="str">
-        <v>cablerow</v>
+        <v>grip</v>
       </c>
       <c r="M107" t="str">
-        <v>Explosive Unilateral Cable Row</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="N107" t="str">
-        <v>exp</v>
+        <v>strength</v>
       </c>
       <c r="O107">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="P107" t="str">
         <v/>
@@ -13130,7 +13138,7 @@
         <v/>
       </c>
       <c r="R107" t="str">
-        <v/>
+        <v>With a grip trainer</v>
       </c>
     </row>
     <row r="108">
@@ -13153,7 +13161,7 @@
         <v>8</v>
       </c>
       <c r="G108" t="str">
-        <v>B-d3s7</v>
+        <v>B-d3s8</v>
       </c>
       <c r="H108" t="str">
         <v>Home</v>
@@ -13168,16 +13176,16 @@
         <v/>
       </c>
       <c r="L108" t="str">
-        <v>grip</v>
+        <v>deskbands</v>
       </c>
       <c r="M108" t="str">
-        <v>Grip Trainer</v>
+        <v>Desk Bands</v>
       </c>
       <c r="N108" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O108">
-        <v>200</v>
+        <v/>
+      </c>
+      <c r="O108" t="str">
+        <v/>
       </c>
       <c r="P108" t="str">
         <v/>
@@ -13186,7 +13194,7 @@
         <v/>
       </c>
       <c r="R108" t="str">
-        <v>With a grip trainer</v>
+        <v>With a resistance band</v>
       </c>
     </row>
     <row r="109">
@@ -13194,10 +13202,10 @@
         <v>B</v>
       </c>
       <c r="B109">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C109" t="str">
-        <v>Day 3</v>
+        <v>Day 4</v>
       </c>
       <c r="D109" t="str">
         <v/>
@@ -13206,13 +13214,13 @@
         <v/>
       </c>
       <c r="F109">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G109" t="str">
-        <v>B-d3s8</v>
+        <v>B-sled4</v>
       </c>
       <c r="H109" t="str">
-        <v>Home</v>
+        <v>Optional</v>
       </c>
       <c r="I109" t="str">
         <v/>
@@ -13221,16 +13229,16 @@
         <v/>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>Optional</v>
       </c>
       <c r="L109" t="str">
-        <v>deskbands</v>
+        <v>sled</v>
       </c>
       <c r="M109" t="str">
-        <v>Desk Bands</v>
+        <v>Sled push → pull</v>
       </c>
       <c r="N109" t="str">
-        <v/>
+        <v>exp</v>
       </c>
       <c r="O109" t="str">
         <v/>
@@ -13239,10 +13247,10 @@
         <v/>
       </c>
       <c r="Q109" t="str">
-        <v/>
+        <v>1 × 3</v>
       </c>
       <c r="R109" t="str">
-        <v>With a resistance band</v>
+        <v/>
       </c>
     </row>
     <row r="110">
@@ -13262,40 +13270,40 @@
         <v/>
       </c>
       <c r="F110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G110" t="str">
-        <v>B-sled4</v>
+        <v>B-d4s1</v>
       </c>
       <c r="H110" t="str">
-        <v>Optional</v>
+        <v>Regular</v>
       </c>
       <c r="I110" t="str">
-        <v/>
+        <v>Primary</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>either</v>
       </c>
       <c r="K110" t="str">
-        <v>Optional</v>
+        <v>Whichever is free</v>
       </c>
       <c r="L110" t="str">
-        <v>sled</v>
+        <v>farmers</v>
       </c>
       <c r="M110" t="str">
-        <v>Sled push → pull</v>
+        <v>Farmers Carry</v>
       </c>
       <c r="N110" t="str">
-        <v>exp</v>
-      </c>
-      <c r="O110" t="str">
-        <v/>
+        <v>strength</v>
+      </c>
+      <c r="O110">
+        <v>40</v>
       </c>
       <c r="P110" t="str">
         <v/>
       </c>
       <c r="Q110" t="str">
-        <v>1 × 3</v>
+        <v/>
       </c>
       <c r="R110" t="str">
         <v/>
@@ -13336,10 +13344,10 @@
         <v>Whichever is free</v>
       </c>
       <c r="L111" t="str">
-        <v>farmers</v>
+        <v>dblunge</v>
       </c>
       <c r="M111" t="str">
-        <v>Farmers Carry</v>
+        <v>DB Lunge</v>
       </c>
       <c r="N111" t="str">
         <v>strength</v>
@@ -13374,34 +13382,34 @@
         <v/>
       </c>
       <c r="F112">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G112" t="str">
-        <v>B-d4s1</v>
+        <v>B-d4s2</v>
       </c>
       <c r="H112" t="str">
         <v>Regular</v>
       </c>
       <c r="I112" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J112" t="str">
-        <v>either</v>
+        <v/>
       </c>
       <c r="K112" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L112" t="str">
-        <v>dblunge</v>
+        <v>innerthigh</v>
       </c>
       <c r="M112" t="str">
-        <v>DB Lunge</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="N112" t="str">
         <v>strength</v>
       </c>
       <c r="O112">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="P112" t="str">
         <v/>
@@ -13430,10 +13438,10 @@
         <v/>
       </c>
       <c r="F113">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G113" t="str">
-        <v>B-d4s2</v>
+        <v>B-d4s3</v>
       </c>
       <c r="H113" t="str">
         <v>Regular</v>
@@ -13448,16 +13456,16 @@
         <v/>
       </c>
       <c r="L113" t="str">
-        <v>innerthigh</v>
+        <v>outerthigh</v>
       </c>
       <c r="M113" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Outer Thigh Adduction</v>
       </c>
       <c r="N113" t="str">
         <v>strength</v>
       </c>
       <c r="O113">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="P113" t="str">
         <v/>
@@ -13486,34 +13494,34 @@
         <v/>
       </c>
       <c r="F114">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G114" t="str">
-        <v>B-d4s3</v>
+        <v>B-d4s4</v>
       </c>
       <c r="H114" t="str">
-        <v>Regular</v>
+        <v>Supersets</v>
       </c>
       <c r="I114" t="str">
-        <v>Accessory</v>
+        <v>Primary</v>
       </c>
       <c r="J114" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K114" t="str">
         <v/>
       </c>
       <c r="L114" t="str">
-        <v>outerthigh</v>
+        <v>arnold</v>
       </c>
       <c r="M114" t="str">
-        <v>Outer Thigh Adduction</v>
+        <v>Arnold Press</v>
       </c>
       <c r="N114" t="str">
         <v>strength</v>
       </c>
       <c r="O114">
-        <v>160</v>
+        <v>35</v>
       </c>
       <c r="P114" t="str">
         <v/>
@@ -13560,16 +13568,16 @@
         <v/>
       </c>
       <c r="L115" t="str">
-        <v>arnold</v>
+        <v>zercher</v>
       </c>
       <c r="M115" t="str">
-        <v>Arnold Press</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="N115" t="str">
         <v>strength</v>
       </c>
       <c r="O115">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="P115" t="str">
         <v/>
@@ -13598,10 +13606,10 @@
         <v/>
       </c>
       <c r="F116">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G116" t="str">
-        <v>B-d4s4</v>
+        <v>B-d4s5</v>
       </c>
       <c r="H116" t="str">
         <v>Supersets</v>
@@ -13616,16 +13624,16 @@
         <v/>
       </c>
       <c r="L116" t="str">
-        <v>zercher</v>
+        <v>hipthrust</v>
       </c>
       <c r="M116" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="N116" t="str">
         <v>strength</v>
       </c>
       <c r="O116">
-        <v>50</v>
+        <v>320</v>
       </c>
       <c r="P116" t="str">
         <v/>
@@ -13672,16 +13680,16 @@
         <v/>
       </c>
       <c r="L117" t="str">
-        <v>hipthrust</v>
+        <v>chestpress</v>
       </c>
       <c r="M117" t="str">
-        <v>Hip Thrust</v>
+        <v>Chest Press</v>
       </c>
       <c r="N117" t="str">
-        <v>strength</v>
+        <v>hyp</v>
       </c>
       <c r="O117">
-        <v>320</v>
+        <v>25</v>
       </c>
       <c r="P117" t="str">
         <v/>
@@ -13710,10 +13718,10 @@
         <v/>
       </c>
       <c r="F118">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G118" t="str">
-        <v>B-d4s5</v>
+        <v>B-d4s6</v>
       </c>
       <c r="H118" t="str">
         <v>Supersets</v>
@@ -13728,16 +13736,16 @@
         <v/>
       </c>
       <c r="L118" t="str">
-        <v>chestpress</v>
+        <v>bss</v>
       </c>
       <c r="M118" t="str">
-        <v>Chest Press</v>
+        <v>Bulgarian Split Squat</v>
       </c>
       <c r="N118" t="str">
-        <v>hyp</v>
+        <v>strength</v>
       </c>
       <c r="O118">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="P118" t="str">
         <v/>
@@ -13784,16 +13792,16 @@
         <v/>
       </c>
       <c r="L119" t="str">
-        <v>bss</v>
+        <v>legcurl</v>
       </c>
       <c r="M119" t="str">
-        <v>Bulgarian Split Squat</v>
+        <v>Prone Leg Curl</v>
       </c>
       <c r="N119" t="str">
         <v>strength</v>
       </c>
       <c r="O119">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P119" t="str">
         <v/>
@@ -13822,16 +13830,16 @@
         <v/>
       </c>
       <c r="F120">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G120" t="str">
-        <v>B-d4s6</v>
+        <v>B-d4s7</v>
       </c>
       <c r="H120" t="str">
         <v>Supersets</v>
       </c>
       <c r="I120" t="str">
-        <v>Primary</v>
+        <v>Accessory</v>
       </c>
       <c r="J120" t="str">
         <v>superset</v>
@@ -13840,22 +13848,22 @@
         <v/>
       </c>
       <c r="L120" t="str">
-        <v>legcurl</v>
+        <v>zottman</v>
       </c>
       <c r="M120" t="str">
-        <v>Prone Leg Curl</v>
+        <v>Zottman Curl</v>
       </c>
       <c r="N120" t="str">
-        <v>strength</v>
+        <v>hyp</v>
       </c>
       <c r="O120">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="P120" t="str">
         <v/>
       </c>
       <c r="Q120" t="str">
-        <v/>
+        <v>3 × 15</v>
       </c>
       <c r="R120" t="str">
         <v/>
@@ -13896,13 +13904,13 @@
         <v/>
       </c>
       <c r="L121" t="str">
-        <v>zottman</v>
+        <v>kbleg</v>
       </c>
       <c r="M121" t="str">
-        <v>Zottman Curl</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="N121" t="str">
-        <v>hyp</v>
+        <v>iso</v>
       </c>
       <c r="O121">
         <v>15</v>
@@ -13911,7 +13919,7 @@
         <v/>
       </c>
       <c r="Q121" t="str">
-        <v>3 × 15</v>
+        <v>3 × 15 s hold</v>
       </c>
       <c r="R121" t="str">
         <v/>
@@ -13934,43 +13942,43 @@
         <v/>
       </c>
       <c r="F122">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G122" t="str">
-        <v>B-d4s7</v>
+        <v>B-d4s8</v>
       </c>
       <c r="H122" t="str">
-        <v>Supersets</v>
+        <v>Home</v>
       </c>
       <c r="I122" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J122" t="str">
-        <v>superset</v>
+        <v/>
       </c>
       <c r="K122" t="str">
         <v/>
       </c>
       <c r="L122" t="str">
-        <v>kbleg</v>
+        <v>grip</v>
       </c>
       <c r="M122" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="N122" t="str">
-        <v>iso</v>
+        <v>strength</v>
       </c>
       <c r="O122">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="P122" t="str">
         <v/>
       </c>
       <c r="Q122" t="str">
-        <v>3 × 15 s hold</v>
+        <v/>
       </c>
       <c r="R122" t="str">
-        <v/>
+        <v>With a grip trainer</v>
       </c>
     </row>
     <row r="123">
@@ -13990,10 +13998,10 @@
         <v/>
       </c>
       <c r="F123">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G123" t="str">
-        <v>B-d4s8</v>
+        <v>B-d4s9</v>
       </c>
       <c r="H123" t="str">
         <v>Home</v>
@@ -14008,16 +14016,16 @@
         <v/>
       </c>
       <c r="L123" t="str">
-        <v>grip</v>
+        <v>deskbands</v>
       </c>
       <c r="M123" t="str">
-        <v>Grip Trainer</v>
+        <v>Desk Bands</v>
       </c>
       <c r="N123" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O123">
-        <v>200</v>
+        <v/>
+      </c>
+      <c r="O123" t="str">
+        <v/>
       </c>
       <c r="P123" t="str">
         <v/>
@@ -14026,7 +14034,7 @@
         <v/>
       </c>
       <c r="R123" t="str">
-        <v>With a grip trainer</v>
+        <v>With a resistance band</v>
       </c>
     </row>
     <row r="124">
@@ -14034,25 +14042,25 @@
         <v>B</v>
       </c>
       <c r="B124">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C124" t="str">
-        <v>Day 4</v>
+        <v>Day 5</v>
       </c>
       <c r="D124" t="str">
         <v/>
       </c>
       <c r="E124" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="F124">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G124" t="str">
-        <v>B-d4s9</v>
+        <v>B-sled5</v>
       </c>
       <c r="H124" t="str">
-        <v>Home</v>
+        <v>Optional</v>
       </c>
       <c r="I124" t="str">
         <v/>
@@ -14061,16 +14069,16 @@
         <v/>
       </c>
       <c r="K124" t="str">
-        <v/>
+        <v>Optional</v>
       </c>
       <c r="L124" t="str">
-        <v>deskbands</v>
+        <v>sled</v>
       </c>
       <c r="M124" t="str">
-        <v>Desk Bands</v>
+        <v>Sled push → pull</v>
       </c>
       <c r="N124" t="str">
-        <v/>
+        <v>exp</v>
       </c>
       <c r="O124" t="str">
         <v/>
@@ -14079,10 +14087,10 @@
         <v/>
       </c>
       <c r="Q124" t="str">
-        <v/>
+        <v>1 × 3</v>
       </c>
       <c r="R124" t="str">
-        <v>With a resistance band</v>
+        <v/>
       </c>
     </row>
     <row r="125">
@@ -14102,40 +14110,40 @@
         <v>Yes</v>
       </c>
       <c r="F125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G125" t="str">
-        <v>B-sled5</v>
+        <v>B-d5s3</v>
       </c>
       <c r="H125" t="str">
-        <v>Optional</v>
+        <v>Regular</v>
       </c>
       <c r="I125" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J125" t="str">
-        <v/>
+        <v>either</v>
       </c>
       <c r="K125" t="str">
-        <v>Optional</v>
+        <v>Whichever is free</v>
       </c>
       <c r="L125" t="str">
-        <v>sled</v>
+        <v>reardelt</v>
       </c>
       <c r="M125" t="str">
-        <v>Sled push → pull</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="N125" t="str">
-        <v>exp</v>
-      </c>
-      <c r="O125" t="str">
-        <v/>
+        <v>iso</v>
+      </c>
+      <c r="O125">
+        <v>50</v>
       </c>
       <c r="P125" t="str">
         <v/>
       </c>
       <c r="Q125" t="str">
-        <v>1 × 3</v>
+        <v>4 × 15 s per arm</v>
       </c>
       <c r="R125" t="str">
         <v/>
@@ -14161,31 +14169,31 @@
         <v>2</v>
       </c>
       <c r="G126" t="str">
-        <v>B-d5s1</v>
+        <v>B-d5s3</v>
       </c>
       <c r="H126" t="str">
         <v>Regular</v>
       </c>
       <c r="I126" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J126" t="str">
-        <v/>
+        <v>either</v>
       </c>
       <c r="K126" t="str">
-        <v/>
+        <v>Whichever is free</v>
       </c>
       <c r="L126" t="str">
-        <v>cablecrunch</v>
+        <v>facepull</v>
       </c>
       <c r="M126" t="str">
-        <v>Kneeling Cable Ab Crunch</v>
+        <v>Face Pull</v>
       </c>
       <c r="N126" t="str">
         <v>strength</v>
       </c>
       <c r="O126">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P126" t="str">
         <v/>
@@ -14217,37 +14225,37 @@
         <v>3</v>
       </c>
       <c r="G127" t="str">
-        <v>B-d5s3</v>
+        <v>B-d5s4</v>
       </c>
       <c r="H127" t="str">
-        <v>Regular</v>
+        <v>Plyometric</v>
       </c>
       <c r="I127" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J127" t="str">
-        <v>either</v>
+        <v/>
       </c>
       <c r="K127" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L127" t="str">
-        <v>reardelt</v>
+        <v>trxpike</v>
       </c>
       <c r="M127" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>TRX Pike Push-Up</v>
       </c>
       <c r="N127" t="str">
-        <v>iso</v>
-      </c>
-      <c r="O127">
-        <v>50</v>
+        <v>exp</v>
+      </c>
+      <c r="O127" t="str">
+        <v/>
       </c>
       <c r="P127" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q127" t="str">
-        <v>4 × 15 s per arm</v>
+        <v/>
       </c>
       <c r="R127" t="str">
         <v/>
@@ -14270,37 +14278,37 @@
         <v>Yes</v>
       </c>
       <c r="F128">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G128" t="str">
-        <v>B-d5s3</v>
+        <v>B-d5s5</v>
       </c>
       <c r="H128" t="str">
-        <v>Regular</v>
+        <v>Plyometric</v>
       </c>
       <c r="I128" t="str">
-        <v>Accessory</v>
+        <v/>
       </c>
       <c r="J128" t="str">
-        <v>either</v>
+        <v/>
       </c>
       <c r="K128" t="str">
-        <v>Whichever is free</v>
+        <v/>
       </c>
       <c r="L128" t="str">
-        <v>facepull</v>
+        <v>trxrow</v>
       </c>
       <c r="M128" t="str">
-        <v>Face Pull</v>
+        <v>TRX Wide-Grip Row</v>
       </c>
       <c r="N128" t="str">
-        <v>strength</v>
-      </c>
-      <c r="O128">
-        <v>30</v>
+        <v>exp</v>
+      </c>
+      <c r="O128" t="str">
+        <v/>
       </c>
       <c r="P128" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q128" t="str">
         <v/>
@@ -14326,10 +14334,10 @@
         <v>Yes</v>
       </c>
       <c r="F129">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G129" t="str">
-        <v>B-d5s4</v>
+        <v>B-d5s6</v>
       </c>
       <c r="H129" t="str">
         <v>Plyometric</v>
@@ -14344,10 +14352,10 @@
         <v/>
       </c>
       <c r="L129" t="str">
-        <v>trxpike</v>
+        <v>medball</v>
       </c>
       <c r="M129" t="str">
-        <v>TRX Pike Push-Up</v>
+        <v>Med Ball Rotational Scoop</v>
       </c>
       <c r="N129" t="str">
         <v>exp</v>
@@ -14356,7 +14364,7 @@
         <v/>
       </c>
       <c r="P129" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q129" t="str">
         <v/>
@@ -14382,10 +14390,10 @@
         <v>Yes</v>
       </c>
       <c r="F130">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G130" t="str">
-        <v>B-d5s5</v>
+        <v>B-d5s7</v>
       </c>
       <c r="H130" t="str">
         <v>Plyometric</v>
@@ -14400,10 +14408,10 @@
         <v/>
       </c>
       <c r="L130" t="str">
-        <v>trxrow</v>
+        <v>latwall</v>
       </c>
       <c r="M130" t="str">
-        <v>TRX Wide-Grip Row</v>
+        <v>Lateral Wall Push</v>
       </c>
       <c r="N130" t="str">
         <v>exp</v>
@@ -14438,31 +14446,31 @@
         <v>Yes</v>
       </c>
       <c r="F131">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G131" t="str">
-        <v>B-d5s6</v>
+        <v>B-xmuy1rdg3uct</v>
       </c>
       <c r="H131" t="str">
-        <v>Plyometric</v>
+        <v>Supersets</v>
       </c>
       <c r="I131" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J131" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K131" t="str">
         <v/>
       </c>
       <c r="L131" t="str">
-        <v>medball</v>
+        <v>seated-cable-crunch</v>
       </c>
       <c r="M131" t="str">
-        <v>Med Ball Rotational Scoop</v>
+        <v>Seated Cable Crunch</v>
       </c>
       <c r="N131" t="str">
-        <v>exp</v>
+        <v>strength</v>
       </c>
       <c r="O131" t="str">
         <v/>
@@ -14497,34 +14505,34 @@
         <v>7</v>
       </c>
       <c r="G132" t="str">
-        <v>B-d5s7</v>
+        <v>B-xmuy1rdg3uct</v>
       </c>
       <c r="H132" t="str">
-        <v>Plyometric</v>
+        <v>Supersets</v>
       </c>
       <c r="I132" t="str">
-        <v/>
+        <v>Accessory</v>
       </c>
       <c r="J132" t="str">
-        <v/>
+        <v>superset</v>
       </c>
       <c r="K132" t="str">
         <v/>
       </c>
       <c r="L132" t="str">
-        <v>latwall</v>
+        <v>wristpd</v>
       </c>
       <c r="M132" t="str">
-        <v>Lateral Wall Push</v>
+        <v>Cable Wrist Pulldown</v>
       </c>
       <c r="N132" t="str">
-        <v>exp</v>
+        <v>strength</v>
       </c>
       <c r="O132" t="str">
         <v/>
       </c>
       <c r="P132" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="Q132" t="str">
         <v/>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">Weeks!$A$1:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Body weight'!$A$1:$D$3</definedName>
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">Programs!$A$1:$R$145</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Program info'!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11">Config!$A$1:$B$16</definedName>
   </definedNames>
 </workbook>
@@ -987,25 +987,25 @@
         <v>Strength</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="str">
         <v>2026-09-29</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-10-07</v>
+        <v>2026-09-29</v>
       </c>
       <c r="F18">
         <v>60</v>
       </c>
       <c r="G18">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="H18">
         <v>60</v>
       </c>
       <c r="I18">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J18">
         <v>100</v>
@@ -1019,10 +1019,10 @@
         <v>Hypertrophy</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-10-05</v>
+        <v>2026-09-27</v>
       </c>
       <c r="E19" t="str">
         <v>2026-10-05</v>
@@ -1045,103 +1045,103 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Lat Pulldown, alternating single-arm</v>
+        <v>Lateral Bound / Skater Hop with Stick</v>
       </c>
       <c r="B20" t="str">
-        <v>Hypertrophy</v>
+        <v>Explosive</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-09-29</v>
-      </c>
-      <c r="F20">
-        <v>45</v>
-      </c>
-      <c r="G20">
-        <v>45</v>
-      </c>
-      <c r="H20">
-        <v>45</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>70</v>
+        <v>2026-10-04</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Lateral Bound / Skater Hop with Stick</v>
+        <v>Leg Extension ISO hold</v>
       </c>
       <c r="B21" t="str">
-        <v>Explosive</v>
+        <v>Isometric</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-10-04</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
-      <c r="G21" t="str">
-        <v/>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21" t="str">
-        <v/>
-      </c>
-      <c r="J21" t="str">
-        <v/>
+        <v>2026-09-29</v>
+      </c>
+      <c r="F21">
+        <v>50</v>
+      </c>
+      <c r="G21">
+        <v>50</v>
+      </c>
+      <c r="H21">
+        <v>50</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>65</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Leg Extension ISO hold</v>
+        <v>Outer Thigh Adduction</v>
       </c>
       <c r="B22" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-05</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-05</v>
       </c>
       <c r="F22">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="G22">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="H22">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>65</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Outer Thigh Adduction</v>
+        <v>Overhead Tricep Extension</v>
       </c>
       <c r="B23" t="str">
         <v>Strength</v>
@@ -1150,30 +1150,30 @@
         <v>1</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-07</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-07</v>
       </c>
       <c r="F23">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="G23">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="H23">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="J23">
-        <v>180</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Overhead Tricep Extension</v>
+        <v>Plate Torso Rotation</v>
       </c>
       <c r="B24" t="str">
         <v>Strength</v>
@@ -1182,19 +1182,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-05</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-05</v>
       </c>
       <c r="F24">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G24">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H24">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1205,66 +1205,66 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Plate Torso Rotation</v>
+        <v>Pogo Hops</v>
       </c>
       <c r="B25" t="str">
-        <v>Strength</v>
+        <v>Explosive</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-10-05</v>
-      </c>
-      <c r="F25">
-        <v>10</v>
-      </c>
-      <c r="G25">
-        <v>10</v>
-      </c>
-      <c r="H25">
-        <v>10</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>30</v>
+        <v>2026-10-04</v>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Pogo Hops</v>
+        <v>Seated Cable Crunch</v>
       </c>
       <c r="B26" t="str">
-        <v>Explosive</v>
+        <v>Strength</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-07</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="F26" t="str">
-        <v/>
-      </c>
-      <c r="G26" t="str">
-        <v/>
-      </c>
-      <c r="H26" t="str">
-        <v/>
-      </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
-      <c r="J26" t="str">
-        <v/>
+        <v>2026-10-07</v>
+      </c>
+      <c r="F26">
+        <v>44</v>
+      </c>
+      <c r="G26">
+        <v>44</v>
+      </c>
+      <c r="H26">
+        <v>44</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>77</v>
       </c>
     </row>
     <row r="27">
@@ -1522,7 +1522,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D115"/>
+  <dimension ref="A1:D117"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.83203125" customWidth="1"/>
@@ -1580,7 +1580,7 @@
         <v>done</v>
       </c>
       <c r="C4" t="str">
-        <v>A-d1s1</v>
+        <v>A-d1s4</v>
       </c>
       <c r="D4" t="str">
         <v>Yes</v>
@@ -1594,7 +1594,7 @@
         <v>done</v>
       </c>
       <c r="C5" t="str">
-        <v>A-d1s4</v>
+        <v>A-d1s6</v>
       </c>
       <c r="D5" t="str">
         <v>Yes</v>
@@ -1608,7 +1608,7 @@
         <v>done</v>
       </c>
       <c r="C6" t="str">
-        <v>A-d1s6</v>
+        <v>A-d1s8</v>
       </c>
       <c r="D6" t="str">
         <v>Yes</v>
@@ -1622,7 +1622,7 @@
         <v>done</v>
       </c>
       <c r="C7" t="str">
-        <v>A-d1s8</v>
+        <v>A-d2s3</v>
       </c>
       <c r="D7" t="str">
         <v>Yes</v>
@@ -1636,7 +1636,7 @@
         <v>done</v>
       </c>
       <c r="C8" t="str">
-        <v>A-d2s3</v>
+        <v>A-d2s5</v>
       </c>
       <c r="D8" t="str">
         <v>Yes</v>
@@ -1650,7 +1650,7 @@
         <v>done</v>
       </c>
       <c r="C9" t="str">
-        <v>A-d2s5</v>
+        <v>A-d3s3</v>
       </c>
       <c r="D9" t="str">
         <v>Yes</v>
@@ -1664,7 +1664,7 @@
         <v>done</v>
       </c>
       <c r="C10" t="str">
-        <v>A-d3s3</v>
+        <v>A-d3s6</v>
       </c>
       <c r="D10" t="str">
         <v>Yes</v>
@@ -1678,7 +1678,7 @@
         <v>done</v>
       </c>
       <c r="C11" t="str">
-        <v>A-d3s6</v>
+        <v>A-d3s6#0</v>
       </c>
       <c r="D11" t="str">
         <v>Yes</v>
@@ -1692,7 +1692,7 @@
         <v>done</v>
       </c>
       <c r="C12" t="str">
-        <v>A-d3s6#0</v>
+        <v>A-d2s4</v>
       </c>
       <c r="D12" t="str">
         <v>Yes</v>
@@ -1706,7 +1706,7 @@
         <v>done</v>
       </c>
       <c r="C13" t="str">
-        <v>A-d2s4</v>
+        <v>A-d1s7</v>
       </c>
       <c r="D13" t="str">
         <v>Yes</v>
@@ -1720,7 +1720,7 @@
         <v>done</v>
       </c>
       <c r="C14" t="str">
-        <v>A-d1s7</v>
+        <v>A-d3s5</v>
       </c>
       <c r="D14" t="str">
         <v>Yes</v>
@@ -1734,7 +1734,7 @@
         <v>done</v>
       </c>
       <c r="C15" t="str">
-        <v>A-d3s5</v>
+        <v>A-d3s1</v>
       </c>
       <c r="D15" t="str">
         <v>Yes</v>
@@ -1748,7 +1748,7 @@
         <v>done</v>
       </c>
       <c r="C16" t="str">
-        <v>A-d3s1</v>
+        <v>A-d4s5</v>
       </c>
       <c r="D16" t="str">
         <v>Yes</v>
@@ -1762,7 +1762,7 @@
         <v>done</v>
       </c>
       <c r="C17" t="str">
-        <v>A-d4s5</v>
+        <v>A-d4s2</v>
       </c>
       <c r="D17" t="str">
         <v>Yes</v>
@@ -1776,7 +1776,7 @@
         <v>done</v>
       </c>
       <c r="C18" t="str">
-        <v>A-d4s2</v>
+        <v>A-d4s4</v>
       </c>
       <c r="D18" t="str">
         <v>Yes</v>
@@ -1790,7 +1790,7 @@
         <v>done</v>
       </c>
       <c r="C19" t="str">
-        <v>A-d4s4</v>
+        <v>A-d6s5</v>
       </c>
       <c r="D19" t="str">
         <v>Yes</v>
@@ -1804,7 +1804,7 @@
         <v>done</v>
       </c>
       <c r="C20" t="str">
-        <v>A-d6s5</v>
+        <v>A-d5s3</v>
       </c>
       <c r="D20" t="str">
         <v>Yes</v>
@@ -1818,7 +1818,7 @@
         <v>done</v>
       </c>
       <c r="C21" t="str">
-        <v>A-d5s3</v>
+        <v>A-d2s2</v>
       </c>
       <c r="D21" t="str">
         <v>Yes</v>
@@ -1832,7 +1832,7 @@
         <v>done</v>
       </c>
       <c r="C22" t="str">
-        <v>A-d2s2</v>
+        <v>A-d2s2#0</v>
       </c>
       <c r="D22" t="str">
         <v>Yes</v>
@@ -1846,7 +1846,7 @@
         <v>done</v>
       </c>
       <c r="C23" t="str">
-        <v>A-d2s2#0</v>
+        <v>A-d3s2</v>
       </c>
       <c r="D23" t="str">
         <v>Yes</v>
@@ -1860,7 +1860,7 @@
         <v>done</v>
       </c>
       <c r="C24" t="str">
-        <v>A-d3s2</v>
+        <v>A-d1s2</v>
       </c>
       <c r="D24" t="str">
         <v>Yes</v>
@@ -1874,7 +1874,7 @@
         <v>done</v>
       </c>
       <c r="C25" t="str">
-        <v>A-d1s2</v>
+        <v>A-d1s1</v>
       </c>
       <c r="D25" t="str">
         <v>Yes</v>
@@ -2991,10 +2991,10 @@
         <v>2026-10-04</v>
       </c>
       <c r="B105" t="str">
-        <v>skipped</v>
+        <v>done</v>
       </c>
       <c r="C105" t="str">
-        <v>B-d6s5</v>
+        <v>B-xmuy1nsai5fs#0</v>
       </c>
       <c r="D105" t="str">
         <v>Yes</v>
@@ -3008,7 +3008,7 @@
         <v>skipped</v>
       </c>
       <c r="C106" t="str">
-        <v>B-sled1</v>
+        <v>B-d6s5</v>
       </c>
       <c r="D106" t="str">
         <v>Yes</v>
@@ -3022,7 +3022,7 @@
         <v>skipped</v>
       </c>
       <c r="C107" t="str">
-        <v>B-d1s7</v>
+        <v>B-sled1</v>
       </c>
       <c r="D107" t="str">
         <v>Yes</v>
@@ -3036,7 +3036,7 @@
         <v>skipped</v>
       </c>
       <c r="C108" t="str">
-        <v>B-sled2</v>
+        <v>B-d1s7</v>
       </c>
       <c r="D108" t="str">
         <v>Yes</v>
@@ -3050,7 +3050,7 @@
         <v>skipped</v>
       </c>
       <c r="C109" t="str">
-        <v>B-d2s6</v>
+        <v>B-sled2</v>
       </c>
       <c r="D109" t="str">
         <v>Yes</v>
@@ -3061,13 +3061,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B110" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C110" t="str">
-        <v>B-d5s2</v>
-      </c>
-      <c r="D110">
-        <v>6</v>
+        <v>B-d2s6</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="111">
@@ -3075,13 +3075,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B111" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C111" t="str">
-        <v>B-d1s3</v>
-      </c>
-      <c r="D111">
-        <v>6</v>
+        <v>B-xmuy1nsai5fs</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="112">
@@ -3092,10 +3092,10 @@
         <v>moved</v>
       </c>
       <c r="C112" t="str">
-        <v>B-d1s9</v>
+        <v>B-d5s2</v>
       </c>
       <c r="D112">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113">
@@ -3106,10 +3106,10 @@
         <v>moved</v>
       </c>
       <c r="C113" t="str">
-        <v>B-d1s5</v>
+        <v>B-d1s3</v>
       </c>
       <c r="D113">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114">
@@ -3120,10 +3120,10 @@
         <v>moved</v>
       </c>
       <c r="C114" t="str">
-        <v>B-d2s8</v>
+        <v>B-d1s9</v>
       </c>
       <c r="D114">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
@@ -3134,16 +3134,44 @@
         <v>moved</v>
       </c>
       <c r="C115" t="str">
+        <v>B-d1s5</v>
+      </c>
+      <c r="D115">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B116" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C116" t="str">
+        <v>B-d2s8</v>
+      </c>
+      <c r="D116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B117" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C117" t="str">
         <v>B-d3s2</v>
       </c>
-      <c r="D115">
+      <c r="D117">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D115"/>
+  <autoFilter ref="A1:D117"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D115"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D117"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3193,7 +3221,7 @@
         <v>ghBackup</v>
       </c>
       <c r="B5" t="str">
-        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"1sdqb2a","last":{"at":"2026-10-05T10:56:57.524Z","url":"https://github.com/jacgit18/iron-log/commit/f6b67ee93ead4d55569495213b1371f9ba297d63"}}</v>
+        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"1b8mcee","last":{"at":"2026-10-07T11:56:05.483Z","url":"https://github.com/jacgit18/iron-log/commit/7f416b7502f7dbd285c22349fe7ecf4ddb8473aa"}}</v>
       </c>
     </row>
     <row r="6">
@@ -3294,7 +3322,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:O54"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -3462,43 +3490,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C4" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Lat Pulldown</v>
       </c>
       <c r="D4" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E4">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F4">
         <v>4</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H4" t="str">
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>50×6, 50×6, 50×6, 50×6</v>
+        <v>45×15, 45×15, 45×15, 45×15</v>
       </c>
       <c r="J4">
-        <v>1200</v>
+        <v>2700</v>
       </c>
       <c r="K4" t="str">
-        <v>Lower back</v>
+        <v>Lats</v>
       </c>
       <c r="L4" t="str">
-        <v>Glutes, Hamstrings, Upper back</v>
+        <v>Biceps, Upper back, Rear delts</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N4" t="str">
-        <v>A-d1s6</v>
+        <v>A-d1s1</v>
       </c>
       <c r="O4" t="str">
-        <v>zercher</v>
+        <v>latpdbi</v>
       </c>
     </row>
     <row r="5">
@@ -3509,10 +3537,10 @@
         <v>2026-09-27</v>
       </c>
       <c r="C5" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="D5" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="E5">
         <v>50</v>
@@ -3520,79 +3548,79 @@
       <c r="F5">
         <v>4</v>
       </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5">
-        <v>15</v>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>50×15s, 50×15s, 50×15s, 50×15s</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
+        <v>50×6, 50×6, 50×6, 50×6</v>
+      </c>
+      <c r="J5">
+        <v>1200</v>
       </c>
       <c r="K5" t="str">
-        <v>Rear delts</v>
+        <v>Lower back</v>
       </c>
       <c r="L5" t="str">
-        <v>Upper back</v>
+        <v>Glutes, Hamstrings, Upper back</v>
       </c>
       <c r="M5" t="str">
         <v/>
       </c>
       <c r="N5" t="str">
-        <v>A-d3s6</v>
+        <v>A-d1s6</v>
       </c>
       <c r="O5" t="str">
-        <v>reardelt</v>
+        <v>zercher</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-27</v>
       </c>
       <c r="B6" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="C6" t="str">
-        <v>Cable Wrist Pulldown</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="D6" t="str">
-        <v>Hypertrophy</v>
+        <v>Isometric</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F6">
         <v>4</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6">
         <v>15</v>
       </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
       <c r="I6" t="str">
-        <v>33×15, 33×15, 33×15, 33×15</v>
-      </c>
-      <c r="J6">
-        <v>1980</v>
+        <v>50×15s, 50×15s, 50×15s, 50×15s</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
       </c>
       <c r="K6" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Rear delts</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>Upper back</v>
       </c>
       <c r="M6" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N6" t="str">
-        <v>A-d3s3</v>
+        <v>A-d3s6</v>
       </c>
       <c r="O6" t="str">
-        <v>wristpd</v>
+        <v>reardelt</v>
       </c>
     </row>
     <row r="7">
@@ -3603,43 +3631,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C7" t="str">
-        <v>Chest Press</v>
+        <v>Cable Wrist Pulldown</v>
       </c>
       <c r="D7" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E7">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F7">
         <v>4</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H7" t="str">
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>35×6, 35×6, 35×6, 35×6</v>
+        <v>33×15, 33×15, 33×15, 33×15</v>
       </c>
       <c r="J7">
-        <v>840</v>
+        <v>1980</v>
       </c>
       <c r="K7" t="str">
-        <v>Chest</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="L7" t="str">
-        <v>Front delts, Triceps</v>
+        <v/>
       </c>
       <c r="M7" t="str">
         <v>From check-off</v>
       </c>
       <c r="N7" t="str">
-        <v>A-d1s6</v>
+        <v>A-d3s3</v>
       </c>
       <c r="O7" t="str">
-        <v>chestpress</v>
+        <v>wristpd</v>
       </c>
     </row>
     <row r="8">
@@ -3650,13 +3678,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="C8" t="str">
-        <v>Grip Trainer</v>
+        <v>Chest Press</v>
       </c>
       <c r="D8" t="str">
         <v>Strength</v>
       </c>
       <c r="E8">
-        <v>200</v>
+        <v>35</v>
       </c>
       <c r="F8">
         <v>4</v>
@@ -3668,25 +3696,25 @@
         <v/>
       </c>
       <c r="I8" t="str">
-        <v>200×6, 200×6, 200×6, 200×6</v>
+        <v>35×6, 35×6, 35×6, 35×6</v>
       </c>
       <c r="J8">
-        <v>4800</v>
+        <v>840</v>
       </c>
       <c r="K8" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Chest</v>
       </c>
       <c r="L8" t="str">
-        <v/>
+        <v>Front delts, Triceps</v>
       </c>
       <c r="M8" t="str">
         <v>From check-off</v>
       </c>
       <c r="N8" t="str">
-        <v>A-d1s8</v>
+        <v>A-d1s6</v>
       </c>
       <c r="O8" t="str">
-        <v>grip</v>
+        <v>chestpress</v>
       </c>
     </row>
     <row r="9">
@@ -3697,13 +3725,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="C9" t="str">
-        <v>Hip Thrust</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="D9" t="str">
         <v>Strength</v>
       </c>
       <c r="E9">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="F9">
         <v>4</v>
@@ -3715,25 +3743,25 @@
         <v/>
       </c>
       <c r="I9" t="str">
-        <v>320×6, 320×6, 320×6, 320×6</v>
+        <v>200×6, 200×6, 200×6, 200×6</v>
       </c>
       <c r="J9">
-        <v>7680</v>
+        <v>4800</v>
       </c>
       <c r="K9" t="str">
-        <v>Glutes</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="L9" t="str">
-        <v>Hamstrings</v>
+        <v/>
       </c>
       <c r="M9" t="str">
         <v>From check-off</v>
       </c>
       <c r="N9" t="str">
-        <v>A-d2s5</v>
+        <v>A-d1s8</v>
       </c>
       <c r="O9" t="str">
-        <v>hipthrust</v>
+        <v>grip</v>
       </c>
     </row>
     <row r="10">
@@ -3744,43 +3772,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C10" t="str">
-        <v>Lat Pulldown, alternating single-arm</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="D10" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E10">
-        <v>45</v>
+        <v>320</v>
       </c>
       <c r="F10">
         <v>4</v>
       </c>
       <c r="G10">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H10" t="str">
         <v/>
       </c>
       <c r="I10" t="str">
-        <v>45×15, 45×15, 45×15, 45×15</v>
+        <v>320×6, 320×6, 320×6, 320×6</v>
       </c>
       <c r="J10">
-        <v>2700</v>
+        <v>7680</v>
       </c>
       <c r="K10" t="str">
-        <v>Lats</v>
+        <v>Glutes</v>
       </c>
       <c r="L10" t="str">
-        <v>Biceps, Upper back, Rear delts</v>
+        <v>Hamstrings</v>
       </c>
       <c r="M10" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N10" t="str">
-        <v>A-d1s1</v>
+        <v>A-d2s5</v>
       </c>
       <c r="O10" t="str">
-        <v>latpd</v>
+        <v>hipthrust</v>
       </c>
     </row>
     <row r="11">
@@ -3979,43 +4007,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C15" t="str">
-        <v>Lat Pulldown, alternating single-arm</v>
+        <v>Leg Extension ISO hold</v>
       </c>
       <c r="D15" t="str">
-        <v>Hypertrophy</v>
+        <v>Isometric</v>
       </c>
       <c r="E15">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F15">
         <v>4</v>
       </c>
-      <c r="G15">
-        <v>15</v>
-      </c>
-      <c r="H15" t="str">
-        <v/>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15">
+        <v>30</v>
       </c>
       <c r="I15" t="str">
-        <v>45×15, 45×15, 45×15, 45×15</v>
-      </c>
-      <c r="J15">
-        <v>2700</v>
+        <v>50×30s, 50×30s, 50×30s, 50×30s</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
       </c>
       <c r="K15" t="str">
-        <v>Lats</v>
+        <v>Quads</v>
       </c>
       <c r="L15" t="str">
-        <v>Biceps, Upper back, Rear delts</v>
+        <v/>
       </c>
       <c r="M15" t="str">
         <v/>
       </c>
       <c r="N15" t="str">
-        <v>A-d3s2</v>
+        <v>A-d3s5</v>
       </c>
       <c r="O15" t="str">
-        <v>latpd</v>
+        <v>legext</v>
       </c>
     </row>
     <row r="16">
@@ -4026,43 +4054,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C16" t="str">
-        <v>Leg Extension ISO hold</v>
+        <v>Suitcase Bottom-Up, single-arm</v>
       </c>
       <c r="D16" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="E16">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F16">
         <v>4</v>
       </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16">
-        <v>30</v>
+      <c r="G16">
+        <v>6</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>50×30s, 50×30s, 50×30s, 50×30s</v>
-      </c>
-      <c r="J16" t="str">
-        <v/>
+        <v>25×6, 25×6, 25×6, 25×6</v>
+      </c>
+      <c r="J16">
+        <v>600</v>
       </c>
       <c r="K16" t="str">
-        <v>Quads</v>
+        <v>Forearms &amp; grip, Obliques</v>
       </c>
       <c r="L16" t="str">
-        <v/>
+        <v>Traps</v>
       </c>
       <c r="M16" t="str">
         <v/>
       </c>
       <c r="N16" t="str">
-        <v>A-d3s5</v>
+        <v>A-d4s1</v>
       </c>
       <c r="O16" t="str">
-        <v>legext</v>
+        <v>suitcase</v>
       </c>
     </row>
     <row r="17">
@@ -4073,90 +4101,90 @@
         <v>2026-09-27</v>
       </c>
       <c r="C17" t="str">
-        <v>Suitcase Bottom-Up, single-arm</v>
+        <v>Zottman Curl</v>
       </c>
       <c r="D17" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E17">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H17" t="str">
         <v/>
       </c>
       <c r="I17" t="str">
-        <v>25×6, 25×6, 25×6, 25×6</v>
+        <v>15×15, 15×15, 15×15</v>
       </c>
       <c r="J17">
-        <v>600</v>
+        <v>675</v>
       </c>
       <c r="K17" t="str">
-        <v>Forearms &amp; grip, Obliques</v>
+        <v>Biceps, Forearms &amp; grip</v>
       </c>
       <c r="L17" t="str">
-        <v>Traps</v>
+        <v/>
       </c>
       <c r="M17" t="str">
         <v/>
       </c>
       <c r="N17" t="str">
-        <v>A-d4s1</v>
+        <v>A-d1s7</v>
       </c>
       <c r="O17" t="str">
-        <v>suitcase</v>
+        <v>zottman</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-30</v>
       </c>
       <c r="B18" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="C18" t="str">
-        <v>Zottman Curl</v>
+        <v>Arnold Press</v>
       </c>
       <c r="D18" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E18">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H18" t="str">
         <v/>
       </c>
       <c r="I18" t="str">
-        <v>15×15, 15×15, 15×15</v>
+        <v>35×6, 35×6, 30×6, 30×6</v>
       </c>
       <c r="J18">
-        <v>675</v>
+        <v>780</v>
       </c>
       <c r="K18" t="str">
-        <v>Biceps, Forearms &amp; grip</v>
+        <v>Front delts, Side delts</v>
       </c>
       <c r="L18" t="str">
-        <v/>
+        <v>Triceps</v>
       </c>
       <c r="M18" t="str">
         <v/>
       </c>
       <c r="N18" t="str">
-        <v>A-d1s7</v>
+        <v>A-d4s4</v>
       </c>
       <c r="O18" t="str">
-        <v>zottman</v>
+        <v>arnold</v>
       </c>
     </row>
     <row r="19">
@@ -4167,43 +4195,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C19" t="str">
-        <v>Arnold Press</v>
+        <v>Chest Press</v>
       </c>
       <c r="D19" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E19">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H19" t="str">
         <v/>
       </c>
       <c r="I19" t="str">
-        <v>35×6, 35×6, 30×6, 30×6</v>
+        <v>25×15, 25×10</v>
       </c>
       <c r="J19">
-        <v>780</v>
+        <v>625</v>
       </c>
       <c r="K19" t="str">
-        <v>Front delts, Side delts</v>
+        <v>Chest</v>
       </c>
       <c r="L19" t="str">
-        <v>Triceps</v>
+        <v>Front delts, Triceps</v>
       </c>
       <c r="M19" t="str">
         <v/>
       </c>
       <c r="N19" t="str">
-        <v>A-d4s4</v>
+        <v>A-d4s5</v>
       </c>
       <c r="O19" t="str">
-        <v>arnold</v>
+        <v>chestpress</v>
       </c>
     </row>
     <row r="20">
@@ -4214,43 +4242,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C20" t="str">
-        <v>Chest Press</v>
+        <v>Hack Squat</v>
       </c>
       <c r="D20" t="str">
         <v>Hypertrophy</v>
       </c>
       <c r="E20">
-        <v>25</v>
+        <v>270</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G20">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H20" t="str">
         <v/>
       </c>
       <c r="I20" t="str">
-        <v>25×15, 25×10</v>
+        <v>270×15, 270×15, 270×15, 270×15</v>
       </c>
       <c r="J20">
-        <v>625</v>
+        <v>16200</v>
       </c>
       <c r="K20" t="str">
-        <v>Chest</v>
+        <v>Quads</v>
       </c>
       <c r="L20" t="str">
-        <v>Front delts, Triceps</v>
+        <v>Glutes, Inner thigh (adductors)</v>
       </c>
       <c r="M20" t="str">
         <v/>
       </c>
       <c r="N20" t="str">
-        <v>A-d4s5</v>
+        <v>A-d3s1</v>
       </c>
       <c r="O20" t="str">
-        <v>chestpress</v>
+        <v>hack</v>
       </c>
     </row>
     <row r="21">
@@ -4261,43 +4289,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C21" t="str">
-        <v>Hack Squat</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="D21" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E21">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H21" t="str">
         <v/>
       </c>
       <c r="I21" t="str">
-        <v>270×15, 270×15, 270×15, 270×15</v>
+        <v>320×6, 320×6</v>
       </c>
       <c r="J21">
-        <v>16200</v>
+        <v>3840</v>
       </c>
       <c r="K21" t="str">
-        <v>Quads</v>
+        <v>Glutes</v>
       </c>
       <c r="L21" t="str">
-        <v>Glutes, Inner thigh (adductors)</v>
+        <v>Hamstrings</v>
       </c>
       <c r="M21" t="str">
         <v/>
       </c>
       <c r="N21" t="str">
-        <v>A-d3s1</v>
+        <v>A-d4s5</v>
       </c>
       <c r="O21" t="str">
-        <v>hack</v>
+        <v>hipthrust</v>
       </c>
     </row>
     <row r="22">
@@ -4308,16 +4336,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="C22" t="str">
-        <v>Hip Thrust</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="D22" t="str">
         <v>Strength</v>
       </c>
       <c r="E22">
-        <v>320</v>
+        <v>180</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22">
         <v>6</v>
@@ -4326,25 +4354,25 @@
         <v/>
       </c>
       <c r="I22" t="str">
-        <v>320×6, 320×6</v>
+        <v>180×6, 180×6, 180×6, 180×6</v>
       </c>
       <c r="J22">
-        <v>3840</v>
+        <v>4320</v>
       </c>
       <c r="K22" t="str">
-        <v>Glutes</v>
+        <v>Inner thigh (adductors)</v>
       </c>
       <c r="L22" t="str">
-        <v>Hamstrings</v>
+        <v/>
       </c>
       <c r="M22" t="str">
         <v/>
       </c>
       <c r="N22" t="str">
-        <v>A-d4s5</v>
+        <v>A-d4s2</v>
       </c>
       <c r="O22" t="str">
-        <v>hipthrust</v>
+        <v>innerthigh</v>
       </c>
     </row>
     <row r="23">
@@ -4355,13 +4383,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="C23" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="D23" t="str">
         <v>Strength</v>
       </c>
       <c r="E23">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="F23">
         <v>4</v>
@@ -4373,45 +4401,45 @@
         <v/>
       </c>
       <c r="I23" t="str">
-        <v>180×6, 180×6, 180×6, 180×6</v>
+        <v>50×6, 50×6, 50×6, 50×6</v>
       </c>
       <c r="J23">
-        <v>4320</v>
+        <v>1200</v>
       </c>
       <c r="K23" t="str">
-        <v>Inner thigh (adductors)</v>
+        <v>Lower back</v>
       </c>
       <c r="L23" t="str">
-        <v/>
+        <v>Glutes, Hamstrings, Upper back</v>
       </c>
       <c r="M23" t="str">
         <v/>
       </c>
       <c r="N23" t="str">
-        <v>A-d4s2</v>
+        <v>A-d4s4</v>
       </c>
       <c r="O23" t="str">
-        <v>innerthigh</v>
+        <v>zercher</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-09-30</v>
+        <v>2026-10-01</v>
       </c>
       <c r="B24" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="C24" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Arnold Press</v>
       </c>
       <c r="D24" t="str">
         <v>Strength</v>
       </c>
       <c r="E24">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G24">
         <v>6</v>
@@ -4420,25 +4448,25 @@
         <v/>
       </c>
       <c r="I24" t="str">
-        <v>50×6, 50×6, 50×6, 50×6</v>
+        <v>25×6</v>
       </c>
       <c r="J24">
-        <v>1200</v>
+        <v>150</v>
       </c>
       <c r="K24" t="str">
-        <v>Lower back</v>
+        <v>Front delts, Side delts</v>
       </c>
       <c r="L24" t="str">
-        <v>Glutes, Hamstrings, Upper back</v>
+        <v>Triceps</v>
       </c>
       <c r="M24" t="str">
         <v/>
       </c>
       <c r="N24" t="str">
-        <v>A-d4s4</v>
+        <v>A-d6s5</v>
       </c>
       <c r="O24" t="str">
-        <v>zercher</v>
+        <v>arnold</v>
       </c>
     </row>
     <row r="25">
@@ -4449,43 +4477,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C25" t="str">
-        <v>Arnold Press</v>
+        <v>Hack Squat</v>
       </c>
       <c r="D25" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E25">
-        <v>25</v>
+        <v>270</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G25">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H25" t="str">
         <v/>
       </c>
       <c r="I25" t="str">
-        <v>25×6</v>
+        <v>270×15, 270×15, 270×15</v>
       </c>
       <c r="J25">
-        <v>150</v>
+        <v>12150</v>
       </c>
       <c r="K25" t="str">
-        <v>Front delts, Side delts</v>
+        <v>Quads</v>
       </c>
       <c r="L25" t="str">
-        <v>Triceps</v>
+        <v>Glutes, Inner thigh (adductors)</v>
       </c>
       <c r="M25" t="str">
         <v/>
       </c>
       <c r="N25" t="str">
-        <v>A-d6s5</v>
+        <v>A-d5s3</v>
       </c>
       <c r="O25" t="str">
-        <v>arnold</v>
+        <v>hack</v>
       </c>
     </row>
     <row r="26">
@@ -4496,90 +4524,90 @@
         <v>2026-09-27</v>
       </c>
       <c r="C26" t="str">
-        <v>Hack Squat</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="D26" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E26">
-        <v>270</v>
+        <v>40</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H26" t="str">
         <v/>
       </c>
       <c r="I26" t="str">
-        <v>270×15, 270×15, 270×15</v>
+        <v>40×6</v>
       </c>
       <c r="J26">
-        <v>12150</v>
+        <v>240</v>
       </c>
       <c r="K26" t="str">
-        <v>Quads</v>
+        <v>Lower back</v>
       </c>
       <c r="L26" t="str">
-        <v>Glutes, Inner thigh (adductors)</v>
+        <v>Glutes, Hamstrings, Upper back</v>
       </c>
       <c r="M26" t="str">
         <v/>
       </c>
       <c r="N26" t="str">
-        <v>A-d5s3</v>
+        <v>A-d6s5</v>
       </c>
       <c r="O26" t="str">
-        <v>hack</v>
+        <v>zercher</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-04</v>
       </c>
       <c r="B27" t="str">
-        <v>2026-09-27</v>
+        <v>2026-10-04</v>
       </c>
       <c r="C27" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Cable Punch ISO hold</v>
       </c>
       <c r="D27" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="E27">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27">
-        <v>6</v>
-      </c>
-      <c r="H27" t="str">
-        <v/>
+        <v>4</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27">
+        <v>15</v>
       </c>
       <c r="I27" t="str">
-        <v>40×6</v>
-      </c>
-      <c r="J27">
-        <v>240</v>
+        <v>30×15s, 30×15s, 30×15s, 30×15s</v>
+      </c>
+      <c r="J27" t="str">
+        <v/>
       </c>
       <c r="K27" t="str">
-        <v>Lower back</v>
+        <v>Obliques, Abs</v>
       </c>
       <c r="L27" t="str">
-        <v>Glutes, Hamstrings, Upper back</v>
+        <v>Chest, Front delts</v>
       </c>
       <c r="M27" t="str">
         <v/>
       </c>
       <c r="N27" t="str">
-        <v>A-d6s5</v>
+        <v>B-d6s6</v>
       </c>
       <c r="O27" t="str">
-        <v>zercher</v>
+        <v>cablepunch</v>
       </c>
     </row>
     <row r="28">
@@ -4590,43 +4618,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C28" t="str">
-        <v>Cable Punch ISO hold</v>
+        <v>Cable Wrist Pulldown</v>
       </c>
       <c r="D28" t="str">
-        <v>Isometric</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E28">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F28">
-        <v>4</v>
-      </c>
-      <c r="G28" t="str">
-        <v/>
-      </c>
-      <c r="H28">
+        <v>2</v>
+      </c>
+      <c r="G28">
         <v>15</v>
       </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
       <c r="I28" t="str">
-        <v>30×15s, 30×15s, 30×15s, 30×15s</v>
-      </c>
-      <c r="J28" t="str">
-        <v/>
+        <v>33×15, 33×15</v>
+      </c>
+      <c r="J28">
+        <v>990</v>
       </c>
       <c r="K28" t="str">
-        <v>Obliques, Abs</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="L28" t="str">
-        <v>Chest, Front delts</v>
+        <v/>
       </c>
       <c r="M28" t="str">
         <v/>
       </c>
       <c r="N28" t="str">
-        <v>B-d6s6</v>
+        <v>B-d1s3</v>
       </c>
       <c r="O28" t="str">
-        <v>cablepunch</v>
+        <v>wristpd</v>
       </c>
     </row>
     <row r="29">
@@ -4637,31 +4665,31 @@
         <v>2026-10-04</v>
       </c>
       <c r="C29" t="str">
-        <v>Cable Wrist Pulldown</v>
+        <v>Clean Jerk &amp; Overhead Press</v>
       </c>
       <c r="D29" t="str">
-        <v>Hypertrophy</v>
+        <v>Explosive</v>
       </c>
       <c r="E29">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H29" t="str">
         <v/>
       </c>
       <c r="I29" t="str">
-        <v>33×15, 33×15</v>
+        <v>20×10, 20×10, 20×10</v>
       </c>
       <c r="J29">
-        <v>990</v>
+        <v>600</v>
       </c>
       <c r="K29" t="str">
-        <v>Forearms &amp; grip</v>
+        <v/>
       </c>
       <c r="L29" t="str">
         <v/>
@@ -4670,10 +4698,10 @@
         <v/>
       </c>
       <c r="N29" t="str">
-        <v>B-d1s3</v>
+        <v>B-d5s2</v>
       </c>
       <c r="O29" t="str">
-        <v>wristpd</v>
+        <v>clean-jerk-overhead-press</v>
       </c>
     </row>
     <row r="30">
@@ -4684,43 +4712,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C30" t="str">
-        <v>Clean Jerk &amp; Overhead Press</v>
+        <v>Depth Drop → Broad Jump → Box Jump</v>
       </c>
       <c r="D30" t="str">
         <v>Explosive</v>
       </c>
-      <c r="E30">
-        <v>20</v>
+      <c r="E30" t="str">
+        <v/>
       </c>
       <c r="F30">
         <v>3</v>
       </c>
       <c r="G30">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H30" t="str">
         <v/>
       </c>
       <c r="I30" t="str">
-        <v>20×10, 20×10, 20×10</v>
-      </c>
-      <c r="J30">
-        <v>600</v>
+        <v>BW×5, BW×5, BW×5</v>
+      </c>
+      <c r="J30" t="str">
+        <v/>
       </c>
       <c r="K30" t="str">
-        <v/>
+        <v>Quads, Glutes, Calves</v>
       </c>
       <c r="L30" t="str">
-        <v/>
+        <v>Hamstrings</v>
       </c>
       <c r="M30" t="str">
         <v/>
       </c>
       <c r="N30" t="str">
-        <v>B-d5s2</v>
+        <v>B-d6s4</v>
       </c>
       <c r="O30" t="str">
-        <v>clean-jerk-overhead-press</v>
+        <v>depthcombo</v>
       </c>
     </row>
     <row r="31">
@@ -4731,43 +4759,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C31" t="str">
-        <v>Depth Drop → Broad Jump → Box Jump</v>
+        <v>Explosive Unilateral Cable Row</v>
       </c>
       <c r="D31" t="str">
         <v>Explosive</v>
       </c>
-      <c r="E31" t="str">
-        <v/>
+      <c r="E31">
+        <v>30</v>
       </c>
       <c r="F31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H31" t="str">
         <v/>
       </c>
       <c r="I31" t="str">
-        <v>BW×5, BW×5, BW×5</v>
-      </c>
-      <c r="J31" t="str">
-        <v/>
+        <v>30×10, 30×10, 30×10, 30×10</v>
+      </c>
+      <c r="J31">
+        <v>1200</v>
       </c>
       <c r="K31" t="str">
-        <v>Quads, Glutes, Calves</v>
+        <v>Lats, Upper back</v>
       </c>
       <c r="L31" t="str">
-        <v>Hamstrings</v>
+        <v>Rear delts, Biceps</v>
       </c>
       <c r="M31" t="str">
         <v/>
       </c>
       <c r="N31" t="str">
-        <v>B-d6s4</v>
+        <v>B-d6s6</v>
       </c>
       <c r="O31" t="str">
-        <v>depthcombo</v>
+        <v>cablerow</v>
       </c>
     </row>
     <row r="32">
@@ -4778,16 +4806,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="C32" t="str">
-        <v>Explosive Unilateral Cable Row</v>
+        <v>Lateral Bound / Skater Hop with Stick</v>
       </c>
       <c r="D32" t="str">
         <v>Explosive</v>
       </c>
-      <c r="E32">
-        <v>30</v>
+      <c r="E32" t="str">
+        <v/>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G32">
         <v>10</v>
@@ -4796,25 +4824,25 @@
         <v/>
       </c>
       <c r="I32" t="str">
-        <v>30×10, 30×10, 30×10, 30×10</v>
-      </c>
-      <c r="J32">
-        <v>1200</v>
+        <v>BW×10, BW×10, BW×10</v>
+      </c>
+      <c r="J32" t="str">
+        <v/>
       </c>
       <c r="K32" t="str">
-        <v>Lats, Upper back</v>
+        <v>Glutes, Outer hip (abductors), Quads</v>
       </c>
       <c r="L32" t="str">
-        <v>Rear delts, Biceps</v>
+        <v>Inner thigh (adductors), Calves</v>
       </c>
       <c r="M32" t="str">
         <v/>
       </c>
       <c r="N32" t="str">
-        <v>B-d6s6</v>
+        <v>B-d6s2</v>
       </c>
       <c r="O32" t="str">
-        <v>cablerow</v>
+        <v>skater</v>
       </c>
     </row>
     <row r="33">
@@ -4825,7 +4853,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="C33" t="str">
-        <v>Lateral Bound / Skater Hop with Stick</v>
+        <v>Pogo Hops</v>
       </c>
       <c r="D33" t="str">
         <v>Explosive</v>
@@ -4849,19 +4877,19 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>Glutes, Outer hip (abductors), Quads</v>
+        <v>Calves</v>
       </c>
       <c r="L33" t="str">
-        <v>Inner thigh (adductors), Calves</v>
+        <v>Shins</v>
       </c>
       <c r="M33" t="str">
         <v/>
       </c>
       <c r="N33" t="str">
-        <v>B-d6s2</v>
+        <v>B-d6s1</v>
       </c>
       <c r="O33" t="str">
-        <v>skater</v>
+        <v>pogo</v>
       </c>
     </row>
     <row r="34">
@@ -4872,43 +4900,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C34" t="str">
-        <v>Pogo Hops</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="D34" t="str">
-        <v>Explosive</v>
-      </c>
-      <c r="E34" t="str">
-        <v/>
+        <v>Strength</v>
+      </c>
+      <c r="E34">
+        <v>50</v>
       </c>
       <c r="F34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H34" t="str">
         <v/>
       </c>
       <c r="I34" t="str">
-        <v>BW×10, BW×10, BW×10</v>
-      </c>
-      <c r="J34" t="str">
-        <v/>
+        <v>50×6, 50×6, 50×6, 50×6</v>
+      </c>
+      <c r="J34">
+        <v>1200</v>
       </c>
       <c r="K34" t="str">
-        <v>Calves</v>
+        <v>Lower back</v>
       </c>
       <c r="L34" t="str">
-        <v>Shins</v>
+        <v>Glutes, Hamstrings, Upper back</v>
       </c>
       <c r="M34" t="str">
         <v/>
       </c>
       <c r="N34" t="str">
-        <v>B-d6s1</v>
+        <v>B-d6s5</v>
       </c>
       <c r="O34" t="str">
-        <v>pogo</v>
+        <v>zercher</v>
       </c>
     </row>
     <row r="35">
@@ -4919,43 +4947,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C35" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Sled push → pull</v>
       </c>
       <c r="D35" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="E35">
-        <v>50</v>
+        <v>Explosive</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H35" t="str">
         <v/>
       </c>
       <c r="I35" t="str">
-        <v>50×6, 50×6, 50×6, 50×6</v>
-      </c>
-      <c r="J35">
-        <v>1200</v>
+        <v>BW×3</v>
+      </c>
+      <c r="J35" t="str">
+        <v/>
       </c>
       <c r="K35" t="str">
-        <v>Lower back</v>
+        <v>Quads, Glutes</v>
       </c>
       <c r="L35" t="str">
-        <v>Glutes, Hamstrings, Upper back</v>
+        <v>Lats, Upper back, Calves</v>
       </c>
       <c r="M35" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N35" t="str">
-        <v>B-d6s5</v>
+        <v>B-sled6</v>
       </c>
       <c r="O35" t="str">
-        <v>zercher</v>
+        <v>sled</v>
       </c>
     </row>
     <row r="36">
@@ -4966,7 +4994,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="C36" t="str">
-        <v>Sled push → pull</v>
+        <v>Split Squat Jumps</v>
       </c>
       <c r="D36" t="str">
         <v>Explosive</v>
@@ -4975,16 +5003,16 @@
         <v/>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H36" t="str">
         <v/>
       </c>
       <c r="I36" t="str">
-        <v>BW×3</v>
+        <v>BW×10, BW×10, BW×10</v>
       </c>
       <c r="J36" t="str">
         <v/>
@@ -4993,63 +5021,63 @@
         <v>Quads, Glutes</v>
       </c>
       <c r="L36" t="str">
-        <v>Lats, Upper back, Calves</v>
+        <v>Calves, Hamstrings</v>
       </c>
       <c r="M36" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N36" t="str">
-        <v>B-sled6</v>
+        <v>B-d6s3</v>
       </c>
       <c r="O36" t="str">
-        <v>sled</v>
+        <v>splitjump</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-05</v>
       </c>
       <c r="B37" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C37" t="str">
-        <v>Split Squat Jumps</v>
+        <v>Canoe Stretch</v>
       </c>
       <c r="D37" t="str">
-        <v>Explosive</v>
-      </c>
-      <c r="E37" t="str">
-        <v/>
+        <v>Isometric</v>
+      </c>
+      <c r="E37">
+        <v>10</v>
       </c>
       <c r="F37">
-        <v>3</v>
-      </c>
-      <c r="G37">
-        <v>10</v>
-      </c>
-      <c r="H37" t="str">
-        <v/>
+        <v>4</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37">
+        <v>15</v>
       </c>
       <c r="I37" t="str">
-        <v>BW×10, BW×10, BW×10</v>
+        <v>10×15s, 10×15s, 10×15s, 10×15s</v>
       </c>
       <c r="J37" t="str">
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>Quads, Glutes</v>
+        <v>Mobility</v>
       </c>
       <c r="L37" t="str">
-        <v>Calves, Hamstrings</v>
+        <v/>
       </c>
       <c r="M37" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N37" t="str">
-        <v>B-d6s3</v>
+        <v>B-d1s11</v>
       </c>
       <c r="O37" t="str">
-        <v>splitjump</v>
+        <v>canoe</v>
       </c>
     </row>
     <row r="38">
@@ -5060,43 +5088,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C38" t="str">
-        <v>Canoe Stretch</v>
+        <v>Chest Press</v>
       </c>
       <c r="D38" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="E38">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F38">
         <v>4</v>
       </c>
-      <c r="G38" t="str">
-        <v/>
-      </c>
-      <c r="H38">
-        <v>15</v>
+      <c r="G38">
+        <v>6</v>
+      </c>
+      <c r="H38" t="str">
+        <v/>
       </c>
       <c r="I38" t="str">
-        <v>10×15s, 10×15s, 10×15s, 10×15s</v>
-      </c>
-      <c r="J38" t="str">
-        <v/>
+        <v>35×6, 35×6, 35×6, 35×6</v>
+      </c>
+      <c r="J38">
+        <v>840</v>
       </c>
       <c r="K38" t="str">
-        <v>Mobility</v>
+        <v>Chest</v>
       </c>
       <c r="L38" t="str">
-        <v/>
+        <v>Front delts, Triceps</v>
       </c>
       <c r="M38" t="str">
         <v>From check-off</v>
       </c>
       <c r="N38" t="str">
-        <v>B-d1s11</v>
+        <v>B-d1s8</v>
       </c>
       <c r="O38" t="str">
-        <v>canoe</v>
+        <v>chestpress</v>
       </c>
     </row>
     <row r="39">
@@ -5107,16 +5135,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="C39" t="str">
-        <v>Chest Press</v>
+        <v>DB 6 Ways</v>
       </c>
       <c r="D39" t="str">
         <v>Strength</v>
       </c>
       <c r="E39">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="F39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G39">
         <v>6</v>
@@ -5125,25 +5153,25 @@
         <v/>
       </c>
       <c r="I39" t="str">
-        <v>35×6, 35×6, 35×6, 35×6</v>
+        <v>5×6, 5×6</v>
       </c>
       <c r="J39">
-        <v>840</v>
+        <v>60</v>
       </c>
       <c r="K39" t="str">
-        <v>Chest</v>
+        <v>Front delts, Side delts</v>
       </c>
       <c r="L39" t="str">
-        <v>Front delts, Triceps</v>
+        <v/>
       </c>
       <c r="M39" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N39" t="str">
-        <v>B-d1s8</v>
+        <v>B-d2s8</v>
       </c>
       <c r="O39" t="str">
-        <v>chestpress</v>
+        <v>db6</v>
       </c>
     </row>
     <row r="40">
@@ -5154,16 +5182,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="C40" t="str">
-        <v>DB 6 Ways</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="D40" t="str">
         <v>Strength</v>
       </c>
       <c r="E40">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G40">
         <v>6</v>
@@ -5172,25 +5200,25 @@
         <v/>
       </c>
       <c r="I40" t="str">
-        <v>5×6, 5×6</v>
+        <v>200×6, 200×6, 200×6, 200×6</v>
       </c>
       <c r="J40">
-        <v>60</v>
+        <v>4800</v>
       </c>
       <c r="K40" t="str">
-        <v>Front delts, Side delts</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="L40" t="str">
         <v/>
       </c>
       <c r="M40" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N40" t="str">
-        <v>B-d2s8</v>
+        <v>B-d1s10</v>
       </c>
       <c r="O40" t="str">
-        <v>db6</v>
+        <v>grip</v>
       </c>
     </row>
     <row r="41">
@@ -5201,43 +5229,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C41" t="str">
-        <v>Grip Trainer</v>
+        <v>Hack Squat</v>
       </c>
       <c r="D41" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E41">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="F41">
         <v>4</v>
       </c>
       <c r="G41">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H41" t="str">
         <v/>
       </c>
       <c r="I41" t="str">
-        <v>200×6, 200×6, 200×6, 200×6</v>
+        <v>270×15, 270×15, 270×15, 270×15</v>
       </c>
       <c r="J41">
-        <v>4800</v>
+        <v>16200</v>
       </c>
       <c r="K41" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Quads</v>
       </c>
       <c r="L41" t="str">
-        <v/>
+        <v>Glutes, Inner thigh (adductors)</v>
       </c>
       <c r="M41" t="str">
         <v>From check-off</v>
       </c>
       <c r="N41" t="str">
-        <v>B-d1s10</v>
+        <v>B-d1s2</v>
       </c>
       <c r="O41" t="str">
-        <v>grip</v>
+        <v>hack</v>
       </c>
     </row>
     <row r="42">
@@ -5248,13 +5276,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="C42" t="str">
-        <v>Hack Squat</v>
+        <v>Lat Pulldown</v>
       </c>
       <c r="D42" t="str">
         <v>Hypertrophy</v>
       </c>
       <c r="E42">
-        <v>270</v>
+        <v>45</v>
       </c>
       <c r="F42">
         <v>4</v>
@@ -5266,25 +5294,25 @@
         <v/>
       </c>
       <c r="I42" t="str">
-        <v>270×15, 270×15, 270×15, 270×15</v>
+        <v>45×15, 45×15, 45×15, 45×15</v>
       </c>
       <c r="J42">
-        <v>16200</v>
+        <v>2700</v>
       </c>
       <c r="K42" t="str">
-        <v>Quads</v>
+        <v>Lats</v>
       </c>
       <c r="L42" t="str">
-        <v>Glutes, Inner thigh (adductors)</v>
+        <v>Biceps, Upper back, Rear delts</v>
       </c>
       <c r="M42" t="str">
         <v>From check-off</v>
       </c>
       <c r="N42" t="str">
-        <v>B-d1s2</v>
+        <v>B-d1s1</v>
       </c>
       <c r="O42" t="str">
-        <v>hack</v>
+        <v>latpdbi</v>
       </c>
     </row>
     <row r="43">
@@ -5295,43 +5323,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C43" t="str">
-        <v>Lat Pulldown</v>
+        <v>Outer Thigh Adduction</v>
       </c>
       <c r="D43" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E43">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="F43">
         <v>4</v>
       </c>
       <c r="G43">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H43" t="str">
         <v/>
       </c>
       <c r="I43" t="str">
-        <v>45×15, 45×15, 45×15, 45×15</v>
+        <v>160×6, 160×6, 160×6, 160×6</v>
       </c>
       <c r="J43">
-        <v>2700</v>
+        <v>3840</v>
       </c>
       <c r="K43" t="str">
-        <v>Lats</v>
+        <v>Outer hip (abductors)</v>
       </c>
       <c r="L43" t="str">
-        <v>Biceps, Upper back, Rear delts</v>
+        <v>Glutes</v>
       </c>
       <c r="M43" t="str">
         <v>From check-off</v>
       </c>
       <c r="N43" t="str">
-        <v>B-d1s1</v>
+        <v>B-d1s6</v>
       </c>
       <c r="O43" t="str">
-        <v>latpdbi</v>
+        <v>outerthigh</v>
       </c>
     </row>
     <row r="44">
@@ -5342,13 +5370,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="C44" t="str">
-        <v>Outer Thigh Adduction</v>
+        <v>Plate Torso Rotation</v>
       </c>
       <c r="D44" t="str">
         <v>Strength</v>
       </c>
       <c r="E44">
-        <v>160</v>
+        <v>10</v>
       </c>
       <c r="F44">
         <v>4</v>
@@ -5360,25 +5388,25 @@
         <v/>
       </c>
       <c r="I44" t="str">
-        <v>160×6, 160×6, 160×6, 160×6</v>
+        <v>10×6, 10×6, 10×6, 10×6</v>
       </c>
       <c r="J44">
-        <v>3840</v>
+        <v>240</v>
       </c>
       <c r="K44" t="str">
-        <v>Outer hip (abductors)</v>
+        <v>Obliques</v>
       </c>
       <c r="L44" t="str">
-        <v>Glutes</v>
+        <v>Abs</v>
       </c>
       <c r="M44" t="str">
         <v>From check-off</v>
       </c>
       <c r="N44" t="str">
-        <v>B-d1s6</v>
+        <v>B-d1s4</v>
       </c>
       <c r="O44" t="str">
-        <v>outerthigh</v>
+        <v>platerot</v>
       </c>
     </row>
     <row r="45">
@@ -5389,13 +5417,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="C45" t="str">
-        <v>Plate Torso Rotation</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="D45" t="str">
         <v>Strength</v>
       </c>
       <c r="E45">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F45">
         <v>4</v>
@@ -5407,72 +5435,72 @@
         <v/>
       </c>
       <c r="I45" t="str">
-        <v>10×6, 10×6, 10×6, 10×6</v>
+        <v>50×6, 50×6, 50×6, 50×6</v>
       </c>
       <c r="J45">
-        <v>240</v>
+        <v>1200</v>
       </c>
       <c r="K45" t="str">
-        <v>Obliques</v>
+        <v>Lower back</v>
       </c>
       <c r="L45" t="str">
-        <v>Abs</v>
+        <v>Glutes, Hamstrings, Upper back</v>
       </c>
       <c r="M45" t="str">
         <v>From check-off</v>
       </c>
       <c r="N45" t="str">
-        <v>B-d1s4</v>
+        <v>B-d1s8</v>
       </c>
       <c r="O45" t="str">
-        <v>platerot</v>
+        <v>zercher</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-07</v>
       </c>
       <c r="B46" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C46" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Chest Press</v>
       </c>
       <c r="D46" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E46">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G46">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H46" t="str">
         <v/>
       </c>
       <c r="I46" t="str">
-        <v>50×6, 50×6, 50×6, 50×6</v>
+        <v>25×15, 25×12</v>
       </c>
       <c r="J46">
-        <v>1200</v>
+        <v>675</v>
       </c>
       <c r="K46" t="str">
-        <v>Lower back</v>
+        <v>Chest</v>
       </c>
       <c r="L46" t="str">
-        <v>Glutes, Hamstrings, Upper back</v>
+        <v>Front delts, Triceps</v>
       </c>
       <c r="M46" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N46" t="str">
-        <v>B-d1s8</v>
+        <v>B-d2s5</v>
       </c>
       <c r="O46" t="str">
-        <v>zercher</v>
+        <v>chestpress</v>
       </c>
     </row>
     <row r="47">
@@ -5483,43 +5511,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C47" t="str">
-        <v>Chest Press</v>
+        <v>Face Pull</v>
       </c>
       <c r="D47" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E47">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F47">
         <v>2</v>
       </c>
       <c r="G47">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H47" t="str">
         <v/>
       </c>
       <c r="I47" t="str">
-        <v>25×15, 25×12</v>
+        <v>27×6, 27×6</v>
       </c>
       <c r="J47">
-        <v>675</v>
+        <v>324</v>
       </c>
       <c r="K47" t="str">
-        <v>Chest</v>
+        <v>Rear delts</v>
       </c>
       <c r="L47" t="str">
-        <v>Front delts, Triceps</v>
+        <v>Upper back, Traps</v>
       </c>
       <c r="M47" t="str">
         <v/>
       </c>
       <c r="N47" t="str">
-        <v>B-d2s5</v>
+        <v>B-d2s3</v>
       </c>
       <c r="O47" t="str">
-        <v>chestpress</v>
+        <v>facepull</v>
       </c>
     </row>
     <row r="48">
@@ -5530,16 +5558,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="C48" t="str">
-        <v>Face Pull</v>
+        <v>Farmers Carry</v>
       </c>
       <c r="D48" t="str">
         <v>Strength</v>
       </c>
       <c r="E48">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G48">
         <v>6</v>
@@ -5548,25 +5576,25 @@
         <v/>
       </c>
       <c r="I48" t="str">
-        <v>27×6, 27×6</v>
+        <v>40×6, 40×6, 40×6, 40×6</v>
       </c>
       <c r="J48">
-        <v>324</v>
+        <v>960</v>
       </c>
       <c r="K48" t="str">
-        <v>Rear delts</v>
+        <v>Forearms &amp; grip, Traps</v>
       </c>
       <c r="L48" t="str">
-        <v>Upper back, Traps</v>
+        <v>Obliques, Abs</v>
       </c>
       <c r="M48" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N48" t="str">
-        <v>B-d2s3</v>
+        <v>B-d2s1</v>
       </c>
       <c r="O48" t="str">
-        <v>facepull</v>
+        <v>farmers</v>
       </c>
     </row>
     <row r="49">
@@ -5577,13 +5605,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="C49" t="str">
-        <v>Farmers Carry</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="D49" t="str">
         <v>Strength</v>
       </c>
       <c r="E49">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="F49">
         <v>4</v>
@@ -5595,25 +5623,25 @@
         <v/>
       </c>
       <c r="I49" t="str">
-        <v>40×6, 40×6, 40×6, 40×6</v>
+        <v>200×6, 200×6, 200×6, 200×6</v>
       </c>
       <c r="J49">
-        <v>960</v>
+        <v>4800</v>
       </c>
       <c r="K49" t="str">
-        <v>Forearms &amp; grip, Traps</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="L49" t="str">
-        <v>Obliques, Abs</v>
+        <v/>
       </c>
       <c r="M49" t="str">
         <v>From check-off</v>
       </c>
       <c r="N49" t="str">
-        <v>B-d2s1</v>
+        <v>B-d2s7</v>
       </c>
       <c r="O49" t="str">
-        <v>farmers</v>
+        <v>grip</v>
       </c>
     </row>
     <row r="50">
@@ -5624,16 +5652,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="C50" t="str">
-        <v>Grip Trainer</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="D50" t="str">
         <v>Strength</v>
       </c>
       <c r="E50">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="F50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G50">
         <v>6</v>
@@ -5642,25 +5670,25 @@
         <v/>
       </c>
       <c r="I50" t="str">
-        <v>200×6, 200×6, 200×6, 200×6</v>
+        <v>320×6, 320×6</v>
       </c>
       <c r="J50">
-        <v>4800</v>
+        <v>3840</v>
       </c>
       <c r="K50" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Glutes</v>
       </c>
       <c r="L50" t="str">
-        <v/>
+        <v>Hamstrings</v>
       </c>
       <c r="M50" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N50" t="str">
-        <v>B-d2s7</v>
+        <v>B-d2s5</v>
       </c>
       <c r="O50" t="str">
-        <v>grip</v>
+        <v>hipthrust</v>
       </c>
     </row>
     <row r="51">
@@ -5671,43 +5699,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C51" t="str">
-        <v>Hip Thrust</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="D51" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="E51">
-        <v>320</v>
+        <v>15</v>
       </c>
       <c r="F51">
-        <v>2</v>
-      </c>
-      <c r="G51">
-        <v>6</v>
-      </c>
-      <c r="H51" t="str">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51">
+        <v>15</v>
       </c>
       <c r="I51" t="str">
-        <v>320×6, 320×6</v>
-      </c>
-      <c r="J51">
-        <v>3840</v>
+        <v>15×15s, 15×15s, 15×15s</v>
+      </c>
+      <c r="J51" t="str">
+        <v/>
       </c>
       <c r="K51" t="str">
-        <v>Glutes</v>
+        <v>Abs, Hip flexors</v>
       </c>
       <c r="L51" t="str">
-        <v>Hamstrings</v>
+        <v/>
       </c>
       <c r="M51" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N51" t="str">
-        <v>B-d2s5</v>
+        <v>B-d1s9</v>
       </c>
       <c r="O51" t="str">
-        <v>hipthrust</v>
+        <v>kbleg</v>
       </c>
     </row>
     <row r="52">
@@ -5718,43 +5746,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C52" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Overhead Tricep Extension</v>
       </c>
       <c r="D52" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="E52">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F52">
-        <v>3</v>
-      </c>
-      <c r="G52" t="str">
-        <v/>
-      </c>
-      <c r="H52">
-        <v>15</v>
+        <v>2</v>
+      </c>
+      <c r="G52">
+        <v>6</v>
+      </c>
+      <c r="H52" t="str">
+        <v/>
       </c>
       <c r="I52" t="str">
-        <v>15×15s, 15×15s, 15×15s</v>
-      </c>
-      <c r="J52" t="str">
-        <v/>
+        <v>17×6, 17×6</v>
+      </c>
+      <c r="J52">
+        <v>204</v>
       </c>
       <c r="K52" t="str">
-        <v>Abs, Hip flexors</v>
+        <v>Triceps</v>
       </c>
       <c r="L52" t="str">
         <v/>
       </c>
       <c r="M52" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N52" t="str">
-        <v>B-d1s9</v>
+        <v>B-d2s2</v>
       </c>
       <c r="O52" t="str">
-        <v>kbleg</v>
+        <v>ohtri</v>
       </c>
     </row>
     <row r="53">
@@ -5765,7 +5793,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="C53" t="str">
-        <v>Kneeling Cable Ab Crunch</v>
+        <v>Seated Cable Crunch</v>
       </c>
       <c r="D53" t="str">
         <v>Strength</v>
@@ -5798,10 +5826,10 @@
         <v/>
       </c>
       <c r="N53" t="str">
-        <v>B-d2s4</v>
+        <v>B-xmuy1nsai5fs</v>
       </c>
       <c r="O53" t="str">
-        <v>cablecrunch</v>
+        <v>seated-cable-crunch</v>
       </c>
     </row>
     <row r="54">
@@ -5812,96 +5840,49 @@
         <v>2026-10-04</v>
       </c>
       <c r="C54" t="str">
-        <v>Overhead Tricep Extension</v>
+        <v>Zottman Curl</v>
       </c>
       <c r="D54" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E54">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G54">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H54" t="str">
         <v/>
       </c>
       <c r="I54" t="str">
-        <v>17×6, 17×6</v>
+        <v>15×15, 15×15, 15×15</v>
       </c>
       <c r="J54">
-        <v>204</v>
+        <v>675</v>
       </c>
       <c r="K54" t="str">
-        <v>Triceps</v>
+        <v>Biceps, Forearms &amp; grip</v>
       </c>
       <c r="L54" t="str">
         <v/>
       </c>
       <c r="M54" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N54" t="str">
-        <v>B-d2s2</v>
+        <v>B-d1s9</v>
       </c>
       <c r="O54" t="str">
-        <v>ohtri</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>2026-10-07</v>
-      </c>
-      <c r="B55" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="C55" t="str">
-        <v>Zottman Curl</v>
-      </c>
-      <c r="D55" t="str">
-        <v>Hypertrophy</v>
-      </c>
-      <c r="E55">
-        <v>15</v>
-      </c>
-      <c r="F55">
-        <v>3</v>
-      </c>
-      <c r="G55">
-        <v>15</v>
-      </c>
-      <c r="H55" t="str">
-        <v/>
-      </c>
-      <c r="I55" t="str">
-        <v>15×15, 15×15, 15×15</v>
-      </c>
-      <c r="J55">
-        <v>675</v>
-      </c>
-      <c r="K55" t="str">
-        <v>Biceps, Forearms &amp; grip</v>
-      </c>
-      <c r="L55" t="str">
-        <v/>
-      </c>
-      <c r="M55" t="str">
-        <v>From check-off</v>
-      </c>
-      <c r="N55" t="str">
-        <v>B-d1s9</v>
-      </c>
-      <c r="O55" t="str">
         <v>zottman</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O55"/>
+  <autoFilter ref="A1:O54"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O54"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5990,16 +5971,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B5" t="str">
-        <v>Upper back</v>
+        <v>Inner thigh (adductors)</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="6">
@@ -6007,16 +5988,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B6" t="str">
-        <v>Rear delts</v>
+        <v>Upper back</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="7">
@@ -6024,16 +6005,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B7" t="str">
-        <v>Inner thigh (adductors)</v>
+        <v>Rear delts</v>
       </c>
       <c r="C7">
         <v>8</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E7">
-        <v>11.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -6075,16 +6056,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B10" t="str">
-        <v>Lats</v>
+        <v>Hamstrings</v>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E10">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11">
@@ -6092,16 +6073,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B11" t="str">
-        <v>Hamstrings</v>
+        <v>Abs</v>
       </c>
       <c r="C11">
+        <v>7</v>
+      </c>
+      <c r="D11">
         <v>0</v>
       </c>
-      <c r="D11">
-        <v>15</v>
-      </c>
       <c r="E11">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -6109,16 +6090,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B12" t="str">
-        <v>Abs</v>
+        <v>Chest</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -6126,16 +6107,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B13" t="str">
-        <v>Biceps</v>
+        <v>Triceps</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E13">
-        <v>7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="14">
@@ -6143,16 +6124,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B14" t="str">
-        <v>Chest</v>
+        <v>Side delts</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -6160,16 +6141,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B15" t="str">
-        <v>Triceps</v>
+        <v>Biceps</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D15">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E15">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -6177,16 +6158,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B16" t="str">
-        <v>Side delts</v>
+        <v>Lats</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -6668,7 +6649,7 @@
         <v>82</v>
       </c>
       <c r="H2">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -6679,19 +6660,19 @@
         <v>B</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H3">
         <v>28</v>
@@ -7114,7 +7095,7 @@
         <v>Exported</v>
       </c>
       <c r="B43" t="str">
-        <v>2026-10-07T11:56:02.918Z</v>
+        <v>2026-10-07T12:02:12.386Z</v>
       </c>
     </row>
   </sheetData>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -25,7 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5">Settings!$A$1:$B$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">Programs!$A$1:$R$145</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Program info'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11">Config!$A$1:$B$16</definedName>
   </definedNames>
@@ -1469,7 +1469,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1512,10 +1512,27 @@
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Emuy4gmmbono4</v>
+      </c>
+      <c r="B3" t="str">
+        <v>tibialis-raise</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Tibialis Raise</v>
+      </c>
+      <c r="D3" t="str">
+        <v>hyp</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E2"/>
+  <autoFilter ref="A1:E3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3205,7 +3222,7 @@
         <v>ex</v>
       </c>
       <c r="B3" t="str">
-        <v>{"deadlift":{"n":"Deadlift","eq":"barbell"},"zercher":{"eq":"shortbar"},"split-stance-cable-hip-rotation":{"n":"Split Stance Cable Hip Rotation","url":"https://youtu.be/ixIEilUM2aY","eq":"cable"},"clean-jerk-overhead-press":{"n":"Clean Jerk &amp; Overhead Press","eq":"dumbbell"},"seated-cable-crunch":{"n":"Seated Cable Crunch","url":"https://youtube.com/shorts/bIbm-p6Q4s8?is=aiC1fOhPbN5QMcgq","eq":"cable"}}</v>
+        <v>{"deadlift":{"n":"Deadlift","eq":"barbell"},"zercher":{"eq":"shortbar"},"split-stance-cable-hip-rotation":{"n":"Split Stance Cable Hip Rotation","url":"https://youtu.be/ixIEilUM2aY","eq":"cable"},"clean-jerk-overhead-press":{"n":"Clean Jerk &amp; Overhead Press","eq":"dumbbell"},"seated-cable-crunch":{"n":"Seated Cable Crunch","url":"https://youtube.com/shorts/bIbm-p6Q4s8?is=aiC1fOhPbN5QMcgq","eq":"cable"},"tibialis-raise":{"n":"Tibialis Raise","url":"https://youtu.be/OPEuhclsTUQ","eq":"bodyweight"}}</v>
       </c>
     </row>
     <row r="4">
@@ -3221,7 +3238,7 @@
         <v>ghBackup</v>
       </c>
       <c r="B5" t="str">
-        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"1b8mcee","last":{"at":"2026-10-07T11:56:05.483Z","url":"https://github.com/jacgit18/iron-log/commit/7f416b7502f7dbd285c22349fe7ecf4ddb8473aa"}}</v>
+        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"4v1m8q","last":{"at":"2026-10-07T12:02:14.826Z","url":"https://github.com/jacgit18/iron-log/commit/09a41cb84b110fe71b69d392576bb74ad6e95a38"}}</v>
       </c>
     </row>
     <row r="6">
@@ -7095,7 +7112,7 @@
         <v>Exported</v>
       </c>
       <c r="B43" t="str">
-        <v>2026-10-07T12:02:12.386Z</v>
+        <v>2026-10-07T13:07:51.040Z</v>
       </c>
     </row>
   </sheetData>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -25,7 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5">Settings!$A$1:$B$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">Programs!$A$1:$R$145</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Program info'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$117</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11">Config!$A$1:$B$16</definedName>
   </definedNames>
@@ -1469,7 +1469,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E8"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1529,10 +1529,95 @@
         <v/>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Emuy5s4fovrz0</v>
+      </c>
+      <c r="B4" t="str">
+        <v>dragon-flag</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Dragon Flag</v>
+      </c>
+      <c r="D4" t="str">
+        <v>strength</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Emuy6td0z0ewk</v>
+      </c>
+      <c r="B5" t="str">
+        <v>garhammer-raise</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Garhammer Raise</v>
+      </c>
+      <c r="D5" t="str">
+        <v>strength</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Emuy6uaskjuej</v>
+      </c>
+      <c r="B6" t="str">
+        <v>abb-roller</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Abb Roller</v>
+      </c>
+      <c r="D6" t="str">
+        <v>strength</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Emuy6v9f8x8gv</v>
+      </c>
+      <c r="B7" t="str">
+        <v>bench-reverse-crunch</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Bench Reverse Crunch</v>
+      </c>
+      <c r="D7" t="str">
+        <v>strength</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Emuy6w0l72ybj</v>
+      </c>
+      <c r="B8" t="str">
+        <v>dead-bugs</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Dead Bugs</v>
+      </c>
+      <c r="D8" t="str">
+        <v>strength</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E3"/>
+  <autoFilter ref="A1:E8"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3222,7 +3307,7 @@
         <v>ex</v>
       </c>
       <c r="B3" t="str">
-        <v>{"deadlift":{"n":"Deadlift","eq":"barbell"},"zercher":{"eq":"shortbar"},"split-stance-cable-hip-rotation":{"n":"Split Stance Cable Hip Rotation","url":"https://youtu.be/ixIEilUM2aY","eq":"cable"},"clean-jerk-overhead-press":{"n":"Clean Jerk &amp; Overhead Press","eq":"dumbbell"},"seated-cable-crunch":{"n":"Seated Cable Crunch","url":"https://youtube.com/shorts/bIbm-p6Q4s8?is=aiC1fOhPbN5QMcgq","eq":"cable"},"tibialis-raise":{"n":"Tibialis Raise","url":"https://youtu.be/OPEuhclsTUQ","eq":"bodyweight"}}</v>
+        <v>{"deadlift":{"n":"Deadlift","eq":"barbell"},"zercher":{"eq":"shortbar"},"split-stance-cable-hip-rotation":{"n":"Split Stance Cable Hip Rotation","url":"https://youtu.be/ixIEilUM2aY","eq":"cable"},"clean-jerk-overhead-press":{"n":"Clean Jerk &amp; Overhead Press","eq":"dumbbell"},"seated-cable-crunch":{"n":"Seated Cable Crunch","url":"https://youtube.com/shorts/bIbm-p6Q4s8?is=aiC1fOhPbN5QMcgq","eq":"cable"},"tibialis-raise":{"n":"Tibialis Raise","url":"https://youtu.be/OPEuhclsTUQ","eq":"bodyweight"},"dragon-flag":{"n":"Dragon Flag","eq":"bodyweight"},"garhammer-raise":{"n":"Garhammer Raise","url":"https://youtu.be/0ShG8aVIvms?t=836"},"abb-roller":{"n":"Abb Roller","eq":"other"},"bench-reverse-crunch":{"n":"Bench Reverse Crunch"},"dead-bugs":{"n":"Dead Bugs"}}</v>
       </c>
     </row>
     <row r="4">
@@ -3238,7 +3323,7 @@
         <v>ghBackup</v>
       </c>
       <c r="B5" t="str">
-        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"4v1m8q","last":{"at":"2026-10-07T12:02:14.826Z","url":"https://github.com/jacgit18/iron-log/commit/09a41cb84b110fe71b69d392576bb74ad6e95a38"}}</v>
+        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"18txhn8","last":{"at":"2026-10-07T13:07:53.744Z","url":"https://github.com/jacgit18/iron-log/commit/a4a4415db914cc2a8bb4b5dbc734452a9362079d"}}</v>
       </c>
     </row>
     <row r="6">
@@ -7112,7 +7197,7 @@
         <v>Exported</v>
       </c>
       <c r="B43" t="str">
-        <v>2026-10-07T13:07:51.040Z</v>
+        <v>2026-10-07T15:00:23.192Z</v>
       </c>
     </row>
   </sheetData>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -25,8 +25,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5">Settings!$A$1:$B$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">Programs!$A$1:$R$145</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Program info'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$119</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11">Config!$A$1:$B$16</definedName>
   </definedNames>
 </workbook>
@@ -1469,7 +1469,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1614,17 +1614,51 @@
         <v/>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Emuy8r5c170x4</v>
+      </c>
+      <c r="B9" t="str">
+        <v>duck-sled-push</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Duck Sled Push</v>
+      </c>
+      <c r="D9" t="str">
+        <v>exp</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Emuy8tsxonx69</v>
+      </c>
+      <c r="B10" t="str">
+        <v>squat-walks</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Squat Walks</v>
+      </c>
+      <c r="D10" t="str">
+        <v>strength</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E8"/>
+  <autoFilter ref="A1:E10"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E10"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D117"/>
+  <dimension ref="A1:D119"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.83203125" customWidth="1"/>
@@ -2743,13 +2777,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B80" t="str">
-        <v>done</v>
+        <v>extra</v>
       </c>
       <c r="C80" t="str">
-        <v>B-d6s1</v>
+        <v>X-muy8rvy9whc0</v>
       </c>
       <c r="D80" t="str">
-        <v>Yes</v>
+        <v>{"id":"X-muy8rvy9whc0","day":3,"ex":"duck-sled-push","ph":"strength","note":""}</v>
       </c>
     </row>
     <row r="81">
@@ -2760,7 +2794,7 @@
         <v>done</v>
       </c>
       <c r="C81" t="str">
-        <v>B-d6s2</v>
+        <v>B-d6s1</v>
       </c>
       <c r="D81" t="str">
         <v>Yes</v>
@@ -2774,7 +2808,7 @@
         <v>done</v>
       </c>
       <c r="C82" t="str">
-        <v>B-d6s3</v>
+        <v>B-d6s2</v>
       </c>
       <c r="D82" t="str">
         <v>Yes</v>
@@ -2788,7 +2822,7 @@
         <v>done</v>
       </c>
       <c r="C83" t="str">
-        <v>B-d6s6</v>
+        <v>B-d6s3</v>
       </c>
       <c r="D83" t="str">
         <v>Yes</v>
@@ -2802,7 +2836,7 @@
         <v>done</v>
       </c>
       <c r="C84" t="str">
-        <v>B-d6s4</v>
+        <v>B-d6s6</v>
       </c>
       <c r="D84" t="str">
         <v>Yes</v>
@@ -2816,7 +2850,7 @@
         <v>done</v>
       </c>
       <c r="C85" t="str">
-        <v>B-d1s3</v>
+        <v>B-d6s4</v>
       </c>
       <c r="D85" t="str">
         <v>Yes</v>
@@ -2830,7 +2864,7 @@
         <v>done</v>
       </c>
       <c r="C86" t="str">
-        <v>B-sled6</v>
+        <v>B-d1s3</v>
       </c>
       <c r="D86" t="str">
         <v>Yes</v>
@@ -2844,7 +2878,7 @@
         <v>done</v>
       </c>
       <c r="C87" t="str">
-        <v>B-d5s2</v>
+        <v>B-sled6</v>
       </c>
       <c r="D87" t="str">
         <v>Yes</v>
@@ -2858,7 +2892,7 @@
         <v>done</v>
       </c>
       <c r="C88" t="str">
-        <v>B-d1s1</v>
+        <v>B-d5s2</v>
       </c>
       <c r="D88" t="str">
         <v>Yes</v>
@@ -2872,7 +2906,7 @@
         <v>done</v>
       </c>
       <c r="C89" t="str">
-        <v>B-d1s4</v>
+        <v>B-d1s1</v>
       </c>
       <c r="D89" t="str">
         <v>Yes</v>
@@ -2886,7 +2920,7 @@
         <v>done</v>
       </c>
       <c r="C90" t="str">
-        <v>B-d1s11</v>
+        <v>B-d1s4</v>
       </c>
       <c r="D90" t="str">
         <v>Yes</v>
@@ -2900,7 +2934,7 @@
         <v>done</v>
       </c>
       <c r="C91" t="str">
-        <v>B-d1s8</v>
+        <v>B-d1s11</v>
       </c>
       <c r="D91" t="str">
         <v>Yes</v>
@@ -2914,7 +2948,7 @@
         <v>done</v>
       </c>
       <c r="C92" t="str">
-        <v>B-d1s2</v>
+        <v>B-d1s8</v>
       </c>
       <c r="D92" t="str">
         <v>Yes</v>
@@ -2928,7 +2962,7 @@
         <v>done</v>
       </c>
       <c r="C93" t="str">
-        <v>B-d1s6</v>
+        <v>B-d1s2</v>
       </c>
       <c r="D93" t="str">
         <v>Yes</v>
@@ -2942,7 +2976,7 @@
         <v>done</v>
       </c>
       <c r="C94" t="str">
-        <v>B-d1s10</v>
+        <v>B-d1s6</v>
       </c>
       <c r="D94" t="str">
         <v>Yes</v>
@@ -2956,7 +2990,7 @@
         <v>done</v>
       </c>
       <c r="C95" t="str">
-        <v>B-d2s8</v>
+        <v>B-d1s10</v>
       </c>
       <c r="D95" t="str">
         <v>Yes</v>
@@ -2970,7 +3004,7 @@
         <v>done</v>
       </c>
       <c r="C96" t="str">
-        <v>B-d1s9</v>
+        <v>B-d2s8</v>
       </c>
       <c r="D96" t="str">
         <v>Yes</v>
@@ -2984,7 +3018,7 @@
         <v>done</v>
       </c>
       <c r="C97" t="str">
-        <v>B-d2s1</v>
+        <v>B-d1s9</v>
       </c>
       <c r="D97" t="str">
         <v>Yes</v>
@@ -2998,7 +3032,7 @@
         <v>done</v>
       </c>
       <c r="C98" t="str">
-        <v>B-d2s1#0</v>
+        <v>B-d2s1</v>
       </c>
       <c r="D98" t="str">
         <v>Yes</v>
@@ -3012,7 +3046,7 @@
         <v>done</v>
       </c>
       <c r="C99" t="str">
-        <v>B-d2s2</v>
+        <v>B-d2s1#0</v>
       </c>
       <c r="D99" t="str">
         <v>Yes</v>
@@ -3026,7 +3060,7 @@
         <v>done</v>
       </c>
       <c r="C100" t="str">
-        <v>B-d2s4</v>
+        <v>B-d2s2</v>
       </c>
       <c r="D100" t="str">
         <v>Yes</v>
@@ -3040,7 +3074,7 @@
         <v>done</v>
       </c>
       <c r="C101" t="str">
-        <v>B-d2s3</v>
+        <v>B-d2s4</v>
       </c>
       <c r="D101" t="str">
         <v>Yes</v>
@@ -3054,7 +3088,7 @@
         <v>done</v>
       </c>
       <c r="C102" t="str">
-        <v>B-d2s3#1</v>
+        <v>B-d2s3</v>
       </c>
       <c r="D102" t="str">
         <v>Yes</v>
@@ -3068,7 +3102,7 @@
         <v>done</v>
       </c>
       <c r="C103" t="str">
-        <v>B-d2s5</v>
+        <v>B-d2s3#1</v>
       </c>
       <c r="D103" t="str">
         <v>Yes</v>
@@ -3082,7 +3116,7 @@
         <v>done</v>
       </c>
       <c r="C104" t="str">
-        <v>B-d2s7</v>
+        <v>B-d2s5</v>
       </c>
       <c r="D104" t="str">
         <v>Yes</v>
@@ -3096,7 +3130,7 @@
         <v>done</v>
       </c>
       <c r="C105" t="str">
-        <v>B-xmuy1nsai5fs#0</v>
+        <v>B-d2s7</v>
       </c>
       <c r="D105" t="str">
         <v>Yes</v>
@@ -3107,10 +3141,10 @@
         <v>2026-10-04</v>
       </c>
       <c r="B106" t="str">
-        <v>skipped</v>
+        <v>done</v>
       </c>
       <c r="C106" t="str">
-        <v>B-d6s5</v>
+        <v>B-xmuy1nsai5fs#0</v>
       </c>
       <c r="D106" t="str">
         <v>Yes</v>
@@ -3124,7 +3158,7 @@
         <v>skipped</v>
       </c>
       <c r="C107" t="str">
-        <v>B-sled1</v>
+        <v>B-d6s5</v>
       </c>
       <c r="D107" t="str">
         <v>Yes</v>
@@ -3138,7 +3172,7 @@
         <v>skipped</v>
       </c>
       <c r="C108" t="str">
-        <v>B-d1s7</v>
+        <v>B-sled1</v>
       </c>
       <c r="D108" t="str">
         <v>Yes</v>
@@ -3152,7 +3186,7 @@
         <v>skipped</v>
       </c>
       <c r="C109" t="str">
-        <v>B-sled2</v>
+        <v>B-d1s7</v>
       </c>
       <c r="D109" t="str">
         <v>Yes</v>
@@ -3166,7 +3200,7 @@
         <v>skipped</v>
       </c>
       <c r="C110" t="str">
-        <v>B-d2s6</v>
+        <v>B-sled2</v>
       </c>
       <c r="D110" t="str">
         <v>Yes</v>
@@ -3180,7 +3214,7 @@
         <v>skipped</v>
       </c>
       <c r="C111" t="str">
-        <v>B-xmuy1nsai5fs</v>
+        <v>B-d2s6</v>
       </c>
       <c r="D111" t="str">
         <v>Yes</v>
@@ -3191,13 +3225,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B112" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C112" t="str">
-        <v>B-d5s2</v>
-      </c>
-      <c r="D112">
-        <v>6</v>
+        <v>B-xmuy1nsai5fs</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="113">
@@ -3208,7 +3242,7 @@
         <v>moved</v>
       </c>
       <c r="C113" t="str">
-        <v>B-d1s3</v>
+        <v>B-d5s2</v>
       </c>
       <c r="D113">
         <v>6</v>
@@ -3222,10 +3256,10 @@
         <v>moved</v>
       </c>
       <c r="C114" t="str">
-        <v>B-d1s9</v>
+        <v>B-d1s3</v>
       </c>
       <c r="D114">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115">
@@ -3236,10 +3270,10 @@
         <v>moved</v>
       </c>
       <c r="C115" t="str">
-        <v>B-d1s5</v>
+        <v>B-d1s9</v>
       </c>
       <c r="D115">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
@@ -3250,10 +3284,10 @@
         <v>moved</v>
       </c>
       <c r="C116" t="str">
-        <v>B-d2s8</v>
+        <v>B-d1s5</v>
       </c>
       <c r="D116">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -3264,16 +3298,44 @@
         <v>moved</v>
       </c>
       <c r="C117" t="str">
+        <v>B-d2s8</v>
+      </c>
+      <c r="D117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B118" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C118" t="str">
         <v>B-d3s2</v>
       </c>
-      <c r="D117">
+      <c r="D118">
         <v>5</v>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B119" t="str">
+        <v>phase</v>
+      </c>
+      <c r="C119" t="str">
+        <v>X-muy8rvy9whc0:0</v>
+      </c>
+      <c r="D119" t="str">
+        <v>exp</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D117"/>
+  <autoFilter ref="A1:D119"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D117"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D119"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3307,7 +3369,7 @@
         <v>ex</v>
       </c>
       <c r="B3" t="str">
-        <v>{"deadlift":{"n":"Deadlift","eq":"barbell"},"zercher":{"eq":"shortbar"},"split-stance-cable-hip-rotation":{"n":"Split Stance Cable Hip Rotation","url":"https://youtu.be/ixIEilUM2aY","eq":"cable"},"clean-jerk-overhead-press":{"n":"Clean Jerk &amp; Overhead Press","eq":"dumbbell"},"seated-cable-crunch":{"n":"Seated Cable Crunch","url":"https://youtube.com/shorts/bIbm-p6Q4s8?is=aiC1fOhPbN5QMcgq","eq":"cable"},"tibialis-raise":{"n":"Tibialis Raise","url":"https://youtu.be/OPEuhclsTUQ","eq":"bodyweight"},"dragon-flag":{"n":"Dragon Flag","eq":"bodyweight"},"garhammer-raise":{"n":"Garhammer Raise","url":"https://youtu.be/0ShG8aVIvms?t=836"},"abb-roller":{"n":"Abb Roller","eq":"other"},"bench-reverse-crunch":{"n":"Bench Reverse Crunch"},"dead-bugs":{"n":"Dead Bugs"}}</v>
+        <v>{"deadlift":{"n":"Deadlift","eq":"barbell"},"zercher":{"eq":"shortbar"},"split-stance-cable-hip-rotation":{"n":"Split Stance Cable Hip Rotation","url":"https://youtu.be/ixIEilUM2aY","eq":"cable"},"clean-jerk-overhead-press":{"n":"Clean Jerk &amp; Overhead Press","eq":"dumbbell"},"seated-cable-crunch":{"n":"Seated Cable Crunch","url":"https://youtube.com/shorts/bIbm-p6Q4s8?is=aiC1fOhPbN5QMcgq","eq":"cable"},"tibialis-raise":{"n":"Tibialis Raise","url":"https://youtu.be/OPEuhclsTUQ","eq":"bodyweight"},"dragon-flag":{"n":"Dragon Flag","eq":"bodyweight"},"garhammer-raise":{"n":"Garhammer Raise","url":"https://youtu.be/0ShG8aVIvms?t=836"},"abb-roller":{"n":"Abb Roller","eq":"other"},"bench-reverse-crunch":{"n":"Bench Reverse Crunch"},"dead-bugs":{"n":"Dead Bugs"},"duck-sled-push":{"n":"Duck Sled Push","url":"https://www.instagram.com/p/DeKUe-qvgF-/","eq":"other"},"squat-walks":{"n":"Squat Walks","url":"https://www.instagram.com/p/DeKAHsWKK4W/","eq":"dumbbell"}}</v>
       </c>
     </row>
     <row r="4">
@@ -3323,7 +3385,7 @@
         <v>ghBackup</v>
       </c>
       <c r="B5" t="str">
-        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"18txhn8","last":{"at":"2026-10-07T13:07:53.744Z","url":"https://github.com/jacgit18/iron-log/commit/a4a4415db914cc2a8bb4b5dbc734452a9362079d"}}</v>
+        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"1xynas1","last":{"at":"2026-10-07T15:00:26.031Z","url":"https://github.com/jacgit18/iron-log/commit/77a20b494f212861ff53abcef165e51a9078683f"}}</v>
       </c>
     </row>
     <row r="6">
@@ -6226,13 +6288,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B14" t="str">
-        <v>Side delts</v>
+        <v>Biceps</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E14">
         <v>5</v>
@@ -6243,13 +6305,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B15" t="str">
-        <v>Biceps</v>
+        <v>Side delts</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -6260,7 +6322,7 @@
         <v>2026-09-27</v>
       </c>
       <c r="B16" t="str">
-        <v>Lats</v>
+        <v>Obliques</v>
       </c>
       <c r="C16">
         <v>4</v>
@@ -6277,7 +6339,7 @@
         <v>2026-09-27</v>
       </c>
       <c r="B17" t="str">
-        <v>Obliques</v>
+        <v>Lats</v>
       </c>
       <c r="C17">
         <v>4</v>
@@ -6464,13 +6526,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B28" t="str">
-        <v>Chest</v>
+        <v>Lower back</v>
       </c>
       <c r="C28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>8</v>
@@ -6498,13 +6560,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B30" t="str">
-        <v>Lower back</v>
+        <v>Chest</v>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -6515,13 +6577,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B31" t="str">
-        <v>Front delts</v>
+        <v>Biceps</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E31">
         <v>7</v>
@@ -6532,13 +6594,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B32" t="str">
-        <v>Biceps</v>
+        <v>Outer hip (abductors)</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D32">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>7</v>
@@ -6549,13 +6611,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B33" t="str">
-        <v>Outer hip (abductors)</v>
+        <v>Front delts</v>
       </c>
       <c r="C33">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E33">
         <v>7</v>
@@ -6583,13 +6645,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B35" t="str">
-        <v>Triceps</v>
+        <v>Traps</v>
       </c>
       <c r="C35">
+        <v>4</v>
+      </c>
+      <c r="D35">
         <v>2</v>
-      </c>
-      <c r="D35">
-        <v>6</v>
       </c>
       <c r="E35">
         <v>5</v>
@@ -6600,13 +6662,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B36" t="str">
-        <v>Traps</v>
+        <v>Triceps</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E36">
         <v>5</v>
@@ -6768,7 +6830,7 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F3">
         <v>6</v>
@@ -7197,7 +7259,7 @@
         <v>Exported</v>
       </c>
       <c r="B43" t="str">
-        <v>2026-10-07T15:00:23.192Z</v>
+        <v>2026-10-07T18:34:20.762Z</v>
       </c>
     </row>
   </sheetData>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">Programs!$A$1:$R$145</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Program info'!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$121</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11">Config!$A$1:$B$16</definedName>
   </definedNames>
 </workbook>
@@ -1658,7 +1658,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D121"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.83203125" customWidth="1"/>
@@ -2511,13 +2511,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B61" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C61" t="str">
-        <v>A-d3s2</v>
-      </c>
-      <c r="D61">
-        <v>2</v>
+        <v>A-xmuy1vz1s5qy</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="62">
@@ -2525,13 +2525,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B62" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C62" t="str">
-        <v>A-d3s3</v>
-      </c>
-      <c r="D62">
-        <v>2</v>
+        <v>A-xmuy1u0ehkgt</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="63">
@@ -2542,10 +2542,10 @@
         <v>moved</v>
       </c>
       <c r="C63" t="str">
-        <v>A-d2s4</v>
+        <v>A-d3s2</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -2556,10 +2556,10 @@
         <v>moved</v>
       </c>
       <c r="C64" t="str">
-        <v>A-d1s7</v>
+        <v>A-d3s3</v>
       </c>
       <c r="D64">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2570,10 +2570,10 @@
         <v>moved</v>
       </c>
       <c r="C65" t="str">
-        <v>A-d3s6</v>
+        <v>A-d2s4</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -2584,10 +2584,10 @@
         <v>moved</v>
       </c>
       <c r="C66" t="str">
-        <v>A-d3s1</v>
+        <v>A-d1s7</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -2598,10 +2598,10 @@
         <v>moved</v>
       </c>
       <c r="C67" t="str">
-        <v>A-d4s6</v>
+        <v>A-d3s6</v>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -2612,10 +2612,10 @@
         <v>moved</v>
       </c>
       <c r="C68" t="str">
-        <v>A-d2s1</v>
+        <v>A-d3s1</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -2626,7 +2626,7 @@
         <v>moved</v>
       </c>
       <c r="C69" t="str">
-        <v>A-d6s5</v>
+        <v>A-d4s6</v>
       </c>
       <c r="D69">
         <v>5</v>
@@ -2640,10 +2640,10 @@
         <v>moved</v>
       </c>
       <c r="C70" t="str">
-        <v>A-d5s8</v>
+        <v>A-d2s1</v>
       </c>
       <c r="D70">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -2654,10 +2654,10 @@
         <v>moved</v>
       </c>
       <c r="C71" t="str">
-        <v>A-d5s7</v>
+        <v>A-d6s5</v>
       </c>
       <c r="D71">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -2668,7 +2668,7 @@
         <v>moved</v>
       </c>
       <c r="C72" t="str">
-        <v>A-d5s6</v>
+        <v>A-d5s8</v>
       </c>
       <c r="D72">
         <v>6</v>
@@ -2682,7 +2682,7 @@
         <v>moved</v>
       </c>
       <c r="C73" t="str">
-        <v>A-d5s5</v>
+        <v>A-d5s7</v>
       </c>
       <c r="D73">
         <v>6</v>
@@ -2696,7 +2696,7 @@
         <v>moved</v>
       </c>
       <c r="C74" t="str">
-        <v>A-d5s4</v>
+        <v>A-d5s6</v>
       </c>
       <c r="D74">
         <v>6</v>
@@ -2710,7 +2710,7 @@
         <v>moved</v>
       </c>
       <c r="C75" t="str">
-        <v>A-d5s2</v>
+        <v>A-d5s5</v>
       </c>
       <c r="D75">
         <v>6</v>
@@ -2724,7 +2724,7 @@
         <v>moved</v>
       </c>
       <c r="C76" t="str">
-        <v>A-d5s1</v>
+        <v>A-d5s4</v>
       </c>
       <c r="D76">
         <v>6</v>
@@ -2732,30 +2732,30 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2026-10-04</v>
+        <v>2026-09-27</v>
       </c>
       <c r="B77" t="str">
-        <v>rest</v>
+        <v>moved</v>
       </c>
       <c r="C77" t="str">
-        <v/>
-      </c>
-      <c r="D77" t="str">
-        <v>3</v>
+        <v>A-d5s2</v>
+      </c>
+      <c r="D77">
+        <v>6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2026-10-04</v>
+        <v>2026-09-27</v>
       </c>
       <c r="B78" t="str">
-        <v>restOn</v>
+        <v>moved</v>
       </c>
       <c r="C78" t="str">
-        <v/>
-      </c>
-      <c r="D78" t="str">
-        <v>2026-10-06</v>
+        <v>A-d5s1</v>
+      </c>
+      <c r="D78">
+        <v>6</v>
       </c>
     </row>
     <row r="79">
@@ -2763,13 +2763,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B79" t="str">
-        <v>order</v>
+        <v>rest</v>
       </c>
       <c r="C79" t="str">
         <v/>
       </c>
       <c r="D79" t="str">
-        <v>6 1 2 3 4 5 7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2777,13 +2777,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B80" t="str">
-        <v>extra</v>
+        <v>restOn</v>
       </c>
       <c r="C80" t="str">
-        <v>X-muy8rvy9whc0</v>
+        <v/>
       </c>
       <c r="D80" t="str">
-        <v>{"id":"X-muy8rvy9whc0","day":3,"ex":"duck-sled-push","ph":"strength","note":""}</v>
+        <v>2026-10-06</v>
       </c>
     </row>
     <row r="81">
@@ -2791,13 +2791,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B81" t="str">
-        <v>done</v>
+        <v>order</v>
       </c>
       <c r="C81" t="str">
-        <v>B-d6s1</v>
+        <v/>
       </c>
       <c r="D81" t="str">
-        <v>Yes</v>
+        <v>6 1 2 3 4 5 7</v>
       </c>
     </row>
     <row r="82">
@@ -2805,13 +2805,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B82" t="str">
-        <v>done</v>
+        <v>extra</v>
       </c>
       <c r="C82" t="str">
-        <v>B-d6s2</v>
+        <v>X-muy8rvy9whc0</v>
       </c>
       <c r="D82" t="str">
-        <v>Yes</v>
+        <v>{"id":"X-muy8rvy9whc0","day":3,"ex":"duck-sled-push","ph":"strength","note":""}</v>
       </c>
     </row>
     <row r="83">
@@ -2822,7 +2822,7 @@
         <v>done</v>
       </c>
       <c r="C83" t="str">
-        <v>B-d6s3</v>
+        <v>B-d6s1</v>
       </c>
       <c r="D83" t="str">
         <v>Yes</v>
@@ -2836,7 +2836,7 @@
         <v>done</v>
       </c>
       <c r="C84" t="str">
-        <v>B-d6s6</v>
+        <v>B-d6s2</v>
       </c>
       <c r="D84" t="str">
         <v>Yes</v>
@@ -2850,7 +2850,7 @@
         <v>done</v>
       </c>
       <c r="C85" t="str">
-        <v>B-d6s4</v>
+        <v>B-d6s3</v>
       </c>
       <c r="D85" t="str">
         <v>Yes</v>
@@ -2864,7 +2864,7 @@
         <v>done</v>
       </c>
       <c r="C86" t="str">
-        <v>B-d1s3</v>
+        <v>B-d6s6</v>
       </c>
       <c r="D86" t="str">
         <v>Yes</v>
@@ -2878,7 +2878,7 @@
         <v>done</v>
       </c>
       <c r="C87" t="str">
-        <v>B-sled6</v>
+        <v>B-d6s4</v>
       </c>
       <c r="D87" t="str">
         <v>Yes</v>
@@ -2892,7 +2892,7 @@
         <v>done</v>
       </c>
       <c r="C88" t="str">
-        <v>B-d5s2</v>
+        <v>B-d1s3</v>
       </c>
       <c r="D88" t="str">
         <v>Yes</v>
@@ -2906,7 +2906,7 @@
         <v>done</v>
       </c>
       <c r="C89" t="str">
-        <v>B-d1s1</v>
+        <v>B-sled6</v>
       </c>
       <c r="D89" t="str">
         <v>Yes</v>
@@ -2920,7 +2920,7 @@
         <v>done</v>
       </c>
       <c r="C90" t="str">
-        <v>B-d1s4</v>
+        <v>B-d5s2</v>
       </c>
       <c r="D90" t="str">
         <v>Yes</v>
@@ -2934,7 +2934,7 @@
         <v>done</v>
       </c>
       <c r="C91" t="str">
-        <v>B-d1s11</v>
+        <v>B-d1s1</v>
       </c>
       <c r="D91" t="str">
         <v>Yes</v>
@@ -2948,7 +2948,7 @@
         <v>done</v>
       </c>
       <c r="C92" t="str">
-        <v>B-d1s8</v>
+        <v>B-d1s4</v>
       </c>
       <c r="D92" t="str">
         <v>Yes</v>
@@ -2962,7 +2962,7 @@
         <v>done</v>
       </c>
       <c r="C93" t="str">
-        <v>B-d1s2</v>
+        <v>B-d1s11</v>
       </c>
       <c r="D93" t="str">
         <v>Yes</v>
@@ -2976,7 +2976,7 @@
         <v>done</v>
       </c>
       <c r="C94" t="str">
-        <v>B-d1s6</v>
+        <v>B-d1s8</v>
       </c>
       <c r="D94" t="str">
         <v>Yes</v>
@@ -2990,7 +2990,7 @@
         <v>done</v>
       </c>
       <c r="C95" t="str">
-        <v>B-d1s10</v>
+        <v>B-d1s2</v>
       </c>
       <c r="D95" t="str">
         <v>Yes</v>
@@ -3004,7 +3004,7 @@
         <v>done</v>
       </c>
       <c r="C96" t="str">
-        <v>B-d2s8</v>
+        <v>B-d1s6</v>
       </c>
       <c r="D96" t="str">
         <v>Yes</v>
@@ -3018,7 +3018,7 @@
         <v>done</v>
       </c>
       <c r="C97" t="str">
-        <v>B-d1s9</v>
+        <v>B-d1s10</v>
       </c>
       <c r="D97" t="str">
         <v>Yes</v>
@@ -3032,7 +3032,7 @@
         <v>done</v>
       </c>
       <c r="C98" t="str">
-        <v>B-d2s1</v>
+        <v>B-d2s8</v>
       </c>
       <c r="D98" t="str">
         <v>Yes</v>
@@ -3046,7 +3046,7 @@
         <v>done</v>
       </c>
       <c r="C99" t="str">
-        <v>B-d2s1#0</v>
+        <v>B-d1s9</v>
       </c>
       <c r="D99" t="str">
         <v>Yes</v>
@@ -3060,7 +3060,7 @@
         <v>done</v>
       </c>
       <c r="C100" t="str">
-        <v>B-d2s2</v>
+        <v>B-d2s1</v>
       </c>
       <c r="D100" t="str">
         <v>Yes</v>
@@ -3074,7 +3074,7 @@
         <v>done</v>
       </c>
       <c r="C101" t="str">
-        <v>B-d2s4</v>
+        <v>B-d2s1#0</v>
       </c>
       <c r="D101" t="str">
         <v>Yes</v>
@@ -3088,7 +3088,7 @@
         <v>done</v>
       </c>
       <c r="C102" t="str">
-        <v>B-d2s3</v>
+        <v>B-d2s2</v>
       </c>
       <c r="D102" t="str">
         <v>Yes</v>
@@ -3102,7 +3102,7 @@
         <v>done</v>
       </c>
       <c r="C103" t="str">
-        <v>B-d2s3#1</v>
+        <v>B-d2s4</v>
       </c>
       <c r="D103" t="str">
         <v>Yes</v>
@@ -3116,7 +3116,7 @@
         <v>done</v>
       </c>
       <c r="C104" t="str">
-        <v>B-d2s5</v>
+        <v>B-d2s3</v>
       </c>
       <c r="D104" t="str">
         <v>Yes</v>
@@ -3130,7 +3130,7 @@
         <v>done</v>
       </c>
       <c r="C105" t="str">
-        <v>B-d2s7</v>
+        <v>B-d2s3#1</v>
       </c>
       <c r="D105" t="str">
         <v>Yes</v>
@@ -3144,7 +3144,7 @@
         <v>done</v>
       </c>
       <c r="C106" t="str">
-        <v>B-xmuy1nsai5fs#0</v>
+        <v>B-d2s5</v>
       </c>
       <c r="D106" t="str">
         <v>Yes</v>
@@ -3155,10 +3155,10 @@
         <v>2026-10-04</v>
       </c>
       <c r="B107" t="str">
-        <v>skipped</v>
+        <v>done</v>
       </c>
       <c r="C107" t="str">
-        <v>B-d6s5</v>
+        <v>B-d2s7</v>
       </c>
       <c r="D107" t="str">
         <v>Yes</v>
@@ -3169,10 +3169,10 @@
         <v>2026-10-04</v>
       </c>
       <c r="B108" t="str">
-        <v>skipped</v>
+        <v>done</v>
       </c>
       <c r="C108" t="str">
-        <v>B-sled1</v>
+        <v>B-xmuy1nsai5fs#0</v>
       </c>
       <c r="D108" t="str">
         <v>Yes</v>
@@ -3186,7 +3186,7 @@
         <v>skipped</v>
       </c>
       <c r="C109" t="str">
-        <v>B-d1s7</v>
+        <v>B-d6s5</v>
       </c>
       <c r="D109" t="str">
         <v>Yes</v>
@@ -3200,7 +3200,7 @@
         <v>skipped</v>
       </c>
       <c r="C110" t="str">
-        <v>B-sled2</v>
+        <v>B-sled1</v>
       </c>
       <c r="D110" t="str">
         <v>Yes</v>
@@ -3214,7 +3214,7 @@
         <v>skipped</v>
       </c>
       <c r="C111" t="str">
-        <v>B-d2s6</v>
+        <v>B-d1s7</v>
       </c>
       <c r="D111" t="str">
         <v>Yes</v>
@@ -3228,7 +3228,7 @@
         <v>skipped</v>
       </c>
       <c r="C112" t="str">
-        <v>B-xmuy1nsai5fs</v>
+        <v>B-sled2</v>
       </c>
       <c r="D112" t="str">
         <v>Yes</v>
@@ -3239,13 +3239,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B113" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C113" t="str">
-        <v>B-d5s2</v>
-      </c>
-      <c r="D113">
-        <v>6</v>
+        <v>B-d2s6</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="114">
@@ -3253,13 +3253,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B114" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C114" t="str">
-        <v>B-d1s3</v>
-      </c>
-      <c r="D114">
-        <v>6</v>
+        <v>B-xmuy1nsai5fs</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="115">
@@ -3270,10 +3270,10 @@
         <v>moved</v>
       </c>
       <c r="C115" t="str">
-        <v>B-d1s9</v>
+        <v>B-d5s2</v>
       </c>
       <c r="D115">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116">
@@ -3284,10 +3284,10 @@
         <v>moved</v>
       </c>
       <c r="C116" t="str">
-        <v>B-d1s5</v>
+        <v>B-d1s3</v>
       </c>
       <c r="D116">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="117">
@@ -3298,10 +3298,10 @@
         <v>moved</v>
       </c>
       <c r="C117" t="str">
-        <v>B-d2s8</v>
+        <v>B-d1s9</v>
       </c>
       <c r="D117">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -3312,10 +3312,10 @@
         <v>moved</v>
       </c>
       <c r="C118" t="str">
-        <v>B-d3s2</v>
+        <v>B-d1s5</v>
       </c>
       <c r="D118">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
@@ -3323,19 +3323,47 @@
         <v>2026-10-04</v>
       </c>
       <c r="B119" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C119" t="str">
+        <v>B-d2s8</v>
+      </c>
+      <c r="D119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B120" t="str">
+        <v>moved</v>
+      </c>
+      <c r="C120" t="str">
+        <v>B-d3s2</v>
+      </c>
+      <c r="D120">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>2026-10-04</v>
+      </c>
+      <c r="B121" t="str">
         <v>phase</v>
       </c>
-      <c r="C119" t="str">
+      <c r="C121" t="str">
         <v>X-muy8rvy9whc0:0</v>
       </c>
-      <c r="D119" t="str">
+      <c r="D121" t="str">
         <v>exp</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D119"/>
+  <autoFilter ref="A1:D121"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D119"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D121"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3385,7 +3413,7 @@
         <v>ghBackup</v>
       </c>
       <c r="B5" t="str">
-        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"1xynas1","last":{"at":"2026-10-07T15:00:26.031Z","url":"https://github.com/jacgit18/iron-log/commit/77a20b494f212861ff53abcef165e51a9078683f"}}</v>
+        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"uu3t2a","last":{"at":"2026-10-07T18:34:23.734Z","url":"https://github.com/jacgit18/iron-log/commit/09b7eac59b005bc09e3e5c95ce5e0dd327c9115f"}}</v>
       </c>
     </row>
     <row r="6">
@@ -6798,19 +6826,19 @@
         <v>A</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2">
         <v>23</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="H2">
         <v>25</v>
@@ -7259,7 +7287,7 @@
         <v>Exported</v>
       </c>
       <c r="B43" t="str">
-        <v>2026-10-07T18:34:20.762Z</v>
+        <v>2026-10-07T19:47:25.451Z</v>
       </c>
     </row>
   </sheetData>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -3413,7 +3413,7 @@
         <v>ghBackup</v>
       </c>
       <c r="B5" t="str">
-        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"uu3t2a","last":{"at":"2026-10-07T18:34:23.734Z","url":"https://github.com/jacgit18/iron-log/commit/09b7eac59b005bc09e3e5c95ce5e0dd327c9115f"}}</v>
+        <v>{"repo":"jacgit18/iron-log","branch":"data","hash":"134a2ax","last":{"at":"2026-10-07T11:39:27.985Z","url":"https://github.com/jacgit18/iron-log/commit/536c96588efc9e75f7607af5b02df3fa6e384403"}}</v>
       </c>
     </row>
     <row r="6">
@@ -7287,7 +7287,7 @@
         <v>Exported</v>
       </c>
       <c r="B43" t="str">
-        <v>2026-10-07T19:47:25.451Z</v>
+        <v>2026-10-08T07:19:33.218Z</v>
       </c>
     </row>
   </sheetData>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -17,8 +17,8 @@
     <sheet name="Config" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">Weeks!$A$1:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Body weight'!$A$1:$D$4</definedName>
@@ -422,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J33"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -790,7 +790,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="B12" t="str">
         <v>Strength</v>
@@ -886,295 +886,295 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Hack Squat</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="B15" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-09-30</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-10-11</v>
+        <v>2026-10-07</v>
       </c>
       <c r="F15">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="G15">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="H15">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>415</v>
+        <v>375</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Hip Thrust</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="B16" t="str">
         <v>Strength</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-27</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-09</v>
       </c>
       <c r="F16">
-        <v>320</v>
+        <v>180</v>
       </c>
       <c r="G16">
-        <v>320</v>
+        <v>180</v>
       </c>
       <c r="H16">
-        <v>320</v>
+        <v>180</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>375</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="B17" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-29</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-10-09</v>
+        <v>2026-10-07</v>
       </c>
       <c r="F17">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="G17">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="H17">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>210</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Kneeling Cable Ab Crunch</v>
       </c>
       <c r="B18" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="str">
         <v>2026-09-29</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-10-07</v>
+        <v>2026-09-29</v>
       </c>
       <c r="F18">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="G18">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="H18">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>21</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Kneeling Cable Ab Crunch</v>
+        <v>Lat Pulldown</v>
       </c>
       <c r="B19" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-27</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-08</v>
       </c>
       <c r="F19">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G19">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H19">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Lat Pulldown</v>
+        <v>Lateral Bound / Skater Hop with Stick</v>
       </c>
       <c r="B20" t="str">
-        <v>Hypertrophy</v>
+        <v>Explosive</v>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-09-27</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-10-08</v>
-      </c>
-      <c r="F20">
-        <v>45</v>
-      </c>
-      <c r="G20">
-        <v>55</v>
-      </c>
-      <c r="H20">
-        <v>55</v>
-      </c>
-      <c r="I20">
-        <v>10</v>
-      </c>
-      <c r="J20">
-        <v>90</v>
+        <v>2026-10-04</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Lateral Bound / Skater Hop with Stick</v>
+        <v>Leg Extension ISO hold</v>
       </c>
       <c r="B21" t="str">
-        <v>Explosive</v>
+        <v>Isometric</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-10-04</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
-      <c r="G21" t="str">
-        <v/>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21" t="str">
-        <v/>
-      </c>
-      <c r="J21" t="str">
-        <v/>
+        <v>2026-09-29</v>
+      </c>
+      <c r="F21">
+        <v>50</v>
+      </c>
+      <c r="G21">
+        <v>50</v>
+      </c>
+      <c r="H21">
+        <v>50</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>65</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Leg Extension ISO hold</v>
+        <v>Outer Thigh Adduction</v>
       </c>
       <c r="B22" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="C22">
         <v>2</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-05</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-08</v>
       </c>
       <c r="F22">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="G22">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="H22">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>65</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Outer Thigh Adduction</v>
+        <v>Overhead Tricep Extension</v>
       </c>
       <c r="B23" t="str">
         <v>Strength</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-07</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-07</v>
       </c>
       <c r="F23">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="G23">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="H23">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="J23">
-        <v>180</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Overhead Tricep Extension</v>
+        <v>Plate Torso Rotation</v>
       </c>
       <c r="B24" t="str">
         <v>Strength</v>
@@ -1183,19 +1183,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-05</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-05</v>
       </c>
       <c r="F24">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G24">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H24">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1206,147 +1206,147 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Plate Torso Rotation</v>
+        <v>Pogo Hops</v>
       </c>
       <c r="B25" t="str">
-        <v>Strength</v>
+        <v>Explosive</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-10-05</v>
-      </c>
-      <c r="F25">
-        <v>10</v>
-      </c>
-      <c r="G25">
-        <v>10</v>
-      </c>
-      <c r="H25">
-        <v>10</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>30</v>
+        <v>2026-10-04</v>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Pogo Hops</v>
+        <v>Prone Leg Curl</v>
       </c>
       <c r="B26" t="str">
-        <v>Explosive</v>
+        <v>Strength</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-09</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="F26" t="str">
-        <v/>
-      </c>
-      <c r="G26" t="str">
-        <v/>
-      </c>
-      <c r="H26" t="str">
-        <v/>
-      </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
-      <c r="J26" t="str">
-        <v/>
+        <v>2026-10-09</v>
+      </c>
+      <c r="F26">
+        <v>50</v>
+      </c>
+      <c r="G26">
+        <v>50</v>
+      </c>
+      <c r="H26">
+        <v>50</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>100</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Prone Leg Curl</v>
+        <v>Seated Cable Crunch</v>
       </c>
       <c r="B27" t="str">
         <v>Strength</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-10-09</v>
+        <v>2026-10-07</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-10-09</v>
+        <v>2026-10-08</v>
       </c>
       <c r="F27">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G27">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H27">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>100</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Seated Cable Crunch</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="B28" t="str">
         <v>Strength</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-10-07</v>
+        <v>2026-09-27</v>
       </c>
       <c r="E28" t="str">
         <v>2026-10-08</v>
       </c>
       <c r="F28">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G28">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H28">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="B29" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="C29">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D29" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-09</v>
       </c>
       <c r="F29">
         <v>50</v>
@@ -1361,44 +1361,44 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>80</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Sled push → pull</v>
       </c>
       <c r="B30" t="str">
-        <v>Isometric</v>
+        <v>Explosive</v>
       </c>
       <c r="C30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-09-27</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-10-09</v>
-      </c>
-      <c r="F30">
-        <v>50</v>
-      </c>
-      <c r="G30">
-        <v>50</v>
-      </c>
-      <c r="H30">
-        <v>50</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>65</v>
+        <v>2026-10-04</v>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Sled push → pull</v>
+        <v>Split Squat Jumps</v>
       </c>
       <c r="B31" t="str">
         <v>Explosive</v>
@@ -1430,104 +1430,72 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Split Squat Jumps</v>
+        <v>Suitcase Bottom-Up, single-arm</v>
       </c>
       <c r="B32" t="str">
-        <v>Explosive</v>
+        <v>Strength</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-10-04</v>
+        <v>2026-09-29</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="F32" t="str">
-        <v/>
-      </c>
-      <c r="G32" t="str">
-        <v/>
-      </c>
-      <c r="H32" t="str">
-        <v/>
-      </c>
-      <c r="I32" t="str">
-        <v/>
-      </c>
-      <c r="J32" t="str">
-        <v/>
+        <v>2026-09-29</v>
+      </c>
+      <c r="F32">
+        <v>25</v>
+      </c>
+      <c r="G32">
+        <v>25</v>
+      </c>
+      <c r="H32">
+        <v>25</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>30</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Suitcase Bottom-Up, single-arm</v>
+        <v>Zottman Curl</v>
       </c>
       <c r="B33" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="str">
         <v>2026-09-29</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-07</v>
       </c>
       <c r="F33">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G33">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H33">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>Zottman Curl</v>
-      </c>
-      <c r="B34" t="str">
-        <v>Hypertrophy</v>
-      </c>
-      <c r="C34">
-        <v>2</v>
-      </c>
-      <c r="D34" t="str">
-        <v>2026-09-29</v>
-      </c>
-      <c r="E34" t="str">
-        <v>2026-10-07</v>
-      </c>
-      <c r="F34">
-        <v>15</v>
-      </c>
-      <c r="G34">
-        <v>15</v>
-      </c>
-      <c r="H34">
-        <v>15</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
         <v>23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J34"/>
+  <autoFilter ref="A1:J33"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J33"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4151,7 +4119,7 @@
         <v>ex</v>
       </c>
       <c r="B3" t="str">
-        <v>{"bss":{"n":"Bulgarian Split Squat","eq":"dumbbell"},"db6":{"n":"DB 6 Ways","eq":"dumbbell"},"dip":{"n":"Wide Tricep Dip","eq":"bodyweight"},"grip":{"n":"Grip Trainer","eq":"other"},"hack":{"n":"Hack Squat","eq":"machine"},"pogo":{"n":"Pogo Hops","eq":"bodyweight","url":"https://youtu.be/iU-TKr4YesM"},"sled":{"n":"Sled push → pull","eq":"sled"},"canoe":{"n":"Canoe Stretch","eq":"barbell","url":"https://youtu.be/yR6EnBqjKNs"},"kbleg":{"n":"Kettlebell Leg Raise","eq":"kettlebell"},"latpd":{"n":"Lat Pulldown, alternating single-arm","eq":"cable"},"ohtri":{"n":"Overhead Tricep Extension","eq":"cable"},"qlext":{"n":"Side Lateral QL Extension","eq":"machine","url":"https://www.youtube.com/watch?v=UaydER2VIUc"},"arnold":{"n":"Arnold Press","eq":"dumbbell"},"legext":{"n":"Leg Extension ISO hold","eq":"machine"},"pallof":{"n":"Pallof Press","eq":"cable"},"skater":{"n":"Lateral Bound / Skater Hop with Stick","eq":"bodyweight","url":"https://youtu.be/4nTDP0G3nhc"},"spinal":{"n":"Spinal Waves","url":"https://youtu.be/KCfh_wCssK8"},"trxrow":{"n":"TRX Wide-Grip Row","eq":"trx","url":"https://youtu.be/o9M1k6OzI-g"},"dbclean":{"n":"DB Clean &amp; Jerk Press","eq":"dumbbell"},"dblunge":{"n":"DB Lunge","eq":"dumbbell"},"farmers":{"n":"Farmers Carry","eq":"dumbbell"},"latpdbi":{"n":"Lat Pulldown","eq":"cable"},"latwall":{"n":"Lateral Wall Push","eq":"bodyweight","url":"https://youtu.be/tIFjnucY09Q"},"legcurl":{"n":"Prone Leg Curl","eq":"machine"},"medball":{"n":"Med Ball Rotational Scoop","eq":"medball","url":"https://youtu.be/xmQfXggU2mU"},"sledlat":{"n":"Sled push → lateral pull","eq":"sled"},"trxpike":{"n":"TRX Pike Push-Up","eq":"trx","url":"https://youtu.be/GIWNRslPEv4"},"wristpd":{"n":"Cable Wrist Pulldown","eq":"cable"},"zercher":{"n":"Seated Zercher Good Morning","eq":"shortbar","url":"https://youtu.be/ahfSSi4MVJQ"},"zottman":{"n":"Zottman Curl","eq":"dumbbell"},"cablerow":{"n":"Explosive Unilateral Cable Row","eq":"cable","url":"https://youtu.be/OrAcowGGU2U"},"deadlift":{"n":"Deadlift","eq":"barbell"},"facepull":{"n":"Face Pull","eq":"cable"},"platerot":{"n":"Plate Torso Rotation","eq":"plate"},"reardelt":{"n":"Side Rear Delt Fly","eq":"cable"},"romanadd":{"n":"Roman Chair Hip Adduction","eq":"bodyweight","url":"https://www.youtube.com/watch?v=j5HWZOfIePI"},"suitcase":{"n":"Suitcase Bottom-Up, single-arm","eq":"kettlebell"},"dead-bugs":{"n":"Dead Bugs"},"deskbands":{"n":"Desk Bands","eq":"band","url":"https://youtu.be/o_uZcQnXaFA"},"hipthrust":{"n":"Hip Thrust","eq":"machine"},"kneeraise":{"n":"Hanging Knee Raise","eq":"bodyweight"},"sled-pull":{"n":"Sled Pull","eq":"other"},"splitjump":{"n":"Split Squat Jumps","eq":"bodyweight","url":"https://www.youtube.com/watch?v=4DMvFDaqIys"},"abb-roller":{"n":"Abb Roller","eq":"other"},"cablepunch":{"n":"Cable Punch ISO hold","eq":"cable"},"chestpress":{"n":"Chest Press","eq":"machine"},"depthcombo":{"n":"Depth Drop → Broad Jump → Box Jump","eq":"bodyweight","url":"https://youtu.be/GZLyZCqF8BQ"},"innerthigh":{"n":"Inner Thigh Abduction","eq":"machine"},"outerthigh":{"n":"Outer Thigh Adduction","eq":"machine"},"cablecrunch":{"n":"Kneeling Cable Ab Crunch","eq":"cable"},"dragon-flag":{"n":"Dragon Flag","eq":"bodyweight"},"squat-walks":{"n":"Squat Walks","eq":"dumbbell","url":"https://www.instagram.com/p/DeKAHsWKK4W/"},"duck-sled-push":{"n":"Duck Sled Push","eq":"other","url":"https://www.instagram.com/p/DeKUe-qvgF-/"},"tibialis-raise":{"n":"Tibialis Raise","eq":"bodyweight","url":"https://youtu.be/OPEuhclsTUQ"},"garhammer-raise":{"n":"Garhammer Raise","url":"https://youtu.be/0ShG8aVIvms?t=836"},"seated-cable-crunch":{"n":"Seated Cable Crunch","eq":"cable","url":"https://youtube.com/shorts/bIbm-p6Q4s8?is=aiC1fOhPbN5QMcgq"},"bench-reverse-crunch":{"n":"Bench Reverse Crunch"},"c:fedb:Clean_and_Jerk":{"n":"Clean and Jerk","eq":"dumbbell"},"clean-jerk-overhead-press":{"n":"Clean Jerk &amp; Overhead Press","eq":"dumbbell"},"c:fedb:Arnold_Dumbbell_Press":{"n":"Arnold Dumbbell Press","eq":"dumbbell"},"split-stance-cable-hip-rotation":{"n":"Split Stance Cable Hip Rotation","eq":"cable","url":"https://youtu.be/ixIEilUM2aY"},"statue-of-liberty-to-fly-to-chest-buster":{"n":"Statue of Liberty to fly to chest busters","eq":"dumbbell","url":"https://www.instagram.com/reel/Dbu6F2ZKW-O/?exln=azRoYnNhb2VsOTRp"}}</v>
+        <v>{"bss":{"n":"Bulgarian Split Squat","eq":"dumbbell"},"db6":{"n":"DB 6 Ways","eq":"dumbbell"},"dip":{"n":"Wide Tricep Dip","eq":"bodyweight"},"grip":{"n":"Grip Trainer","eq":"other"},"hack":{"n":"Hack Squats","eq":"machine"},"pogo":{"n":"Pogo Hops","eq":"bodyweight","url":"https://youtu.be/iU-TKr4YesM"},"sled":{"n":"Sled push → pull","eq":"sled"},"canoe":{"n":"Canoe Stretch","eq":"barbell","url":"https://youtu.be/yR6EnBqjKNs"},"kbleg":{"n":"Kettlebell Leg Raise","eq":"kettlebell"},"latpd":{"n":"Lat Pulldown, alternating single-arm","eq":"cable"},"ohtri":{"n":"Overhead Tricep Extension","eq":"cable"},"qlext":{"n":"Side Lateral QL Extension","eq":"machine","url":"https://www.youtube.com/watch?v=UaydER2VIUc"},"arnold":{"n":"Arnold Press","eq":"dumbbell"},"legext":{"n":"Leg Extension ISO hold","eq":"machine"},"pallof":{"n":"Pallof Press","eq":"cable"},"skater":{"n":"Lateral Bound / Skater Hop with Stick","eq":"bodyweight","url":"https://youtu.be/4nTDP0G3nhc"},"spinal":{"n":"Spinal Waves","url":"https://youtu.be/KCfh_wCssK8"},"trxrow":{"n":"TRX Wide-Grip Row","eq":"trx","url":"https://youtu.be/o9M1k6OzI-g"},"dbclean":{"n":"DB Clean &amp; Jerk Press","eq":"dumbbell"},"dblunge":{"n":"DB Lunge","eq":"dumbbell"},"farmers":{"n":"Farmers Carry","eq":"dumbbell"},"latpdbi":{"n":"Lat Pulldown","eq":"cable"},"latwall":{"n":"Lateral Wall Push","eq":"bodyweight","url":"https://youtu.be/tIFjnucY09Q"},"legcurl":{"n":"Prone Leg Curl","eq":"machine"},"medball":{"n":"Med Ball Rotational Scoop","eq":"medball","url":"https://youtu.be/xmQfXggU2mU"},"sledlat":{"n":"Sled push → lateral pull","eq":"sled"},"trxpike":{"n":"TRX Pike Push-Up","eq":"trx","url":"https://youtu.be/GIWNRslPEv4"},"wristpd":{"n":"Cable Wrist Pulldown","eq":"cable"},"zercher":{"n":"Seated Zercher Good Morning","eq":"shortbar","url":"https://youtu.be/ahfSSi4MVJQ"},"zottman":{"n":"Zottman Curl","eq":"dumbbell"},"cablerow":{"n":"Explosive Unilateral Cable Row","eq":"cable","url":"https://youtu.be/OrAcowGGU2U"},"deadlift":{"n":"Deadlift","eq":"barbell"},"facepull":{"n":"Face Pulls","eq":"cable"},"platerot":{"n":"Plate Torso Rotation","eq":"plate"},"reardelt":{"n":"Side Rear Delt Fly","eq":"cable"},"romanadd":{"n":"Roman Chair Hip Adduction","eq":"bodyweight","url":"https://www.youtube.com/watch?v=j5HWZOfIePI"},"suitcase":{"n":"Suitcase Bottom-Up, single-arm","eq":"kettlebell"},"dead-bugs":{"n":"Dead Bugs"},"deskbands":{"n":"Desk Bands","eq":"band","url":"https://youtu.be/o_uZcQnXaFA"},"hipthrust":{"n":"Hip Thrust","eq":"machine"},"kneeraise":{"n":"Hanging Knee Raise","eq":"bodyweight"},"sled-pull":{"n":"Sled Pull","eq":"other"},"splitjump":{"n":"Split Squat Jumps","eq":"bodyweight","url":"https://www.youtube.com/watch?v=4DMvFDaqIys"},"abb-roller":{"n":"Abb Roller","eq":"other"},"cablepunch":{"n":"Cable Punch ISO hold","eq":"cable"},"chestpress":{"n":"Chest Press","eq":"machine"},"depthcombo":{"n":"Depth Drop → Broad Jump → Box Jump","eq":"bodyweight","url":"https://youtu.be/GZLyZCqF8BQ"},"innerthigh":{"n":"Inner Thigh Abduction","eq":"machine"},"outerthigh":{"n":"Outer Thigh Adduction","eq":"machine"},"cablecrunch":{"n":"Kneeling Cable Ab Crunch","eq":"cable"},"dragon-flag":{"n":"Dragon Flag","eq":"bodyweight"},"squat-walks":{"n":"Squat Walks","eq":"dumbbell","url":"https://www.instagram.com/p/DeKAHsWKK4W/"},"duck-sled-push":{"n":"Duck Sled Push","eq":"other","url":"https://www.instagram.com/p/DeKUe-qvgF-/"},"tibialis-raise":{"n":"Tibialis Raise","eq":"bodyweight","url":"https://youtu.be/OPEuhclsTUQ"},"garhammer-raise":{"n":"Garhammer Raise","url":"https://youtu.be/0ShG8aVIvms?t=836"},"c:fedb:Face_Pull":{"n":"Face Pull","eq":"cable"},"c:fedb:Sled_Push":{"n":"Sled Push","eq":"other"},"c:fedb:Hack_Squat":{"n":"Hack Squat","eq":"machine"},"c:fedb:Farmers_Walk":{"n":"Farmer's Walk","eq":"other"},"c:fedb:Hanging_Pike":{"n":"Hanging Pike","eq":"bodyweight"},"seated-cable-crunch":{"n":"Seated Cable Crunch","eq":"cable","url":"https://youtube.com/shorts/bIbm-p6Q4s8?is=aiC1fOhPbN5QMcgq"},"bench-reverse-crunch":{"n":"Bench Reverse Crunch"},"c:fedb:Clean_and_Jerk":{"n":"Clean and Jerk","eq":"dumbbell"},"c:fedb:Leg_Extensions":{"n":"Leg Extensions","eq":"machine"},"c:fedb:Thigh_Abductor":{"n":"Thigh Abductor","eq":"machine"},"c:fedb:Thigh_Adductor":{"n":"Thigh Adductor","eq":"machine"},"c:fedb:Clean_and_Press":{"n":"Clean and Press","eq":"barbell"},"c:fedb:Dumbbell_Lunges":{"n":"Dumbbell Lunges","eq":"dumbbell"},"c:fedb:Kettlebell_Halo":{"n":"Kettlebell Halo","eq":"kettlebell"},"c:fedb:Lying_Leg_Curls":{"n":"Lying Leg Curls","eq":"machine"},"c:fedb:Cable_Wrist_Curl":{"n":"Cable Wrist Curl","eq":"cable"},"c:fedb:Hanging_Leg_Raise":{"n":"Hanging Leg Raise","eq":"bodyweight"},"clean-jerk-overhead-press":{"n":"Clean Jerk &amp; Overhead Press","eq":"dumbbell"},"c:fedb:Sled_Drag_-_Harness":{"n":"Sled Drag - Harness","eq":"other"},"c:fedb:Dumbbell_Bench_Press":{"n":"Dumbbell Bench Press","eq":"dumbbell"},"c:fedb:Seated_Good_Mornings":{"n":"Seated Good Mornings","eq":"barbell"},"c:fedb:Arnold_Dumbbell_Press":{"n":"Arnold Dumbbell Press","eq":"dumbbell"},"c:fedb:Single-Leg_Leg_Extension":{"n":"Single-Leg Leg Extension","eq":"machine"},"split-stance-cable-hip-rotation":{"n":"Split Stance Cable Hip Rotation","eq":"cable","url":"https://youtu.be/ixIEilUM2aY"},"c:fedb:Close-Grip_Front_Lat_Pulldown":{"n":"Close-Grip Front Lat Pulldown","eq":"cable"},"c:fedb:Cable_One_Arm_Tricep_Extension":{"n":"Cable One Arm Tricep Extension","eq":"cable"},"statue-of-liberty-to-fly-to-chest-buster":{"n":"Statue of Liberty to fly to chest busters","eq":"dumbbell","url":"https://www.instagram.com/reel/Dbu6F2ZKW-O/?exln=azRoYnNhb2VsOTRp"},"c:fedb:Cable_Rope_Overhead_Triceps_Extension":{"n":"Cable Rope Overhead Triceps Extension","eq":"cable"}}</v>
       </c>
     </row>
     <row r="4">
@@ -4215,7 +4183,7 @@
         <v>muscleMap</v>
       </c>
       <c r="B11" t="str">
-        <v>{"seated-cable-crunch":{"p":["abs"],"s":[]},"c:fedb:Clean_and_Jerk":{"p":["frontdelt","sidedelt"],"s":["abs","glutes","hamstrings","lowerback","quads","traps","triceps"]},"c:fedb:Arnold_Dumbbell_Press":{"p":["frontdelt","sidedelt"],"s":["triceps"]}}</v>
+        <v>{"c:fedb:Face_Pull":{"p":["frontdelt","sidedelt"],"s":["upperback"]},"c:fedb:Sled_Push":{"p":["quads"],"s":["calves","chest","glutes","hamstrings","triceps"]},"c:fedb:Hack_Squat":{"p":["quads"],"s":["calves","glutes","hamstrings"]},"c:fedb:Farmers_Walk":{"p":["forearms"],"s":["abs","glutes","hamstrings","lowerback","quads","traps"]},"c:fedb:Hanging_Pike":{"p":["abs"]},"seated-cable-crunch":{"p":["abs"],"s":[]},"c:fedb:Clean_and_Jerk":{"p":["frontdelt","sidedelt"],"s":["abs","glutes","hamstrings","lowerback","quads","traps","triceps"]},"c:fedb:Leg_Extensions":{"p":["quads"]},"c:fedb:Thigh_Abductor":{"p":["abductors"],"s":["glutes"]},"c:fedb:Thigh_Adductor":{"p":["adductors"],"s":["glutes","hamstrings"]},"c:fedb:Clean_and_Press":{"p":["frontdelt","sidedelt"],"s":["abs","calves","glutes","hamstrings","lowerback","upperback","quads","traps","triceps"]},"c:fedb:Dumbbell_Lunges":{"p":["quads"],"s":["calves","glutes","hamstrings"]},"c:fedb:Kettlebell_Halo":{"p":["frontdelt","sidedelt"],"s":["traps","upperback","abs","triceps"]},"c:fedb:Lying_Leg_Curls":{"p":["hamstrings"]},"c:fedb:Cable_Wrist_Curl":{"p":["forearms"]},"c:fedb:Hanging_Leg_Raise":{"p":["abs"]},"c:fedb:Sled_Drag_-_Harness":{"p":["quads"],"s":["calves","glutes","hamstrings"]},"c:fedb:Dumbbell_Bench_Press":{"p":["chest"],"s":["frontdelt","sidedelt","triceps"]},"c:fedb:Seated_Good_Mornings":{"p":["lowerback"],"s":["glutes"]},"c:fedb:Arnold_Dumbbell_Press":{"p":["frontdelt","sidedelt"],"s":["triceps"]},"c:fedb:Single-Leg_Leg_Extension":{"p":["quads"]},"c:fedb:Close-Grip_Front_Lat_Pulldown":{"p":["lats"],"s":["biceps","upperback","frontdelt","sidedelt"]},"c:fedb:Cable_One_Arm_Tricep_Extension":{"p":["triceps"]},"c:fedb:Cable_Rope_Overhead_Triceps_Extension":{"p":["triceps"]}}</v>
       </c>
     </row>
     <row r="12">
@@ -4268,7 +4236,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O69"/>
+  <dimension ref="A1:O64"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -5141,43 +5109,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C19" t="str">
-        <v>Hack Squat</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="D19" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E19">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G19">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H19" t="str">
         <v/>
       </c>
       <c r="I19" t="str">
-        <v>270×15, 270×15, 270×15, 270×15</v>
+        <v>320×6, 320×6</v>
       </c>
       <c r="J19">
-        <v>16200</v>
+        <v>3840</v>
       </c>
       <c r="K19" t="str">
-        <v>Quads</v>
+        <v>Glutes</v>
       </c>
       <c r="L19" t="str">
-        <v>Glutes, Inner thigh (adductors)</v>
+        <v>Hamstrings</v>
       </c>
       <c r="M19" t="str">
         <v/>
       </c>
       <c r="N19" t="str">
-        <v>A-d3s1</v>
+        <v>A-d4s5</v>
       </c>
       <c r="O19" t="str">
-        <v>hack</v>
+        <v>hipthrust</v>
       </c>
     </row>
     <row r="20">
@@ -5188,16 +5156,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="C20" t="str">
-        <v>Hip Thrust</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="D20" t="str">
         <v>Strength</v>
       </c>
       <c r="E20">
-        <v>320</v>
+        <v>180</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G20">
         <v>6</v>
@@ -5206,25 +5174,25 @@
         <v/>
       </c>
       <c r="I20" t="str">
-        <v>320×6, 320×6</v>
+        <v>180×6, 180×6, 180×6, 180×6</v>
       </c>
       <c r="J20">
-        <v>3840</v>
+        <v>4320</v>
       </c>
       <c r="K20" t="str">
-        <v>Glutes</v>
+        <v>Inner thigh (adductors)</v>
       </c>
       <c r="L20" t="str">
-        <v>Hamstrings</v>
+        <v/>
       </c>
       <c r="M20" t="str">
         <v/>
       </c>
       <c r="N20" t="str">
-        <v>A-d4s5</v>
+        <v>A-d4s2</v>
       </c>
       <c r="O20" t="str">
-        <v>hipthrust</v>
+        <v>innerthigh</v>
       </c>
     </row>
     <row r="21">
@@ -5235,13 +5203,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="C21" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="D21" t="str">
         <v>Strength</v>
       </c>
       <c r="E21">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="F21">
         <v>4</v>
@@ -5253,30 +5221,30 @@
         <v/>
       </c>
       <c r="I21" t="str">
-        <v>180×6, 180×6, 180×6, 180×6</v>
+        <v>50×6, 50×6, 50×6, 50×6</v>
       </c>
       <c r="J21">
-        <v>4320</v>
+        <v>1200</v>
       </c>
       <c r="K21" t="str">
-        <v>Inner thigh (adductors)</v>
+        <v>Lower back</v>
       </c>
       <c r="L21" t="str">
-        <v/>
+        <v>Glutes, Hamstrings, Upper back</v>
       </c>
       <c r="M21" t="str">
         <v/>
       </c>
       <c r="N21" t="str">
-        <v>A-d4s2</v>
+        <v>A-d4s4</v>
       </c>
       <c r="O21" t="str">
-        <v>innerthigh</v>
+        <v>zercher</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-09-30</v>
+        <v>2026-10-01</v>
       </c>
       <c r="B22" t="str">
         <v>2026-09-27</v>
@@ -5288,10 +5256,10 @@
         <v>Strength</v>
       </c>
       <c r="E22">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>6</v>
@@ -5300,10 +5268,10 @@
         <v/>
       </c>
       <c r="I22" t="str">
-        <v>50×6, 50×6, 50×6, 50×6</v>
+        <v>40×6</v>
       </c>
       <c r="J22">
-        <v>1200</v>
+        <v>240</v>
       </c>
       <c r="K22" t="str">
         <v>Lower back</v>
@@ -5315,7 +5283,7 @@
         <v/>
       </c>
       <c r="N22" t="str">
-        <v>A-d4s4</v>
+        <v>A-d6s5</v>
       </c>
       <c r="O22" t="str">
         <v>zercher</v>
@@ -5323,96 +5291,96 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-04</v>
       </c>
       <c r="B23" t="str">
-        <v>2026-09-27</v>
+        <v>2026-10-04</v>
       </c>
       <c r="C23" t="str">
-        <v>Hack Squat</v>
+        <v>Cable Punch ISO hold</v>
       </c>
       <c r="D23" t="str">
-        <v>Hypertrophy</v>
+        <v>Isometric</v>
       </c>
       <c r="E23">
-        <v>270</v>
+        <v>30</v>
       </c>
       <c r="F23">
-        <v>3</v>
-      </c>
-      <c r="G23">
+        <v>4</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23">
         <v>15</v>
       </c>
-      <c r="H23" t="str">
-        <v/>
-      </c>
       <c r="I23" t="str">
-        <v>270×15, 270×15, 270×15</v>
-      </c>
-      <c r="J23">
-        <v>12150</v>
+        <v>30×15s, 30×15s, 30×15s, 30×15s</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
       </c>
       <c r="K23" t="str">
-        <v>Quads</v>
+        <v>Obliques, Abs</v>
       </c>
       <c r="L23" t="str">
-        <v>Glutes, Inner thigh (adductors)</v>
+        <v>Chest, Front delts</v>
       </c>
       <c r="M23" t="str">
         <v/>
       </c>
       <c r="N23" t="str">
-        <v>A-d5s3</v>
+        <v>B-d6s6</v>
       </c>
       <c r="O23" t="str">
-        <v>hack</v>
+        <v>cablepunch</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-04</v>
       </c>
       <c r="B24" t="str">
-        <v>2026-09-27</v>
+        <v>2026-10-04</v>
       </c>
       <c r="C24" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Cable Wrist Pulldown</v>
       </c>
       <c r="D24" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E24">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H24" t="str">
         <v/>
       </c>
       <c r="I24" t="str">
-        <v>40×6</v>
+        <v>33×15, 33×15</v>
       </c>
       <c r="J24">
-        <v>240</v>
+        <v>990</v>
       </c>
       <c r="K24" t="str">
-        <v>Lower back</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="L24" t="str">
-        <v>Glutes, Hamstrings, Upper back</v>
+        <v/>
       </c>
       <c r="M24" t="str">
         <v/>
       </c>
       <c r="N24" t="str">
-        <v>A-d6s5</v>
+        <v>B-d1s3</v>
       </c>
       <c r="O24" t="str">
-        <v>zercher</v>
+        <v>wristpd</v>
       </c>
     </row>
     <row r="25">
@@ -5423,43 +5391,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C25" t="str">
-        <v>Cable Punch ISO hold</v>
+        <v>Clean Jerk &amp; Overhead Press</v>
       </c>
       <c r="D25" t="str">
-        <v>Isometric</v>
+        <v>Explosive</v>
       </c>
       <c r="E25">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F25">
-        <v>4</v>
-      </c>
-      <c r="G25" t="str">
-        <v/>
-      </c>
-      <c r="H25">
-        <v>15</v>
+        <v>3</v>
+      </c>
+      <c r="G25">
+        <v>10</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
       </c>
       <c r="I25" t="str">
-        <v>30×15s, 30×15s, 30×15s, 30×15s</v>
-      </c>
-      <c r="J25" t="str">
-        <v/>
+        <v>20×10, 20×10, 20×10</v>
+      </c>
+      <c r="J25">
+        <v>600</v>
       </c>
       <c r="K25" t="str">
-        <v>Obliques, Abs</v>
+        <v/>
       </c>
       <c r="L25" t="str">
-        <v>Chest, Front delts</v>
+        <v/>
       </c>
       <c r="M25" t="str">
         <v/>
       </c>
       <c r="N25" t="str">
-        <v>B-d6s6</v>
+        <v>B-d5s2</v>
       </c>
       <c r="O25" t="str">
-        <v>cablepunch</v>
+        <v>clean-jerk-overhead-press</v>
       </c>
     </row>
     <row r="26">
@@ -5470,43 +5438,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C26" t="str">
-        <v>Cable Wrist Pulldown</v>
+        <v>Depth Drop → Broad Jump → Box Jump</v>
       </c>
       <c r="D26" t="str">
-        <v>Hypertrophy</v>
-      </c>
-      <c r="E26">
-        <v>33</v>
+        <v>Explosive</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H26" t="str">
         <v/>
       </c>
       <c r="I26" t="str">
-        <v>33×15, 33×15</v>
-      </c>
-      <c r="J26">
-        <v>990</v>
+        <v>BW×5, BW×5, BW×5</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
       </c>
       <c r="K26" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Quads, Glutes, Calves</v>
       </c>
       <c r="L26" t="str">
-        <v/>
+        <v>Hamstrings</v>
       </c>
       <c r="M26" t="str">
         <v/>
       </c>
       <c r="N26" t="str">
-        <v>B-d1s3</v>
+        <v>B-d6s4</v>
       </c>
       <c r="O26" t="str">
-        <v>wristpd</v>
+        <v>depthcombo</v>
       </c>
     </row>
     <row r="27">
@@ -5517,16 +5485,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="C27" t="str">
-        <v>Clean Jerk &amp; Overhead Press</v>
+        <v>Explosive Unilateral Cable Row</v>
       </c>
       <c r="D27" t="str">
         <v>Explosive</v>
       </c>
       <c r="E27">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27">
         <v>10</v>
@@ -5535,25 +5503,25 @@
         <v/>
       </c>
       <c r="I27" t="str">
-        <v>20×10, 20×10, 20×10</v>
+        <v>30×10, 30×10, 30×10, 30×10</v>
       </c>
       <c r="J27">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="K27" t="str">
-        <v/>
+        <v>Lats, Upper back</v>
       </c>
       <c r="L27" t="str">
-        <v/>
+        <v>Rear delts, Biceps</v>
       </c>
       <c r="M27" t="str">
         <v/>
       </c>
       <c r="N27" t="str">
-        <v>B-d5s2</v>
+        <v>B-d6s6</v>
       </c>
       <c r="O27" t="str">
-        <v>clean-jerk-overhead-press</v>
+        <v>cablerow</v>
       </c>
     </row>
     <row r="28">
@@ -5564,7 +5532,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="C28" t="str">
-        <v>Depth Drop → Broad Jump → Box Jump</v>
+        <v>Lateral Bound / Skater Hop with Stick</v>
       </c>
       <c r="D28" t="str">
         <v>Explosive</v>
@@ -5576,31 +5544,31 @@
         <v>3</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H28" t="str">
         <v/>
       </c>
       <c r="I28" t="str">
-        <v>BW×5, BW×5, BW×5</v>
+        <v>BW×10, BW×10, BW×10</v>
       </c>
       <c r="J28" t="str">
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>Quads, Glutes, Calves</v>
+        <v>Glutes, Outer hip (abductors), Quads</v>
       </c>
       <c r="L28" t="str">
-        <v>Hamstrings</v>
+        <v>Inner thigh (adductors), Calves</v>
       </c>
       <c r="M28" t="str">
         <v/>
       </c>
       <c r="N28" t="str">
-        <v>B-d6s4</v>
+        <v>B-d6s2</v>
       </c>
       <c r="O28" t="str">
-        <v>depthcombo</v>
+        <v>skater</v>
       </c>
     </row>
     <row r="29">
@@ -5611,16 +5579,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="C29" t="str">
-        <v>Explosive Unilateral Cable Row</v>
+        <v>Pogo Hops</v>
       </c>
       <c r="D29" t="str">
         <v>Explosive</v>
       </c>
-      <c r="E29">
-        <v>30</v>
+      <c r="E29" t="str">
+        <v/>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29">
         <v>10</v>
@@ -5629,25 +5597,25 @@
         <v/>
       </c>
       <c r="I29" t="str">
-        <v>30×10, 30×10, 30×10, 30×10</v>
-      </c>
-      <c r="J29">
-        <v>1200</v>
+        <v>BW×10, BW×10, BW×10</v>
+      </c>
+      <c r="J29" t="str">
+        <v/>
       </c>
       <c r="K29" t="str">
-        <v>Lats, Upper back</v>
+        <v>Calves</v>
       </c>
       <c r="L29" t="str">
-        <v>Rear delts, Biceps</v>
+        <v>Shins</v>
       </c>
       <c r="M29" t="str">
         <v/>
       </c>
       <c r="N29" t="str">
-        <v>B-d6s6</v>
+        <v>B-d6s1</v>
       </c>
       <c r="O29" t="str">
-        <v>cablerow</v>
+        <v>pogo</v>
       </c>
     </row>
     <row r="30">
@@ -5658,43 +5626,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C30" t="str">
-        <v>Lateral Bound / Skater Hop with Stick</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="D30" t="str">
-        <v>Explosive</v>
-      </c>
-      <c r="E30" t="str">
-        <v/>
+        <v>Strength</v>
+      </c>
+      <c r="E30">
+        <v>50</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H30" t="str">
         <v/>
       </c>
       <c r="I30" t="str">
-        <v>BW×10, BW×10, BW×10</v>
-      </c>
-      <c r="J30" t="str">
-        <v/>
+        <v>50×6, 50×6, 50×6, 50×6</v>
+      </c>
+      <c r="J30">
+        <v>1200</v>
       </c>
       <c r="K30" t="str">
-        <v>Glutes, Outer hip (abductors), Quads</v>
+        <v>Lower back</v>
       </c>
       <c r="L30" t="str">
-        <v>Inner thigh (adductors), Calves</v>
+        <v>Glutes, Hamstrings, Upper back</v>
       </c>
       <c r="M30" t="str">
         <v/>
       </c>
       <c r="N30" t="str">
-        <v>B-d6s2</v>
+        <v>B-d6s5</v>
       </c>
       <c r="O30" t="str">
-        <v>skater</v>
+        <v>zercher</v>
       </c>
     </row>
     <row r="31">
@@ -5705,7 +5673,7 @@
         <v>2026-10-04</v>
       </c>
       <c r="C31" t="str">
-        <v>Pogo Hops</v>
+        <v>Sled push → pull</v>
       </c>
       <c r="D31" t="str">
         <v>Explosive</v>
@@ -5714,34 +5682,34 @@
         <v/>
       </c>
       <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
         <v>3</v>
       </c>
-      <c r="G31">
-        <v>10</v>
-      </c>
       <c r="H31" t="str">
         <v/>
       </c>
       <c r="I31" t="str">
-        <v>BW×10, BW×10, BW×10</v>
+        <v>BW×3</v>
       </c>
       <c r="J31" t="str">
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>Calves</v>
+        <v>Quads, Glutes</v>
       </c>
       <c r="L31" t="str">
-        <v>Shins</v>
+        <v>Lats, Upper back, Calves</v>
       </c>
       <c r="M31" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N31" t="str">
-        <v>B-d6s1</v>
+        <v>B-sled6</v>
       </c>
       <c r="O31" t="str">
-        <v>pogo</v>
+        <v>sled</v>
       </c>
     </row>
     <row r="32">
@@ -5752,137 +5720,137 @@
         <v>2026-10-04</v>
       </c>
       <c r="C32" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Split Squat Jumps</v>
       </c>
       <c r="D32" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="E32">
-        <v>50</v>
+        <v>Explosive</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H32" t="str">
         <v/>
       </c>
       <c r="I32" t="str">
-        <v>50×6, 50×6, 50×6, 50×6</v>
-      </c>
-      <c r="J32">
-        <v>1200</v>
+        <v>BW×10, BW×10, BW×10</v>
+      </c>
+      <c r="J32" t="str">
+        <v/>
       </c>
       <c r="K32" t="str">
-        <v>Lower back</v>
+        <v>Quads, Glutes</v>
       </c>
       <c r="L32" t="str">
-        <v>Glutes, Hamstrings, Upper back</v>
+        <v>Calves, Hamstrings</v>
       </c>
       <c r="M32" t="str">
         <v/>
       </c>
       <c r="N32" t="str">
-        <v>B-d6s5</v>
+        <v>B-d6s3</v>
       </c>
       <c r="O32" t="str">
-        <v>zercher</v>
+        <v>splitjump</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-05</v>
       </c>
       <c r="B33" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C33" t="str">
-        <v>Sled push → pull</v>
+        <v>Canoe Stretch</v>
       </c>
       <c r="D33" t="str">
-        <v>Explosive</v>
-      </c>
-      <c r="E33" t="str">
-        <v/>
+        <v>Isometric</v>
+      </c>
+      <c r="E33">
+        <v>10</v>
       </c>
       <c r="F33">
-        <v>1</v>
-      </c>
-      <c r="G33">
-        <v>3</v>
-      </c>
-      <c r="H33" t="str">
-        <v/>
+        <v>4</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33">
+        <v>15</v>
       </c>
       <c r="I33" t="str">
-        <v>BW×3</v>
+        <v>10×15s, 10×15s, 10×15s, 10×15s</v>
       </c>
       <c r="J33" t="str">
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>Quads, Glutes</v>
+        <v>Mobility</v>
       </c>
       <c r="L33" t="str">
-        <v>Lats, Upper back, Calves</v>
+        <v/>
       </c>
       <c r="M33" t="str">
         <v>From check-off</v>
       </c>
       <c r="N33" t="str">
-        <v>B-sled6</v>
+        <v>B-d1s11</v>
       </c>
       <c r="O33" t="str">
-        <v>sled</v>
+        <v>canoe</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-05</v>
       </c>
       <c r="B34" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C34" t="str">
-        <v>Split Squat Jumps</v>
+        <v>Chest Press</v>
       </c>
       <c r="D34" t="str">
-        <v>Explosive</v>
-      </c>
-      <c r="E34" t="str">
-        <v/>
+        <v>Strength</v>
+      </c>
+      <c r="E34">
+        <v>35</v>
       </c>
       <c r="F34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H34" t="str">
         <v/>
       </c>
       <c r="I34" t="str">
-        <v>BW×10, BW×10, BW×10</v>
-      </c>
-      <c r="J34" t="str">
-        <v/>
+        <v>35×6, 35×6, 35×6, 35×6</v>
+      </c>
+      <c r="J34">
+        <v>840</v>
       </c>
       <c r="K34" t="str">
-        <v>Quads, Glutes</v>
+        <v>Chest</v>
       </c>
       <c r="L34" t="str">
-        <v>Calves, Hamstrings</v>
+        <v>Front delts, Triceps</v>
       </c>
       <c r="M34" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N34" t="str">
-        <v>B-d6s3</v>
+        <v>B-d1s8</v>
       </c>
       <c r="O34" t="str">
-        <v>splitjump</v>
+        <v>chestpress</v>
       </c>
     </row>
     <row r="35">
@@ -5893,43 +5861,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C35" t="str">
-        <v>Canoe Stretch</v>
+        <v>DB 6 Ways</v>
       </c>
       <c r="D35" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="E35">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F35">
-        <v>4</v>
-      </c>
-      <c r="G35" t="str">
-        <v/>
-      </c>
-      <c r="H35">
-        <v>15</v>
+        <v>2</v>
+      </c>
+      <c r="G35">
+        <v>6</v>
+      </c>
+      <c r="H35" t="str">
+        <v/>
       </c>
       <c r="I35" t="str">
-        <v>10×15s, 10×15s, 10×15s, 10×15s</v>
-      </c>
-      <c r="J35" t="str">
-        <v/>
+        <v>5×6, 5×6</v>
+      </c>
+      <c r="J35">
+        <v>60</v>
       </c>
       <c r="K35" t="str">
-        <v>Mobility</v>
+        <v>Front delts, Side delts</v>
       </c>
       <c r="L35" t="str">
         <v/>
       </c>
       <c r="M35" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N35" t="str">
-        <v>B-d1s11</v>
+        <v>B-d2s8</v>
       </c>
       <c r="O35" t="str">
-        <v>canoe</v>
+        <v>db6</v>
       </c>
     </row>
     <row r="36">
@@ -5940,13 +5908,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="C36" t="str">
-        <v>Chest Press</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="D36" t="str">
         <v>Strength</v>
       </c>
       <c r="E36">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="F36">
         <v>4</v>
@@ -5958,25 +5926,25 @@
         <v/>
       </c>
       <c r="I36" t="str">
-        <v>35×6, 35×6, 35×6, 35×6</v>
+        <v>200×6, 200×6, 200×6, 200×6</v>
       </c>
       <c r="J36">
-        <v>840</v>
+        <v>4800</v>
       </c>
       <c r="K36" t="str">
-        <v>Chest</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="L36" t="str">
-        <v>Front delts, Triceps</v>
+        <v/>
       </c>
       <c r="M36" t="str">
         <v>From check-off</v>
       </c>
       <c r="N36" t="str">
-        <v>B-d1s8</v>
+        <v>B-d1s10</v>
       </c>
       <c r="O36" t="str">
-        <v>chestpress</v>
+        <v>grip</v>
       </c>
     </row>
     <row r="37">
@@ -5987,43 +5955,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C37" t="str">
-        <v>DB 6 Ways</v>
+        <v>Lat Pulldown</v>
       </c>
       <c r="D37" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E37">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G37">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H37" t="str">
         <v/>
       </c>
       <c r="I37" t="str">
-        <v>5×6, 5×6</v>
+        <v>45×15, 45×15, 45×15, 45×15</v>
       </c>
       <c r="J37">
-        <v>60</v>
+        <v>2700</v>
       </c>
       <c r="K37" t="str">
-        <v>Front delts, Side delts</v>
+        <v>Lats</v>
       </c>
       <c r="L37" t="str">
-        <v/>
+        <v>Biceps, Upper back, Rear delts</v>
       </c>
       <c r="M37" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N37" t="str">
-        <v>B-d2s8</v>
+        <v>B-d1s1</v>
       </c>
       <c r="O37" t="str">
-        <v>db6</v>
+        <v>latpdbi</v>
       </c>
     </row>
     <row r="38">
@@ -6034,13 +6002,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="C38" t="str">
-        <v>Grip Trainer</v>
+        <v>Outer Thigh Adduction</v>
       </c>
       <c r="D38" t="str">
         <v>Strength</v>
       </c>
       <c r="E38">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="F38">
         <v>4</v>
@@ -6052,25 +6020,25 @@
         <v/>
       </c>
       <c r="I38" t="str">
-        <v>200×6, 200×6, 200×6, 200×6</v>
+        <v>160×6, 160×6, 160×6, 160×6</v>
       </c>
       <c r="J38">
-        <v>4800</v>
+        <v>3840</v>
       </c>
       <c r="K38" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Outer hip (abductors)</v>
       </c>
       <c r="L38" t="str">
-        <v/>
+        <v>Glutes</v>
       </c>
       <c r="M38" t="str">
         <v>From check-off</v>
       </c>
       <c r="N38" t="str">
-        <v>B-d1s10</v>
+        <v>B-d1s6</v>
       </c>
       <c r="O38" t="str">
-        <v>grip</v>
+        <v>outerthigh</v>
       </c>
     </row>
     <row r="39">
@@ -6081,43 +6049,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C39" t="str">
-        <v>Hack Squat</v>
+        <v>Plate Torso Rotation</v>
       </c>
       <c r="D39" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E39">
-        <v>270</v>
+        <v>10</v>
       </c>
       <c r="F39">
         <v>4</v>
       </c>
       <c r="G39">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H39" t="str">
         <v/>
       </c>
       <c r="I39" t="str">
-        <v>270×15, 270×15, 270×15, 270×15</v>
+        <v>10×6, 10×6, 10×6, 10×6</v>
       </c>
       <c r="J39">
-        <v>16200</v>
+        <v>240</v>
       </c>
       <c r="K39" t="str">
-        <v>Quads</v>
+        <v>Obliques</v>
       </c>
       <c r="L39" t="str">
-        <v>Glutes, Inner thigh (adductors)</v>
+        <v>Abs</v>
       </c>
       <c r="M39" t="str">
         <v>From check-off</v>
       </c>
       <c r="N39" t="str">
-        <v>B-d1s2</v>
+        <v>B-d1s4</v>
       </c>
       <c r="O39" t="str">
-        <v>hack</v>
+        <v>platerot</v>
       </c>
     </row>
     <row r="40">
@@ -6128,110 +6096,110 @@
         <v>2026-10-04</v>
       </c>
       <c r="C40" t="str">
-        <v>Lat Pulldown</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="D40" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E40">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F40">
         <v>4</v>
       </c>
       <c r="G40">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H40" t="str">
         <v/>
       </c>
       <c r="I40" t="str">
-        <v>45×15, 45×15, 45×15, 45×15</v>
+        <v>50×6, 50×6, 50×6, 50×6</v>
       </c>
       <c r="J40">
-        <v>2700</v>
+        <v>1200</v>
       </c>
       <c r="K40" t="str">
-        <v>Lats</v>
+        <v>Lower back</v>
       </c>
       <c r="L40" t="str">
-        <v>Biceps, Upper back, Rear delts</v>
+        <v>Glutes, Hamstrings, Upper back</v>
       </c>
       <c r="M40" t="str">
         <v>From check-off</v>
       </c>
       <c r="N40" t="str">
-        <v>B-d1s1</v>
+        <v>B-d1s8</v>
       </c>
       <c r="O40" t="str">
-        <v>latpdbi</v>
+        <v>zercher</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-07</v>
       </c>
       <c r="B41" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C41" t="str">
-        <v>Outer Thigh Adduction</v>
+        <v>Chest Press</v>
       </c>
       <c r="D41" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E41">
-        <v>160</v>
+        <v>25</v>
       </c>
       <c r="F41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G41">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H41" t="str">
         <v/>
       </c>
       <c r="I41" t="str">
-        <v>160×6, 160×6, 160×6, 160×6</v>
+        <v>25×15, 25×12</v>
       </c>
       <c r="J41">
-        <v>3840</v>
+        <v>675</v>
       </c>
       <c r="K41" t="str">
-        <v>Outer hip (abductors)</v>
+        <v>Chest</v>
       </c>
       <c r="L41" t="str">
-        <v>Glutes</v>
+        <v>Front delts, Triceps</v>
       </c>
       <c r="M41" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N41" t="str">
-        <v>B-d1s6</v>
+        <v>B-d2s5</v>
       </c>
       <c r="O41" t="str">
-        <v>outerthigh</v>
+        <v>chestpress</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-07</v>
       </c>
       <c r="B42" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C42" t="str">
-        <v>Plate Torso Rotation</v>
+        <v>Face Pulls</v>
       </c>
       <c r="D42" t="str">
         <v>Strength</v>
       </c>
       <c r="E42">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F42">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G42">
         <v>6</v>
@@ -6240,42 +6208,42 @@
         <v/>
       </c>
       <c r="I42" t="str">
-        <v>10×6, 10×6, 10×6, 10×6</v>
+        <v>27×6, 27×6</v>
       </c>
       <c r="J42">
-        <v>240</v>
+        <v>324</v>
       </c>
       <c r="K42" t="str">
-        <v>Obliques</v>
+        <v>Rear delts</v>
       </c>
       <c r="L42" t="str">
-        <v>Abs</v>
+        <v>Upper back, Traps</v>
       </c>
       <c r="M42" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N42" t="str">
-        <v>B-d1s4</v>
+        <v>B-d2s3</v>
       </c>
       <c r="O42" t="str">
-        <v>platerot</v>
+        <v>facepull</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-07</v>
       </c>
       <c r="B43" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C43" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Farmers Carry</v>
       </c>
       <c r="D43" t="str">
         <v>Strength</v>
       </c>
       <c r="E43">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F43">
         <v>4</v>
@@ -6287,25 +6255,25 @@
         <v/>
       </c>
       <c r="I43" t="str">
-        <v>50×6, 50×6, 50×6, 50×6</v>
+        <v>40×6, 40×6, 40×6, 40×6</v>
       </c>
       <c r="J43">
-        <v>1200</v>
+        <v>960</v>
       </c>
       <c r="K43" t="str">
-        <v>Lower back</v>
+        <v>Forearms &amp; grip, Traps</v>
       </c>
       <c r="L43" t="str">
-        <v>Glutes, Hamstrings, Upper back</v>
+        <v>Obliques, Abs</v>
       </c>
       <c r="M43" t="str">
         <v>From check-off</v>
       </c>
       <c r="N43" t="str">
-        <v>B-d1s8</v>
+        <v>B-d2s1</v>
       </c>
       <c r="O43" t="str">
-        <v>zercher</v>
+        <v>farmers</v>
       </c>
     </row>
     <row r="44">
@@ -6316,43 +6284,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C44" t="str">
-        <v>Chest Press</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="D44" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E44">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="F44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G44">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H44" t="str">
         <v/>
       </c>
       <c r="I44" t="str">
-        <v>25×15, 25×12</v>
+        <v>200×6, 200×6, 200×6, 200×6</v>
       </c>
       <c r="J44">
-        <v>675</v>
+        <v>4800</v>
       </c>
       <c r="K44" t="str">
-        <v>Chest</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="L44" t="str">
-        <v>Front delts, Triceps</v>
+        <v/>
       </c>
       <c r="M44" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N44" t="str">
-        <v>B-d2s5</v>
+        <v>B-d2s7</v>
       </c>
       <c r="O44" t="str">
-        <v>chestpress</v>
+        <v>grip</v>
       </c>
     </row>
     <row r="45">
@@ -6363,13 +6331,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="C45" t="str">
-        <v>Face Pull</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="D45" t="str">
         <v>Strength</v>
       </c>
       <c r="E45">
-        <v>27</v>
+        <v>320</v>
       </c>
       <c r="F45">
         <v>2</v>
@@ -6381,25 +6349,25 @@
         <v/>
       </c>
       <c r="I45" t="str">
-        <v>27×6, 27×6</v>
+        <v>320×6, 320×6</v>
       </c>
       <c r="J45">
-        <v>324</v>
+        <v>3840</v>
       </c>
       <c r="K45" t="str">
-        <v>Rear delts</v>
+        <v>Glutes</v>
       </c>
       <c r="L45" t="str">
-        <v>Upper back, Traps</v>
+        <v>Hamstrings</v>
       </c>
       <c r="M45" t="str">
         <v/>
       </c>
       <c r="N45" t="str">
-        <v>B-d2s3</v>
+        <v>B-d2s5</v>
       </c>
       <c r="O45" t="str">
-        <v>facepull</v>
+        <v>hipthrust</v>
       </c>
     </row>
     <row r="46">
@@ -6410,43 +6378,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C46" t="str">
-        <v>Farmers Carry</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="D46" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="E46">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F46">
-        <v>4</v>
-      </c>
-      <c r="G46">
-        <v>6</v>
-      </c>
-      <c r="H46" t="str">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46">
+        <v>15</v>
       </c>
       <c r="I46" t="str">
-        <v>40×6, 40×6, 40×6, 40×6</v>
-      </c>
-      <c r="J46">
-        <v>960</v>
+        <v>15×15s, 15×15s, 15×15s</v>
+      </c>
+      <c r="J46" t="str">
+        <v/>
       </c>
       <c r="K46" t="str">
-        <v>Forearms &amp; grip, Traps</v>
+        <v>Abs, Hip flexors</v>
       </c>
       <c r="L46" t="str">
-        <v>Obliques, Abs</v>
+        <v/>
       </c>
       <c r="M46" t="str">
         <v>From check-off</v>
       </c>
       <c r="N46" t="str">
-        <v>B-d2s1</v>
+        <v>B-d1s9</v>
       </c>
       <c r="O46" t="str">
-        <v>farmers</v>
+        <v>kbleg</v>
       </c>
     </row>
     <row r="47">
@@ -6457,16 +6425,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="C47" t="str">
-        <v>Grip Trainer</v>
+        <v>Overhead Tricep Extension</v>
       </c>
       <c r="D47" t="str">
         <v>Strength</v>
       </c>
       <c r="E47">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="F47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G47">
         <v>6</v>
@@ -6475,25 +6443,25 @@
         <v/>
       </c>
       <c r="I47" t="str">
-        <v>200×6, 200×6, 200×6, 200×6</v>
+        <v>17×6, 17×6</v>
       </c>
       <c r="J47">
-        <v>4800</v>
+        <v>204</v>
       </c>
       <c r="K47" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Triceps</v>
       </c>
       <c r="L47" t="str">
         <v/>
       </c>
       <c r="M47" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N47" t="str">
-        <v>B-d2s7</v>
+        <v>B-d2s2</v>
       </c>
       <c r="O47" t="str">
-        <v>grip</v>
+        <v>ohtri</v>
       </c>
     </row>
     <row r="48">
@@ -6504,16 +6472,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="C48" t="str">
-        <v>Hip Thrust</v>
+        <v>Seated Cable Crunch</v>
       </c>
       <c r="D48" t="str">
         <v>Strength</v>
       </c>
       <c r="E48">
-        <v>320</v>
+        <v>44</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G48">
         <v>6</v>
@@ -6522,25 +6490,25 @@
         <v/>
       </c>
       <c r="I48" t="str">
-        <v>320×6, 320×6</v>
+        <v>44×6, 44×6, 44×6, 44×6</v>
       </c>
       <c r="J48">
-        <v>3840</v>
+        <v>1056</v>
       </c>
       <c r="K48" t="str">
-        <v>Glutes</v>
+        <v>Abs</v>
       </c>
       <c r="L48" t="str">
-        <v>Hamstrings</v>
+        <v/>
       </c>
       <c r="M48" t="str">
         <v/>
       </c>
       <c r="N48" t="str">
-        <v>B-d2s5</v>
+        <v>B-xmuy1nsai5fs</v>
       </c>
       <c r="O48" t="str">
-        <v>hipthrust</v>
+        <v>seated-cable-crunch</v>
       </c>
     </row>
     <row r="49">
@@ -6551,10 +6519,10 @@
         <v>2026-10-04</v>
       </c>
       <c r="C49" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Zottman Curl</v>
       </c>
       <c r="D49" t="str">
-        <v>Isometric</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E49">
         <v>15</v>
@@ -6562,20 +6530,20 @@
       <c r="F49">
         <v>3</v>
       </c>
-      <c r="G49" t="str">
-        <v/>
-      </c>
-      <c r="H49">
+      <c r="G49">
         <v>15</v>
       </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
       <c r="I49" t="str">
-        <v>15×15s, 15×15s, 15×15s</v>
-      </c>
-      <c r="J49" t="str">
-        <v/>
+        <v>15×15, 15×15, 15×15</v>
+      </c>
+      <c r="J49">
+        <v>675</v>
       </c>
       <c r="K49" t="str">
-        <v>Abs, Hip flexors</v>
+        <v>Biceps, Forearms &amp; grip</v>
       </c>
       <c r="L49" t="str">
         <v/>
@@ -6587,27 +6555,27 @@
         <v>B-d1s9</v>
       </c>
       <c r="O49" t="str">
-        <v>kbleg</v>
+        <v>zottman</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-08</v>
       </c>
       <c r="B50" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C50" t="str">
-        <v>Overhead Tricep Extension</v>
+        <v>Cable Wrist Pulldown</v>
       </c>
       <c r="D50" t="str">
         <v>Strength</v>
       </c>
       <c r="E50">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G50">
         <v>6</v>
@@ -6616,13 +6584,13 @@
         <v/>
       </c>
       <c r="I50" t="str">
-        <v>17×6, 17×6</v>
+        <v>44×6, 44×6, 44×6, 44×6</v>
       </c>
       <c r="J50">
-        <v>204</v>
+        <v>1056</v>
       </c>
       <c r="K50" t="str">
-        <v>Triceps</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="L50" t="str">
         <v/>
@@ -6631,27 +6599,27 @@
         <v/>
       </c>
       <c r="N50" t="str">
-        <v>B-d2s2</v>
+        <v>B-xmuy1rdg3uct</v>
       </c>
       <c r="O50" t="str">
-        <v>ohtri</v>
+        <v>wristpd</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-08</v>
       </c>
       <c r="B51" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C51" t="str">
-        <v>Seated Cable Crunch</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="D51" t="str">
         <v>Strength</v>
       </c>
       <c r="E51">
-        <v>44</v>
+        <v>180</v>
       </c>
       <c r="F51">
         <v>4</v>
@@ -6663,13 +6631,13 @@
         <v/>
       </c>
       <c r="I51" t="str">
-        <v>44×6, 44×6, 44×6, 44×6</v>
+        <v>180×6, 180×6, 180×6, 180×6</v>
       </c>
       <c r="J51">
-        <v>1056</v>
+        <v>4320</v>
       </c>
       <c r="K51" t="str">
-        <v>Abs</v>
+        <v>Inner thigh (adductors)</v>
       </c>
       <c r="L51" t="str">
         <v/>
@@ -6678,30 +6646,30 @@
         <v/>
       </c>
       <c r="N51" t="str">
-        <v>B-xmuy1nsai5fs</v>
+        <v>B-d1s5</v>
       </c>
       <c r="O51" t="str">
-        <v>seated-cable-crunch</v>
+        <v>innerthigh</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-08</v>
       </c>
       <c r="B52" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C52" t="str">
-        <v>Zottman Curl</v>
+        <v>Lat Pulldown</v>
       </c>
       <c r="D52" t="str">
         <v>Hypertrophy</v>
       </c>
       <c r="E52">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52">
         <v>15</v>
@@ -6710,25 +6678,25 @@
         <v/>
       </c>
       <c r="I52" t="str">
-        <v>15×15, 15×15, 15×15</v>
+        <v>55×15, 55×15, 55×15, 55×15</v>
       </c>
       <c r="J52">
-        <v>675</v>
+        <v>3300</v>
       </c>
       <c r="K52" t="str">
-        <v>Biceps, Forearms &amp; grip</v>
+        <v>Lats</v>
       </c>
       <c r="L52" t="str">
-        <v/>
+        <v>Biceps, Upper back, Rear delts</v>
       </c>
       <c r="M52" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N52" t="str">
-        <v>B-d1s9</v>
+        <v>B-d3s2</v>
       </c>
       <c r="O52" t="str">
-        <v>zottman</v>
+        <v>latpdbi</v>
       </c>
     </row>
     <row r="53">
@@ -6739,13 +6707,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="C53" t="str">
-        <v>Cable Wrist Pulldown</v>
+        <v>Outer Thigh Adduction</v>
       </c>
       <c r="D53" t="str">
         <v>Strength</v>
       </c>
       <c r="E53">
-        <v>44</v>
+        <v>160</v>
       </c>
       <c r="F53">
         <v>4</v>
@@ -6757,25 +6725,25 @@
         <v/>
       </c>
       <c r="I53" t="str">
-        <v>44×6, 44×6, 44×6, 44×6</v>
+        <v>160×6, 160×6, 160×6, 160×6</v>
       </c>
       <c r="J53">
-        <v>1056</v>
+        <v>3840</v>
       </c>
       <c r="K53" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Outer hip (abductors)</v>
       </c>
       <c r="L53" t="str">
-        <v/>
+        <v>Glutes</v>
       </c>
       <c r="M53" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N53" t="str">
-        <v>B-xmuy1rdg3uct</v>
+        <v>B-d4s3</v>
       </c>
       <c r="O53" t="str">
-        <v>wristpd</v>
+        <v>outerthigh</v>
       </c>
     </row>
     <row r="54">
@@ -6786,43 +6754,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C54" t="str">
-        <v>Hack Squat</v>
+        <v>Seated Cable Crunch</v>
       </c>
       <c r="D54" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E54">
-        <v>270</v>
+        <v>44</v>
       </c>
       <c r="F54">
         <v>4</v>
       </c>
       <c r="G54">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H54" t="str">
         <v/>
       </c>
       <c r="I54" t="str">
-        <v>270×15, 270×15, 270×15, 270×15</v>
+        <v>44×6, 44×6, 44×6, 44×6</v>
       </c>
       <c r="J54">
-        <v>16200</v>
+        <v>1056</v>
       </c>
       <c r="K54" t="str">
-        <v>Quads</v>
+        <v>Abs</v>
       </c>
       <c r="L54" t="str">
-        <v>Glutes, Inner thigh (adductors)</v>
+        <v/>
       </c>
       <c r="M54" t="str">
         <v>From check-off</v>
       </c>
       <c r="N54" t="str">
-        <v>B-d3s1</v>
+        <v>B-xmuy1rdg3uct</v>
       </c>
       <c r="O54" t="str">
-        <v>hack</v>
+        <v>seated-cable-crunch</v>
       </c>
     </row>
     <row r="55">
@@ -6833,16 +6801,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="C55" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="D55" t="str">
         <v>Strength</v>
       </c>
       <c r="E55">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="F55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -6851,89 +6819,89 @@
         <v/>
       </c>
       <c r="I55" t="str">
-        <v>180×6, 180×6, 180×6, 180×6</v>
+        <v>50×6, 50×6, 50×6</v>
       </c>
       <c r="J55">
-        <v>4320</v>
+        <v>900</v>
       </c>
       <c r="K55" t="str">
-        <v>Inner thigh (adductors)</v>
+        <v>Lower back</v>
       </c>
       <c r="L55" t="str">
-        <v/>
+        <v>Glutes, Hamstrings, Upper back</v>
       </c>
       <c r="M55" t="str">
         <v/>
       </c>
       <c r="N55" t="str">
-        <v>B-d1s5</v>
+        <v>B-d4s4</v>
       </c>
       <c r="O55" t="str">
-        <v>innerthigh</v>
+        <v>zercher</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-09</v>
       </c>
       <c r="B56" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C56" t="str">
-        <v>Lat Pulldown</v>
+        <v>Bulgarian Split Squat</v>
       </c>
       <c r="D56" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E56">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="F56">
         <v>4</v>
       </c>
       <c r="G56">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H56" t="str">
         <v/>
       </c>
       <c r="I56" t="str">
-        <v>55×15, 55×15, 55×15, 55×15</v>
+        <v>40×6, 40×6, 40×6, 40×6</v>
       </c>
       <c r="J56">
-        <v>3300</v>
+        <v>960</v>
       </c>
       <c r="K56" t="str">
-        <v>Lats</v>
+        <v>Quads, Glutes</v>
       </c>
       <c r="L56" t="str">
-        <v>Biceps, Upper back, Rear delts</v>
+        <v>Inner thigh (adductors), Hamstrings</v>
       </c>
       <c r="M56" t="str">
         <v/>
       </c>
       <c r="N56" t="str">
-        <v>B-d3s2</v>
+        <v>B-d4s6</v>
       </c>
       <c r="O56" t="str">
-        <v>latpdbi</v>
+        <v>bss</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-09</v>
       </c>
       <c r="B57" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C57" t="str">
-        <v>Outer Thigh Adduction</v>
+        <v>Farmers Carry</v>
       </c>
       <c r="D57" t="str">
         <v>Strength</v>
       </c>
       <c r="E57">
-        <v>160</v>
+        <v>40</v>
       </c>
       <c r="F57">
         <v>4</v>
@@ -6945,42 +6913,42 @@
         <v/>
       </c>
       <c r="I57" t="str">
-        <v>160×6, 160×6, 160×6, 160×6</v>
+        <v>40×6, 40×6, 40×6, 40×6</v>
       </c>
       <c r="J57">
-        <v>3840</v>
+        <v>960</v>
       </c>
       <c r="K57" t="str">
-        <v>Outer hip (abductors)</v>
+        <v>Forearms &amp; grip, Traps</v>
       </c>
       <c r="L57" t="str">
-        <v>Glutes</v>
+        <v>Obliques, Abs</v>
       </c>
       <c r="M57" t="str">
         <v>From check-off</v>
       </c>
       <c r="N57" t="str">
-        <v>B-d4s3</v>
+        <v>B-d4s1</v>
       </c>
       <c r="O57" t="str">
-        <v>outerthigh</v>
+        <v>farmers</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-09</v>
       </c>
       <c r="B58" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C58" t="str">
-        <v>Seated Cable Crunch</v>
+        <v>Inner Thigh Abduction</v>
       </c>
       <c r="D58" t="str">
         <v>Strength</v>
       </c>
       <c r="E58">
-        <v>44</v>
+        <v>180</v>
       </c>
       <c r="F58">
         <v>4</v>
@@ -6992,36 +6960,36 @@
         <v/>
       </c>
       <c r="I58" t="str">
-        <v>44×6, 44×6, 44×6, 44×6</v>
+        <v>180×6, 180×6, 180×6, 180×6</v>
       </c>
       <c r="J58">
-        <v>1056</v>
+        <v>4320</v>
       </c>
       <c r="K58" t="str">
-        <v>Abs</v>
+        <v>Inner thigh (adductors)</v>
       </c>
       <c r="L58" t="str">
         <v/>
       </c>
       <c r="M58" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N58" t="str">
-        <v>B-xmuy1rdg3uct</v>
+        <v>B-d4s2</v>
       </c>
       <c r="O58" t="str">
-        <v>seated-cable-crunch</v>
+        <v>innerthigh</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2026-10-08</v>
+        <v>2026-10-09</v>
       </c>
       <c r="B59" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C59" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Prone Leg Curl</v>
       </c>
       <c r="D59" t="str">
         <v>Strength</v>
@@ -7030,7 +6998,7 @@
         <v>50</v>
       </c>
       <c r="F59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G59">
         <v>6</v>
@@ -7039,25 +7007,25 @@
         <v/>
       </c>
       <c r="I59" t="str">
-        <v>50×6, 50×6, 50×6</v>
+        <v>50×6, 50×6, 50×6, 50×6</v>
       </c>
       <c r="J59">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="K59" t="str">
-        <v>Lower back</v>
+        <v>Hamstrings</v>
       </c>
       <c r="L59" t="str">
-        <v>Glutes, Hamstrings, Upper back</v>
+        <v>Calves</v>
       </c>
       <c r="M59" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N59" t="str">
-        <v>B-d4s4</v>
+        <v>B-d4s6</v>
       </c>
       <c r="O59" t="str">
-        <v>zercher</v>
+        <v>legcurl</v>
       </c>
     </row>
     <row r="60">
@@ -7068,472 +7036,237 @@
         <v>2026-10-04</v>
       </c>
       <c r="C60" t="str">
-        <v>Bulgarian Split Squat</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="D60" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="E60">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F60">
         <v>4</v>
       </c>
-      <c r="G60">
-        <v>6</v>
-      </c>
-      <c r="H60" t="str">
-        <v/>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60">
+        <v>15</v>
       </c>
       <c r="I60" t="str">
-        <v>40×6, 40×6, 40×6, 40×6</v>
-      </c>
-      <c r="J60">
-        <v>960</v>
+        <v>50×15s, 50×15s, 50×15s, 50×15s</v>
+      </c>
+      <c r="J60" t="str">
+        <v/>
       </c>
       <c r="K60" t="str">
-        <v>Quads, Glutes</v>
+        <v>Rear delts</v>
       </c>
       <c r="L60" t="str">
-        <v>Inner thigh (adductors), Hamstrings</v>
+        <v>Upper back</v>
       </c>
       <c r="M60" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N60" t="str">
-        <v>B-d4s6</v>
+        <v>B-d5s3</v>
       </c>
       <c r="O60" t="str">
-        <v>bss</v>
+        <v>reardelt</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2026-10-09</v>
+        <v>2026-10-10</v>
       </c>
       <c r="B61" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C61" t="str">
-        <v>Farmers Carry</v>
+        <v>Cable Punch ISO hold</v>
       </c>
       <c r="D61" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="E61">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F61">
-        <v>4</v>
-      </c>
-      <c r="G61">
-        <v>6</v>
-      </c>
-      <c r="H61" t="str">
-        <v/>
+        <v>2</v>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61">
+        <v>15</v>
       </c>
       <c r="I61" t="str">
-        <v>40×6, 40×6, 40×6, 40×6</v>
-      </c>
-      <c r="J61">
-        <v>960</v>
+        <v>30×15s, 30×15s</v>
+      </c>
+      <c r="J61" t="str">
+        <v/>
       </c>
       <c r="K61" t="str">
-        <v>Forearms &amp; grip, Traps</v>
+        <v>Obliques, Abs</v>
       </c>
       <c r="L61" t="str">
-        <v>Obliques, Abs</v>
+        <v>Chest, Front delts</v>
       </c>
       <c r="M61" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N61" t="str">
-        <v>B-d4s1</v>
+        <v>B-d3s6</v>
       </c>
       <c r="O61" t="str">
-        <v>farmers</v>
+        <v>cablepunch</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2026-10-09</v>
+        <v>2026-10-10</v>
       </c>
       <c r="B62" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C62" t="str">
-        <v>Inner Thigh Abduction</v>
+        <v>Chest Press</v>
       </c>
       <c r="D62" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E62">
-        <v>180</v>
+        <v>25</v>
       </c>
       <c r="F62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G62">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H62" t="str">
         <v/>
       </c>
       <c r="I62" t="str">
-        <v>180×6, 180×6, 180×6, 180×6</v>
+        <v>25×15, 25×10</v>
       </c>
       <c r="J62">
-        <v>4320</v>
+        <v>625</v>
       </c>
       <c r="K62" t="str">
-        <v>Inner thigh (adductors)</v>
+        <v>Chest</v>
       </c>
       <c r="L62" t="str">
-        <v/>
+        <v>Front delts, Triceps</v>
       </c>
       <c r="M62" t="str">
         <v/>
       </c>
       <c r="N62" t="str">
-        <v>B-d4s2</v>
+        <v>B-d4s5</v>
       </c>
       <c r="O62" t="str">
-        <v>innerthigh</v>
+        <v>chestpress</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2026-10-09</v>
+        <v>2026-10-10</v>
       </c>
       <c r="B63" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C63" t="str">
-        <v>Prone Leg Curl</v>
+        <v>Duck Sled Push</v>
       </c>
       <c r="D63" t="str">
-        <v>Strength</v>
+        <v>Explosive</v>
       </c>
       <c r="E63">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G63">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H63" t="str">
         <v/>
       </c>
       <c r="I63" t="str">
-        <v>50×6, 50×6, 50×6, 50×6</v>
+        <v>20×10</v>
       </c>
       <c r="J63">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="K63" t="str">
-        <v>Hamstrings</v>
+        <v/>
       </c>
       <c r="L63" t="str">
-        <v>Calves</v>
+        <v/>
       </c>
       <c r="M63" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N63" t="str">
-        <v>B-d4s6</v>
+        <v>X-muy8rvy9whc0</v>
       </c>
       <c r="O63" t="str">
-        <v>legcurl</v>
+        <v>duck-sled-push</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2026-10-09</v>
+        <v>2026-10-10</v>
       </c>
       <c r="B64" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C64" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Explosive Unilateral Cable Row</v>
       </c>
       <c r="D64" t="str">
-        <v>Isometric</v>
+        <v>Explosive</v>
       </c>
       <c r="E64">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F64">
-        <v>4</v>
-      </c>
-      <c r="G64" t="str">
-        <v/>
-      </c>
-      <c r="H64">
-        <v>15</v>
+        <v>2</v>
+      </c>
+      <c r="G64">
+        <v>10</v>
+      </c>
+      <c r="H64" t="str">
+        <v/>
       </c>
       <c r="I64" t="str">
-        <v>50×15s, 50×15s, 50×15s, 50×15s</v>
-      </c>
-      <c r="J64" t="str">
-        <v/>
+        <v>30×10, 30×10</v>
+      </c>
+      <c r="J64">
+        <v>600</v>
       </c>
       <c r="K64" t="str">
-        <v>Rear delts</v>
+        <v>Lats, Upper back</v>
       </c>
       <c r="L64" t="str">
-        <v>Upper back</v>
+        <v>Rear delts, Biceps</v>
       </c>
       <c r="M64" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N64" t="str">
-        <v>B-d5s3</v>
+        <v>B-d3s6</v>
       </c>
       <c r="O64" t="str">
-        <v>reardelt</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v>2026-10-10</v>
-      </c>
-      <c r="B65" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="C65" t="str">
-        <v>Cable Punch ISO hold</v>
-      </c>
-      <c r="D65" t="str">
-        <v>Isometric</v>
-      </c>
-      <c r="E65">
-        <v>30</v>
-      </c>
-      <c r="F65">
-        <v>2</v>
-      </c>
-      <c r="G65" t="str">
-        <v/>
-      </c>
-      <c r="H65">
-        <v>15</v>
-      </c>
-      <c r="I65" t="str">
-        <v>30×15s, 30×15s</v>
-      </c>
-      <c r="J65" t="str">
-        <v/>
-      </c>
-      <c r="K65" t="str">
-        <v>Obliques, Abs</v>
-      </c>
-      <c r="L65" t="str">
-        <v>Chest, Front delts</v>
-      </c>
-      <c r="M65" t="str">
-        <v/>
-      </c>
-      <c r="N65" t="str">
-        <v>B-d3s6</v>
-      </c>
-      <c r="O65" t="str">
-        <v>cablepunch</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v>2026-10-10</v>
-      </c>
-      <c r="B66" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="C66" t="str">
-        <v>Chest Press</v>
-      </c>
-      <c r="D66" t="str">
-        <v>Hypertrophy</v>
-      </c>
-      <c r="E66">
-        <v>25</v>
-      </c>
-      <c r="F66">
-        <v>2</v>
-      </c>
-      <c r="G66">
-        <v>10</v>
-      </c>
-      <c r="H66" t="str">
-        <v/>
-      </c>
-      <c r="I66" t="str">
-        <v>25×15, 25×10</v>
-      </c>
-      <c r="J66">
-        <v>625</v>
-      </c>
-      <c r="K66" t="str">
-        <v>Chest</v>
-      </c>
-      <c r="L66" t="str">
-        <v>Front delts, Triceps</v>
-      </c>
-      <c r="M66" t="str">
-        <v/>
-      </c>
-      <c r="N66" t="str">
-        <v>B-d4s5</v>
-      </c>
-      <c r="O66" t="str">
-        <v>chestpress</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>2026-10-10</v>
-      </c>
-      <c r="B67" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="C67" t="str">
-        <v>Duck Sled Push</v>
-      </c>
-      <c r="D67" t="str">
-        <v>Explosive</v>
-      </c>
-      <c r="E67">
-        <v>20</v>
-      </c>
-      <c r="F67">
-        <v>1</v>
-      </c>
-      <c r="G67">
-        <v>10</v>
-      </c>
-      <c r="H67" t="str">
-        <v/>
-      </c>
-      <c r="I67" t="str">
-        <v>20×10</v>
-      </c>
-      <c r="J67">
-        <v>200</v>
-      </c>
-      <c r="K67" t="str">
-        <v/>
-      </c>
-      <c r="L67" t="str">
-        <v/>
-      </c>
-      <c r="M67" t="str">
-        <v/>
-      </c>
-      <c r="N67" t="str">
-        <v>X-muy8rvy9whc0</v>
-      </c>
-      <c r="O67" t="str">
-        <v>duck-sled-push</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>2026-10-10</v>
-      </c>
-      <c r="B68" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="C68" t="str">
-        <v>Explosive Unilateral Cable Row</v>
-      </c>
-      <c r="D68" t="str">
-        <v>Explosive</v>
-      </c>
-      <c r="E68">
-        <v>30</v>
-      </c>
-      <c r="F68">
-        <v>2</v>
-      </c>
-      <c r="G68">
-        <v>10</v>
-      </c>
-      <c r="H68" t="str">
-        <v/>
-      </c>
-      <c r="I68" t="str">
-        <v>30×10, 30×10</v>
-      </c>
-      <c r="J68">
-        <v>600</v>
-      </c>
-      <c r="K68" t="str">
-        <v>Lats, Upper back</v>
-      </c>
-      <c r="L68" t="str">
-        <v>Rear delts, Biceps</v>
-      </c>
-      <c r="M68" t="str">
-        <v/>
-      </c>
-      <c r="N68" t="str">
-        <v>B-d3s6</v>
-      </c>
-      <c r="O68" t="str">
         <v>cablerow</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>2026-10-11</v>
-      </c>
-      <c r="B69" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="C69" t="str">
-        <v>Hack Squat</v>
-      </c>
-      <c r="D69" t="str">
-        <v>Hypertrophy</v>
-      </c>
-      <c r="E69">
-        <v>270</v>
-      </c>
-      <c r="F69">
-        <v>4</v>
-      </c>
-      <c r="G69">
-        <v>15</v>
-      </c>
-      <c r="H69" t="str">
-        <v/>
-      </c>
-      <c r="I69" t="str">
-        <v>270×15, 270×15, 270×15, 270×15</v>
-      </c>
-      <c r="J69">
-        <v>16200</v>
-      </c>
-      <c r="K69" t="str">
-        <v>Quads</v>
-      </c>
-      <c r="L69" t="str">
-        <v>Glutes, Inner thigh (adductors)</v>
-      </c>
-      <c r="M69" t="str">
-        <v>From check-off</v>
-      </c>
-      <c r="N69" t="str">
-        <v>Pa2gom-d1s2</v>
-      </c>
-      <c r="O69" t="str">
-        <v>hack</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O69"/>
+  <autoFilter ref="A1:O64"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O64"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7588,16 +7321,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B3" t="str">
-        <v>Quads</v>
+        <v>Glutes</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="4">
@@ -7605,16 +7338,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B4" t="str">
-        <v>Glutes</v>
+        <v>Upper back</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="5">
@@ -7622,16 +7355,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B5" t="str">
-        <v>Inner thigh (adductors)</v>
+        <v>Rear delts</v>
       </c>
       <c r="C5">
         <v>8</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>11.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -7639,16 +7372,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B6" t="str">
-        <v>Upper back</v>
+        <v>Lower back</v>
       </c>
       <c r="C6">
+        <v>9</v>
+      </c>
+      <c r="D6">
         <v>0</v>
       </c>
-      <c r="D6">
-        <v>21</v>
-      </c>
       <c r="E6">
-        <v>10.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -7656,16 +7389,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B7" t="str">
-        <v>Rear delts</v>
+        <v>Inner thigh (adductors)</v>
       </c>
       <c r="C7">
         <v>8</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -7673,16 +7406,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B8" t="str">
-        <v>Lower back</v>
+        <v>Quads</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -7866,10 +7599,10 @@
         <v>16</v>
       </c>
       <c r="D19">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E19">
-        <v>31.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="20">
@@ -7877,16 +7610,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B20" t="str">
-        <v>Quads</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="C20">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -7894,16 +7627,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B21" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Abs</v>
       </c>
       <c r="C21">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E21">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -7911,16 +7644,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B22" t="str">
-        <v>Abs</v>
+        <v>Upper back</v>
       </c>
       <c r="C22">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D22">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E22">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -7928,16 +7661,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B23" t="str">
-        <v>Upper back</v>
+        <v>Hamstrings</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D23">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E23">
-        <v>19</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="24">
@@ -7945,16 +7678,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B24" t="str">
-        <v>Inner thigh (adductors)</v>
+        <v>Lats</v>
       </c>
       <c r="C24">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D24">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="25">
@@ -7962,16 +7695,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B25" t="str">
-        <v>Hamstrings</v>
+        <v>Quads</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D25">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>15.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
@@ -7979,16 +7712,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B26" t="str">
-        <v>Lats</v>
+        <v>Obliques</v>
       </c>
       <c r="C26">
+        <v>10</v>
+      </c>
+      <c r="D26">
+        <v>8</v>
+      </c>
+      <c r="E26">
         <v>14</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26">
-        <v>14.5</v>
       </c>
     </row>
     <row r="27">
@@ -7996,16 +7729,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B27" t="str">
-        <v>Obliques</v>
+        <v>Rear delts</v>
       </c>
       <c r="C27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D27">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E27">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
@@ -8013,16 +7746,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B28" t="str">
-        <v>Rear delts</v>
+        <v>Inner thigh (adductors)</v>
       </c>
       <c r="C28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D28">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E28">
-        <v>13</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="29">
@@ -8283,7 +8016,7 @@
         <v>96</v>
       </c>
       <c r="H2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -8309,7 +8042,7 @@
         <v>3</v>
       </c>
       <c r="H3">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -8580,7 +8313,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>1RM: Face Pull</v>
+        <v>1RM: Face Pulls</v>
       </c>
       <c r="B23">
         <v>50</v>
@@ -8604,7 +8337,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>1RM: Hack Squat</v>
+        <v>1RM: Hack Squats</v>
       </c>
       <c r="B26">
         <v>415</v>
@@ -8751,7 +8484,7 @@
         <v>Exported</v>
       </c>
       <c r="B44" t="str">
-        <v>2026-10-12T02:59:56.692Z</v>
+        <v>2026-10-12T04:59:38.884Z</v>
       </c>
     </row>
   </sheetData>
@@ -9720,7 +9453,7 @@
         <v>facepull</v>
       </c>
       <c r="M17" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="N17" t="str">
         <v>strength</v>
@@ -10333,7 +10066,7 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>hack</v>
+        <v>c:fedb:Hack_Squat</v>
       </c>
       <c r="M28" t="str">
         <v>Hack Squat</v>
@@ -10345,7 +10078,7 @@
         <v>270</v>
       </c>
       <c r="P28" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q28" t="str">
         <v/>
@@ -10560,7 +10293,7 @@
         <v>facepull</v>
       </c>
       <c r="M32" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="N32" t="str">
         <v>strength</v>
@@ -11677,7 +11410,7 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>hack</v>
+        <v>c:fedb:Hack_Squat</v>
       </c>
       <c r="M52" t="str">
         <v>Hack Squat</v>
@@ -11689,7 +11422,7 @@
         <v>270</v>
       </c>
       <c r="P52" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="Q52" t="str">
         <v/>
@@ -11792,7 +11525,7 @@
         <v>facepull</v>
       </c>
       <c r="M54" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="N54" t="str">
         <v>strength</v>
@@ -13021,7 +12754,7 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>hack</v>
+        <v>c:fedb:Hack_Squat</v>
       </c>
       <c r="M76" t="str">
         <v>Hack Squat</v>
@@ -14088,7 +13821,7 @@
         <v>facepull</v>
       </c>
       <c r="M95" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="N95" t="str">
         <v>strength</v>
@@ -14701,7 +14434,7 @@
         <v/>
       </c>
       <c r="L106" t="str">
-        <v>hack</v>
+        <v>c:fedb:Hack_Squat</v>
       </c>
       <c r="M106" t="str">
         <v>Hack Squat</v>
@@ -14872,7 +14605,7 @@
         <v>facepull</v>
       </c>
       <c r="M109" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="N109" t="str">
         <v>strength</v>
@@ -16328,7 +16061,7 @@
         <v>facepull</v>
       </c>
       <c r="M135" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="N135" t="str">
         <v>strength</v>
@@ -18344,7 +18077,7 @@
         <v>facepull</v>
       </c>
       <c r="M171" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="N171" t="str">
         <v>strength</v>
@@ -18960,7 +18693,7 @@
         <v>hack</v>
       </c>
       <c r="M182" t="str">
-        <v>Hack Squat</v>
+        <v>Hack Squats</v>
       </c>
       <c r="N182" t="str">
         <v>hyp</v>
@@ -19184,7 +18917,7 @@
         <v>facepull</v>
       </c>
       <c r="M186" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="N186" t="str">
         <v>strength</v>
@@ -20304,7 +20037,7 @@
         <v>hack</v>
       </c>
       <c r="M206" t="str">
-        <v>Hack Squat</v>
+        <v>Hack Squats</v>
       </c>
       <c r="N206" t="str">
         <v>hyp</v>
@@ -20416,7 +20149,7 @@
         <v>facepull</v>
       </c>
       <c r="M208" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="N208" t="str">
         <v>strength</v>
@@ -21648,7 +21381,7 @@
         <v>hack</v>
       </c>
       <c r="M230" t="str">
-        <v>Hack Squat</v>
+        <v>Hack Squats</v>
       </c>
       <c r="N230" t="str">
         <v>hyp</v>
@@ -22712,7 +22445,7 @@
         <v>facepull</v>
       </c>
       <c r="M249" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="N249" t="str">
         <v>strength</v>
@@ -23328,7 +23061,7 @@
         <v>hack</v>
       </c>
       <c r="M260" t="str">
-        <v>Hack Squat</v>
+        <v>Hack Squats</v>
       </c>
       <c r="N260" t="str">
         <v>hyp</v>
@@ -23496,7 +23229,7 @@
         <v>facepull</v>
       </c>
       <c r="M263" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="N263" t="str">
         <v>strength</v>
@@ -24952,7 +24685,7 @@
         <v>facepull</v>
       </c>
       <c r="M289" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="N289" t="str">
         <v>strength</v>
@@ -26968,7 +26701,7 @@
         <v>facepull</v>
       </c>
       <c r="M325" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="N325" t="str">
         <v>strength</v>
@@ -27584,7 +27317,7 @@
         <v>hack</v>
       </c>
       <c r="M336" t="str">
-        <v>Hack Squat</v>
+        <v>Hack Squats</v>
       </c>
       <c r="N336" t="str">
         <v>hyp</v>
@@ -27808,7 +27541,7 @@
         <v>facepull</v>
       </c>
       <c r="M340" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="N340" t="str">
         <v>strength</v>
@@ -28928,7 +28661,7 @@
         <v>hack</v>
       </c>
       <c r="M360" t="str">
-        <v>Hack Squat</v>
+        <v>Hack Squats</v>
       </c>
       <c r="N360" t="str">
         <v>hyp</v>
@@ -29040,7 +28773,7 @@
         <v>facepull</v>
       </c>
       <c r="M362" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="N362" t="str">
         <v>strength</v>
@@ -30272,7 +30005,7 @@
         <v>hack</v>
       </c>
       <c r="M384" t="str">
-        <v>Hack Squat</v>
+        <v>Hack Squats</v>
       </c>
       <c r="N384" t="str">
         <v>hyp</v>
@@ -31224,7 +30957,7 @@
         <v>facepull</v>
       </c>
       <c r="M401" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="N401" t="str">
         <v>strength</v>
@@ -31728,7 +31461,7 @@
         <v>hack</v>
       </c>
       <c r="M410" t="str">
-        <v>Hack Squat</v>
+        <v>Hack Squats</v>
       </c>
       <c r="N410" t="str">
         <v>hyp</v>
@@ -31896,7 +31629,7 @@
         <v>facepull</v>
       </c>
       <c r="M413" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="N413" t="str">
         <v>strength</v>
@@ -33128,7 +32861,7 @@
         <v>facepull</v>
       </c>
       <c r="M435" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="N435" t="str">
         <v>strength</v>
@@ -34301,7 +34034,7 @@
         <v/>
       </c>
       <c r="L456" t="str">
-        <v>hack</v>
+        <v>c:fedb:Hack_Squat</v>
       </c>
       <c r="M456" t="str">
         <v>Hack Squat</v>
@@ -35368,7 +35101,7 @@
         <v>facepull</v>
       </c>
       <c r="M475" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="N475" t="str">
         <v>strength</v>
@@ -35981,7 +35714,7 @@
         <v/>
       </c>
       <c r="L486" t="str">
-        <v>hack</v>
+        <v>c:fedb:Hack_Squat</v>
       </c>
       <c r="M486" t="str">
         <v>Hack Squat</v>
@@ -36152,7 +35885,7 @@
         <v>facepull</v>
       </c>
       <c r="M489" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="N489" t="str">
         <v>strength</v>
@@ -37608,7 +37341,7 @@
         <v>facepull</v>
       </c>
       <c r="M515" t="str">
-        <v>Face Pull</v>
+        <v>Face Pulls</v>
       </c>
       <c r="N515" t="str">
         <v>strength</v>

--- a/iron-log.xlsx
+++ b/iron-log.xlsx
@@ -17,9 +17,9 @@
     <sheet name="Config" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$58</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$1:$J$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Sessions!$A$1:$O$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">Muscles!$A$1:$E$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">Weeks!$A$1:$H$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Body weight'!$A$1:$D$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5">Settings!$A$1:$B$44</definedName>
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'Program info'!$A$1:$B$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8">'Saved versions'!$A$1:$F$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9">Experiments!$A$1:$E$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$183</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10">'Check-offs'!$A$1:$D$178</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11">Config!$A$1:$B$16</definedName>
   </definedNames>
 </workbook>
@@ -422,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J25"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -534,167 +534,167 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Cable Wrist Pulldown</v>
+        <v>Canoe Stretch</v>
       </c>
       <c r="B4" t="str">
-        <v>Hypertrophy</v>
+        <v>Isometric</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-09-27</v>
+        <v>2026-10-05</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-05</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="H4">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>48</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Canoe Stretch</v>
+        <v>Clean Jerk &amp; Overhead Press</v>
       </c>
       <c r="B5" t="str">
-        <v>Isometric</v>
+        <v>Explosive</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-04</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>13.33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Clean Jerk &amp; Overhead Press</v>
+        <v>Close-Grip Front Lat Pulldown</v>
       </c>
       <c r="B6" t="str">
-        <v>Explosive</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-12</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-12</v>
       </c>
       <c r="F6">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
-        <v>45</v>
+      <c r="J6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Close-Grip Front Lat Pulldown</v>
+        <v>DB 6 Ways</v>
       </c>
       <c r="B7" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-05</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-05</v>
       </c>
       <c r="F7">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7" t="str">
-        <v/>
+      <c r="J7">
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>DB 6 Ways</v>
+        <v>Depth Drop → Broad Jump → Box Jump</v>
       </c>
       <c r="B8" t="str">
-        <v>Strength</v>
+        <v>Explosive</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-10-05</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>20</v>
+        <v>2026-10-04</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Depth Drop → Broad Jump → Box Jump</v>
+        <v>Duck Sled Push</v>
       </c>
       <c r="B9" t="str">
         <v>Explosive</v>
@@ -703,22 +703,22 @@
         <v>1</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-10</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v/>
+        <v>2026-10-10</v>
+      </c>
+      <c r="F9">
+        <v>20</v>
+      </c>
+      <c r="G9">
+        <v>20</v>
+      </c>
+      <c r="H9">
+        <v>20</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -726,28 +726,28 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Duck Sled Push</v>
+        <v>Dumbbell Bench Press</v>
       </c>
       <c r="B10" t="str">
-        <v>Explosive</v>
+        <v>Strength</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-10-10</v>
+        <v>2026-10-12</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-10-10</v>
+        <v>2026-10-12</v>
       </c>
       <c r="F10">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G10">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H10">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -758,191 +758,191 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Dumbbell Bench Press</v>
+        <v>Explosive Unilateral Cable Row</v>
       </c>
       <c r="B11" t="str">
-        <v>Strength</v>
+        <v>Explosive</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-10</v>
       </c>
       <c r="F11">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G11">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H11">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
-      <c r="J11" t="str">
-        <v/>
+      <c r="J11">
+        <v>70</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Explosive Unilateral Cable Row</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="B12" t="str">
-        <v>Explosive</v>
+        <v>Strength</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-10-04</v>
+        <v>2026-09-28</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-10-10</v>
+        <v>2026-10-07</v>
       </c>
       <c r="F12">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="G12">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="H12">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>70</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Face Pulls</v>
+        <v>Hack Squat</v>
       </c>
       <c r="B13" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-12</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-12</v>
       </c>
       <c r="F13">
-        <v>27</v>
+        <v>270</v>
       </c>
       <c r="G13">
-        <v>27</v>
+        <v>270</v>
       </c>
       <c r="H13">
-        <v>27</v>
+        <v>270</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
-      <c r="J13">
-        <v>50</v>
+      <c r="J13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Farmers Carry</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="B14" t="str">
         <v>Strength</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="E14" t="str">
         <v>2026-10-07</v>
       </c>
-      <c r="E14" t="str">
-        <v>2026-10-09</v>
-      </c>
       <c r="F14">
-        <v>40</v>
+        <v>320</v>
       </c>
       <c r="G14">
-        <v>40</v>
+        <v>320</v>
       </c>
       <c r="H14">
-        <v>40</v>
+        <v>320</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>65</v>
+        <v>375</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Grip Trainer</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="B15" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="E15" t="str">
         <v>2026-10-07</v>
       </c>
       <c r="F15">
-        <v>200</v>
+        <v>15</v>
       </c>
       <c r="G15">
-        <v>200</v>
+        <v>15</v>
       </c>
       <c r="H15">
-        <v>200</v>
+        <v>15</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>235</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Hack Squat</v>
+        <v>Lateral Bound / Skater Hop with Stick</v>
       </c>
       <c r="B16" t="str">
-        <v>Hypertrophy</v>
+        <v>Explosive</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-10-12</v>
-      </c>
-      <c r="F16">
-        <v>270</v>
-      </c>
-      <c r="G16">
-        <v>270</v>
-      </c>
-      <c r="H16">
-        <v>270</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
+        <v>2026-10-04</v>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -950,71 +950,71 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Hip Thrust</v>
+        <v>Plate Torso Rotation</v>
       </c>
       <c r="B17" t="str">
         <v>Strength</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-09-28</v>
+        <v>2026-10-05</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-05</v>
       </c>
       <c r="F17">
-        <v>320</v>
+        <v>10</v>
       </c>
       <c r="G17">
-        <v>320</v>
+        <v>10</v>
       </c>
       <c r="H17">
-        <v>320</v>
+        <v>10</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>375</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Pogo Hops</v>
       </c>
       <c r="B18" t="str">
-        <v>Isometric</v>
+        <v>Explosive</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-10-07</v>
-      </c>
-      <c r="F18">
-        <v>15</v>
-      </c>
-      <c r="G18">
-        <v>15</v>
-      </c>
-      <c r="H18">
-        <v>15</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>21</v>
+        <v>2026-10-04</v>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Kneeling Cable Ab Crunch</v>
+        <v>Seated Good Mornings</v>
       </c>
       <c r="B19" t="str">
         <v>Strength</v>
@@ -1023,86 +1023,86 @@
         <v>1</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-12</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-12</v>
       </c>
       <c r="F19">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G19">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H19">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
-      <c r="J19">
-        <v>100</v>
+      <c r="J19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Lateral Bound / Skater Hop with Stick</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="B20" t="str">
-        <v>Explosive</v>
+        <v>Strength</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-10-04</v>
+        <v>2026-09-27</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="F20" t="str">
-        <v/>
-      </c>
-      <c r="G20" t="str">
-        <v/>
-      </c>
-      <c r="H20" t="str">
-        <v/>
-      </c>
-      <c r="I20" t="str">
-        <v/>
-      </c>
-      <c r="J20" t="str">
-        <v/>
+        <v>2026-10-08</v>
+      </c>
+      <c r="F20">
+        <v>50</v>
+      </c>
+      <c r="G20">
+        <v>50</v>
+      </c>
+      <c r="H20">
+        <v>50</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>80</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Leg Extension ISO hold</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="B21" t="str">
         <v>Isometric</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-27</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-12</v>
       </c>
       <c r="F21">
         <v>50</v>
       </c>
       <c r="G21">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H21">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>65</v>
@@ -1110,39 +1110,39 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Overhead Tricep Extension</v>
+        <v>Split Squat Jumps</v>
       </c>
       <c r="B22" t="str">
-        <v>Strength</v>
+        <v>Explosive</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-04</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-10-07</v>
-      </c>
-      <c r="F22">
-        <v>17</v>
-      </c>
-      <c r="G22">
-        <v>17</v>
-      </c>
-      <c r="H22">
-        <v>17</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>30</v>
+        <v>2026-10-04</v>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Plate Torso Rotation</v>
+        <v>Suitcase Bottom-Up, single-arm</v>
       </c>
       <c r="B23" t="str">
         <v>Strength</v>
@@ -1151,19 +1151,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-10-05</v>
+        <v>2026-09-29</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-10-05</v>
+        <v>2026-09-29</v>
       </c>
       <c r="F23">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G23">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H23">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1174,31 +1174,31 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Pogo Hops</v>
+        <v>Thigh Abductor</v>
       </c>
       <c r="B24" t="str">
-        <v>Explosive</v>
+        <v>Strength</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-12</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="F24" t="str">
-        <v/>
-      </c>
-      <c r="G24" t="str">
-        <v/>
-      </c>
-      <c r="H24" t="str">
-        <v/>
-      </c>
-      <c r="I24" t="str">
-        <v/>
+        <v>2026-10-12</v>
+      </c>
+      <c r="F24">
+        <v>180</v>
+      </c>
+      <c r="G24">
+        <v>180</v>
+      </c>
+      <c r="H24">
+        <v>180</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
       </c>
       <c r="J24" t="str">
         <v/>
@@ -1206,7 +1206,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Prone Leg Curl</v>
+        <v>Thigh Adductor</v>
       </c>
       <c r="B25" t="str">
         <v>Strength</v>
@@ -1215,351 +1215,31 @@
         <v>1</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-10-09</v>
+        <v>2026-10-12</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-10-09</v>
+        <v>2026-10-12</v>
       </c>
       <c r="F25">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="G25">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="H25">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
-      <c r="J25">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Seated Cable Crunch</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="D26" t="str">
-        <v>2026-10-07</v>
-      </c>
-      <c r="E26" t="str">
-        <v>2026-10-08</v>
-      </c>
-      <c r="F26">
-        <v>44</v>
-      </c>
-      <c r="G26">
-        <v>44</v>
-      </c>
-      <c r="H26">
-        <v>44</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>Seated Good Mornings</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27" t="str">
-        <v>2026-10-12</v>
-      </c>
-      <c r="E27" t="str">
-        <v>2026-10-12</v>
-      </c>
-      <c r="F27">
-        <v>45</v>
-      </c>
-      <c r="G27">
-        <v>45</v>
-      </c>
-      <c r="H27">
-        <v>45</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Seated Zercher Good Morning</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="C28">
-        <v>6</v>
-      </c>
-      <c r="D28" t="str">
-        <v>2026-09-27</v>
-      </c>
-      <c r="E28" t="str">
-        <v>2026-10-08</v>
-      </c>
-      <c r="F28">
-        <v>50</v>
-      </c>
-      <c r="G28">
-        <v>50</v>
-      </c>
-      <c r="H28">
-        <v>50</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>Side Rear Delt Fly</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Isometric</v>
-      </c>
-      <c r="C29">
-        <v>4</v>
-      </c>
-      <c r="D29" t="str">
-        <v>2026-09-27</v>
-      </c>
-      <c r="E29" t="str">
-        <v>2026-10-12</v>
-      </c>
-      <c r="F29">
-        <v>50</v>
-      </c>
-      <c r="G29">
-        <v>60</v>
-      </c>
-      <c r="H29">
-        <v>60</v>
-      </c>
-      <c r="I29">
-        <v>10</v>
-      </c>
-      <c r="J29">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>Sled push → pull</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Explosive</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="E30" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="F30" t="str">
-        <v/>
-      </c>
-      <c r="G30" t="str">
-        <v/>
-      </c>
-      <c r="H30" t="str">
-        <v/>
-      </c>
-      <c r="I30" t="str">
-        <v/>
-      </c>
-      <c r="J30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>Split Squat Jumps</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Explosive</v>
-      </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="E31" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="F31" t="str">
-        <v/>
-      </c>
-      <c r="G31" t="str">
-        <v/>
-      </c>
-      <c r="H31" t="str">
-        <v/>
-      </c>
-      <c r="I31" t="str">
-        <v/>
-      </c>
-      <c r="J31" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>Suitcase Bottom-Up, single-arm</v>
-      </c>
-      <c r="B32" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-      <c r="D32" t="str">
-        <v>2026-09-29</v>
-      </c>
-      <c r="E32" t="str">
-        <v>2026-09-29</v>
-      </c>
-      <c r="F32">
-        <v>25</v>
-      </c>
-      <c r="G32">
-        <v>25</v>
-      </c>
-      <c r="H32">
-        <v>25</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>Thigh Abductor</v>
-      </c>
-      <c r="B33" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33" t="str">
-        <v>2026-10-12</v>
-      </c>
-      <c r="E33" t="str">
-        <v>2026-10-12</v>
-      </c>
-      <c r="F33">
-        <v>180</v>
-      </c>
-      <c r="G33">
-        <v>180</v>
-      </c>
-      <c r="H33">
-        <v>180</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>Thigh Adductor</v>
-      </c>
-      <c r="B34" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34" t="str">
-        <v>2026-10-12</v>
-      </c>
-      <c r="E34" t="str">
-        <v>2026-10-12</v>
-      </c>
-      <c r="F34">
-        <v>140</v>
-      </c>
-      <c r="G34">
-        <v>140</v>
-      </c>
-      <c r="H34">
-        <v>140</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>Zottman Curls</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Hypertrophy</v>
-      </c>
-      <c r="C35">
-        <v>2</v>
-      </c>
-      <c r="D35" t="str">
-        <v>2026-09-29</v>
-      </c>
-      <c r="E35" t="str">
-        <v>2026-10-07</v>
-      </c>
-      <c r="F35">
-        <v>15</v>
-      </c>
-      <c r="G35">
-        <v>15</v>
-      </c>
-      <c r="H35">
-        <v>15</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>23</v>
+      <c r="J25" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J35"/>
+  <autoFilter ref="A1:J25"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J25"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1772,7 +1452,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D183"/>
+  <dimension ref="A1:D178"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.83203125" customWidth="1"/>
@@ -2068,7 +1748,7 @@
         <v>done</v>
       </c>
       <c r="C21" t="str">
-        <v>A-d4s4</v>
+        <v>A-d4s5</v>
       </c>
       <c r="D21" t="str">
         <v>Yes</v>
@@ -2082,7 +1762,7 @@
         <v>done</v>
       </c>
       <c r="C22" t="str">
-        <v>A-d4s5</v>
+        <v>A-d5s3</v>
       </c>
       <c r="D22" t="str">
         <v>Yes</v>
@@ -2096,7 +1776,7 @@
         <v>done</v>
       </c>
       <c r="C23" t="str">
-        <v>A-d5s3</v>
+        <v>A-d2s2#0</v>
       </c>
       <c r="D23" t="str">
         <v>Yes</v>
@@ -2110,7 +1790,7 @@
         <v>done</v>
       </c>
       <c r="C24" t="str">
-        <v>A-d6s5</v>
+        <v>A-d3s6#0</v>
       </c>
       <c r="D24" t="str">
         <v>Yes</v>
@@ -2124,7 +1804,7 @@
         <v>done</v>
       </c>
       <c r="C25" t="str">
-        <v>A-d2s2#0</v>
+        <v>A-d4s4#1</v>
       </c>
       <c r="D25" t="str">
         <v>Yes</v>
@@ -2138,7 +1818,7 @@
         <v>done</v>
       </c>
       <c r="C26" t="str">
-        <v>A-d3s6#0</v>
+        <v>A-d6s5#1</v>
       </c>
       <c r="D26" t="str">
         <v>Yes</v>
@@ -2667,13 +2347,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B64" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C64" t="str">
-        <v>A-d1s7</v>
-      </c>
-      <c r="D64">
-        <v>3</v>
+        <v>A-d4s4</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="65">
@@ -2681,13 +2361,13 @@
         <v>2026-09-27</v>
       </c>
       <c r="B65" t="str">
-        <v>moved</v>
+        <v>skipped</v>
       </c>
       <c r="C65" t="str">
-        <v>A-d2s1</v>
-      </c>
-      <c r="D65">
-        <v>5</v>
+        <v>A-d6s5</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="66">
@@ -2698,7 +2378,7 @@
         <v>moved</v>
       </c>
       <c r="C66" t="str">
-        <v>A-d2s4</v>
+        <v>A-d1s7</v>
       </c>
       <c r="D66">
         <v>3</v>
@@ -2712,10 +2392,10 @@
         <v>moved</v>
       </c>
       <c r="C67" t="str">
-        <v>A-d3s1</v>
+        <v>A-d2s1</v>
       </c>
       <c r="D67">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -2726,10 +2406,10 @@
         <v>moved</v>
       </c>
       <c r="C68" t="str">
-        <v>A-d3s2</v>
+        <v>A-d2s4</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -2740,10 +2420,10 @@
         <v>moved</v>
       </c>
       <c r="C69" t="str">
-        <v>A-d3s3</v>
+        <v>A-d3s1</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -2754,10 +2434,10 @@
         <v>moved</v>
       </c>
       <c r="C70" t="str">
-        <v>A-d3s6</v>
+        <v>A-d3s2</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2768,10 +2448,10 @@
         <v>moved</v>
       </c>
       <c r="C71" t="str">
-        <v>A-d4s6</v>
+        <v>A-d3s3</v>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -2782,10 +2462,10 @@
         <v>moved</v>
       </c>
       <c r="C72" t="str">
-        <v>A-d5s1</v>
+        <v>A-d3s6</v>
       </c>
       <c r="D72">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -2796,10 +2476,10 @@
         <v>moved</v>
       </c>
       <c r="C73" t="str">
-        <v>A-d5s2</v>
+        <v>A-d4s6</v>
       </c>
       <c r="D73">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -2810,7 +2490,7 @@
         <v>moved</v>
       </c>
       <c r="C74" t="str">
-        <v>A-d5s4</v>
+        <v>A-d5s1</v>
       </c>
       <c r="D74">
         <v>6</v>
@@ -2824,7 +2504,7 @@
         <v>moved</v>
       </c>
       <c r="C75" t="str">
-        <v>A-d5s5</v>
+        <v>A-d5s2</v>
       </c>
       <c r="D75">
         <v>6</v>
@@ -2838,7 +2518,7 @@
         <v>moved</v>
       </c>
       <c r="C76" t="str">
-        <v>A-d5s6</v>
+        <v>A-d5s4</v>
       </c>
       <c r="D76">
         <v>6</v>
@@ -2852,7 +2532,7 @@
         <v>moved</v>
       </c>
       <c r="C77" t="str">
-        <v>A-d5s7</v>
+        <v>A-d5s5</v>
       </c>
       <c r="D77">
         <v>6</v>
@@ -2866,7 +2546,7 @@
         <v>moved</v>
       </c>
       <c r="C78" t="str">
-        <v>A-d5s8</v>
+        <v>A-d5s6</v>
       </c>
       <c r="D78">
         <v>6</v>
@@ -2880,38 +2560,38 @@
         <v>moved</v>
       </c>
       <c r="C79" t="str">
-        <v>A-d6s5</v>
+        <v>A-d5s7</v>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2026-10-04</v>
+        <v>2026-09-27</v>
       </c>
       <c r="B80" t="str">
-        <v>ran</v>
+        <v>moved</v>
       </c>
       <c r="C80" t="str">
-        <v/>
-      </c>
-      <c r="D80" t="str">
-        <v>B</v>
+        <v>A-d5s8</v>
+      </c>
+      <c r="D80">
+        <v>6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2026-10-04</v>
+        <v>2026-09-27</v>
       </c>
       <c r="B81" t="str">
-        <v>rest</v>
+        <v>moved</v>
       </c>
       <c r="C81" t="str">
-        <v/>
-      </c>
-      <c r="D81" t="str">
-        <v>3</v>
+        <v>A-d6s5</v>
+      </c>
+      <c r="D81">
+        <v>5</v>
       </c>
     </row>
     <row r="82">
@@ -2919,13 +2599,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B82" t="str">
-        <v>restOn</v>
+        <v>ran</v>
       </c>
       <c r="C82" t="str">
         <v/>
       </c>
       <c r="D82" t="str">
-        <v>2026-10-06</v>
+        <v>B</v>
       </c>
     </row>
     <row r="83">
@@ -2933,13 +2613,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B83" t="str">
-        <v>order</v>
+        <v>rest</v>
       </c>
       <c r="C83" t="str">
         <v/>
       </c>
       <c r="D83" t="str">
-        <v>6 1 2 3 4 5 7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -2947,13 +2627,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B84" t="str">
-        <v>extra</v>
+        <v>restOn</v>
       </c>
       <c r="C84" t="str">
-        <v>X-muy8rvy9whc0</v>
+        <v/>
       </c>
       <c r="D84" t="str">
-        <v>{"id":"X-muy8rvy9whc0","day":3,"ex":"duck-sled-push","ph":"strength","note":""}</v>
+        <v>2026-10-06</v>
       </c>
     </row>
     <row r="85">
@@ -2961,13 +2641,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B85" t="str">
-        <v>done</v>
+        <v>order</v>
       </c>
       <c r="C85" t="str">
-        <v>B-d1s1</v>
+        <v/>
       </c>
       <c r="D85" t="str">
-        <v>Yes</v>
+        <v>6 1 2 3 4 5 7</v>
       </c>
     </row>
     <row r="86">
@@ -2978,7 +2658,7 @@
         <v>done</v>
       </c>
       <c r="C86" t="str">
-        <v>B-d1s2</v>
+        <v>B-d1s1</v>
       </c>
       <c r="D86" t="str">
         <v>Yes</v>
@@ -2992,7 +2672,7 @@
         <v>done</v>
       </c>
       <c r="C87" t="str">
-        <v>B-d1s3</v>
+        <v>B-d1s2</v>
       </c>
       <c r="D87" t="str">
         <v>Yes</v>
@@ -3006,7 +2686,7 @@
         <v>done</v>
       </c>
       <c r="C88" t="str">
-        <v>B-d1s4</v>
+        <v>B-d1s3</v>
       </c>
       <c r="D88" t="str">
         <v>Yes</v>
@@ -3020,7 +2700,7 @@
         <v>done</v>
       </c>
       <c r="C89" t="str">
-        <v>B-d1s5</v>
+        <v>B-d1s4</v>
       </c>
       <c r="D89" t="str">
         <v>Yes</v>
@@ -3034,7 +2714,7 @@
         <v>done</v>
       </c>
       <c r="C90" t="str">
-        <v>B-d1s6</v>
+        <v>B-d1s5</v>
       </c>
       <c r="D90" t="str">
         <v>Yes</v>
@@ -3048,7 +2728,7 @@
         <v>done</v>
       </c>
       <c r="C91" t="str">
-        <v>B-d1s8</v>
+        <v>B-d1s6</v>
       </c>
       <c r="D91" t="str">
         <v>Yes</v>
@@ -3062,7 +2742,7 @@
         <v>done</v>
       </c>
       <c r="C92" t="str">
-        <v>B-d1s9</v>
+        <v>B-d1s8</v>
       </c>
       <c r="D92" t="str">
         <v>Yes</v>
@@ -3076,7 +2756,7 @@
         <v>done</v>
       </c>
       <c r="C93" t="str">
-        <v>B-d2s1</v>
+        <v>B-d1s9</v>
       </c>
       <c r="D93" t="str">
         <v>Yes</v>
@@ -3090,7 +2770,7 @@
         <v>done</v>
       </c>
       <c r="C94" t="str">
-        <v>B-d2s2</v>
+        <v>B-d2s1</v>
       </c>
       <c r="D94" t="str">
         <v>Yes</v>
@@ -3104,7 +2784,7 @@
         <v>done</v>
       </c>
       <c r="C95" t="str">
-        <v>B-d2s3</v>
+        <v>B-d2s2</v>
       </c>
       <c r="D95" t="str">
         <v>Yes</v>
@@ -3118,7 +2798,7 @@
         <v>done</v>
       </c>
       <c r="C96" t="str">
-        <v>B-d2s4</v>
+        <v>B-d2s3</v>
       </c>
       <c r="D96" t="str">
         <v>Yes</v>
@@ -3132,7 +2812,7 @@
         <v>done</v>
       </c>
       <c r="C97" t="str">
-        <v>B-d2s5</v>
+        <v>B-d2s4</v>
       </c>
       <c r="D97" t="str">
         <v>Yes</v>
@@ -3146,7 +2826,7 @@
         <v>done</v>
       </c>
       <c r="C98" t="str">
-        <v>B-d2s7</v>
+        <v>B-d2s5</v>
       </c>
       <c r="D98" t="str">
         <v>Yes</v>
@@ -3160,7 +2840,7 @@
         <v>done</v>
       </c>
       <c r="C99" t="str">
-        <v>B-d2s8</v>
+        <v>B-d2s7</v>
       </c>
       <c r="D99" t="str">
         <v>Yes</v>
@@ -3174,7 +2854,7 @@
         <v>done</v>
       </c>
       <c r="C100" t="str">
-        <v>B-d3s1</v>
+        <v>B-d2s8</v>
       </c>
       <c r="D100" t="str">
         <v>Yes</v>
@@ -3188,7 +2868,7 @@
         <v>done</v>
       </c>
       <c r="C101" t="str">
-        <v>B-d3s2</v>
+        <v>B-d3s1</v>
       </c>
       <c r="D101" t="str">
         <v>Yes</v>
@@ -3202,7 +2882,7 @@
         <v>done</v>
       </c>
       <c r="C102" t="str">
-        <v>B-d3s6</v>
+        <v>B-d3s2</v>
       </c>
       <c r="D102" t="str">
         <v>Yes</v>
@@ -3216,7 +2896,7 @@
         <v>done</v>
       </c>
       <c r="C103" t="str">
-        <v>B-d4s1</v>
+        <v>B-d3s6</v>
       </c>
       <c r="D103" t="str">
         <v>Yes</v>
@@ -3230,7 +2910,7 @@
         <v>done</v>
       </c>
       <c r="C104" t="str">
-        <v>B-d4s2</v>
+        <v>B-d4s1</v>
       </c>
       <c r="D104" t="str">
         <v>Yes</v>
@@ -3244,7 +2924,7 @@
         <v>done</v>
       </c>
       <c r="C105" t="str">
-        <v>B-d4s3</v>
+        <v>B-d4s2</v>
       </c>
       <c r="D105" t="str">
         <v>Yes</v>
@@ -3258,7 +2938,7 @@
         <v>done</v>
       </c>
       <c r="C106" t="str">
-        <v>B-d4s4</v>
+        <v>B-d4s3</v>
       </c>
       <c r="D106" t="str">
         <v>Yes</v>
@@ -3272,7 +2952,7 @@
         <v>done</v>
       </c>
       <c r="C107" t="str">
-        <v>B-d4s6</v>
+        <v>B-d4s4</v>
       </c>
       <c r="D107" t="str">
         <v>Yes</v>
@@ -3286,7 +2966,7 @@
         <v>done</v>
       </c>
       <c r="C108" t="str">
-        <v>B-d5s2</v>
+        <v>B-d4s6</v>
       </c>
       <c r="D108" t="str">
         <v>Yes</v>
@@ -3300,7 +2980,7 @@
         <v>done</v>
       </c>
       <c r="C109" t="str">
-        <v>B-d5s3</v>
+        <v>B-d5s2</v>
       </c>
       <c r="D109" t="str">
         <v>Yes</v>
@@ -3314,7 +2994,7 @@
         <v>done</v>
       </c>
       <c r="C110" t="str">
-        <v>B-d6s1</v>
+        <v>B-d5s3</v>
       </c>
       <c r="D110" t="str">
         <v>Yes</v>
@@ -3328,7 +3008,7 @@
         <v>done</v>
       </c>
       <c r="C111" t="str">
-        <v>B-d6s2</v>
+        <v>B-d6s1</v>
       </c>
       <c r="D111" t="str">
         <v>Yes</v>
@@ -3342,7 +3022,7 @@
         <v>done</v>
       </c>
       <c r="C112" t="str">
-        <v>B-d6s3</v>
+        <v>B-d6s2</v>
       </c>
       <c r="D112" t="str">
         <v>Yes</v>
@@ -3356,7 +3036,7 @@
         <v>done</v>
       </c>
       <c r="C113" t="str">
-        <v>B-d6s4</v>
+        <v>B-d6s3</v>
       </c>
       <c r="D113" t="str">
         <v>Yes</v>
@@ -3370,7 +3050,7 @@
         <v>done</v>
       </c>
       <c r="C114" t="str">
-        <v>B-d6s6</v>
+        <v>B-d6s4</v>
       </c>
       <c r="D114" t="str">
         <v>Yes</v>
@@ -3384,7 +3064,7 @@
         <v>done</v>
       </c>
       <c r="C115" t="str">
-        <v>B-d1s10</v>
+        <v>B-d6s6</v>
       </c>
       <c r="D115" t="str">
         <v>Yes</v>
@@ -3398,7 +3078,7 @@
         <v>done</v>
       </c>
       <c r="C116" t="str">
-        <v>B-d1s11</v>
+        <v>B-d1s10</v>
       </c>
       <c r="D116" t="str">
         <v>Yes</v>
@@ -3412,7 +3092,7 @@
         <v>done</v>
       </c>
       <c r="C117" t="str">
-        <v>B-sled6</v>
+        <v>B-d1s11</v>
       </c>
       <c r="D117" t="str">
         <v>Yes</v>
@@ -3426,7 +3106,7 @@
         <v>done</v>
       </c>
       <c r="C118" t="str">
-        <v>B-d2s1#0</v>
+        <v>B-sled6</v>
       </c>
       <c r="D118" t="str">
         <v>Yes</v>
@@ -3440,7 +3120,7 @@
         <v>done</v>
       </c>
       <c r="C119" t="str">
-        <v>B-d2s3#1</v>
+        <v>B-d2s1#0</v>
       </c>
       <c r="D119" t="str">
         <v>Yes</v>
@@ -3454,7 +3134,7 @@
         <v>done</v>
       </c>
       <c r="C120" t="str">
-        <v>B-d4s1#0</v>
+        <v>B-d2s3#1</v>
       </c>
       <c r="D120" t="str">
         <v>Yes</v>
@@ -3468,7 +3148,7 @@
         <v>done</v>
       </c>
       <c r="C121" t="str">
-        <v>B-d4s5#1</v>
+        <v>B-d4s1#0</v>
       </c>
       <c r="D121" t="str">
         <v>Yes</v>
@@ -3482,7 +3162,7 @@
         <v>done</v>
       </c>
       <c r="C122" t="str">
-        <v>B-d5s3#0</v>
+        <v>B-d4s5#1</v>
       </c>
       <c r="D122" t="str">
         <v>Yes</v>
@@ -3496,7 +3176,7 @@
         <v>done</v>
       </c>
       <c r="C123" t="str">
-        <v>Pa2gom-d1s2</v>
+        <v>B-d5s3#0</v>
       </c>
       <c r="D123" t="str">
         <v>Yes</v>
@@ -3524,7 +3204,7 @@
         <v>done</v>
       </c>
       <c r="C125" t="str">
-        <v>X-muy8rvy9whc0</v>
+        <v>B-xmuy1nsai5fs#0</v>
       </c>
       <c r="D125" t="str">
         <v>Yes</v>
@@ -3535,10 +3215,10 @@
         <v>2026-10-04</v>
       </c>
       <c r="B126" t="str">
-        <v>done</v>
+        <v>skipped</v>
       </c>
       <c r="C126" t="str">
-        <v>B-xmuy1nsai5fs#0</v>
+        <v>B-d1s7</v>
       </c>
       <c r="D126" t="str">
         <v>Yes</v>
@@ -3552,7 +3232,7 @@
         <v>skipped</v>
       </c>
       <c r="C127" t="str">
-        <v>B-d1s7</v>
+        <v>B-d2s6</v>
       </c>
       <c r="D127" t="str">
         <v>Yes</v>
@@ -3566,7 +3246,7 @@
         <v>skipped</v>
       </c>
       <c r="C128" t="str">
-        <v>B-d2s6</v>
+        <v>B-d3s4</v>
       </c>
       <c r="D128" t="str">
         <v>Yes</v>
@@ -3580,7 +3260,7 @@
         <v>skipped</v>
       </c>
       <c r="C129" t="str">
-        <v>B-d3s4</v>
+        <v>B-d3s5</v>
       </c>
       <c r="D129" t="str">
         <v>Yes</v>
@@ -3594,7 +3274,7 @@
         <v>skipped</v>
       </c>
       <c r="C130" t="str">
-        <v>B-d3s5</v>
+        <v>B-d3s7</v>
       </c>
       <c r="D130" t="str">
         <v>Yes</v>
@@ -3608,7 +3288,7 @@
         <v>skipped</v>
       </c>
       <c r="C131" t="str">
-        <v>B-d3s7</v>
+        <v>B-d3s8</v>
       </c>
       <c r="D131" t="str">
         <v>Yes</v>
@@ -3622,7 +3302,7 @@
         <v>skipped</v>
       </c>
       <c r="C132" t="str">
-        <v>B-d3s8</v>
+        <v>B-d4s5</v>
       </c>
       <c r="D132" t="str">
         <v>Yes</v>
@@ -3636,7 +3316,7 @@
         <v>skipped</v>
       </c>
       <c r="C133" t="str">
-        <v>B-d4s5</v>
+        <v>B-d4s7</v>
       </c>
       <c r="D133" t="str">
         <v>Yes</v>
@@ -3650,7 +3330,7 @@
         <v>skipped</v>
       </c>
       <c r="C134" t="str">
-        <v>B-d4s7</v>
+        <v>B-d4s8</v>
       </c>
       <c r="D134" t="str">
         <v>Yes</v>
@@ -3664,7 +3344,7 @@
         <v>skipped</v>
       </c>
       <c r="C135" t="str">
-        <v>B-d4s8</v>
+        <v>B-d4s9</v>
       </c>
       <c r="D135" t="str">
         <v>Yes</v>
@@ -3678,7 +3358,7 @@
         <v>skipped</v>
       </c>
       <c r="C136" t="str">
-        <v>B-d4s9</v>
+        <v>B-d5s4</v>
       </c>
       <c r="D136" t="str">
         <v>Yes</v>
@@ -3692,7 +3372,7 @@
         <v>skipped</v>
       </c>
       <c r="C137" t="str">
-        <v>B-d5s4</v>
+        <v>B-d5s5</v>
       </c>
       <c r="D137" t="str">
         <v>Yes</v>
@@ -3706,7 +3386,7 @@
         <v>skipped</v>
       </c>
       <c r="C138" t="str">
-        <v>B-d5s5</v>
+        <v>B-d5s6</v>
       </c>
       <c r="D138" t="str">
         <v>Yes</v>
@@ -3720,7 +3400,7 @@
         <v>skipped</v>
       </c>
       <c r="C139" t="str">
-        <v>B-d5s6</v>
+        <v>B-d5s7</v>
       </c>
       <c r="D139" t="str">
         <v>Yes</v>
@@ -3734,7 +3414,7 @@
         <v>skipped</v>
       </c>
       <c r="C140" t="str">
-        <v>B-d5s7</v>
+        <v>B-d5s8</v>
       </c>
       <c r="D140" t="str">
         <v>Yes</v>
@@ -3748,7 +3428,7 @@
         <v>skipped</v>
       </c>
       <c r="C141" t="str">
-        <v>B-d5s8</v>
+        <v>B-d5s9</v>
       </c>
       <c r="D141" t="str">
         <v>Yes</v>
@@ -3762,7 +3442,7 @@
         <v>skipped</v>
       </c>
       <c r="C142" t="str">
-        <v>B-d5s9</v>
+        <v>B-d6s5</v>
       </c>
       <c r="D142" t="str">
         <v>Yes</v>
@@ -3776,7 +3456,7 @@
         <v>skipped</v>
       </c>
       <c r="C143" t="str">
-        <v>B-d6s5</v>
+        <v>B-sled1</v>
       </c>
       <c r="D143" t="str">
         <v>Yes</v>
@@ -3790,7 +3470,7 @@
         <v>skipped</v>
       </c>
       <c r="C144" t="str">
-        <v>B-sled1</v>
+        <v>B-sled2</v>
       </c>
       <c r="D144" t="str">
         <v>Yes</v>
@@ -3804,7 +3484,7 @@
         <v>skipped</v>
       </c>
       <c r="C145" t="str">
-        <v>B-sled2</v>
+        <v>B-sled3</v>
       </c>
       <c r="D145" t="str">
         <v>Yes</v>
@@ -3818,7 +3498,7 @@
         <v>skipped</v>
       </c>
       <c r="C146" t="str">
-        <v>B-sled3</v>
+        <v>B-sled4</v>
       </c>
       <c r="D146" t="str">
         <v>Yes</v>
@@ -3832,7 +3512,7 @@
         <v>skipped</v>
       </c>
       <c r="C147" t="str">
-        <v>B-sled4</v>
+        <v>B-sled5</v>
       </c>
       <c r="D147" t="str">
         <v>Yes</v>
@@ -3846,7 +3526,7 @@
         <v>skipped</v>
       </c>
       <c r="C148" t="str">
-        <v>B-sled5</v>
+        <v>Pa2gom-d6s1</v>
       </c>
       <c r="D148" t="str">
         <v>Yes</v>
@@ -3860,7 +3540,7 @@
         <v>skipped</v>
       </c>
       <c r="C149" t="str">
-        <v>Pa2gom-d1s1</v>
+        <v>B-xmuy1nsai5fs</v>
       </c>
       <c r="D149" t="str">
         <v>Yes</v>
@@ -3874,7 +3554,7 @@
         <v>skipped</v>
       </c>
       <c r="C150" t="str">
-        <v>Pa2gom-d1s3</v>
+        <v>B-xmv2inqvwi0q</v>
       </c>
       <c r="D150" t="str">
         <v>Yes</v>
@@ -3885,13 +3565,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B151" t="str">
-        <v>skipped</v>
+        <v>moved</v>
       </c>
       <c r="C151" t="str">
-        <v>Pa2gom-d6s1</v>
-      </c>
-      <c r="D151" t="str">
-        <v>Yes</v>
+        <v>B-d1s3</v>
+      </c>
+      <c r="D151">
+        <v>6</v>
       </c>
     </row>
     <row r="152">
@@ -3899,13 +3579,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B152" t="str">
-        <v>skipped</v>
+        <v>moved</v>
       </c>
       <c r="C152" t="str">
-        <v>B-xmuy1nsai5fs</v>
-      </c>
-      <c r="D152" t="str">
-        <v>Yes</v>
+        <v>B-d1s5</v>
+      </c>
+      <c r="D152">
+        <v>3</v>
       </c>
     </row>
     <row r="153">
@@ -3913,13 +3593,13 @@
         <v>2026-10-04</v>
       </c>
       <c r="B153" t="str">
-        <v>skipped</v>
+        <v>moved</v>
       </c>
       <c r="C153" t="str">
-        <v>B-xmv2inqvwi0q</v>
-      </c>
-      <c r="D153" t="str">
-        <v>Yes</v>
+        <v>B-d1s9</v>
+      </c>
+      <c r="D153">
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -3930,10 +3610,10 @@
         <v>moved</v>
       </c>
       <c r="C154" t="str">
-        <v>B-d1s3</v>
+        <v>B-d2s8</v>
       </c>
       <c r="D154">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -3944,10 +3624,10 @@
         <v>moved</v>
       </c>
       <c r="C155" t="str">
-        <v>B-d1s5</v>
+        <v>B-d3s6</v>
       </c>
       <c r="D155">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156">
@@ -3958,10 +3638,10 @@
         <v>moved</v>
       </c>
       <c r="C156" t="str">
-        <v>B-d1s9</v>
+        <v>B-d4s3</v>
       </c>
       <c r="D156">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
@@ -3972,10 +3652,10 @@
         <v>moved</v>
       </c>
       <c r="C157" t="str">
-        <v>B-d2s8</v>
+        <v>B-d4s4</v>
       </c>
       <c r="D157">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158">
@@ -3986,7 +3666,7 @@
         <v>moved</v>
       </c>
       <c r="C158" t="str">
-        <v>B-d3s6</v>
+        <v>B-d4s5</v>
       </c>
       <c r="D158">
         <v>5</v>
@@ -4000,10 +3680,10 @@
         <v>moved</v>
       </c>
       <c r="C159" t="str">
-        <v>B-d4s3</v>
+        <v>B-d5s2</v>
       </c>
       <c r="D159">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="160">
@@ -4014,10 +3694,10 @@
         <v>moved</v>
       </c>
       <c r="C160" t="str">
-        <v>B-d4s4</v>
+        <v>B-d5s3</v>
       </c>
       <c r="D160">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161">
@@ -4028,80 +3708,80 @@
         <v>moved</v>
       </c>
       <c r="C161" t="str">
-        <v>B-d4s5</v>
+        <v>B-xmuy1rdg3uct</v>
       </c>
       <c r="D161">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-11</v>
       </c>
       <c r="B162" t="str">
-        <v>moved</v>
+        <v>ran</v>
       </c>
       <c r="C162" t="str">
-        <v>B-d5s2</v>
-      </c>
-      <c r="D162">
-        <v>6</v>
+        <v/>
+      </c>
+      <c r="D162" t="str">
+        <v>B</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-11</v>
       </c>
       <c r="B163" t="str">
-        <v>moved</v>
+        <v>rest</v>
       </c>
       <c r="C163" t="str">
-        <v>B-d5s3</v>
-      </c>
-      <c r="D163">
-        <v>4</v>
+        <v/>
+      </c>
+      <c r="D163" t="str">
+        <v>1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-11</v>
       </c>
       <c r="B164" t="str">
-        <v>moved</v>
+        <v>restOn</v>
       </c>
       <c r="C164" t="str">
-        <v>B-xmuy1rdg3uct</v>
-      </c>
-      <c r="D164">
-        <v>3</v>
+        <v/>
+      </c>
+      <c r="D164" t="str">
+        <v>2026-10-11</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-11</v>
       </c>
       <c r="B165" t="str">
-        <v>moved</v>
+        <v>done</v>
       </c>
       <c r="C165" t="str">
-        <v>X-muy8rvy9whc0</v>
-      </c>
-      <c r="D165">
-        <v>5</v>
+        <v>Pa2gom-d1s2</v>
+      </c>
+      <c r="D165" t="str">
+        <v>Yes</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-11</v>
       </c>
       <c r="B166" t="str">
-        <v>phase</v>
+        <v>done</v>
       </c>
       <c r="C166" t="str">
-        <v>X-muy8rvy9whc0:0</v>
+        <v>Pa2gom-d1s4</v>
       </c>
       <c r="D166" t="str">
-        <v>exp</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="167">
@@ -4109,13 +3789,13 @@
         <v>2026-10-11</v>
       </c>
       <c r="B167" t="str">
-        <v>ran</v>
+        <v>done</v>
       </c>
       <c r="C167" t="str">
-        <v/>
+        <v>Pa2gom-d1s5</v>
       </c>
       <c r="D167" t="str">
-        <v>B</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="168">
@@ -4123,13 +3803,13 @@
         <v>2026-10-11</v>
       </c>
       <c r="B168" t="str">
-        <v>rest</v>
+        <v>done</v>
       </c>
       <c r="C168" t="str">
-        <v/>
+        <v>Pa2gom-d1s7</v>
       </c>
       <c r="D168" t="str">
-        <v>1</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="169">
@@ -4137,13 +3817,13 @@
         <v>2026-10-11</v>
       </c>
       <c r="B169" t="str">
-        <v>restOn</v>
+        <v>done</v>
       </c>
       <c r="C169" t="str">
-        <v/>
+        <v>Pa2gom-d1s9</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-10-11</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="170">
@@ -4154,7 +3834,7 @@
         <v>done</v>
       </c>
       <c r="C170" t="str">
-        <v>Pa2gom-d1s2</v>
+        <v>Pa2gom-d2s4</v>
       </c>
       <c r="D170" t="str">
         <v>Yes</v>
@@ -4168,7 +3848,7 @@
         <v>done</v>
       </c>
       <c r="C171" t="str">
-        <v>Pa2gom-d1s4</v>
+        <v>Pa2gom-d2s4#0</v>
       </c>
       <c r="D171" t="str">
         <v>Yes</v>
@@ -4179,10 +3859,10 @@
         <v>2026-10-11</v>
       </c>
       <c r="B172" t="str">
-        <v>done</v>
+        <v>skipped</v>
       </c>
       <c r="C172" t="str">
-        <v>Pa2gom-d1s5</v>
+        <v>Pa2gom-d1s1</v>
       </c>
       <c r="D172" t="str">
         <v>Yes</v>
@@ -4193,10 +3873,10 @@
         <v>2026-10-11</v>
       </c>
       <c r="B173" t="str">
-        <v>done</v>
+        <v>skipped</v>
       </c>
       <c r="C173" t="str">
-        <v>Pa2gom-d1s7</v>
+        <v>Pa2gom-d1s3</v>
       </c>
       <c r="D173" t="str">
         <v>Yes</v>
@@ -4207,10 +3887,10 @@
         <v>2026-10-11</v>
       </c>
       <c r="B174" t="str">
-        <v>done</v>
+        <v>skipped</v>
       </c>
       <c r="C174" t="str">
-        <v>Pa2gom-d1s9</v>
+        <v>Pa2gom-d1s6</v>
       </c>
       <c r="D174" t="str">
         <v>Yes</v>
@@ -4221,10 +3901,10 @@
         <v>2026-10-11</v>
       </c>
       <c r="B175" t="str">
-        <v>done</v>
+        <v>skipped</v>
       </c>
       <c r="C175" t="str">
-        <v>Pa2gom-d2s4</v>
+        <v>Pa2gom-d1s10</v>
       </c>
       <c r="D175" t="str">
         <v>Yes</v>
@@ -4235,10 +3915,10 @@
         <v>2026-10-11</v>
       </c>
       <c r="B176" t="str">
-        <v>done</v>
+        <v>skipped</v>
       </c>
       <c r="C176" t="str">
-        <v>Pa2gom-d2s4#0</v>
+        <v>Pa2gom-d1s11</v>
       </c>
       <c r="D176" t="str">
         <v>Yes</v>
@@ -4249,13 +3929,13 @@
         <v>2026-10-11</v>
       </c>
       <c r="B177" t="str">
-        <v>skipped</v>
+        <v>moved</v>
       </c>
       <c r="C177" t="str">
-        <v>Pa2gom-d1s1</v>
-      </c>
-      <c r="D177" t="str">
-        <v>Yes</v>
+        <v>Pa2gom-d1s8</v>
+      </c>
+      <c r="D177">
+        <v>2</v>
       </c>
     </row>
     <row r="178">
@@ -4263,89 +3943,19 @@
         <v>2026-10-11</v>
       </c>
       <c r="B178" t="str">
-        <v>skipped</v>
+        <v>moved</v>
       </c>
       <c r="C178" t="str">
-        <v>Pa2gom-d1s3</v>
-      </c>
-      <c r="D178" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="str">
-        <v>2026-10-11</v>
-      </c>
-      <c r="B179" t="str">
-        <v>skipped</v>
-      </c>
-      <c r="C179" t="str">
-        <v>Pa2gom-d1s6</v>
-      </c>
-      <c r="D179" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="str">
-        <v>2026-10-11</v>
-      </c>
-      <c r="B180" t="str">
-        <v>skipped</v>
-      </c>
-      <c r="C180" t="str">
-        <v>Pa2gom-d1s10</v>
-      </c>
-      <c r="D180" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="str">
-        <v>2026-10-11</v>
-      </c>
-      <c r="B181" t="str">
-        <v>skipped</v>
-      </c>
-      <c r="C181" t="str">
-        <v>Pa2gom-d1s11</v>
-      </c>
-      <c r="D181" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="str">
-        <v>2026-10-11</v>
-      </c>
-      <c r="B182" t="str">
-        <v>moved</v>
-      </c>
-      <c r="C182" t="str">
-        <v>Pa2gom-d1s8</v>
-      </c>
-      <c r="D182">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="str">
-        <v>2026-10-11</v>
-      </c>
-      <c r="B183" t="str">
-        <v>moved</v>
-      </c>
-      <c r="C183" t="str">
         <v>Pa2gom-d2s4</v>
       </c>
-      <c r="D183">
+      <c r="D178">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D183"/>
+  <autoFilter ref="A1:D178"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D183"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D178"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4379,7 +3989,7 @@
         <v>ex</v>
       </c>
       <c r="B3" t="str">
-        <v>{"bss":{"n":"Bulgarian Split Squat","eq":"dumbbell"},"db6":{"n":"DB 6 Ways","eq":"dumbbell"},"dip":{"n":"Wide Tricep Dip","eq":"bodyweight"},"grip":{"n":"Grip Trainer","eq":"other"},"hack":{"n":"Hack Squats","eq":"machine"},"pogo":{"n":"Pogo Hops","eq":"bodyweight","url":"https://youtu.be/iU-TKr4YesM"},"sled":{"n":"Sled push → pull","eq":"sled"},"canoe":{"n":"Canoe Stretch","eq":"barbell","url":"https://youtu.be/yR6EnBqjKNs"},"kbleg":{"n":"Kettlebell Leg Raise","eq":"kettlebell"},"latpd":{"n":"Lat Pulldown, alternating single-arm","eq":"cable"},"ohtri":{"n":"Overhead Tricep Extension","eq":"cable"},"qlext":{"n":"Side Lateral QL Extension","eq":"machine","url":"https://www.youtube.com/watch?v=UaydER2VIUc"},"arnold":{"n":"Arnold Press","eq":"dumbbell"},"legext":{"n":"Leg Extension ISO hold","eq":"machine"},"pallof":{"n":"Pallof Pressf h h","eq":"cable"},"skater":{"n":"Lateral Bound / Skater Hop with Stick","eq":"bodyweight","url":"https://youtu.be/4nTDP0G3nhc"},"spinal":{"n":"Spinal Waves","url":"https://youtu.be/KCfh_wCssK8"},"trxrow":{"n":"TRX Wide-Grip Row","eq":"trx","url":"https://youtu.be/o9M1k6OzI-g"},"dbclean":{"n":"DB Clean &amp; Jerk Press","eq":"dumbbell"},"dblunge":{"n":"DB Lunge","eq":"dumbbell"},"farmers":{"n":"Farmers Carry","eq":"dumbbell"},"latpdbi":{"n":"Lat Pulldowns","eq":"cable"},"latwall":{"n":"Lateral Wall Push","eq":"bodyweight","url":"https://youtu.be/tIFjnucY09Q"},"legcurl":{"n":"Prone Leg Curl","eq":"machine"},"medball":{"n":"Med Ball Rotational Scoop","eq":"medball","url":"https://youtu.be/xmQfXggU2mU"},"sledlat":{"n":"Sled push → lateral pull","eq":"sled"},"trxpike":{"n":"TRX Pike Push-Up","eq":"trx","url":"https://youtu.be/GIWNRslPEv4"},"wristpd":{"n":"Cable Wrist Pulldown","eq":"cable"},"zercher":{"n":"Seated Zercher Good Morning","eq":"shortbar","url":"https://youtu.be/ahfSSi4MVJQ"},"zottman":{"n":"Zottman Curls","eq":"dumbbell"},"cablerow":{"n":"Explosive Unilateral Cable Row","eq":"cable","url":"https://youtu.be/OrAcowGGU2U"},"deadlift":{"n":"Deadlift","eq":"barbell"},"facepull":{"n":"Face Pulls","eq":"cable"},"platerot":{"n":"Plate Torso Rotation","eq":"plate"},"reardelt":{"n":"Side Rear Delt Fly","eq":"cable"},"romanadd":{"n":"Roman Chair Hip Adduction","eq":"bodyweight","url":"https://www.youtube.com/watch?v=j5HWZOfIePI"},"suitcase":{"n":"Suitcase Bottom-Up, single-arm","eq":"kettlebell"},"dead-bugs":{"n":"Dead Bugs"},"deskbands":{"n":"Desk Bands","eq":"band","url":"https://youtu.be/o_uZcQnXaFA"},"hipthrust":{"n":"Hip Thrust","eq":"machine"},"kneeraise":{"n":"Hanging Knee Raise","eq":"bodyweight"},"sled-pull":{"n":"Sled Pull","eq":"sled"},"splitjump":{"n":"Split Squat Jumps","eq":"bodyweight","url":"https://www.youtube.com/watch?v=4DMvFDaqIys"},"abb-roller":{"n":"Abb Roller","eq":"other"},"cablepunch":{"n":"Cable Punch ISO hold","eq":"cable"},"chestpress":{"n":"Chest Press","eq":"machine"},"depthcombo":{"n":"Depth Drop → Broad Jump → Box Jump","eq":"bodyweight","url":"https://youtu.be/GZLyZCqF8BQ"},"innerthigh":{"n":"Inner Thigh Abduction","eq":"machine"},"outerthigh":{"n":"Outer Thigh Adduction","eq":"machine"},"cablecrunch":{"n":"Kneeling Cable Ab Crunch","eq":"cable"},"dragon-flag":{"n":"Dragon Flag","eq":"bodyweight"},"squat-walks":{"n":"Squat Walks","eq":"dumbbell","url":"https://www.instagram.com/p/DeKAHsWKK4W/"},"leg-extension":{"n":"Leg Extension","eq":"machine"},"duck-sled-push":{"n":"Duck Sled Push","eq":"sled","url":"https://www.instagram.com/p/DeKUe-qvgF-/"},"tibialis-raise":{"n":"Tibialis Raise","eq":"bodyweight","url":"https://youtu.be/OPEuhclsTUQ"},"garhammer-raise":{"n":"Garhammer Raise","url":"https://youtu.be/0ShG8aVIvms?t=836"},"c:fedb:Face_Pull":{"n":"Face Pull","eq":"cable"},"c:fedb:Sled_Push":{"n":"Sled Push","eq":"sled"},"pallof-pressesed":{"n":"Pallof Pressesed"},"c:fedb:Hack_Squat":{"n":"Hack Squat","eq":"machine"},"sled-lateral-pull":{"n":"Sled Lateral pull","eq":"sled"},"c:fedb:Dip_Machine":{"n":"Dip Machine","eq":"machine"},"c:fedb:Cable_Crunch":{"n":"Cable Crunch","eq":"cable"},"c:fedb:Farmers_Walk":{"n":"Farmer's Walk","eq":"dumbbell"},"c:fedb:Hanging_Pike":{"n":"Hanging Pike","eq":"bodyweight"},"c:fedb:Pallof_Press":{"n":"Pallof Press","eq":"cable"},"c:fedb:Zottman_Curl":{"n":"Zottman Curl","eq":"dumbbell"},"hanging-knee-raises":{"n":"Hanging Knee Raises","eq":"machine"},"seated-cable-crunch":{"n":"Seated Cable Crunch","eq":"cable","url":"https://youtube.com/shorts/bIbm-p6Q4s8?is=aiC1fOhPbN5QMcgq"},"bench-reverse-crunch":{"n":"Bench Reverse Crunch"},"c:fedb:Clean_and_Jerk":{"n":"Clean and Jerk","eq":"dumbbell"},"c:fedb:Leg_Extensions":{"n":"Leg Extensions","eq":"machine"},"c:fedb:Thigh_Abductor":{"n":"Thigh Abductor","eq":"machine"},"c:fedb:Thigh_Adductor":{"n":"Thigh Adductor","eq":"machine"},"c:fedb:Clean_and_Press":{"n":"Clean and Press","eq":"barbell"},"c:fedb:Dumbbell_Lunges":{"n":"Dumbbell Lunges","eq":"dumbbell"},"c:fedb:Kettlebell_Halo":{"n":"Kettlebell Halo","eq":"kettlebell"},"c:fedb:Lying_Leg_Curls":{"n":"Lying Leg Curls","eq":"machine"},"c:fedb:Cable_Wrist_Curl":{"n":"Cable Wrist Curl","eq":"cable"},"c:fedb:Hanging_Leg_Raise":{"n":"Hanging Leg Raise","eq":"bodyweight"},"clean-jerk-overhead-press":{"n":"Clean Jerk &amp; Overhead Press","eq":"dumbbell"},"c:fedb:Cable_Seated_Crunch":{"n":"Cable Seated Crunch","eq":"cable"},"c:fedb:Sled_Drag_-_Harness":{"n":"Sled Drag - Harness","eq":"other"},"c:fedb:Dips_-_Chest_Version":{"n":"Dips - Chest Version","eq":"other"},"c:fedb:Dumbbell_Bench_Press":{"n":"Dumbbell Bench Press","eq":"dumbbell"},"c:fedb:Seated_Good_Mornings":{"n":"Seated Good Mornings","eq":"shortbar"},"c:fedb:Arnold_Dumbbell_Press":{"n":"Arnold Dumbbell Press","eq":"dumbbell"},"c:fedb:Dips_-_Triceps_Version":{"n":"Dips - Triceps Version","eq":"machine"},"c:fedb:Single-Leg_Leg_Extension":{"n":"Single-Leg Leg Extension","eq":"machine"},"split-stance-cable-hip-rotation":{"n":"Split Stance Cable Hip Rotation","eq":"cable","url":"https://youtu.be/ixIEilUM2aY"},"c:fedb:Close-Grip_Front_Lat_Pulldown":{"n":"Close-Grip Front Lat Pulldown","eq":"cable"},"c:fedb:Cable_One_Arm_Tricep_Extension":{"n":"Cable One Arm Tricep Extension","eq":"cable"},"statue-of-liberty-to-fly-to-chest-buster":{"n":"Statue of Liberty to fly to chest busters","eq":"dumbbell","url":"https://www.instagram.com/reel/Dbu6F2ZKW-O/?exln=azRoYnNhb2VsOTRp"},"c:fedb:Cable_Rope_Overhead_Triceps_Extension":{"n":"Cable Rope Overhead Triceps Extension","eq":"cable"}}</v>
+        <v>{"bss":{"n":"Bulgarian Split Squat","eq":"dumbbell"},"db6":{"n":"DB 6 Ways","eq":"dumbbell"},"dip":{"n":"Wide Tricep Dip","eq":"bodyweight"},"grip":{"n":"Grip Trainer","eq":"other"},"hack":{"n":"Hack Squats","eq":"machine"},"pogo":{"n":"Pogo Hops","eq":"bodyweight","url":"https://youtu.be/iU-TKr4YesM"},"sled":{"n":"Sled push → pull","eq":"sled"},"canoe":{"n":"Canoe Stretch","eq":"barbell","url":"https://youtu.be/yR6EnBqjKNs"},"kbleg":{"n":"Kettlebell Leg Raise","eq":"kettlebell"},"latpd":{"n":"Lat Pulldown, alternating single-arm","eq":"cable"},"ohtri":{"n":"Overhead Tricep Extension","eq":"cable"},"qlext":{"n":"Side Lateral QL Extension","eq":"machine","url":"https://www.youtube.com/watch?v=UaydER2VIUc"},"arnold":{"n":"Arnold Press","eq":"dumbbell"},"legext":{"n":"Leg Extension ISO hold","eq":"machine"},"pallof":{"n":"Pallof Pressf h h","eq":"cable"},"skater":{"n":"Lateral Bound / Skater Hop with Stick","eq":"bodyweight","url":"https://youtu.be/4nTDP0G3nhc"},"spinal":{"n":"Spinal Waves","url":"https://youtu.be/KCfh_wCssK8"},"trxrow":{"n":"TRX Wide-Grip Row","eq":"trx","url":"https://youtu.be/o9M1k6OzI-g"},"dbclean":{"n":"DB Clean &amp; Jerk Press","eq":"dumbbell"},"dblunge":{"n":"DB Lunge","eq":"dumbbell"},"farmers":{"n":"Farmers Carry","eq":"dumbbell"},"latpdbi":{"n":"Lat Pulldowns","eq":"cable"},"latwall":{"n":"Lateral Wall Push","eq":"bodyweight","url":"https://youtu.be/tIFjnucY09Q"},"legcurl":{"n":"Prone Leg Curl","eq":"machine"},"medball":{"n":"Med Ball Rotational Scoop","eq":"medball","url":"https://youtu.be/xmQfXggU2mU"},"sledlat":{"n":"Sled push → lateral pull","eq":"sled"},"trxpike":{"n":"TRX Pike Push-Up","eq":"trx","url":"https://youtu.be/GIWNRslPEv4"},"wristpd":{"n":"Cable Wrist Pulldown","eq":"cable"},"zercher":{"n":"Seated Zercher Good Morning","eq":"shortbar","url":"https://youtu.be/ahfSSi4MVJQ"},"zottman":{"n":"Zottman Curls","eq":"dumbbell"},"cablerow":{"n":"Explosive Unilateral Cable Row","eq":"cable","url":"https://youtu.be/OrAcowGGU2U"},"deadlift":{"n":"Deadlift","eq":"barbell"},"facepull":{"n":"Face Pulls","eq":"cable"},"platerot":{"n":"Plate Torso Rotation","eq":"plate"},"reardelt":{"n":"Side Rear Delt Fly","eq":"cable"},"romanadd":{"n":"Roman Chair Hip Adduction","eq":"bodyweight","url":"https://www.youtube.com/watch?v=j5HWZOfIePI"},"suitcase":{"n":"Suitcase Bottom-Up, single-arm","eq":"kettlebell"},"dead-bugs":{"n":"Dead Bugs"},"deskbands":{"n":"Desk Bands","eq":"band","url":"https://youtu.be/o_uZcQnXaFA"},"hipthrust":{"n":"Hip Thrust","eq":"machine"},"kneeraise":{"n":"Hanging Knee Raise","eq":"bodyweight"},"sled-pull":{"n":"Sled Pull","eq":"sled"},"splitjump":{"n":"Split Squat Jumps","eq":"bodyweight","url":"https://www.youtube.com/watch?v=4DMvFDaqIys"},"abb-roller":{"n":"Abb Roller","eq":"other"},"cablepunch":{"n":"Cable Punch ISO hold","eq":"cable"},"chestpress":{"n":"Chest Press","eq":"machine"},"depthcombo":{"n":"Depth Drop → Broad Jump → Box Jump","eq":"bodyweight","url":"https://youtu.be/GZLyZCqF8BQ"},"innerthigh":{"n":"Inner Thigh Abduction","eq":"machine"},"outerthigh":{"n":"Outer Thigh Adduction","eq":"machine"},"cablecrunch":{"n":"Kneeling Cable Ab Crunch","eq":"cable"},"dragon-flag":{"n":"Dragon Flag","eq":"bodyweight"},"squat-walks":{"n":"Squat Walks","eq":"dumbbell","url":"https://www.instagram.com/p/DeKAHsWKK4W/"},"leg-extension":{"n":"Leg Extension","eq":"machine"},"duck-sled-push":{"n":"Duck Sled Push","eq":"sled","url":"https://www.instagram.com/p/DeKUe-qvgF-/"},"tibialis-raise":{"n":"Tibialis Raise","eq":"bodyweight","url":"https://youtu.be/OPEuhclsTUQ"},"garhammer-raise":{"n":"Garhammer Raise","url":"https://youtu.be/0ShG8aVIvms?t=836"},"c:fedb:Face_Pull":{"n":"Face Pull","eq":"cable"},"c:fedb:Sled_Push":{"n":"Sled Push","eq":"sled"},"pallof-pressesed":{"n":"Pallof Pressesed"},"c:fedb:Hack_Squat":{"n":"Hack Squat","eq":"machine"},"sled-lateral-pull":{"n":"Sled Lateral pull","eq":"sled"},"c:fedb:Dip_Machine":{"n":"Dip Machine","eq":"machine"},"c:fedb:Cable_Crunch":{"n":"Cable Crunch","eq":"cable"},"c:fedb:Farmers_Walk":{"n":"Farmer's Walk","eq":"dumbbell"},"c:fedb:Hanging_Pike":{"n":"Hanging Pike","eq":"bodyweight"},"c:fedb:Pallof_Press":{"n":"Pallof Press","eq":"cable"},"c:fedb:Zottman_Curl":{"n":"Zottman Curl","eq":"dumbbell"},"hanging-knee-raises":{"n":"Hanging Knee Raises","eq":"machine"},"seated-cable-crunch":{"n":"Seated Cable Crunch","eq":"cable","url":"https://youtube.com/shorts/bIbm-p6Q4s8?is=aiC1fOhPbN5QMcgq"},"bench-reverse-crunch":{"n":"Bench Reverse Crunch"},"c:fedb:Lateral_Bound":{"n":"Lateral Bound","eq":"bodyweight"},"c:fedb:Clean_and_Jerk":{"n":"Clean and Jerk","eq":"dumbbell"},"c:fedb:Leg_Extensions":{"n":"Leg Extensions","eq":"machine"},"c:fedb:Thigh_Abductor":{"n":"Thigh Abductor","eq":"machine"},"c:fedb:Thigh_Adductor":{"n":"Thigh Adductor","eq":"machine"},"c:fedb:Clean_and_Press":{"n":"Clean and Press","eq":"barbell"},"c:fedb:Dumbbell_Lunges":{"n":"Dumbbell Lunges","eq":"dumbbell"},"c:fedb:Kettlebell_Halo":{"n":"Kettlebell Halo","eq":"kettlebell"},"c:fedb:Lying_Leg_Curls":{"n":"Lying Leg Curls","eq":"machine"},"c:fedb:Cable_Wrist_Curl":{"n":"Cable Wrist Curl","eq":"cable"},"c:fedb:Hanging_Leg_Raise":{"n":"Hanging Leg Raise","eq":"bodyweight"},"clean-jerk-overhead-press":{"n":"Clean Jerk &amp; Overhead Press","eq":"dumbbell"},"c:fedb:Cable_Seated_Crunch":{"n":"Cable Seated Crunch","eq":"cable"},"c:fedb:Sled_Drag_-_Harness":{"n":"Sled Drag - Harness","eq":"other"},"c:fedb:Dips_-_Chest_Version":{"n":"Dips - Chest Version","eq":"other"},"c:fedb:Dumbbell_Bench_Press":{"n":"Dumbbell Bench Press","eq":"dumbbell"},"c:fedb:Seated_Good_Mornings":{"n":"Seated Good Mornings","eq":"shortbar"},"c:fedb:Arnold_Dumbbell_Press":{"n":"Arnold Dumbbell Press","eq":"dumbbell"},"c:fedb:Dips_-_Triceps_Version":{"n":"Dips - Triceps Version","eq":"machine"},"c:fedb:Single-Leg_Leg_Extension":{"n":"Single-Leg Leg Extension","eq":"machine"},"split-stance-cable-hip-rotation":{"n":"Split Stance Cable Hip Rotation","eq":"cable","url":"https://youtu.be/ixIEilUM2aY"},"c:fedb:Close-Grip_Front_Lat_Pulldown":{"n":"Close-Grip Front Lat Pulldown","eq":"cable"},"c:fedb:Cable_One_Arm_Tricep_Extension":{"n":"Cable One Arm Tricep Extension","eq":"cable"},"statue-of-liberty-to-fly-to-chest-buster":{"n":"Statue of Liberty to fly to chest busters","eq":"dumbbell","url":"https://www.instagram.com/reel/Dbu6F2ZKW-O/?exln=azRoYnNhb2VsOTRp"},"c:fedb:Cable_Rope_Overhead_Triceps_Extension":{"n":"Cable Rope Overhead Triceps Extension","eq":"cable"}}</v>
       </c>
     </row>
     <row r="4">
@@ -4443,7 +4053,7 @@
         <v>muscleMap</v>
       </c>
       <c r="B11" t="str">
-        <v>{"c:fedb:Face_Pull":{"p":["frontdelt","sidedelt"],"s":["upperback"]},"c:fedb:Sled_Push":{"p":["quads"],"s":["calves","chest","glutes","hamstrings","triceps"]},"c:fedb:Hack_Squat":{"p":["quads"],"s":["calves","glutes","hamstrings"]},"c:fedb:Dip_Machine":{"p":["triceps"],"s":["chest","frontdelt","sidedelt"]},"c:fedb:Cable_Crunch":{"p":["abs"]},"c:fedb:Farmers_Walk":{"p":["forearms"],"s":["abs","glutes","hamstrings","lowerback","quads","traps"]},"c:fedb:Hanging_Pike":{"p":["abs"]},"c:fedb:Pallof_Press":{"p":["abs"],"s":["chest","frontdelt","sidedelt","triceps"]},"c:fedb:Zottman_Curl":{"p":["biceps"],"s":["forearms"]},"seated-cable-crunch":{"p":["abs"],"s":[]},"c:fedb:Clean_and_Jerk":{"p":["frontdelt","sidedelt"],"s":["abs","glutes","hamstrings","lowerback","quads","traps","triceps"]},"c:fedb:Leg_Extensions":{"p":["quads"]},"c:fedb:Thigh_Abductor":{"p":["abductors"],"s":["glutes"]},"c:fedb:Thigh_Adductor":{"p":["adductors"],"s":["glutes","hamstrings"]},"c:fedb:Clean_and_Press":{"p":["frontdelt","sidedelt"],"s":["abs","calves","glutes","hamstrings","lowerback","upperback","quads","traps","triceps"]},"c:fedb:Dumbbell_Lunges":{"p":["quads"],"s":["calves","glutes","hamstrings"]},"c:fedb:Kettlebell_Halo":{"p":["frontdelt","sidedelt"],"s":["traps","upperback","abs","triceps"]},"c:fedb:Lying_Leg_Curls":{"p":["hamstrings"]},"c:fedb:Cable_Wrist_Curl":{"p":["forearms"]},"c:fedb:Hanging_Leg_Raise":{"p":["abs"]},"c:fedb:Cable_Seated_Crunch":{"p":["abs"]},"c:fedb:Sled_Drag_-_Harness":{"p":["quads"],"s":["calves","glutes","hamstrings"]},"c:fedb:Dips_-_Chest_Version":{"p":["chest"],"s":["frontdelt","sidedelt","triceps"]},"c:fedb:Dumbbell_Bench_Press":{"p":["chest"],"s":["frontdelt","sidedelt","triceps"]},"c:fedb:Seated_Good_Mornings":{"p":["lowerback"],"s":["glutes"]},"c:fedb:Arnold_Dumbbell_Press":{"p":["frontdelt","sidedelt"],"s":["triceps"]},"c:fedb:Dips_-_Triceps_Version":{"p":["triceps"],"s":["chest","frontdelt","sidedelt"]},"c:fedb:Single-Leg_Leg_Extension":{"p":["quads"]},"c:fedb:Close-Grip_Front_Lat_Pulldown":{"p":["lats"],"s":["biceps","upperback","frontdelt","sidedelt"]},"c:fedb:Cable_One_Arm_Tricep_Extension":{"p":["triceps"]},"c:fedb:Cable_Rope_Overhead_Triceps_Extension":{"p":["triceps"]}}</v>
+        <v>{"c:fedb:Face_Pull":{"p":["frontdelt","sidedelt"],"s":["upperback"]},"c:fedb:Sled_Push":{"p":["quads"],"s":["calves","chest","glutes","hamstrings","triceps"]},"c:fedb:Hack_Squat":{"p":["quads"],"s":["calves","glutes","hamstrings"]},"c:fedb:Dip_Machine":{"p":["triceps"],"s":["chest","frontdelt","sidedelt"]},"c:fedb:Cable_Crunch":{"p":["abs"]},"c:fedb:Farmers_Walk":{"p":["forearms"],"s":["abs","glutes","hamstrings","lowerback","quads","traps"]},"c:fedb:Hanging_Pike":{"p":["abs"]},"c:fedb:Pallof_Press":{"p":["abs"],"s":["chest","frontdelt","sidedelt","triceps"]},"c:fedb:Zottman_Curl":{"p":["biceps"],"s":["forearms"]},"seated-cable-crunch":{"p":["abs"],"s":[]},"c:fedb:Lateral_Bound":{"p":["adductors"],"s":["abductors","calves","glutes","hamstrings","quads"]},"c:fedb:Clean_and_Jerk":{"p":["frontdelt","sidedelt"],"s":["abs","glutes","hamstrings","lowerback","quads","traps","triceps"]},"c:fedb:Leg_Extensions":{"p":["quads"]},"c:fedb:Thigh_Abductor":{"p":["abductors"],"s":["glutes"]},"c:fedb:Thigh_Adductor":{"p":["adductors"],"s":["glutes","hamstrings"]},"c:fedb:Clean_and_Press":{"p":["frontdelt","sidedelt"],"s":["abs","calves","glutes","hamstrings","lowerback","upperback","quads","traps","triceps"]},"c:fedb:Dumbbell_Lunges":{"p":["quads"],"s":["calves","glutes","hamstrings"]},"c:fedb:Kettlebell_Halo":{"p":["frontdelt","sidedelt"],"s":["traps","upperback","abs","triceps"]},"c:fedb:Lying_Leg_Curls":{"p":["hamstrings"]},"c:fedb:Cable_Wrist_Curl":{"p":["forearms"]},"c:fedb:Hanging_Leg_Raise":{"p":["abs"]},"c:fedb:Cable_Seated_Crunch":{"p":["abs"]},"c:fedb:Sled_Drag_-_Harness":{"p":["quads"],"s":["calves","glutes","hamstrings"]},"c:fedb:Dips_-_Chest_Version":{"p":["chest"],"s":["frontdelt","sidedelt","triceps"]},"c:fedb:Dumbbell_Bench_Press":{"p":["chest"],"s":["frontdelt","sidedelt","triceps"]},"c:fedb:Seated_Good_Mornings":{"p":["lowerback"],"s":["glutes"]},"c:fedb:Arnold_Dumbbell_Press":{"p":["frontdelt","sidedelt"],"s":["triceps"]},"c:fedb:Dips_-_Triceps_Version":{"p":["triceps"],"s":["chest","frontdelt","sidedelt"]},"c:fedb:Single-Leg_Leg_Extension":{"p":["quads"]},"c:fedb:Close-Grip_Front_Lat_Pulldown":{"p":["lats"],"s":["biceps","upperback","frontdelt","sidedelt"]},"c:fedb:Cable_One_Arm_Tricep_Extension":{"p":["triceps"]},"c:fedb:Cable_Rope_Overhead_Triceps_Extension":{"p":["triceps"]}}</v>
       </c>
     </row>
     <row r="12">
@@ -4496,7 +4106,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O58"/>
+  <dimension ref="A1:O40"/>
   <cols>
     <col min="1" max="1" width="11.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -4570,43 +4180,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C2" t="str">
-        <v>Cable Wrist Pulldown</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="D2" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F2">
         <v>4</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H2" t="str">
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>33×15, 33×15, 33×15, 33×15</v>
+        <v>50×6, 50×6, 50×6, 50×6</v>
       </c>
       <c r="J2">
-        <v>1980</v>
+        <v>1200</v>
       </c>
       <c r="K2" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Lower back</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>Glutes, Hamstrings, Upper back</v>
       </c>
       <c r="M2" t="str">
         <v/>
       </c>
       <c r="N2" t="str">
-        <v>A-d1s2</v>
+        <v>A-d1s6</v>
       </c>
       <c r="O2" t="str">
-        <v>wristpd</v>
+        <v>zercher</v>
       </c>
     </row>
     <row r="3">
@@ -4617,10 +4227,10 @@
         <v>2026-09-27</v>
       </c>
       <c r="C3" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="D3" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="E3">
         <v>50</v>
@@ -4628,79 +4238,79 @@
       <c r="F3">
         <v>4</v>
       </c>
-      <c r="G3">
-        <v>6</v>
-      </c>
-      <c r="H3" t="str">
-        <v/>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3">
+        <v>15</v>
       </c>
       <c r="I3" t="str">
-        <v>50×6, 50×6, 50×6, 50×6</v>
-      </c>
-      <c r="J3">
-        <v>1200</v>
+        <v>50×15s, 50×15s, 50×15s, 50×15s</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
       </c>
       <c r="K3" t="str">
-        <v>Lower back</v>
+        <v>Rear delts</v>
       </c>
       <c r="L3" t="str">
-        <v>Glutes, Hamstrings, Upper back</v>
+        <v>Upper back</v>
       </c>
       <c r="M3" t="str">
         <v/>
       </c>
       <c r="N3" t="str">
-        <v>A-d1s6</v>
+        <v>A-d3s6</v>
       </c>
       <c r="O3" t="str">
-        <v>zercher</v>
+        <v>reardelt</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="B4" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="C4" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="D4" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="E4">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F4">
         <v>4</v>
       </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4">
-        <v>15</v>
+      <c r="G4">
+        <v>6</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>50×15s, 50×15s, 50×15s, 50×15s</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
+        <v>200×6, 200×6, 200×6, 200×6</v>
+      </c>
+      <c r="J4">
+        <v>4800</v>
       </c>
       <c r="K4" t="str">
-        <v>Rear delts</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="L4" t="str">
-        <v>Upper back</v>
+        <v/>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N4" t="str">
-        <v>A-d3s6</v>
+        <v>A-d1s8</v>
       </c>
       <c r="O4" t="str">
-        <v>reardelt</v>
+        <v>grip</v>
       </c>
     </row>
     <row r="5">
@@ -4711,43 +4321,43 @@
         <v>2026-09-27</v>
       </c>
       <c r="C5" t="str">
-        <v>Cable Wrist Pulldown</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="D5" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>320</v>
       </c>
       <c r="F5">
         <v>4</v>
       </c>
       <c r="G5">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H5" t="str">
         <v/>
       </c>
       <c r="I5" t="str">
-        <v>33×15, 33×15, 33×15, 33×15</v>
+        <v>320×6, 320×6, 320×6, 320×6</v>
       </c>
       <c r="J5">
-        <v>1980</v>
+        <v>7680</v>
       </c>
       <c r="K5" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Glutes</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>Hamstrings</v>
       </c>
       <c r="M5" t="str">
         <v>From check-off</v>
       </c>
       <c r="N5" t="str">
-        <v>A-d3s3</v>
+        <v>A-d2s5</v>
       </c>
       <c r="O5" t="str">
-        <v>wristpd</v>
+        <v>hipthrust</v>
       </c>
     </row>
     <row r="6">
@@ -4758,251 +4368,251 @@
         <v>2026-09-27</v>
       </c>
       <c r="C6" t="str">
-        <v>Grip Trainer</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="D6" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="E6">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F6">
         <v>4</v>
       </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-      <c r="H6" t="str">
-        <v/>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6">
+        <v>15</v>
       </c>
       <c r="I6" t="str">
-        <v>200×6, 200×6, 200×6, 200×6</v>
-      </c>
-      <c r="J6">
-        <v>4800</v>
+        <v>50×15s, 50×15s, 50×15s, 50×15s</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
       </c>
       <c r="K6" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Rear delts</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>Upper back</v>
       </c>
       <c r="M6" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N6" t="str">
-        <v>A-d1s8</v>
+        <v>A-d2s2</v>
       </c>
       <c r="O6" t="str">
-        <v>grip</v>
+        <v>reardelt</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="B7" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="C7" t="str">
-        <v>Hip Thrust</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="D7" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="E7">
-        <v>320</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-      <c r="H7" t="str">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7">
+        <v>15</v>
       </c>
       <c r="I7" t="str">
-        <v>320×6, 320×6, 320×6, 320×6</v>
-      </c>
-      <c r="J7">
-        <v>7680</v>
+        <v>15×15s, 15×15s, 15×15s</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
       </c>
       <c r="K7" t="str">
-        <v>Glutes</v>
+        <v>Abs, Hip flexors</v>
       </c>
       <c r="L7" t="str">
-        <v>Hamstrings</v>
+        <v/>
       </c>
       <c r="M7" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N7" t="str">
-        <v>A-d2s5</v>
+        <v>A-d1s7</v>
       </c>
       <c r="O7" t="str">
-        <v>hipthrust</v>
+        <v>kbleg</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="B8" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="C8" t="str">
-        <v>Leg Extension ISO hold</v>
+        <v>Suitcase Bottom-Up, single-arm</v>
       </c>
       <c r="D8" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="E8">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F8">
         <v>4</v>
       </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8">
-        <v>30</v>
+      <c r="G8">
+        <v>6</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>50×30s, 50×30s, 50×30s, 50×30s</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
+        <v>25×6, 25×6, 25×6, 25×6</v>
+      </c>
+      <c r="J8">
+        <v>600</v>
       </c>
       <c r="K8" t="str">
-        <v>Quads</v>
+        <v>Forearms &amp; grip, Obliques</v>
       </c>
       <c r="L8" t="str">
-        <v/>
+        <v>Traps</v>
       </c>
       <c r="M8" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N8" t="str">
-        <v>A-d2s3</v>
+        <v>A-d4s1</v>
       </c>
       <c r="O8" t="str">
-        <v>legext</v>
+        <v>suitcase</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-30</v>
       </c>
       <c r="B9" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="C9" t="str">
-        <v>Side Rear Delt Fly</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="D9" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="E9">
-        <v>50</v>
+        <v>320</v>
       </c>
       <c r="F9">
-        <v>4</v>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9">
-        <v>15</v>
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>6</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>50×15s, 50×15s, 50×15s, 50×15s</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
+        <v>320×6, 320×6</v>
+      </c>
+      <c r="J9">
+        <v>3840</v>
       </c>
       <c r="K9" t="str">
-        <v>Rear delts</v>
+        <v>Glutes</v>
       </c>
       <c r="L9" t="str">
-        <v>Upper back</v>
+        <v>Hamstrings</v>
       </c>
       <c r="M9" t="str">
         <v/>
       </c>
       <c r="N9" t="str">
-        <v>A-d2s2</v>
+        <v>A-d4s5</v>
       </c>
       <c r="O9" t="str">
-        <v>reardelt</v>
+        <v>hipthrust</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-09-29</v>
+        <v>2026-09-30</v>
       </c>
       <c r="B10" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="C10" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="D10" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="E10">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F10">
-        <v>3</v>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10">
-        <v>15</v>
+        <v>4</v>
+      </c>
+      <c r="G10">
+        <v>6</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>15×15s, 15×15s, 15×15s</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
+        <v>50×6, 50×6, 50×6, 50×6</v>
+      </c>
+      <c r="J10">
+        <v>1200</v>
       </c>
       <c r="K10" t="str">
-        <v>Abs, Hip flexors</v>
+        <v>Lower back</v>
       </c>
       <c r="L10" t="str">
-        <v/>
+        <v>Glutes, Hamstrings, Upper back</v>
       </c>
       <c r="M10" t="str">
         <v/>
       </c>
       <c r="N10" t="str">
-        <v>A-d1s7</v>
+        <v>A-d4s4</v>
       </c>
       <c r="O10" t="str">
-        <v>kbleg</v>
+        <v>zercher</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-01</v>
       </c>
       <c r="B11" t="str">
         <v>2026-09-27</v>
       </c>
       <c r="C11" t="str">
-        <v>Kneeling Cable Ab Crunch</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="D11" t="str">
         <v>Strength</v>
       </c>
       <c r="E11">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G11">
         <v>6</v>
@@ -5011,42 +4621,42 @@
         <v/>
       </c>
       <c r="I11" t="str">
-        <v>60×6, 60×6, 60×6, 60×6</v>
+        <v>40×6</v>
       </c>
       <c r="J11">
-        <v>1440</v>
+        <v>240</v>
       </c>
       <c r="K11" t="str">
-        <v>Abs</v>
+        <v>Lower back</v>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>Glutes, Hamstrings, Upper back</v>
       </c>
       <c r="M11" t="str">
         <v/>
       </c>
       <c r="N11" t="str">
-        <v>A-d2s4</v>
+        <v>A-d6s5</v>
       </c>
       <c r="O11" t="str">
-        <v>cablecrunch</v>
+        <v>zercher</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-04</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-09-27</v>
+        <v>2026-10-04</v>
       </c>
       <c r="C12" t="str">
-        <v>Leg Extension ISO hold</v>
+        <v>Cable Punch ISO hold</v>
       </c>
       <c r="D12" t="str">
         <v>Isometric</v>
       </c>
       <c r="E12">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F12">
         <v>4</v>
@@ -5055,263 +4665,263 @@
         <v/>
       </c>
       <c r="H12">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I12" t="str">
-        <v>50×30s, 50×30s, 50×30s, 50×30s</v>
+        <v>30×15s, 30×15s, 30×15s, 30×15s</v>
       </c>
       <c r="J12" t="str">
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>Quads</v>
+        <v>Obliques, Abs</v>
       </c>
       <c r="L12" t="str">
-        <v/>
+        <v>Chest, Front delts</v>
       </c>
       <c r="M12" t="str">
         <v/>
       </c>
       <c r="N12" t="str">
-        <v>A-d3s5</v>
+        <v>B-d6s6</v>
       </c>
       <c r="O12" t="str">
-        <v>legext</v>
+        <v>cablepunch</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-04</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-09-27</v>
+        <v>2026-10-04</v>
       </c>
       <c r="C13" t="str">
-        <v>Suitcase Bottom-Up, single-arm</v>
+        <v>Clean Jerk &amp; Overhead Press</v>
       </c>
       <c r="D13" t="str">
-        <v>Strength</v>
+        <v>Explosive</v>
       </c>
       <c r="E13">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H13" t="str">
         <v/>
       </c>
       <c r="I13" t="str">
-        <v>25×6, 25×6, 25×6, 25×6</v>
+        <v>20×10, 20×10, 20×10</v>
       </c>
       <c r="J13">
         <v>600</v>
       </c>
       <c r="K13" t="str">
-        <v>Forearms &amp; grip, Obliques</v>
+        <v/>
       </c>
       <c r="L13" t="str">
-        <v>Traps</v>
+        <v/>
       </c>
       <c r="M13" t="str">
         <v/>
       </c>
       <c r="N13" t="str">
-        <v>A-d4s1</v>
+        <v>B-d5s2</v>
       </c>
       <c r="O13" t="str">
-        <v>suitcase</v>
+        <v>clean-jerk-overhead-press</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-09-29</v>
+        <v>2026-10-04</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-09-27</v>
+        <v>2026-10-04</v>
       </c>
       <c r="C14" t="str">
-        <v>Zottman Curls</v>
+        <v>Depth Drop → Broad Jump → Box Jump</v>
       </c>
       <c r="D14" t="str">
-        <v>Hypertrophy</v>
-      </c>
-      <c r="E14">
-        <v>15</v>
+        <v>Explosive</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
       </c>
       <c r="F14">
         <v>3</v>
       </c>
       <c r="G14">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H14" t="str">
         <v/>
       </c>
       <c r="I14" t="str">
-        <v>15×15, 15×15, 15×15</v>
-      </c>
-      <c r="J14">
-        <v>675</v>
+        <v>BW×5, BW×5, BW×5</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
       </c>
       <c r="K14" t="str">
-        <v>Biceps, Forearms &amp; grip</v>
+        <v>Quads, Glutes, Calves</v>
       </c>
       <c r="L14" t="str">
-        <v/>
+        <v>Hamstrings</v>
       </c>
       <c r="M14" t="str">
         <v/>
       </c>
       <c r="N14" t="str">
-        <v>A-d1s7</v>
+        <v>B-d6s4</v>
       </c>
       <c r="O14" t="str">
-        <v>zottman</v>
+        <v>depthcombo</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-09-30</v>
+        <v>2026-10-04</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-09-27</v>
+        <v>2026-10-04</v>
       </c>
       <c r="C15" t="str">
-        <v>Hip Thrust</v>
+        <v>Explosive Unilateral Cable Row</v>
       </c>
       <c r="D15" t="str">
-        <v>Strength</v>
+        <v>Explosive</v>
       </c>
       <c r="E15">
-        <v>320</v>
+        <v>30</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H15" t="str">
         <v/>
       </c>
       <c r="I15" t="str">
-        <v>320×6, 320×6</v>
+        <v>30×10, 30×10, 30×10, 30×10</v>
       </c>
       <c r="J15">
-        <v>3840</v>
+        <v>1200</v>
       </c>
       <c r="K15" t="str">
-        <v>Glutes</v>
+        <v>Lats, Upper back</v>
       </c>
       <c r="L15" t="str">
-        <v>Hamstrings</v>
+        <v>Rear delts, Biceps</v>
       </c>
       <c r="M15" t="str">
         <v/>
       </c>
       <c r="N15" t="str">
-        <v>A-d4s5</v>
+        <v>B-d6s6</v>
       </c>
       <c r="O15" t="str">
-        <v>hipthrust</v>
+        <v>cablerow</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-09-30</v>
+        <v>2026-10-04</v>
       </c>
       <c r="B16" t="str">
-        <v>2026-09-27</v>
+        <v>2026-10-04</v>
       </c>
       <c r="C16" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Lateral Bound / Skater Hop with Stick</v>
       </c>
       <c r="D16" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="E16">
-        <v>50</v>
+        <v>Explosive</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H16" t="str">
         <v/>
       </c>
       <c r="I16" t="str">
-        <v>50×6, 50×6, 50×6, 50×6</v>
-      </c>
-      <c r="J16">
-        <v>1200</v>
+        <v>BW×10, BW×10, BW×10</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
       </c>
       <c r="K16" t="str">
-        <v>Lower back</v>
+        <v>Glutes, Outer hip (abductors), Quads</v>
       </c>
       <c r="L16" t="str">
-        <v>Glutes, Hamstrings, Upper back</v>
+        <v>Inner thigh (adductors), Calves</v>
       </c>
       <c r="M16" t="str">
         <v/>
       </c>
       <c r="N16" t="str">
-        <v>A-d4s4</v>
+        <v>B-d6s2</v>
       </c>
       <c r="O16" t="str">
-        <v>zercher</v>
+        <v>skater</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-10-01</v>
+        <v>2026-10-04</v>
       </c>
       <c r="B17" t="str">
-        <v>2026-09-27</v>
+        <v>2026-10-04</v>
       </c>
       <c r="C17" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Pogo Hops</v>
       </c>
       <c r="D17" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="E17">
-        <v>40</v>
+        <v>Explosive</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H17" t="str">
         <v/>
       </c>
       <c r="I17" t="str">
-        <v>40×6</v>
-      </c>
-      <c r="J17">
-        <v>240</v>
+        <v>BW×10, BW×10, BW×10</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
       </c>
       <c r="K17" t="str">
-        <v>Lower back</v>
+        <v>Calves</v>
       </c>
       <c r="L17" t="str">
-        <v>Glutes, Hamstrings, Upper back</v>
+        <v>Shins</v>
       </c>
       <c r="M17" t="str">
         <v/>
       </c>
       <c r="N17" t="str">
-        <v>A-d6s5</v>
+        <v>B-d6s1</v>
       </c>
       <c r="O17" t="str">
-        <v>zercher</v>
+        <v>pogo</v>
       </c>
     </row>
     <row r="18">
@@ -5322,43 +4932,43 @@
         <v>2026-10-04</v>
       </c>
       <c r="C18" t="str">
-        <v>Cable Punch ISO hold</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="D18" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="E18">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F18">
         <v>4</v>
       </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18">
-        <v>15</v>
+      <c r="G18">
+        <v>6</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v>30×15s, 30×15s, 30×15s, 30×15s</v>
-      </c>
-      <c r="J18" t="str">
-        <v/>
+        <v>50×6, 50×6, 50×6, 50×6</v>
+      </c>
+      <c r="J18">
+        <v>1200</v>
       </c>
       <c r="K18" t="str">
-        <v>Obliques, Abs</v>
+        <v>Lower back</v>
       </c>
       <c r="L18" t="str">
-        <v>Chest, Front delts</v>
+        <v>Glutes, Hamstrings, Upper back</v>
       </c>
       <c r="M18" t="str">
         <v/>
       </c>
       <c r="N18" t="str">
-        <v>B-d6s6</v>
+        <v>B-d6s5</v>
       </c>
       <c r="O18" t="str">
-        <v>cablepunch</v>
+        <v>zercher</v>
       </c>
     </row>
     <row r="19">
@@ -5369,295 +4979,295 @@
         <v>2026-10-04</v>
       </c>
       <c r="C19" t="str">
-        <v>Cable Wrist Pulldown</v>
+        <v>Split Squat Jumps</v>
       </c>
       <c r="D19" t="str">
-        <v>Hypertrophy</v>
-      </c>
-      <c r="E19">
-        <v>33</v>
+        <v>Explosive</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H19" t="str">
         <v/>
       </c>
       <c r="I19" t="str">
-        <v>33×15, 33×15</v>
-      </c>
-      <c r="J19">
-        <v>990</v>
+        <v>BW×10, BW×10, BW×10</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
       </c>
       <c r="K19" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Quads, Glutes</v>
       </c>
       <c r="L19" t="str">
-        <v/>
+        <v>Calves, Hamstrings</v>
       </c>
       <c r="M19" t="str">
         <v/>
       </c>
       <c r="N19" t="str">
-        <v>B-d1s3</v>
+        <v>B-d6s3</v>
       </c>
       <c r="O19" t="str">
-        <v>wristpd</v>
+        <v>splitjump</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-05</v>
       </c>
       <c r="B20" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C20" t="str">
-        <v>Clean Jerk &amp; Overhead Press</v>
+        <v>Canoe Stretch</v>
       </c>
       <c r="D20" t="str">
-        <v>Explosive</v>
+        <v>Isometric</v>
       </c>
       <c r="E20">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F20">
-        <v>3</v>
-      </c>
-      <c r="G20">
-        <v>10</v>
-      </c>
-      <c r="H20" t="str">
-        <v/>
+        <v>4</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20">
+        <v>15</v>
       </c>
       <c r="I20" t="str">
-        <v>20×10, 20×10, 20×10</v>
-      </c>
-      <c r="J20">
-        <v>600</v>
+        <v>10×15s, 10×15s, 10×15s, 10×15s</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
       </c>
       <c r="K20" t="str">
-        <v/>
+        <v>Mobility</v>
       </c>
       <c r="L20" t="str">
         <v/>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N20" t="str">
-        <v>B-d5s2</v>
+        <v>B-d1s11</v>
       </c>
       <c r="O20" t="str">
-        <v>clean-jerk-overhead-press</v>
+        <v>canoe</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-05</v>
       </c>
       <c r="B21" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C21" t="str">
-        <v>Depth Drop → Broad Jump → Box Jump</v>
+        <v>DB 6 Ways</v>
       </c>
       <c r="D21" t="str">
-        <v>Explosive</v>
-      </c>
-      <c r="E21" t="str">
-        <v/>
+        <v>Strength</v>
+      </c>
+      <c r="E21">
+        <v>5</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H21" t="str">
         <v/>
       </c>
       <c r="I21" t="str">
-        <v>BW×5, BW×5, BW×5</v>
-      </c>
-      <c r="J21" t="str">
-        <v/>
+        <v>5×6, 5×6</v>
+      </c>
+      <c r="J21">
+        <v>60</v>
       </c>
       <c r="K21" t="str">
-        <v>Quads, Glutes, Calves</v>
+        <v>Front delts, Side delts</v>
       </c>
       <c r="L21" t="str">
-        <v>Hamstrings</v>
+        <v/>
       </c>
       <c r="M21" t="str">
         <v/>
       </c>
       <c r="N21" t="str">
-        <v>B-d6s4</v>
+        <v>B-d2s8</v>
       </c>
       <c r="O21" t="str">
-        <v>depthcombo</v>
+        <v>db6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-05</v>
       </c>
       <c r="B22" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C22" t="str">
-        <v>Explosive Unilateral Cable Row</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="D22" t="str">
-        <v>Explosive</v>
+        <v>Strength</v>
       </c>
       <c r="E22">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="F22">
         <v>4</v>
       </c>
       <c r="G22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H22" t="str">
         <v/>
       </c>
       <c r="I22" t="str">
-        <v>30×10, 30×10, 30×10, 30×10</v>
+        <v>200×6, 200×6, 200×6, 200×6</v>
       </c>
       <c r="J22">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="K22" t="str">
-        <v>Lats, Upper back</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="L22" t="str">
-        <v>Rear delts, Biceps</v>
+        <v/>
       </c>
       <c r="M22" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N22" t="str">
-        <v>B-d6s6</v>
+        <v>B-d1s10</v>
       </c>
       <c r="O22" t="str">
-        <v>cablerow</v>
+        <v>grip</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-05</v>
       </c>
       <c r="B23" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C23" t="str">
-        <v>Lateral Bound / Skater Hop with Stick</v>
+        <v>Plate Torso Rotation</v>
       </c>
       <c r="D23" t="str">
-        <v>Explosive</v>
-      </c>
-      <c r="E23" t="str">
-        <v/>
+        <v>Strength</v>
+      </c>
+      <c r="E23">
+        <v>10</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H23" t="str">
         <v/>
       </c>
       <c r="I23" t="str">
-        <v>BW×10, BW×10, BW×10</v>
-      </c>
-      <c r="J23" t="str">
-        <v/>
+        <v>10×6, 10×6, 10×6, 10×6</v>
+      </c>
+      <c r="J23">
+        <v>240</v>
       </c>
       <c r="K23" t="str">
-        <v>Glutes, Outer hip (abductors), Quads</v>
+        <v>Obliques</v>
       </c>
       <c r="L23" t="str">
-        <v>Inner thigh (adductors), Calves</v>
+        <v>Abs</v>
       </c>
       <c r="M23" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N23" t="str">
-        <v>B-d6s2</v>
+        <v>B-d1s4</v>
       </c>
       <c r="O23" t="str">
-        <v>skater</v>
+        <v>platerot</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-05</v>
       </c>
       <c r="B24" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C24" t="str">
-        <v>Pogo Hops</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="D24" t="str">
-        <v>Explosive</v>
-      </c>
-      <c r="E24" t="str">
-        <v/>
+        <v>Strength</v>
+      </c>
+      <c r="E24">
+        <v>50</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H24" t="str">
         <v/>
       </c>
       <c r="I24" t="str">
-        <v>BW×10, BW×10, BW×10</v>
-      </c>
-      <c r="J24" t="str">
-        <v/>
+        <v>50×6, 50×6, 50×6, 50×6</v>
+      </c>
+      <c r="J24">
+        <v>1200</v>
       </c>
       <c r="K24" t="str">
-        <v>Calves</v>
+        <v>Lower back</v>
       </c>
       <c r="L24" t="str">
-        <v>Shins</v>
+        <v>Glutes, Hamstrings, Upper back</v>
       </c>
       <c r="M24" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N24" t="str">
-        <v>B-d6s1</v>
+        <v>B-d1s8</v>
       </c>
       <c r="O24" t="str">
-        <v>pogo</v>
+        <v>zercher</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-07</v>
       </c>
       <c r="B25" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C25" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Grip Trainer</v>
       </c>
       <c r="D25" t="str">
         <v>Strength</v>
       </c>
       <c r="E25">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F25">
         <v>4</v>
@@ -5669,186 +5279,186 @@
         <v/>
       </c>
       <c r="I25" t="str">
-        <v>50×6, 50×6, 50×6, 50×6</v>
+        <v>200×6, 200×6, 200×6, 200×6</v>
       </c>
       <c r="J25">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="K25" t="str">
-        <v>Lower back</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="L25" t="str">
-        <v>Glutes, Hamstrings, Upper back</v>
+        <v/>
       </c>
       <c r="M25" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N25" t="str">
-        <v>B-d6s5</v>
+        <v>B-d2s7</v>
       </c>
       <c r="O25" t="str">
-        <v>zercher</v>
+        <v>grip</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-07</v>
       </c>
       <c r="B26" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C26" t="str">
-        <v>Sled push → pull</v>
+        <v>Hip Thrust</v>
       </c>
       <c r="D26" t="str">
-        <v>Explosive</v>
-      </c>
-      <c r="E26" t="str">
-        <v/>
+        <v>Strength</v>
+      </c>
+      <c r="E26">
+        <v>320</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H26" t="str">
         <v/>
       </c>
       <c r="I26" t="str">
-        <v>BW×3</v>
-      </c>
-      <c r="J26" t="str">
-        <v/>
+        <v>320×6, 320×6</v>
+      </c>
+      <c r="J26">
+        <v>3840</v>
       </c>
       <c r="K26" t="str">
-        <v>Quads, Glutes</v>
+        <v>Glutes</v>
       </c>
       <c r="L26" t="str">
-        <v>Lats, Upper back, Calves</v>
+        <v>Hamstrings</v>
       </c>
       <c r="M26" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N26" t="str">
-        <v>B-sled6</v>
+        <v>B-d2s5</v>
       </c>
       <c r="O26" t="str">
-        <v>sled</v>
+        <v>hipthrust</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-07</v>
       </c>
       <c r="B27" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C27" t="str">
-        <v>Split Squat Jumps</v>
+        <v>Kettlebell Leg Raise</v>
       </c>
       <c r="D27" t="str">
-        <v>Explosive</v>
-      </c>
-      <c r="E27" t="str">
-        <v/>
+        <v>Isometric</v>
+      </c>
+      <c r="E27">
+        <v>15</v>
       </c>
       <c r="F27">
         <v>3</v>
       </c>
-      <c r="G27">
-        <v>10</v>
-      </c>
-      <c r="H27" t="str">
-        <v/>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27">
+        <v>15</v>
       </c>
       <c r="I27" t="str">
-        <v>BW×10, BW×10, BW×10</v>
+        <v>15×15s, 15×15s, 15×15s</v>
       </c>
       <c r="J27" t="str">
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>Quads, Glutes</v>
+        <v>Abs, Hip flexors</v>
       </c>
       <c r="L27" t="str">
-        <v>Calves, Hamstrings</v>
+        <v/>
       </c>
       <c r="M27" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N27" t="str">
-        <v>B-d6s3</v>
+        <v>B-d1s9</v>
       </c>
       <c r="O27" t="str">
-        <v>splitjump</v>
+        <v>kbleg</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-08</v>
       </c>
       <c r="B28" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C28" t="str">
-        <v>Canoe Stretch</v>
+        <v>Seated Zercher Good Morning</v>
       </c>
       <c r="D28" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="E28">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F28">
-        <v>4</v>
-      </c>
-      <c r="G28" t="str">
-        <v/>
-      </c>
-      <c r="H28">
-        <v>15</v>
+        <v>3</v>
+      </c>
+      <c r="G28">
+        <v>6</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
       </c>
       <c r="I28" t="str">
-        <v>10×15s, 10×15s, 10×15s, 10×15s</v>
-      </c>
-      <c r="J28" t="str">
-        <v/>
+        <v>50×6, 50×6, 50×6</v>
+      </c>
+      <c r="J28">
+        <v>900</v>
       </c>
       <c r="K28" t="str">
-        <v>Mobility</v>
+        <v>Lower back</v>
       </c>
       <c r="L28" t="str">
-        <v/>
+        <v>Glutes, Hamstrings, Upper back</v>
       </c>
       <c r="M28" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N28" t="str">
-        <v>B-d1s11</v>
+        <v>B-d4s4</v>
       </c>
       <c r="O28" t="str">
-        <v>canoe</v>
+        <v>zercher</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-09</v>
       </c>
       <c r="B29" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C29" t="str">
-        <v>DB 6 Ways</v>
+        <v>Bulgarian Split Squat</v>
       </c>
       <c r="D29" t="str">
         <v>Strength</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G29">
         <v>6</v>
@@ -5857,277 +5467,277 @@
         <v/>
       </c>
       <c r="I29" t="str">
-        <v>5×6, 5×6</v>
+        <v>40×6, 40×6, 40×6, 40×6</v>
       </c>
       <c r="J29">
-        <v>60</v>
+        <v>960</v>
       </c>
       <c r="K29" t="str">
-        <v>Front delts, Side delts</v>
+        <v>Quads, Glutes</v>
       </c>
       <c r="L29" t="str">
-        <v/>
+        <v>Inner thigh (adductors), Hamstrings</v>
       </c>
       <c r="M29" t="str">
         <v/>
       </c>
       <c r="N29" t="str">
-        <v>B-d2s8</v>
+        <v>B-d4s6</v>
       </c>
       <c r="O29" t="str">
-        <v>db6</v>
+        <v>bss</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-09</v>
       </c>
       <c r="B30" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C30" t="str">
-        <v>Grip Trainer</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="D30" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="E30">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F30">
         <v>4</v>
       </c>
-      <c r="G30">
-        <v>6</v>
-      </c>
-      <c r="H30" t="str">
-        <v/>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30">
+        <v>15</v>
       </c>
       <c r="I30" t="str">
-        <v>200×6, 200×6, 200×6, 200×6</v>
-      </c>
-      <c r="J30">
-        <v>4800</v>
+        <v>50×15s, 50×15s, 50×15s, 50×15s</v>
+      </c>
+      <c r="J30" t="str">
+        <v/>
       </c>
       <c r="K30" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Rear delts</v>
       </c>
       <c r="L30" t="str">
-        <v/>
+        <v>Upper back</v>
       </c>
       <c r="M30" t="str">
         <v>From check-off</v>
       </c>
       <c r="N30" t="str">
-        <v>B-d1s10</v>
+        <v>B-d5s3</v>
       </c>
       <c r="O30" t="str">
-        <v>grip</v>
+        <v>reardelt</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-10</v>
       </c>
       <c r="B31" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C31" t="str">
-        <v>Plate Torso Rotation</v>
+        <v>Cable Punch ISO hold</v>
       </c>
       <c r="D31" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="E31">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F31">
-        <v>4</v>
-      </c>
-      <c r="G31">
-        <v>6</v>
-      </c>
-      <c r="H31" t="str">
-        <v/>
+        <v>2</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31">
+        <v>15</v>
       </c>
       <c r="I31" t="str">
-        <v>10×6, 10×6, 10×6, 10×6</v>
-      </c>
-      <c r="J31">
-        <v>240</v>
+        <v>30×15s, 30×15s</v>
+      </c>
+      <c r="J31" t="str">
+        <v/>
       </c>
       <c r="K31" t="str">
-        <v>Obliques</v>
+        <v>Obliques, Abs</v>
       </c>
       <c r="L31" t="str">
-        <v>Abs</v>
+        <v>Chest, Front delts</v>
       </c>
       <c r="M31" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N31" t="str">
-        <v>B-d1s4</v>
+        <v>B-d3s6</v>
       </c>
       <c r="O31" t="str">
-        <v>platerot</v>
+        <v>cablepunch</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-10-05</v>
+        <v>2026-10-10</v>
       </c>
       <c r="B32" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C32" t="str">
-        <v>Seated Zercher Good Morning</v>
+        <v>Duck Sled Push</v>
       </c>
       <c r="D32" t="str">
-        <v>Strength</v>
+        <v>Explosive</v>
       </c>
       <c r="E32">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H32" t="str">
         <v/>
       </c>
       <c r="I32" t="str">
-        <v>50×6, 50×6, 50×6, 50×6</v>
+        <v>20×10</v>
       </c>
       <c r="J32">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="K32" t="str">
-        <v>Lower back</v>
+        <v/>
       </c>
       <c r="L32" t="str">
-        <v>Glutes, Hamstrings, Upper back</v>
+        <v/>
       </c>
       <c r="M32" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N32" t="str">
-        <v>B-d1s8</v>
+        <v>X-muy8rvy9whc0</v>
       </c>
       <c r="O32" t="str">
-        <v>zercher</v>
+        <v>duck-sled-push</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-10</v>
       </c>
       <c r="B33" t="str">
         <v>2026-10-04</v>
       </c>
       <c r="C33" t="str">
-        <v>Face Pulls</v>
+        <v>Explosive Unilateral Cable Row</v>
       </c>
       <c r="D33" t="str">
-        <v>Strength</v>
+        <v>Explosive</v>
       </c>
       <c r="E33">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F33">
         <v>2</v>
       </c>
       <c r="G33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H33" t="str">
         <v/>
       </c>
       <c r="I33" t="str">
-        <v>27×6, 27×6</v>
+        <v>30×10, 30×10</v>
       </c>
       <c r="J33">
-        <v>324</v>
+        <v>600</v>
       </c>
       <c r="K33" t="str">
-        <v>Rear delts</v>
+        <v>Lats, Upper back</v>
       </c>
       <c r="L33" t="str">
-        <v>Upper back, Traps</v>
+        <v>Rear delts, Biceps</v>
       </c>
       <c r="M33" t="str">
         <v/>
       </c>
       <c r="N33" t="str">
-        <v>B-d2s3</v>
+        <v>B-d3s6</v>
       </c>
       <c r="O33" t="str">
-        <v>facepull</v>
+        <v>cablerow</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-12</v>
       </c>
       <c r="B34" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-11</v>
       </c>
       <c r="C34" t="str">
-        <v>Farmers Carry</v>
+        <v>Close-Grip Front Lat Pulldown</v>
       </c>
       <c r="D34" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E34">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F34">
         <v>4</v>
       </c>
       <c r="G34">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H34" t="str">
         <v/>
       </c>
       <c r="I34" t="str">
-        <v>40×6, 40×6, 40×6, 40×6</v>
+        <v>55×15, 55×15, 55×15, 55×15</v>
       </c>
       <c r="J34">
-        <v>960</v>
+        <v>3300</v>
       </c>
       <c r="K34" t="str">
-        <v>Forearms &amp; grip, Traps</v>
+        <v>Lats</v>
       </c>
       <c r="L34" t="str">
-        <v>Obliques, Abs</v>
+        <v>Biceps, Upper back, Front delts, Side delts</v>
       </c>
       <c r="M34" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N34" t="str">
-        <v>B-d2s1</v>
+        <v>Pa2gom-d1s9</v>
       </c>
       <c r="O34" t="str">
-        <v>farmers</v>
+        <v>c:fedb:Close-Grip_Front_Lat_Pulldown</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-12</v>
       </c>
       <c r="B35" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-11</v>
       </c>
       <c r="C35" t="str">
-        <v>Grip Trainer</v>
+        <v>Dumbbell Bench Press</v>
       </c>
       <c r="D35" t="str">
         <v>Strength</v>
       </c>
       <c r="E35">
-        <v>200</v>
+        <v>35</v>
       </c>
       <c r="F35">
         <v>4</v>
@@ -6139,183 +5749,183 @@
         <v/>
       </c>
       <c r="I35" t="str">
-        <v>200×6, 200×6, 200×6, 200×6</v>
+        <v>35×6, 35×6, 35×6, 35×6</v>
       </c>
       <c r="J35">
-        <v>4800</v>
+        <v>840</v>
       </c>
       <c r="K35" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Chest</v>
       </c>
       <c r="L35" t="str">
-        <v/>
+        <v>Front delts, Side delts, Triceps</v>
       </c>
       <c r="M35" t="str">
         <v>From check-off</v>
       </c>
       <c r="N35" t="str">
-        <v>B-d2s7</v>
+        <v>Pa2gom-d1s7</v>
       </c>
       <c r="O35" t="str">
-        <v>grip</v>
+        <v>c:fedb:Dumbbell_Bench_Press</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-12</v>
       </c>
       <c r="B36" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-11</v>
       </c>
       <c r="C36" t="str">
-        <v>Hip Thrust</v>
+        <v>Hack Squat</v>
       </c>
       <c r="D36" t="str">
-        <v>Strength</v>
+        <v>Hypertrophy</v>
       </c>
       <c r="E36">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G36">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H36" t="str">
         <v/>
       </c>
       <c r="I36" t="str">
-        <v>320×6, 320×6</v>
+        <v>270×15, 270×15, 270×15, 270×15</v>
       </c>
       <c r="J36">
-        <v>3840</v>
+        <v>16200</v>
       </c>
       <c r="K36" t="str">
-        <v>Glutes</v>
+        <v>Quads</v>
       </c>
       <c r="L36" t="str">
-        <v>Hamstrings</v>
+        <v>Calves, Glutes, Hamstrings</v>
       </c>
       <c r="M36" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N36" t="str">
-        <v>B-d2s5</v>
+        <v>Pa2gom-d1s2</v>
       </c>
       <c r="O36" t="str">
-        <v>hipthrust</v>
+        <v>c:fedb:Hack_Squat</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-12</v>
       </c>
       <c r="B37" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-11</v>
       </c>
       <c r="C37" t="str">
-        <v>Kettlebell Leg Raise</v>
+        <v>Seated Good Mornings</v>
       </c>
       <c r="D37" t="str">
-        <v>Isometric</v>
+        <v>Strength</v>
       </c>
       <c r="E37">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F37">
-        <v>3</v>
-      </c>
-      <c r="G37" t="str">
-        <v/>
-      </c>
-      <c r="H37">
-        <v>15</v>
+        <v>4</v>
+      </c>
+      <c r="G37">
+        <v>6</v>
+      </c>
+      <c r="H37" t="str">
+        <v/>
       </c>
       <c r="I37" t="str">
-        <v>15×15s, 15×15s, 15×15s</v>
-      </c>
-      <c r="J37" t="str">
-        <v/>
+        <v>45×6, 45×6, 45×6, 45×6</v>
+      </c>
+      <c r="J37">
+        <v>1080</v>
       </c>
       <c r="K37" t="str">
-        <v>Abs, Hip flexors</v>
+        <v>Lower back</v>
       </c>
       <c r="L37" t="str">
-        <v/>
+        <v>Glutes</v>
       </c>
       <c r="M37" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N37" t="str">
-        <v>B-d1s9</v>
+        <v>Pa2gom-d1s7</v>
       </c>
       <c r="O37" t="str">
-        <v>kbleg</v>
+        <v>c:fedb:Seated_Good_Mornings</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-12</v>
       </c>
       <c r="B38" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-11</v>
       </c>
       <c r="C38" t="str">
-        <v>Overhead Tricep Extension</v>
+        <v>Side Rear Delt Fly</v>
       </c>
       <c r="D38" t="str">
-        <v>Strength</v>
+        <v>Isometric</v>
       </c>
       <c r="E38">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="F38">
-        <v>2</v>
-      </c>
-      <c r="G38">
-        <v>6</v>
-      </c>
-      <c r="H38" t="str">
-        <v/>
+        <v>4</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38">
+        <v>15</v>
       </c>
       <c r="I38" t="str">
-        <v>17×6, 17×6</v>
-      </c>
-      <c r="J38">
-        <v>204</v>
+        <v>50×15s, 50×15s, 60×15s, 60×15s</v>
+      </c>
+      <c r="J38" t="str">
+        <v/>
       </c>
       <c r="K38" t="str">
-        <v>Triceps</v>
+        <v>Rear delts</v>
       </c>
       <c r="L38" t="str">
-        <v/>
+        <v>Upper back</v>
       </c>
       <c r="M38" t="str">
         <v/>
       </c>
       <c r="N38" t="str">
-        <v>B-d2s2</v>
+        <v>Pa2gom-d2s4</v>
       </c>
       <c r="O38" t="str">
-        <v>ohtri</v>
+        <v>reardelt</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-12</v>
       </c>
       <c r="B39" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-11</v>
       </c>
       <c r="C39" t="str">
-        <v>Seated Cable Crunch</v>
+        <v>Thigh Abductor</v>
       </c>
       <c r="D39" t="str">
         <v>Strength</v>
       </c>
       <c r="E39">
-        <v>44</v>
+        <v>180</v>
       </c>
       <c r="F39">
         <v>4</v>
@@ -6327,931 +5937,85 @@
         <v/>
       </c>
       <c r="I39" t="str">
-        <v>44×6, 44×6, 44×6, 44×6</v>
+        <v>180×6, 180×6, 180×6, 180×6</v>
       </c>
       <c r="J39">
-        <v>1056</v>
+        <v>4320</v>
       </c>
       <c r="K39" t="str">
-        <v>Abs</v>
+        <v>Outer hip (abductors)</v>
       </c>
       <c r="L39" t="str">
-        <v/>
+        <v>Glutes</v>
       </c>
       <c r="M39" t="str">
-        <v/>
+        <v>From check-off</v>
       </c>
       <c r="N39" t="str">
-        <v>B-xmuy1nsai5fs</v>
+        <v>Pa2gom-d1s4</v>
       </c>
       <c r="O39" t="str">
-        <v>seated-cable-crunch</v>
+        <v>c:fedb:Thigh_Abductor</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2026-10-07</v>
+        <v>2026-10-12</v>
       </c>
       <c r="B40" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-11</v>
       </c>
       <c r="C40" t="str">
-        <v>Zottman Curls</v>
+        <v>Thigh Adductor</v>
       </c>
       <c r="D40" t="str">
-        <v>Hypertrophy</v>
+        <v>Strength</v>
       </c>
       <c r="E40">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="F40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G40">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H40" t="str">
         <v/>
       </c>
       <c r="I40" t="str">
-        <v>15×15, 15×15, 15×15</v>
+        <v>130×6, 130×6, 140×6, 140×6</v>
       </c>
       <c r="J40">
-        <v>675</v>
+        <v>3240</v>
       </c>
       <c r="K40" t="str">
-        <v>Biceps, Forearms &amp; grip</v>
+        <v>Inner thigh (adductors)</v>
       </c>
       <c r="L40" t="str">
-        <v/>
+        <v>Glutes, Hamstrings</v>
       </c>
       <c r="M40" t="str">
-        <v>From check-off</v>
+        <v/>
       </c>
       <c r="N40" t="str">
-        <v>B-d1s9</v>
+        <v>Pa2gom-d1s5</v>
       </c>
       <c r="O40" t="str">
-        <v>zottman</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>2026-10-08</v>
-      </c>
-      <c r="B41" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="C41" t="str">
-        <v>Cable Wrist Pulldown</v>
-      </c>
-      <c r="D41" t="str">
-        <v>Hypertrophy</v>
-      </c>
-      <c r="E41">
-        <v>44</v>
-      </c>
-      <c r="F41">
-        <v>4</v>
-      </c>
-      <c r="G41">
-        <v>6</v>
-      </c>
-      <c r="H41" t="str">
-        <v/>
-      </c>
-      <c r="I41" t="str">
-        <v>44×6, 44×6, 44×6, 44×6</v>
-      </c>
-      <c r="J41">
-        <v>1056</v>
-      </c>
-      <c r="K41" t="str">
-        <v>Forearms &amp; grip</v>
-      </c>
-      <c r="L41" t="str">
-        <v/>
-      </c>
-      <c r="M41" t="str">
-        <v/>
-      </c>
-      <c r="N41" t="str">
-        <v>B-xmuy1rdg3uct</v>
-      </c>
-      <c r="O41" t="str">
-        <v>wristpd</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>2026-10-08</v>
-      </c>
-      <c r="B42" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="C42" t="str">
-        <v>Seated Cable Crunch</v>
-      </c>
-      <c r="D42" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="E42">
-        <v>44</v>
-      </c>
-      <c r="F42">
-        <v>4</v>
-      </c>
-      <c r="G42">
-        <v>6</v>
-      </c>
-      <c r="H42" t="str">
-        <v/>
-      </c>
-      <c r="I42" t="str">
-        <v>44×6, 44×6, 44×6, 44×6</v>
-      </c>
-      <c r="J42">
-        <v>1056</v>
-      </c>
-      <c r="K42" t="str">
-        <v>Abs</v>
-      </c>
-      <c r="L42" t="str">
-        <v/>
-      </c>
-      <c r="M42" t="str">
-        <v>From check-off</v>
-      </c>
-      <c r="N42" t="str">
-        <v>B-xmuy1rdg3uct</v>
-      </c>
-      <c r="O42" t="str">
-        <v>seated-cable-crunch</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>2026-10-08</v>
-      </c>
-      <c r="B43" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="C43" t="str">
-        <v>Seated Zercher Good Morning</v>
-      </c>
-      <c r="D43" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="E43">
-        <v>50</v>
-      </c>
-      <c r="F43">
-        <v>3</v>
-      </c>
-      <c r="G43">
-        <v>6</v>
-      </c>
-      <c r="H43" t="str">
-        <v/>
-      </c>
-      <c r="I43" t="str">
-        <v>50×6, 50×6, 50×6</v>
-      </c>
-      <c r="J43">
-        <v>900</v>
-      </c>
-      <c r="K43" t="str">
-        <v>Lower back</v>
-      </c>
-      <c r="L43" t="str">
-        <v>Glutes, Hamstrings, Upper back</v>
-      </c>
-      <c r="M43" t="str">
-        <v/>
-      </c>
-      <c r="N43" t="str">
-        <v>B-d4s4</v>
-      </c>
-      <c r="O43" t="str">
-        <v>zercher</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>2026-10-09</v>
-      </c>
-      <c r="B44" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="C44" t="str">
-        <v>Bulgarian Split Squat</v>
-      </c>
-      <c r="D44" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="E44">
-        <v>40</v>
-      </c>
-      <c r="F44">
-        <v>4</v>
-      </c>
-      <c r="G44">
-        <v>6</v>
-      </c>
-      <c r="H44" t="str">
-        <v/>
-      </c>
-      <c r="I44" t="str">
-        <v>40×6, 40×6, 40×6, 40×6</v>
-      </c>
-      <c r="J44">
-        <v>960</v>
-      </c>
-      <c r="K44" t="str">
-        <v>Quads, Glutes</v>
-      </c>
-      <c r="L44" t="str">
-        <v>Inner thigh (adductors), Hamstrings</v>
-      </c>
-      <c r="M44" t="str">
-        <v/>
-      </c>
-      <c r="N44" t="str">
-        <v>B-d4s6</v>
-      </c>
-      <c r="O44" t="str">
-        <v>bss</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>2026-10-09</v>
-      </c>
-      <c r="B45" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="C45" t="str">
-        <v>Farmers Carry</v>
-      </c>
-      <c r="D45" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="E45">
-        <v>40</v>
-      </c>
-      <c r="F45">
-        <v>4</v>
-      </c>
-      <c r="G45">
-        <v>6</v>
-      </c>
-      <c r="H45" t="str">
-        <v/>
-      </c>
-      <c r="I45" t="str">
-        <v>40×6, 40×6, 40×6, 40×6</v>
-      </c>
-      <c r="J45">
-        <v>960</v>
-      </c>
-      <c r="K45" t="str">
-        <v>Forearms &amp; grip, Traps</v>
-      </c>
-      <c r="L45" t="str">
-        <v>Obliques, Abs</v>
-      </c>
-      <c r="M45" t="str">
-        <v>From check-off</v>
-      </c>
-      <c r="N45" t="str">
-        <v>B-d4s1</v>
-      </c>
-      <c r="O45" t="str">
-        <v>farmers</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>2026-10-09</v>
-      </c>
-      <c r="B46" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="C46" t="str">
-        <v>Prone Leg Curl</v>
-      </c>
-      <c r="D46" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="E46">
-        <v>50</v>
-      </c>
-      <c r="F46">
-        <v>4</v>
-      </c>
-      <c r="G46">
-        <v>6</v>
-      </c>
-      <c r="H46" t="str">
-        <v/>
-      </c>
-      <c r="I46" t="str">
-        <v>50×6, 50×6, 50×6, 50×6</v>
-      </c>
-      <c r="J46">
-        <v>1200</v>
-      </c>
-      <c r="K46" t="str">
-        <v>Hamstrings</v>
-      </c>
-      <c r="L46" t="str">
-        <v>Calves</v>
-      </c>
-      <c r="M46" t="str">
-        <v>From check-off</v>
-      </c>
-      <c r="N46" t="str">
-        <v>B-d4s6</v>
-      </c>
-      <c r="O46" t="str">
-        <v>legcurl</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>2026-10-09</v>
-      </c>
-      <c r="B47" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="C47" t="str">
-        <v>Side Rear Delt Fly</v>
-      </c>
-      <c r="D47" t="str">
-        <v>Isometric</v>
-      </c>
-      <c r="E47">
-        <v>50</v>
-      </c>
-      <c r="F47">
-        <v>4</v>
-      </c>
-      <c r="G47" t="str">
-        <v/>
-      </c>
-      <c r="H47">
-        <v>15</v>
-      </c>
-      <c r="I47" t="str">
-        <v>50×15s, 50×15s, 50×15s, 50×15s</v>
-      </c>
-      <c r="J47" t="str">
-        <v/>
-      </c>
-      <c r="K47" t="str">
-        <v>Rear delts</v>
-      </c>
-      <c r="L47" t="str">
-        <v>Upper back</v>
-      </c>
-      <c r="M47" t="str">
-        <v>From check-off</v>
-      </c>
-      <c r="N47" t="str">
-        <v>B-d5s3</v>
-      </c>
-      <c r="O47" t="str">
-        <v>reardelt</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>2026-10-10</v>
-      </c>
-      <c r="B48" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="C48" t="str">
-        <v>Cable Punch ISO hold</v>
-      </c>
-      <c r="D48" t="str">
-        <v>Isometric</v>
-      </c>
-      <c r="E48">
-        <v>30</v>
-      </c>
-      <c r="F48">
-        <v>2</v>
-      </c>
-      <c r="G48" t="str">
-        <v/>
-      </c>
-      <c r="H48">
-        <v>15</v>
-      </c>
-      <c r="I48" t="str">
-        <v>30×15s, 30×15s</v>
-      </c>
-      <c r="J48" t="str">
-        <v/>
-      </c>
-      <c r="K48" t="str">
-        <v>Obliques, Abs</v>
-      </c>
-      <c r="L48" t="str">
-        <v>Chest, Front delts</v>
-      </c>
-      <c r="M48" t="str">
-        <v/>
-      </c>
-      <c r="N48" t="str">
-        <v>B-d3s6</v>
-      </c>
-      <c r="O48" t="str">
-        <v>cablepunch</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>2026-10-10</v>
-      </c>
-      <c r="B49" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="C49" t="str">
-        <v>Duck Sled Push</v>
-      </c>
-      <c r="D49" t="str">
-        <v>Explosive</v>
-      </c>
-      <c r="E49">
-        <v>20</v>
-      </c>
-      <c r="F49">
-        <v>1</v>
-      </c>
-      <c r="G49">
-        <v>10</v>
-      </c>
-      <c r="H49" t="str">
-        <v/>
-      </c>
-      <c r="I49" t="str">
-        <v>20×10</v>
-      </c>
-      <c r="J49">
-        <v>200</v>
-      </c>
-      <c r="K49" t="str">
-        <v/>
-      </c>
-      <c r="L49" t="str">
-        <v/>
-      </c>
-      <c r="M49" t="str">
-        <v/>
-      </c>
-      <c r="N49" t="str">
-        <v>X-muy8rvy9whc0</v>
-      </c>
-      <c r="O49" t="str">
-        <v>duck-sled-push</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>2026-10-10</v>
-      </c>
-      <c r="B50" t="str">
-        <v>2026-10-04</v>
-      </c>
-      <c r="C50" t="str">
-        <v>Explosive Unilateral Cable Row</v>
-      </c>
-      <c r="D50" t="str">
-        <v>Explosive</v>
-      </c>
-      <c r="E50">
-        <v>30</v>
-      </c>
-      <c r="F50">
-        <v>2</v>
-      </c>
-      <c r="G50">
-        <v>10</v>
-      </c>
-      <c r="H50" t="str">
-        <v/>
-      </c>
-      <c r="I50" t="str">
-        <v>30×10, 30×10</v>
-      </c>
-      <c r="J50">
-        <v>600</v>
-      </c>
-      <c r="K50" t="str">
-        <v>Lats, Upper back</v>
-      </c>
-      <c r="L50" t="str">
-        <v>Rear delts, Biceps</v>
-      </c>
-      <c r="M50" t="str">
-        <v/>
-      </c>
-      <c r="N50" t="str">
-        <v>B-d3s6</v>
-      </c>
-      <c r="O50" t="str">
-        <v>cablerow</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>2026-10-12</v>
-      </c>
-      <c r="B51" t="str">
-        <v>2026-10-11</v>
-      </c>
-      <c r="C51" t="str">
-        <v>Cable Wrist Pulldown</v>
-      </c>
-      <c r="D51" t="str">
-        <v>Hypertrophy</v>
-      </c>
-      <c r="E51">
-        <v>44</v>
-      </c>
-      <c r="F51">
-        <v>4</v>
-      </c>
-      <c r="G51">
-        <v>15</v>
-      </c>
-      <c r="H51" t="str">
-        <v/>
-      </c>
-      <c r="I51" t="str">
-        <v>44×15, 44×15, 44×15, 44×15</v>
-      </c>
-      <c r="J51">
-        <v>2640</v>
-      </c>
-      <c r="K51" t="str">
-        <v>Forearms &amp; grip</v>
-      </c>
-      <c r="L51" t="str">
-        <v/>
-      </c>
-      <c r="M51" t="str">
-        <v/>
-      </c>
-      <c r="N51" t="str">
-        <v>Pa2gom-d1s9</v>
-      </c>
-      <c r="O51" t="str">
-        <v>wristpd</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>2026-10-12</v>
-      </c>
-      <c r="B52" t="str">
-        <v>2026-10-11</v>
-      </c>
-      <c r="C52" t="str">
-        <v>Close-Grip Front Lat Pulldown</v>
-      </c>
-      <c r="D52" t="str">
-        <v>Hypertrophy</v>
-      </c>
-      <c r="E52">
-        <v>55</v>
-      </c>
-      <c r="F52">
-        <v>4</v>
-      </c>
-      <c r="G52">
-        <v>15</v>
-      </c>
-      <c r="H52" t="str">
-        <v/>
-      </c>
-      <c r="I52" t="str">
-        <v>55×15, 55×15, 55×15, 55×15</v>
-      </c>
-      <c r="J52">
-        <v>3300</v>
-      </c>
-      <c r="K52" t="str">
-        <v>Lats</v>
-      </c>
-      <c r="L52" t="str">
-        <v>Biceps, Upper back, Front delts, Side delts</v>
-      </c>
-      <c r="M52" t="str">
-        <v/>
-      </c>
-      <c r="N52" t="str">
-        <v>Pa2gom-d1s9</v>
-      </c>
-      <c r="O52" t="str">
-        <v>c:fedb:Close-Grip_Front_Lat_Pulldown</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>2026-10-12</v>
-      </c>
-      <c r="B53" t="str">
-        <v>2026-10-11</v>
-      </c>
-      <c r="C53" t="str">
-        <v>Dumbbell Bench Press</v>
-      </c>
-      <c r="D53" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="E53">
-        <v>35</v>
-      </c>
-      <c r="F53">
-        <v>4</v>
-      </c>
-      <c r="G53">
-        <v>6</v>
-      </c>
-      <c r="H53" t="str">
-        <v/>
-      </c>
-      <c r="I53" t="str">
-        <v>35×6, 35×6, 35×6, 35×6</v>
-      </c>
-      <c r="J53">
-        <v>840</v>
-      </c>
-      <c r="K53" t="str">
-        <v>Chest</v>
-      </c>
-      <c r="L53" t="str">
-        <v>Front delts, Side delts, Triceps</v>
-      </c>
-      <c r="M53" t="str">
-        <v>From check-off</v>
-      </c>
-      <c r="N53" t="str">
-        <v>Pa2gom-d1s7</v>
-      </c>
-      <c r="O53" t="str">
-        <v>c:fedb:Dumbbell_Bench_Press</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>2026-10-12</v>
-      </c>
-      <c r="B54" t="str">
-        <v>2026-10-11</v>
-      </c>
-      <c r="C54" t="str">
-        <v>Hack Squat</v>
-      </c>
-      <c r="D54" t="str">
-        <v>Hypertrophy</v>
-      </c>
-      <c r="E54">
-        <v>270</v>
-      </c>
-      <c r="F54">
-        <v>4</v>
-      </c>
-      <c r="G54">
-        <v>15</v>
-      </c>
-      <c r="H54" t="str">
-        <v/>
-      </c>
-      <c r="I54" t="str">
-        <v>270×15, 270×15, 270×15, 270×15</v>
-      </c>
-      <c r="J54">
-        <v>16200</v>
-      </c>
-      <c r="K54" t="str">
-        <v>Quads</v>
-      </c>
-      <c r="L54" t="str">
-        <v>Calves, Glutes, Hamstrings</v>
-      </c>
-      <c r="M54" t="str">
-        <v>From check-off</v>
-      </c>
-      <c r="N54" t="str">
-        <v>Pa2gom-d1s2</v>
-      </c>
-      <c r="O54" t="str">
-        <v>c:fedb:Hack_Squat</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>2026-10-12</v>
-      </c>
-      <c r="B55" t="str">
-        <v>2026-10-11</v>
-      </c>
-      <c r="C55" t="str">
-        <v>Seated Good Mornings</v>
-      </c>
-      <c r="D55" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="E55">
-        <v>45</v>
-      </c>
-      <c r="F55">
-        <v>4</v>
-      </c>
-      <c r="G55">
-        <v>6</v>
-      </c>
-      <c r="H55" t="str">
-        <v/>
-      </c>
-      <c r="I55" t="str">
-        <v>45×6, 45×6, 45×6, 45×6</v>
-      </c>
-      <c r="J55">
-        <v>1080</v>
-      </c>
-      <c r="K55" t="str">
-        <v>Lower back</v>
-      </c>
-      <c r="L55" t="str">
-        <v>Glutes</v>
-      </c>
-      <c r="M55" t="str">
-        <v/>
-      </c>
-      <c r="N55" t="str">
-        <v>Pa2gom-d1s7</v>
-      </c>
-      <c r="O55" t="str">
-        <v>c:fedb:Seated_Good_Mornings</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>2026-10-12</v>
-      </c>
-      <c r="B56" t="str">
-        <v>2026-10-11</v>
-      </c>
-      <c r="C56" t="str">
-        <v>Side Rear Delt Fly</v>
-      </c>
-      <c r="D56" t="str">
-        <v>Isometric</v>
-      </c>
-      <c r="E56">
-        <v>60</v>
-      </c>
-      <c r="F56">
-        <v>4</v>
-      </c>
-      <c r="G56" t="str">
-        <v/>
-      </c>
-      <c r="H56">
-        <v>15</v>
-      </c>
-      <c r="I56" t="str">
-        <v>50×15s, 50×15s, 60×15s, 60×15s</v>
-      </c>
-      <c r="J56" t="str">
-        <v/>
-      </c>
-      <c r="K56" t="str">
-        <v>Rear delts</v>
-      </c>
-      <c r="L56" t="str">
-        <v>Upper back</v>
-      </c>
-      <c r="M56" t="str">
-        <v/>
-      </c>
-      <c r="N56" t="str">
-        <v>Pa2gom-d2s4</v>
-      </c>
-      <c r="O56" t="str">
-        <v>reardelt</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>2026-10-12</v>
-      </c>
-      <c r="B57" t="str">
-        <v>2026-10-11</v>
-      </c>
-      <c r="C57" t="str">
-        <v>Thigh Abductor</v>
-      </c>
-      <c r="D57" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="E57">
-        <v>180</v>
-      </c>
-      <c r="F57">
-        <v>4</v>
-      </c>
-      <c r="G57">
-        <v>6</v>
-      </c>
-      <c r="H57" t="str">
-        <v/>
-      </c>
-      <c r="I57" t="str">
-        <v>180×6, 180×6, 180×6, 180×6</v>
-      </c>
-      <c r="J57">
-        <v>4320</v>
-      </c>
-      <c r="K57" t="str">
-        <v>Outer hip (abductors)</v>
-      </c>
-      <c r="L57" t="str">
-        <v>Glutes</v>
-      </c>
-      <c r="M57" t="str">
-        <v>From check-off</v>
-      </c>
-      <c r="N57" t="str">
-        <v>Pa2gom-d1s4</v>
-      </c>
-      <c r="O57" t="str">
-        <v>c:fedb:Thigh_Abductor</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>2026-10-12</v>
-      </c>
-      <c r="B58" t="str">
-        <v>2026-10-11</v>
-      </c>
-      <c r="C58" t="str">
-        <v>Thigh Adductor</v>
-      </c>
-      <c r="D58" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="E58">
-        <v>140</v>
-      </c>
-      <c r="F58">
-        <v>4</v>
-      </c>
-      <c r="G58">
-        <v>6</v>
-      </c>
-      <c r="H58" t="str">
-        <v/>
-      </c>
-      <c r="I58" t="str">
-        <v>130×6, 130×6, 140×6, 140×6</v>
-      </c>
-      <c r="J58">
-        <v>3240</v>
-      </c>
-      <c r="K58" t="str">
-        <v>Inner thigh (adductors)</v>
-      </c>
-      <c r="L58" t="str">
-        <v>Glutes, Hamstrings</v>
-      </c>
-      <c r="M58" t="str">
-        <v/>
-      </c>
-      <c r="N58" t="str">
-        <v>Pa2gom-d1s5</v>
-      </c>
-      <c r="O58" t="str">
         <v>c:fedb:Thigh_Adductor</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O58"/>
+  <autoFilter ref="A1:O40"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O58"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O40"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E45"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -7282,16 +6046,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B2" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Glutes</v>
       </c>
       <c r="C2">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="3">
@@ -7299,16 +6063,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B3" t="str">
-        <v>Glutes</v>
+        <v>Lower back</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>9</v>
-      </c>
-      <c r="E3">
-        <v>10.5</v>
       </c>
     </row>
     <row r="4">
@@ -7316,16 +6080,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B4" t="str">
-        <v>Lower back</v>
+        <v>Upper back</v>
       </c>
       <c r="C4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="5">
@@ -7333,16 +6097,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B5" t="str">
-        <v>Upper back</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
         <v>0</v>
       </c>
-      <c r="D5">
-        <v>17</v>
-      </c>
       <c r="E5">
-        <v>8.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -7350,7 +6114,7 @@
         <v>2026-09-27</v>
       </c>
       <c r="B6" t="str">
-        <v>Quads</v>
+        <v>Rear delts</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -7367,16 +6131,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B7" t="str">
-        <v>Rear delts</v>
+        <v>Hamstrings</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="8">
@@ -7384,16 +6148,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B8" t="str">
-        <v>Hamstrings</v>
+        <v>Obliques</v>
       </c>
       <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
         <v>0</v>
       </c>
-      <c r="D8">
-        <v>15</v>
-      </c>
       <c r="E8">
-        <v>7.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -7404,13 +6168,13 @@
         <v>Abs</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -7418,16 +6182,16 @@
         <v>2026-09-27</v>
       </c>
       <c r="B10" t="str">
-        <v>Obliques</v>
+        <v>Hip flexors</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -7435,50 +6199,50 @@
         <v>2026-09-27</v>
       </c>
       <c r="B11" t="str">
-        <v>Hip flexors</v>
+        <v>Traps</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-09-27</v>
+        <v>2026-10-04</v>
       </c>
       <c r="B12" t="str">
-        <v>Biceps</v>
+        <v>Glutes</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-09-27</v>
+        <v>2026-10-04</v>
       </c>
       <c r="B13" t="str">
-        <v>Traps</v>
+        <v>Upper back</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="14">
@@ -7486,16 +6250,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B14" t="str">
-        <v>Forearms &amp; grip</v>
+        <v>Quads</v>
       </c>
       <c r="C14">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -7503,16 +6267,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B15" t="str">
-        <v>Abs</v>
+        <v>Hamstrings</v>
       </c>
       <c r="C15">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E15">
-        <v>23</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="16">
@@ -7520,16 +6284,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B16" t="str">
-        <v>Glutes</v>
+        <v>Abs</v>
       </c>
       <c r="C16">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16">
         <v>11</v>
-      </c>
-      <c r="E16">
-        <v>21.5</v>
       </c>
     </row>
     <row r="17">
@@ -7537,16 +6301,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B17" t="str">
-        <v>Hamstrings</v>
+        <v>Lower back</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D17">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>15.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -7554,16 +6318,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B18" t="str">
-        <v>Upper back</v>
+        <v>Obliques</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D18">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -7571,16 +6335,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B19" t="str">
-        <v>Quads</v>
+        <v>Calves</v>
       </c>
       <c r="C19">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E19">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -7588,16 +6352,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B20" t="str">
-        <v>Obliques</v>
+        <v>Forearms &amp; grip</v>
       </c>
       <c r="C20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
         <v>8</v>
-      </c>
-      <c r="E20">
-        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -7605,16 +6369,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B21" t="str">
-        <v>Calves</v>
+        <v>Rear delts</v>
       </c>
       <c r="C21">
+        <v>4</v>
+      </c>
+      <c r="D21">
         <v>6</v>
       </c>
-      <c r="D21">
-        <v>11</v>
-      </c>
       <c r="E21">
-        <v>11.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -7622,16 +6386,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B22" t="str">
-        <v>Lower back</v>
+        <v>Lats</v>
       </c>
       <c r="C22">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -7639,16 +6403,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B23" t="str">
-        <v>Rear delts</v>
+        <v>Front delts</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D23">
         <v>6</v>
       </c>
       <c r="E23">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -7656,16 +6420,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B24" t="str">
-        <v>Traps</v>
+        <v>Inner thigh (adductors)</v>
       </c>
       <c r="C24">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E24">
-        <v>9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="25">
@@ -7673,16 +6437,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B25" t="str">
-        <v>Lats</v>
+        <v>Chest</v>
       </c>
       <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
         <v>6</v>
       </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
       <c r="E25">
-        <v>6.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -7693,13 +6457,13 @@
         <v>Biceps</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>6</v>
       </c>
       <c r="E26">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -7707,16 +6471,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B27" t="str">
-        <v>Front delts</v>
+        <v>Hip flexors</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -7724,16 +6488,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B28" t="str">
-        <v>Inner thigh (adductors)</v>
+        <v>Outer hip (abductors)</v>
       </c>
       <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28">
         <v>0</v>
       </c>
-      <c r="D28">
-        <v>7</v>
-      </c>
       <c r="E28">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -7741,16 +6505,16 @@
         <v>2026-10-04</v>
       </c>
       <c r="B29" t="str">
-        <v>Chest</v>
+        <v>Side delts</v>
       </c>
       <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
         <v>0</v>
       </c>
-      <c r="D29">
-        <v>6</v>
-      </c>
       <c r="E29">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -7758,84 +6522,84 @@
         <v>2026-10-04</v>
       </c>
       <c r="B30" t="str">
-        <v>Hip flexors</v>
+        <v>Shins</v>
       </c>
       <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
         <v>3</v>
       </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
       <c r="E30">
-        <v>3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-11</v>
       </c>
       <c r="B31" t="str">
-        <v>Outer hip (abductors)</v>
+        <v>Glutes</v>
       </c>
       <c r="C31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-11</v>
       </c>
       <c r="B32" t="str">
-        <v>Side delts</v>
+        <v>Lats</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-11</v>
       </c>
       <c r="B33" t="str">
-        <v>Triceps</v>
+        <v>Upper back</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-10-04</v>
+        <v>2026-10-11</v>
       </c>
       <c r="B34" t="str">
-        <v>Shins</v>
+        <v>Front delts</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E34">
-        <v>1.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -7843,16 +6607,16 @@
         <v>2026-10-11</v>
       </c>
       <c r="B35" t="str">
-        <v>Glutes</v>
+        <v>Side delts</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E35">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -7860,7 +6624,7 @@
         <v>2026-10-11</v>
       </c>
       <c r="B36" t="str">
-        <v>Lats</v>
+        <v>Chest</v>
       </c>
       <c r="C36">
         <v>4</v>
@@ -7877,13 +6641,13 @@
         <v>2026-10-11</v>
       </c>
       <c r="B37" t="str">
-        <v>Upper back</v>
+        <v>Quads</v>
       </c>
       <c r="C37">
+        <v>4</v>
+      </c>
+      <c r="D37">
         <v>0</v>
-      </c>
-      <c r="D37">
-        <v>8</v>
       </c>
       <c r="E37">
         <v>4</v>
@@ -7894,7 +6658,7 @@
         <v>2026-10-11</v>
       </c>
       <c r="B38" t="str">
-        <v>Front delts</v>
+        <v>Hamstrings</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -7911,13 +6675,13 @@
         <v>2026-10-11</v>
       </c>
       <c r="B39" t="str">
-        <v>Side delts</v>
+        <v>Lower back</v>
       </c>
       <c r="C39">
+        <v>4</v>
+      </c>
+      <c r="D39">
         <v>0</v>
-      </c>
-      <c r="D39">
-        <v>8</v>
       </c>
       <c r="E39">
         <v>4</v>
@@ -7928,7 +6692,7 @@
         <v>2026-10-11</v>
       </c>
       <c r="B40" t="str">
-        <v>Chest</v>
+        <v>Outer hip (abductors)</v>
       </c>
       <c r="C40">
         <v>4</v>
@@ -7945,7 +6709,7 @@
         <v>2026-10-11</v>
       </c>
       <c r="B41" t="str">
-        <v>Quads</v>
+        <v>Inner thigh (adductors)</v>
       </c>
       <c r="C41">
         <v>4</v>
@@ -7962,13 +6726,13 @@
         <v>2026-10-11</v>
       </c>
       <c r="B42" t="str">
-        <v>Hamstrings</v>
+        <v>Rear delts</v>
       </c>
       <c r="C42">
+        <v>4</v>
+      </c>
+      <c r="D42">
         <v>0</v>
-      </c>
-      <c r="D42">
-        <v>8</v>
       </c>
       <c r="E42">
         <v>4</v>
@@ -7979,16 +6743,16 @@
         <v>2026-10-11</v>
       </c>
       <c r="B43" t="str">
-        <v>Lower back</v>
+        <v>Biceps</v>
       </c>
       <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
         <v>4</v>
       </c>
-      <c r="D43">
-        <v>0</v>
-      </c>
       <c r="E43">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -7996,16 +6760,16 @@
         <v>2026-10-11</v>
       </c>
       <c r="B44" t="str">
-        <v>Outer hip (abductors)</v>
+        <v>Triceps</v>
       </c>
       <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
         <v>4</v>
       </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
       <c r="E44">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -8013,107 +6777,22 @@
         <v>2026-10-11</v>
       </c>
       <c r="B45" t="str">
-        <v>Inner thigh (adductors)</v>
+        <v>Calves</v>
       </c>
       <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
         <v>4</v>
       </c>
-      <c r="D45">
-        <v>0</v>
-      </c>
       <c r="E45">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>2026-10-11</v>
-      </c>
-      <c r="B46" t="str">
-        <v>Rear delts</v>
-      </c>
-      <c r="C46">
-        <v>4</v>
-      </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
-      <c r="E46">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>2026-10-11</v>
-      </c>
-      <c r="B47" t="str">
-        <v>Forearms &amp; grip</v>
-      </c>
-      <c r="C47">
-        <v>4</v>
-      </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
-      <c r="E47">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>2026-10-11</v>
-      </c>
-      <c r="B48" t="str">
-        <v>Biceps</v>
-      </c>
-      <c r="C48">
-        <v>0</v>
-      </c>
-      <c r="D48">
-        <v>4</v>
-      </c>
-      <c r="E48">
         <v>2</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>2026-10-11</v>
-      </c>
-      <c r="B49" t="str">
-        <v>Triceps</v>
-      </c>
-      <c r="C49">
-        <v>0</v>
-      </c>
-      <c r="D49">
-        <v>4</v>
-      </c>
-      <c r="E49">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>2026-10-11</v>
-      </c>
-      <c r="B50" t="str">
-        <v>Calves</v>
-      </c>
-      <c r="C50">
-        <v>0</v>
-      </c>
-      <c r="D50">
-        <v>4</v>
-      </c>
-      <c r="E50">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E50"/>
+  <autoFilter ref="A1:E45"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E45"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -8169,19 +6848,19 @@
         <v>5</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G2">
         <v>96</v>
       </c>
       <c r="H2">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -8195,19 +6874,19 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -8233,7 +6912,7 @@
         <v>11</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -8675,7 +7354,7 @@
         <v>Exported</v>
       </c>
       <c r="B44" t="str">
-        <v>2026-10-13T00:12:39.307Z</v>
+        <v>2026-10-13T01:40:02.961Z</v>
       </c>
     </row>
   </sheetData>
